--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -15,7 +15,8 @@
     <sheet name="Tabela 6" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Tabela 7" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Tabela 8" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Sinais e fonte" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Tabela 9" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Sinais e fonte" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,6 +942,638 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Sinais convencionais, conforme a Norma de Apresentacao Tabular do IBGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dado numerico igual a zero, nao resultante de arredondamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>..</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nao se aplica dado numerico</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>dado numerico nao disponivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dado numerico omitido a fim de evitar a individualizacao da informacao</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dado numerico igual a zero resultante de arredondamento de valor menor que a metade da unidade adotada</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 18:22:23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Conferencias desta extracao</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>candidatos_linhas</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20984</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>candidatos_sq_unicos</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>20984</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>complementar_linhas</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>20984</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>complementar_sem_par_no_principal</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>principal_sem_complementar</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cpf_publicado</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>20981</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cpf_nao_publicado</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cpf_com_digito_invalido</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cpf_repetido_entre_candidaturas</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>candidaturas_de_pessoa_com_mais_de_uma</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>receitas_linhas</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>118115</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>receitas_valor_ilegivel</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>receitas_total</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5662847203.74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>candidatos_com_mais_de_um_prestador</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>data_ultima_prestacao</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>receitas_por_grupo</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>{"REC_FEFC": 4640335681.25, "REC_FINANCIAMENTO_COLETIVO": 13368899.5, "REC_FUNDO_PARTIDARIO": 383435440.19, "REC_ORIGEM_NAO_IDENTIFICADA": 760428.53, "REC_OUTROS_CANDIDATOS": 74533044.08, "REC_PARTIDO_OUTROS_RECURSOS": 97804382.98, "REC_PESSOAS_FISICAS": 358196079.53, "REC_PROPRIOS": 94413247.68, "REC_SEM_ORIGEM": 0.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>doadores_distintos</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>52198</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>bens_linhas</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>77155</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>bens_valor_ilegivel</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>bens_chave_repetida_sq_ordem</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>bens_total</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32253496244.68</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>candidatos_com_bem_acima_50mi</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>despesas_contratadas_linhas</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>735740</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>despesas_contratadas_sq_unicos</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>586089</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>despesas_contratadas_total</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3639294391.85</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>despesas_pagas_linhas</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>370817</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>despesas_pagas_total</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2057636895.87</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>pagas_sem_despesa_contratada</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>pagas_sem_contratada_valor</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>despesas_sem_documento_fornecedor</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>48248</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>pago_sem_documento_fornecedor</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>385539.31</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fornecedores_com_mais_de_um_municipio</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>fornecedores_distintos</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>424833</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cnpj_consultados_nesta_rodada</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cnpj_em_cache</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fornecedores_pj</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fornecedores_pj_sem_localizacao</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>43379</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cnpj_rodada_interrompida_por_429</t>
+        </is>
+      </c>
+      <c r="B50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fornecedores_com_documento_invalido</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Fundo Especial de Financiamento de Campanha | CANDIDATOS | pago total</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1779406409.12</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Fundo Especial de Financiamento de Campanha | CANDIDATOS | transferido a outros prestadores</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>43899672.26</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Fundo Partidário | CANDIDATOS | pago total</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>82017230.56999999</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Fundo Partidário | CANDIDATOS | transferido a outros prestadores</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>858310.02</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Fundo Especial de Financiamento de Campanha | PARTIDOS | pago total</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4736070164.83</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Fundo Especial de Financiamento de Campanha | PARTIDOS | transferido a outros prestadores</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>4686383743.4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Fundo Partidário | PARTIDOS | pago total</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>417477887.97</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Fundo Partidário | PARTIDOS | transferido a outros prestadores</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>373913357.68</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>votacao_linhas</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>gerado_em</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:22:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>soma_receitas_candidatos_confere</t>
+        </is>
+      </c>
+      <c r="B62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>pago_por_fornecedor_confere</t>
+        </is>
+      </c>
+      <c r="B63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>receitas_de_sq_fora_do_cadastro</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -16588,12 +17221,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E175"/>
+  <dimension ref="A1:E231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
@@ -17089,7 +17722,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
@@ -17595,7 +18228,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
@@ -18423,7 +19056,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
       <c r="D82" s="6" t="n">
@@ -19205,7 +19838,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
       <c r="D116" s="6" t="n">
@@ -20240,7 +20873,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
@@ -20458,51 +21091,1339 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="7" t="inlineStr">
+      <c r="A171" s="4" t="inlineStr">
         <is>
           <t>Doacao de pessoa fisica, pela UF do candidato</t>
         </is>
       </c>
-      <c r="B171" s="7" t="inlineStr">
+      <c r="B171" s="4" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="C171" s="7" t="inlineStr">
+      <c r="C171" s="4" t="inlineStr">
         <is>
           <t>Amapá</t>
         </is>
       </c>
-      <c r="D171" s="9" t="n">
+      <c r="D171" s="6" t="n">
         <v>1674383.36</v>
       </c>
-      <c r="E171" s="13" t="n">
+      <c r="E171" s="12" t="n">
         <v>0.47</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="10" t="inlineStr">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="n">
+        <v>2628</v>
+      </c>
+      <c r="E172" s="12" t="n">
+        <v>12.52</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="n">
+        <v>2055</v>
+      </c>
+      <c r="E173" s="12" t="n">
+        <v>9.789999999999999</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>Minas Gerais</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="n">
+        <v>1832</v>
+      </c>
+      <c r="E174" s="12" t="n">
+        <v>8.73</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="n">
+        <v>1224</v>
+      </c>
+      <c r="E175" s="12" t="n">
+        <v>5.83</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>Paraná</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="n">
+        <v>1090</v>
+      </c>
+      <c r="E176" s="12" t="n">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="n">
+        <v>1053</v>
+      </c>
+      <c r="E177" s="12" t="n">
+        <v>5.02</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>Pernambuco</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="n">
+        <v>961</v>
+      </c>
+      <c r="E178" s="12" t="n">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="n">
+        <v>905</v>
+      </c>
+      <c r="E179" s="12" t="n">
+        <v>4.31</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>Pará</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="n">
+        <v>741</v>
+      </c>
+      <c r="E180" s="12" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="n">
+        <v>713</v>
+      </c>
+      <c r="E181" s="12" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="E182" s="12" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>Distrito Federal</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="n">
+        <v>668</v>
+      </c>
+      <c r="E183" s="12" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>Maranhão</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="n">
+        <v>619</v>
+      </c>
+      <c r="E184" s="12" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>Espírito Santo</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="n">
+        <v>591</v>
+      </c>
+      <c r="E185" s="12" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="n">
+        <v>475</v>
+      </c>
+      <c r="E186" s="12" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>Mato Grosso</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="n">
+        <v>455</v>
+      </c>
+      <c r="E187" s="12" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>Paraíba</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="E188" s="12" t="n">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>Rondônia</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="n">
+        <v>438</v>
+      </c>
+      <c r="E189" s="12" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>Mato Grosso do Sul</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="n">
+        <v>425</v>
+      </c>
+      <c r="E190" s="12" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>Roraima</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="n">
+        <v>413</v>
+      </c>
+      <c r="E191" s="12" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="n">
+        <v>411</v>
+      </c>
+      <c r="E192" s="12" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>Piauí</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="n">
+        <v>402</v>
+      </c>
+      <c r="E193" s="12" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>Acre</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="n">
+        <v>388</v>
+      </c>
+      <c r="E194" s="12" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>Tocantins</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="n">
+        <v>368</v>
+      </c>
+      <c r="E195" s="12" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>Rio Grande do Norte</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="n">
+        <v>330</v>
+      </c>
+      <c r="E196" s="12" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>Amapá</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="n">
+        <v>322</v>
+      </c>
+      <c r="E197" s="12" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>Alagoas</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="n">
+        <v>299</v>
+      </c>
+      <c r="E198" s="12" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>candidatos</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>Presidenciáveis, circunscrição nacional</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E199" s="12" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>Minas Gerais</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="E200" s="12" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>Maranhão</t>
+        </is>
+      </c>
+      <c r="D201" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="E201" s="12" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>Distrito Federal</t>
+        </is>
+      </c>
+      <c r="D202" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="E202" s="12" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="D203" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="E203" s="12" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="E204" s="12" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>Pernambuco</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E205" s="12" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>Rio Grande do Norte</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E206" s="12" t="n">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E207" s="12" t="n">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E208" s="12" t="n">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E209" s="12" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>Santa Catarina</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E210" s="12" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E211" s="12" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>Pará</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E212" s="12" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>Paraná</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E213" s="12" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>Mato Grosso</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E214" s="12" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>Espírito Santo</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E215" s="12" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>Acre</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E216" s="12" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>Paraíba</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E217" s="12" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>Piauí</t>
+        </is>
+      </c>
+      <c r="D218" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E218" s="12" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="D219" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E219" s="12" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>Roraima</t>
+        </is>
+      </c>
+      <c r="D220" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E220" s="12" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>Mato Grosso do Sul</t>
+        </is>
+      </c>
+      <c r="D221" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E221" s="12" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="D222" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E222" s="12" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>Tocantins</t>
+        </is>
+      </c>
+      <c r="D223" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E223" s="12" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>Amapá</t>
+        </is>
+      </c>
+      <c r="D224" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E224" s="12" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>Rondônia</t>
+        </is>
+      </c>
+      <c r="D225" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E225" s="12" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>Alagoas</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E226" s="12" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B227" s="7" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C227" s="7" t="inlineStr">
+        <is>
+          <t>Presidenciáveis, circunscrição nacional</t>
+        </is>
+      </c>
+      <c r="D227" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="E227" s="13" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="10" t="inlineStr">
         <is>
           <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 18:22:23.</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="10" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="10" t="inlineStr">
         <is>
           <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-19.</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="10" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="10" t="inlineStr">
         <is>
           <t>Nota 1: a serie de fornecedores cobre 45.5% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="10" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="10" t="inlineStr">
         <is>
           <t>Nota 2: a serie por UF do doador cobre apenas 8.3% do valor doado, porque o TSE nao publica a UF do doador pessoa fisica. Para leitura integral use a serie por UF do candidato que recebeu.</t>
         </is>
@@ -26285,628 +28206,1409 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Sinais convencionais, conforme a Norma de Apresentacao Tabular do IBGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>dado numerico igual a zero, nao resultante de arredondamento</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tabela 9 - Eleitorado apto, populacao residente e dinheiro de campanha, por unidade da federacao - Brasil - 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Eleitores e habitantes em numero absoluto, valores em R$ 1,00</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>..</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>nao se aplica dado numerico</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Unidade da federacao</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Habitantes</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Eleitores aptos</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Participacao no eleitorado (%)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Eleitores sobre habitantes (%)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Candidaturas</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Vagas</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Eleitores por vaga</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Candidaturas por 100 mil eleitores</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Receita de campanha</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Receita por habitante</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Receita por eleitor</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Dinheiro publico por eleitor</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>46179008</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>34105332</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>73.84999999999999</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>2628</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>198287</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>810574199.1900001</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>21.18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>21460311</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>16379547</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>76.31999999999999</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1832</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>118692</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>465589840.32</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>28.43</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>23.73</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>17225410</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>12857388</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>74.64</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2055</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>103689</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>452184964.68</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>35.17</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>32.54</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>14889472</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>11321934</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>76.04000000000001</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1224</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>102927</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>313098347.49</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>25.49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>11952456</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8610076</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>72.04000000000001</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1090</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>93588</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>288440062.88</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>28.74</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>11233317</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>8526505</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1053</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>90708</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>287776923.16</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>29.91</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9583176</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>7226975</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>75.41</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>961</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>88134</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>227630341.53</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>28.64</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>9302211</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7000978</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>75.26000000000001</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>713</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>92118</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>210683767.02</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>26.23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>8756324</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>6267107</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>741</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>94956</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>173396708</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>25.02</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>8312759</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>5725998</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>89469</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>186720168.89</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>32.61</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>27.24</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>7024557</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5188115</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>73.86</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>619</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>76296</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>199700334.94</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>28.43</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>35.02</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7495033</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>5081043</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>67.79000000000001</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>905</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>76986</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>196363339.4</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>32.95</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>4182828</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3248007</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>58000</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>134119341.65</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>32.06</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>38.83</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>4150692</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2990582</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>591</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>62304</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>121510720.38</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>40.63</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>34.96</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>4360926</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2802091</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>475</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>70052</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>133207564.44</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>43.41</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>3392617</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>2708756</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>79.84</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>402</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>56432</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>131934587.08</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>42.96</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3463737</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>2660947</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>76.81999999999999</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>330</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>66524</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>96738393.37</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>3950330</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>2639075</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>66.81</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>455</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>65977</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>126651011.45</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>32.06</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>34.95</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>3221128</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>2442275</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>75.81999999999999</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>299</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>55506</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>109643825.13</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>34.04</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>42.15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>3009996</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>2253238</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>668</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>56331</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>29.65</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>138731909.46</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>61.57</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>51.94</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2946317</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>2025001</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>68.73</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>50625</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>104015513.56</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>51.37</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>45.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>2307255</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>1740240</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>75.42</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>411</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>43506</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>110998484.05</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>48.11</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>60.44</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1757338</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>1268667</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>72.19</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>438</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>31717</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>121344202.8</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>83.78</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1595994</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>1182768</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>74.11</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>368</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>29569</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>107313260.82</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>67.23999999999999</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>90.73</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>79.27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>887794</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>614631</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>388</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>15366</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>63.13</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>92017991.75</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>149.71</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>139.69</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>809953</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>577698</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>71.31999999999999</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>322</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>14442</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>55.74</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>102028469.09</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>125.97</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>176.61</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>170.82</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>761012</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>401573</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>52.77</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>413</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>10039</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>99728125.06</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>131.05</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>248.34</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>239.15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Presidenciaveis (nacional)</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>dado numerico nao disponivel</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>dado numerico omitido a fim de evitar a individualizacao da informacao</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>dado numerico igual a zero resultante de arredondamento de valor menor que a metade da unidade adotada</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 18:22:23.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>120704806.15</v>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>214211951</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>157846547</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>73.69</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>20984</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>1790</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>88182</v>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>5662847203.74</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>26.44</v>
+      </c>
+      <c r="L33" s="9" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>31.83</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Fonte: TSE, perfil do eleitorado, arquivo ATUAL, geracao declarada pela fonte em 01/09/2026; IBGE, estimativa da populacao residente, agregado 6579, referencia 2026; TSE, prestacao de contas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-19.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Conferencias desta extracao</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>candidatos_linhas</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>20984</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>candidatos_sq_unicos</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>20984</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>complementar_linhas</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>20984</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>complementar_sem_par_no_principal</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>principal_sem_complementar</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cpf_publicado</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>20981</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cpf_nao_publicado</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cpf_com_digito_invalido</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cpf_repetido_entre_candidaturas</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>candidaturas_de_pessoa_com_mais_de_uma</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>receitas_linhas</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>118115</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>receitas_valor_ilegivel</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>receitas_total</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>5662847203.74</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>candidatos_com_mais_de_um_prestador</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>data_ultima_prestacao</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>receitas_por_grupo</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{"REC_FEFC": 4640335681.25, "REC_FINANCIAMENTO_COLETIVO": 13368899.5, "REC_FUNDO_PARTIDARIO": 383435440.19, "REC_ORIGEM_NAO_IDENTIFICADA": 760428.53, "REC_OUTROS_CANDIDATOS": 74533044.08, "REC_PARTIDO_OUTROS_RECURSOS": 97804382.98, "REC_PESSOAS_FISICAS": 358196079.53, "REC_PROPRIOS": 94413247.68, "REC_SEM_ORIGEM": 0.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>doadores_distintos</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>52198</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>bens_linhas</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>77155</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>bens_valor_ilegivel</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>bens_chave_repetida_sq_ordem</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>bens_total</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>32253496244.68</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>candidatos_com_bem_acima_50mi</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>despesas_contratadas_linhas</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>735740</v>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>despesas_contratadas_sq_unicos</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>586089</v>
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Nota 1: a linha 'Presidenciaveis (nacional)' e' a circunscricao nacional, onde correm presidente e vice. Ela nao tem populacao nem eleitorado proprios, e por isso os denominadores aparecem vazios.</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>despesas_contratadas_total</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>3639294391.85</v>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Nota 2: o eleitorado no exterior, de 918.911 eleitores, nao pertence a unidade da federacao alguma e fica fora do rateio por estado.</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>despesas_pagas_linhas</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>370817</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>despesas_pagas_total</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>2057636895.87</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>pagas_sem_despesa_contratada</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>pagas_sem_contratada_valor</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>despesas_sem_documento_fornecedor</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>48248</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>pago_sem_documento_fornecedor</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>385539.31</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>fornecedores_com_mais_de_um_municipio</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>fornecedores_distintos</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>424833</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>cnpj_consultados_nesta_rodada</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>cnpj_em_cache</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>2085</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>fornecedores_pj</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>46192</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fornecedores_pj_sem_localizacao</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>43379</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>cnpj_rodada_interrompida_por_429</t>
-        </is>
-      </c>
-      <c r="B50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>fornecedores_com_documento_invalido</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Fundo Especial de Financiamento de Campanha | CANDIDATOS | pago total</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1779406409.12</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Fundo Especial de Financiamento de Campanha | CANDIDATOS | transferido a outros prestadores</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>43899672.26</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Fundo Partidário | CANDIDATOS | pago total</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>82017230.56999999</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Fundo Partidário | CANDIDATOS | transferido a outros prestadores</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>858310.02</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Fundo Especial de Financiamento de Campanha | PARTIDOS | pago total</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>4736070164.83</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Fundo Especial de Financiamento de Campanha | PARTIDOS | transferido a outros prestadores</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>4686383743.4</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Fundo Partidário | PARTIDOS | pago total</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>417477887.97</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Fundo Partidário | PARTIDOS | transferido a outros prestadores</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>373913357.68</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>votacao_linhas</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>gerado_em</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-09-19 18:22:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>soma_receitas_candidatos_confere</t>
-        </is>
-      </c>
-      <c r="B62" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>pago_por_fornecedor_confere</t>
-        </is>
-      </c>
-      <c r="B63" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>receitas_de_sq_fora_do_cadastro</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0</v>
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Nota 3: habitante nao vota. A proporcao entre eleitorado e populacao varia entre os estados, e por isso as duas colunas aparecem lado a lado em vez de uma so'.</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 18:22:23.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 21:18:00.</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 18:22:23.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 21:18:00.</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2085</v>
+        <v>4085</v>
       </c>
     </row>
     <row r="48">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>43379</v>
+        <v>41437</v>
       </c>
     </row>
     <row r="50">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-19 18:22:23</t>
+          <t>2026-09-19 21:18:00</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,31 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>colunas_da_ordem_do_usuario_ausentes</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>colunas_novas_fora_da_ordem_do_usuario</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8818,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 18:22:23.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 21:18:00.</t>
         </is>
       </c>
     </row>
@@ -15471,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 18:22:23.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 21:18:00.</t>
         </is>
       </c>
     </row>
@@ -17182,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 18:22:23.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 21:18:00.</t>
         </is>
       </c>
     </row>
@@ -19221,10 +19245,10 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>462595184.59</v>
+        <v>498139778.39</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>27.91</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="90">
@@ -19244,10 +19268,10 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>101552567.11</v>
+        <v>123277093.61</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>6.13</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="91">
@@ -19258,19 +19282,19 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Distrito Federal</t>
+          <t>Minas Gerais</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>97450940.03</v>
+        <v>115875593.82</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>5.88</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="92">
@@ -19281,19 +19305,19 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Minas Gerais</t>
+          <t>Distrito Federal</t>
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>95952384.93000001</v>
+        <v>109143285.14</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>5.79</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="93">
@@ -19313,10 +19337,10 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>75382314.42</v>
+        <v>90224348.83</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>4.55</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="94">
@@ -19327,19 +19351,19 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Paraná</t>
+          <t>Rio Grande do Sul</t>
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>59023776.93</v>
+        <v>72603182.98</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="95">
@@ -19350,19 +19374,19 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Sul</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>58653681.05</v>
+        <v>71953659.25</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="96">
@@ -19373,19 +19397,19 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Paraná</t>
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>56216311.01</v>
+        <v>70164634.72</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>3.39</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="97">
@@ -19405,10 +19429,10 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>55912430.48</v>
+        <v>68388277.31999999</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="98">
@@ -19428,10 +19452,10 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>54990895.48</v>
+        <v>68299073.65000001</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="99">
@@ -19451,10 +19475,10 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>54194985.89</v>
+        <v>65686053.35</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="100">
@@ -19465,19 +19489,19 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Norte</t>
+          <t>Santa Catarina</t>
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>47402453.19</v>
+        <v>56664663.25</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="101">
@@ -19488,19 +19512,19 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Santa Catarina</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>46648452.04</v>
+        <v>54766020.66</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="102">
@@ -19511,19 +19535,19 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Paraíba</t>
+          <t>Rio Grande do Norte</t>
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>45565472.58</v>
+        <v>54024536.17</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="103">
@@ -19543,10 +19567,10 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>37022743.63</v>
+        <v>45655169.75</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="104">
@@ -19557,19 +19581,19 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso</t>
+          <t>Pará</t>
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>32159075.09</v>
+        <v>42981889.7</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="105">
@@ -19580,19 +19604,19 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Amapá</t>
+          <t>Mato Grosso</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>31737257.25</v>
+        <v>40022422.59</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="106">
@@ -19603,19 +19627,19 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Alagoas</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>31321100.44</v>
+        <v>39931257.77</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="107">
@@ -19626,19 +19650,19 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Pará</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>30666950.44</v>
+        <v>38670285.43</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="108">
@@ -19649,19 +19673,19 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Alagoas</t>
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>29400082.53</v>
+        <v>34815776.47</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="109">
@@ -19672,19 +19696,19 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>27283929.47</v>
+        <v>34294871.11</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="110">
@@ -19695,19 +19719,19 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>27266283.34</v>
+        <v>33415958.86</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="111">
@@ -19727,10 +19751,10 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>25217946.81</v>
+        <v>30479668.63</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="112">
@@ -19750,10 +19774,10 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>24468624.21</v>
+        <v>29653706.56</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="113">
@@ -19773,10 +19797,10 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>21320236.66</v>
+        <v>26463959.67</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="114">
@@ -19796,10 +19820,10 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>15198576.14</v>
+        <v>19996902.86</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="115">
@@ -19819,10 +19843,10 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>11475857.08</v>
+        <v>16559874.57</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="116">
@@ -19845,7 +19869,7 @@
         <v>1095000</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="117">
@@ -22404,7 +22428,7 @@
     <row r="228">
       <c r="A228" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 18:22:23.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 21:18:00.</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22442,7 @@
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: a serie de fornecedores cobre 45.5% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
+          <t>Nota 1: a serie de fornecedores cobre 53.7% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
         </is>
       </c>
     </row>
@@ -23730,7 +23754,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 18:22:23.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 21:18:00.</t>
         </is>
       </c>
     </row>
@@ -25257,7 +25281,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 18:22:23.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 21:18:00.</t>
         </is>
       </c>
     </row>
@@ -28160,7 +28184,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 18:22:23.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-19 21:18:00.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 08:48:12.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 08:48:12.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
         </is>
       </c>
     </row>
@@ -1380,179 +1380,179 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cnpj_consultados_nesta_rodada</t>
+          <t>cnpj_falhas_transporte</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2000</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cnpj_em_cache</t>
+          <t>cnpj_consultados_nesta_rodada</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10298</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>fornecedores_pj</t>
+          <t>cnpj_em_cache</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>46377</v>
+        <v>14299</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>fornecedores_pj_sem_localizacao</t>
+          <t>fornecedores_pj</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>35641</v>
+        <v>46377</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cnpj_rodada_interrompida_por_429</t>
-        </is>
-      </c>
-      <c r="B50" t="b">
-        <v>0</v>
+          <t>fornecedores_pj_sem_localizacao</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>31804</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fornecedores_com_documento_invalido</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1010</v>
+          <t>cnpj_rodada_interrompida_por_429</t>
+        </is>
+      </c>
+      <c r="B51" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Fundo Especial de Financiamento de Campanha | CANDIDATOS | pago total</t>
+          <t>fornecedores_com_documento_invalido</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1799419147.56</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Fundo Especial de Financiamento de Campanha | CANDIDATOS | transferido a outros prestadores</t>
+          <t>Fundo Especial de Financiamento de Campanha | CANDIDATOS | pago total</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>43990672.26</v>
+        <v>1799419147.56</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Fundo Partidário | CANDIDATOS | pago total</t>
+          <t>Fundo Especial de Financiamento de Campanha | CANDIDATOS | transferido a outros prestadores</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>82356216.09</v>
+        <v>43990672.26</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Fundo Partidário | CANDIDATOS | transferido a outros prestadores</t>
+          <t>Fundo Partidário | CANDIDATOS | pago total</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>858310.02</v>
+        <v>82356216.09</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Fundo Especial de Financiamento de Campanha | PARTIDOS | pago total</t>
+          <t>Fundo Partidário | CANDIDATOS | transferido a outros prestadores</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4736266491.33</v>
+        <v>858310.02</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Fundo Especial de Financiamento de Campanha | PARTIDOS | transferido a outros prestadores</t>
+          <t>Fundo Especial de Financiamento de Campanha | PARTIDOS | pago total</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4686473156.8</v>
+        <v>4729329167.93</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Fundo Partidário | PARTIDOS | pago total</t>
+          <t>Fundo Especial de Financiamento de Campanha | PARTIDOS | transferido a outros prestadores</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>464413493.97</v>
+        <v>4679535836.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Fundo Partidário | PARTIDOS | transferido a outros prestadores</t>
+          <t>Fundo Partidário | PARTIDOS | pago total</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>420753357.68</v>
+        <v>465311994.44</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>votacao_linhas</t>
+          <t>Fundo Partidário | PARTIDOS | transferido a outros prestadores</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>421649296.46</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>gerado_em</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-09-21 08:48:12</t>
-        </is>
+          <t>votacao_linhas</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>soma_receitas_candidatos_confere</t>
-        </is>
-      </c>
-      <c r="B62" t="b">
-        <v>1</v>
+          <t>gerado_em</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:26:41</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>pago_por_fornecedor_confere</t>
+          <t>soma_receitas_candidatos_confere</t>
         </is>
       </c>
       <c r="B63" t="b">
@@ -1562,32 +1562,42 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>receitas_de_sq_fora_do_cadastro</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0</v>
+          <t>pago_por_fornecedor_confere</t>
+        </is>
+      </c>
+      <c r="B64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>colunas_da_ordem_do_usuario_ausentes</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+          <t>receitas_de_sq_fora_do_cadastro</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>colunas_da_ordem_do_usuario_ausentes</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>colunas_novas_fora_da_ordem_do_usuario</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -2053,7 +2063,7 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>575680870.9499999</v>
+        <v>575680870.95</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1.77</v>
@@ -4751,7 +4761,7 @@
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>75659161.20999999</v>
+        <v>75659161.21000001</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0.23</v>
@@ -8842,7 +8852,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 08:48:12.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15505,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 08:48:12.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17216,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 08:48:12.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
         </is>
       </c>
     </row>
@@ -19245,10 +19255,10 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>548030399.4299999</v>
+        <v>559559597.25</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>23.88</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="90">
@@ -19268,10 +19278,10 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>147327590.89</v>
+        <v>152989718.15</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>6.42</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="91">
@@ -19291,10 +19301,10 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>138476052.55</v>
+        <v>145030505.46</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>6.03</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="92">
@@ -19314,10 +19324,10 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>120563042.07</v>
+        <v>123005077.01</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>5.25</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="93">
@@ -19337,10 +19347,10 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>106991152.11</v>
+        <v>112131463.12</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="94">
@@ -19360,10 +19370,10 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>89617990.20999999</v>
+        <v>94706370.86</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>3.9</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="95">
@@ -19383,10 +19393,10 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>87354522.77</v>
+        <v>92584538.93000001</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>3.81</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="96">
@@ -19406,10 +19416,10 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>86664426.72</v>
+        <v>91139252.15000001</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="97">
@@ -19429,7 +19439,7 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>84152351.08</v>
+        <v>87496556.56</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>3.67</v>
@@ -19452,10 +19462,10 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>78864313.90000001</v>
+        <v>82730067.38</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="99">
@@ -19475,10 +19485,10 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>78688487.86</v>
+        <v>81149175.73999999</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="100">
@@ -19498,10 +19508,10 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>69290664.54000001</v>
+        <v>72754664.08</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="101">
@@ -19521,10 +19531,10 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>66219472.98</v>
+        <v>69200572.7</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="102">
@@ -19544,7 +19554,7 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>63313977.39</v>
+        <v>65843638.06</v>
       </c>
       <c r="E102" s="12" t="n">
         <v>2.76</v>
@@ -19567,10 +19577,10 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>57355532.64</v>
+        <v>60458233.91</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="104">
@@ -19590,10 +19600,10 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>53895517.75</v>
+        <v>57231270.25</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="105">
@@ -19613,10 +19623,10 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>49623915.24</v>
+        <v>52540469.58</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="106">
@@ -19636,10 +19646,10 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>49091220.97</v>
+        <v>51863893.1</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="107">
@@ -19659,10 +19669,10 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>43006662.3</v>
+        <v>44057845.64</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="108">
@@ -19682,10 +19692,10 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>41014541.7</v>
+        <v>43313092.33</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="109">
@@ -19705,10 +19715,10 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>40507735.88</v>
+        <v>41920605.82</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="110">
@@ -19728,7 +19738,7 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>40323471.8</v>
+        <v>41916749.8</v>
       </c>
       <c r="E110" s="12" t="n">
         <v>1.76</v>
@@ -19751,7 +19761,7 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>37025135.63</v>
+        <v>38501477.17</v>
       </c>
       <c r="E111" s="12" t="n">
         <v>1.61</v>
@@ -19774,10 +19784,10 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>36640243.55</v>
+        <v>38411616.53</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="113">
@@ -19797,10 +19807,10 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>33186972.51</v>
+        <v>34320412.13</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="114">
@@ -19820,10 +19830,10 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>23415004.22</v>
+        <v>25153987.36</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="115">
@@ -19843,10 +19853,10 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>23273327.69</v>
+        <v>23943473.94</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -22428,7 +22438,7 @@
     <row r="228">
       <c r="A228" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 08:48:12.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22452,7 @@
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: a serie de fornecedores cobre 62.8% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
+          <t>Nota 1: a serie de fornecedores cobre 65.3% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
         </is>
       </c>
     </row>
@@ -22620,10 +22630,10 @@
         <v>4405616.89</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>13393511.95</v>
+        <v>13394786.95</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>14740734.54</v>
+        <v>14742009.54</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>11.78</v>
@@ -22930,10 +22940,10 @@
         <v>145297.42</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1209956.13</v>
+        <v>1210842.82</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2459605.62</v>
+        <v>2460492.31</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>1.97</v>
@@ -23209,10 +23219,10 @@
         <v>19500</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>29110.94</v>
+        <v>29510.94</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>252560.9</v>
+        <v>252960.9</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>0.2</v>
@@ -23547,7 +23557,7 @@
         <v>10906.01</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>86753.31</v>
+        <v>86749.91</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>7321.34</v>
@@ -23559,7 +23569,7 @@
         <v>0.01</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>317908.35</v>
+        <v>317904.95</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0.02</v>
@@ -23754,7 +23764,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 08:48:12.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25291,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 08:48:12.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
         </is>
       </c>
     </row>
@@ -28184,7 +28194,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 08:48:12.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -671,7 +671,7 @@
         <v>53.81</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>12371172120.18</v>
+        <v>12372157364.57</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>38.14</v>
@@ -702,7 +702,7 @@
         <v>37.17</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>8707872900.040001</v>
+        <v>8706972900.040001</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>26.84</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32439034482.1</v>
+        <v>32439119726.49</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 21:19:15.</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 21:19:15.</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32439034482.1</v>
+        <v>32439119726.49</v>
       </c>
     </row>
     <row r="34">
@@ -1380,179 +1380,179 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cnpj_falhas_transporte</t>
+          <t>cnpj_consultados_nesta_rodada</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cnpj_consultados_nesta_rodada</t>
+          <t>cnpj_em_cache</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2000</v>
+        <v>17297</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cnpj_em_cache</t>
+          <t>fornecedores_pj</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>14299</v>
+        <v>46377</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>fornecedores_pj</t>
+          <t>fornecedores_pj_sem_localizacao</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>46377</v>
+        <v>28851</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fornecedores_pj_sem_localizacao</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>31804</v>
+          <t>cnpj_rodada_interrompida_por_429</t>
+        </is>
+      </c>
+      <c r="B50" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>cnpj_rodada_interrompida_por_429</t>
-        </is>
-      </c>
-      <c r="B51" t="b">
-        <v>0</v>
+          <t>fornecedores_com_documento_invalido</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1010</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>fornecedores_com_documento_invalido</t>
+          <t>Fundo Especial de Financiamento de Campanha | CANDIDATOS | pago total</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1010</v>
+        <v>1799419147.56</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Fundo Especial de Financiamento de Campanha | CANDIDATOS | pago total</t>
+          <t>Fundo Especial de Financiamento de Campanha | CANDIDATOS | transferido a outros prestadores</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1799419147.56</v>
+        <v>43990672.26</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Fundo Especial de Financiamento de Campanha | CANDIDATOS | transferido a outros prestadores</t>
+          <t>Fundo Partidário | CANDIDATOS | pago total</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>43990672.26</v>
+        <v>82356216.09</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Fundo Partidário | CANDIDATOS | pago total</t>
+          <t>Fundo Partidário | CANDIDATOS | transferido a outros prestadores</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>82356216.09</v>
+        <v>858310.02</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Fundo Partidário | CANDIDATOS | transferido a outros prestadores</t>
+          <t>Fundo Especial de Financiamento de Campanha | PARTIDOS | pago total</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>858310.02</v>
+        <v>4729329167.93</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Fundo Especial de Financiamento de Campanha | PARTIDOS | pago total</t>
+          <t>Fundo Especial de Financiamento de Campanha | PARTIDOS | transferido a outros prestadores</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4729329167.93</v>
+        <v>4679535836.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Fundo Especial de Financiamento de Campanha | PARTIDOS | transferido a outros prestadores</t>
+          <t>Fundo Partidário | PARTIDOS | pago total</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4679535836.8</v>
+        <v>465311994.44</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Fundo Partidário | PARTIDOS | pago total</t>
+          <t>Fundo Partidário | PARTIDOS | transferido a outros prestadores</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>465311994.44</v>
+        <v>421649296.46</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Fundo Partidário | PARTIDOS | transferido a outros prestadores</t>
+          <t>votacao_linhas</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>421649296.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>votacao_linhas</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0</v>
+          <t>gerado_em</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:19:15</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>gerado_em</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-09-21 15:26:41</t>
-        </is>
+          <t>soma_receitas_candidatos_confere</t>
+        </is>
+      </c>
+      <c r="B62" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>soma_receitas_candidatos_confere</t>
+          <t>pago_por_fornecedor_confere</t>
         </is>
       </c>
       <c r="B63" t="b">
@@ -1562,42 +1562,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>pago_por_fornecedor_confere</t>
-        </is>
-      </c>
-      <c r="B64" t="b">
-        <v>1</v>
+          <t>receitas_de_sq_fora_do_cadastro</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>receitas_de_sq_fora_do_cadastro</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>0</v>
+          <t>colunas_da_ordem_do_usuario_ausentes</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>colunas_da_ordem_do_usuario_ausentes</t>
+          <t>colunas_novas_fora_da_ordem_do_usuario</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>colunas_novas_fora_da_ordem_do_usuario</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -2063,7 +2053,7 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>575680870.95</v>
+        <v>575680870.9499999</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1.77</v>
@@ -8852,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 21:19:15.</t>
         </is>
       </c>
     </row>
@@ -15505,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 21:19:15.</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 21:19:15.</t>
         </is>
       </c>
     </row>
@@ -19255,10 +19245,10 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>559559597.25</v>
+        <v>566657118.96</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>23.46</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="90">
@@ -19278,10 +19268,10 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>152989718.15</v>
+        <v>155238081.43</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>6.41</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="91">
@@ -19301,10 +19291,10 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>145030505.46</v>
+        <v>148266487.92</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>6.08</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="92">
@@ -19324,10 +19314,10 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>123005077.01</v>
+        <v>124145548.38</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>5.16</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="93">
@@ -19347,10 +19337,10 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>112131463.12</v>
+        <v>114685296.02</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>4.7</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="94">
@@ -19370,10 +19360,10 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>94706370.86</v>
+        <v>97816359.68000001</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="95">
@@ -19393,10 +19383,10 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>92584538.93000001</v>
+        <v>94764516.70999999</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="96">
@@ -19416,10 +19406,10 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>91139252.15000001</v>
+        <v>93129252.87</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="97">
@@ -19439,10 +19429,10 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>87496556.56</v>
+        <v>88938226.75</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="98">
@@ -19462,10 +19452,10 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>82730067.38</v>
+        <v>84507017.28</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="99">
@@ -19485,10 +19475,10 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>81149175.73999999</v>
+        <v>81900135.95999999</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="100">
@@ -19508,10 +19498,10 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>72754664.08</v>
+        <v>74744454.3</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="101">
@@ -19531,7 +19521,7 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>69200572.7</v>
+        <v>70355357.59</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>2.9</v>
@@ -19554,7 +19544,7 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>65843638.06</v>
+        <v>67100547.61</v>
       </c>
       <c r="E102" s="12" t="n">
         <v>2.76</v>
@@ -19577,10 +19567,10 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>60458233.91</v>
+        <v>61936138.99</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="104">
@@ -19600,10 +19590,10 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>57231270.25</v>
+        <v>58939356.4</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="105">
@@ -19623,10 +19613,10 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>52540469.58</v>
+        <v>53777645.42</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="106">
@@ -19646,10 +19636,10 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>51863893.1</v>
+        <v>53089363.21</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="107">
@@ -19660,19 +19650,19 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Amapá</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>44057845.64</v>
+        <v>44426828.53</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="108">
@@ -19683,16 +19673,16 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>43313092.33</v>
+        <v>44308814.37</v>
       </c>
       <c r="E108" s="12" t="n">
         <v>1.82</v>
@@ -19706,16 +19696,16 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Alagoas</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>41920605.82</v>
+        <v>42863716.15</v>
       </c>
       <c r="E109" s="12" t="n">
         <v>1.76</v>
@@ -19729,19 +19719,19 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Alagoas</t>
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>41916749.8</v>
+        <v>42471422.45</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="111">
@@ -19752,16 +19742,16 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>38501477.17</v>
+        <v>39178507.76</v>
       </c>
       <c r="E111" s="12" t="n">
         <v>1.61</v>
@@ -19775,16 +19765,16 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>38411616.53</v>
+        <v>39134639.44</v>
       </c>
       <c r="E112" s="12" t="n">
         <v>1.61</v>
@@ -19807,7 +19797,7 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>34320412.13</v>
+        <v>34914355.11</v>
       </c>
       <c r="E113" s="12" t="n">
         <v>1.44</v>
@@ -19830,10 +19820,10 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>25153987.36</v>
+        <v>25972008.08</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="115">
@@ -19853,7 +19843,7 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>23943473.94</v>
+        <v>24286229.65</v>
       </c>
       <c r="E115" s="12" t="n">
         <v>1</v>
@@ -22438,7 +22428,7 @@
     <row r="228">
       <c r="A228" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 21:19:15.</t>
         </is>
       </c>
     </row>
@@ -22452,7 +22442,7 @@
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: a serie de fornecedores cobre 65.3% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
+          <t>Nota 1: a serie de fornecedores cobre 66.5% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
         </is>
       </c>
     </row>
@@ -23764,7 +23754,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 21:19:15.</t>
         </is>
       </c>
     </row>
@@ -23921,7 +23911,7 @@
         <v>7.85</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4898708042.51</v>
+        <v>4897808042.51</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1027468247.63</v>
@@ -24013,7 +24003,7 @@
         <v>4.03</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1816726464.43</v>
+        <v>1817691708.82</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>571969347.25</v>
@@ -24105,7 +24095,7 @@
         <v>6.24</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2484173186.63</v>
+        <v>2484193186.63</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>494951834.63</v>
@@ -25291,7 +25281,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 21:19:15.</t>
         </is>
       </c>
     </row>
@@ -28194,7 +28184,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 15:26:41.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-21 21:19:15.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -581,7 +581,7 @@
         <v>4488861531.07</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>13.84</v>
+        <v>13.85</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>0</v>
@@ -640,7 +640,7 @@
         <v>2.06</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>337096041.14</v>
+        <v>337146041.14</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1.04</v>
@@ -671,10 +671,10 @@
         <v>53.81</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>12372157364.57</v>
+        <v>12354475064.57</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>38.14</v>
+        <v>38.11</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>1493416713.82</v>
@@ -702,10 +702,10 @@
         <v>37.17</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>8706972900.040001</v>
+        <v>8706826204.209999</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>26.84</v>
+        <v>26.86</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>3105368925.3</v>
@@ -767,7 +767,7 @@
         <v>1185110246.56</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>136347659.97</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32439119726.49</v>
+        <v>32421340730.66</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 09:19:31.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 09:19:31.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>77233</v>
+        <v>77234</v>
       </c>
     </row>
     <row r="31">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32439119726.49</v>
+        <v>32421340730.66</v>
       </c>
     </row>
     <row r="34">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>20299</v>
+        <v>23299</v>
       </c>
     </row>
     <row r="48">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26445</v>
+        <v>23468</v>
       </c>
     </row>
     <row r="50">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-22 09:19:31</t>
+          <t>2026-09-22 21:18:32</t>
         </is>
       </c>
     </row>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>575680870.9499999</v>
+        <v>575680870.95</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>22</v>
@@ -2198,7 +2198,7 @@
         <v>501085000</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>9</v>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="G48" s="6" t="n">
-        <v>75658784.06999999</v>
+        <v>75658784.07000001</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>0.23</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="G59" s="6" t="n">
-        <v>62944315.4</v>
+        <v>62944315.40000001</v>
       </c>
       <c r="H59" s="6" t="n">
         <v>0.19</v>
@@ -6600,7 +6600,7 @@
         <v>50280000</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I73" s="5" t="n">
         <v>3</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 09:19:31.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 09:19:31.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 09:19:31.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
         </is>
       </c>
     </row>
@@ -19245,10 +19245,10 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>582788070</v>
+        <v>586202407.04</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>23.44</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="90">
@@ -19268,10 +19268,10 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>162784561.86</v>
+        <v>163692040.49</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>6.55</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="91">
@@ -19291,10 +19291,10 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>152036260.51</v>
+        <v>154081573.55</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>6.11</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="92">
@@ -19314,10 +19314,10 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>125774783.9</v>
+        <v>126366850.9</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>5.06</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="93">
@@ -19337,10 +19337,10 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>117366024.97</v>
+        <v>118592461.52</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>4.72</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="94">
@@ -19360,10 +19360,10 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>101050867.01</v>
+        <v>102684036.47</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="95">
@@ -19383,10 +19383,10 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>97403249.45</v>
+        <v>98840685.39</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="96">
@@ -19406,10 +19406,10 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>94817568.09</v>
+        <v>95775751.31</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="97">
@@ -19429,10 +19429,10 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>90192566.48</v>
+        <v>90621945.61</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="98">
@@ -19452,7 +19452,7 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>86280095.59999999</v>
+        <v>87084855.31</v>
       </c>
       <c r="E98" s="12" t="n">
         <v>3.47</v>
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>82832872.51000001</v>
+        <v>83163697.64</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="100">
@@ -19498,10 +19498,10 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>76123580.68000001</v>
+        <v>77256447.73999999</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="101">
@@ -19521,7 +19521,7 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>71432907.81</v>
+        <v>72005073.73999999</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>2.87</v>
@@ -19544,10 +19544,10 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>68117774.27</v>
+        <v>68565335.68000001</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="103">
@@ -19567,10 +19567,10 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>63997669.94</v>
+        <v>64810137.51</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="104">
@@ -19590,7 +19590,7 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>61229903.01</v>
+        <v>61774777.62</v>
       </c>
       <c r="E104" s="12" t="n">
         <v>2.46</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>54434748.16</v>
+        <v>54880461.09</v>
       </c>
       <c r="E105" s="12" t="n">
         <v>2.19</v>
@@ -19636,10 +19636,10 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>54320821.45</v>
+        <v>54848648.93</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="107">
@@ -19659,7 +19659,7 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>44915318.26</v>
+        <v>45507143.42</v>
       </c>
       <c r="E107" s="12" t="n">
         <v>1.81</v>
@@ -19682,10 +19682,10 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>44333337.7</v>
+        <v>44490631.2</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="109">
@@ -19705,7 +19705,7 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>43429045.49</v>
+        <v>43822645.81</v>
       </c>
       <c r="E109" s="12" t="n">
         <v>1.75</v>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>43221283.06</v>
+        <v>43511705.34</v>
       </c>
       <c r="E110" s="12" t="n">
         <v>1.74</v>
@@ -19751,7 +19751,7 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>40215693.2</v>
+        <v>40626110.42</v>
       </c>
       <c r="E111" s="12" t="n">
         <v>1.62</v>
@@ -19774,7 +19774,7 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>40024464.31</v>
+        <v>40317383.31</v>
       </c>
       <c r="E112" s="12" t="n">
         <v>1.61</v>
@@ -19797,10 +19797,10 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>35209006.6</v>
+        <v>35355535.04</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="114">
@@ -19820,10 +19820,10 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>26435662.75</v>
+        <v>26822083.87</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="115">
@@ -19843,7 +19843,7 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>24771808.17</v>
+        <v>24957278.21</v>
       </c>
       <c r="E115" s="12" t="n">
         <v>1</v>
@@ -22428,7 +22428,7 @@
     <row r="228">
       <c r="A228" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 09:19:31.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22442,7 @@
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: a serie de fornecedores cobre 67.3% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
+          <t>Nota 1: a serie de fornecedores cobre 67.9% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
         </is>
       </c>
     </row>
@@ -23754,7 +23754,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 09:19:31.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
         </is>
       </c>
     </row>
@@ -23802,7 +23802,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -23957,7 +23957,7 @@
         <v>5.26</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>788901122.24</v>
+        <v>771218822.24</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>610172112.4</v>
@@ -24325,7 +24325,7 @@
         <v>4.6</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>930897493.99</v>
+        <v>930727493.99</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>186158214.82</v>
@@ -24877,7 +24877,7 @@
         <v>2.61</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>183981649.68</v>
+        <v>184054953.85</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>8219868.98</v>
@@ -25281,7 +25281,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 09:19:31.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
         </is>
       </c>
     </row>
@@ -28184,7 +28184,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 09:19:31.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -646,16 +646,16 @@
         <v>1.04</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>36587640.1</v>
+        <v>37592200.23</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>23265939.71</v>
+        <v>23723234.65</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="8">
@@ -677,13 +677,13 @@
         <v>38.11</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1493416713.82</v>
+        <v>1507459676.46</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>25.91</v>
+        <v>25.97</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>938083924.87</v>
+        <v>944725941.59</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>25.39</v>
@@ -708,16 +708,16 @@
         <v>26.86</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3105368925.3</v>
+        <v>3124543875.63</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>53.88</v>
+        <v>53.82</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>1863882061.76</v>
+        <v>1879320642.27</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>50.46</v>
+        <v>50.52</v>
       </c>
     </row>
     <row r="10">
@@ -739,16 +739,16 @@
         <v>3.97</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>523232851.08</v>
+        <v>526733584.75</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>400932070.18</v>
+        <v>402863951.17</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>10.85</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="11">
@@ -770,16 +770,16 @@
         <v>3.66</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>136347659.97</v>
+        <v>137949190.58</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>155658008.36</v>
+        <v>156027524.59</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="12">
@@ -801,16 +801,16 @@
         <v>6.41</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>468202507.57</v>
+        <v>471242649.77</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>8.119999999999999</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>312161556.5</v>
+        <v>313626229.93</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>8.449999999999999</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="13">
@@ -894,13 +894,13 @@
         <v>100</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>5763156297.84</v>
+        <v>5805521177.42</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>3693983561.38</v>
+        <v>3720287524.2</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>100</v>
@@ -909,14 +909,14 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-22.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-23.</t>
         </is>
       </c>
     </row>
@@ -1025,14 +1025,14 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-22.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-23.</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>122746</v>
+        <v>125149</v>
       </c>
     </row>
     <row r="24">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5763156297.84</v>
+        <v>5805521177.42</v>
       </c>
     </row>
     <row r="26">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{"REC_FEFC": 4678006236.25, "REC_FINANCIAMENTO_COLETIVO": 13837356.29, "REC_FUNDO_PARTIDARIO": 404076593.86, "REC_ORIGEM_NAO_IDENTIFICADA": 1118440.94, "REC_OUTROS_CANDIDATOS": 78998598.33, "REC_PARTIDO_OUTROS_RECURSOS": 109762052.51, "REC_PESSOAS_FISICAS": 379471098.64, "REC_PROPRIOS": 97885921.02, "REC_SEM_ORIGEM": 0.0}</t>
+          <t>{"REC_FEFC": 4684717431.24, "REC_FINANCIAMENTO_COLETIVO": 14180774.85, "REC_FUNDO_PARTIDARIO": 418392968.05, "REC_ORIGEM_NAO_IDENTIFICADA": 1278440.94, "REC_OUTROS_CANDIDATOS": 81504569.54, "REC_PARTIDO_OUTROS_RECURSOS": 112021527.66, "REC_PESSOAS_FISICAS": 393014916.26, "REC_PROPRIOS": 100410548.88, "REC_SEM_ORIGEM": 0.0}</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>54519</v>
+        <v>55771</v>
       </c>
     </row>
     <row r="30">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>751148</v>
+        <v>758447</v>
       </c>
     </row>
     <row r="36">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>598038</v>
+        <v>603460</v>
       </c>
     </row>
     <row r="37">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3693983561.38</v>
+        <v>3720287524.2</v>
       </c>
     </row>
     <row r="38">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>390175</v>
+        <v>399794</v>
       </c>
     </row>
     <row r="39">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2133846341.53</v>
+        <v>2174251811.83</v>
       </c>
     </row>
     <row r="40">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>49561</v>
+        <v>50234</v>
       </c>
     </row>
     <row r="43">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>405249.36</v>
+        <v>412938.08</v>
       </c>
     </row>
     <row r="44">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>431383</v>
+        <v>434612</v>
       </c>
     </row>
     <row r="46">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23299</v>
+        <v>26299</v>
       </c>
     </row>
     <row r="48">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>46878</v>
+        <v>47219</v>
       </c>
     </row>
     <row r="49">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>23468</v>
+        <v>20860</v>
       </c>
     </row>
     <row r="50">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="52">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1841630974.23</v>
+        <v>1870003068.74</v>
       </c>
     </row>
     <row r="53">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>45641876.51</v>
+        <v>47060625.23</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>85986986.63</v>
+        <v>89620481.69</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4752298621.13</v>
+        <v>4764744082.58</v>
       </c>
     </row>
     <row r="57">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4702155224.08</v>
+        <v>4714432640.58</v>
       </c>
     </row>
     <row r="58">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>471825958.92</v>
+        <v>476531234.12</v>
       </c>
     </row>
     <row r="59">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>427176297.06</v>
+        <v>431335868.73</v>
       </c>
     </row>
     <row r="60">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-22 21:18:32</t>
+          <t>2026-09-23 09:17:53</t>
         </is>
       </c>
     </row>
@@ -3064,13 +3064,13 @@
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>2921247.85</v>
+        <v>3121247.85</v>
       </c>
       <c r="M23" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>350000</v>
+        <v>550000</v>
       </c>
       <c r="O23" s="6" t="n">
         <v>212062</v>
@@ -3079,7 +3079,7 @@
         <v>1323232.77</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="R23" s="6" t="n">
         <v>1030953.08</v>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="L26" s="6" t="n">
-        <v>4496568.61</v>
+        <v>5296568.61</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="N26" s="6" t="n">
         <v>0</v>
@@ -3289,10 +3289,10 @@
         <v>300010.5</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>3500000</v>
+        <v>4300000</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>0.87</v>
+        <v>1.03</v>
       </c>
       <c r="R26" s="6" t="n">
         <v>500000</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>75659161.21000001</v>
+        <v>75659161.20999999</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0.23</v>
@@ -4783,7 +4783,7 @@
         <v>187402.38</v>
       </c>
       <c r="Q47" s="6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="R47" s="6" t="n">
         <v>1116878.14</v>
@@ -5428,7 +5428,7 @@
         <v>11000000</v>
       </c>
       <c r="S56" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="57">
@@ -5620,13 +5620,13 @@
         </is>
       </c>
       <c r="L59" s="6" t="n">
-        <v>3194000</v>
+        <v>3294000</v>
       </c>
       <c r="M59" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>120000</v>
+        <v>220000</v>
       </c>
       <c r="O59" s="6" t="n">
         <v>44000</v>
@@ -6416,7 +6416,7 @@
         <v>1495000</v>
       </c>
       <c r="Q70" s="6" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="R70" s="6" t="n">
         <v>0</v>
@@ -6685,13 +6685,13 @@
         </is>
       </c>
       <c r="L74" s="6" t="n">
-        <v>760150</v>
+        <v>800150</v>
       </c>
       <c r="M74" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="N74" s="6" t="n">
-        <v>760000</v>
+        <v>800000</v>
       </c>
       <c r="O74" s="6" t="n">
         <v>150</v>
@@ -7126,7 +7126,7 @@
         <v>2396323.01</v>
       </c>
       <c r="Q80" s="6" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="R80" s="6" t="n">
         <v>0</v>
@@ -7182,16 +7182,16 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>1235500</v>
+        <v>1643000</v>
       </c>
       <c r="M81" s="6" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="N81" s="6" t="n">
-        <v>435500</v>
+        <v>635500</v>
       </c>
       <c r="O81" s="6" t="n">
-        <v>800000</v>
+        <v>1007500</v>
       </c>
       <c r="P81" s="6" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="L88" s="6" t="n">
-        <v>705701.63</v>
+        <v>730701.63</v>
       </c>
       <c r="M88" s="6" t="n">
         <v>0.01</v>
@@ -7688,7 +7688,7 @@
         <v>0</v>
       </c>
       <c r="O88" s="6" t="n">
-        <v>705701.63</v>
+        <v>730701.63</v>
       </c>
       <c r="P88" s="6" t="n">
         <v>0</v>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="L96" s="6" t="n">
-        <v>577500</v>
+        <v>604500</v>
       </c>
       <c r="M96" s="6" t="n">
         <v>0.01</v>
@@ -8256,7 +8256,7 @@
         <v>125000</v>
       </c>
       <c r="O96" s="6" t="n">
-        <v>302500</v>
+        <v>329500</v>
       </c>
       <c r="P96" s="6" t="n">
         <v>0</v>
@@ -8842,14 +8842,14 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-22.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-23.</t>
         </is>
       </c>
     </row>
@@ -9032,19 +9032,19 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>5296</v>
+        <v>5315</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>162783279.76</v>
+        <v>166719733.64</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>4.41</v>
+        <v>4.48</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>156018580.69</v>
+        <v>160082080.09</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>95.84</v>
+        <v>96.02</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>LULA (PT); CIRO GOMES (PSDB)</t>
+          <t>LULA (PT); CÉLIO STUDART (PSD)</t>
         </is>
       </c>
     </row>
@@ -9097,19 +9097,19 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1733</v>
+        <v>1736</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>63544234.42</v>
+        <v>64781393.41</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>61528778.73</v>
+        <v>62770937.72</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>96.83</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>31000000</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>15000000</v>
@@ -9301,10 +9301,10 @@
         <v>0.36</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>5390000</v>
+        <v>9320000</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>40.22</v>
+        <v>69.55</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>8708000</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>6229000</v>
@@ -9425,16 +9425,16 @@
         <v>29</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>7629340</v>
+        <v>8077840</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>3450720</v>
+        <v>3567420</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>45.23</v>
+        <v>44.16</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
@@ -9487,19 +9487,19 @@
         </is>
       </c>
       <c r="I12" s="5" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>7521467.03</v>
+        <v>7788567.03</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>7284372.03</v>
+        <v>7551472.03</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>96.84999999999999</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
@@ -9552,19 +9552,19 @@
         </is>
       </c>
       <c r="I13" s="5" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>6509910.5</v>
+        <v>6577731.35</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0.18</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>5371068.65</v>
+        <v>5512866.07</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>82.51000000000001</v>
+        <v>83.81</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
@@ -9620,16 +9620,16 @@
         <v>59</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>6506881.18</v>
+        <v>6512831.18</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0.18</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>3012590.4</v>
+        <v>3018540.4</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>46.3</v>
+        <v>46.35</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>5750000</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>3750000</v>
@@ -10072,19 +10072,19 @@
         </is>
       </c>
       <c r="I21" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>5394012.13</v>
+        <v>5398462.13</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0.15</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>3456333.74</v>
+        <v>3566865.74</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>64.08</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
@@ -10140,16 +10140,16 @@
         <v>208</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>5111261.23</v>
+        <v>5185954.75</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0.14</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>3859692.91</v>
+        <v>3955848.93</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>75.51000000000001</v>
+        <v>76.28</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>67.314.597/0001-10</t>
+          <t>35.659.497/0001-39</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>ALL MG26 COMUNICACAO E ESTRATEGIA SPE LTDA</t>
+          <t>GRAFICA NMC LTDA</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -10267,28 +10267,28 @@
         </is>
       </c>
       <c r="I24" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>4800000</v>
+        <v>4915747.61</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0.13</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4800000</v>
+        <v>2201400.04</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>100</v>
+        <v>44.78</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PT; PL; REPUBLICANOS; UNIÃO</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>ALEXANDRE KALIL (PDT)</t>
+          <t>LULA (PT); MENDONÇA FILHO (PL)</t>
         </is>
       </c>
     </row>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>04.986.141/0001-86</t>
+          <t>67.314.597/0001-10</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>F7 COMUNICACAO LTDA</t>
+          <t>ALL MG26 COMUNICACAO E ESTRATEGIA SPE LTDA</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>SALVADOR</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -10332,28 +10332,28 @@
         </is>
       </c>
       <c r="I25" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>4750000</v>
+        <v>4800000</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0.13</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>1100000</v>
+        <v>4800000</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>23.16</v>
+        <v>100</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>MDB; PSD</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>RENAN FILHO (MDB); DANIEL VILELA (MDB)</t>
+          <t>ALEXANDRE KALIL (PDT)</t>
         </is>
       </c>
     </row>
@@ -10363,12 +10363,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>02.933.302/0001-48</t>
+          <t>04.986.141/0001-86</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>QUALIGRAF - EDITORA E GRAFICA LTDA</t>
+          <t>F7 COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>FORTALEZA</t>
+          <t>SALVADOR</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -10397,28 +10397,28 @@
         </is>
       </c>
       <c r="I26" s="5" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>4666165.9</v>
+        <v>4750000</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0.13</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>3427014.9</v>
+        <v>1100000</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>73.44</v>
+        <v>23.16</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>PL; PT; PP; REPUBLICANOS</t>
+          <t>MDB; PSD</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>DANILO FORTE (PP); FERNANDO SANTANA (PT)</t>
+          <t>RENAN FILHO (MDB); DANIEL VILELA (MDB)</t>
         </is>
       </c>
     </row>
@@ -10428,12 +10428,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>05.060.706/0001-62</t>
+          <t>02.933.302/0001-48</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>SANTANA   ASSOCIADOS MARKETING E PROPAGANDA LTDA</t>
+          <t>QUALIGRAF - EDITORA E GRAFICA LTDA</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>LAURO DE FREITAS</t>
+          <t>FORTALEZA</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -10462,28 +10462,28 @@
         </is>
       </c>
       <c r="I27" s="5" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>4600000</v>
+        <v>4666165.9</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>2000000</v>
+        <v>3427014.9</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>43.48</v>
+        <v>73.44</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO; PL</t>
+          <t>PL; PT; PP; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>ALCIDES FERNANDES (PL); CAPITÃO WAGNER (UNIÃO)</t>
+          <t>DANILO FORTE (PP); FERNANDO SANTANA (PT)</t>
         </is>
       </c>
     </row>
@@ -10493,12 +10493,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>35.659.497/0001-39</t>
+          <t>05.060.706/0001-62</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>GRAFICA NMC LTDA</t>
+          <t>SANTANA   ASSOCIADOS MARKETING E PROPAGANDA LTDA</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -10508,17 +10508,17 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>LAURO DE FREITAS</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -10527,28 +10527,28 @@
         </is>
       </c>
       <c r="I28" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>4443460.11</v>
+        <v>4600000</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0.12</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>2201400.04</v>
+        <v>2000000</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>49.54</v>
+        <v>43.48</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>PT; PL; REPUBLICANOS; UNIÃO</t>
+          <t>UNIÃO; PL</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>LULA (PT); MENDONÇA FILHO (PL)</t>
+          <t>ALCIDES FERNANDES (PL); CAPITÃO WAGNER (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -10595,16 +10595,16 @@
         <v>44</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>4303626.65</v>
+        <v>4323456.65</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0.12</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>2783347.11</v>
+        <v>2803177.11</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>64.67</v>
+        <v>64.84</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>4273052.5</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>3210705.5</v>
@@ -10728,7 +10728,7 @@
         <v>4268716</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>2074304</v>
@@ -10753,12 +10753,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>67.565.691/0001-41</t>
+          <t>07.263.666/0001-81</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>D26 COMUNICACAO SPE LTDA.</t>
+          <t>BRASPOR GRAFICA E EDITORA LTDA.</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -10768,17 +10768,17 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>OSASCO</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -10787,28 +10787,28 @@
         </is>
       </c>
       <c r="I32" s="5" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>4025000</v>
+        <v>4040194.61</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0.11</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>4025000</v>
+        <v>1777252.4</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>100</v>
+        <v>43.99</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>PL; PSD</t>
+          <t>PT; PL; PODE; UNIÃO</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>CARLOS PORTINHO (PL); DOUGLAS RUAS (PL)</t>
+          <t>FLAVIO BOLSONARO (PL); ARLINDO CHINAGLIA (PT)</t>
         </is>
       </c>
     </row>
@@ -10818,12 +10818,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>07.263.666/0001-81</t>
+          <t>67.565.691/0001-41</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>BRASPOR GRAFICA E EDITORA LTDA.</t>
+          <t>D26 COMUNICACAO SPE LTDA.</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -10833,17 +10833,17 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>OSASCO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -10852,28 +10852,28 @@
         </is>
       </c>
       <c r="I33" s="5" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>4008755.11</v>
+        <v>4025000</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0.11</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>1757905.9</v>
+        <v>4025000</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>43.85</v>
+        <v>100</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>PT; PL; PODE; UNIÃO</t>
+          <t>PL; PSD</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL); ARLINDO CHINAGLIA (PT)</t>
+          <t>CARLOS PORTINHO (PL); DOUGLAS RUAS (PL)</t>
         </is>
       </c>
     </row>
@@ -10917,19 +10917,19 @@
         </is>
       </c>
       <c r="I34" s="5" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>3970111.96</v>
+        <v>4008181.96</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0.11</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>2894461.96</v>
+        <v>2937531.96</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>72.91</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
@@ -10991,10 +10991,10 @@
         <v>0.1</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>1500000</v>
+        <v>3303000</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>39.47</v>
+        <v>86.92</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
@@ -11143,12 +11143,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>67.949.812/0001-59</t>
+          <t>04.405.470/0001-96</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>ALGORITMO DADOS ESTRATEGIA E COMUNICACAO LTDA</t>
+          <t>CONTACTO RELACOES PUBLICAS LTDA</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -11158,17 +11158,17 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Agências de notícias</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>NATAL</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -11177,7 +11177,7 @@
         </is>
       </c>
       <c r="I38" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>3600000</v>
@@ -11186,19 +11186,19 @@
         <v>0.1</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>1800000</v>
+        <v>0</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT; PSB; REDE</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>ELMANO DE FREITAS (PT); CID GOMES (PSB)</t>
         </is>
       </c>
     </row>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>04.405.470/0001-96</t>
+          <t>67.949.812/0001-59</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>CONTACTO RELACOES PUBLICAS LTDA</t>
+          <t>ALGORITMO DADOS ESTRATEGIA E COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -11223,17 +11223,17 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Agências de notícias</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>NATAL</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="I39" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39" s="6" t="n">
         <v>3600000</v>
@@ -11251,19 +11251,19 @@
         <v>0.1</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>PT; PSB; REDE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>ELMANO DE FREITAS (PT); CID GOMES (PSB)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -11338,12 +11338,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>04.639.525/0001-22</t>
+          <t>30.007.119/0001-57</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>MALHEIROS, PENTEADO E TOLEDO - ADVOGADOS</t>
+          <t>CONNECT FILMES - PRODUCAO DE FILMES E PUBLICIDADE LTDA</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -11353,17 +11353,17 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Atividades jurídicas, exceto cartórios</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -11372,7 +11372,7 @@
         </is>
       </c>
       <c r="I41" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" s="6" t="n">
         <v>3500000</v>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS; PSD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>TARCÍSIO (REPUBLICANOS); RONALDO CAIADO (PSD)</t>
+          <t>TARCÍSIO (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -11403,12 +11403,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>30.007.119/0001-57</t>
+          <t>04.639.525/0001-22</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>CONNECT FILMES - PRODUCAO DE FILMES E PUBLICIDADE LTDA</t>
+          <t>MALHEIROS, PENTEADO E TOLEDO - ADVOGADOS</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -11418,17 +11418,17 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Atividades jurídicas, exceto cartórios</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -11437,7 +11437,7 @@
         </is>
       </c>
       <c r="I42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" s="6" t="n">
         <v>3500000</v>
@@ -11446,19 +11446,19 @@
         <v>0.09</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>1500000</v>
+        <v>2500000</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>42.86</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>REPUBLICANOS; PSD</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>TARCÍSIO (REPUBLICANOS)</t>
+          <t>TARCÍSIO (REPUBLICANOS); RONALDO CAIADO (PSD)</t>
         </is>
       </c>
     </row>
@@ -11833,7 +11833,7 @@
         <v>3159619.5</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="L48" s="6" t="n">
         <v>2198755</v>
@@ -11898,7 +11898,7 @@
         <v>3150000</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="L49" s="6" t="n">
         <v>1575000</v>
@@ -12248,12 +12248,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>23.087.346/0001-74</t>
+          <t>34.028.316/0001-03</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>VENTURA ESTUDIO LTDA</t>
+          <t>EMPRESA BRASILEIRA DE CORREIOS E TELEGRAFOS</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -12263,17 +12263,17 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Atividades de Correio</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>FLORIANOPOLIS</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -12282,28 +12282,28 @@
         </is>
       </c>
       <c r="I55" s="5" t="n">
-        <v>3</v>
+        <v>128</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>2985000</v>
+        <v>2987067.62</v>
       </c>
       <c r="K55" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>2985000</v>
+        <v>2968002.61</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>100</v>
+        <v>99.36</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD; UNIÃO; MDB; PL</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>CARLOS BOLSONARO (PL); CAROL DE TONI (PL)</t>
+          <t>FABIO SILVA (UNIÃO); PAULO FILHO DA FUNDAÇÃO (PSD)</t>
         </is>
       </c>
     </row>
@@ -12313,12 +12313,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>27.830.860/0001-09</t>
+          <t>23.087.346/0001-74</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>F PIRES PRODUCOES DE EVENTOS, COMERCIO E SERVICOS LTDA</t>
+          <t>VENTURA ESTUDIO LTDA</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -12328,17 +12328,17 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de produtos diversos não especificados anteriormente</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>BELEM</t>
+          <t>FLORIANOPOLIS</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -12347,28 +12347,28 @@
         </is>
       </c>
       <c r="I56" s="5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>2974320</v>
+        <v>2985000</v>
       </c>
       <c r="K56" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>2974320</v>
+        <v>2985000</v>
       </c>
       <c r="M56" s="6" t="n">
         <v>100</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>DELEGADO FEDERAL EGUCHI (REPUBLICANOS); WR DO TAPAJÓS (REPUBLICANOS)</t>
+          <t>CARLOS BOLSONARO (PL); CAROL DE TONI (PL)</t>
         </is>
       </c>
     </row>
@@ -12378,12 +12378,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>34.028.316/0001-03</t>
+          <t>27.830.860/0001-09</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>EMPRESA BRASILEIRA DE CORREIOS E TELEGRAFOS</t>
+          <t>F PIRES PRODUCOES DE EVENTOS, COMERCIO E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -12393,17 +12393,17 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Atividades de Correio</t>
+          <t>Fabricação de produtos diversos não especificados anteriormente</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>BELEM</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -12412,28 +12412,28 @@
         </is>
       </c>
       <c r="I57" s="5" t="n">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>2877742.51</v>
+        <v>2974320</v>
       </c>
       <c r="K57" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>2858677.5</v>
+        <v>2974320</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>99.34</v>
+        <v>100</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>PSD; UNIÃO; PL; MDB</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>FABIO SILVA (UNIÃO); PAULO FILHO DA FUNDAÇÃO (PSD)</t>
+          <t>DELEGADO FEDERAL EGUCHI (REPUBLICANOS); WR DO TAPAJÓS (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12548,7 @@
         <v>2777530.15</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L59" s="6" t="n">
         <v>1562335.45</v>
@@ -12805,16 +12805,16 @@
         <v>65</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>2694545.21</v>
+        <v>2695690.16</v>
       </c>
       <c r="K63" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L63" s="6" t="n">
-        <v>2037954.12</v>
+        <v>2039099.07</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>75.63</v>
+        <v>75.64</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
@@ -13071,10 +13071,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="L67" s="6" t="n">
-        <v>1376688.5</v>
+        <v>1597383.5</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>52.08</v>
+        <v>60.42</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
@@ -13288,12 +13288,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>26.983.273/0001-97</t>
+          <t>41.470.063/0001-99</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>VITORINO   MENDONCA LTDA</t>
+          <t>SETE CORES INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -13303,17 +13303,17 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -13322,28 +13322,28 @@
         </is>
       </c>
       <c r="I71" s="5" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>2550000</v>
+        <v>2566061.2</v>
       </c>
       <c r="K71" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L71" s="6" t="n">
-        <v>1800000</v>
+        <v>2314576.2</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>70.59</v>
+        <v>90.2</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PL; PCDOB; PDT; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>WILDER MORAIS (PL); MARCOS ROGÉRIO (PL)</t>
+          <t>SILVIO ANTÔNIO (PL); WEVERTON ROCHA (PDT)</t>
         </is>
       </c>
     </row>
@@ -13353,12 +13353,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>09.649.862/0001-14</t>
+          <t>26.983.273/0001-97</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>IRMAOS SOUTELLO   MENDONCA CONSULTORIA, COMUNICACAO E DESENVOLVIMENTO DE PROJETOS LTDA.</t>
+          <t>VITORINO   MENDONCA LTDA</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Atividades de consultoria em gestão empresarial</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -13396,19 +13396,19 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>2540000</v>
+        <v>1800000</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>99.61</v>
+        <v>70.59</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>PSB; PL; PSDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>SIMONE TEBET (PSB); ARTHUR HENRIQUE (PL)</t>
+          <t>WILDER MORAIS (PL); MARCOS ROGÉRIO (PL)</t>
         </is>
       </c>
     </row>
@@ -13418,12 +13418,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>30.985.686/0001-88</t>
+          <t>09.649.862/0001-14</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>INK IMPRESSAO DE  MATERIAL PUBLICITARIO, ENCADERNACAO E EDICAO DE CADASTROS LTDA</t>
+          <t>IRMAOS SOUTELLO   MENDONCA CONSULTORIA, COMUNICACAO E DESENVOLVIMENTO DE PROJETOS LTDA.</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -13433,17 +13433,17 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades de consultoria em gestão empresarial</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>JOAO PESSOA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -13452,28 +13452,28 @@
         </is>
       </c>
       <c r="I73" s="5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>2537085</v>
+        <v>2550000</v>
       </c>
       <c r="K73" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L73" s="6" t="n">
-        <v>2129710</v>
+        <v>2540000</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>83.94</v>
+        <v>99.61</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>PSD; PODE; MDB; UNIÃO</t>
+          <t>PSB; PL; PSDB</t>
         </is>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>DOUTOR JHONY (PSD); SILVIA DA PESCA (PODE)</t>
+          <t>SIMONE TEBET (PSB); ARTHUR HENRIQUE (PL)</t>
         </is>
       </c>
     </row>
@@ -13483,12 +13483,12 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>07.556.546/0001-72</t>
+          <t>30.985.686/0001-88</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>PRESSGRAF IMPORTACAO TECNOLOGIA E SERVICOS GRAFICOS LTDA</t>
+          <t>INK IMPRESSAO DE  MATERIAL PUBLICITARIO, ENCADERNACAO E EDICAO DE CADASTROS LTDA</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -13503,12 +13503,12 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>SALVADOR</t>
+          <t>JOAO PESSOA</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -13517,28 +13517,28 @@
         </is>
       </c>
       <c r="I74" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>2521118.45</v>
+        <v>2537085</v>
       </c>
       <c r="K74" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L74" s="6" t="n">
-        <v>2288977.3</v>
+        <v>2129710</v>
       </c>
       <c r="M74" s="6" t="n">
-        <v>90.79000000000001</v>
+        <v>83.94</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS; PSD; PSDB; UNIÃO</t>
+          <t>PSD; PODE; MDB; UNIÃO</t>
         </is>
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>RAIMUNDO COSTA (PSD); MÁRCIO MARINHO (REPUBLICANOS)</t>
+          <t>DOUTOR JHONY (PSD); SILVIA DA PESCA (PODE)</t>
         </is>
       </c>
     </row>
@@ -13548,12 +13548,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>22.966.876/0001-20</t>
+          <t>07.556.546/0001-72</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>REDE DE NEGOCIOS E PRODUCAO DE EVENTOS LTDA</t>
+          <t>PRESSGRAF IMPORTACAO TECNOLOGIA E SERVICOS GRAFICOS LTDA</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -13563,17 +13563,17 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Atividades de organização de eventos, exceto culturais e esportivos</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>SALVADOR</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -13582,28 +13582,28 @@
         </is>
       </c>
       <c r="I75" s="5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>2500000</v>
+        <v>2521118.45</v>
       </c>
       <c r="K75" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L75" s="6" t="n">
-        <v>1000000</v>
+        <v>2288977.3</v>
       </c>
       <c r="M75" s="6" t="n">
-        <v>40</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>REPUBLICANOS; PSD; PSDB; UNIÃO</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>RAQUEL LYRA (PSD)</t>
+          <t>RAIMUNDO COSTA (PSD); MÁRCIO MARINHO (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -13613,12 +13613,12 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>05.555.136/0001-81</t>
+          <t>68.154.614/0001-61</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>CONDADO MARKETING LTDA</t>
+          <t>ESTUDIO 90 PRODUCOES LTDA</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>LAJEADO</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -13647,7 +13647,7 @@
         </is>
       </c>
       <c r="I76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J76" s="6" t="n">
         <v>2500000</v>
@@ -13656,19 +13656,19 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="L76" s="6" t="n">
-        <v>2500000</v>
+        <v>1700000</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>MDB; PSD</t>
         </is>
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>JULIANA BRIZOLA (PDT)</t>
+          <t>GABRIEL SOUZA (MDB); FREDERICO ANTUNES (PSD)</t>
         </is>
       </c>
     </row>
@@ -13678,12 +13678,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>68.154.614/0001-61</t>
+          <t>22.966.876/0001-20</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>ESTUDIO 90 PRODUCOES LTDA</t>
+          <t>REDE DE NEGOCIOS E PRODUCAO DE EVENTOS LTDA</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -13693,17 +13693,17 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Atividades de organização de eventos, exceto culturais e esportivos</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -13712,7 +13712,7 @@
         </is>
       </c>
       <c r="I77" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J77" s="6" t="n">
         <v>2500000</v>
@@ -13721,19 +13721,19 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="L77" s="6" t="n">
-        <v>1700000</v>
+        <v>1000000</v>
       </c>
       <c r="M77" s="6" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>MDB; PSD</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>GABRIEL SOUZA (MDB); FREDERICO ANTUNES (PSD)</t>
+          <t>RAQUEL LYRA (PSD)</t>
         </is>
       </c>
     </row>
@@ -13743,12 +13743,12 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>14.876.708/0001-15</t>
+          <t>05.555.136/0001-81</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>NOGUEIRA, ALBUQUERQUE E FREIRE ASSOCIADOS S/S</t>
+          <t>CONDADO MARKETING LTDA</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -13758,17 +13758,17 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Atividades de contabilidade, consultoria e auditoria contábil e tributária</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>LAJEADO</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -13777,28 +13777,28 @@
         </is>
       </c>
       <c r="I78" s="5" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>2474000</v>
+        <v>2500000</v>
       </c>
       <c r="K78" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L78" s="6" t="n">
-        <v>740500</v>
+        <v>2500000</v>
       </c>
       <c r="M78" s="6" t="n">
-        <v>29.93</v>
+        <v>100</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>MDB; PP; PL; PSDB</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>ARTHUR LIRA (PP); DANIEL BARBOSA (PP)</t>
+          <t>JULIANA BRIZOLA (PDT)</t>
         </is>
       </c>
     </row>
@@ -13808,12 +13808,12 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>41.470.063/0001-99</t>
+          <t>14.876.708/0001-15</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>SETE CORES INDUSTRIA E COMERCIO LTDA</t>
+          <t>NOGUEIRA, ALBUQUERQUE E FREIRE ASSOCIADOS S/S</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -13823,17 +13823,17 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Atividades de contabilidade, consultoria e auditoria contábil e tributária</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>SAO LUIS</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -13842,28 +13842,28 @@
         </is>
       </c>
       <c r="I79" s="5" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>2465641.2</v>
+        <v>2474000</v>
       </c>
       <c r="K79" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L79" s="6" t="n">
-        <v>2184690.2</v>
+        <v>740500</v>
       </c>
       <c r="M79" s="6" t="n">
-        <v>88.61</v>
+        <v>29.93</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>PL; PCDOB; REPUBLICANOS; PDT</t>
+          <t>MDB; PP; PL; PSDB</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>SILVIO ANTÔNIO (PL); WEVERTON ROCHA (PDT)</t>
+          <t>ARTHUR LIRA (PP); DANIEL BARBOSA (PP)</t>
         </is>
       </c>
     </row>
@@ -13975,16 +13975,16 @@
         <v>20</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>2404585.1</v>
+        <v>2410585.1</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L81" s="6" t="n">
-        <v>1776934.1</v>
+        <v>1782934.1</v>
       </c>
       <c r="M81" s="6" t="n">
-        <v>73.90000000000001</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
@@ -14037,19 +14037,19 @@
         </is>
       </c>
       <c r="I82" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>2361205.71</v>
+        <v>2363055.71</v>
       </c>
       <c r="K82" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L82" s="6" t="n">
-        <v>1380955.95</v>
+        <v>1382805.95</v>
       </c>
       <c r="M82" s="6" t="n">
-        <v>58.49</v>
+        <v>58.52</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
@@ -14631,10 +14631,10 @@
         <v>0.06</v>
       </c>
       <c r="L91" s="6" t="n">
-        <v>1966760</v>
+        <v>2006660</v>
       </c>
       <c r="M91" s="6" t="n">
-        <v>90.95</v>
+        <v>92.8</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
@@ -14653,12 +14653,12 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>64.433.090/0001-97</t>
+          <t>64.752.158/0001-09</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>GAB INDUSTRIA GRAFICA LTDA</t>
+          <t>OKAN COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -14668,17 +14668,17 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>NEROPOLIS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -14687,28 +14687,28 @@
         </is>
       </c>
       <c r="I92" s="5" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>2107371.87</v>
+        <v>2149000</v>
       </c>
       <c r="K92" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L92" s="6" t="n">
-        <v>1786148.56</v>
+        <v>2099000</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>84.76000000000001</v>
+        <v>97.67</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>PT; UNIÃO; MDB; REPUBLICANOS</t>
+          <t>PT; PSOL; UNIÃO</t>
         </is>
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>GRACINHA CAIADO (UNIÃO); RUBENS OTONI (PT)</t>
+          <t>PATRUS ANANIAS (PT); MARÍLIA CAMPOS (PT)</t>
         </is>
       </c>
     </row>
@@ -14718,12 +14718,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>47.461.986/0001-60</t>
+          <t>64.433.090/0001-97</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>BLUEGRAF EDITORA LTDA</t>
+          <t>GAB INDUSTRIA GRAFICA LTDA</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -14738,12 +14738,12 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>GUARULHOS</t>
+          <t>NEROPOLIS</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -14755,25 +14755,25 @@
         <v>33</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>2103818.7</v>
+        <v>2107371.87</v>
       </c>
       <c r="K93" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L93" s="6" t="n">
-        <v>1395970.1</v>
+        <v>1786148.56</v>
       </c>
       <c r="M93" s="6" t="n">
-        <v>66.34999999999999</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>PSD; PL; PP; REPUBLICANOS</t>
+          <t>PT; UNIÃO; MDB; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>WALTER IHOSHI (PSD); DRA. SANDRA TADEU (PL)</t>
+          <t>GRACINHA CAIADO (UNIÃO); RUBENS OTONI (PT)</t>
         </is>
       </c>
     </row>
@@ -14783,12 +14783,12 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>64.752.158/0001-09</t>
+          <t>47.461.986/0001-60</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>OKAN COMUNICACAO LTDA</t>
+          <t>BLUEGRAF EDITORA LTDA</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -14798,17 +14798,17 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>GUARULHOS</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -14817,28 +14817,28 @@
         </is>
       </c>
       <c r="I94" s="5" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>2099000</v>
+        <v>2103818.7</v>
       </c>
       <c r="K94" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L94" s="6" t="n">
-        <v>2049000</v>
+        <v>1412760.9</v>
       </c>
       <c r="M94" s="6" t="n">
-        <v>97.62</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>PT; PSOL; UNIÃO</t>
+          <t>PSD; PL; PP; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>PATRUS ANANIAS (PT); MARÍLIA CAMPOS (PT)</t>
+          <t>WALTER IHOSHI (PSD); DRA. SANDRA TADEU (PL)</t>
         </is>
       </c>
     </row>
@@ -15018,7 +15018,7 @@
         <v>2044887.73</v>
       </c>
       <c r="K97" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L97" s="6" t="n">
         <v>1413610.84</v>
@@ -15083,7 +15083,7 @@
         <v>2042555</v>
       </c>
       <c r="K98" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L98" s="6" t="n">
         <v>1981475</v>
@@ -15495,14 +15495,14 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-22.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-23.</t>
         </is>
       </c>
     </row>
@@ -15543,7 +15543,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="33" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -15623,16 +15623,16 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1847</v>
+        <v>1856</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>922887586.53</v>
+        <v>928727586.53</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>16.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -15655,16 +15655,16 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2043</v>
+        <v>2048</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>538613251.35</v>
+        <v>538716331.35</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>9.35</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -15690,13 +15690,13 @@
         <v>701</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>509790673.71</v>
+        <v>510133812.2</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>8.85</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -15719,16 +15719,16 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1125</v>
+        <v>1136</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>465703812.13</v>
+        <v>467112012.13</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>8.08</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -15751,16 +15751,16 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1037</v>
+        <v>1044</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>444428813.14</v>
+        <v>445598813.14</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>7.71</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="10">
@@ -15783,16 +15783,16 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>396759721.3</v>
+        <v>397307221.3</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>6.88</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="11">
@@ -15815,16 +15815,16 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1334</v>
+        <v>1344</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>347361189.08</v>
+        <v>348211970.23</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>6.03</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -15850,13 +15850,13 @@
         <v>813</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>216436226.53</v>
+        <v>216841226.53</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="13">
@@ -15879,16 +15879,16 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>204584510.02</v>
+        <v>205734510.02</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="14">
@@ -15911,16 +15911,16 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1080</v>
+        <v>1087</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>135494567.76</v>
+        <v>136954567.76</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="15">
@@ -15943,16 +15943,16 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>132020896.53</v>
+        <v>132072896.53</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="16">
@@ -15978,13 +15978,13 @@
         <v>698</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>120696927.17</v>
+        <v>120810920.73</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="17">
@@ -16010,13 +16010,13 @@
         <v>848</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1883</v>
+        <v>1899</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>81085945.8</v>
+        <v>82793115.8</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="18">
@@ -16039,16 +16039,16 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>66217212.82</v>
+        <v>67132512.81999999</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="19">
@@ -16074,10 +16074,10 @@
         <v>330</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>63031379.77</v>
+        <v>63131379.77</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>1.09</v>
@@ -16112,7 +16112,7 @@
         <v>61544522.54</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="21">
@@ -16135,13 +16135,13 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>46844510</v>
+        <v>46944510</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>0.8100000000000001</v>
@@ -16176,7 +16176,7 @@
         <v>41990998</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="23">
@@ -16202,13 +16202,13 @@
         <v>142</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>39584652.31</v>
+        <v>39702914.61</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="24">
@@ -16234,13 +16234,13 @@
         <v>82</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>2105</v>
+        <v>2115</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>27701618.52</v>
+        <v>28677618.52</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="25">
@@ -16336,7 +16336,7 @@
         <v>16454969.43</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="28">
@@ -16359,13 +16359,13 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>1458</v>
+        <v>1493</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>12619433.87</v>
+        <v>12839089.81</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0.22</v>
@@ -16394,10 +16394,10 @@
         <v>57</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>11834308.44</v>
+        <v>12060308.44</v>
       </c>
       <c r="H29" s="6" t="n">
         <v>0.21</v>
@@ -16487,13 +16487,13 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>8308809.08</v>
+        <v>8413809.08</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>0.14</v>
@@ -16519,13 +16519,13 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>6962810.35</v>
+        <v>7000602.55</v>
       </c>
       <c r="H33" s="6" t="n">
         <v>0.12</v>
@@ -16554,13 +16554,13 @@
         <v>34</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>5723713.57</v>
+        <v>6223713.57</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="35">
@@ -16586,10 +16586,10 @@
         <v>32</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>5584256.19</v>
+        <v>5827746.850000001</v>
       </c>
       <c r="H35" s="6" t="n">
         <v>0.1</v>
@@ -16746,10 +16746,10 @@
         <v>20</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>4671500</v>
+        <v>4721500</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>0.08</v>
@@ -16807,13 +16807,13 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>4486056.52</v>
+        <v>4536042.82</v>
       </c>
       <c r="H42" s="6" t="n">
         <v>0.08</v>
@@ -16874,10 +16874,10 @@
         <v>88</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>4383537.2</v>
+        <v>4386037.2</v>
       </c>
       <c r="H44" s="6" t="n">
         <v>0.08</v>
@@ -16921,7 +16921,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS - BAHIA - ESTADUAL</t>
+          <t>PARTIDO SOCIALISTA BRASILEIRO - SAO PAULO - SP - ESTADUAL</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -16931,17 +16931,17 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>4111352.33</v>
+        <v>4221030.61</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -16953,7 +16953,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>PARTIDO SOCIALISTA BRASILEIRO - SAO PAULO - SP - ESTADUAL</t>
+          <t>REPUBLICANOS - BAHIA - ESTADUAL</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -16963,17 +16963,17 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>189</v>
+        <v>238</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>3954555.61</v>
+        <v>4111352.33</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -16985,27 +16985,27 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>ALEXANDRE GRENDENE BARTELLE</t>
+          <t>PARTIDO LIBERAL SAO PAULO SP ESTADUAL</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Recursos de pessoas físicas</t>
+          <t>Recursos de partido político</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>7</v>
+        <v>424</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>3950000</v>
+        <v>4063800.47</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -17017,27 +17017,27 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>PARTIDO LIBERAL SAO PAULO SP ESTADUAL</t>
+          <t>ALEXANDRE GRENDENE BARTELLE</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Recursos de partido político</t>
+          <t>Recursos de pessoas físicas</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>...</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>410</v>
+        <v>7</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>3928252.66</v>
+        <v>3950000</v>
       </c>
       <c r="H49" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS - ACRE - AC - ESTADUAL</t>
+          <t>PARTIDO LIBERAL - MARANHAO - MA- ESTADUAL</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -17059,17 +17059,17 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>3908003.22</v>
+        <v>3910000</v>
       </c>
       <c r="H50" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>PARTIDO SOCIAL DEMOCRATICO</t>
+          <t>REPUBLICANOS - ACRE - AC - ESTADUAL</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -17091,20 +17091,20 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>659</v>
+        <v>15</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>3659485.32</v>
+        <v>3908003.22</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -17123,20 +17123,20 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>33</v>
+        <v>660</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>3595000</v>
+        <v>3784485.32</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>PARTIDO MISSAO</t>
+          <t>UNIAO BRASIL - MARANHAO - MA- ESTADUAL</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -17155,17 +17155,17 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>469</v>
+        <v>23</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>486</v>
+        <v>31</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>3449422.72</v>
+        <v>3614000</v>
       </c>
       <c r="H53" s="6" t="n">
         <v>0.06</v>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>REPUBLICANOS - TOCANTINS - TO - ESTADUAL</t>
+          <t>PARTIDO SOCIAL DEMOCRATICO</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -17187,17 +17187,17 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E54" s="8" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>213</v>
+        <v>33</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>3437889.93</v>
+        <v>3595000</v>
       </c>
       <c r="H54" s="9" t="n">
         <v>0.06</v>
@@ -17206,14 +17206,14 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-22.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-23.</t>
         </is>
       </c>
     </row>
@@ -17313,10 +17313,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>820269525.98</v>
+        <v>826957435.4</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>14.23</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="6">
@@ -17336,10 +17336,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>471748294.21</v>
+        <v>474653061.28</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>8.19</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="7">
@@ -17359,10 +17359,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>460939832.4</v>
+        <v>462959210.53</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>8</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="8">
@@ -17382,7 +17382,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>317235433.55</v>
+        <v>319487309</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>5.5</v>
@@ -17405,10 +17405,10 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>297783154.35</v>
+        <v>301361755.9</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>5.17</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="10">
@@ -17428,10 +17428,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>290652931.56</v>
+        <v>292098182.19</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="11">
@@ -17451,10 +17451,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>231985742.33</v>
+        <v>234886984.33</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.03</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="12">
@@ -17474,10 +17474,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>213947162.63</v>
+        <v>216781721.91</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="13">
@@ -17497,10 +17497,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>201927826.94</v>
+        <v>204058209.94</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="14">
@@ -17520,10 +17520,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>199488338.22</v>
+        <v>201971967.08</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="15">
@@ -17543,10 +17543,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>189319796.4</v>
+        <v>191421338.9</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="16">
@@ -17566,10 +17566,10 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>173997252.68</v>
+        <v>174505609.68</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="17">
@@ -17589,10 +17589,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>140698770.08</v>
+        <v>142757224.66</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="18">
@@ -17612,10 +17612,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>136347659.97</v>
+        <v>137949190.58</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="19">
@@ -17626,16 +17626,16 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Paraíba</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>135764338.65</v>
+        <v>137219155.39</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>2.36</v>
@@ -17649,19 +17649,19 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>135075740.39</v>
+        <v>136180246.65</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="21">
@@ -17681,10 +17681,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>132932338.68</v>
+        <v>133548822.09</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="22">
@@ -17704,7 +17704,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>129530005.95</v>
+        <v>130654310.74</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>2.25</v>
@@ -17727,10 +17727,10 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>126690682.48</v>
+        <v>127167410.29</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="24">
@@ -17750,10 +17750,10 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>122880968.33</v>
+        <v>123333353.33</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="25">
@@ -17773,10 +17773,10 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>113252800.91</v>
+        <v>113301947.41</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="26">
@@ -17796,10 +17796,10 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>110174125.13</v>
+        <v>110452755.13</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="27">
@@ -17819,7 +17819,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>108175510.82</v>
+        <v>109070475.18</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>1.88</v>
@@ -17842,10 +17842,10 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>105663981.86</v>
+        <v>105576888.85</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="29">
@@ -17865,10 +17865,10 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>102228361.13</v>
+        <v>102266586.13</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="30">
@@ -17888,10 +17888,10 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>100582622.06</v>
+        <v>100669144.7</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="31">
@@ -17911,10 +17911,10 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>97244344.3</v>
+        <v>97540224.3</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="32">
@@ -17934,10 +17934,10 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>96618755.84999999</v>
+        <v>96690655.84999999</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="33">
@@ -17957,10 +17957,10 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>124089201.8</v>
+        <v>128237572.29</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>30.71</v>
+        <v>30.65</v>
       </c>
     </row>
     <row r="34">
@@ -17980,10 +17980,10 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>25358783.49</v>
+        <v>25799583.49</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>6.28</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="35">
@@ -18003,10 +18003,10 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>24959286.94</v>
+        <v>25599286.94</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>6.18</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="36">
@@ -18026,10 +18026,10 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>21647097.32</v>
+        <v>21701767.32</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>5.36</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="37">
@@ -18049,10 +18049,10 @@
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>15773908.81</v>
+        <v>15903908.81</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="38">
@@ -18075,7 +18075,7 @@
         <v>15262288.01</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="39">
@@ -18095,10 +18095,10 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>13518319.45</v>
+        <v>15078319.45</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="40">
@@ -18109,19 +18109,19 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Santa Catarina</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>13336864.1</v>
+        <v>14207631.64</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="41">
@@ -18132,19 +18132,19 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>13104475.41</v>
+        <v>13926200.1</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>3.24</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="42">
@@ -18155,19 +18155,19 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Santa Catarina</t>
+          <t>Piauí</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>12677131.64</v>
+        <v>13104475.41</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="43">
@@ -18187,10 +18187,10 @@
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>11823674.57</v>
+        <v>12511165.23</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="44">
@@ -18213,7 +18213,7 @@
         <v>10942987.78</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="45">
@@ -18233,10 +18233,10 @@
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>9895920.960000001</v>
+        <v>9916920.960000001</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="46">
@@ -18247,16 +18247,16 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Paraíba</t>
+          <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>9299949.800000001</v>
+        <v>9620232.77</v>
       </c>
       <c r="E46" s="12" t="n">
         <v>2.3</v>
@@ -18270,19 +18270,19 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Presidenciáveis, circunscrição nacional</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>8820232.77</v>
+        <v>9299949.800000001</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="48">
@@ -18293,19 +18293,19 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>7932515.61</v>
+        <v>8312525.42</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="49">
@@ -18316,19 +18316,19 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>7236532.99</v>
+        <v>8074015.61</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="50">
@@ -18339,19 +18339,19 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Alagoas</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>7071028.8</v>
+        <v>7236532.99</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="51">
@@ -18362,19 +18362,19 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Alagoas</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>6847123.38</v>
+        <v>7111028.8</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="52">
@@ -18397,7 +18397,7 @@
         <v>6157267.24</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="53">
@@ -18420,7 +18420,7 @@
         <v>6118338.31</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="54">
@@ -18440,10 +18440,10 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>6068288.52</v>
+        <v>6104288.52</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="55">
@@ -18454,19 +18454,19 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Pará</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>5416259.45</v>
+        <v>6009012.76</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="56">
@@ -18477,19 +18477,19 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso</t>
+          <t>Pará</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>5169203.96</v>
+        <v>5419859.45</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="57">
@@ -18500,19 +18500,19 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Mato Grosso</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>4516384.5</v>
+        <v>5319203.96</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="58">
@@ -18523,19 +18523,19 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>4231307.76</v>
+        <v>4616384.5</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="59">
@@ -18558,7 +18558,7 @@
         <v>3592630</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="60">
@@ -18581,7 +18581,7 @@
         <v>3209590.49</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="61">
@@ -18601,10 +18601,10 @@
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>601985905.86</v>
+        <v>601862257.45</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>12.87</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="62">
@@ -18624,7 +18624,7 @@
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>403151237.63</v>
+        <v>403721718.11</v>
       </c>
       <c r="E62" s="12" t="n">
         <v>8.619999999999999</v>
@@ -18647,7 +18647,7 @@
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>366208564.37</v>
+        <v>366828564.37</v>
       </c>
       <c r="E63" s="12" t="n">
         <v>7.83</v>
@@ -18670,10 +18670,10 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>275348324.13</v>
+        <v>276474984.13</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="65">
@@ -18693,7 +18693,7 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>240187294.71</v>
+        <v>240276811.05</v>
       </c>
       <c r="E65" s="12" t="n">
         <v>5.13</v>
@@ -18716,10 +18716,10 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>227662148.98</v>
+        <v>228657933.98</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="67">
@@ -18739,7 +18739,7 @@
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>196145398.27</v>
+        <v>196405398.27</v>
       </c>
       <c r="E67" s="12" t="n">
         <v>4.19</v>
@@ -18762,7 +18762,7 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>178804423.24</v>
+        <v>178824423.24</v>
       </c>
       <c r="E68" s="12" t="n">
         <v>3.82</v>
@@ -18785,10 +18785,10 @@
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>169058674.29</v>
+        <v>170000338.29</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="70">
@@ -18808,10 +18808,10 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>159927269.27</v>
+        <v>161010312.76</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="71">
@@ -18831,7 +18831,7 @@
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>151566201.47</v>
+        <v>151796201.47</v>
       </c>
       <c r="E71" s="12" t="n">
         <v>3.24</v>
@@ -18854,10 +18854,10 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>144439181.64</v>
+        <v>144495261.64</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="73">
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>118383461.3</v>
+        <v>118483461.3</v>
       </c>
       <c r="E73" s="12" t="n">
         <v>2.53</v>
@@ -18900,7 +18900,7 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>117831939.45</v>
+        <v>118025647.45</v>
       </c>
       <c r="E74" s="12" t="n">
         <v>2.52</v>
@@ -18946,10 +18946,10 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>105885687.66</v>
+        <v>106127608.95</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="77">
@@ -18969,7 +18969,7 @@
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>103541965.53</v>
+        <v>103626077.83</v>
       </c>
       <c r="E77" s="12" t="n">
         <v>2.21</v>
@@ -18992,7 +18992,7 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>101968180.74</v>
+        <v>101981180.74</v>
       </c>
       <c r="E78" s="12" t="n">
         <v>2.18</v>
@@ -19038,7 +19038,7 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>96408328.98</v>
+        <v>96418328.98</v>
       </c>
       <c r="E80" s="12" t="n">
         <v>2.06</v>
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>96038119.08</v>
+        <v>96043529.08</v>
       </c>
       <c r="E81" s="12" t="n">
         <v>2.05</v>
@@ -19107,7 +19107,7 @@
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>90361210.48999999</v>
+        <v>90413267.13</v>
       </c>
       <c r="E83" s="12" t="n">
         <v>1.93</v>
@@ -19130,7 +19130,7 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>88404829.11</v>
+        <v>88504829.11</v>
       </c>
       <c r="E84" s="12" t="n">
         <v>1.89</v>
@@ -19222,10 +19222,10 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>83062724.62</v>
+        <v>83104130.48</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="89">
@@ -19245,10 +19245,10 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>586202407.04</v>
+        <v>596837953.77</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>23.38</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="90">
@@ -19268,10 +19268,10 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>163692040.49</v>
+        <v>164683280.01</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>6.53</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="91">
@@ -19291,10 +19291,10 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>154081573.55</v>
+        <v>156442101.35</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="92">
@@ -19314,10 +19314,10 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>126366850.9</v>
+        <v>127146823.16</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -19337,10 +19337,10 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>118592461.52</v>
+        <v>119731453.47</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>4.73</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="94">
@@ -19360,10 +19360,10 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>102684036.47</v>
+        <v>105018777.32</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>4.09</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="95">
@@ -19383,10 +19383,10 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>98840685.39</v>
+        <v>100772555.84</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="96">
@@ -19406,7 +19406,7 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>95775751.31</v>
+        <v>97133403.63</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>3.82</v>
@@ -19429,7 +19429,7 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>90621945.61</v>
+        <v>91767176.59999999</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>3.61</v>
@@ -19452,10 +19452,10 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>87084855.31</v>
+        <v>87685363</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="99">
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>83163697.64</v>
+        <v>83644136.72</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="100">
@@ -19498,10 +19498,10 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>77256447.73999999</v>
+        <v>78707049.53</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="101">
@@ -19521,10 +19521,10 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>72005073.73999999</v>
+        <v>72573697.29000001</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="102">
@@ -19544,10 +19544,10 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>68565335.68000001</v>
+        <v>68851162.08</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="103">
@@ -19567,10 +19567,10 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>64810137.51</v>
+        <v>66238723.53</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="104">
@@ -19590,10 +19590,10 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>61774777.62</v>
+        <v>62369707.4</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="105">
@@ -19604,19 +19604,19 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Mato Grosso</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>54880461.09</v>
+        <v>55859891.88</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="106">
@@ -19627,19 +19627,19 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>54848648.93</v>
+        <v>55239359.08</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="107">
@@ -19659,10 +19659,10 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>45507143.42</v>
+        <v>46220288.81</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="108">
@@ -19682,10 +19682,10 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>44490631.2</v>
+        <v>44590223.2</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="109">
@@ -19705,10 +19705,10 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>43822645.81</v>
+        <v>44252658.84</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="110">
@@ -19728,10 +19728,10 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>43511705.34</v>
+        <v>43680404.44</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="111">
@@ -19751,10 +19751,10 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>40626110.42</v>
+        <v>41867563.86</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="112">
@@ -19774,10 +19774,10 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>40317383.31</v>
+        <v>40670496.86</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="113">
@@ -19797,10 +19797,10 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>35355535.04</v>
+        <v>35469082.96</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="114">
@@ -19820,7 +19820,7 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>26822083.87</v>
+        <v>27151030.86</v>
       </c>
       <c r="E114" s="12" t="n">
         <v>1.07</v>
@@ -19843,10 +19843,10 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>24957278.21</v>
+        <v>25234984.45</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="116">
@@ -19889,10 +19889,10 @@
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>110373851.49</v>
+        <v>112932704.43</v>
       </c>
       <c r="E117" s="12" t="n">
-        <v>22.29</v>
+        <v>22.26</v>
       </c>
     </row>
     <row r="118">
@@ -19912,10 +19912,10 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>38938122.65</v>
+        <v>39584273.13</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>7.86</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="119">
@@ -19935,10 +19935,10 @@
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>37252502.29</v>
+        <v>37649956.02</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>7.52</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="120">
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>34427247.9</v>
+        <v>35799123.4</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>6.95</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="121">
@@ -19981,7 +19981,7 @@
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>23734193.34</v>
+        <v>24309635.44</v>
       </c>
       <c r="E121" s="12" t="n">
         <v>4.79</v>
@@ -20004,10 +20004,10 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>20646040.46</v>
+        <v>21016820.15</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="123">
@@ -20027,10 +20027,10 @@
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>18937120.69</v>
+        <v>19037783.19</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="124">
@@ -20050,10 +20050,10 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>17734636.06</v>
+        <v>17975636.06</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="125">
@@ -20073,10 +20073,10 @@
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>16865358.18</v>
+        <v>17441267.97</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="126">
@@ -20087,19 +20087,19 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Distrito Federal</t>
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>14775360.85</v>
+        <v>15485814.04</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="127">
@@ -20110,19 +20110,19 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Distrito Federal</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>14757527.38</v>
+        <v>15239259.46</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
@@ -20133,19 +20133,19 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>14651000.96</v>
+        <v>15060246.01</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="129">
@@ -20156,19 +20156,19 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
-        <v>14125246.01</v>
+        <v>14943250.85</v>
       </c>
       <c r="E129" s="12" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="130">
@@ -20188,10 +20188,10 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>13848477.88</v>
+        <v>13923985.88</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="131">
@@ -20211,10 +20211,10 @@
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>12318590.83</v>
+        <v>12697708.78</v>
       </c>
       <c r="E131" s="12" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="132">
@@ -20225,19 +20225,19 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso do Sul</t>
+          <t>Pará</t>
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>11297770.52</v>
+        <v>11358166.99</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="133">
@@ -20248,19 +20248,19 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Pará</t>
+          <t>Mato Grosso do Sul</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>11195566.99</v>
+        <v>11104327.51</v>
       </c>
       <c r="E133" s="12" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="134">
@@ -20280,10 +20280,10 @@
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>10543060.75</v>
+        <v>10760260.75</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="135">
@@ -20303,10 +20303,10 @@
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>9005970.9</v>
+        <v>9051077.49</v>
       </c>
       <c r="E135" s="12" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="136">
@@ -20317,19 +20317,19 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>8521620.23</v>
+        <v>8785853.529999999</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="137">
@@ -20340,19 +20340,19 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Acre</t>
+          <t>Piauí</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>7211958.47</v>
+        <v>8542970.23</v>
       </c>
       <c r="E137" s="12" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="138">
@@ -20363,19 +20363,19 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Roraima</t>
+          <t>Acre</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>7018890.22</v>
+        <v>7247958.47</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="139">
@@ -20386,19 +20386,19 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Roraima</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
-        <v>7000038.53</v>
+        <v>7018890.22</v>
       </c>
       <c r="E139" s="12" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="140">
@@ -20418,10 +20418,10 @@
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>6718357.4</v>
+        <v>6781567.4</v>
       </c>
       <c r="E140" s="12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="141">
@@ -20441,10 +20441,10 @@
         </is>
       </c>
       <c r="D141" s="6" t="n">
-        <v>5431148.95</v>
+        <v>5494595.45</v>
       </c>
       <c r="E141" s="12" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="142">
@@ -20464,10 +20464,10 @@
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>4800508.97</v>
+        <v>4960358.97</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="143">
@@ -20487,10 +20487,10 @@
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>3077644.5</v>
+        <v>3089144.5</v>
       </c>
       <c r="E143" s="12" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="144">
@@ -20510,10 +20510,10 @@
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>60746111.95</v>
+        <v>62026518.17</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>16.01</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="145">
@@ -20533,10 +20533,10 @@
         </is>
       </c>
       <c r="D145" s="6" t="n">
-        <v>47811514.62</v>
+        <v>49286152.96</v>
       </c>
       <c r="E145" s="12" t="n">
-        <v>12.6</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="146">
@@ -20556,10 +20556,10 @@
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>22798262.59</v>
+        <v>23396637.59</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>6.01</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="147">
@@ -20579,10 +20579,10 @@
         </is>
       </c>
       <c r="D147" s="6" t="n">
-        <v>21133051.62</v>
+        <v>22465067.39</v>
       </c>
       <c r="E147" s="12" t="n">
-        <v>5.57</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="148">
@@ -20602,10 +20602,10 @@
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>20792726.19</v>
+        <v>21831558.84</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>5.48</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="149">
@@ -20625,10 +20625,10 @@
         </is>
       </c>
       <c r="D149" s="6" t="n">
-        <v>19718158.21</v>
+        <v>20716664.26</v>
       </c>
       <c r="E149" s="12" t="n">
-        <v>5.2</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="150">
@@ -20648,10 +20648,10 @@
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>18474141.43</v>
+        <v>19462692.43</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>4.87</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="151">
@@ -20671,10 +20671,10 @@
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>17645428.26</v>
+        <v>18344794.54</v>
       </c>
       <c r="E151" s="12" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="152">
@@ -20694,10 +20694,10 @@
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>14876180.03</v>
+        <v>14993807.53</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>3.92</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="153">
@@ -20717,10 +20717,10 @@
         </is>
       </c>
       <c r="D153" s="6" t="n">
-        <v>14282932.66</v>
+        <v>14726682.66</v>
       </c>
       <c r="E153" s="12" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="154">
@@ -20740,10 +20740,10 @@
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>13241979.9</v>
+        <v>13904102.53</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>3.49</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="155">
@@ -20754,19 +20754,19 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Pernambuco</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
-        <v>11897575.68</v>
+        <v>12728825.41</v>
       </c>
       <c r="E155" s="12" t="n">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="156">
@@ -20777,19 +20777,19 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Pernambuco</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>11860483.41</v>
+        <v>12260635.68</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="157">
@@ -20809,10 +20809,10 @@
         </is>
       </c>
       <c r="D157" s="6" t="n">
-        <v>10167601.99</v>
+        <v>10427129.8</v>
       </c>
       <c r="E157" s="12" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="158">
@@ -20832,10 +20832,10 @@
         </is>
       </c>
       <c r="D158" s="6" t="n">
-        <v>9439211.369999999</v>
+        <v>9539851.369999999</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="159">
@@ -20855,10 +20855,10 @@
         </is>
       </c>
       <c r="D159" s="6" t="n">
-        <v>7902795</v>
+        <v>8424666.109999999</v>
       </c>
       <c r="E159" s="12" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="160">
@@ -20869,19 +20869,19 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
       <c r="D160" s="6" t="n">
-        <v>7609400.6</v>
+        <v>7878117.78</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -20892,19 +20892,19 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Presidenciáveis, circunscrição nacional</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
-        <v>7422982.52</v>
+        <v>7788045.6</v>
       </c>
       <c r="E161" s="12" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="162">
@@ -20924,10 +20924,10 @@
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>6522326.8</v>
+        <v>6779926.8</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="163">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="D163" s="6" t="n">
-        <v>6307300.04</v>
+        <v>6529400.04</v>
       </c>
       <c r="E163" s="12" t="n">
         <v>1.66</v>
@@ -20970,10 +20970,10 @@
         </is>
       </c>
       <c r="D164" s="6" t="n">
-        <v>5558609.92</v>
+        <v>5567609.92</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="165">
@@ -20993,10 +20993,10 @@
         </is>
       </c>
       <c r="D165" s="6" t="n">
-        <v>4797225.81</v>
+        <v>4903575.81</v>
       </c>
       <c r="E165" s="12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="166">
@@ -21007,19 +21007,19 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Alagoas</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="D166" s="6" t="n">
-        <v>4277866.79</v>
+        <v>4493457.08</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="167">
@@ -21030,19 +21030,19 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Paraíba</t>
+          <t>Alagoas</t>
         </is>
       </c>
       <c r="D167" s="6" t="n">
-        <v>4273057.08</v>
+        <v>4491866.79</v>
       </c>
       <c r="E167" s="12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="168">
@@ -21062,10 +21062,10 @@
         </is>
       </c>
       <c r="D168" s="6" t="n">
-        <v>3071962.49</v>
+        <v>3107862.49</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="169">
@@ -21085,10 +21085,10 @@
         </is>
       </c>
       <c r="D169" s="6" t="n">
-        <v>2580939.35</v>
+        <v>2616969.35</v>
       </c>
       <c r="E169" s="12" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="170">
@@ -21108,10 +21108,10 @@
         </is>
       </c>
       <c r="D170" s="6" t="n">
-        <v>2537388.97</v>
+        <v>2571688.97</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="171">
@@ -21131,7 +21131,7 @@
         </is>
       </c>
       <c r="D171" s="6" t="n">
-        <v>1723883.36</v>
+        <v>1750608.36</v>
       </c>
       <c r="E171" s="12" t="n">
         <v>0.45</v>
@@ -22428,28 +22428,28 @@
     <row r="228">
       <c r="A228" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-22.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-23.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: a serie de fornecedores cobre 67.9% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
+          <t>Nota 1: a serie de fornecedores cobre 68.3% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="10" t="inlineStr">
         <is>
-          <t>Nota 2: a serie por UF do doador cobre apenas 8.6% do valor doado, porque o TSE nao publica a UF do doador pessoa fisica. Para leitura integral use a serie por UF do candidato que recebeu.</t>
+          <t>Nota 2: a serie por UF do doador cobre apenas 8.7% do valor doado, porque o TSE nao publica a UF do doador pessoa fisica. Para leitura integral use a serie por UF do candidato que recebeu.</t>
         </is>
       </c>
     </row>
@@ -22549,10 +22549,10 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>413094585.02</v>
+        <v>417700568.62</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>16859960.41</v>
+        <v>17769580.74</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>4556010.95</v>
@@ -22561,16 +22561,16 @@
         <v>7330302.17</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>24190262.58</v>
+        <v>25099882.91</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>18.64</v>
+        <v>18.74</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>417650595.97</v>
+        <v>422256579.57</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>22.62</v>
+        <v>22.54</v>
       </c>
     </row>
     <row r="6">
@@ -22580,28 +22580,28 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>293932257.93</v>
+        <v>300453182.19</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>17765228.44</v>
+        <v>18444676.62</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>15391719.88</v>
+        <v>15420541.37</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>4710150.94</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>22475379.38</v>
+        <v>23154827.56</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>17.32</v>
+        <v>17.29</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>309323977.81</v>
+        <v>315873723.56</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>16.76</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="7">
@@ -22611,7 +22611,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>122834209.66</v>
+        <v>123177544.66</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1437422.59</v>
@@ -22620,19 +22620,19 @@
         <v>4405616.89</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>13489786.95</v>
+        <v>13634436.95</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>14927209.54</v>
+        <v>15071859.54</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>11.5</v>
+        <v>11.25</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>127239826.55</v>
+        <v>127583161.55</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.89</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="8">
@@ -22642,10 +22642,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>165388958.68</v>
+        <v>168597117.68</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>13694237.88</v>
+        <v>14353368.52</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>317350</v>
@@ -22654,16 +22654,16 @@
         <v>162830.33</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>13857068.21</v>
+        <v>14516198.85</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>10.68</v>
+        <v>10.84</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>165706308.68</v>
+        <v>168914467.68</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>8.98</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="9">
@@ -22673,28 +22673,28 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>93780812.62</v>
+        <v>94461137.41</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5818996.63</v>
+        <v>6168996.63</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>10048725.59</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>6852138.82</v>
+        <v>7246108.82</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>12671135.45</v>
+        <v>13415105.45</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>9.76</v>
+        <v>10.01</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>103829538.21</v>
+        <v>104509863</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.62</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="10">
@@ -22704,10 +22704,10 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>123637607.42</v>
+        <v>124593904.06</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>4128526.44</v>
+        <v>4161714.81</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>2145619.45</v>
@@ -22716,16 +22716,16 @@
         <v>2068680.85</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>6197207.29</v>
+        <v>6230395.66</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>4.78</v>
+        <v>4.65</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>125783226.87</v>
+        <v>126739523.51</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>6.81</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="11">
@@ -22735,10 +22735,10 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>134041754.3</v>
+        <v>137156254.97</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5915863.82</v>
+        <v>6038263.82</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>848977</v>
@@ -22747,16 +22747,16 @@
         <v>135747.66</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>6051611.48</v>
+        <v>6174011.48</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>4.66</v>
+        <v>4.61</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>134890731.3</v>
+        <v>138005231.97</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>7.31</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="12">
@@ -22766,10 +22766,10 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>52039532.75</v>
+        <v>52482608.92</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2000564.76</v>
+        <v>2360564.76</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>8707553.99</v>
@@ -22778,16 +22778,16 @@
         <v>3518340.69</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>5518905.45</v>
+        <v>5878905.45</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4.25</v>
+        <v>4.39</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>60747086.74</v>
+        <v>61190162.91</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="13">
@@ -22797,10 +22797,10 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>126674004.7</v>
+        <v>130661374.56</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>5015495.31</v>
+        <v>5198499.79</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>542259.41</v>
@@ -22809,16 +22809,16 @@
         <v>123368</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>5138863.31</v>
+        <v>5321867.79</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3.96</v>
+        <v>3.97</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>127216264.11</v>
+        <v>131203633.97</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>6.89</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -22828,10 +22828,10 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>59953191.66</v>
+        <v>60838400.87</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2013952.22</v>
+        <v>2065216.85</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>50040</v>
@@ -22840,13 +22840,13 @@
         <v>904244.78</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>2918197</v>
+        <v>2969461.63</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>60003231.66</v>
+        <v>60888440.87</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>3.25</v>
@@ -22859,10 +22859,10 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>44940306.19</v>
+        <v>45145376.44</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>1736737.76</v>
+        <v>1791749.66</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>752452.6</v>
@@ -22871,16 +22871,16 @@
         <v>1153315.55</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2890053.31</v>
+        <v>2945065.21</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>45692758.79</v>
+        <v>45897829.04</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="16">
@@ -22890,10 +22890,10 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>31825332.08</v>
+        <v>32068748.59</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2098447.07</v>
+        <v>2103947.07</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>212885.86</v>
@@ -22902,16 +22902,16 @@
         <v>595304.64</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>2693751.71</v>
+        <v>2699251.71</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>32038217.94</v>
+        <v>32281634.45</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="17">
@@ -22921,13 +22921,13 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>18241100.6</v>
+        <v>18418714.77</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>1297649.49</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>145297.42</v>
+        <v>284297.42</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>1210842.82</v>
@@ -22936,10 +22936,10 @@
         <v>2508492.31</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>18386398.02</v>
+        <v>18703012.19</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>1</v>
@@ -22952,7 +22952,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>10037180.75</v>
+        <v>10157180.75</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>206100</v>
@@ -22967,13 +22967,13 @@
         <v>1505663</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>10804162.75</v>
+        <v>10924162.75</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="19">
@@ -22983,7 +22983,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>15020581.11</v>
+        <v>15056148.21</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>648502.09</v>
@@ -22998,13 +22998,13 @@
         <v>1146629.04</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>15020581.11</v>
+        <v>15056148.21</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
@@ -23014,25 +23014,25 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>17853230.93</v>
+        <v>18183087.44</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>871286.49</v>
+        <v>943536.67</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>25327.5</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>41691.01</v>
+        <v>48767.64</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>912977.5</v>
+        <v>992304.3100000001</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>17878558.43</v>
+        <v>18208414.94</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0.97</v>
@@ -23045,10 +23045,10 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>9140166.529999999</v>
+        <v>9178250.33</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>492836.27</v>
+        <v>527606.27</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>16144.98</v>
@@ -23057,78 +23057,78 @@
         <v>177284.49</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>670120.76</v>
+        <v>704890.76</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>9156311.51</v>
+        <v>9194395.310000001</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Produção de jingles, vinhetas e slogans</t>
+          <t>Serviços próprios prestados por terceiros</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>11715368.46</v>
+        <v>8895466.42</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>632203.35</v>
+        <v>664343.29</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>56000</v>
+        <v>31000</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>4500</v>
+        <v>20500</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>636703.35</v>
+        <v>684843.29</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>11771368.46</v>
+        <v>8926466.42</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.64</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Serviços próprios prestados por terceiros</t>
+          <t>Produção de jingles, vinhetas e slogans</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>8859991.42</v>
+        <v>11818859.46</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>610843.29</v>
+        <v>646403.35</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>31000</v>
+        <v>56000</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>20500</v>
+        <v>4500</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>631343.29</v>
+        <v>650903.35</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>0.49</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>8890991.42</v>
+        <v>11874859.46</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.48</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="24">
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>6684142.27</v>
+        <v>6706385.4</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>386623.09</v>
@@ -23150,13 +23150,13 @@
         <v>151786.7</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>538409.79</v>
+        <v>538409.7899999999</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>6684142.27</v>
+        <v>6706385.4</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0.36</v>
@@ -23169,7 +23169,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>8664975.24</v>
+        <v>8704190.66</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>313333.95</v>
@@ -23184,13 +23184,13 @@
         <v>313333.95</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>9595975.24</v>
+        <v>9635190.66</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="26">
@@ -23200,10 +23200,10 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>4038567.18</v>
+        <v>4078798.49</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>227235.58</v>
+        <v>235828.57</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>19500</v>
@@ -23212,13 +23212,13 @@
         <v>29510.94</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>256746.52</v>
+        <v>265339.51</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>4058067.18</v>
+        <v>4098298.49</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0.22</v>
@@ -23227,63 +23227,63 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Pré-instalação física de comitê de campanha</t>
+          <t>Publicidade por jornais e revistas</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>2942880.05</v>
+        <v>4274244</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>230349.76</v>
+        <v>233645.92</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>230349.76</v>
+        <v>234065.92</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>2942880.05</v>
+        <v>4274244</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Publicidade por jornais e revistas</t>
+          <t>Pré-instalação física de comitê de campanha</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>3995545</v>
+        <v>3016969.02</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>224946.92</v>
+        <v>230349.76</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>225366.92</v>
+        <v>230349.76</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>0.17</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>3995545</v>
+        <v>3016969.02</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="29">
@@ -23293,25 +23293,25 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>2039581.39</v>
+        <v>2044736.13</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>153455.82</v>
+        <v>155445.62</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>8076.8</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>48965.99000000001</v>
+        <v>48965.99</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>202421.81</v>
+        <v>204411.61</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>2047658.19</v>
+        <v>2052812.93</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0.11</v>
@@ -23324,10 +23324,10 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>9115499.390000001</v>
+        <v>9555940.51</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>153192.32</v>
+        <v>160238.59</v>
       </c>
       <c r="D30" s="6" t="n">
         <v>8104.55</v>
@@ -23336,78 +23336,78 @@
         <v>0</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>153192.32</v>
+        <v>160238.59</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>0.12</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>9123603.939999999</v>
+        <v>9564045.060000001</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Despesas com Hospedagem</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>1082067.54</v>
+        <v>599763.71</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>24244.69</v>
+        <v>77183.94</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0</v>
+        <v>3658.83</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>38153.96</v>
+        <v>0</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>62398.65</v>
+        <v>77183.94</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>1082067.54</v>
+        <v>603422.5399999999</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Despesas com Hospedagem</t>
+          <t>Água</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>597130.71</v>
+        <v>1087204.02</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>53384.75</v>
+        <v>24244.69</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3658.83</v>
+        <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0</v>
+        <v>38153.96</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>53384.75</v>
+        <v>62398.65</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>600789.5399999999</v>
+        <v>1087204.02</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="33">
@@ -23423,7 +23423,7 @@
         <v>904.1</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>51744.89000000001</v>
+        <v>51744.89</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>40426.19</v>
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>842311.55</v>
+        <v>845811.55</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>39273.94</v>
@@ -23466,7 +23466,7 @@
         <v>0.03</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>842311.55</v>
+        <v>845811.55</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0.05</v>
@@ -23479,7 +23479,7 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>1150909.97</v>
+        <v>1154409.97</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>35630</v>
@@ -23497,7 +23497,7 @@
         <v>0.03</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1150909.97</v>
+        <v>1154409.97</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0.06</v>
@@ -23541,25 +23541,25 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>245324.25</v>
+        <v>249562.06</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>11043.01</v>
+        <v>11122.11</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>88943.83</v>
+        <v>89167.28999999999</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>7444.64</v>
+        <v>7451.54</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>18487.65</v>
+        <v>18573.65</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>334268.08</v>
+        <v>338729.35</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0.02</v>
@@ -23572,7 +23572,7 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>17185.42</v>
+        <v>17696.69</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>0</v>
@@ -23590,7 +23590,7 @@
         <v>0.01</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>17185.42</v>
+        <v>17696.69</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
@@ -23686,7 +23686,7 @@
         <v>835292.89</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="42">
@@ -23754,14 +23754,14 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-22.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-23.</t>
         </is>
       </c>
     </row>
@@ -23802,9 +23802,9 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -23914,34 +23914,34 @@
         <v>4897808042.51</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1035448468.52</v>
+        <v>1044635855.12</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>17.97</v>
+        <v>17.99</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>866099139.6800001</v>
+        <v>867349139.6800001</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>18.51</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>65276468.02</v>
+        <v>70198397.90000001</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>16.15</v>
+        <v>16.78</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>12185019.15</v>
+        <v>12378760.7</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>59158312.15</v>
+        <v>61483622.09</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>694979864.48</v>
+        <v>697619240.59</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>89.95</v>
+        <v>89.75</v>
       </c>
     </row>
     <row r="6">
@@ -23960,34 +23960,34 @@
         <v>771218822.24</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>610172112.4</v>
+        <v>612723087.3099999</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>10.59</v>
+        <v>10.55</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>535297615.6</v>
+        <v>535480359.6</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>11.44</v>
+        <v>11.43</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>3939848.35</v>
+        <v>3890184.35</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>7931808.73</v>
+        <v>8117228.23</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>43712087.74</v>
+        <v>45257799.8</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>411753442.11</v>
+        <v>415100672.67</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>88.37</v>
+        <v>88.03</v>
       </c>
     </row>
     <row r="7">
@@ -24006,34 +24006,34 @@
         <v>1817691708.82</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>575343482.72</v>
+        <v>579884589.98</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>511476297.05</v>
+        <v>511775635.54</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>10.93</v>
+        <v>10.92</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>36394219.62</v>
+        <v>39697924.62</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>9.01</v>
+        <v>9.49</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4239853.56</v>
+        <v>4361653.56</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>15178866.53</v>
+        <v>15703623.53</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>372957882.82</v>
+        <v>374850031.99</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>95.22</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -24052,34 +24052,34 @@
         <v>2533019885.72</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>546477353.15</v>
+        <v>549389459.22</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>9.48</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>419449461.46</v>
+        <v>419534020.85</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>8.970000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>29015867.67</v>
+        <v>29916308.28</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>7.18</v>
+        <v>7.15</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>11080792.88</v>
+        <v>11485499.48</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>49737816.57</v>
+        <v>50868740.12</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>401095092.77</v>
+        <v>405162532.82</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>82.06</v>
+        <v>81.81</v>
       </c>
     </row>
     <row r="9">
@@ -24098,34 +24098,34 @@
         <v>2484193186.63</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>500065628.82</v>
+        <v>503260188.17</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>8.68</v>
+        <v>8.67</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>337474242.04</v>
+        <v>337975023.19</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>7.21</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>102926220.25</v>
+        <v>103247710.91</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>25.47</v>
+        <v>24.68</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>7342481.3</v>
+        <v>7190018.63</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>37997042.78</v>
+        <v>38790934.79</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>329547076.13</v>
+        <v>332502758.14</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>88.06999999999999</v>
+        <v>87.67</v>
       </c>
     </row>
     <row r="10">
@@ -24144,34 +24144,34 @@
         <v>1294302106.67</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>487214457.57</v>
+        <v>489235505.5</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>8.449999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>410483533.57</v>
+        <v>410783533.57</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>8.77</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>44350427.8</v>
+        <v>45471427.8</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>10.98</v>
+        <v>10.87</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>4397674.87</v>
+        <v>4436890.8</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>18548590.77</v>
+        <v>18874422.77</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>276751805.99</v>
+        <v>277340985.93</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>93.34999999999999</v>
+        <v>93.26000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -24190,34 +24190,34 @@
         <v>3339120580.55</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>470669176.46</v>
+        <v>474305324.68</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>8.17</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>393740018.84</v>
+        <v>394292811.04</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>8.42</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>14764935.7</v>
+        <v>15172435.7</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>10057311.12</v>
+        <v>10373701.12</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>37239358.57</v>
+        <v>39170608.59</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>274105271.99</v>
+        <v>276373975.29</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>86.79000000000001</v>
+        <v>86.33</v>
       </c>
     </row>
     <row r="12">
@@ -24236,34 +24236,34 @@
         <v>1839875005.9</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>249233732.86</v>
+        <v>251100294.7</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>219095412.57</v>
+        <v>219760928.91</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>2369891.06</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>5155469.43</v>
+        <v>5259669.43</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>17128482.66</v>
+        <v>17841559.66</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>155820306.8</v>
+        <v>156865147.17</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>88.86</v>
+        <v>88.45999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -24282,7 +24282,7 @@
         <v>1457794419.27</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>217913592.06</v>
+        <v>219350106.51</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>3.78</v>
@@ -24294,22 +24294,22 @@
         <v>3.56</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>40799408.8</v>
+        <v>41950508.8</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>10.1</v>
+        <v>10.03</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>1709698.63</v>
+        <v>1774257.58</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>6520873.95</v>
+        <v>6626729.45</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>123341160.01</v>
+        <v>124157970.91</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>95.20999999999999</v>
+        <v>95.12</v>
       </c>
     </row>
     <row r="14">
@@ -24328,13 +24328,13 @@
         <v>930727493.99</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>186158214.82</v>
+        <v>187574990.34</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>3.23</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>141849945.82</v>
+        <v>142146552.84</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>3.03</v>
@@ -24343,19 +24343,19 @@
         <v>2953599.16</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>6835119.85</v>
+        <v>7014525.350000001</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>22388758.27</v>
+        <v>23138058.27</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>132375998.5</v>
+        <v>134184349.02</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>77.79000000000001</v>
+        <v>77.36</v>
       </c>
     </row>
     <row r="15">
@@ -24374,34 +24374,34 @@
         <v>2591553797.35</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>176274507.28</v>
+        <v>179262240.05</v>
       </c>
       <c r="F15" s="6" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>143299891.45</v>
+      </c>
+      <c r="H15" s="6" t="n">
         <v>3.06</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>141839891.45</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>3.03</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>4283385.55</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>8298928.73</v>
+        <v>8477122.73</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>15219876.96</v>
+        <v>16596703.3</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>109368440.46</v>
+        <v>109917170</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>82.90000000000001</v>
+        <v>82.33</v>
       </c>
     </row>
     <row r="16">
@@ -24420,34 +24420,34 @@
         <v>139488473.87</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>130084653.97</v>
+        <v>130384652.77</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>121940448.43</v>
+        <v>122042724.53</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>2.61</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1748418.34</v>
+        <v>1770355.26</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>436729.11</v>
+        <v>466729.11</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>2526278.45</v>
+        <v>2622419.23</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>80379580.69</v>
+        <v>80473605.36</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>95.08</v>
+        <v>94.95999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -24466,34 +24466,34 @@
         <v>1884009041.62</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>117148915.83</v>
+        <v>120000384.18</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>34045473.66</v>
+        <v>34044523.66</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>0.73</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>36685118.53</v>
+        <v>38401753.65</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>9.08</v>
+        <v>9.18</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>3963837.2</v>
+        <v>4220947.2</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>18682253.16</v>
+        <v>19400339.81</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>70922844.64</v>
+        <v>72246423.42</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>60.38</v>
+        <v>60.37</v>
       </c>
     </row>
     <row r="18">
@@ -24512,34 +24512,34 @@
         <v>577531754.64</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>84232256.77</v>
+        <v>84465256.77</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>64972751.35</v>
+        <v>64998751.35</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>1.39</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>10841715.09</v>
+        <v>10941715.09</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>1776609.77</v>
+        <v>1821609.77</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>4557004.68</v>
+        <v>4619004.68</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>48636765.51</v>
+        <v>48688078.98</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>90.01000000000001</v>
+        <v>89.91</v>
       </c>
     </row>
     <row r="19">
@@ -24558,16 +24558,16 @@
         <v>280452197.14</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>81821380.38</v>
+        <v>82297680.38</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>1.42</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>78736279.77</v>
+        <v>79086279.77</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>824000</v>
@@ -24576,16 +24576,16 @@
         <v>0.2</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>579449.24</v>
+        <v>687049.24</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>1331633.25</v>
+        <v>1350333.25</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>38575082.05</v>
+        <v>39652317.97</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>97.23999999999999</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -24604,34 +24604,34 @@
         <v>1071997156.04</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>77089474.98999999</v>
+        <v>78629364.98999999</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>61671850.94</v>
+        <v>62171850.94</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>2839298.9</v>
+        <v>3239598.9</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>3049262.3</v>
+        <v>3313262.3</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>7532240.63</v>
+        <v>7889221.63</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>46461229.02</v>
+        <v>46741986.22</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>83.68000000000001</v>
+        <v>83.19</v>
       </c>
     </row>
     <row r="21">
@@ -24650,10 +24650,10 @@
         <v>81485614.53</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>67763294.56</v>
+        <v>67958830.34999999</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>60288837.28</v>
@@ -24665,19 +24665,19 @@
         <v>2942529.01</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>580043.52</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>1967888.31</v>
+        <v>2055359.42</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>41728007.88</v>
+        <v>42135971.37</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>93.31</v>
+        <v>93.04000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -24696,7 +24696,7 @@
         <v>328303892.2</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>52671066.35</v>
+        <v>52884166.35</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>0.91</v>
@@ -24714,108 +24714,108 @@
         <v>0.04</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>2130587.16</v>
+        <v>2161087.16</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>5969166.95</v>
+        <v>6151766.95</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>36886529.66</v>
+        <v>37371402</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>81.23</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>REDE</t>
+          <t>CIDADANIA</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>355</v>
+        <v>158</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>1.69</v>
+        <v>0.75</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>587079065.02</v>
+        <v>121249861.96</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>30259577.49</v>
+        <v>30303634.71</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>27567586.54</v>
+        <v>27746497.8</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>0.59</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>432960.64</v>
+        <v>494133.92</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>380089.36</v>
+        <v>315936.82</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>1360250.05</v>
+        <v>864138.79</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>15834636.72</v>
+        <v>7405965.88</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>92.53</v>
+        <v>93.19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>CIDADANIA</t>
+          <t>REDE</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>158</v>
+        <v>355</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>0.75</v>
+        <v>1.69</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>121249861.96</v>
+        <v>587079065.02</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>30182372.41</v>
+        <v>30294261.99</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>0.52</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>27628235.5</v>
+        <v>27574594.54</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0.59</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>494133.92</v>
+        <v>432960.64</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>312936.82</v>
+        <v>395099.86</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>864138.79</v>
+        <v>1372916.05</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>7352797.37</v>
+        <v>15851247.77</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>93.17</v>
+        <v>92.45</v>
       </c>
     </row>
     <row r="25">
@@ -24834,7 +24834,7 @@
         <v>286783318.5</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>8438800.1</v>
+        <v>8643100.1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>0.15</v>
@@ -24855,13 +24855,13 @@
         <v>1480553.46</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>4751402.3</v>
+        <v>4955702.3</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>5384564.67</v>
+        <v>5490999.85</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>24.35</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="26">
@@ -24880,7 +24880,7 @@
         <v>184054953.85</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>8219868.98</v>
+        <v>8221846.24</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>0.14</v>
@@ -24904,10 +24904,10 @@
         <v>1100022.97</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>4549362.47</v>
+        <v>4549401.76</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>39.84</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="27">
@@ -24926,7 +24926,7 @@
         <v>592432021.5700001</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>6403152.22</v>
+        <v>6552125.22</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>0.11</v>
@@ -24944,16 +24944,16 @@
         <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>1263278.09</v>
+        <v>1349774.09</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>3016618.4</v>
+        <v>3078595.4</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>5631841.08</v>
+        <v>5889991.74</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>31.56</v>
+        <v>30.84</v>
       </c>
     </row>
     <row r="28">
@@ -24972,7 +24972,7 @@
         <v>652684016.89</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>5104505.56</v>
+        <v>5147742.56</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>0.09</v>
@@ -24990,16 +24990,16 @@
         <v>0.01</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>666234.95</v>
+        <v>673576.95</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>1239100.88</v>
+        <v>1270770.88</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>2742103.33</v>
+        <v>2754115.35</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>57.46</v>
+        <v>56.98</v>
       </c>
     </row>
     <row r="29">
@@ -25018,7 +25018,7 @@
         <v>26021399.15</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>3257582.84</v>
+        <v>3258282.84</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>0.06</v>
@@ -25039,13 +25039,13 @@
         <v>24057.29</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>84426.55</v>
+        <v>85126.55</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>2652560.61</v>
+        <v>2739560.61</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>95.56</v>
+        <v>95.54000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -25064,7 +25064,7 @@
         <v>463597846.48</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>2862381.34</v>
+        <v>3092398.84</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>0.05</v>
@@ -25082,13 +25082,13 @@
         <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>1613480.18</v>
+        <v>1656880.18</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>1121321.9</v>
+        <v>1307939.4</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>2360935.23</v>
+        <v>2432472.24</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>0</v>
@@ -25156,13 +25156,13 @@
         <v>16313701.99</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>1187520.8</v>
+        <v>1205772.96</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>762113.54</v>
+        <v>778373.54</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>0.02</v>
@@ -25177,13 +25177,13 @@
         <v>7051.67</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>142532.89</v>
+        <v>143705.05</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>996428.98</v>
+        <v>997156.2899999999</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>64.18000000000001</v>
+        <v>64.55</v>
       </c>
     </row>
     <row r="33">
@@ -25248,7 +25248,7 @@
         <v>4118169.08</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>64350.08</v>
+        <v>65618.08</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>0</v>
@@ -25272,7 +25272,7 @@
         <v>20130</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>64086.61</v>
+        <v>64130.06</v>
       </c>
       <c r="N34" s="9" t="n">
         <v>0</v>
@@ -25281,14 +25281,14 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-22.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-23.</t>
         </is>
       </c>
     </row>
@@ -25337,7 +25337,7 @@
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25453,19 +25453,19 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>4328942.649999999</v>
+        <v>4348984.35</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>5000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>2105909.01</v>
+        <v>2125950.71</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>1044739.18</v>
@@ -25654,41 +25654,41 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>NIKOLAS FERREIRA</t>
+          <t>KIKO CAPUTO</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO FEDERAL</t>
+          <t>GOVERNADOR</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1352759.23</v>
+        <v>1643000</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0</v>
+        <v>635500</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0</v>
+        <v>38.68</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1285055.01</v>
+        <v>1007500</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>67704.22</v>
+        <v>0</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
@@ -25700,50 +25700,50 @@
         <v>0</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>1231692.85</v>
+        <v>1001717.87</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1016424.55</v>
+        <v>464933.24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>KIKO CAPUTO</t>
+          <t>NIKOLAS FERREIRA</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>GOVERNADOR</t>
+          <t>DEPUTADO FEDERAL</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1235500</v>
+        <v>1502759.23</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>435500</v>
+        <v>0</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>35.25</v>
+        <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>800000</v>
+        <v>1435055.01</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0</v>
+        <v>67704.22</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0</v>
@@ -25755,10 +25755,10 @@
         <v>0</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>1001717.87</v>
+        <v>1235957.85</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>464933.24</v>
+        <v>1016424.55</v>
       </c>
     </row>
     <row r="11">
@@ -26039,7 +26039,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>GUSTAVO VALADARES</t>
+          <t>BOTELHO</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -26049,52 +26049,52 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>926350</v>
+        <v>931174.52</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>214700</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0</v>
+        <v>23.06</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>555350</v>
+        <v>516474.52</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>370000</v>
+        <v>200000</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0</v>
+        <v>71374.52</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>233638</v>
+        <v>744922.8</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>215638</v>
+        <v>474354.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>BOTELHO</t>
+          <t>GUSTAVO VALADARES</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -26104,46 +26104,46 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>926174.52</v>
+        <v>926350</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>214700</v>
+        <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>23.18</v>
+        <v>0</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>511474.52</v>
+        <v>555350</v>
       </c>
       <c r="J17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>200000</v>
+        <v>370000</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>71374.52</v>
+        <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>744922.8</v>
+        <v>233638</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>461854.52</v>
+        <v>215638</v>
       </c>
     </row>
     <row r="18">
@@ -26281,7 +26281,7 @@
         <v>870184.7200000001</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>114951</v>
@@ -26534,44 +26534,44 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>TAUILLO TEZELLI</t>
+          <t>VETERINÁRIO WILSON GRASSI</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO FEDERAL</t>
+          <t>PRESIDENTE</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>DEMOCRATA</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>800000</v>
+        <v>800150</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0</v>
+        <v>99.98</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="J25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>0</v>
@@ -26580,35 +26580,35 @@
         <v>0</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>335919.75</v>
+        <v>850019.66</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>78844.75</v>
+        <v>796019.66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>TAUILLO TEZELLI</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO ESTADUAL</t>
+          <t>DEPUTADO FEDERAL</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>786420</v>
+        <v>800000</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>0.01</v>
@@ -26620,62 +26620,62 @@
         <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>676420</v>
+        <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>189836.4</v>
+        <v>335919.75</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>132682.4</v>
+        <v>78844.75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>VETERINÁRIO WILSON GRASSI</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>PRESIDENTE</t>
+          <t>DEPUTADO ESTADUAL</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>DEMOCRATA</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>760150</v>
+        <v>786420</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>760000</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>99.98</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>150</v>
+        <v>676420</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>0</v>
@@ -26684,16 +26684,16 @@
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>808791.65</v>
+        <v>189836.4</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>754791.65</v>
+        <v>132682.4</v>
       </c>
     </row>
     <row r="28">
@@ -26803,7 +26803,7 @@
         <v>412937.49</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>85087.49000000001</v>
+        <v>85087.48999999999</v>
       </c>
     </row>
     <row r="30">
@@ -26828,7 +26828,7 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>705701.63</v>
+        <v>730701.63</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>0.01</v>
@@ -26840,7 +26840,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>705701.63</v>
+        <v>730701.63</v>
       </c>
       <c r="J30" s="6" t="n">
         <v>0</v>
@@ -26855,10 +26855,10 @@
         <v>36700</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>720265.88</v>
+        <v>775545.88</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>364315.88</v>
+        <v>399595.88</v>
       </c>
     </row>
     <row r="31">
@@ -27488,7 +27488,7 @@
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>614425.8200000001</v>
+        <v>619425.8200000001</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>0.01</v>
@@ -27497,10 +27497,10 @@
         <v>10000</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>496833.32</v>
+        <v>501833.32</v>
       </c>
       <c r="J42" s="6" t="n">
         <v>0</v>
@@ -27515,10 +27515,10 @@
         <v>132425.82</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>454678.68</v>
+        <v>465213.22</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>343087.35</v>
+        <v>353087.35</v>
       </c>
     </row>
     <row r="43">
@@ -27689,7 +27689,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>THIAGO BUHRER</t>
+          <t>NAY BARBALHO</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -27699,52 +27699,52 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>591700</v>
+        <v>592979.55</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>132600</v>
+        <v>521200</v>
       </c>
       <c r="J46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>458300</v>
+        <v>0</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>800</v>
+        <v>1779.55</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>26700</v>
+        <v>31379.55</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>267300.91</v>
+        <v>419988.34</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>90179.91</v>
+        <v>291988.34</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>LAERTE GOMES</t>
+          <t>THIAGO BUHRER</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -27754,7 +27754,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -27763,43 +27763,43 @@
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>587989</v>
+        <v>591700</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>577989</v>
+        <v>132600</v>
       </c>
       <c r="J47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0</v>
+        <v>458300</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>71189</v>
+        <v>26700</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>649754.7</v>
+        <v>267300.91</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>166105.7</v>
+        <v>90179.91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>NAY BARBALHO</t>
+          <t>LAERTE GOMES</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -27809,28 +27809,28 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>587979.55</v>
+        <v>587989</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>70000</v>
+        <v>10000</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>11.91</v>
+        <v>1.7</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>516200</v>
+        <v>577989</v>
       </c>
       <c r="J48" s="6" t="n">
         <v>0</v>
@@ -27839,22 +27839,22 @@
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>1779.55</v>
+        <v>0</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>31379.55</v>
+        <v>71189</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>419988.34</v>
+        <v>649754.7</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>291988.34</v>
+        <v>166105.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>FLORENCIO NETO</t>
+          <t>FERNANDO KRELLING</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -27864,7 +27864,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -27873,19 +27873,19 @@
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>577500</v>
+        <v>578000</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>577500</v>
+        <v>468000</v>
       </c>
       <c r="J49" s="6" t="n">
         <v>0</v>
@@ -27894,22 +27894,22 @@
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>12500</v>
+        <v>5000</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>357938.1</v>
+        <v>200301.7</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>293538.1</v>
+        <v>143745.11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>TITO TORRES</t>
+          <t>FLORENCIO NETO</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -27919,52 +27919,52 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>575985</v>
+        <v>577500</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>153610</v>
+        <v>577500</v>
       </c>
       <c r="J50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>397375</v>
+        <v>0</v>
       </c>
       <c r="L50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>3500</v>
+        <v>12500</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>432545.58</v>
+        <v>357938.1</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>248305.75</v>
+        <v>293538.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>PEDRO FERNANDES</t>
+          <t>TITO TORRES</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -27974,52 +27974,52 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>PRD</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>575066</v>
+        <v>575985</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>120000</v>
+        <v>25000</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>20.87</v>
+        <v>4.34</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>305166</v>
+        <v>153610</v>
       </c>
       <c r="J51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>0</v>
+        <v>397375</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>149900</v>
+        <v>0</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>30166</v>
+        <v>3500</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>602437.34</v>
+        <v>432545.58</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>373812.88</v>
+        <v>248305.75</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO VALLE</t>
+          <t>PEDRO FERNANDES</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -28029,52 +28029,52 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PRD</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>570224.1799999999</v>
+        <v>575066</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0</v>
+        <v>20.87</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>545840.1799999999</v>
+        <v>305166</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>24384</v>
+        <v>0</v>
       </c>
       <c r="K52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>0</v>
+        <v>149900</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0</v>
+        <v>30166</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>390238.06</v>
+        <v>602437.34</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>292988.06</v>
+        <v>373812.88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>FERNANDO KRELLING</t>
+          <t>FLAVIO VALLE</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -28084,46 +28084,46 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>568000</v>
+        <v>570224.1799999999</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>458000</v>
+        <v>545840.1799999999</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0</v>
+        <v>24384</v>
       </c>
       <c r="K53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>200301.7</v>
+        <v>390238.06</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>143745.11</v>
+        <v>292988.06</v>
       </c>
     </row>
     <row r="54">
@@ -28184,35 +28184,35 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-22 21:18:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-22.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-23.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: sao 2030 candidaturas com receita declarada e sem um real dos dois fundos publicos. que somam R$ 145.362.688,81 de receita.</t>
+          <t>Nota 1: sao 2040 candidaturas com receita declarada e sem um real dos dois fundos publicos. que somam R$ 149.138.125,90 de receita.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Nota 2: outras 4774 candidaturas NAO declararam receita alguma, das quais 924 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
+          <t>Nota 2: outras 4740 candidaturas NAO declararam receita alguma, das quais 924 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Nota 3: destas, 1282 nao receberam recurso partidario de especie alguma, nem mesmo fora dos dois fundos.</t>
+          <t>Nota 3: destas, 1288 nao receberam recurso partidario de especie alguma, nem mesmo fora dos dois fundos.</t>
         </is>
       </c>
     </row>
@@ -28360,16 +28360,16 @@
         <v>7.71</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>820269525.98</v>
+        <v>826957435.4</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>17.76</v>
+        <v>17.91</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>24.05</v>
+        <v>24.25</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>21.29</v>
+        <v>21.41</v>
       </c>
     </row>
     <row r="6">
@@ -28403,16 +28403,16 @@
         <v>11.18</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>471748294.21</v>
+        <v>474653061.28</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>21.98</v>
+        <v>22.12</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>28.8</v>
+        <v>28.98</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>23.91</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="7">
@@ -28446,16 +28446,16 @@
         <v>15.98</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>460939832.4</v>
+        <v>462959210.53</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>26.76</v>
+        <v>26.88</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>35.85</v>
+        <v>36.01</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>33.04</v>
+        <v>33.09</v>
       </c>
     </row>
     <row r="8">
@@ -28489,16 +28489,16 @@
         <v>10.81</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>317235433.55</v>
+        <v>319487309</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>21.31</v>
+        <v>21.46</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>28.02</v>
+        <v>28.22</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>25.67</v>
+        <v>25.77</v>
       </c>
     </row>
     <row r="9">
@@ -28532,16 +28532,16 @@
         <v>12.66</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>297783154.35</v>
+        <v>301361755.9</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>24.91</v>
+        <v>25.21</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>34.59</v>
+        <v>35</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>29.34</v>
+        <v>29.53</v>
       </c>
     </row>
     <row r="10">
@@ -28575,16 +28575,16 @@
         <v>12.35</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>290652931.56</v>
+        <v>292098182.19</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>25.87</v>
+        <v>26</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>34.09</v>
+        <v>34.26</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>30.02</v>
+        <v>30.05</v>
       </c>
     </row>
     <row r="11">
@@ -28618,16 +28618,16 @@
         <v>13.3</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>231985742.33</v>
+        <v>234886984.33</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>24.21</v>
+        <v>24.51</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>32.1</v>
+        <v>32.5</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>29.01</v>
+        <v>29.26</v>
       </c>
     </row>
     <row r="12">
@@ -28661,16 +28661,16 @@
         <v>10.18</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>213947162.63</v>
+        <v>216781721.91</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>30.56</v>
+        <v>30.96</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>26.52</v>
+        <v>26.73</v>
       </c>
     </row>
     <row r="13">
@@ -28704,16 +28704,16 @@
         <v>11.82</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>173997252.68</v>
+        <v>174505609.68</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>19.87</v>
+        <v>19.93</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>27.76</v>
+        <v>27.84</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>25.05</v>
+        <v>25.09</v>
       </c>
     </row>
     <row r="14">
@@ -28747,16 +28747,16 @@
         <v>12.22</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>189319796.4</v>
+        <v>191421338.9</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>22.77</v>
+        <v>23.03</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>33.06</v>
+        <v>33.43</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>27.44</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="15">
@@ -28790,16 +28790,16 @@
         <v>11.93</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>201927826.94</v>
+        <v>204058209.94</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>28.75</v>
+        <v>29.05</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>38.92</v>
+        <v>39.33</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>35.16</v>
+        <v>35.45</v>
       </c>
     </row>
     <row r="16">
@@ -28833,16 +28833,16 @@
         <v>17.81</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>199488338.22</v>
+        <v>201971967.08</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>26.62</v>
+        <v>26.95</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>39.26</v>
+        <v>39.75</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>33.04</v>
+        <v>33.28</v>
       </c>
     </row>
     <row r="17">
@@ -28876,16 +28876,16 @@
         <v>13.85</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>135764338.65</v>
+        <v>136180246.65</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>32.46</v>
+        <v>32.56</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>41.8</v>
+        <v>41.93</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>39.14</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="18">
@@ -28919,16 +28919,16 @@
         <v>19.76</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>122880968.33</v>
+        <v>123333353.33</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>29.6</v>
+        <v>29.71</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>41.09</v>
+        <v>41.24</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>35.13</v>
+        <v>35.16</v>
       </c>
     </row>
     <row r="19">
@@ -28962,16 +28962,16 @@
         <v>16.95</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>135075740.39</v>
+        <v>137219155.39</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>30.97</v>
+        <v>31.47</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>48.21</v>
+        <v>48.97</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>43.76</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="20">
@@ -29005,16 +29005,16 @@
         <v>14.84</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>132932338.68</v>
+        <v>133548822.09</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>39.18</v>
+        <v>39.36</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>49.08</v>
+        <v>49.3</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>43.06</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="21">
@@ -29048,16 +29048,16 @@
         <v>12.4</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>97244344.3</v>
+        <v>97540224.3</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>28.07</v>
+        <v>28.16</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>36.55</v>
+        <v>36.66</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>34.43</v>
+        <v>34.47</v>
       </c>
     </row>
     <row r="22">
@@ -29091,16 +29091,16 @@
         <v>17.24</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>129530005.95</v>
+        <v>130654310.74</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>32.79</v>
+        <v>33.07</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>49.08</v>
+        <v>49.51</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>35.32</v>
+        <v>35.37</v>
       </c>
     </row>
     <row r="23">
@@ -29134,16 +29134,16 @@
         <v>12.24</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>110174125.13</v>
+        <v>110452755.13</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>34.2</v>
+        <v>34.29</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>45.11</v>
+        <v>45.23</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>42.22</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="24">
@@ -29177,16 +29177,16 @@
         <v>29.65</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>140698770.08</v>
+        <v>142757224.66</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>46.74</v>
+        <v>47.43</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>62.44</v>
+        <v>63.36</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>52.24</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="25">
@@ -29220,13 +29220,13 @@
         <v>20.99</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>105663981.86</v>
+        <v>105576888.85</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>35.86</v>
+        <v>35.83</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>52.18</v>
+        <v>52.14</v>
       </c>
       <c r="M25" s="6" t="n">
         <v>46.21</v>
@@ -29263,16 +29263,16 @@
         <v>23.62</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>113252800.91</v>
+        <v>113301947.41</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>49.09</v>
+        <v>49.11</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>65.08</v>
+        <v>65.11</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>61.09</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="27">
@@ -29306,16 +29306,16 @@
         <v>34.52</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>126690682.48</v>
+        <v>127167410.29</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>72.09</v>
+        <v>72.36</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>99.86</v>
+        <v>100.24</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>86.08</v>
+        <v>86.09</v>
       </c>
     </row>
     <row r="28">
@@ -29349,16 +29349,16 @@
         <v>31.11</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>108175510.82</v>
+        <v>109070475.18</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>67.78</v>
+        <v>68.34</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>91.45999999999999</v>
+        <v>92.22</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>79.48</v>
+        <v>79.51000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -29392,16 +29392,16 @@
         <v>63.13</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>96618755.84999999</v>
+        <v>96690655.84999999</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>108.83</v>
+        <v>108.91</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>157.2</v>
+        <v>157.31</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>146.76</v>
+        <v>146.82</v>
       </c>
     </row>
     <row r="30">
@@ -29435,13 +29435,13 @@
         <v>55.74</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>102228361.13</v>
+        <v>102266586.13</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>126.22</v>
+        <v>126.26</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>176.96</v>
+        <v>177.02</v>
       </c>
       <c r="M30" s="6" t="n">
         <v>170.99</v>
@@ -29478,16 +29478,16 @@
         <v>102.85</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>100582622.06</v>
+        <v>100669144.7</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>132.17</v>
+        <v>132.28</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>250.47</v>
+        <v>250.69</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>240.25</v>
+        <v>240.38</v>
       </c>
     </row>
     <row r="32">
@@ -29533,7 +29533,7 @@
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>136347659.97</v>
+        <v>137949190.58</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -29582,16 +29582,16 @@
         <v>13.29</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>5763156297.840001</v>
+        <v>5805521177.42</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>36.51</v>
+        <v>36.78</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>32.2</v>
+        <v>32.33</v>
       </c>
     </row>
     <row r="34">
@@ -29604,7 +29604,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-22.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-23.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 15:20:52.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 15:20:52.</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26299</v>
+        <v>29298</v>
       </c>
     </row>
     <row r="48">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20860</v>
+        <v>17880</v>
       </c>
     </row>
     <row r="50">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-23 09:17:53</t>
+          <t>2026-09-23 15:20:52</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>75659161.20999999</v>
+        <v>75659161.21000001</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0.23</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 15:20:52.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 15:20:52.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 15:20:52.</t>
         </is>
       </c>
     </row>
@@ -19245,10 +19245,10 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>596837953.77</v>
+        <v>598444864.4400001</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>23.49</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="90">
@@ -19268,10 +19268,10 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>164683280.01</v>
+        <v>165156983.71</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="91">
@@ -19291,10 +19291,10 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>156442101.35</v>
+        <v>157484419.62</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>6.16</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="92">
@@ -19314,7 +19314,7 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>127146823.16</v>
+        <v>127458248.79</v>
       </c>
       <c r="E92" s="12" t="n">
         <v>5</v>
@@ -19337,10 +19337,10 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>119731453.47</v>
+        <v>120320431.42</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="94">
@@ -19360,10 +19360,10 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>105018777.32</v>
+        <v>105831247.37</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="95">
@@ -19383,10 +19383,10 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>100772555.84</v>
+        <v>101507628.22</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="96">
@@ -19406,7 +19406,7 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>97133403.63</v>
+        <v>97466671.56</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>3.82</v>
@@ -19429,7 +19429,7 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>91767176.59999999</v>
+        <v>91988965.93000001</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>3.61</v>
@@ -19452,7 +19452,7 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>87685363</v>
+        <v>88118529.61</v>
       </c>
       <c r="E98" s="12" t="n">
         <v>3.45</v>
@@ -19475,7 +19475,7 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>83644136.72</v>
+        <v>83824991.72</v>
       </c>
       <c r="E99" s="12" t="n">
         <v>3.29</v>
@@ -19498,10 +19498,10 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>78707049.53</v>
+        <v>79228185</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="101">
@@ -19521,10 +19521,10 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>72573697.29000001</v>
+        <v>72779424.06</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="102">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>68851162.08</v>
+        <v>69052699.27</v>
       </c>
       <c r="E102" s="12" t="n">
         <v>2.71</v>
@@ -19567,10 +19567,10 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>66238723.53</v>
+        <v>66779026.83</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="104">
@@ -19590,7 +19590,7 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>62369707.4</v>
+        <v>62589885.01</v>
       </c>
       <c r="E104" s="12" t="n">
         <v>2.45</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>55859891.88</v>
+        <v>56205272.09</v>
       </c>
       <c r="E105" s="12" t="n">
         <v>2.2</v>
@@ -19636,7 +19636,7 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>55239359.08</v>
+        <v>55412642.3</v>
       </c>
       <c r="E106" s="12" t="n">
         <v>2.17</v>
@@ -19659,7 +19659,7 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>46220288.81</v>
+        <v>46475147.24</v>
       </c>
       <c r="E107" s="12" t="n">
         <v>1.82</v>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>44590223.2</v>
+        <v>44644398.81</v>
       </c>
       <c r="E108" s="12" t="n">
         <v>1.75</v>
@@ -19705,7 +19705,7 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>44252658.84</v>
+        <v>44471806.78</v>
       </c>
       <c r="E109" s="12" t="n">
         <v>1.74</v>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>43680404.44</v>
+        <v>43803566.64</v>
       </c>
       <c r="E110" s="12" t="n">
         <v>1.72</v>
@@ -19751,7 +19751,7 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>41867563.86</v>
+        <v>42032253.44</v>
       </c>
       <c r="E111" s="12" t="n">
         <v>1.65</v>
@@ -19774,7 +19774,7 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>40670496.86</v>
+        <v>40808673.05</v>
       </c>
       <c r="E112" s="12" t="n">
         <v>1.6</v>
@@ -19797,10 +19797,10 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>35469082.96</v>
+        <v>35534051.36</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="114">
@@ -19820,7 +19820,7 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>27151030.86</v>
+        <v>27320526.46</v>
       </c>
       <c r="E114" s="12" t="n">
         <v>1.07</v>
@@ -19843,7 +19843,7 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>25234984.45</v>
+        <v>25286467.35</v>
       </c>
       <c r="E115" s="12" t="n">
         <v>0.99</v>
@@ -22428,7 +22428,7 @@
     <row r="228">
       <c r="A228" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 15:20:52.</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22442,7 @@
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: a serie de fornecedores cobre 68.3% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
+          <t>Nota 1: a serie de fornecedores cobre 68.6% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
         </is>
       </c>
     </row>
@@ -23754,7 +23754,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 15:20:52.</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 15:20:52.</t>
         </is>
       </c>
     </row>
@@ -28184,7 +28184,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 09:17:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-23 15:20:52.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 07:47:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 07:47:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34299</v>
+        <v>36299</v>
       </c>
     </row>
     <row r="48">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>13353</v>
+        <v>11382</v>
       </c>
     </row>
     <row r="50">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4764744082.58</v>
+        <v>4772139234.33</v>
       </c>
     </row>
     <row r="57">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4714432640.58</v>
+        <v>4718525185.58</v>
       </c>
     </row>
     <row r="58">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>476531234.12</v>
+        <v>479003500.02</v>
       </c>
     </row>
     <row r="59">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>431335868.73</v>
+        <v>433269095.24</v>
       </c>
     </row>
     <row r="60">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-24 07:47:46</t>
+          <t>2026-09-24 09:19:07</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>575680870.95</v>
+        <v>575680870.9499999</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1.78</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>75659161.21000001</v>
+        <v>75659161.20999999</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0.23</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="G59" s="6" t="n">
-        <v>62944315.40000001</v>
+        <v>62944315.4</v>
       </c>
       <c r="H59" s="6" t="n">
         <v>0.19</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 07:47:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 07:47:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 07:47:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
         </is>
       </c>
     </row>
@@ -17245,7 +17245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E231"/>
+  <dimension ref="A1:E232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
@@ -19245,10 +19245,10 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>610066087</v>
+        <v>610399910.0599999</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>23.64</v>
+        <v>23.63</v>
       </c>
     </row>
     <row r="90">
@@ -19268,7 +19268,7 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>167360024.85</v>
+        <v>167437678.87</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>6.48</v>
@@ -19291,10 +19291,10 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>160040844.6</v>
+        <v>160315545.81</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>6.2</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="92">
@@ -19314,7 +19314,7 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>128277981.05</v>
+        <v>128343924.02</v>
       </c>
       <c r="E92" s="12" t="n">
         <v>4.97</v>
@@ -19337,7 +19337,7 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>121414088.47</v>
+        <v>121512202.79</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>4.7</v>
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>106878184.52</v>
+        <v>107062353.14</v>
       </c>
       <c r="E94" s="12" t="n">
         <v>4.14</v>
@@ -19383,7 +19383,7 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>102860939.22</v>
+        <v>103040938.56</v>
       </c>
       <c r="E95" s="12" t="n">
         <v>3.99</v>
@@ -19406,7 +19406,7 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>98512850.88</v>
+        <v>98581276.86</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>3.82</v>
@@ -19429,7 +19429,7 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>92424083.16</v>
+        <v>92451872.34999999</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>3.58</v>
@@ -19452,7 +19452,7 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>88566491.56</v>
+        <v>88629734.43000001</v>
       </c>
       <c r="E98" s="12" t="n">
         <v>3.43</v>
@@ -19475,7 +19475,7 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>84112765.19</v>
+        <v>84157310.75</v>
       </c>
       <c r="E99" s="12" t="n">
         <v>3.26</v>
@@ -19498,7 +19498,7 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>80214793.27</v>
+        <v>80328521.43000001</v>
       </c>
       <c r="E100" s="12" t="n">
         <v>3.11</v>
@@ -19521,7 +19521,7 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>73072162.7</v>
+        <v>73117225.06</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>2.83</v>
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>69505943.75</v>
+        <v>69544574.78</v>
       </c>
       <c r="E102" s="12" t="n">
         <v>2.69</v>
@@ -19567,7 +19567,7 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>67622093.89</v>
+        <v>67724974.7</v>
       </c>
       <c r="E103" s="12" t="n">
         <v>2.62</v>
@@ -19590,7 +19590,7 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>63390322.43</v>
+        <v>63445152.62</v>
       </c>
       <c r="E104" s="12" t="n">
         <v>2.46</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>56936427.55</v>
+        <v>57006831.18</v>
       </c>
       <c r="E105" s="12" t="n">
         <v>2.21</v>
@@ -19636,7 +19636,7 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>55594909.26</v>
+        <v>55631376.34</v>
       </c>
       <c r="E106" s="12" t="n">
         <v>2.15</v>
@@ -19659,7 +19659,7 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>47128542.41</v>
+        <v>47201182.01</v>
       </c>
       <c r="E107" s="12" t="n">
         <v>1.83</v>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>44923739.43</v>
+        <v>44938130.46</v>
       </c>
       <c r="E108" s="12" t="n">
         <v>1.74</v>
@@ -19705,7 +19705,7 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>44815685.95</v>
+        <v>44887831.16</v>
       </c>
       <c r="E109" s="12" t="n">
         <v>1.74</v>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>43945126.59</v>
+        <v>43976203.98</v>
       </c>
       <c r="E110" s="12" t="n">
         <v>1.7</v>
@@ -19751,7 +19751,7 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>42236505.79</v>
+        <v>42273490.41</v>
       </c>
       <c r="E111" s="12" t="n">
         <v>1.64</v>
@@ -19774,7 +19774,7 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>41491444.46</v>
+        <v>41517892.79</v>
       </c>
       <c r="E112" s="12" t="n">
         <v>1.61</v>
@@ -19797,7 +19797,7 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>35604161.05</v>
+        <v>35611767.07</v>
       </c>
       <c r="E113" s="12" t="n">
         <v>1.38</v>
@@ -19820,7 +19820,7 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>27533766.51</v>
+        <v>27567405.68</v>
       </c>
       <c r="E114" s="12" t="n">
         <v>1.07</v>
@@ -19843,7 +19843,7 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>25328005.44</v>
+        <v>25341311.92</v>
       </c>
       <c r="E115" s="12" t="n">
         <v>0.98</v>
@@ -19875,24 +19875,24 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>Valor doado, pela UF do doador</t>
+          <t>Valor contratado de fornecedores</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>114899305.01</v>
+        <v>1010.55</v>
       </c>
       <c r="E117" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -19903,19 +19903,19 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>40037432.89</v>
+        <v>114899305.01</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>7.67</v>
+        <v>22</v>
       </c>
     </row>
     <row r="119">
@@ -19926,19 +19926,19 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Minas Gerais</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>38680832.03</v>
+        <v>40037432.89</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>7.41</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="120">
@@ -19949,19 +19949,19 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Paraná</t>
+          <t>Minas Gerais</t>
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>36464616.78</v>
+        <v>38680832.03</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>6.98</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="121">
@@ -19972,19 +19972,19 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Paraná</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>25243345.44</v>
+        <v>36464616.78</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>4.83</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="122">
@@ -19995,19 +19995,19 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Sul</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>21817618.71</v>
+        <v>25243345.44</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>4.18</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="123">
@@ -20018,19 +20018,19 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Santa Catarina</t>
+          <t>Rio Grande do Sul</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>19557005.19</v>
+        <v>21817618.71</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>3.74</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="124">
@@ -20041,19 +20041,19 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Pernambuco</t>
+          <t>Santa Catarina</t>
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>18614196.06</v>
+        <v>19557005.19</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>3.56</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="125">
@@ -20064,19 +20064,19 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso</t>
+          <t>Pernambuco</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>17994047.39</v>
+        <v>18614196.06</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="126">
@@ -20087,19 +20087,19 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Distrito Federal</t>
+          <t>Mato Grosso</t>
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>16168065.74</v>
+        <v>17994047.39</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="127">
@@ -20110,19 +20110,19 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Distrito Federal</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>15430690.89</v>
+        <v>16168065.74</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="128">
@@ -20133,19 +20133,19 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>15374746.01</v>
+        <v>15430690.89</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="129">
@@ -20156,19 +20156,19 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
-        <v>15167790.85</v>
+        <v>15374746.01</v>
       </c>
       <c r="E129" s="12" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="130">
@@ -20179,19 +20179,19 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Paraíba</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>14662450.88</v>
+        <v>15167790.85</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="131">
@@ -20202,19 +20202,19 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>13504364.28</v>
+        <v>14662450.88</v>
       </c>
       <c r="E131" s="12" t="n">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="132">
@@ -20225,19 +20225,19 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso do Sul</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>11395718.8</v>
+        <v>13504364.28</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>2.18</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="133">
@@ -20248,16 +20248,16 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Pará</t>
+          <t>Mato Grosso do Sul</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>11374266.99</v>
+        <v>11395718.8</v>
       </c>
       <c r="E133" s="12" t="n">
         <v>2.18</v>
@@ -20271,19 +20271,19 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Pará</t>
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>10909260.75</v>
+        <v>11374266.99</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="135">
@@ -20294,19 +20294,19 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>9559738.529999999</v>
+        <v>10909260.75</v>
       </c>
       <c r="E135" s="12" t="n">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="136">
@@ -20317,19 +20317,19 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>9421680.49</v>
+        <v>9559738.529999999</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="137">
@@ -20340,19 +20340,19 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>8552970.23</v>
+        <v>9421680.49</v>
       </c>
       <c r="E137" s="12" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="138">
@@ -20363,19 +20363,19 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Acre</t>
+          <t>Piauí</t>
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>7472958.47</v>
+        <v>8552970.23</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="139">
@@ -20386,19 +20386,19 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Roraima</t>
+          <t>Acre</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
-        <v>7155890.22</v>
+        <v>7472958.47</v>
       </c>
       <c r="E139" s="12" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="140">
@@ -20409,19 +20409,19 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Alagoas</t>
+          <t>Roraima</t>
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>6781567.4</v>
+        <v>7155890.22</v>
       </c>
       <c r="E140" s="12" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="141">
@@ -20432,19 +20432,19 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Alagoas</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
-        <v>5626098.78</v>
+        <v>6781567.4</v>
       </c>
       <c r="E141" s="12" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="142">
@@ -20455,19 +20455,19 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Amapá</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>5383564.5</v>
+        <v>5626098.78</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="143">
@@ -20478,42 +20478,42 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Norte</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>5013592.3</v>
+        <v>5383564.5</v>
       </c>
       <c r="E143" s="12" t="n">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>Doacao de pessoa fisica, pela UF do candidato</t>
+          <t>Valor doado, pela UF do doador</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Rio Grande do Norte</t>
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>64138783.06</v>
+        <v>5013592.3</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>15.75</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="145">
@@ -20524,19 +20524,19 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Minas Gerais</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D145" s="6" t="n">
-        <v>51151182.79</v>
+        <v>64138783.06</v>
       </c>
       <c r="E145" s="12" t="n">
-        <v>12.56</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="146">
@@ -20547,19 +20547,19 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso</t>
+          <t>Minas Gerais</t>
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>24233913.07</v>
+        <v>51151182.79</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>5.95</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="147">
@@ -20570,19 +20570,19 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Mato Grosso</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
-        <v>23033154.85</v>
+        <v>24233913.07</v>
       </c>
       <c r="E147" s="12" t="n">
-        <v>5.66</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="148">
@@ -20593,19 +20593,19 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>22671481.34</v>
+        <v>23033154.85</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>5.57</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="149">
@@ -20616,19 +20616,19 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Paraná</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
-        <v>21672779.44</v>
+        <v>22671481.34</v>
       </c>
       <c r="E149" s="12" t="n">
-        <v>5.32</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="150">
@@ -20639,19 +20639,19 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Paraná</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>20038777.52</v>
+        <v>21672779.44</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>4.92</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="151">
@@ -20662,19 +20662,19 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Sul</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>19005254.09</v>
+        <v>20038777.52</v>
       </c>
       <c r="E151" s="12" t="n">
-        <v>4.67</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="152">
@@ -20685,19 +20685,19 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Rio Grande do Sul</t>
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>15656007.44</v>
+        <v>19005254.09</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>3.85</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="153">
@@ -20708,19 +20708,19 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Santa Catarina</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
-        <v>15407239.46</v>
+        <v>15656007.44</v>
       </c>
       <c r="E153" s="12" t="n">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="154">
@@ -20731,19 +20731,19 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Distrito Federal</t>
+          <t>Santa Catarina</t>
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>14420380.52</v>
+        <v>15407239.46</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>3.54</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="155">
@@ -20754,19 +20754,19 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Pernambuco</t>
+          <t>Distrito Federal</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
-        <v>12974654.42</v>
+        <v>14420380.52</v>
       </c>
       <c r="E155" s="12" t="n">
-        <v>3.19</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="156">
@@ -20777,19 +20777,19 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Pernambuco</t>
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>12497985.68</v>
+        <v>12974654.42</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>3.07</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="157">
@@ -20800,19 +20800,19 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
-        <v>11093129.79</v>
+        <v>12497985.68</v>
       </c>
       <c r="E157" s="12" t="n">
-        <v>2.72</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="158">
@@ -20823,19 +20823,19 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Pará</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D158" s="6" t="n">
-        <v>9846151.369999999</v>
+        <v>11093129.79</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="159">
@@ -20846,19 +20846,19 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Pará</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
-        <v>8884066.109999999</v>
+        <v>9846151.369999999</v>
       </c>
       <c r="E159" s="12" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="160">
@@ -20869,19 +20869,19 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Piauí</t>
         </is>
       </c>
       <c r="D160" s="6" t="n">
-        <v>8176294.7</v>
+        <v>8884066.109999999</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="161">
@@ -20892,19 +20892,19 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Presidenciáveis, circunscrição nacional</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
-        <v>8044237.19</v>
+        <v>8176294.7</v>
       </c>
       <c r="E161" s="12" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="162">
@@ -20915,19 +20915,19 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>6783926.8</v>
+        <v>8044237.19</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="163">
@@ -20938,19 +20938,19 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D163" s="6" t="n">
-        <v>6584908.54</v>
+        <v>6783926.8</v>
       </c>
       <c r="E163" s="12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="164">
@@ -20961,19 +20961,19 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="D164" s="6" t="n">
-        <v>5743109.92</v>
+        <v>6584908.54</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="165">
@@ -20984,19 +20984,19 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso do Sul</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="D165" s="6" t="n">
-        <v>5693835.81</v>
+        <v>5743109.92</v>
       </c>
       <c r="E165" s="12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="166">
@@ -21007,19 +21007,19 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Paraíba</t>
+          <t>Mato Grosso do Sul</t>
         </is>
       </c>
       <c r="D166" s="6" t="n">
-        <v>4614157.08</v>
+        <v>5693835.81</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="167">
@@ -21030,19 +21030,19 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Alagoas</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="D167" s="6" t="n">
-        <v>4562900.79</v>
+        <v>4614157.08</v>
       </c>
       <c r="E167" s="12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="168">
@@ -21053,19 +21053,19 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Acre</t>
+          <t>Alagoas</t>
         </is>
       </c>
       <c r="D168" s="6" t="n">
-        <v>3173862.49</v>
+        <v>4562900.79</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>0.78</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="169">
@@ -21076,19 +21076,19 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Norte</t>
+          <t>Acre</t>
         </is>
       </c>
       <c r="D169" s="6" t="n">
-        <v>2673769.35</v>
+        <v>3173862.49</v>
       </c>
       <c r="E169" s="12" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="170">
@@ -21099,19 +21099,19 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Roraima</t>
+          <t>Rio Grande do Norte</t>
         </is>
       </c>
       <c r="D170" s="6" t="n">
-        <v>2589888.97</v>
+        <v>2673769.35</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="171">
@@ -21122,42 +21122,42 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Amapá</t>
+          <t>Roraima</t>
         </is>
       </c>
       <c r="D171" s="6" t="n">
-        <v>1755108.36</v>
+        <v>2589888.97</v>
       </c>
       <c r="E171" s="12" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>candidatos</t>
+          <t>Doacao de pessoa fisica, pela UF do candidato</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="D172" s="6" t="n">
-        <v>2630</v>
+        <v>1755108.36</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>12.53</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="173">
@@ -21168,19 +21168,19 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D173" s="6" t="n">
-        <v>2055</v>
+        <v>2630</v>
       </c>
       <c r="E173" s="12" t="n">
-        <v>9.789999999999999</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="174">
@@ -21191,19 +21191,19 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Minas Gerais</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D174" s="6" t="n">
-        <v>1832</v>
+        <v>2055</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>8.73</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="175">
@@ -21214,19 +21214,19 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Minas Gerais</t>
         </is>
       </c>
       <c r="D175" s="6" t="n">
-        <v>1224</v>
+        <v>1832</v>
       </c>
       <c r="E175" s="12" t="n">
-        <v>5.83</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="176">
@@ -21237,19 +21237,19 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Paraná</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="D176" s="6" t="n">
-        <v>1090</v>
+        <v>1224</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>5.19</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="177">
@@ -21260,19 +21260,19 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Sul</t>
+          <t>Paraná</t>
         </is>
       </c>
       <c r="D177" s="6" t="n">
-        <v>1053</v>
+        <v>1090</v>
       </c>
       <c r="E177" s="12" t="n">
-        <v>5.02</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="178">
@@ -21283,19 +21283,19 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Pernambuco</t>
+          <t>Rio Grande do Sul</t>
         </is>
       </c>
       <c r="D178" s="6" t="n">
-        <v>961</v>
+        <v>1053</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>4.58</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="179">
@@ -21306,19 +21306,19 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Pernambuco</t>
         </is>
       </c>
       <c r="D179" s="6" t="n">
-        <v>905</v>
+        <v>961</v>
       </c>
       <c r="E179" s="12" t="n">
-        <v>4.31</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="180">
@@ -21329,19 +21329,19 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Pará</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="D180" s="6" t="n">
-        <v>741</v>
+        <v>905</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>3.53</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="181">
@@ -21352,19 +21352,19 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Pará</t>
         </is>
       </c>
       <c r="D181" s="6" t="n">
-        <v>713</v>
+        <v>741</v>
       </c>
       <c r="E181" s="12" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="182">
@@ -21375,19 +21375,19 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Santa Catarina</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="D182" s="6" t="n">
-        <v>700</v>
+        <v>713</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="183">
@@ -21398,19 +21398,19 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Distrito Federal</t>
+          <t>Santa Catarina</t>
         </is>
       </c>
       <c r="D183" s="6" t="n">
-        <v>668</v>
+        <v>700</v>
       </c>
       <c r="E183" s="12" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="184">
@@ -21421,19 +21421,19 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Distrito Federal</t>
         </is>
       </c>
       <c r="D184" s="6" t="n">
-        <v>619</v>
+        <v>668</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="185">
@@ -21444,19 +21444,19 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D185" s="6" t="n">
-        <v>591</v>
+        <v>619</v>
       </c>
       <c r="E185" s="12" t="n">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="186">
@@ -21467,19 +21467,19 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D186" s="6" t="n">
-        <v>475</v>
+        <v>591</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>2.26</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="187">
@@ -21490,19 +21490,19 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D187" s="6" t="n">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="E187" s="12" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="188">
@@ -21513,19 +21513,19 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Paraíba</t>
+          <t>Mato Grosso</t>
         </is>
       </c>
       <c r="D188" s="6" t="n">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="E188" s="12" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="189">
@@ -21536,19 +21536,19 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="D189" s="6" t="n">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="E189" s="12" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="190">
@@ -21559,19 +21559,19 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso do Sul</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D190" s="6" t="n">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="E190" s="12" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="191">
@@ -21582,19 +21582,19 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Roraima</t>
+          <t>Mato Grosso do Sul</t>
         </is>
       </c>
       <c r="D191" s="6" t="n">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="E191" s="12" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="192">
@@ -21605,19 +21605,19 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Roraima</t>
         </is>
       </c>
       <c r="D192" s="6" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E192" s="12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="193">
@@ -21628,19 +21628,19 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="D193" s="6" t="n">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="E193" s="12" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="194">
@@ -21651,19 +21651,19 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Acre</t>
+          <t>Piauí</t>
         </is>
       </c>
       <c r="D194" s="6" t="n">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="E194" s="12" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="195">
@@ -21674,19 +21674,19 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Acre</t>
         </is>
       </c>
       <c r="D195" s="6" t="n">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="E195" s="12" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="196">
@@ -21697,19 +21697,19 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Norte</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="D196" s="6" t="n">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="E196" s="12" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="197">
@@ -21720,19 +21720,19 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Amapá</t>
+          <t>Rio Grande do Norte</t>
         </is>
       </c>
       <c r="D197" s="6" t="n">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E197" s="12" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="198">
@@ -21743,19 +21743,19 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>Alagoas</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="D198" s="6" t="n">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="E198" s="12" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="199">
@@ -21766,42 +21766,42 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Presidenciáveis, circunscrição nacional</t>
+          <t>Alagoas</t>
         </is>
       </c>
       <c r="D199" s="6" t="n">
-        <v>28</v>
+        <v>299</v>
       </c>
       <c r="E199" s="12" t="n">
-        <v>0.13</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>partidos</t>
+          <t>candidatos</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>Minas Gerais</t>
+          <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
       <c r="D200" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E200" s="12" t="n">
-        <v>4.2</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="201">
@@ -21812,12 +21812,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Minas Gerais</t>
         </is>
       </c>
       <c r="D201" s="6" t="n">
@@ -21835,12 +21835,12 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>Distrito Federal</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D202" s="6" t="n">
@@ -21858,12 +21858,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Distrito Federal</t>
         </is>
       </c>
       <c r="D203" s="6" t="n">
@@ -21881,12 +21881,12 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D204" s="6" t="n">
@@ -21904,19 +21904,19 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Pernambuco</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="D205" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E205" s="12" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="206">
@@ -21927,19 +21927,19 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Norte</t>
+          <t>Pernambuco</t>
         </is>
       </c>
       <c r="D206" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E206" s="12" t="n">
-        <v>3.91</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="207">
@@ -21950,12 +21950,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Sul</t>
+          <t>Rio Grande do Norte</t>
         </is>
       </c>
       <c r="D207" s="6" t="n">
@@ -21973,12 +21973,12 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Rio Grande do Sul</t>
         </is>
       </c>
       <c r="D208" s="6" t="n">
@@ -21996,19 +21996,19 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="D209" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E209" s="12" t="n">
-        <v>3.76</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="210">
@@ -22019,12 +22019,12 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Santa Catarina</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="D210" s="6" t="n">
@@ -22042,12 +22042,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Santa Catarina</t>
         </is>
       </c>
       <c r="D211" s="6" t="n">
@@ -22065,12 +22065,12 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>Pará</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="D212" s="6" t="n">
@@ -22088,12 +22088,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Paraná</t>
+          <t>Pará</t>
         </is>
       </c>
       <c r="D213" s="6" t="n">
@@ -22111,19 +22111,19 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso</t>
+          <t>Paraná</t>
         </is>
       </c>
       <c r="D214" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E214" s="12" t="n">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="215">
@@ -22134,12 +22134,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Mato Grosso</t>
         </is>
       </c>
       <c r="D215" s="6" t="n">
@@ -22157,19 +22157,19 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Acre</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D216" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E216" s="12" t="n">
-        <v>3.47</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="217">
@@ -22180,12 +22180,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Paraíba</t>
+          <t>Acre</t>
         </is>
       </c>
       <c r="D217" s="6" t="n">
@@ -22203,12 +22203,12 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="D218" s="6" t="n">
@@ -22226,19 +22226,19 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Piauí</t>
         </is>
       </c>
       <c r="D219" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E219" s="12" t="n">
-        <v>3.33</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="220">
@@ -22249,12 +22249,12 @@
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Roraima</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D220" s="6" t="n">
@@ -22272,12 +22272,12 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso do Sul</t>
+          <t>Roraima</t>
         </is>
       </c>
       <c r="D221" s="6" t="n">
@@ -22295,19 +22295,19 @@
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Mato Grosso do Sul</t>
         </is>
       </c>
       <c r="D222" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E222" s="12" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="223">
@@ -22318,19 +22318,19 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="D223" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E223" s="12" t="n">
-        <v>3.04</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="224">
@@ -22341,19 +22341,19 @@
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Amapá</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="D224" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E224" s="12" t="n">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="225">
@@ -22364,12 +22364,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="D225" s="6" t="n">
@@ -22387,67 +22387,90 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>Rondônia</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E226" s="12" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>partidos</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="C226" s="4" t="inlineStr">
+      <c r="C227" s="4" t="inlineStr">
         <is>
           <t>Alagoas</t>
         </is>
       </c>
-      <c r="D226" s="6" t="n">
+      <c r="D227" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="E226" s="12" t="n">
+      <c r="E227" s="12" t="n">
         <v>2.75</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="7" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="7" t="inlineStr">
         <is>
           <t>partidos</t>
         </is>
       </c>
-      <c r="B227" s="7" t="inlineStr">
+      <c r="B228" s="7" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="C227" s="7" t="inlineStr">
+      <c r="C228" s="7" t="inlineStr">
         <is>
           <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
-      <c r="D227" s="9" t="n">
+      <c r="D228" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="E227" s="13" t="n">
+      <c r="E228" s="13" t="n">
         <v>2.03</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="10" t="inlineStr">
-        <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 07:47:46.</t>
-        </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-24.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: a serie de fornecedores cobre 68.8% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-09-24.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="10" t="inlineStr">
+        <is>
+          <t>Nota 1: a serie de fornecedores cobre 68.9% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="10" t="inlineStr">
         <is>
           <t>Nota 2: a serie por UF do doador cobre apenas 8.9% do valor doado, porque o TSE nao publica a UF do doador pessoa fisica. Para leitura integral use a serie por UF do candidato que recebeu.</t>
         </is>
@@ -22555,22 +22578,22 @@
         <v>18485111.6</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4556010.95</v>
+        <v>5013285.95</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>7330302.17</v>
+        <v>7506630.92</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>25815413.77</v>
+        <v>25991742.52</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>18.84</v>
+        <v>18.9</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>425203448.53</v>
+        <v>425660723.53</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>22.41</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="6">
@@ -22586,22 +22609,22 @@
         <v>18767611.87</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>15420541.37</v>
+        <v>15423331.37</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>4710150.94</v>
+        <v>4970836.14</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>23477762.81</v>
+        <v>23738448.01</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>17.14</v>
+        <v>17.26</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>318668598.53</v>
+        <v>318671388.53</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>16.8</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="7">
@@ -22617,22 +22640,22 @@
         <v>2024422.59</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>4405616.89</v>
+        <v>4755616.89</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>13634436.95</v>
+        <v>13373751.75</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>15658859.54</v>
+        <v>15398174.34</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>11.43</v>
+        <v>11.19</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>127902245.35</v>
+        <v>128252245.35</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6.74</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
@@ -22657,13 +22680,13 @@
         <v>15087102.75</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>11.01</v>
+        <v>10.97</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>172914762.35</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="9">
@@ -22679,22 +22702,22 @@
         <v>6213996.63</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>10048725.59</v>
+        <v>10352176.89</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>7246108.82</v>
+        <v>7469958.82</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>13460105.45</v>
+        <v>13683955.45</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>9.82</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>104807058</v>
+        <v>105110509.3</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.52</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="10">
@@ -22710,22 +22733,22 @@
         <v>6181808.82</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>848977</v>
+        <v>941897</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>135747.66</v>
+        <v>169747.66</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>6317556.48</v>
+        <v>6351556.48</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>4.61</v>
+        <v>4.62</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>142036297.98</v>
+        <v>142129217.98</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>7.49</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="11">
@@ -22744,19 +22767,19 @@
         <v>2145619.45</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2068680.85</v>
+        <v>2015572.35</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>6306180.640000001</v>
+        <v>6253072.140000001</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>127727630.51</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>6.73</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="12">
@@ -22772,22 +22795,22 @@
         <v>2370564.76</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>8707553.99</v>
+        <v>10803413.04</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>3518340.69</v>
+        <v>3568340.77</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>5888905.449999999</v>
+        <v>5938905.529999999</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>61626161.59</v>
+        <v>63722020.64</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="13">
@@ -22812,13 +22835,13 @@
         <v>5628437.98</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>134762194.74</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="14">
@@ -22843,7 +22866,7 @@
         <v>3019071.63</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>61699039.53</v>
@@ -22868,10 +22891,10 @@
         <v>752452.6</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1153315.55</v>
+        <v>1154315.55</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2910177.28</v>
+        <v>2911177.28</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>2.12</v>
@@ -22905,7 +22928,7 @@
         <v>2760868.21</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>32675488.27</v>
@@ -22936,7 +22959,7 @@
         <v>2508732.31</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>19049050.9</v>
@@ -22961,19 +22984,19 @@
         <v>766982</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1299563</v>
+        <v>1400921</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1505663</v>
+        <v>1607021</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>10924162.75</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="19">
@@ -23004,7 +23027,7 @@
         <v>15867628.34</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="20">
@@ -23302,7 +23325,7 @@
         <v>8076.8</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>48965.99</v>
+        <v>48965.99000000001</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>209391.57</v>
@@ -23423,7 +23446,7 @@
         <v>923.7</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>51744.89</v>
+        <v>51744.89000000001</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>40426.19</v>
@@ -23537,63 +23560,63 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Encargos financeiros, taxas bancárias e/ou op. cartão de crédito</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>258182.07</v>
+        <v>17696.69</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>11474.01</v>
+        <v>0</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>89167.28999999999</v>
+        <v>0</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>7451.54</v>
+        <v>23429.19</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>18925.55</v>
+        <v>23429.19</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>347349.36</v>
+        <v>17696.69</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Encargos financeiros, taxas bancárias e/ou op. cartão de crédito</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>17696.69</v>
+        <v>258182.07</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>0</v>
+        <v>11474.01</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>0</v>
+        <v>89478.69</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>17836.93</v>
+        <v>7470.34</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>17836.93</v>
+        <v>18944.35</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>17696.69</v>
+        <v>347660.76</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="39">
@@ -23754,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 07:47:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 07:47:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
         </is>
       </c>
     </row>
@@ -28184,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 07:47:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>36299</v>
+        <v>38299</v>
       </c>
     </row>
     <row r="48">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>11382</v>
+        <v>9388</v>
       </c>
     </row>
     <row r="50">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-24 09:19:07</t>
+          <t>2026-09-24 15:20:22</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
         </is>
       </c>
     </row>
@@ -19245,10 +19245,10 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>610399910.0599999</v>
+        <v>610635408.6</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>23.63</v>
+        <v>23.62</v>
       </c>
     </row>
     <row r="90">
@@ -19268,7 +19268,7 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>167437678.87</v>
+        <v>167492273.67</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>6.48</v>
@@ -19291,7 +19291,7 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>160315545.81</v>
+        <v>160531043.51</v>
       </c>
       <c r="E91" s="12" t="n">
         <v>6.21</v>
@@ -19314,7 +19314,7 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>128343924.02</v>
+        <v>128378900.29</v>
       </c>
       <c r="E92" s="12" t="n">
         <v>4.97</v>
@@ -19337,7 +19337,7 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>121512202.79</v>
+        <v>121583362.46</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>4.7</v>
@@ -19360,10 +19360,10 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>107062353.14</v>
+        <v>107218219.4</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="95">
@@ -19383,7 +19383,7 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>103040938.56</v>
+        <v>103186668.67</v>
       </c>
       <c r="E95" s="12" t="n">
         <v>3.99</v>
@@ -19406,7 +19406,7 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>98581276.86</v>
+        <v>98631902.77</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>3.82</v>
@@ -19429,7 +19429,7 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>92451872.34999999</v>
+        <v>92465423.15000001</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>3.58</v>
@@ -19452,7 +19452,7 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>88629734.43000001</v>
+        <v>88672478.52</v>
       </c>
       <c r="E98" s="12" t="n">
         <v>3.43</v>
@@ -19475,7 +19475,7 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>84157310.75</v>
+        <v>84187598.81999999</v>
       </c>
       <c r="E99" s="12" t="n">
         <v>3.26</v>
@@ -19498,7 +19498,7 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>80328521.43000001</v>
+        <v>80408738.55</v>
       </c>
       <c r="E100" s="12" t="n">
         <v>3.11</v>
@@ -19521,7 +19521,7 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>73117225.06</v>
+        <v>73142071.83</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>2.83</v>
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>69544574.78</v>
+        <v>69583027.84999999</v>
       </c>
       <c r="E102" s="12" t="n">
         <v>2.69</v>
@@ -19567,7 +19567,7 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>67724974.7</v>
+        <v>67794648.15000001</v>
       </c>
       <c r="E103" s="12" t="n">
         <v>2.62</v>
@@ -19590,7 +19590,7 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>63445152.62</v>
+        <v>63475860.89</v>
       </c>
       <c r="E104" s="12" t="n">
         <v>2.46</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>57006831.18</v>
+        <v>57079358.25</v>
       </c>
       <c r="E105" s="12" t="n">
         <v>2.21</v>
@@ -19636,7 +19636,7 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>55631376.34</v>
+        <v>55645363.38</v>
       </c>
       <c r="E106" s="12" t="n">
         <v>2.15</v>
@@ -19659,7 +19659,7 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>47201182.01</v>
+        <v>47234880.15</v>
       </c>
       <c r="E107" s="12" t="n">
         <v>1.83</v>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>44938130.46</v>
+        <v>44943052.59</v>
       </c>
       <c r="E108" s="12" t="n">
         <v>1.74</v>
@@ -19705,7 +19705,7 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>44887831.16</v>
+        <v>44931106.03</v>
       </c>
       <c r="E109" s="12" t="n">
         <v>1.74</v>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>43976203.98</v>
+        <v>43995454.21</v>
       </c>
       <c r="E110" s="12" t="n">
         <v>1.7</v>
@@ -19751,7 +19751,7 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>42273490.41</v>
+        <v>42294991.35</v>
       </c>
       <c r="E111" s="12" t="n">
         <v>1.64</v>
@@ -19774,7 +19774,7 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>41517892.79</v>
+        <v>41534065.8</v>
       </c>
       <c r="E112" s="12" t="n">
         <v>1.61</v>
@@ -19797,7 +19797,7 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>35611767.07</v>
+        <v>35617710.8</v>
       </c>
       <c r="E113" s="12" t="n">
         <v>1.38</v>
@@ -19820,7 +19820,7 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>27567405.68</v>
+        <v>27600150.33</v>
       </c>
       <c r="E114" s="12" t="n">
         <v>1.07</v>
@@ -19843,7 +19843,7 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>25341311.92</v>
+        <v>25346575.28</v>
       </c>
       <c r="E115" s="12" t="n">
         <v>0.98</v>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
         </is>
       </c>
     </row>
@@ -23823,7 +23823,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 09:19:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -671,7 +671,7 @@
         <v>53.81</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>12355237266.73</v>
+        <v>12355307266.73</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>38.14</v>
@@ -702,7 +702,7 @@
         <v>37.18</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>8706826684.209999</v>
+        <v>8707006684.209999</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>26.88</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32395103412.82</v>
+        <v>32395353412.82</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>77251</v>
+        <v>77254</v>
       </c>
     </row>
     <row r="31">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32395103412.82</v>
+        <v>32395353412.82</v>
       </c>
     </row>
     <row r="34">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>38299</v>
+        <v>41299</v>
       </c>
     </row>
     <row r="48">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>9388</v>
+        <v>6394</v>
       </c>
     </row>
     <row r="50">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4772139234.33</v>
+        <v>4773054933.99</v>
       </c>
     </row>
     <row r="57">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4718525185.58</v>
+        <v>4718944665.58</v>
       </c>
     </row>
     <row r="58">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>479003500.02</v>
+        <v>481594978.42</v>
       </c>
     </row>
     <row r="59">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>433269095.24</v>
+        <v>435070177.29</v>
       </c>
     </row>
     <row r="60">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-24 15:20:22</t>
+          <t>2026-09-25 09:17:40</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="G63" s="6" t="n">
-        <v>58445503.79</v>
+        <v>58445503.79000001</v>
       </c>
       <c r="H63" s="6" t="n">
         <v>0.18</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
         </is>
       </c>
     </row>
@@ -19245,7 +19245,7 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>610635408.6</v>
+        <v>610846190.9299999</v>
       </c>
       <c r="E89" s="12" t="n">
         <v>23.62</v>
@@ -19268,7 +19268,7 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>167492273.67</v>
+        <v>167536445.27</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>6.48</v>
@@ -19291,10 +19291,10 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>160531043.51</v>
+        <v>160744853.84</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>6.21</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="92">
@@ -19314,7 +19314,7 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>128378900.29</v>
+        <v>128421003.07</v>
       </c>
       <c r="E92" s="12" t="n">
         <v>4.97</v>
@@ -19337,7 +19337,7 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>121583362.46</v>
+        <v>121665049.83</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>4.7</v>
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>107218219.4</v>
+        <v>107359698.44</v>
       </c>
       <c r="E94" s="12" t="n">
         <v>4.15</v>
@@ -19383,7 +19383,7 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>103186668.67</v>
+        <v>103302328.44</v>
       </c>
       <c r="E95" s="12" t="n">
         <v>3.99</v>
@@ -19406,7 +19406,7 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>98631902.77</v>
+        <v>98668430.09999999</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>3.82</v>
@@ -19429,7 +19429,7 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>92465423.15000001</v>
+        <v>92487807.61</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>3.58</v>
@@ -19452,7 +19452,7 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>88672478.52</v>
+        <v>88715475.05</v>
       </c>
       <c r="E98" s="12" t="n">
         <v>3.43</v>
@@ -19475,7 +19475,7 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>84187598.81999999</v>
+        <v>84219299.45</v>
       </c>
       <c r="E99" s="12" t="n">
         <v>3.26</v>
@@ -19498,7 +19498,7 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>80408738.55</v>
+        <v>80477201.81999999</v>
       </c>
       <c r="E100" s="12" t="n">
         <v>3.11</v>
@@ -19521,7 +19521,7 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>73142071.83</v>
+        <v>73168666.61</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>2.83</v>
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>69583027.84999999</v>
+        <v>69607927.37</v>
       </c>
       <c r="E102" s="12" t="n">
         <v>2.69</v>
@@ -19567,7 +19567,7 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>67794648.15000001</v>
+        <v>67862763.75</v>
       </c>
       <c r="E103" s="12" t="n">
         <v>2.62</v>
@@ -19590,7 +19590,7 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>63475860.89</v>
+        <v>63501156.98</v>
       </c>
       <c r="E104" s="12" t="n">
         <v>2.46</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>57079358.25</v>
+        <v>57145340.82</v>
       </c>
       <c r="E105" s="12" t="n">
         <v>2.21</v>
@@ -19636,7 +19636,7 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>55645363.38</v>
+        <v>55666882.79</v>
       </c>
       <c r="E106" s="12" t="n">
         <v>2.15</v>
@@ -19659,7 +19659,7 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>47234880.15</v>
+        <v>47271306.16</v>
       </c>
       <c r="E107" s="12" t="n">
         <v>1.83</v>
@@ -19673,16 +19673,16 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Amapá</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>44943052.59</v>
+        <v>44961266.69</v>
       </c>
       <c r="E108" s="12" t="n">
         <v>1.74</v>
@@ -19696,16 +19696,16 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>44931106.03</v>
+        <v>44949128.99</v>
       </c>
       <c r="E109" s="12" t="n">
         <v>1.74</v>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>43995454.21</v>
+        <v>44012231.34</v>
       </c>
       <c r="E110" s="12" t="n">
         <v>1.7</v>
@@ -19751,7 +19751,7 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>42294991.35</v>
+        <v>42316501.36</v>
       </c>
       <c r="E111" s="12" t="n">
         <v>1.64</v>
@@ -19774,7 +19774,7 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>41534065.8</v>
+        <v>41549782.74</v>
       </c>
       <c r="E112" s="12" t="n">
         <v>1.61</v>
@@ -19797,7 +19797,7 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>35617710.8</v>
+        <v>35621478.43</v>
       </c>
       <c r="E113" s="12" t="n">
         <v>1.38</v>
@@ -19820,7 +19820,7 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>27600150.33</v>
+        <v>27627477.94</v>
       </c>
       <c r="E114" s="12" t="n">
         <v>1.07</v>
@@ -19843,7 +19843,7 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>25346575.28</v>
+        <v>25350876.29</v>
       </c>
       <c r="E115" s="12" t="n">
         <v>0.98</v>
@@ -19889,7 +19889,7 @@
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>1010.55</v>
+        <v>1510.55</v>
       </c>
       <c r="E117" s="12" t="n">
         <v>0</v>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
         </is>
       </c>
     </row>
@@ -22465,7 +22465,7 @@
     <row r="231">
       <c r="A231" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: a serie de fornecedores cobre 68.9% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
+          <t>Nota 1: a serie de fornecedores cobre 69.0% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
         </is>
       </c>
     </row>
@@ -22578,22 +22578,22 @@
         <v>18485111.6</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>5013285.95</v>
+        <v>5043776.95</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>7506630.92</v>
+        <v>7671920.92</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>25991742.52</v>
+        <v>26157032.52</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>18.9</v>
+        <v>18.91</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>425660723.53</v>
+        <v>425691214.53</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>22.4</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="6">
@@ -22609,7 +22609,7 @@
         <v>18767611.87</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>15423331.37</v>
+        <v>15440831.37</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>4970836.14</v>
@@ -22618,13 +22618,13 @@
         <v>23738448.01</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>17.26</v>
+        <v>17.16</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>318671388.53</v>
+        <v>318688888.53</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>16.77</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="7">
@@ -22640,19 +22640,19 @@
         <v>2024422.59</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>4755616.89</v>
+        <v>4773716.89</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>13373751.75</v>
+        <v>13491962.55</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>15398174.34</v>
+        <v>15516385.14</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>11.19</v>
+        <v>11.22</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>128252245.35</v>
+        <v>128270345.35</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>6.75</v>
@@ -22671,7 +22671,7 @@
         <v>14924272.42</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>317350</v>
+        <v>317650</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>162830.33</v>
@@ -22680,10 +22680,10 @@
         <v>15087102.75</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>10.97</v>
+        <v>10.91</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>172914762.35</v>
+        <v>172915062.35</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>9.1</v>
@@ -22711,7 +22711,7 @@
         <v>13683955.45</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>9.949999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>105110509.3</v>
@@ -22733,22 +22733,22 @@
         <v>6181808.82</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>941897</v>
+        <v>1276644</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>169747.66</v>
+        <v>382542.16</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>6351556.48</v>
+        <v>6564350.98</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>4.62</v>
+        <v>4.75</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>142129217.98</v>
+        <v>142463964.98</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>7.48</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="11">
@@ -22767,13 +22767,13 @@
         <v>2145619.45</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2015572.35</v>
+        <v>2025570.6</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>6253072.140000001</v>
+        <v>6263070.390000001</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>4.55</v>
+        <v>4.53</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>127727630.51</v>
@@ -22795,7 +22795,7 @@
         <v>2370564.76</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>10803413.04</v>
+        <v>10853996.9</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>3568340.77</v>
@@ -22804,10 +22804,10 @@
         <v>5938905.529999999</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>63722020.64</v>
+        <v>63772604.5</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>3.35</v>
@@ -22829,13 +22829,13 @@
         <v>542259.41</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>123368</v>
+        <v>202368</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>5628437.98</v>
+        <v>5707437.98</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>4.09</v>
+        <v>4.13</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>134762194.74</v>
@@ -22847,63 +22847,63 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Cessão ou locação de veículos</t>
+          <t>Diversas a especificar</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>61648999.53</v>
+        <v>45621032.07</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2114826.85</v>
+        <v>1756861.73</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>50040</v>
+        <v>752452.6</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>904244.78</v>
+        <v>1358698.35</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>3019071.63</v>
+        <v>3115560.08</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>61699039.53</v>
+        <v>46373484.67</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>3.25</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Diversas a especificar</t>
+          <t>Cessão ou locação de veículos</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>45621032.07</v>
+        <v>61648999.53</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>1756861.73</v>
+        <v>2114826.85</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>752452.6</v>
+        <v>50040</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1154315.55</v>
+        <v>904244.78</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2911177.28</v>
+        <v>3019071.63</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>46373484.67</v>
+        <v>61699039.53</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="16">
@@ -22928,7 +22928,7 @@
         <v>2760868.21</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>32675488.27</v>
@@ -22950,19 +22950,19 @@
         <v>1297889.49</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>284297.42</v>
+        <v>326185.19</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1210842.82</v>
+        <v>1211542.82</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2508732.31</v>
+        <v>2509432.31</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>19049050.9</v>
+        <v>19090938.67</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>1</v>
@@ -22990,7 +22990,7 @@
         <v>1607021</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>10924162.75</v>
@@ -23021,7 +23021,7 @@
         <v>1177839.04</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>15867628.34</v>
@@ -23052,7 +23052,7 @@
         <v>1013264.29</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>18566885.41</v>
@@ -23083,7 +23083,7 @@
         <v>725663.76</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>9455125.310000001</v>
@@ -23145,7 +23145,7 @@
         <v>683734.35</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>11938959.46</v>
@@ -23173,7 +23173,7 @@
         <v>151786.7</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>538409.7899999999</v>
+        <v>538409.79</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>0.39</v>
@@ -23198,7 +23198,7 @@
         <v>313333.95</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>931000</v>
+        <v>933500</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>0</v>
@@ -23210,7 +23210,7 @@
         <v>0.23</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>9978290.66</v>
+        <v>9980790.66</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0.53</v>
@@ -23325,7 +23325,7 @@
         <v>8076.8</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>48965.99000000001</v>
+        <v>48965.99</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>209391.57</v>
@@ -23446,7 +23446,7 @@
         <v>923.7</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>51744.89000000001</v>
+        <v>51744.89</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>40426.19</v>
@@ -23601,19 +23601,19 @@
         <v>11474.01</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>89478.69</v>
+        <v>89588.72</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>7470.34</v>
+        <v>7490.34</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>18944.35</v>
+        <v>18964.35</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>347660.76</v>
+        <v>347770.79</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0.02</v>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
         </is>
       </c>
     </row>
@@ -23823,7 +23823,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -23934,7 +23934,7 @@
         <v>7.85</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4898570244.67</v>
+        <v>4898750244.67</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1049723932.87</v>
@@ -24026,7 +24026,7 @@
         <v>4.03</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1817691708.82</v>
+        <v>1817696708.82</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>585224449.03</v>
@@ -24164,7 +24164,7 @@
         <v>3.43</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1294302106.67</v>
+        <v>1294367106.67</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>491285958.95</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-24 15:20:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 15:22:28.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 15:22:28.</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>41299</v>
+        <v>44299</v>
       </c>
     </row>
     <row r="48">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>6394</v>
+        <v>3398</v>
       </c>
     </row>
     <row r="50">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-25 09:17:40</t>
+          <t>2026-09-25 15:22:28</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="G63" s="6" t="n">
-        <v>58445503.79000001</v>
+        <v>58445503.79</v>
       </c>
       <c r="H63" s="6" t="n">
         <v>0.18</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 15:22:28.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 15:22:28.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 15:22:28.</t>
         </is>
       </c>
     </row>
@@ -19245,7 +19245,7 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>610846190.9299999</v>
+        <v>610954988.74</v>
       </c>
       <c r="E89" s="12" t="n">
         <v>23.62</v>
@@ -19268,7 +19268,7 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>167536445.27</v>
+        <v>167563007.99</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>6.48</v>
@@ -19291,7 +19291,7 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>160744853.84</v>
+        <v>160891101.2</v>
       </c>
       <c r="E91" s="12" t="n">
         <v>6.22</v>
@@ -19314,10 +19314,10 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>128421003.07</v>
+        <v>128441851.4</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4.97</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="93">
@@ -19337,7 +19337,7 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>121665049.83</v>
+        <v>121706586.89</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>4.7</v>
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>107359698.44</v>
+        <v>107451059.43</v>
       </c>
       <c r="E94" s="12" t="n">
         <v>4.15</v>
@@ -19383,10 +19383,10 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>103302328.44</v>
+        <v>103375597.68</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
@@ -19406,10 +19406,10 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>98668430.09999999</v>
+        <v>98688693.78</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="97">
@@ -19429,7 +19429,7 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>92487807.61</v>
+        <v>92496839.87</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>3.58</v>
@@ -19452,7 +19452,7 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>88715475.05</v>
+        <v>88730845.01000001</v>
       </c>
       <c r="E98" s="12" t="n">
         <v>3.43</v>
@@ -19475,7 +19475,7 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>84219299.45</v>
+        <v>84233880.98999999</v>
       </c>
       <c r="E99" s="12" t="n">
         <v>3.26</v>
@@ -19498,7 +19498,7 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>80477201.81999999</v>
+        <v>80516471.73</v>
       </c>
       <c r="E100" s="12" t="n">
         <v>3.11</v>
@@ -19521,7 +19521,7 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>73168666.61</v>
+        <v>73184842.70999999</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>2.83</v>
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>69607927.37</v>
+        <v>69616117.09999999</v>
       </c>
       <c r="E102" s="12" t="n">
         <v>2.69</v>
@@ -19567,7 +19567,7 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>67862763.75</v>
+        <v>67900019.25</v>
       </c>
       <c r="E103" s="12" t="n">
         <v>2.62</v>
@@ -19590,7 +19590,7 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>63501156.98</v>
+        <v>63516081.46</v>
       </c>
       <c r="E104" s="12" t="n">
         <v>2.46</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>57145340.82</v>
+        <v>57174482.15</v>
       </c>
       <c r="E105" s="12" t="n">
         <v>2.21</v>
@@ -19636,7 +19636,7 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>55666882.79</v>
+        <v>55675092.03</v>
       </c>
       <c r="E106" s="12" t="n">
         <v>2.15</v>
@@ -19659,7 +19659,7 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>47271306.16</v>
+        <v>47295265.79</v>
       </c>
       <c r="E107" s="12" t="n">
         <v>1.83</v>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>44961266.69</v>
+        <v>44973680.18</v>
       </c>
       <c r="E108" s="12" t="n">
         <v>1.74</v>
@@ -19705,7 +19705,7 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>44949128.99</v>
+        <v>44954101.79</v>
       </c>
       <c r="E109" s="12" t="n">
         <v>1.74</v>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>44012231.34</v>
+        <v>44021491.03</v>
       </c>
       <c r="E110" s="12" t="n">
         <v>1.7</v>
@@ -19751,7 +19751,7 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>42316501.36</v>
+        <v>42324034.78</v>
       </c>
       <c r="E111" s="12" t="n">
         <v>1.64</v>
@@ -19774,7 +19774,7 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>41549782.74</v>
+        <v>41557645.04</v>
       </c>
       <c r="E112" s="12" t="n">
         <v>1.61</v>
@@ -19797,7 +19797,7 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>35621478.43</v>
+        <v>35622700.33</v>
       </c>
       <c r="E113" s="12" t="n">
         <v>1.38</v>
@@ -19820,7 +19820,7 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>27627477.94</v>
+        <v>27646250.52</v>
       </c>
       <c r="E114" s="12" t="n">
         <v>1.07</v>
@@ -19843,7 +19843,7 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>25350876.29</v>
+        <v>25353499.59</v>
       </c>
       <c r="E115" s="12" t="n">
         <v>0.98</v>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 15:22:28.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 15:22:28.</t>
         </is>
       </c>
     </row>
@@ -23823,7 +23823,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 15:22:28.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 09:17:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-25 15:22:28.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -702,7 +702,7 @@
         <v>37.18</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>8707690841.16</v>
+        <v>8708281692.280001</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>26.88</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32396037569.77</v>
+        <v>32396628420.89</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-26 09:17:45.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 09:01:54.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-26 09:17:45.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 09:01:54.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>77264</v>
+        <v>77272</v>
       </c>
     </row>
     <row r="31">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32396037569.77</v>
+        <v>32396628420.89</v>
       </c>
     </row>
     <row r="34">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>47298</v>
+        <v>48146</v>
       </c>
     </row>
     <row r="48">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>870</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4773054933.99</v>
+        <v>4808511355.97</v>
       </c>
     </row>
     <row r="57">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4718944665.58</v>
+        <v>4754567725.27</v>
       </c>
     </row>
     <row r="58">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>481594978.42</v>
+        <v>501869180.65</v>
       </c>
     </row>
     <row r="59">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>435070177.29</v>
+        <v>454145362.3</v>
       </c>
     </row>
     <row r="60">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-26 09:17:45</t>
+          <t>2026-09-27 09:01:54</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="G48" s="6" t="n">
-        <v>75658784.07000001</v>
+        <v>75658784.06999999</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>0.23</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-26 09:17:45.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 09:01:54.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-26 09:17:45.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 09:01:54.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-26 09:17:45.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 09:01:54.</t>
         </is>
       </c>
     </row>
@@ -19245,7 +19245,7 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>624278126.8099999</v>
+        <v>624283690.54</v>
       </c>
       <c r="E89" s="12" t="n">
         <v>23.85</v>
@@ -19268,7 +19268,7 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>169521130.46</v>
+        <v>169522158.94</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>6.48</v>
@@ -19291,7 +19291,7 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>161929039.94</v>
+        <v>161936482.22</v>
       </c>
       <c r="E91" s="12" t="n">
         <v>6.19</v>
@@ -19314,7 +19314,7 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>129041550.02</v>
+        <v>129043454.95</v>
       </c>
       <c r="E92" s="12" t="n">
         <v>4.93</v>
@@ -19337,7 +19337,7 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>122192554.86</v>
+        <v>122195675.28</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>4.67</v>
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>108453001.54</v>
+        <v>108456139.85</v>
       </c>
       <c r="E94" s="12" t="n">
         <v>4.14</v>
@@ -19383,7 +19383,7 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>104612520.3</v>
+        <v>104615766.46</v>
       </c>
       <c r="E95" s="12" t="n">
         <v>4</v>
@@ -19406,7 +19406,7 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>100927707.42</v>
+        <v>100928292.37</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>3.86</v>
@@ -19429,7 +19429,7 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>92630495.37</v>
+        <v>92630748.37</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>3.54</v>
@@ -19452,7 +19452,7 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>90204087.08</v>
+        <v>90204957.91</v>
       </c>
       <c r="E98" s="12" t="n">
         <v>3.45</v>
@@ -19475,7 +19475,7 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>84326194.87</v>
+        <v>84326369.94</v>
       </c>
       <c r="E99" s="12" t="n">
         <v>3.22</v>
@@ -19498,7 +19498,7 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>81777912.06</v>
+        <v>81779449.09999999</v>
       </c>
       <c r="E100" s="12" t="n">
         <v>3.12</v>
@@ -19521,7 +19521,7 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>73446137.18000001</v>
+        <v>73446754.23999999</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>2.81</v>
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>69735726.16</v>
+        <v>69736088.06999999</v>
       </c>
       <c r="E102" s="12" t="n">
         <v>2.66</v>
@@ -19567,7 +19567,7 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>68894949.47</v>
+        <v>68896580.34999999</v>
       </c>
       <c r="E103" s="12" t="n">
         <v>2.63</v>
@@ -19590,7 +19590,7 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>63952697.66</v>
+        <v>63953073.2</v>
       </c>
       <c r="E104" s="12" t="n">
         <v>2.44</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>58193961.23</v>
+        <v>58194508.79</v>
       </c>
       <c r="E105" s="12" t="n">
         <v>2.22</v>
@@ -19636,7 +19636,7 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>56148967.83</v>
+        <v>56149337.83</v>
       </c>
       <c r="E106" s="12" t="n">
         <v>2.15</v>
@@ -19659,7 +19659,7 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>47393236.7</v>
+        <v>47394053.15</v>
       </c>
       <c r="E107" s="12" t="n">
         <v>1.81</v>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>46283661.9</v>
+        <v>46284731.82</v>
       </c>
       <c r="E108" s="12" t="n">
         <v>1.77</v>
@@ -19705,7 +19705,7 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>45152823.49</v>
+        <v>45153063.13</v>
       </c>
       <c r="E109" s="12" t="n">
         <v>1.73</v>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>44131438.22</v>
+        <v>44131907.24</v>
       </c>
       <c r="E110" s="12" t="n">
         <v>1.69</v>
@@ -19751,7 +19751,7 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>42374174.35</v>
+        <v>42374379.09</v>
       </c>
       <c r="E111" s="12" t="n">
         <v>1.62</v>
@@ -19774,7 +19774,7 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>41739509.63</v>
+        <v>41739817.8</v>
       </c>
       <c r="E112" s="12" t="n">
         <v>1.59</v>
@@ -19797,7 +19797,7 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>35624630.42</v>
+        <v>35624690.42</v>
       </c>
       <c r="E113" s="12" t="n">
         <v>1.36</v>
@@ -19820,7 +19820,7 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>27673572.69</v>
+        <v>27673990.25</v>
       </c>
       <c r="E114" s="12" t="n">
         <v>1.06</v>
@@ -19843,7 +19843,7 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>25358805.36</v>
+        <v>25359098.32</v>
       </c>
       <c r="E115" s="12" t="n">
         <v>0.97</v>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-26 09:17:45.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 09:01:54.</t>
         </is>
       </c>
     </row>
@@ -22581,13 +22581,13 @@
         <v>5043776.95</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>7671920.92</v>
+        <v>7793773.42</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27260890.51</v>
+        <v>27382743.01</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>18.72</v>
+        <v>18.65</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>432131697.64</v>
@@ -22609,22 +22609,22 @@
         <v>20822161.87</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>15440831.37</v>
+        <v>15515831.37</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>4970836.14</v>
+        <v>5120836.14</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>25792998.01</v>
+        <v>25942998.01</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>17.72</v>
+        <v>17.67</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>322079944.32</v>
+        <v>322154944.32</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>16.65</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="7">
@@ -22649,7 +22649,7 @@
         <v>16031380.14</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>11.01</v>
+        <v>10.92</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>129267947.35</v>
@@ -22680,7 +22680,7 @@
         <v>15832602.75</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>10.87</v>
+        <v>10.79</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>178497634.1</v>
@@ -22705,13 +22705,13 @@
         <v>10352176.89</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>7469958.82</v>
+        <v>7629708.82</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>14267057.45</v>
+        <v>14426807.45</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>106182009.34</v>
@@ -22742,7 +22742,7 @@
         <v>7281014.58</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>146467770.79</v>
@@ -22773,7 +22773,7 @@
         <v>6579241.1</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>4.52</v>
+        <v>4.48</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>129425907.52</v>
@@ -22795,22 +22795,22 @@
         <v>2398064.76</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>10853996.9</v>
+        <v>10611259.25</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>3568340.77</v>
+        <v>3833813.59</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>5966405.529999999</v>
+        <v>6231878.35</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>64480995.5</v>
+        <v>64238257.85</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="13">
@@ -22835,7 +22835,7 @@
         <v>5935999.58</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>139900815.51</v>
@@ -22860,13 +22860,13 @@
         <v>50040</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>904244.78</v>
+        <v>962161.61</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>3161155.83</v>
+        <v>3219072.66</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>62465731.73</v>
@@ -22897,7 +22897,7 @@
         <v>3107574.63</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>46919216.33</v>
@@ -22922,13 +22922,13 @@
         <v>212885.86</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>595304.64</v>
+        <v>649607.63</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>2815219.2</v>
+        <v>2869522.19</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>33012515.92</v>
@@ -22959,7 +22959,7 @@
         <v>2658732.31</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>19269657</v>
@@ -22984,13 +22984,13 @@
         <v>766982</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1400921</v>
+        <v>1585921</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1607021</v>
+        <v>1792021</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>11294162.75</v>
@@ -23015,10 +23015,10 @@
         <v>16144.98</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>177284.49</v>
+        <v>195694.49</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1231243.76</v>
+        <v>1249653.76</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>0.85</v>
@@ -23052,7 +23052,7 @@
         <v>1206319.04</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>16005356.34</v>
@@ -23077,13 +23077,13 @@
         <v>25327.5</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>48767.64</v>
+        <v>128380.68</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1029020.79</v>
+        <v>1108633.83</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>19006025.91</v>
@@ -23201,13 +23201,13 @@
         <v>933500</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>334753.95</v>
+        <v>394753.95</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>10399296.46</v>
@@ -23232,13 +23232,13 @@
         <v>19500</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>29510.94</v>
+        <v>69512.94</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>285706.22</v>
+        <v>325708.22</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>4369783.01</v>
@@ -23312,63 +23312,63 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Correspondências e despesas postais</t>
+          <t>Materiais de expediente</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>10466575.67</v>
+        <v>2091545.81</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>219276</v>
+        <v>168725.58</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>8104.55</v>
+        <v>8076.8</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0</v>
+        <v>54815.99</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>219276</v>
+        <v>223541.57</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>0.15</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>10474680.22</v>
+        <v>2099622.61</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.54</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Materiais de expediente</t>
+          <t>Correspondências e despesas postais</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>2091545.81</v>
+        <v>10466575.67</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>168725.58</v>
+        <v>219276</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>8076.8</v>
+        <v>8104.55</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>48965.99</v>
+        <v>0</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>217691.57</v>
+        <v>219276</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>0.15</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>2099622.61</v>
+        <v>10474680.22</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.11</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="31">
@@ -23601,19 +23601,19 @@
         <v>12476.63</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>89588.72</v>
+        <v>90688.66</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>7490.34</v>
+        <v>8337.379999999999</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>19966.97</v>
+        <v>20814.01</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>354732.11</v>
+        <v>355832.05</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0.02</v>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-26 09:17:45.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 09:01:54.</t>
         </is>
       </c>
     </row>
@@ -23825,7 +23825,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -24348,7 +24348,7 @@
         <v>4.6</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>930727493.99</v>
+        <v>931318345.11</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>192144239.43</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-26 09:17:45.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 09:01:54.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-26 09:17:45.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 09:01:54.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 15:11:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 15:11:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-27 15:11:15</t>
+          <t>2026-09-28 09:03:04</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 15:11:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 15:11:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 15:11:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 15:11:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 15:11:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 15:11:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-27 15:11:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4808553854.53</v>
+        <v>4808907836.6</v>
       </c>
     </row>
     <row r="57">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4754610203.83</v>
+        <v>4754847597.83</v>
       </c>
     </row>
     <row r="58">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>502584184.15</v>
+        <v>505778862.15</v>
       </c>
     </row>
     <row r="59">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>454860362.3</v>
+        <v>458055040.3</v>
       </c>
     </row>
     <row r="60">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-28 09:03:04</t>
+          <t>2026-09-28 15:01:22</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>75659161.21000001</v>
+        <v>75659161.20999999</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0.23</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
         </is>
       </c>
     </row>
@@ -22578,7 +22578,7 @@
         <v>20301520.71</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>5043776.95</v>
+        <v>5069389.45</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>7793773.42</v>
@@ -22590,7 +22590,7 @@
         <v>18.45</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>443996722.16</v>
+        <v>444022334.66</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>22.24</v>
@@ -22702,7 +22702,7 @@
         <v>6876918.63</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>10352176.89</v>
+        <v>10360176.89</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>7629708.82</v>
@@ -22714,7 +22714,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>108155653.64</v>
+        <v>108163653.64</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>5.42</v>
@@ -22733,7 +22733,7 @@
         <v>7610790.2</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1276644</v>
+        <v>1293819</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>382542.16</v>
@@ -22745,7 +22745,7 @@
         <v>5.25</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>152062636.23</v>
+        <v>152079811.23</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>7.62</v>
@@ -22764,7 +22764,7 @@
         <v>5043295.5</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2145619.45</v>
+        <v>2148319.45</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>2025570.6</v>
@@ -22776,7 +22776,7 @@
         <v>4.64</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>131513829.82</v>
+        <v>131516529.82</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>6.59</v>
@@ -22826,7 +22826,7 @@
         <v>2460064.76</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>10611259.25</v>
+        <v>10635259.25</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>3833813.59</v>
@@ -22838,7 +22838,7 @@
         <v>4.13</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>65687233.64</v>
+        <v>65711233.64</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>3.29</v>
@@ -22950,7 +22950,7 @@
         <v>1447189.49</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>326185.19</v>
+        <v>360815.21</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>1211542.82</v>
@@ -22962,7 +22962,7 @@
         <v>1.75</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>19607067.63</v>
+        <v>19641697.65</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0.98</v>
@@ -23167,7 +23167,7 @@
         <v>386653.95</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>933500</v>
+        <v>933850</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>60000</v>
@@ -23179,7 +23179,7 @@
         <v>0.29</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>10612368.8</v>
+        <v>10612718.8</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0.53</v>
@@ -23229,7 +23229,7 @@
         <v>268457.36</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>19500</v>
+        <v>22074.32</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>69512.94</v>
@@ -23241,7 +23241,7 @@
         <v>0.22</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>4571371.15</v>
+        <v>4573945.470000001</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0.23</v>
@@ -23415,7 +23415,7 @@
         <v>77483.94</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3658.83</v>
+        <v>5031.08</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>0</v>
@@ -23427,7 +23427,7 @@
         <v>0.05</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>661413.4399999999</v>
+        <v>662785.6899999999</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0.03</v>
@@ -23601,7 +23601,7 @@
         <v>12943.55</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>90708.66</v>
+        <v>90882.64</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>8340.879999999999</v>
@@ -23613,7 +23613,7 @@
         <v>0.01</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>362979.89</v>
+        <v>363153.87</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0.02</v>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -640,7 +640,7 @@
         <v>2.06</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>337146041.14</v>
+        <v>337221041.14</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1.04</v>
@@ -671,7 +671,7 @@
         <v>53.81</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>12355307266.73</v>
+        <v>12355427266.73</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>38.14</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32396628420.89</v>
+        <v>32396823420.89</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>77272</v>
+        <v>77274</v>
       </c>
     </row>
     <row r="31">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32396628420.89</v>
+        <v>32396823420.89</v>
       </c>
     </row>
     <row r="34">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-28 15:01:22</t>
+          <t>2026-09-28 21:01:50</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>575680870.9499999</v>
+        <v>575680870.95</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1.78</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>75659161.20999999</v>
+        <v>75659161.21000001</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0.23</v>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="G48" s="6" t="n">
-        <v>75658784.06999999</v>
+        <v>75658784.07000001</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>0.23</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="G59" s="6" t="n">
-        <v>62944315.4</v>
+        <v>62944315.40000001</v>
       </c>
       <c r="H59" s="6" t="n">
         <v>0.19</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
         </is>
       </c>
     </row>
@@ -24072,7 +24072,7 @@
         <v>5.4</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2533019885.72</v>
+        <v>2533139885.72</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>567960113.11</v>
@@ -24348,7 +24348,7 @@
         <v>4.6</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>931318345.11</v>
+        <v>931393345.11</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>195840397.38</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 15:01:22.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 03:01:53.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 03:01:53.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-28 21:01:50</t>
+          <t>2026-09-29 03:01:53</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 03:01:53.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 03:01:53.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 03:01:53.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 03:01:53.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 03:01:53.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 03:01:53.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-28 21:01:50.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 03:01:53.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>11293</v>
+        <v>11294</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>53.81</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>12355427266.73</v>
+        <v>12355909075.85</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>38.14</v>
@@ -882,13 +882,13 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>20987</v>
+        <v>20988</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32396823420.89</v>
+        <v>32397305230.01</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 15:04:24.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 15:04:24.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20987</v>
+        <v>20988</v>
       </c>
     </row>
     <row r="14">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20987</v>
+        <v>20988</v>
       </c>
     </row>
     <row r="15">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20987</v>
+        <v>20988</v>
       </c>
     </row>
     <row r="16">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20984</v>
+        <v>20985</v>
       </c>
     </row>
     <row r="19">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>77274</v>
+        <v>77280</v>
       </c>
     </row>
     <row r="31">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32396823420.89</v>
+        <v>32397305230.01</v>
       </c>
     </row>
     <row r="34">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-29 15:04:24</t>
+          <t>2026-09-29 21:01:44</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>75659161.20999999</v>
+        <v>75659161.21000001</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0.23</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 15:04:24.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 15:04:24.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 15:04:24.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
         </is>
       </c>
     </row>
@@ -21338,10 +21338,10 @@
         </is>
       </c>
       <c r="D180" s="6" t="n">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="181">
@@ -21594,7 +21594,7 @@
         <v>425</v>
       </c>
       <c r="E191" s="12" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="192">
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 15:04:24.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 15:04:24.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
         </is>
       </c>
     </row>
@@ -24204,13 +24204,13 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>6.76</v>
+        <v>6.77</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3339120580.55</v>
+        <v>3339602389.67</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>489418353.19</v>
@@ -24299,7 +24299,7 @@
         <v>1126</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>5.37</v>
+        <v>5.36</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>1457794419.27</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 15:04:24.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 15:04:24.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
         </is>
       </c>
     </row>
@@ -28228,7 +28228,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Nota 2: outras 4501 candidaturas NAO declararam receita alguma, das quais 924 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
+          <t>Nota 2: outras 4502 candidaturas NAO declararam receita alguma, das quais 924 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
         </is>
       </c>
     </row>
@@ -28844,7 +28844,7 @@
         <v>67.79000000000001</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>66</v>
@@ -28853,7 +28853,7 @@
         <v>76986</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>17.81</v>
+        <v>17.83</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>211367594.27</v>
@@ -29593,7 +29593,7 @@
         <v>73.69</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>20987</v>
+        <v>20988</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>1790</v>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-29 21:01:44</t>
+          <t>2026-09-30 03:01:16</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-29 21:01:44.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 09:03:54.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 09:03:54.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-30 03:01:16</t>
+          <t>2026-09-30 09:03:54</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>75659161.21000001</v>
+        <v>75659161.20999999</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0.23</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 09:03:54.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 09:03:54.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 09:03:54.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 09:03:54.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 09:03:54.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 09:03:54.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 03:01:16.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 09:03:54.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -671,7 +671,7 @@
         <v>53.81</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>12355909075.85</v>
+        <v>12356029456.34</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>38.14</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32397305230.01</v>
+        <v>32397425610.5</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 15:13:21.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 15:13:21.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>77280</v>
+        <v>77287</v>
       </c>
     </row>
     <row r="31">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32397305230.01</v>
+        <v>32397425610.5</v>
       </c>
     </row>
     <row r="34">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4828055659.18</v>
+        <v>4834201798.98</v>
       </c>
     </row>
     <row r="57">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4771135909.28</v>
+        <v>4778281329.28</v>
       </c>
     </row>
     <row r="58">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>513845434.28</v>
+        <v>528045214.04</v>
       </c>
     </row>
     <row r="59">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>465919753.7</v>
+        <v>476858476.1</v>
       </c>
     </row>
     <row r="60">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-30 15:13:21</t>
+          <t>2026-10-01 10:33:02</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>575680870.9499999</v>
+        <v>575680870.95</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1.78</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>75659161.20999999</v>
+        <v>75659161.21000001</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0.23</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="G63" s="6" t="n">
-        <v>58445503.79</v>
+        <v>58445503.79000001</v>
       </c>
       <c r="H63" s="6" t="n">
         <v>0.18</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 15:13:21.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 15:13:21.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 15:13:21.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 15:13:21.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
         </is>
       </c>
     </row>
@@ -22581,19 +22581,19 @@
         <v>5990625.45</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>7793773.42</v>
+        <v>8052840.52</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>29944904</v>
+        <v>30203971.1</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>18.71</v>
+        <v>18.49</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>458330010.06</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>22.04</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="6">
@@ -22609,22 +22609,22 @@
         <v>22526202.73</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>15675831.37</v>
+        <v>15829031.37</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>5120836.14</v>
+        <v>5254836.14</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>27647038.87</v>
+        <v>27781038.87</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>17.27</v>
+        <v>17.01</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>339365331.9</v>
+        <v>339518531.9</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>16.32</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="7">
@@ -22640,7 +22640,7 @@
         <v>18071583.12</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>328350</v>
+        <v>328650</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>162830.33</v>
@@ -22649,13 +22649,13 @@
         <v>18234413.45</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>11.39</v>
+        <v>11.16</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>206512488.29</v>
+        <v>206512788.29</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>9.93</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="8">
@@ -22674,13 +22674,13 @@
         <v>6113730.34</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>13495322.55</v>
+        <v>14830072.55</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>16538970.14</v>
+        <v>17873720.14</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>10.33</v>
+        <v>10.94</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>136721289.8</v>
@@ -22702,22 +22702,22 @@
         <v>7060017.63</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>10360176.89</v>
+        <v>9164676.890000001</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>7769708.82</v>
+        <v>8666108.82</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>14829726.45</v>
+        <v>15726126.45</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>9.26</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>110842203.64</v>
+        <v>109646703.64</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.33</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="10">
@@ -22736,13 +22736,13 @@
         <v>1367612</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>382542.16</v>
+        <v>472076.16</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>8713971.99</v>
+        <v>8803505.99</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>5.44</v>
+        <v>5.39</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>162688883.5</v>
@@ -22767,19 +22767,19 @@
         <v>542259.41</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>202368</v>
+        <v>270650.66</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>7681448.78</v>
+        <v>7749731.44</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>4.8</v>
+        <v>4.74</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>154319282.15</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>7.42</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="12">
@@ -22798,13 +22798,13 @@
         <v>2148319.45</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>2025570.6</v>
+        <v>2054580.6</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>7196159.960000001</v>
+        <v>7225169.960000001</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4.5</v>
+        <v>4.42</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>136550181.98</v>
@@ -22826,19 +22826,19 @@
         <v>2576933.74</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>10668209.27</v>
+        <v>10710109.27</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>3860313.59</v>
+        <v>4232613.59</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>6437247.33</v>
+        <v>6809547.33</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>4.02</v>
+        <v>4.17</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>67165758.36</v>
+        <v>67207658.36</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>3.23</v>
@@ -22860,13 +22860,13 @@
         <v>50040</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>962161.61</v>
+        <v>987161.61</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>3529932.02</v>
+        <v>3554932.02</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>67219062.33</v>
@@ -22897,7 +22897,7 @@
         <v>3401023.78</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>48722266.66</v>
@@ -22928,7 +22928,7 @@
         <v>3112459.75</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>21078988.82</v>
@@ -22953,13 +22953,13 @@
         <v>212885.86</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>649607.63</v>
+        <v>657107.63</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>3014398.19</v>
+        <v>3021898.19</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>34621441.92</v>
@@ -22984,13 +22984,13 @@
         <v>891275</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1585921</v>
+        <v>1630921</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1812021</v>
+        <v>1857021</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>11837387.65</v>
@@ -23021,7 +23021,7 @@
         <v>1293333.76</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>10440788.11</v>
@@ -23052,7 +23052,7 @@
         <v>1217919.04</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>17118044.58</v>
@@ -23083,7 +23083,7 @@
         <v>1162181.93</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>20859987.55</v>
@@ -23114,7 +23114,7 @@
         <v>966073.29</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>9879105.67</v>
@@ -23145,7 +23145,7 @@
         <v>708832.35</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>12327241.96</v>
@@ -23176,7 +23176,7 @@
         <v>399253.95</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>11576593.4</v>
@@ -23269,7 +23269,7 @@
         <v>318080.58</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>4891188.27</v>
@@ -23300,7 +23300,7 @@
         <v>299961.15</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>12151906.48</v>
@@ -23331,7 +23331,7 @@
         <v>269240.64</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H29" s="6" t="n">
         <v>3081820.14</v>
@@ -23517,7 +23517,7 @@
         <v>40173.94</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H35" s="6" t="n">
         <v>927554.89</v>
@@ -23601,19 +23601,19 @@
         <v>13299.67</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>92174.00999999999</v>
+        <v>92993.81</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>8413.48</v>
+        <v>8627.08</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>21713.15</v>
+        <v>21926.75</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>400487.27</v>
+        <v>401307.07</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0.02</v>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 15:13:21.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
         <v>5.21</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>2591573797.35</v>
+        <v>2591694177.84</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>190867359.45</v>
@@ -24973,7 +24973,7 @@
         <v>4041559.33</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>6970270.9</v>
+        <v>6970270.899999999</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>26.21</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 15:13:21.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-09-30 15:13:21.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 15:18:36.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 15:18:36.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-01 10:33:02</t>
+          <t>2026-10-01 15:18:36</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>575680870.95</v>
+        <v>575680870.9499999</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1.78</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="G63" s="6" t="n">
-        <v>58445503.79000001</v>
+        <v>58445503.79</v>
       </c>
       <c r="H63" s="6" t="n">
         <v>0.18</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 15:18:36.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 15:18:36.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 15:18:36.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 15:18:36.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 15:18:36.</t>
         </is>
       </c>
     </row>
@@ -24973,7 +24973,7 @@
         <v>4041559.33</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>6970270.899999999</v>
+        <v>6970270.9</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>26.21</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 15:18:36.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 10:33:02.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-01 15:18:36.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -665,16 +665,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>11294</v>
+        <v>11295</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>53.81</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>12006494956.34</v>
+        <v>12006774956.34</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>37.46</v>
+        <v>37.47</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>1718637324.19</v>
@@ -882,13 +882,13 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>20988</v>
+        <v>20989</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32047377110.5</v>
+        <v>32047657110.5</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 15:14:13.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 15:14:13.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20988</v>
+        <v>20989</v>
       </c>
     </row>
     <row r="14">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20988</v>
+        <v>20989</v>
       </c>
     </row>
     <row r="15">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20988</v>
+        <v>20989</v>
       </c>
     </row>
     <row r="16">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20985</v>
+        <v>20986</v>
       </c>
     </row>
     <row r="19">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>77288</v>
+        <v>77289</v>
       </c>
     </row>
     <row r="31">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32047377110.5</v>
+        <v>32047657110.5</v>
       </c>
     </row>
     <row r="34">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-03 15:14:13</t>
+          <t>2026-10-03 16:42:27</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>575680870.9499999</v>
+        <v>575680870.95</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1.8</v>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="G58" s="6" t="n">
-        <v>62944315.4</v>
+        <v>62944315.40000001</v>
       </c>
       <c r="H58" s="6" t="n">
         <v>0.2</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 15:14:13.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 15:14:13.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 15:14:13.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
         </is>
       </c>
     </row>
@@ -21384,7 +21384,7 @@
         </is>
       </c>
       <c r="D182" s="6" t="n">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E182" s="12" t="n">
         <v>3.4</v>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 15:14:13.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 15:14:13.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
         </is>
       </c>
     </row>
@@ -24894,13 +24894,13 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>242782021.57</v>
+        <v>243062021.57</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>9423852.75</v>
@@ -25035,7 +25035,7 @@
         <v>467</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>463597846.48</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 15:14:13.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 15:14:13.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
         </is>
       </c>
     </row>
@@ -28228,7 +28228,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Nota 2: outras 4292 candidaturas NAO declararam receita alguma, das quais 924 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
+          <t>Nota 2: outras 4293 candidaturas NAO declararam receita alguma, das quais 924 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
         </is>
       </c>
     </row>
@@ -28672,7 +28672,7 @@
         <v>75.26000000000001</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>76</v>
@@ -28681,7 +28681,7 @@
         <v>92118</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>10.18</v>
+        <v>10.2</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>242341798.97</v>
@@ -29593,7 +29593,7 @@
         <v>73.69</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>20988</v>
+        <v>20989</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>1790</v>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -640,10 +640,10 @@
         <v>2.06</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>337221041.14</v>
+        <v>338296381.14</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>45409970.61</v>
@@ -674,7 +674,7 @@
         <v>12006774956.34</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>37.47</v>
+        <v>37.46</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>1718637324.19</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32047657110.5</v>
+        <v>32048732450.5</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 21:02:10.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 21:02:10.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>77289</v>
+        <v>77294</v>
       </c>
     </row>
     <row r="31">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32047657110.5</v>
+        <v>32048732450.5</v>
       </c>
     </row>
     <row r="34">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-03 16:42:27</t>
+          <t>2026-10-03 21:02:10</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>575680870.95</v>
+        <v>575680870.9499999</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1.8</v>
@@ -3121,7 +3121,7 @@
         <v>184278955.2</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>53</v>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="G46" s="6" t="n">
-        <v>75659161.20999999</v>
+        <v>75659161.21000001</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>0.24</v>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="G58" s="6" t="n">
-        <v>62944315.40000001</v>
+        <v>62944315.4</v>
       </c>
       <c r="H58" s="6" t="n">
         <v>0.2</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 21:02:10.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 21:02:10.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 21:02:10.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 21:02:10.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 21:02:10.</t>
         </is>
       </c>
     </row>
@@ -23934,7 +23934,7 @@
         <v>7.85</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4898750244.67</v>
+        <v>4898820044.67</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1120393927.99</v>
@@ -24072,7 +24072,7 @@
         <v>5.4</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2533139885.72</v>
+        <v>2534145425.72</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>609952077.85</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 21:02:10.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 16:42:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-03 21:02:10.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -9373,7 +9373,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>PL; UNIÃO; REPUBLICANOS; PT</t>
+          <t>PL; UNIÃO; REPUBLICANOS; MDB</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO; PSDB; PP; PL</t>
+          <t>UNIÃO; PSDB; REPUBLICANOS; PP</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>ANDRÉ DO PRADO (PL); ELEUSES PAIVA (PSD)</t>
+          <t>ELEUSES PAIVA (PSD); ANDRÉ DO PRADO (PL)</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>PDT; PCDOB; PSD; UNIÃO</t>
+          <t>PDT; PSD; PCDOB; UNIÃO</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>LULA (PT); PATRUS ANANIAS (PT)</t>
+          <t>LULA (PT); MENDONÇA FILHO (PL)</t>
         </is>
       </c>
     </row>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>PL; PSD; UNIÃO; PT</t>
+          <t>PSD; PL; UNIÃO; PT</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL); ARLINDO CHINAGLIA (PT)</t>
+          <t>FLAVIO BOLSONARO (PL); CARLOS ZARATTINI (PT)</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>PSD; MDB; UNIÃO; REPUBLICANOS</t>
+          <t>PSD; MDB; REPUBLICANOS; UNIÃO</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>PP; PL; NOVO; PSD</t>
+          <t>PP; NOVO; PL; PSD</t>
         </is>
       </c>
       <c r="O68" s="4" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>PSD; REPUBLICANOS; MDB; PL</t>
+          <t>PSD; MDB; REPUBLICANOS; PL</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>TARCÍSIO (REPUBLICANOS); DUARTE NOGUEIRA (PSD)</t>
+          <t>TARCÍSIO (REPUBLICANOS); BALEIA ROSSI (MDB)</t>
         </is>
       </c>
     </row>
@@ -13533,12 +13533,12 @@
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>REDE; PSOL; PT; PSD</t>
+          <t>REDE; PSD; PSOL; PT</t>
         </is>
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>MARINA SILVA (REDE); SÔNIA GUAJAJARA (PSOL)</t>
+          <t>MARINA SILVA (REDE); RACHEL SHEHERAZADE (PSD)</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>DOUTOR JHONY (PSD); SILVIA DA PESCA (PODE)</t>
+          <t>DOUTOR JHONY (PSD); MERSINHO LUCENA (PSD)</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>PL; PSD; PP; REPUBLICANOS</t>
+          <t>PL; PSD; PT; PP</t>
         </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>PT; UNIÃO; REPUBLICANOS; MDB</t>
+          <t>UNIÃO; PT; REPUBLICANOS; MDB</t>
         </is>
       </c>
       <c r="O94" s="4" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
-          <t>PL; PV; PT; PDT</t>
+          <t>PL; PT; PV; PDT</t>
         </is>
       </c>
       <c r="O98" s="4" t="inlineStr">

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -671,10 +671,10 @@
         <v>53.81</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>12006774956.34</v>
+        <v>12007234956.34</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>37.46</v>
+        <v>37.47</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>1740653890.53</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32048732450.5</v>
+        <v>32049192450.5</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 10:04:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 15:05:45.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 10:04:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 15:05:45.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>77294</v>
+        <v>77297</v>
       </c>
     </row>
     <row r="31">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32048732450.5</v>
+        <v>32049192450.5</v>
       </c>
     </row>
     <row r="34">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>6661888</v>
       </c>
     </row>
     <row r="61">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-05 10:04:29</t>
+          <t>2026-10-05 15:05:45</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["VOTOS_VALIDOS_1T", "RESULTADO"]</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="G46" s="6" t="n">
-        <v>75659161.20999999</v>
+        <v>75659161.21000001</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>0.24</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 10:04:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 15:05:45.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 10:04:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 15:05:45.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 10:04:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 15:05:45.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 10:04:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 15:05:45.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 10:04:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 15:05:45.</t>
         </is>
       </c>
     </row>
@@ -24900,7 +24900,7 @@
         <v>2.77</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>243062021.57</v>
+        <v>243522021.57</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>9643703.76</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 10:04:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 15:05:45.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 10:04:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-05 15:05:45.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 09:12:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 15:16:20.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 09:12:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 15:16:20.</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>758</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-06 09:12:51</t>
+          <t>2026-10-06 15:16:20</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 09:12:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 15:16:20.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 09:12:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 15:16:20.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 09:12:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 15:16:20.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 09:12:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 15:16:20.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 09:12:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 15:16:20.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 09:12:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 15:16:20.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 09:12:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-06 15:16:20.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -646,13 +646,13 @@
         <v>1.06</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>47335768.64</v>
+        <v>47440502.89</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>0.73</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>30855614.59</v>
+        <v>30974167.79</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0.6899999999999999</v>
@@ -671,22 +671,22 @@
         <v>53.81</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>12007234956.34</v>
+        <v>12007434756.34</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>37.47</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1767069979.72</v>
+        <v>1772759804.56</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>27.25</v>
+        <v>27.28</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>1151720566.96</v>
+        <v>1158942727.8</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>25.9</v>
+        <v>25.97</v>
       </c>
     </row>
     <row r="9">
@@ -708,16 +708,16 @@
         <v>27.17</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3386050020.8</v>
+        <v>3389970239.32</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>52.21</v>
+        <v>52.16</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2243795886.96</v>
+        <v>2251200736.08</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>50.46</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="10">
@@ -739,16 +739,16 @@
         <v>4.02</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>582983480.66</v>
+        <v>584544062.41</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>8.99</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>469931824.4</v>
+        <v>470907613.19</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>10.57</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="11">
@@ -770,16 +770,16 @@
         <v>3.7</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>185428004.32</v>
+        <v>187323426.67</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>165229936.98</v>
+        <v>164366964.99</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="12">
@@ -801,13 +801,13 @@
         <v>6.48</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>516880886.67</v>
+        <v>517357478.44</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>7.97</v>
+        <v>7.96</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>384827248.34</v>
+        <v>385831334.03</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>8.65</v>
@@ -888,19 +888,19 @@
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32049192450.5</v>
+        <v>32049392250.5</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>6485748140.809999</v>
+        <v>6499395514.29</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>4446361078.23</v>
+        <v>4462223543.88</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-07 09:05:33.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-07 09:05:33.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32049192450.5</v>
+        <v>32049392250.5</v>
       </c>
     </row>
     <row r="34">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>6661888</v>
+        <v>6737183</v>
       </c>
     </row>
     <row r="61">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-07 09:05:33</t>
+          <t>2026-10-08 06:53:14</t>
         </is>
       </c>
     </row>
@@ -2993,13 +2993,13 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>3556350.86</v>
+        <v>3656350.86</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>550000</v>
+        <v>650000</v>
       </c>
       <c r="O22" s="6" t="n">
         <v>212062</v>
@@ -5833,13 +5833,13 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>2563171</v>
+        <v>2568735</v>
       </c>
       <c r="M62" s="6" t="n">
         <v>0.04</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>38104</v>
+        <v>43668</v>
       </c>
       <c r="O62" s="6" t="n">
         <v>25067</v>
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="n">
-        <v>1928900</v>
+        <v>1964900</v>
       </c>
       <c r="M64" s="6" t="n">
         <v>0.03</v>
@@ -5984,7 +5984,7 @@
         <v>0</v>
       </c>
       <c r="O64" s="6" t="n">
-        <v>479000</v>
+        <v>515000</v>
       </c>
       <c r="P64" s="6" t="n">
         <v>449900</v>
@@ -6614,16 +6614,16 @@
         </is>
       </c>
       <c r="L73" s="6" t="n">
-        <v>1050150</v>
+        <v>1078710</v>
       </c>
       <c r="M73" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>1050000</v>
+        <v>1077350</v>
       </c>
       <c r="O73" s="6" t="n">
-        <v>150</v>
+        <v>1350</v>
       </c>
       <c r="P73" s="6" t="n">
         <v>0</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-07 09:05:33.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
         </is>
       </c>
     </row>
@@ -9032,19 +9032,19 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>5908</v>
+        <v>5923</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>267872827.58</v>
+        <v>269798117.44</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>6.02</v>
+        <v>6.05</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>260308320.31</v>
+        <v>262152136.67</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>97.18000000000001</v>
+        <v>97.17</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -9097,19 +9097,19 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>93956491.40000001</v>
+        <v>94364219.55</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>2.11</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>92179435.70999999</v>
+        <v>92587163.86</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>98.11</v>
+        <v>98.12</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>31000000</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>15000000</v>
@@ -9425,16 +9425,16 @@
         <v>207</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>12732015.88</v>
+        <v>12912015.88</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0.29</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>12359711.88</v>
+        <v>12539711.88</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>97.08</v>
+        <v>97.12</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
@@ -9583,12 +9583,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>28.573.576/0001-67</t>
+          <t>08.142.850/0001-36</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>URISSANE COMUNICACAO LTDA</t>
+          <t>WBL GRAFICA E EDITORA LTDA</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Portais, provedores de conteúdo e outros serviços de informação na Internet</t>
+          <t>Serviços de acabamentos gráficos</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>FERRAZ DE VASCONCELOS</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -9617,28 +9617,28 @@
         </is>
       </c>
       <c r="I14" s="5" t="n">
-        <v>6</v>
+        <v>240</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>8920500</v>
+        <v>9055989.939999999</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>6879000</v>
+        <v>8037942.98</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>77.11</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>PT; PDT; MDB; PSDB</t>
+          <t>PL; PSD; NOVO; PP</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>FERNANDO HADDAD (PT); GLEISI (PT)</t>
+          <t>ELEUSES PAIVA (PSD); ANDRÉ DO PRADO (PL)</t>
         </is>
       </c>
     </row>
@@ -9648,12 +9648,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>08.142.850/0001-36</t>
+          <t>28.573.576/0001-67</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>WBL GRAFICA E EDITORA LTDA</t>
+          <t>URISSANE COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Serviços de acabamentos gráficos</t>
+          <t>Portais, provedores de conteúdo e outros serviços de informação na Internet</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>FERRAZ DE VASCONCELOS</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -9682,28 +9682,28 @@
         </is>
       </c>
       <c r="I15" s="5" t="n">
-        <v>240</v>
+        <v>6</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>8905924.41</v>
+        <v>8920500</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>7885901.51</v>
+        <v>6879000</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>88.55</v>
+        <v>77.11</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>PL; PSD; NOVO; PP</t>
+          <t>PT; PDT; MDB; PSDB</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>ELEUSES PAIVA (PSD); ANDRÉ DO PRADO (PL)</t>
+          <t>FERNANDO HADDAD (PT); GLEISI (PT)</t>
         </is>
       </c>
     </row>
@@ -9945,16 +9945,16 @@
         <v>20</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>6276827</v>
+        <v>6279227</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0.14</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>4669782.32</v>
+        <v>4672182.32</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>74.40000000000001</v>
+        <v>74.41</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
@@ -9973,37 +9973,37 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>***.883.424-**</t>
+          <t>05.060.706/0003-24</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>EULINA PONCE DE LEON</t>
+          <t>SANTANA   ASSOCIADOS MARKETING E PROPAGANDA LTDA</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>PESSOA FÍSICA</t>
+          <t>PESSOA JURÍDICA</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>SALVADOR</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>Receita (BrasilAPI)</t>
         </is>
       </c>
       <c r="I20" s="5" t="n">
@@ -10016,19 +10016,19 @@
         <v>0.13</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>1000</v>
+        <v>6000000</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.02</v>
+        <v>100</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>DANI PORTELA (PT)</t>
+          <t>ACM NETO (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -10038,37 +10038,37 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>05.060.706/0003-24</t>
+          <t>***.883.424-**</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>SANTANA   ASSOCIADOS MARKETING E PROPAGANDA LTDA</t>
+          <t>EULINA PONCE DE LEON</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>PESSOA JURÍDICA</t>
+          <t>PESSOA FÍSICA</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>...</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>...</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>SALVADOR</t>
+          <t>...</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Receita (BrasilAPI)</t>
+          <t>...</t>
         </is>
       </c>
       <c r="I21" s="5" t="n">
@@ -10081,19 +10081,19 @@
         <v>0.13</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>6000000</v>
+        <v>1000</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>100</v>
+        <v>0.02</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>ACM NETO (UNIÃO)</t>
+          <t>DANI PORTELA (PT)</t>
         </is>
       </c>
     </row>
@@ -10137,10 +10137,10 @@
         </is>
       </c>
       <c r="I22" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>5935949.63</v>
+        <v>5941049.63</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0.13</v>
@@ -10149,7 +10149,7 @@
         <v>4377145.24</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>73.73999999999999</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
@@ -10202,16 +10202,16 @@
         </is>
       </c>
       <c r="I23" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>5624132.58</v>
+        <v>5628876.28</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0.13</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>3187138.97</v>
+        <v>3189855.97</v>
       </c>
       <c r="M23" s="6" t="n">
         <v>56.67</v>
@@ -10270,16 +10270,16 @@
         <v>66</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>5325934</v>
+        <v>5425934</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0.12</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4405407.5</v>
+        <v>4505407.5</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>82.72</v>
+        <v>83.03</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
@@ -10660,16 +10660,16 @@
         <v>222</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>4691058.18</v>
+        <v>4690491.89</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0.11</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>4244235.95</v>
+        <v>4243669.66</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>90.48</v>
+        <v>90.47</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
@@ -10917,16 +10917,16 @@
         </is>
       </c>
       <c r="I34" s="5" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>4342573</v>
+        <v>4349875.07</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>4331735.77</v>
+        <v>4339037.84</v>
       </c>
       <c r="M34" s="6" t="n">
         <v>99.75</v>
@@ -11053,7 +11053,7 @@
         <v>4228431.96</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>3387031.96</v>
@@ -11310,16 +11310,16 @@
         <v>28</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>3979904.9</v>
+        <v>3992074.4</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>3333355.3</v>
+        <v>3345524.8</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>83.75</v>
+        <v>83.8</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>3790000</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="L43" s="6" t="n">
         <v>2050000</v>
@@ -11570,13 +11570,13 @@
         <v>1</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>3735863.99</v>
+        <v>3748738.99</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>3735863.99</v>
+        <v>3748738.99</v>
       </c>
       <c r="M44" s="6" t="n">
         <v>100</v>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>04.405.470/0001-96</t>
+          <t>67.949.812/0001-59</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>CONTACTO RELACOES PUBLICAS LTDA</t>
+          <t>ALGORITMO DADOS ESTRATEGIA E COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Agências de notícias</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>NATAL</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -11762,7 +11762,7 @@
         </is>
       </c>
       <c r="I47" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J47" s="6" t="n">
         <v>3600000</v>
@@ -11771,19 +11771,19 @@
         <v>0.08</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>PT; PSB; REDE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>ELMANO DE FREITAS (PT); CID GOMES (PSB)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -11793,12 +11793,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>67.949.812/0001-59</t>
+          <t>04.405.470/0001-96</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>ALGORITMO DADOS ESTRATEGIA E COMUNICACAO LTDA</t>
+          <t>CONTACTO RELACOES PUBLICAS LTDA</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -11808,17 +11808,17 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Agências de notícias</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>NATAL</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -11827,7 +11827,7 @@
         </is>
       </c>
       <c r="I48" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J48" s="6" t="n">
         <v>3600000</v>
@@ -11836,19 +11836,19 @@
         <v>0.08</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>3600000</v>
+        <v>0</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT; PSB; REDE</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>ELMANO DE FREITAS (PT); CID GOMES (PSB)</t>
         </is>
       </c>
     </row>
@@ -12155,13 +12155,13 @@
         <v>17</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>3490488.61</v>
+        <v>3491368.61</v>
       </c>
       <c r="K53" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>3154984.57</v>
+        <v>3155864.57</v>
       </c>
       <c r="M53" s="6" t="n">
         <v>90.39</v>
@@ -12313,12 +12313,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>22.317.550/0001-71</t>
+          <t>24.347.979/0001-37</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>M DESIGNER CITY LTDA</t>
+          <t>MACIEL ART DESIGNER GRAFICO - LTDA</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Edição de livros</t>
+          <t>Comércio varejista de artigos recreativos e esportivos</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -12347,28 +12347,28 @@
         </is>
       </c>
       <c r="I56" s="5" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>3341293.16</v>
+        <v>3355250.5</v>
       </c>
       <c r="K56" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>2206257.46</v>
+        <v>2294770</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>66.03</v>
+        <v>68.39</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>PT; REPUBLICANOS; UNIÃO; PSD</t>
+          <t>PSD; PT; PODE; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>LULA (PT); JILMAR TATTO (PT)</t>
+          <t>DANIEL COELHO (PSD); LUNA ZARATTINI (PT)</t>
         </is>
       </c>
     </row>
@@ -12378,12 +12378,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>24.347.979/0001-37</t>
+          <t>22.317.550/0001-71</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>MACIEL ART DESIGNER GRAFICO - LTDA</t>
+          <t>M DESIGNER CITY LTDA</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Comércio varejista de artigos recreativos e esportivos</t>
+          <t>Edição de livros</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -12412,28 +12412,28 @@
         </is>
       </c>
       <c r="I57" s="5" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>3295250.5</v>
+        <v>3342913.16</v>
       </c>
       <c r="K57" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>2294770</v>
+        <v>2232877.46</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>69.64</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>PSD; PT; PODE; REPUBLICANOS</t>
+          <t>PT; REPUBLICANOS; UNIÃO; PSD</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>DANIEL COELHO (PSD); LUNA ZARATTINI (PT)</t>
+          <t>LULA (PT); JILMAR TATTO (PT)</t>
         </is>
       </c>
     </row>
@@ -12870,7 +12870,7 @@
         <v>51</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>3102120</v>
+        <v>3095620</v>
       </c>
       <c r="K64" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -12879,7 +12879,7 @@
         <v>2638885</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>85.06999999999999</v>
+        <v>85.25</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>41</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>3075046.88</v>
+        <v>3076436.88</v>
       </c>
       <c r="K66" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -13009,7 +13009,7 @@
         <v>1172389.14</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>38.13</v>
+        <v>38.11</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
@@ -13517,19 +13517,19 @@
         </is>
       </c>
       <c r="I74" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>2965914.9</v>
+        <v>2973690.65</v>
       </c>
       <c r="K74" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L74" s="6" t="n">
-        <v>2286605.39</v>
+        <v>2313704.49</v>
       </c>
       <c r="M74" s="6" t="n">
-        <v>77.09999999999999</v>
+        <v>77.81</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
@@ -13548,12 +13548,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>46.439.622/0001-11</t>
+          <t>24.935.788/0001-96</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>FEIRA BANDEIRAS E IMPRESSOS LTDA</t>
+          <t>AFA INDUSTRIA COMERCIO E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -13563,17 +13563,17 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
+          <t>Confecção de roupas profissionais</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>FEIRA DE SANTANA</t>
+          <t>APARECIDA DE GOIANIA</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -13582,28 +13582,28 @@
         </is>
       </c>
       <c r="I75" s="5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>2956779.23</v>
+        <v>2964622.1</v>
       </c>
       <c r="K75" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L75" s="6" t="n">
-        <v>2752822.74</v>
+        <v>2169411.1</v>
       </c>
       <c r="M75" s="6" t="n">
-        <v>93.09999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO; PT; PSB; PSD</t>
+          <t>SOLIDARIEDADE; UNIÃO; PSDB; MDB</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>PROFESSORA DAYANE PIMENTEL (UNIÃO); VITOR BONFIM (PSB)</t>
+          <t>DENES PEREIRA (SOLIDARIEDADE); SALMA DA PESTALOZZI (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -13613,12 +13613,12 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>00.212.872/0001-13</t>
+          <t>46.439.622/0001-11</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>ASA SUL INDUSTRIA E COMERCIO DE MALHAS LTDA</t>
+          <t>FEIRA BANDEIRAS E IMPRESSOS LTDA</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -13628,17 +13628,17 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Confecção de peças do vestuário, exceto roupas íntimas</t>
+          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>FORTALEZA</t>
+          <t>FEIRA DE SANTANA</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -13647,28 +13647,28 @@
         </is>
       </c>
       <c r="I76" s="5" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>2908749</v>
+        <v>2956779.23</v>
       </c>
       <c r="K76" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L76" s="6" t="n">
-        <v>2580439</v>
+        <v>2752822.74</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>88.70999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>PSB; PT; UNIÃO; PRD</t>
+          <t>UNIÃO; PT; PSB; PSD</t>
         </is>
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>DAYANY DO CAPITÃO (UNIÃO); TAINAH MARINHO (PSB)</t>
+          <t>PROFESSORA DAYANE PIMENTEL (UNIÃO); VITOR BONFIM (PSB)</t>
         </is>
       </c>
     </row>
@@ -13678,12 +13678,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>24.935.788/0001-96</t>
+          <t>00.212.872/0001-13</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>AFA INDUSTRIA COMERCIO E SERVICOS LTDA</t>
+          <t>ASA SUL INDUSTRIA E COMERCIO DE MALHAS LTDA</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -13693,17 +13693,17 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Confecção de roupas profissionais</t>
+          <t>Confecção de peças do vestuário, exceto roupas íntimas</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>APARECIDA DE GOIANIA</t>
+          <t>FORTALEZA</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -13712,28 +13712,28 @@
         </is>
       </c>
       <c r="I77" s="5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>2884622.1</v>
+        <v>2908749</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L77" s="6" t="n">
-        <v>2089411.1</v>
+        <v>2580439</v>
       </c>
       <c r="M77" s="6" t="n">
-        <v>72.43000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE; UNIÃO; MDB; PSDB</t>
+          <t>PSB; PT; UNIÃO; PRD</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>DENES PEREIRA (SOLIDARIEDADE); SALMA DA PESTALOZZI (UNIÃO)</t>
+          <t>DAYANY DO CAPITÃO (UNIÃO); TAINAH MARINHO (PSB)</t>
         </is>
       </c>
     </row>
@@ -13777,19 +13777,19 @@
         </is>
       </c>
       <c r="I78" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>2847831.1</v>
+        <v>2848600.1</v>
       </c>
       <c r="K78" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L78" s="6" t="n">
-        <v>2151863.8</v>
+        <v>2152632.8</v>
       </c>
       <c r="M78" s="6" t="n">
-        <v>75.56</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
@@ -14328,12 +14328,12 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>16.724.877/0001-65</t>
+          <t>56.019.930/0001-41</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>EBA - COMUNICACAO E MARKETING POLITICO LTDA</t>
+          <t>INOVE IMPRESSOES GRAFICAS E MARKETING POLITICO LTDA</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -14343,17 +14343,17 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>NATAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -14362,28 +14362,28 @@
         </is>
       </c>
       <c r="I87" s="5" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>2590000</v>
+        <v>2604716.91</v>
       </c>
       <c r="K87" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L87" s="6" t="n">
-        <v>750000</v>
+        <v>1664652.53</v>
       </c>
       <c r="M87" s="6" t="n">
-        <v>28.96</v>
+        <v>63.91</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>PL; PODE; PSDB</t>
+          <t>PL; PSB; UNIÃO; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>ÁLVARO DIAS (PL); STYVENSON VALENTIM (PODE)</t>
+          <t>VINICIUS DINIZ (PL); BERNARDO ROSSI (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -14393,12 +14393,12 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>31.321.080/0001-00</t>
+          <t>16.724.877/0001-65</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>UNIGRAFICA INDUSTRIA GRAFICA LTDA</t>
+          <t>EBA - COMUNICACAO E MARKETING POLITICO LTDA</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de embalagens de papel</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>PARNAMIRIM</t>
+          <t>NATAL</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -14427,28 +14427,28 @@
         </is>
       </c>
       <c r="I88" s="5" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>2582999.36</v>
+        <v>2590000</v>
       </c>
       <c r="K88" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L88" s="6" t="n">
-        <v>1845935</v>
+        <v>750000</v>
       </c>
       <c r="M88" s="6" t="n">
-        <v>71.45999999999999</v>
+        <v>28.96</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>PL; UNIÃO; PSD; PP</t>
+          <t>PL; PODE; PSDB</t>
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>JUNINHO SAIA RODADA (PL); ZENAIDE MAIA (PSD)</t>
+          <t>ÁLVARO DIAS (PL); STYVENSON VALENTIM (PODE)</t>
         </is>
       </c>
     </row>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>64.752.158/0001-09</t>
+          <t>31.321.080/0001-00</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>OKAN COMUNICACAO LTDA</t>
+          <t>UNIGRAFICA INDUSTRIA GRAFICA LTDA</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -14473,17 +14473,17 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Fabricação de embalagens de papel</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>PARNAMIRIM</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -14492,28 +14492,28 @@
         </is>
       </c>
       <c r="I89" s="5" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>2567000</v>
+        <v>2582999.36</v>
       </c>
       <c r="K89" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L89" s="6" t="n">
-        <v>2517000</v>
+        <v>1845935</v>
       </c>
       <c r="M89" s="6" t="n">
-        <v>98.05</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>PT; PSOL; UNIÃO</t>
+          <t>PL; UNIÃO; PSD; PP</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>PATRUS ANANIAS (PT); DUDA SALABERT (PSOL)</t>
+          <t>JUNINHO SAIA RODADA (PL); ZENAIDE MAIA (PSD)</t>
         </is>
       </c>
     </row>
@@ -14523,12 +14523,12 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>26.983.273/0001-97</t>
+          <t>64.752.158/0001-09</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>VITORINO   MENDONCA LTDA</t>
+          <t>OKAN COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -14538,17 +14538,17 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -14557,28 +14557,28 @@
         </is>
       </c>
       <c r="I90" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>2550000</v>
+        <v>2567000</v>
       </c>
       <c r="K90" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L90" s="6" t="n">
-        <v>1950000</v>
+        <v>2517000</v>
       </c>
       <c r="M90" s="6" t="n">
-        <v>76.47</v>
+        <v>98.05</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT; PSOL; UNIÃO</t>
         </is>
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>WILDER MORAIS (PL); MARCOS ROGÉRIO (PL)</t>
+          <t>PATRUS ANANIAS (PT); DUDA SALABERT (PSOL)</t>
         </is>
       </c>
     </row>
@@ -14588,12 +14588,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>35.593.706/0001-99</t>
+          <t>26.983.273/0001-97</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>UNIPAUTA FORMULARIOS LTDA</t>
+          <t>VITORINO   MENDONCA LTDA</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -14603,17 +14603,17 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Impressão de material de segurança</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>OLINDA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -14622,28 +14622,28 @@
         </is>
       </c>
       <c r="I91" s="5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>2531795</v>
+        <v>2550000</v>
       </c>
       <c r="K91" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L91" s="6" t="n">
-        <v>2316995</v>
+        <v>1950000</v>
       </c>
       <c r="M91" s="6" t="n">
-        <v>91.52</v>
+        <v>76.47</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>MDB; PCDOB; REPUBLICANOS; PODE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>IZA ARRUDA (MDB); RENILDO CALHEIROS (PCDOB)</t>
+          <t>WILDER MORAIS (PL); MARCOS ROGÉRIO (PL)</t>
         </is>
       </c>
     </row>
@@ -14653,12 +14653,12 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>17.340.447/0001-02</t>
+          <t>67.820.413/0001-93</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>MARICLEYDSON COSTA DA SILVA  LTDA</t>
+          <t>LGS SERVICOS LTDA</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -14673,12 +14673,12 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>NATAL</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -14687,28 +14687,28 @@
         </is>
       </c>
       <c r="I92" s="5" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>2521373</v>
+        <v>2544850</v>
       </c>
       <c r="K92" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L92" s="6" t="n">
-        <v>1711900.5</v>
+        <v>2259050</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>67.90000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>PL; PT; PV; PDT</t>
+          <t>PSD; REPUBLICANOS; UNIÃO; PL</t>
         </is>
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>NINA (PL); LUÍZ EDUARDO (PL)</t>
+          <t>CAPITÃO SAMUEL (UNIÃO); GRACINHA GARCEZ (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -14718,12 +14718,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>56.019.930/0001-41</t>
+          <t>35.593.706/0001-99</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>INOVE IMPRESSOES GRAFICAS E MARKETING POLITICO LTDA</t>
+          <t>UNIPAUTA FORMULARIOS LTDA</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -14733,17 +14733,17 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Impressão de material de segurança</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>OLINDA</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -14752,28 +14752,28 @@
         </is>
       </c>
       <c r="I93" s="5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>2513960.91</v>
+        <v>2531795</v>
       </c>
       <c r="K93" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L93" s="6" t="n">
-        <v>1573896.53</v>
+        <v>2316995</v>
       </c>
       <c r="M93" s="6" t="n">
-        <v>62.61</v>
+        <v>91.52</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>PL; PSB; UNIÃO; REPUBLICANOS</t>
+          <t>MDB; PCDOB; REPUBLICANOS; PODE</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>VINICIUS DINIZ (PL); BERNARDO ROSSI (UNIÃO)</t>
+          <t>IZA ARRUDA (MDB); RENILDO CALHEIROS (PCDOB)</t>
         </is>
       </c>
     </row>
@@ -14783,12 +14783,12 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>68.154.614/0001-61</t>
+          <t>17.340.447/0001-02</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>ESTUDIO 90 PRODUCOES LTDA</t>
+          <t>MARICLEYDSON COSTA DA SILVA  LTDA</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -14798,17 +14798,17 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>NATAL</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -14817,28 +14817,28 @@
         </is>
       </c>
       <c r="I94" s="5" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>2500000</v>
+        <v>2521373</v>
       </c>
       <c r="K94" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L94" s="6" t="n">
-        <v>2500000</v>
+        <v>1786590.5</v>
       </c>
       <c r="M94" s="6" t="n">
-        <v>100</v>
+        <v>70.86</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>MDB; PSD</t>
+          <t>PL; PT; PV; PDT</t>
         </is>
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>GABRIEL SOUZA (MDB); FREDERICO ANTUNES (PSD)</t>
+          <t>NINA (PL); LUÍZ EDUARDO (PL)</t>
         </is>
       </c>
     </row>
@@ -14848,12 +14848,12 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>05.555.136/0001-81</t>
+          <t>22.966.876/0001-20</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>CONDADO MARKETING LTDA</t>
+          <t>REDE DE NEGOCIOS E PRODUCAO DE EVENTOS LTDA</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -14863,17 +14863,17 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Atividades de organização de eventos, exceto culturais e esportivos</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>LAJEADO</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -14891,19 +14891,19 @@
         <v>0.06</v>
       </c>
       <c r="L95" s="6" t="n">
-        <v>2500000</v>
+        <v>1000000</v>
       </c>
       <c r="M95" s="6" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>JULIANA BRIZOLA (PDT)</t>
+          <t>RAQUEL LYRA (PSD)</t>
         </is>
       </c>
     </row>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>22.966.876/0001-20</t>
+          <t>05.555.136/0001-81</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>REDE DE NEGOCIOS E PRODUCAO DE EVENTOS LTDA</t>
+          <t>CONDADO MARKETING LTDA</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -14928,17 +14928,17 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Atividades de organização de eventos, exceto culturais e esportivos</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>LAJEADO</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -14956,19 +14956,19 @@
         <v>0.06</v>
       </c>
       <c r="L96" s="6" t="n">
-        <v>1000000</v>
+        <v>2500000</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>RAQUEL LYRA (PSD)</t>
+          <t>JULIANA BRIZOLA (PDT)</t>
         </is>
       </c>
     </row>
@@ -14978,12 +14978,12 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>67.820.413/0001-93</t>
+          <t>68.154.614/0001-61</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>LGS SERVICOS LTDA</t>
+          <t>ESTUDIO 90 PRODUCOES LTDA</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -14993,17 +14993,17 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -15012,28 +15012,28 @@
         </is>
       </c>
       <c r="I97" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J97" s="6" t="n">
-        <v>2493850</v>
+        <v>2500000</v>
       </c>
       <c r="K97" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L97" s="6" t="n">
-        <v>2181050</v>
+        <v>2500000</v>
       </c>
       <c r="M97" s="6" t="n">
-        <v>87.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>PSD; REPUBLICANOS; UNIÃO; PL</t>
+          <t>MDB; PSD</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>CAPITÃO SAMUEL (UNIÃO); GRACINHA GARCEZ (REPUBLICANOS)</t>
+          <t>GABRIEL SOUZA (MDB); FREDERICO ANTUNES (PSD)</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-07 09:05:33.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
         </is>
       </c>
     </row>
@@ -15626,13 +15626,13 @@
         <v>1417</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>964348352.83</v>
+        <v>964378352.83</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>14.87</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="6">
@@ -15664,7 +15664,7 @@
         <v>576606752.99</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>8.890000000000001</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -15690,13 +15690,13 @@
         <v>704</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>528534996.97</v>
+        <v>528558048.97</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>8.15</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -15719,13 +15719,13 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>482371435.23</v>
+        <v>483327337.61</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>7.44</v>
@@ -15754,13 +15754,13 @@
         <v>798</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>472401618.52</v>
+        <v>472611618.52</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>7.28</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="10">
@@ -15783,16 +15783,16 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>402739251.3</v>
+        <v>402819251.3</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>6.21</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="11">
@@ -15824,7 +15824,7 @@
         <v>361526325.06</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>5.57</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="12">
@@ -15850,13 +15850,13 @@
         <v>836</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>233245027.03</v>
+        <v>233295027.03</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="13">
@@ -15882,10 +15882,10 @@
         <v>845</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>208346091.46</v>
+        <v>208376091.46</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>3.21</v>
@@ -15911,13 +15911,13 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>142066485.78</v>
+        <v>142076485.78</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>2.19</v>
@@ -16016,7 +16016,7 @@
         <v>89213574.70999999</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="18">
@@ -16039,13 +16039,13 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>79756011.43000001</v>
+        <v>80071011.43000001</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>1.23</v>
@@ -16074,10 +16074,10 @@
         <v>339</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>66340947.27</v>
+        <v>66440947.27</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>1.02</v>
@@ -16170,10 +16170,10 @@
         <v>151</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1849</v>
+        <v>1866</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>45413096.12</v>
+        <v>45522472.12</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0.7</v>
@@ -16304,7 +16304,7 @@
         <v>25003823.64</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="27">
@@ -16359,13 +16359,13 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1201</v>
+        <v>1212</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>2345</v>
+        <v>2384</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>15814735.96</v>
+        <v>15862750.11</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0.24</v>
@@ -16432,7 +16432,7 @@
         <v>12670598.3</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="31">
@@ -16679,13 +16679,13 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>776</v>
+        <v>796</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>6204749.92</v>
+        <v>6223706.05</v>
       </c>
       <c r="H38" s="6" t="n">
         <v>0.1</v>
@@ -16714,10 +16714,10 @@
         <v>59</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>6026129.13</v>
+        <v>6056127.43</v>
       </c>
       <c r="H39" s="6" t="n">
         <v>0.09</v>
@@ -16746,10 +16746,10 @@
         <v>140</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>6015315.61</v>
+        <v>6019815.61</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>0.09</v>
@@ -16807,13 +16807,13 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>5569474.45</v>
+        <v>5577830.67</v>
       </c>
       <c r="H42" s="6" t="n">
         <v>0.09</v>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>PARTIDO NOVO - MINAS GERAIS - MG - ESTADUAL</t>
+          <t>REPUBLICANOS RIO GRANDE DO SUL - RS - ESTADUAL</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -16867,17 +16867,17 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>1044</v>
+        <v>245</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>5332249.61</v>
+        <v>5335314</v>
       </c>
       <c r="H44" s="6" t="n">
         <v>0.08</v>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS RIO GRANDE DO SUL - RS - ESTADUAL</t>
+          <t>PARTIDO NOVO - MINAS GERAIS - MG - ESTADUAL</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -16899,17 +16899,17 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>243</v>
+        <v>1045</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>5299783</v>
+        <v>5334249.61</v>
       </c>
       <c r="H45" s="6" t="n">
         <v>0.08</v>
@@ -16921,7 +16921,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>PARTIDO SOCIAL DEMOCRATICO</t>
+          <t>REPUBLICANOS - MINAS GERAIS - MG - ESTADUAL</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -16931,17 +16931,17 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>5225000</v>
+        <v>5251869.74</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>0.08</v>
@@ -16953,7 +16953,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS - MINAS GERAIS - MG - ESTADUAL</t>
+          <t>PARTIDO SOCIAL DEMOCRATICO</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -16963,17 +16963,17 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="F47" s="5" t="n">
-        <v>170</v>
-      </c>
       <c r="G47" s="6" t="n">
-        <v>5201869.74</v>
+        <v>5225000</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0.08</v>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-07 09:05:33.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
         </is>
       </c>
     </row>
@@ -17313,10 +17313,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>934299547.1</v>
+        <v>935524547.88</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>14.41</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="6">
@@ -17336,10 +17336,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>534282294.27</v>
+        <v>536492301.75</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>8.24</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="7">
@@ -17359,7 +17359,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>499396080.69</v>
+        <v>500176968.65</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>7.7</v>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>345443239.42</v>
+        <v>345824803.85</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>5.33</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="9">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>344151335.45</v>
+        <v>345027195.36</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>5.31</v>
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>318096004.64</v>
+        <v>318528670.12</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.9</v>
@@ -17451,7 +17451,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>259725823.68</v>
+        <v>259982154.41</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4</v>
@@ -17474,10 +17474,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>244308904.76</v>
+        <v>244547395.26</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="13">
@@ -17497,10 +17497,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>230628971.85</v>
+        <v>231028562.48</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="14">
@@ -17520,7 +17520,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>221972949.17</v>
+        <v>222531299.84</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>3.42</v>
@@ -17543,10 +17543,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>213477278.38</v>
+        <v>214384400.5</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="16">
@@ -17566,10 +17566,10 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>190353983.9</v>
+        <v>191061311.88</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="17">
@@ -17589,10 +17589,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>185428004.32</v>
+        <v>187323426.67</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="18">
@@ -17612,7 +17612,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>164269169.71</v>
+        <v>164729989.99</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>2.53</v>
@@ -17635,7 +17635,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>160935288</v>
+        <v>161162563.31</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>2.48</v>
@@ -17658,10 +17658,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>154156738.59</v>
+        <v>154325409.09</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="21">
@@ -17681,7 +17681,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>149263234.88</v>
+        <v>149268375.28</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>2.3</v>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>145290064.16</v>
+        <v>146052855.8</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="23">
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>144954748.36</v>
+        <v>145049721.48</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>2.23</v>
@@ -17750,10 +17750,10 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>141088030.19</v>
+        <v>141159582.32</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="25">
@@ -17773,7 +17773,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>121877051.62</v>
+        <v>122153368.29</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>1.88</v>
@@ -17796,7 +17796,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>118530986.22</v>
+        <v>118642264.33</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>1.83</v>
@@ -17819,7 +17819,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>117550093.37</v>
+        <v>117865243.1</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>1.81</v>
@@ -17842,10 +17842,10 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>115913132.66</v>
+        <v>115916347.26</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="29">
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>115661926.51</v>
+        <v>115848420.48</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>1.78</v>
@@ -17888,7 +17888,7 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>105685049.13</v>
+        <v>105716419.13</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>1.63</v>
@@ -17911,7 +17911,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>105187690.11</v>
+        <v>105206552.11</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>1.62</v>
@@ -17934,7 +17934,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>103820519.67</v>
+        <v>103865363.67</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>1.6</v>
@@ -17957,10 +17957,10 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>148104514.06</v>
+        <v>148105636.54</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>27.49</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="34">
@@ -17980,10 +17980,10 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>35183323.72</v>
+        <v>35734691.7</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>6.53</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="35">
@@ -18003,10 +18003,10 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>31233591.35</v>
+        <v>31619091.35</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>5.8</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="36">
@@ -18029,7 +18029,7 @@
         <v>27914615.98</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="37">
@@ -18049,7 +18049,7 @@
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>21684804.7</v>
+        <v>21733441.1</v>
       </c>
       <c r="E37" s="12" t="n">
         <v>4.02</v>
@@ -18075,7 +18075,7 @@
         <v>21166735.92</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="39">
@@ -18095,7 +18095,7 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>17790460.01</v>
+        <v>17840460.01</v>
       </c>
       <c r="E39" s="12" t="n">
         <v>3.3</v>
@@ -18118,7 +18118,7 @@
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>17643906.7</v>
+        <v>17679437.7</v>
       </c>
       <c r="E40" s="12" t="n">
         <v>3.27</v>
@@ -18144,7 +18144,7 @@
         <v>17543696.24</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="42">
@@ -18164,7 +18164,7 @@
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>17071108.64</v>
+        <v>17121108.64</v>
       </c>
       <c r="E42" s="12" t="n">
         <v>3.17</v>
@@ -18187,10 +18187,10 @@
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>16953697.06</v>
+        <v>16979850.61</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="44">
@@ -18236,7 +18236,7 @@
         <v>15345139.27</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="46">
@@ -18259,7 +18259,7 @@
         <v>12909864.17</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="47">
@@ -18279,7 +18279,7 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>12557314.14</v>
+        <v>12557489.96</v>
       </c>
       <c r="E47" s="12" t="n">
         <v>2.33</v>
@@ -18328,7 +18328,7 @@
         <v>11635177.76</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="50">
@@ -18351,7 +18351,7 @@
         <v>10539115.61</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="51">
@@ -18397,7 +18397,7 @@
         <v>8166532.99</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="53">
@@ -18466,7 +18466,7 @@
         <v>7791238</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="56">
@@ -18486,7 +18486,7 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>7510933.45</v>
+        <v>7513506.75</v>
       </c>
       <c r="E56" s="12" t="n">
         <v>1.39</v>
@@ -18532,10 +18532,10 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>6934342.45</v>
+        <v>6935311.45</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="59">
@@ -18601,10 +18601,10 @@
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>621068075.63</v>
+        <v>621095945.2</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>12.89</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="62">
@@ -18624,7 +18624,7 @@
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>411858890.94</v>
+        <v>412041448.93</v>
       </c>
       <c r="E62" s="12" t="n">
         <v>8.550000000000001</v>
@@ -18647,10 +18647,10 @@
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>374632407.2</v>
+        <v>375318192.89</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>7.77</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="64">
@@ -18670,7 +18670,7 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>282528963.37</v>
+        <v>282663417.37</v>
       </c>
       <c r="E64" s="12" t="n">
         <v>5.86</v>
@@ -18693,7 +18693,7 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>248563445.1</v>
+        <v>248624423.42</v>
       </c>
       <c r="E65" s="12" t="n">
         <v>5.16</v>
@@ -18739,7 +18739,7 @@
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>199424569.32</v>
+        <v>199434569.32</v>
       </c>
       <c r="E67" s="12" t="n">
         <v>4.14</v>
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>164083596.42</v>
+        <v>164158536.19</v>
       </c>
       <c r="E70" s="12" t="n">
         <v>3.41</v>
@@ -18854,7 +18854,7 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>145716980.5</v>
+        <v>145766980.5</v>
       </c>
       <c r="E72" s="12" t="n">
         <v>3.02</v>
@@ -18880,7 +18880,7 @@
         <v>136625008.59</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="74">
@@ -18923,7 +18923,7 @@
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>119655278.8</v>
+        <v>119665278.8</v>
       </c>
       <c r="E75" s="12" t="n">
         <v>2.48</v>
@@ -18946,10 +18946,10 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>108585260.16</v>
+        <v>108892976.98</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="77">
@@ -18960,16 +18960,16 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>105814677.94</v>
+        <v>105817480.74</v>
       </c>
       <c r="E77" s="12" t="n">
         <v>2.2</v>
@@ -18983,19 +18983,19 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>105607480.74</v>
+        <v>105814677.94</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="79">
@@ -19015,7 +19015,7 @@
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>104049277.83</v>
+        <v>104059277.83</v>
       </c>
       <c r="E79" s="12" t="n">
         <v>2.16</v>
@@ -19199,7 +19199,7 @@
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>87393403.06</v>
+        <v>87405825.06</v>
       </c>
       <c r="E87" s="12" t="n">
         <v>1.81</v>
@@ -19245,10 +19245,10 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>793600180.01</v>
+        <v>798051618.42</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>25.73</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="90">
@@ -19268,7 +19268,7 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>200591482.38</v>
+        <v>201026073.13</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>6.5</v>
@@ -19291,10 +19291,10 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>184077152.59</v>
+        <v>185083512.5</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>5.97</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="92">
@@ -19314,10 +19314,10 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>155507044.8</v>
+        <v>155751874.92</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="93">
@@ -19337,10 +19337,10 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>140797368.73</v>
+        <v>139721770.38</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="94">
@@ -19360,10 +19360,10 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>123804197.69</v>
+        <v>124277198.89</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="95">
@@ -19383,10 +19383,10 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>122457512.74</v>
+        <v>122552846.66</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="96">
@@ -19406,10 +19406,10 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>117830730.58</v>
+        <v>117926888.02</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="97">
@@ -19429,10 +19429,10 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>106038221.48</v>
+        <v>106191707.33</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="98">
@@ -19452,10 +19452,10 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>104807509.93</v>
+        <v>105812466.09</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="99">
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>93566777.43000001</v>
+        <v>93358987.54000001</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="100">
@@ -19498,10 +19498,10 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>92433885.11</v>
+        <v>92675251.43000001</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="101">
@@ -19521,10 +19521,10 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>85284453.97</v>
+        <v>85619840.72</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="102">
@@ -19544,10 +19544,10 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>84062604.75</v>
+        <v>84766144.15000001</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="103">
@@ -19567,7 +19567,7 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>73669865.14</v>
+        <v>73862440.19</v>
       </c>
       <c r="E103" s="12" t="n">
         <v>2.39</v>
@@ -19590,10 +19590,10 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>73073788.01000001</v>
+        <v>73095482.01000001</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="105">
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>69381701.06</v>
+        <v>69385205.05</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="106">
@@ -19636,7 +19636,7 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>59382282.3</v>
+        <v>59667766.88</v>
       </c>
       <c r="E106" s="12" t="n">
         <v>1.93</v>
@@ -19659,7 +19659,7 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>56244117.34</v>
+        <v>56411850.88</v>
       </c>
       <c r="E107" s="12" t="n">
         <v>1.82</v>
@@ -19682,10 +19682,10 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>53061036.31</v>
+        <v>53535821.99</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="109">
@@ -19705,7 +19705,7 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>51626529.74</v>
+        <v>51772049.74</v>
       </c>
       <c r="E109" s="12" t="n">
         <v>1.67</v>
@@ -19731,7 +19731,7 @@
         <v>51392372.95</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="111">
@@ -19751,10 +19751,10 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>47176793.13</v>
+        <v>47850311.83</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="112">
@@ -19774,10 +19774,10 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>47133565.83</v>
+        <v>47186787.26</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="113">
@@ -19797,7 +19797,7 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>37591906.43</v>
+        <v>37694623.51</v>
       </c>
       <c r="E113" s="12" t="n">
         <v>1.22</v>
@@ -19820,7 +19820,7 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>30631155.78</v>
+        <v>30651514.87</v>
       </c>
       <c r="E114" s="12" t="n">
         <v>0.99</v>
@@ -19843,10 +19843,10 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>28227267.34</v>
+        <v>28231264.3</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="116">
@@ -19866,7 +19866,7 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>1096696</v>
+        <v>1246696</v>
       </c>
       <c r="E116" s="12" t="n">
         <v>0.04</v>
@@ -19912,10 +19912,10 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>145669933.8</v>
+        <v>146164004.47</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>20.32</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="119">
@@ -19935,10 +19935,10 @@
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>54999442.05</v>
+        <v>56205816.06</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>7.67</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="120">
@@ -19958,7 +19958,7 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>51081969.3</v>
+        <v>51482416.15</v>
       </c>
       <c r="E120" s="12" t="n">
         <v>7.13</v>
@@ -19981,10 +19981,10 @@
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>49610803.19</v>
+        <v>49754664.88</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>6.92</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="122">
@@ -20004,10 +20004,10 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>33870973.27</v>
+        <v>34055066.7</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>4.73</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="123">
@@ -20027,10 +20027,10 @@
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>32987691.84</v>
+        <v>33156633.25</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>4.6</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="124">
@@ -20050,7 +20050,7 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>30813923.79</v>
+        <v>31008189.51</v>
       </c>
       <c r="E124" s="12" t="n">
         <v>4.3</v>
@@ -20073,10 +20073,10 @@
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>26857832.04</v>
+        <v>27638788.4</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="126">
@@ -20096,10 +20096,10 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>22305142.46</v>
+        <v>22359572.16</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="127">
@@ -20119,10 +20119,10 @@
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>21977442.89</v>
+        <v>22012312.44</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="128">
@@ -20142,7 +20142,7 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>21688392.29</v>
+        <v>21883524.82</v>
       </c>
       <c r="E128" s="12" t="n">
         <v>3.03</v>
@@ -20156,19 +20156,19 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
-        <v>21379731.02</v>
+        <v>21447871.33</v>
       </c>
       <c r="E129" s="12" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="130">
@@ -20179,16 +20179,16 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>21282240.66</v>
+        <v>21422880.06</v>
       </c>
       <c r="E130" s="12" t="n">
         <v>2.97</v>
@@ -20211,10 +20211,10 @@
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>20192093.23</v>
+        <v>20192402.55</v>
       </c>
       <c r="E131" s="12" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="132">
@@ -20234,10 +20234,10 @@
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>19649640.12</v>
+        <v>19652740.12</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="133">
@@ -20257,10 +20257,10 @@
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>16071182.79</v>
+        <v>16313832.27</v>
       </c>
       <c r="E133" s="12" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="134">
@@ -20280,10 +20280,10 @@
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>16001955.69</v>
+        <v>16160265.73</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="135">
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>15523544.28</v>
+        <v>15633544.78</v>
       </c>
       <c r="E135" s="12" t="n">
         <v>2.17</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>14612855.76</v>
+        <v>14744225.24</v>
       </c>
       <c r="E136" s="12" t="n">
         <v>2.04</v>
@@ -20349,7 +20349,7 @@
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>14222216.66</v>
+        <v>14282031.16</v>
       </c>
       <c r="E137" s="12" t="n">
         <v>1.98</v>
@@ -20372,10 +20372,10 @@
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>13526805.08</v>
+        <v>13530019.68</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="139">
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="D139" s="6" t="n">
-        <v>10267145.24</v>
+        <v>10334138.36</v>
       </c>
       <c r="E139" s="12" t="n">
         <v>1.43</v>
@@ -20418,10 +20418,10 @@
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>9738667.689999999</v>
+        <v>9739917.689999999</v>
       </c>
       <c r="E140" s="12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="141">
@@ -20441,10 +20441,10 @@
         </is>
       </c>
       <c r="D141" s="6" t="n">
-        <v>8661487.1</v>
+        <v>8770912.27</v>
       </c>
       <c r="E141" s="12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="142">
@@ -20464,7 +20464,7 @@
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>8479950.220000001</v>
+        <v>8511320.220000001</v>
       </c>
       <c r="E142" s="12" t="n">
         <v>1.18</v>
@@ -20490,7 +20490,7 @@
         <v>8285966.18</v>
       </c>
       <c r="E143" s="12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="144">
@@ -20510,10 +20510,10 @@
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>7065507.8</v>
+        <v>7070546.8</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="145">
@@ -20533,10 +20533,10 @@
         </is>
       </c>
       <c r="D145" s="6" t="n">
-        <v>94079568.27</v>
+        <v>94769412.2</v>
       </c>
       <c r="E145" s="12" t="n">
-        <v>14.73</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="146">
@@ -20556,10 +20556,10 @@
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>78115487.75</v>
+        <v>78649098.06999999</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>12.23</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="147">
@@ -20579,10 +20579,10 @@
         </is>
       </c>
       <c r="D147" s="6" t="n">
-        <v>37580754.74</v>
+        <v>37637528.64</v>
       </c>
       <c r="E147" s="12" t="n">
-        <v>5.89</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="148">
@@ -20602,7 +20602,7 @@
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>37197682.96</v>
+        <v>37575692.07</v>
       </c>
       <c r="E148" s="12" t="n">
         <v>5.83</v>
@@ -20625,10 +20625,10 @@
         </is>
       </c>
       <c r="D149" s="6" t="n">
-        <v>34080474.44</v>
+        <v>34295471.64</v>
       </c>
       <c r="E149" s="12" t="n">
-        <v>5.34</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="150">
@@ -20648,10 +20648,10 @@
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>33737809.03</v>
+        <v>33938280.45</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>5.28</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="151">
@@ -20671,10 +20671,10 @@
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>33275421.99</v>
+        <v>33399621.99</v>
       </c>
       <c r="E151" s="12" t="n">
-        <v>5.21</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="152">
@@ -20694,10 +20694,10 @@
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>26509719.61</v>
+        <v>26627067.37</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="153">
@@ -20717,10 +20717,10 @@
         </is>
       </c>
       <c r="D153" s="6" t="n">
-        <v>25429200.51</v>
+        <v>25504666.27</v>
       </c>
       <c r="E153" s="12" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="154">
@@ -20740,10 +20740,10 @@
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>23329975.8</v>
+        <v>23411111.83</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="155">
@@ -20763,10 +20763,10 @@
         </is>
       </c>
       <c r="D155" s="6" t="n">
-        <v>23094552.92</v>
+        <v>23192388.82</v>
       </c>
       <c r="E155" s="12" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="156">
@@ -20786,10 +20786,10 @@
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>21406675.16</v>
+        <v>21833097.32</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="157">
@@ -20809,10 +20809,10 @@
         </is>
       </c>
       <c r="D157" s="6" t="n">
-        <v>20028915.46</v>
+        <v>20441635.46</v>
       </c>
       <c r="E157" s="12" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="158">
@@ -20832,10 +20832,10 @@
         </is>
       </c>
       <c r="D158" s="6" t="n">
-        <v>19827774.67</v>
+        <v>20019175.17</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="159">
@@ -20855,10 +20855,10 @@
         </is>
       </c>
       <c r="D159" s="6" t="n">
-        <v>16329313.82</v>
+        <v>16864270.76</v>
       </c>
       <c r="E159" s="12" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="160">
@@ -20878,10 +20878,10 @@
         </is>
       </c>
       <c r="D160" s="6" t="n">
-        <v>15335402.37</v>
+        <v>15353382.37</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="161">
@@ -20892,19 +20892,19 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
-        <v>13567646.61</v>
+        <v>13965313.08</v>
       </c>
       <c r="E161" s="12" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="162">
@@ -20915,19 +20915,19 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Presidenciáveis, circunscrição nacional</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>12464112.86</v>
+        <v>13594264.7</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="163">
@@ -20947,10 +20947,10 @@
         </is>
       </c>
       <c r="D163" s="6" t="n">
-        <v>11984091.75</v>
+        <v>12042761.75</v>
       </c>
       <c r="E163" s="12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="164">
@@ -20970,7 +20970,7 @@
         </is>
       </c>
       <c r="D164" s="6" t="n">
-        <v>9685217.449999999</v>
+        <v>9796186.24</v>
       </c>
       <c r="E164" s="12" t="n">
         <v>1.52</v>
@@ -20993,7 +20993,7 @@
         </is>
       </c>
       <c r="D165" s="6" t="n">
-        <v>9593683.640000001</v>
+        <v>9666183.890000001</v>
       </c>
       <c r="E165" s="12" t="n">
         <v>1.5</v>
@@ -21016,10 +21016,10 @@
         </is>
       </c>
       <c r="D166" s="6" t="n">
-        <v>9210619.59</v>
+        <v>9377511.09</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="167">
@@ -21039,10 +21039,10 @@
         </is>
       </c>
       <c r="D167" s="6" t="n">
-        <v>7575082.06</v>
+        <v>7577122.46</v>
       </c>
       <c r="E167" s="12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="168">
@@ -21062,10 +21062,10 @@
         </is>
       </c>
       <c r="D168" s="6" t="n">
-        <v>6978299.39</v>
+        <v>7163793.36</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="169">
@@ -21085,7 +21085,7 @@
         </is>
       </c>
       <c r="D169" s="6" t="n">
-        <v>5387549.76</v>
+        <v>5427049.76</v>
       </c>
       <c r="E169" s="12" t="n">
         <v>0.84</v>
@@ -21108,7 +21108,7 @@
         </is>
       </c>
       <c r="D170" s="6" t="n">
-        <v>4881792.25</v>
+        <v>4883292.25</v>
       </c>
       <c r="E170" s="12" t="n">
         <v>0.76</v>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-07 09:05:33.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
         </is>
       </c>
     </row>
@@ -22572,28 +22572,28 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>374505981.95</v>
+        <v>376586968.39</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>36085324.87</v>
+        <v>36632976.11</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>20333031.37</v>
+        <v>20334031.37</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>6017898.32</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>42103223.19</v>
+        <v>42650874.43</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>18.53</v>
+        <v>18.44</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>394839013.32</v>
+        <v>396920999.76</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>15.87</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="6">
@@ -22603,28 +22603,28 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>518173255.96</v>
+        <v>520147030.9</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>32299122.71</v>
+        <v>32676158.66</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>7835443.22</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>8694338.77</v>
+        <v>8813874.460000001</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>40993461.48</v>
+        <v>41490033.12</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>18.04</v>
+        <v>17.94</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>526008699.18</v>
+        <v>527982474.12</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>21.15</v>
+        <v>21.06</v>
       </c>
     </row>
     <row r="7">
@@ -22634,10 +22634,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>256121735</v>
+        <v>257589351.81</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>26618884.81</v>
+        <v>27112684.81</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>328650</v>
@@ -22646,16 +22646,16 @@
         <v>162830.33</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>26781715.14</v>
+        <v>27275515.14</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>11.79</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>256450385</v>
+        <v>257918001.81</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>10.31</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="8">
@@ -22665,10 +22665,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>144277138.7</v>
+        <v>145123738.7</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3920163.95</v>
+        <v>3937863.95</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>10528907.87</v>
@@ -22677,16 +22677,16 @@
         <v>16191098.24</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>20111262.19</v>
+        <v>20128962.19</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>8.85</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>154806046.57</v>
+        <v>155652646.57</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.22</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="9">
@@ -22696,10 +22696,10 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>114829851.79</v>
+        <v>115338691.79</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>8446618.130000001</v>
+        <v>8554118.130000001</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>13371262.57</v>
@@ -22708,78 +22708,78 @@
         <v>9518476.6</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>17965094.73</v>
+        <v>18072594.73</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>7.91</v>
+        <v>7.82</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>128201114.36</v>
+        <v>128709954.36</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.15</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Despesas com pessoal</t>
+          <t>Atividades de militância e mobilização de rua</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>212655944.86</v>
+        <v>221272006.58</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>14901677.41</v>
+        <v>16293479.85</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1405640</v>
+        <v>1056169.06</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>529244.16</v>
+        <v>310317.66</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>15430921.57</v>
+        <v>16603797.51</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>6.79</v>
+        <v>7.18</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>214061584.86</v>
+        <v>222328175.64</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>8.609999999999999</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Atividades de militância e mobilização de rua</t>
+          <t>Despesas com pessoal</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>214876231.88</v>
+        <v>216012050.47</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>14698172.54</v>
+        <v>15131498.41</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1056169.06</v>
+        <v>1405640</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>310317.66</v>
+        <v>529244.16</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>15008490.2</v>
+        <v>15660742.57</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>6.61</v>
+        <v>6.77</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>215932400.94</v>
+        <v>217417690.47</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>8.68</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="12">
@@ -22789,28 +22789,28 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>156366534.17</v>
+        <v>157129630.57</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>6563649.46</v>
+        <v>6771887.82</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>2161173.45</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>2210763.68</v>
+        <v>2230704.43</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>8774413.140000001</v>
+        <v>9002592.25</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>158527707.6199999</v>
+        <v>159290804.02</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>6.37</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="13">
@@ -22820,10 +22820,10 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>64855005.98</v>
+        <v>65045147.91</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>3438755.24</v>
+        <v>3475751.24</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>12284674.22</v>
@@ -22832,16 +22832,16 @@
         <v>5327962.31</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>8766717.550000001</v>
+        <v>8803713.550000001</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3.86</v>
+        <v>3.81</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>77139680.19999999</v>
+        <v>77329822.13</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="14">
@@ -22851,10 +22851,10 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>80978563.34999999</v>
+        <v>81468297.16</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>3850120.68</v>
+        <v>3956290.68</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>53190</v>
@@ -22863,16 +22863,16 @@
         <v>990661.61</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>4840782.29</v>
+        <v>4946952.29</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>81031753.34999999</v>
+        <v>81521487.16</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="15">
@@ -22882,7 +22882,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>53347017.9</v>
+        <v>53518868.33</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>2323152.66</v>
@@ -22897,13 +22897,13 @@
         <v>4829859.060000001</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>54099470.5</v>
+        <v>54271320.93</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="16">
@@ -22913,7 +22913,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>26468256.83</v>
+        <v>26736109.96</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>2811660.79</v>
@@ -22928,10 +22928,10 @@
         <v>4410543.74</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>26904112.7</v>
+        <v>27171965.83</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>1.08</v>
@@ -22944,10 +22944,10 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>37542379.86</v>
+        <v>37661085.66</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>2717894.78</v>
+        <v>2733647.78</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>214985.86</v>
@@ -22956,16 +22956,16 @@
         <v>662907.63</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>3380802.41</v>
+        <v>3396555.41</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>37757365.72</v>
+        <v>37876071.52</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="18">
@@ -22975,10 +22975,10 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>13795831.4</v>
+        <v>13868331.4</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>476200</v>
+        <v>509200</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>965416.5</v>
@@ -22987,13 +22987,13 @@
         <v>2034321</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>2510521</v>
+        <v>2543521</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>14761247.9</v>
+        <v>14833747.9</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0.59</v>
@@ -23006,10 +23006,10 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>26415678.37</v>
+        <v>26566626.7</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>1630498.68</v>
+        <v>1677077.84</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>25327.5</v>
@@ -23018,13 +23018,13 @@
         <v>267576.1</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1898074.78</v>
+        <v>1944653.94</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>0.84</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>26441005.87</v>
+        <v>26591954.2</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>1.06</v>
@@ -23037,10 +23037,10 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>19936203.44</v>
+        <v>20170902.44</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>920028.09</v>
+        <v>947828.09</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>125000</v>
@@ -23049,13 +23049,13 @@
         <v>544826.95</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1464855.04</v>
+        <v>1492655.04</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>20061203.44</v>
+        <v>20295902.44</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0.8100000000000001</v>
@@ -23068,10 +23068,10 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>11378775.23</v>
+        <v>11544271.23</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>1162804.01</v>
+        <v>1169604.01</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>113916.98</v>
@@ -23080,13 +23080,13 @@
         <v>195694.49</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1358498.5</v>
+        <v>1365298.5</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>11492692.21</v>
+        <v>11658188.21</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0.46</v>
@@ -23099,7 +23099,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>10460266.93</v>
+        <v>10479380.03</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>1146621.39</v>
@@ -23114,10 +23114,10 @@
         <v>1267121.39</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>10666266.93</v>
+        <v>10685380.03</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0.43</v>
@@ -23130,7 +23130,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>13615514.41</v>
+        <v>13681281.41</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>938469.42</v>
@@ -23145,10 +23145,10 @@
         <v>956969.42</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>13671514.41</v>
+        <v>13737281.41</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0.55</v>
@@ -23161,10 +23161,10 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>13787731.98</v>
+        <v>14102355.98</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>762587.63</v>
+        <v>816887.63</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>933850</v>
@@ -23173,16 +23173,16 @@
         <v>110000</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>872587.63</v>
+        <v>926887.63</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>14721581.98</v>
+        <v>15036205.98</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="25">
@@ -23192,7 +23192,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5888876.4</v>
+        <v>5963501.9</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>673385.51</v>
@@ -23207,10 +23207,10 @@
         <v>673805.51</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>5888876.4</v>
+        <v>5963501.9</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0.24</v>
@@ -23223,10 +23223,10 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>6767795.71</v>
+        <v>6907363.25</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>542297.13</v>
+        <v>557631.13</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>22074.32</v>
@@ -23235,16 +23235,16 @@
         <v>90296.60000000001</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>632593.73</v>
+        <v>647927.73</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>0.28</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>6789870.03</v>
+        <v>6929437.57</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="27">
@@ -23254,7 +23254,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>14655539.06</v>
+        <v>14674454.1</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>556113.71</v>
@@ -23272,7 +23272,7 @@
         <v>0.24</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>14663643.61</v>
+        <v>14682558.65</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0.59</v>
@@ -23285,7 +23285,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>8878807.35</v>
+        <v>8983257.35</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>278862.09</v>
@@ -23303,7 +23303,7 @@
         <v>0.19</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>8878807.35</v>
+        <v>8983257.35</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0.36</v>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>2577695.04</v>
+        <v>2587085.93</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>253249.3</v>
@@ -23334,7 +23334,7 @@
         <v>0.15</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>2586821.84</v>
+        <v>2596212.73</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0.1</v>
@@ -23378,7 +23378,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>2347155.54</v>
+        <v>2357155.54</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>120030</v>
@@ -23396,7 +23396,7 @@
         <v>0.05</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>2347155.54</v>
+        <v>2357155.54</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0.09</v>
@@ -23409,7 +23409,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>887415.66</v>
+        <v>891415.66</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>81300.24000000001</v>
@@ -23427,7 +23427,7 @@
         <v>0.05</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>906032.16</v>
+        <v>910032.16</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0.04</v>
@@ -23440,7 +23440,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>1398462.05</v>
+        <v>1415038.3</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>55357.11</v>
@@ -23458,7 +23458,7 @@
         <v>0.04</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1398462.05</v>
+        <v>1415038.3</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0.06</v>
@@ -23502,13 +23502,13 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>80138.59</v>
+        <v>83637.59</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>1110.6</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>51744.89</v>
+        <v>51744.89000000001</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>40426.19</v>
@@ -23520,7 +23520,7 @@
         <v>0.02</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>131883.48</v>
+        <v>135382.48</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0.01</v>
@@ -23564,25 +23564,25 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>411411.3</v>
+        <v>414442.35</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>21806.32</v>
+        <v>22411.82</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>96674.00999999999</v>
+        <v>99104.31</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>11348.08</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>33154.4</v>
+        <v>33759.9</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>508085.31</v>
+        <v>513546.66</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0.02</v>
@@ -23626,7 +23626,7 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>31298.08</v>
+        <v>32149.94</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>3261.35</v>
@@ -23644,7 +23644,7 @@
         <v>0.01</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>31298.08</v>
+        <v>32149.94</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>23376.35</v>
+        <v>23908.85</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>249.98</v>
@@ -23706,7 +23706,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>23376.35</v>
+        <v>23908.85</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
@@ -23719,7 +23719,7 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>9847.049999999999</v>
+        <v>9864.049999999999</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>2.5</v>
@@ -23737,7 +23737,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>9847.049999999999</v>
+        <v>9864.049999999999</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-07 09:05:33.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
         </is>
       </c>
     </row>
@@ -23823,13 +23823,13 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="44" customWidth="1" min="14" max="14"/>
@@ -23937,34 +23937,34 @@
         <v>4898820044.67</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1145905997.82</v>
+        <v>1149518095.54</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>17.67</v>
+        <v>17.69</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>868725521.58</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>18.03</v>
+        <v>18.02</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>105707587.24</v>
+        <v>105708709.72</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>19.62</v>
+        <v>19.58</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>20620138.14</v>
+        <v>20992709.25</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>104046934.78</v>
+        <v>106372798.74</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>821362151.99</v>
+        <v>822766020.1799999</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>85.04000000000001</v>
+        <v>84.77</v>
       </c>
     </row>
     <row r="6">
@@ -23983,34 +23983,34 @@
         <v>771218822.24</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>690290514.83</v>
+        <v>691127168.02</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>10.64</v>
+        <v>10.63</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>571872107.1900001</v>
+        <v>572009546.96</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>11.87</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>4669622.71</v>
+        <v>4699622.71</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>0.87</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>11835188.27</v>
+        <v>11897417.44</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>73189724.19</v>
+        <v>73605129.86</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>483831468.61</v>
+        <v>486199579.28</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>83.52</v>
+        <v>83.44</v>
       </c>
     </row>
     <row r="7">
@@ -24029,7 +24029,7 @@
         <v>1817696708.82</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>640406127.24</v>
+        <v>641323471.98</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>9.869999999999999</v>
@@ -24041,22 +24041,22 @@
         <v>10.88</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>63582344.59</v>
+        <v>63670862.19</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>11.8</v>
+        <v>11.79</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>7330156.17</v>
+        <v>7544502.05</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>28197431.12</v>
+        <v>28646075.89</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>447120058.09</v>
+        <v>448157580.2</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>91.81</v>
+        <v>91.69</v>
       </c>
     </row>
     <row r="8">
@@ -24075,34 +24075,34 @@
         <v>2534145425.72</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>629133301.6799999</v>
+        <v>630875611.73</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>9.699999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>430151803.71</v>
+        <v>430461803.71</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>8.93</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>34396834.64</v>
+        <v>34932737.02</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>6.38</v>
+        <v>6.47</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>18019932.08</v>
+        <v>18417754.28</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>81982875.28</v>
+        <v>82465460.2</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>486784026.59</v>
+        <v>487004024.69</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>73.84</v>
+        <v>73.77</v>
       </c>
     </row>
     <row r="9">
@@ -24121,7 +24121,7 @@
         <v>2484193186.63</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>570976774.03</v>
+        <v>571930991.74</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>8.800000000000001</v>
@@ -24130,25 +24130,25 @@
         <v>350106242.76</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>7.27</v>
+        <v>7.26</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>116857540.5</v>
+        <v>116943247.32</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>21.69</v>
+        <v>21.66</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>10936428.19</v>
+        <v>10966433.69</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>60999437.9</v>
+        <v>61743245.04</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>393690835.06</v>
+        <v>394669906.42</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>81.78</v>
+        <v>81.66</v>
       </c>
     </row>
     <row r="10">
@@ -24167,34 +24167,34 @@
         <v>1294367106.67</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>523661877.06</v>
+        <v>524598363.5</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>8.07</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>418125289.17</v>
+        <v>418495289.17</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>8.68</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>53017527.01</v>
+        <v>53087527.01</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>7238906.9</v>
+        <v>7522399.47</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>28966188.71</v>
+        <v>29118742.14</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>329744914.61</v>
+        <v>332500834.58</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>89.97</v>
+        <v>89.89</v>
       </c>
     </row>
     <row r="11">
@@ -24213,34 +24213,34 @@
         <v>3339602389.67</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>518808609.99</v>
+        <v>519879285.55</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>8</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>395767248.96</v>
+        <v>395797248.96</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>8.210000000000001</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>17130434.05</v>
+        <v>17142487.45</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>14175461.22</v>
+        <v>14427090.12</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>63871602.32</v>
+        <v>64239383.58</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>333319965.51</v>
+        <v>335396569.12</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>79.59</v>
+        <v>79.43000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -24259,34 +24259,34 @@
         <v>1812875005.9</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>293530087.89</v>
+        <v>294099080.52</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>4.53</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>237676981.54</v>
+        <v>237797448.66</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>4.93</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5594103.26</v>
+        <v>5620256.810000001</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>1.04</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>9634113.779999999</v>
+        <v>9827977.789999999</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>30680838.67</v>
+        <v>30867425.62</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>190744593.09</v>
+        <v>191567318.38</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>82.88</v>
+        <v>82.77</v>
       </c>
     </row>
     <row r="13">
@@ -24305,7 +24305,7 @@
         <v>1457794419.27</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>229240515.33</v>
+        <v>229368308.22</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>3.53</v>
@@ -24314,25 +24314,25 @@
         <v>166995631.66</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>46132970.28</v>
+        <v>46135543.58</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>8.56</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>2845470.27</v>
+        <v>2873309.66</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>9527755.5</v>
+        <v>9574955.5</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>146062528.4</v>
+        <v>146356782.65</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>92.97</v>
+        <v>92.92</v>
       </c>
     </row>
     <row r="14">
@@ -24351,13 +24351,13 @@
         <v>931393345.11</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>219751251.15</v>
+        <v>220080910.29</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>3.39</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>148432792.38</v>
+        <v>148444360.38</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>3.08</v>
@@ -24369,16 +24369,16 @@
         <v>1.24</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>10548022.61</v>
+        <v>10646376.76</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>34228638.4</v>
+        <v>34434380.89</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>167930860</v>
+        <v>169544610.29</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>70.59999999999999</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="15">
@@ -24397,16 +24397,16 @@
         <v>2591694177.84</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>207736471.94</v>
+        <v>208621707.96</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>149693040.41</v>
+        <v>150243044.11</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>4462718.01</v>
@@ -24415,16 +24415,16 @@
         <v>0.83</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>11297507.8</v>
+        <v>11443964.99</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>30313649.54</v>
+        <v>30487243.12</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>141723187.85</v>
+        <v>142544619.45</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>74.20999999999999</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="16">
@@ -24440,10 +24440,10 @@
         <v>6.24</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1884009041.62</v>
+        <v>1884208841.62</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>143357371.64</v>
+        <v>143413052.69</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>2.21</v>
@@ -24458,19 +24458,19 @@
         <v>44447677.11</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>8.25</v>
+        <v>8.23</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>7226892.17</v>
+        <v>7229526.15</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>26636844.35</v>
+        <v>26683281.42</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>88005785.33</v>
+        <v>88022921.40000001</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>54.98</v>
+        <v>54.96</v>
       </c>
     </row>
     <row r="17">
@@ -24489,13 +24489,13 @@
         <v>139488473.87</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>135170518.21</v>
+        <v>135256177.68</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>2.08</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>123920796.05</v>
+        <v>123923665.62</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>2.57</v>
@@ -24507,16 +24507,16 @@
         <v>0.36</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>791809.51</v>
+        <v>792957.91</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>4037644.13</v>
+        <v>4109715.63</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>89228517.59999999</v>
+        <v>89457013.03</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>93.13</v>
+        <v>93.06999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -24535,34 +24535,34 @@
         <v>1072776812.99</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>97358291.54000001</v>
+        <v>97828964.2</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>65231386.54</v>
+        <v>65246386.54</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>1.35</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>12801331.38</v>
+        <v>13101331.38</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>4550634.24</v>
+        <v>4669665.97</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>12385182.28</v>
+        <v>12420032.78</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>58495186.45</v>
+        <v>59392648.37</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>80.15000000000001</v>
+        <v>80.09</v>
       </c>
     </row>
     <row r="19">
@@ -24581,7 +24581,7 @@
         <v>577531754.64</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>96798129.71000001</v>
+        <v>97145407.43000001</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>1.49</v>
@@ -24596,19 +24596,19 @@
         <v>14150615.09</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>3262467.12</v>
+        <v>3296872.12</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>8741972.949999999</v>
+        <v>9052071.720000001</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>60015600.98</v>
+        <v>60073666.48</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>84.43000000000001</v>
+        <v>84.13</v>
       </c>
     </row>
     <row r="20">
@@ -24627,13 +24627,13 @@
         <v>280452197.14</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>91654048.28</v>
+        <v>91843047.55</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>1.41</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>83698847.27</v>
+        <v>83798847.27</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>1.74</v>
@@ -24645,16 +24645,16 @@
         <v>0.3</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>1781726.69</v>
+        <v>1812125.96</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>3736690.4</v>
+        <v>3741690.4</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>52223680.23</v>
+        <v>52241095.04</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>93.09</v>
+        <v>93.01000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -24673,7 +24673,7 @@
         <v>81485614.53</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>73202182.78</v>
+        <v>73226002.78</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>1.13</v>
@@ -24694,13 +24694,13 @@
         <v>1268839.67</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>3904377.41</v>
+        <v>3927597.41</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>49352542.44</v>
+        <v>49353565.38</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>88.59</v>
+        <v>88.56</v>
       </c>
     </row>
     <row r="22">
@@ -24719,7 +24719,7 @@
         <v>328303892.2</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>59961861.91</v>
+        <v>60063742.37</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>0.92</v>
@@ -24737,16 +24737,16 @@
         <v>0.04</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>3368486.86</v>
+        <v>3368487.36</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>10879997.04</v>
+        <v>10981877</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>43253303.52</v>
+        <v>43318570.24</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>72.22</v>
+        <v>72.09</v>
       </c>
     </row>
     <row r="23">
@@ -24765,13 +24765,13 @@
         <v>121249861.96</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>35759055.36</v>
+        <v>35868431.86</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>0.55</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>32727008.31</v>
+        <v>32836384.31</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>0.68</v>
@@ -24783,16 +24783,16 @@
         <v>0.09</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>562324.8300000001</v>
+        <v>562325.3300000001</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>1037869.75</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>11082604.22</v>
+        <v>11082604.72</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>92.89</v>
+        <v>92.91</v>
       </c>
     </row>
     <row r="24">
@@ -24811,13 +24811,13 @@
         <v>587079065.02</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>33605149.94</v>
+        <v>33622820.94</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>0.52</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>29347914.3</v>
+        <v>29357914.3</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0.61</v>
@@ -24829,16 +24829,16 @@
         <v>0.08</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>450718.86</v>
+        <v>450719.86</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>2557459.84</v>
+        <v>2564759.84</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>19605023.51</v>
+        <v>19622885.87</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>88.56</v>
+        <v>88.54000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -24857,13 +24857,13 @@
         <v>286783798.5</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>11693994.66</v>
+        <v>11748494.66</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>0.18</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>2224662.44</v>
+        <v>2234662.44</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>0.05</v>
@@ -24875,16 +24875,16 @@
         <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>1983289.67</v>
+        <v>1999789.67</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>7147920.65</v>
+        <v>7175920.65</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>7371697.15</v>
+        <v>7475977.35</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>19.03</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="26">
@@ -24903,7 +24903,7 @@
         <v>243522021.57</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>10046253.64</v>
+        <v>10050258.14</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>0.15</v>
@@ -24921,16 +24921,16 @@
         <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>1831602.13</v>
+        <v>1832246.63</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>5454505.95</v>
+        <v>5455606.95</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>8103281.57</v>
+        <v>8130625.21</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>23.07</v>
+        <v>23.06</v>
       </c>
     </row>
     <row r="27">
@@ -24995,10 +24995,10 @@
         <v>652170016.89</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>6047224.88</v>
+        <v>6200194.04</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>2903963.13</v>
@@ -25013,16 +25013,16 @@
         <v>0.01</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>997745.89</v>
+        <v>1031444.47</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>1791806.22</v>
+        <v>1911076.8</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>3410411.79</v>
+        <v>3426265.68</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>48.56</v>
+        <v>47.36</v>
       </c>
     </row>
     <row r="29">
@@ -25041,7 +25041,7 @@
         <v>463597846.48</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>5147838.42</v>
+        <v>5190778.42</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>0.08</v>
@@ -25059,13 +25059,13 @@
         <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>2176077.14</v>
+        <v>2204427.14</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>2037633.58</v>
+        <v>2051483.58</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>3314018.3</v>
+        <v>3331690.38</v>
       </c>
       <c r="N29" s="6" t="n">
         <v>0.12</v>
@@ -25087,7 +25087,7 @@
         <v>26021399.15</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>3555651.12</v>
+        <v>3556151.12</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>0.05</v>
@@ -25108,13 +25108,13 @@
         <v>24107.29</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>125925.33</v>
+        <v>126425.33</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>3032759.84</v>
+        <v>3033459.84</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>89.75</v>
+        <v>89.73</v>
       </c>
     </row>
     <row r="31">
@@ -25133,7 +25133,7 @@
         <v>16313701.99</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>1891965.49</v>
+        <v>1898231.09</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>0.03</v>
@@ -25154,13 +25154,13 @@
         <v>8271.67</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>242823.55</v>
+        <v>248034.15</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>1094964.11</v>
+        <v>1095012.48</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>67.78</v>
+        <v>67.56</v>
       </c>
     </row>
     <row r="32">
@@ -25225,7 +25225,7 @@
         <v>4118169.08</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>82107.08</v>
+        <v>85797.08</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>0</v>
@@ -25249,7 +25249,7 @@
         <v>26960</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>76335.03</v>
+        <v>76920.81</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>0</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-07 09:05:33.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
         </is>
       </c>
     </row>
@@ -25861,7 +25861,7 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>1317214.5</v>
+        <v>1319171.57</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>0.02</v>
@@ -25873,7 +25873,7 @@
         <v>0.44</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1311414.5</v>
+        <v>1313371.57</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>0</v>
@@ -26667,62 +26667,62 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>RAUL BELEM</t>
+          <t>VETERINÁRIO WILSON GRASSI</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO ESTADUAL</t>
+          <t>PRESIDENTE</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>DEMOCRATA</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1077696.73</v>
+        <v>1078710</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>120000</v>
+        <v>1077350</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>11.13</v>
+        <v>99.87</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>895000</v>
+        <v>1350</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>62696.73</v>
+        <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>12696.73</v>
+        <v>1200</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>916632.36</v>
+        <v>1075899.66</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>665951.84</v>
+        <v>1075899.66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>CARLOS AVALLONE</t>
+          <t>RAUL BELEM</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -26732,52 +26732,52 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>1075392.88</v>
+        <v>1077696.73</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>115000</v>
+        <v>120000</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>10.69</v>
+        <v>11.13</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>860392.88</v>
+        <v>895000</v>
       </c>
       <c r="J28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>100000</v>
+        <v>62696.73</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>68392.88</v>
+        <v>12696.73</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>321606.61</v>
+        <v>916632.36</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>37099.32</v>
+        <v>665951.84</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>FABINHO TARDIN</t>
+          <t>CARLOS AVALLONE</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -26792,47 +26792,47 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>1071142.26</v>
+        <v>1075392.88</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>120000</v>
+        <v>115000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>11.2</v>
+        <v>10.69</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>951142.26</v>
+        <v>860392.88</v>
       </c>
       <c r="J29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>43142.26</v>
+        <v>68392.88</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1019703.23</v>
+        <v>321606.61</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>938502.16</v>
+        <v>37099.32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>FABINHO TARDIN</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -26842,16 +26842,16 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>1057896</v>
+        <v>1071142.26</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>0.02</v>
@@ -26860,83 +26860,83 @@
         <v>120000</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>11.34</v>
+        <v>11.2</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>777896</v>
+        <v>951142.26</v>
       </c>
       <c r="J30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>26000</v>
+        <v>43142.26</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>218599.63</v>
+        <v>1019703.23</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>132682.4</v>
+        <v>938502.16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>VETERINÁRIO WILSON GRASSI</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>PRESIDENTE</t>
+          <t>DEPUTADO ESTADUAL</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>DEMOCRATA</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>1050150</v>
+        <v>1057896</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>1050000</v>
+        <v>120000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>99.98999999999999</v>
+        <v>11.34</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>150</v>
+        <v>777896</v>
       </c>
       <c r="J31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>1075399.66</v>
+        <v>218599.63</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1048399.66</v>
+        <v>132682.4</v>
       </c>
     </row>
     <row r="32">
@@ -27428,10 +27428,10 @@
         <v>31240</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>851941.8099999999</v>
+        <v>851941.8100000001</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>851941.8099999999</v>
+        <v>851941.8100000001</v>
       </c>
     </row>
     <row r="41">
@@ -27547,7 +27547,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>HUSSEIN BAKRI</t>
+          <t>ROBERTO ANDRADE</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -27557,52 +27557,52 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PRD</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>901941</v>
+        <v>925831.29</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>76000</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>8.43</v>
+        <v>0</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>530900</v>
+        <v>886530.37</v>
       </c>
       <c r="J43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>288025</v>
+        <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>7016</v>
+        <v>39300.92</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>28216</v>
+        <v>56700.92</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1016661.6</v>
+        <v>549049.09</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>836974.85</v>
+        <v>331063.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>DRA LAÍS SANTIAGO</t>
+          <t>HUSSEIN BAKRI</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -27612,83 +27612,83 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>894497.5</v>
+        <v>901941</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>21697.5</v>
+        <v>76000</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>2.43</v>
+        <v>8.43</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>872800</v>
+        <v>530900</v>
       </c>
       <c r="J44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0</v>
+        <v>288025</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0</v>
+        <v>7016</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>42800</v>
+        <v>28216</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>514552</v>
+        <v>1016661.6</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>467552</v>
+        <v>836974.85</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>DR.HILTON GONÇALO</t>
+          <t>DRA LAÍS SANTIAGO</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>SENADOR</t>
+          <t>DEPUTADO ESTADUAL</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>MOBILIZA</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>892749</v>
+        <v>894497.5</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>4500</v>
+        <v>21697.5</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0.5</v>
+        <v>2.43</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>885794</v>
+        <v>872800</v>
       </c>
       <c r="J45" s="6" t="n">
         <v>0</v>
@@ -27697,53 +27697,53 @@
         <v>0</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>2455</v>
+        <v>0</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>12455</v>
+        <v>42800</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>635732.25</v>
+        <v>514552</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>516282.25</v>
+        <v>467552</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>ROBERTO ANDRADE</t>
+          <t>DR.HILTON GONÇALO</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO ESTADUAL</t>
+          <t>SENADOR</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>PRD</t>
+          <t>MOBILIZA</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>892497.9600000001</v>
+        <v>892749</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>853197.04</v>
+        <v>885794</v>
       </c>
       <c r="J46" s="6" t="n">
         <v>0</v>
@@ -27752,16 +27752,16 @@
         <v>0</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>39300.92</v>
+        <v>2455</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>56700.92</v>
+        <v>12455</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>549049.09</v>
+        <v>635732.25</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>331063.4</v>
+        <v>516282.25</v>
       </c>
     </row>
     <row r="47">
@@ -27981,7 +27981,7 @@
         <v>831239.7</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>831239.7</v>
+        <v>831239.7000000001</v>
       </c>
     </row>
     <row r="51">
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-07 09:05:33.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
         </is>
       </c>
     </row>
@@ -28221,14 +28221,14 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: sao 2180 candidaturas com receita declarada e sem um real dos dois fundos publicos. que somam R$ 218.414.624,53 de receita.</t>
+          <t>Nota 1: sao 2189 candidaturas com receita declarada e sem um real dos dois fundos publicos. que somam R$ 219.479.618,92 de receita.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Nota 2: outras 4201 candidaturas NAO declararam receita alguma, das quais 924 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
+          <t>Nota 2: outras 4183 candidaturas NAO declararam receita alguma, das quais 924 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
         </is>
       </c>
     </row>
@@ -28383,13 +28383,13 @@
         <v>7.71</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>934299547.1</v>
+        <v>935524547.88</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>20.23</v>
+        <v>20.26</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>27.39</v>
+        <v>27.43</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>22.55</v>
@@ -28426,16 +28426,16 @@
         <v>11.18</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>534282294.27</v>
+        <v>536492301.75</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>32.62</v>
+        <v>32.75</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>24.78</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="7">
@@ -28469,16 +28469,16 @@
         <v>15.98</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>499396080.69</v>
+        <v>500176968.65</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>28.99</v>
+        <v>29.04</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>38.84</v>
+        <v>38.9</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>34.2</v>
+        <v>34.22</v>
       </c>
     </row>
     <row r="8">
@@ -28512,16 +28512,16 @@
         <v>10.81</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>345443239.42</v>
+        <v>345824803.85</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>23.2</v>
+        <v>23.23</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>30.51</v>
+        <v>30.54</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>26.87</v>
+        <v>26.89</v>
       </c>
     </row>
     <row r="9">
@@ -28555,16 +28555,16 @@
         <v>12.66</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>344151335.45</v>
+        <v>345027195.36</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>28.79</v>
+        <v>28.87</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>39.97</v>
+        <v>40.07</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>31.67</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="10">
@@ -28598,16 +28598,16 @@
         <v>12.36</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>318096004.64</v>
+        <v>318528670.12</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>28.32</v>
+        <v>28.36</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>37.31</v>
+        <v>37.36</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>31.22</v>
+        <v>31.23</v>
       </c>
     </row>
     <row r="11">
@@ -28641,13 +28641,13 @@
         <v>13.3</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>259725823.68</v>
+        <v>259982154.41</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>27.1</v>
+        <v>27.13</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>35.94</v>
+        <v>35.97</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>30.52</v>
@@ -28684,13 +28684,13 @@
         <v>10.2</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>244308904.76</v>
+        <v>244547395.26</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>26.26</v>
+        <v>26.29</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>34.9</v>
+        <v>34.93</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>28.56</v>
@@ -28727,13 +28727,13 @@
         <v>11.82</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>190353983.9</v>
+        <v>191061311.88</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>21.74</v>
+        <v>21.82</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>30.37</v>
+        <v>30.49</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>25.82</v>
@@ -28770,16 +28770,16 @@
         <v>12.22</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>213477278.38</v>
+        <v>214384400.5</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>25.68</v>
+        <v>25.79</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>37.28</v>
+        <v>37.44</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>28.56</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="15">
@@ -28813,13 +28813,13 @@
         <v>11.93</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>221972949.17</v>
+        <v>222531299.84</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>31.6</v>
+        <v>31.68</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>42.78</v>
+        <v>42.89</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>36.48</v>
@@ -28856,16 +28856,16 @@
         <v>17.83</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>230628971.85</v>
+        <v>231028562.48</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>30.77</v>
+        <v>30.82</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>45.39</v>
+        <v>45.47</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>34.37</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="17">
@@ -28899,10 +28899,10 @@
         <v>13.85</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>149263234.88</v>
+        <v>149268375.28</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>35.68</v>
+        <v>35.69</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>45.96</v>
@@ -28942,13 +28942,13 @@
         <v>19.76</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>141088030.19</v>
+        <v>141159582.32</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>33.99</v>
+        <v>34.01</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>47.18</v>
+        <v>47.2</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>37.99</v>
@@ -28985,16 +28985,16 @@
         <v>16.95</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>154156738.59</v>
+        <v>154325409.09</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>35.35</v>
+        <v>35.39</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>55.01</v>
+        <v>55.08</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>46.85</v>
+        <v>46.86</v>
       </c>
     </row>
     <row r="20">
@@ -29028,13 +29028,13 @@
         <v>14.84</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>144954748.36</v>
+        <v>145049721.48</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>42.73</v>
+        <v>42.75</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>53.51</v>
+        <v>53.55</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>44.08</v>
@@ -29071,13 +29071,13 @@
         <v>12.4</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>103820519.67</v>
+        <v>103865363.67</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>29.97</v>
+        <v>29.99</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>39.02</v>
+        <v>39.03</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>35.34</v>
@@ -29114,13 +29114,13 @@
         <v>17.24</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>160935288</v>
+        <v>161162563.31</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>40.74</v>
+        <v>40.8</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>60.98</v>
+        <v>61.07</v>
       </c>
       <c r="M22" s="6" t="n">
         <v>36.34</v>
@@ -29157,13 +29157,13 @@
         <v>12.24</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>115661926.51</v>
+        <v>115848420.48</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>35.91</v>
+        <v>35.97</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>47.36</v>
+        <v>47.43</v>
       </c>
       <c r="M23" s="6" t="n">
         <v>42.42</v>
@@ -29200,16 +29200,16 @@
         <v>29.65</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>164269169.71</v>
+        <v>164729989.99</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>54.57</v>
+        <v>54.73</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>72.90000000000001</v>
+        <v>73.11</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>55.71</v>
+        <v>55.86</v>
       </c>
     </row>
     <row r="25">
@@ -29243,13 +29243,13 @@
         <v>20.99</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>117550093.37</v>
+        <v>117865243.1</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>58.05</v>
+        <v>58.21</v>
       </c>
       <c r="M25" s="6" t="n">
         <v>47.35</v>
@@ -29286,13 +29286,13 @@
         <v>23.62</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>121877051.62</v>
+        <v>122153368.29</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>52.82</v>
+        <v>52.94</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>70.03</v>
+        <v>70.19</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>63.31</v>
@@ -29329,16 +29329,16 @@
         <v>34.52</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>145290064.16</v>
+        <v>146052855.8</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>82.68000000000001</v>
+        <v>83.11</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>114.52</v>
+        <v>115.12</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>89.68000000000001</v>
+        <v>89.84999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -29372,13 +29372,13 @@
         <v>31.11</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>118530986.22</v>
+        <v>118642264.33</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>74.27</v>
+        <v>74.34</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>100.21</v>
+        <v>100.31</v>
       </c>
       <c r="M28" s="6" t="n">
         <v>82.29000000000001</v>
@@ -29415,16 +29415,16 @@
         <v>63.13</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>105187690.11</v>
+        <v>105206552.11</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>118.48</v>
+        <v>118.5</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>171.14</v>
+        <v>171.17</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>155.02</v>
+        <v>155.04</v>
       </c>
     </row>
     <row r="30">
@@ -29458,7 +29458,7 @@
         <v>55.74</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>115913132.66</v>
+        <v>115916347.26</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>143.11</v>
@@ -29501,13 +29501,13 @@
         <v>102.85</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>105685049.13</v>
+        <v>105716419.13</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>138.87</v>
+        <v>138.92</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>263.18</v>
+        <v>263.26</v>
       </c>
       <c r="M31" s="6" t="n">
         <v>245.99</v>
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>185428004.32</v>
+        <v>187323426.67</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -29605,16 +29605,16 @@
         <v>13.3</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>6485748140.809999</v>
+        <v>6499395514.29</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>30.28</v>
+        <v>30.34</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>41.09</v>
+        <v>41.18</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>33.94</v>
+        <v>33.96</v>
       </c>
     </row>
     <row r="34">

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,14 +909,14 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-07.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-08.</t>
         </is>
       </c>
     </row>
@@ -1025,14 +1025,14 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-07.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-08.</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>171354</v>
+        <v>172432</v>
       </c>
     </row>
     <row r="24">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6485748140.81</v>
+        <v>6499395514.29</v>
       </c>
     </row>
     <row r="26">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{"REC_FEFC": 4818741267.43, "REC_FINANCIAMENTO_COLETIVO": 17574106.81, "REC_FUNDO_PARTIDARIO": 538846836.48, "REC_ORIGEM_NAO_IDENTIFICADA": 1119823.18, "REC_OUTROS_CANDIDATOS": 118629219.19, "REC_PARTIDO_OUTROS_RECURSOS": 197024752.4, "REC_PESSOAS_FISICAS": 638514963.77, "REC_PROPRIOS": 155297171.55, "REC_SEM_ORIGEM": 0.0}</t>
+          <t>{"REC_FEFC": 4820517991.59, "REC_FINANCIAMENTO_COLETIVO": 17893226.27, "REC_FUNDO_PARTIDARIO": 539998866.01, "REC_ORIGEM_NAO_IDENTIFICADA": 1111351.96, "REC_OUTROS_CANDIDATOS": 119614174.89, "REC_PARTIDO_OUTROS_RECURSOS": 197783790.57, "REC_PESSOAS_FISICAS": 644833517.92, "REC_PROPRIOS": 157642595.08, "REC_SEM_ORIGEM": 0.0}</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>76673</v>
+        <v>77181</v>
       </c>
     </row>
     <row r="30">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>972276</v>
+        <v>978191</v>
       </c>
     </row>
     <row r="36">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>773200</v>
+        <v>777849</v>
       </c>
     </row>
     <row r="37">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4446361078.23</v>
+        <v>4462223543.88</v>
       </c>
     </row>
     <row r="38">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>668061</v>
+        <v>683428</v>
       </c>
     </row>
     <row r="39">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3051673419.1</v>
+        <v>3088142099.12</v>
       </c>
     </row>
     <row r="40">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>70429</v>
+        <v>71176</v>
       </c>
     </row>
     <row r="43">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>703318.24</v>
+        <v>711894.52</v>
       </c>
     </row>
     <row r="44">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>536391</v>
+        <v>538865</v>
       </c>
     </row>
     <row r="46">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>55116</v>
+        <v>55393</v>
       </c>
     </row>
     <row r="48">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>54975</v>
+        <v>55248</v>
       </c>
     </row>
     <row r="49">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>973</v>
+        <v>957</v>
       </c>
     </row>
     <row r="52">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2476493769.98</v>
+        <v>2497165173.04</v>
       </c>
     </row>
     <row r="53">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>62467265.72</v>
+        <v>63098984.72</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>171112707.12</v>
+        <v>175037098.64</v>
       </c>
     </row>
     <row r="55">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2454620.52</v>
+        <v>2458620.52</v>
       </c>
     </row>
     <row r="56">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4866017907.18</v>
+        <v>4867433267.48</v>
       </c>
     </row>
     <row r="57">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4792590050.36</v>
+        <v>4794001980.36</v>
       </c>
     </row>
     <row r="58">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>560363771.8200001</v>
+        <v>560638228.26</v>
       </c>
     </row>
     <row r="59">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>501831902.14</v>
+        <v>501966882.14</v>
       </c>
     </row>
     <row r="60">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-08 06:53:14</t>
+          <t>2026-10-08 09:03:34</t>
         </is>
       </c>
     </row>
@@ -8842,14 +8842,14 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-07.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-08.</t>
         </is>
       </c>
     </row>
@@ -15495,14 +15495,14 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-07.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-08.</t>
         </is>
       </c>
     </row>
@@ -17206,14 +17206,14 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-07.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-08.</t>
         </is>
       </c>
     </row>
@@ -22451,14 +22451,14 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-07.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-08.</t>
         </is>
       </c>
     </row>
@@ -23777,14 +23777,14 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-07.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-08.</t>
         </is>
       </c>
     </row>
@@ -25304,14 +25304,14 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-07.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-08.</t>
         </is>
       </c>
     </row>
@@ -28207,14 +28207,14 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 06:53:14.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-07.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-08.</t>
         </is>
       </c>
     </row>
@@ -29627,7 +29627,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-07.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-08.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -578,10 +578,10 @@
         <v>1.66</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4461861531.07</v>
+        <v>4464124482.29</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>13.92</v>
+        <v>13.93</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>0</v>
@@ -674,7 +674,7 @@
         <v>12007434756.34</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>37.47</v>
+        <v>37.46</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>1772759804.56</v>
@@ -888,7 +888,7 @@
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32049392250.5</v>
+        <v>32051655201.72</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 15:03:33.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 15:03:33.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>77297</v>
+        <v>77316</v>
       </c>
     </row>
     <row r="31">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32049392250.5</v>
+        <v>32051655201.72</v>
       </c>
     </row>
     <row r="34">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-08 09:03:34</t>
+          <t>2026-10-08 15:03:33</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="G46" s="6" t="n">
-        <v>75659161.21000001</v>
+        <v>75659161.20999999</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>0.24</v>
@@ -8446,7 +8446,7 @@
         <v>40063200</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I99" s="5" t="n">
         <v>22</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 15:03:33.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 15:03:33.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 15:03:33.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 15:03:33.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 15:03:33.</t>
         </is>
       </c>
     </row>
@@ -24072,7 +24072,7 @@
         <v>5.4</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2534145425.72</v>
+        <v>2536408376.94</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>630875611.73</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 15:03:33.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 09:03:34.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-08 15:03:33.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 13:33:26.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 13:33:26.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>55396</v>
+        <v>55637</v>
       </c>
     </row>
     <row r="48">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>282</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>6737183</v>
+        <v>6706621</v>
       </c>
     </row>
     <row r="61">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-09 13:33:26</t>
+          <t>2026-10-09 18:50:07</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>575680870.95</v>
+        <v>575680870.9499999</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1.79</v>
@@ -5816,7 +5816,7 @@
         </is>
       </c>
       <c r="G62" s="6" t="n">
-        <v>58445503.79000001</v>
+        <v>58445503.79</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>0.18</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 13:33:26.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 13:33:26.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 13:33:26.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
         </is>
       </c>
     </row>
@@ -19245,7 +19245,7 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>803006087.61</v>
+        <v>803275588.21</v>
       </c>
       <c r="E89" s="12" t="n">
         <v>25.84</v>
@@ -19268,7 +19268,7 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>201274903.61</v>
+        <v>201313907.16</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>6.48</v>
@@ -19291,7 +19291,7 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>185694104.16</v>
+        <v>185868293.63</v>
       </c>
       <c r="E91" s="12" t="n">
         <v>5.98</v>
@@ -19314,7 +19314,7 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>156000157.57</v>
+        <v>156006823.63</v>
       </c>
       <c r="E92" s="12" t="n">
         <v>5.02</v>
@@ -19337,7 +19337,7 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>139922914.49</v>
+        <v>139965790.09</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>4.5</v>
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>124693773.27</v>
+        <v>124777509.58</v>
       </c>
       <c r="E94" s="12" t="n">
         <v>4.01</v>
@@ -19383,7 +19383,7 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>122765809.64</v>
+        <v>122776549.64</v>
       </c>
       <c r="E95" s="12" t="n">
         <v>3.95</v>
@@ -19406,7 +19406,7 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>118110886.99</v>
+        <v>118244586.69</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>3.8</v>
@@ -19429,7 +19429,7 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>107392100.21</v>
+        <v>107587049.99</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>3.46</v>
@@ -19452,7 +19452,7 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>106467061.09</v>
+        <v>106774005.47</v>
       </c>
       <c r="E98" s="12" t="n">
         <v>3.43</v>
@@ -19475,7 +19475,7 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>93776156.98999999</v>
+        <v>93790000.17</v>
       </c>
       <c r="E99" s="12" t="n">
         <v>3.02</v>
@@ -19498,7 +19498,7 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>93667391.73</v>
+        <v>93696280.23</v>
       </c>
       <c r="E100" s="12" t="n">
         <v>3.01</v>
@@ -19521,7 +19521,7 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>85800132.06</v>
+        <v>85821334.78</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>2.76</v>
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>84864555.48999999</v>
+        <v>84954922.27</v>
       </c>
       <c r="E102" s="12" t="n">
         <v>2.73</v>
@@ -19567,7 +19567,7 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>74041631.22</v>
+        <v>74061922.67</v>
       </c>
       <c r="E103" s="12" t="n">
         <v>2.38</v>
@@ -19590,7 +19590,7 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>73221516.77</v>
+        <v>73223846.77</v>
       </c>
       <c r="E104" s="12" t="n">
         <v>2.36</v>
@@ -19636,7 +19636,7 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>59710995.88</v>
+        <v>59767995.88</v>
       </c>
       <c r="E106" s="12" t="n">
         <v>1.92</v>
@@ -19659,7 +19659,7 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>56858624.46</v>
+        <v>56904220.24</v>
       </c>
       <c r="E107" s="12" t="n">
         <v>1.83</v>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>53771897.11</v>
+        <v>53815730.83</v>
       </c>
       <c r="E108" s="12" t="n">
         <v>1.73</v>
@@ -19705,7 +19705,7 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>51930816.04</v>
+        <v>52017316.04</v>
       </c>
       <c r="E109" s="12" t="n">
         <v>1.67</v>
@@ -19731,7 +19731,7 @@
         <v>51437272.95</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="111">
@@ -19751,7 +19751,7 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>48042549.9</v>
+        <v>48046110.9</v>
       </c>
       <c r="E111" s="12" t="n">
         <v>1.55</v>
@@ -19820,7 +19820,7 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>30805520.48</v>
+        <v>30823545.36</v>
       </c>
       <c r="E114" s="12" t="n">
         <v>0.99</v>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 13:33:26.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 13:33:26.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 13:33:26.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 13:33:26.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -581,7 +581,7 @@
         <v>4495080252.41</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>14.01</v>
+        <v>13.89</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>0</v>
@@ -606,13 +606,13 @@
         <v>350</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>923439500.0599999</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>0</v>
@@ -649,13 +649,13 @@
         <v>47583315.55</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>31357670.85</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="8">
@@ -668,25 +668,25 @@
         <v>11295</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>53.81</v>
+        <v>53.72</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>12007434756.34</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>37.42</v>
+        <v>37.1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>1777374091.67</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>27.28</v>
+        <v>25.19</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>1168200609.16</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>26.06</v>
+        <v>23.72</v>
       </c>
     </row>
     <row r="9">
@@ -699,25 +699,25 @@
         <v>7803</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>37.18</v>
+        <v>37.11</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>8707767692.280001</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>27.14</v>
+        <v>26.9</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>3393590543.44</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>52.09</v>
+        <v>48.1</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>2260223604.13</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>50.41</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="10">
@@ -727,28 +727,28 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.96</v>
+        <v>1.01</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1286968966.8</v>
+        <v>1375157757.93</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>4.01</v>
+        <v>4.25</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>590669062.51</v>
+        <v>657096811.87</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>9.07</v>
+        <v>9.31</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>473197459.29</v>
+        <v>521914943.73</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>10.55</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="11">
@@ -758,28 +758,28 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1185110246.56</v>
+        <v>1223996865.97</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>3.69</v>
+        <v>3.78</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>187525522.68</v>
+        <v>662466396.2700001</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2.88</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>164366234.86</v>
+        <v>557634642.58</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>3.67</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="12">
@@ -798,19 +798,19 @@
         <v>2079741446.05</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>6.48</v>
+        <v>6.43</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>517658937.19</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>7.95</v>
+        <v>7.34</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>386139164.45</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>8.609999999999999</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="13">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>496443932.15</v>
+        <v>639716216.1799999</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>0</v>
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>564169565.05</v>
+        <v>575737935.76</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>0</v>
@@ -882,25 +882,25 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>20989</v>
+        <v>21025</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32084452738.84</v>
+        <v>32366368804.12</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>6514401473.04</v>
+        <v>7055770095.990001</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>4483484742.74</v>
+        <v>4925470634.900001</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 00:46:28.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 00:46:28.</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20989</v>
+        <v>21001</v>
       </c>
     </row>
     <row r="14">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20989</v>
+        <v>21001</v>
       </c>
     </row>
     <row r="16">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20986</v>
+        <v>21022</v>
       </c>
     </row>
     <row r="19">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>111</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>200</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>55637</v>
+        <v>55644</v>
       </c>
     </row>
     <row r="48">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-09 18:50:07</t>
+          <t>2026-10-10 00:46:28</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="B62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>-541368622.95</v>
       </c>
     </row>
     <row r="65">
@@ -1620,7 +1620,7 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
@@ -1772,7 +1772,7 @@
         <v>1226983360</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>4</v>
@@ -1843,7 +1843,7 @@
         <v>677740390.27</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>29</v>
@@ -1914,7 +1914,7 @@
         <v>650405604.49</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>15</v>
@@ -1985,7 +1985,7 @@
         <v>613221297.87</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>7</v>
@@ -2020,7 +2020,7 @@
         <v>2800000</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -2056,7 +2056,7 @@
         <v>575680870.9499999</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>22</v>
@@ -2073,7 +2073,7 @@
         <v>7535730.35</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>500000</v>
@@ -2085,7 +2085,7 @@
         <v>1000000</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="R9" s="6" t="n">
         <v>3000000</v>
@@ -2127,7 +2127,7 @@
         <v>548600000</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>3</v>
@@ -2198,7 +2198,7 @@
         <v>501085000</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>9</v>
@@ -2269,7 +2269,7 @@
         <v>495224296</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>7</v>
@@ -2340,7 +2340,7 @@
         <v>495030000</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>5</v>
@@ -2411,7 +2411,7 @@
         <v>480000000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>2</v>
@@ -2482,7 +2482,7 @@
         <v>478688485.93</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>58</v>
@@ -2553,7 +2553,7 @@
         <v>400000000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>3</v>
@@ -2624,7 +2624,7 @@
         <v>359743243.37</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>26</v>
@@ -2695,7 +2695,7 @@
         <v>356809269.47</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>34</v>
@@ -2766,7 +2766,7 @@
         <v>315201070.12</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>74</v>
@@ -2837,7 +2837,7 @@
         <v>291023623.16</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>10</v>
@@ -2908,7 +2908,7 @@
         <v>281039715.29</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>37</v>
@@ -2979,7 +2979,7 @@
         <v>242593012.43</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>60</v>
@@ -2996,7 +2996,7 @@
         <v>3656350.86</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>650000</v>
@@ -3008,7 +3008,7 @@
         <v>1744850.78</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="R22" s="6" t="n">
         <v>1030953.08</v>
@@ -3050,7 +3050,7 @@
         <v>201352865.22</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>28</v>
@@ -3192,7 +3192,7 @@
         <v>178707610.09</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>18</v>
@@ -3221,7 +3221,7 @@
         <v>4300000</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="R25" s="6" t="n">
         <v>500000</v>
@@ -3334,7 +3334,7 @@
         <v>156766941.44</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>120</v>
@@ -3547,7 +3547,7 @@
         <v>149986151.74</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>43</v>
@@ -3706,7 +3706,7 @@
         <v>4530000</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>30000</v>
@@ -4115,7 +4115,7 @@
         <v>95000000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>1</v>
@@ -4416,7 +4416,7 @@
         <v>17454194.03</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="N42" s="6" t="n">
         <v>0</v>
@@ -4434,7 +4434,7 @@
         <v>16008194.03</v>
       </c>
       <c r="S42" s="6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="43">
@@ -4541,7 +4541,7 @@
         <v>78678550.66</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>121</v>
@@ -4683,7 +4683,7 @@
         <v>75659161.21000001</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>16</v>
@@ -4718,7 +4718,7 @@
         <v>1305780.52</v>
       </c>
       <c r="S46" s="6" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="47">
@@ -4754,7 +4754,7 @@
         <v>75658784.06999999</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I47" s="5" t="n">
         <v>35</v>
@@ -4771,7 +4771,7 @@
         <v>3105570</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="N47" s="6" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>1750000</v>
       </c>
       <c r="S48" s="6" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="49">
@@ -5339,7 +5339,7 @@
         <v>11275000</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="N55" s="6" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>11000000</v>
       </c>
       <c r="S55" s="6" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="56">
@@ -5535,7 +5535,7 @@
         <v>62944315.4</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="I58" s="5" t="n">
         <v>6</v>
@@ -5694,7 +5694,7 @@
         <v>3680000</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="N60" s="6" t="n">
         <v>20000</v>
@@ -5748,7 +5748,7 @@
         <v>59852043</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="I61" s="5" t="n">
         <v>65</v>
@@ -6061,7 +6061,7 @@
         <v>611286.47</v>
       </c>
       <c r="Q65" s="6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="R65" s="6" t="n">
         <v>800000</v>
@@ -6120,7 +6120,7 @@
         <v>3007407.41</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="N66" s="6" t="n">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>625000</v>
       </c>
       <c r="Q66" s="6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="R66" s="6" t="n">
         <v>580000</v>
@@ -6333,7 +6333,7 @@
         <v>13190970.74</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="N69" s="6" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
         <v>1499763</v>
       </c>
       <c r="Q69" s="6" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="R69" s="6" t="n">
         <v>0</v>
@@ -6671,7 +6671,7 @@
         <v>50000000</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I74" s="5" t="n">
         <v>1</v>
@@ -6842,7 +6842,7 @@
         <v>27185.18</v>
       </c>
       <c r="Q76" s="6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="R76" s="6" t="n">
         <v>1016650</v>
@@ -7114,7 +7114,7 @@
         <v>2410970.42</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="N80" s="6" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>2396323.01</v>
       </c>
       <c r="Q80" s="6" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="R80" s="6" t="n">
         <v>0</v>
@@ -7452,7 +7452,7 @@
         <v>46721417.82</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="I85" s="5" t="n">
         <v>18</v>
@@ -7496,40 +7496,40 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>RAUAN SILVA</t>
+          <t>GUSTAVO ROCHA</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO ESTADUAL</t>
+          <t>VICE-GOVERNADOR</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>OUTROS</t>
+          <t>ADVOGADO</t>
         </is>
       </c>
       <c r="G86" s="6" t="n">
-        <v>46700000</v>
+        <v>46721417.82</v>
       </c>
       <c r="H86" s="6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>46700000</v>
+        <v>26850444.14</v>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
@@ -7567,40 +7567,40 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>JOSE NELTO</t>
+          <t>GUSTAVO ROCHA</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO FEDERAL</t>
+          <t>VICE-GOVERNADOR</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO</t>
+          <t>ADVOGADO</t>
         </is>
       </c>
       <c r="G87" s="6" t="n">
-        <v>46363907.43</v>
+        <v>46721417.82</v>
       </c>
       <c r="H87" s="6" t="n">
         <v>0.14</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>31500000</v>
+        <v>26850444.14</v>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
@@ -7608,28 +7608,28 @@
         </is>
       </c>
       <c r="L87" s="6" t="n">
-        <v>2915894.39</v>
+        <v>0</v>
       </c>
       <c r="M87" s="6" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="N87" s="6" t="n">
-        <v>70540</v>
+        <v>0</v>
       </c>
       <c r="O87" s="6" t="n">
-        <v>229200</v>
+        <v>0</v>
       </c>
       <c r="P87" s="6" t="n">
-        <v>95000</v>
+        <v>0</v>
       </c>
       <c r="Q87" s="6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="R87" s="6" t="n">
-        <v>2507629.39</v>
+        <v>0</v>
       </c>
       <c r="S87" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -7638,40 +7638,40 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>GUSTAVO ROCHA</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>SENADOR</t>
+          <t>VICE-GOVERNADOR</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>AGRICULTOR</t>
+          <t>ADVOGADO</t>
         </is>
       </c>
       <c r="G88" s="6" t="n">
-        <v>46302824.91</v>
+        <v>46721417.82</v>
       </c>
       <c r="H88" s="6" t="n">
         <v>0.14</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>29240990.29</v>
+        <v>26850444.14</v>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
@@ -7679,16 +7679,16 @@
         </is>
       </c>
       <c r="L88" s="6" t="n">
-        <v>1082545.38</v>
+        <v>0</v>
       </c>
       <c r="M88" s="6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="N88" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O88" s="6" t="n">
-        <v>1082545.38</v>
+        <v>0</v>
       </c>
       <c r="P88" s="6" t="n">
         <v>0</v>
@@ -7709,40 +7709,40 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>CARLOS ERNESTO TETI</t>
+          <t>RAUAN SILVA</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>1º SUPLENTE</t>
+          <t>DEPUTADO ESTADUAL</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>SOLIDARIEDADE</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>AGRÔNOMO</t>
+          <t>OUTROS</t>
         </is>
       </c>
       <c r="G89" s="6" t="n">
-        <v>46109918.9</v>
+        <v>46700000</v>
       </c>
       <c r="H89" s="6" t="n">
         <v>0.14</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>14480000</v>
+        <v>46700000</v>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
@@ -7780,40 +7780,40 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>RICARDO LEITE</t>
+          <t>JOSE NELTO</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>VICE-GOVERNADOR</t>
+          <t>DEPUTADO FEDERAL</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>EMPRESÁRIO</t>
+          <t>DEPUTADO</t>
         </is>
       </c>
       <c r="G90" s="6" t="n">
-        <v>45470504.08</v>
+        <v>46363907.43</v>
       </c>
       <c r="H90" s="6" t="n">
         <v>0.14</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>10100000</v>
+        <v>31500000</v>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
@@ -7821,28 +7821,28 @@
         </is>
       </c>
       <c r="L90" s="6" t="n">
-        <v>0</v>
+        <v>2915894.39</v>
       </c>
       <c r="M90" s="6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="N90" s="6" t="n">
-        <v>0</v>
+        <v>70540</v>
       </c>
       <c r="O90" s="6" t="n">
-        <v>0</v>
+        <v>229200</v>
       </c>
       <c r="P90" s="6" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="Q90" s="6" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="R90" s="6" t="n">
-        <v>0</v>
+        <v>2507629.39</v>
       </c>
       <c r="S90" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="91">
@@ -7851,40 +7851,40 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>ARI NASCIMENTO</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO ESTADUAL</t>
+          <t>SENADOR</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>VEREADOR</t>
+          <t>AGRICULTOR</t>
         </is>
       </c>
       <c r="G91" s="6" t="n">
-        <v>45400000</v>
+        <v>46302824.91</v>
       </c>
       <c r="H91" s="6" t="n">
         <v>0.14</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>40000000</v>
+        <v>29240990.29</v>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
@@ -7892,16 +7892,16 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>270000</v>
+        <v>1082545.38</v>
       </c>
       <c r="M91" s="6" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N91" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O91" s="6" t="n">
-        <v>0</v>
+        <v>1082545.38</v>
       </c>
       <c r="P91" s="6" t="n">
         <v>0</v>
@@ -7910,10 +7910,10 @@
         <v>0</v>
       </c>
       <c r="R91" s="6" t="n">
-        <v>270000</v>
+        <v>0</v>
       </c>
       <c r="S91" s="6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -7922,40 +7922,40 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>MARCELINHO CARIOCA</t>
+          <t>CARLOS ERNESTO TETI</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO DISTRITAL</t>
+          <t>1º SUPLENTE</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>EMPRESÁRIO</t>
+          <t>AGRÔNOMO</t>
         </is>
       </c>
       <c r="G92" s="6" t="n">
-        <v>45370000</v>
+        <v>46109918.9</v>
       </c>
       <c r="H92" s="6" t="n">
         <v>0.14</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>40000000</v>
+        <v>14480000</v>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
@@ -7963,28 +7963,28 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>590752.51</v>
+        <v>0</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="N92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O92" s="6" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="P92" s="6" t="n">
-        <v>237276.41</v>
+        <v>0</v>
       </c>
       <c r="Q92" s="6" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="R92" s="6" t="n">
-        <v>348476.1</v>
+        <v>0</v>
       </c>
       <c r="S92" s="6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -7993,22 +7993,22 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>RICARDO ABRÃO</t>
+          <t>RICARDO LEITE</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO FEDERAL</t>
+          <t>VICE-GOVERNADOR</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -8017,16 +8017,16 @@
         </is>
       </c>
       <c r="G93" s="6" t="n">
-        <v>44497052.1</v>
+        <v>45470504.08</v>
       </c>
       <c r="H93" s="6" t="n">
         <v>0.14</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>6473502.02</v>
+        <v>10100000</v>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
@@ -8034,13 +8034,13 @@
         </is>
       </c>
       <c r="L93" s="6" t="n">
-        <v>1197650</v>
+        <v>0</v>
       </c>
       <c r="M93" s="6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="N93" s="6" t="n">
-        <v>317650</v>
+        <v>0</v>
       </c>
       <c r="O93" s="6" t="n">
         <v>0</v>
@@ -8052,10 +8052,10 @@
         <v>0</v>
       </c>
       <c r="R93" s="6" t="n">
-        <v>880000</v>
+        <v>0</v>
       </c>
       <c r="S93" s="6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -8064,40 +8064,40 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>MAURÍCIO RIZZI</t>
+          <t>ARI NASCIMENTO</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>1º SUPLENTE</t>
+          <t>DEPUTADO ESTADUAL</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>PECUARISTA</t>
+          <t>VEREADOR</t>
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>42895492.61</v>
+        <v>45400000</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>13638662</v>
+        <v>40000000</v>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         </is>
       </c>
       <c r="L94" s="6" t="n">
-        <v>0</v>
+        <v>270000</v>
       </c>
       <c r="M94" s="6" t="n">
         <v>0</v>
@@ -8123,10 +8123,10 @@
         <v>0</v>
       </c>
       <c r="R94" s="6" t="n">
-        <v>0</v>
+        <v>270000</v>
       </c>
       <c r="S94" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="95">
@@ -8135,40 +8135,40 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>HÉLIO FLÁVIO</t>
+          <t>MARCELINHO CARIOCA</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>1º SUPLENTE</t>
+          <t>DEPUTADO DISTRITAL</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>FISCAL</t>
+          <t>EMPRESÁRIO</t>
         </is>
       </c>
       <c r="G95" s="6" t="n">
-        <v>42244770</v>
+        <v>45370000</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>35073160</v>
+        <v>40000000</v>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
@@ -8176,28 +8176,28 @@
         </is>
       </c>
       <c r="L95" s="6" t="n">
-        <v>0</v>
+        <v>590752.51</v>
       </c>
       <c r="M95" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="N95" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O95" s="6" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="P95" s="6" t="n">
-        <v>0</v>
+        <v>237276.41</v>
       </c>
       <c r="Q95" s="6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="R95" s="6" t="n">
-        <v>0</v>
+        <v>348476.1</v>
       </c>
       <c r="S95" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="96">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>CHIQUINHO DO DUDA</t>
+          <t>RICARDO ABRÃO</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO ESTADUAL</t>
+          <t>DEPUTADO FEDERAL</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -8230,16 +8230,16 @@
         </is>
       </c>
       <c r="G96" s="6" t="n">
-        <v>42202498.53</v>
+        <v>44497052.1</v>
       </c>
       <c r="H96" s="6" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>16000000</v>
+        <v>6473502.02</v>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
@@ -8247,16 +8247,16 @@
         </is>
       </c>
       <c r="L96" s="6" t="n">
-        <v>650000</v>
+        <v>1197650</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="N96" s="6" t="n">
-        <v>125000</v>
+        <v>317650</v>
       </c>
       <c r="O96" s="6" t="n">
-        <v>375000</v>
+        <v>0</v>
       </c>
       <c r="P96" s="6" t="n">
         <v>0</v>
@@ -8265,10 +8265,10 @@
         <v>0</v>
       </c>
       <c r="R96" s="6" t="n">
-        <v>150000</v>
+        <v>880000</v>
       </c>
       <c r="S96" s="6" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="97">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>VICENTE SANTINI</t>
+          <t>MAURÍCIO RIZZI</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -8287,30 +8287,30 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>ADVOGADO</t>
+          <t>PECUARISTA</t>
         </is>
       </c>
       <c r="G97" s="6" t="n">
-        <v>41555091.06</v>
+        <v>42895492.61</v>
       </c>
       <c r="H97" s="6" t="n">
         <v>0.13</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="J97" s="6" t="n">
-        <v>25374808.01</v>
+        <v>13638662</v>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>MARCOS ESPINHEIRA</t>
+          <t>HÉLIO FLÁVIO</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -8358,30 +8358,30 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>MOBILIZA</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>EMPRESÁRIO</t>
+          <t>FISCAL</t>
         </is>
       </c>
       <c r="G98" s="6" t="n">
-        <v>41134000</v>
+        <v>42244770</v>
       </c>
       <c r="H98" s="6" t="n">
         <v>0.13</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J98" s="6" t="n">
-        <v>18000000</v>
+        <v>35073160</v>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
@@ -8419,40 +8419,40 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>NELSON PADOVANI</t>
+          <t>CHIQUINHO DO DUDA</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>2º SUPLENTE</t>
+          <t>DEPUTADO ESTADUAL</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRADOR</t>
+          <t>EMPRESÁRIO</t>
         </is>
       </c>
       <c r="G99" s="6" t="n">
-        <v>41009681.74</v>
+        <v>42202498.53</v>
       </c>
       <c r="H99" s="6" t="n">
         <v>0.13</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>17704839</v>
+        <v>16000000</v>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
@@ -8460,16 +8460,16 @@
         </is>
       </c>
       <c r="L99" s="6" t="n">
-        <v>0</v>
+        <v>650000</v>
       </c>
       <c r="M99" s="6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="N99" s="6" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="O99" s="6" t="n">
-        <v>0</v>
+        <v>375000</v>
       </c>
       <c r="P99" s="6" t="n">
         <v>0</v>
@@ -8478,7 +8478,7 @@
         <v>0</v>
       </c>
       <c r="R99" s="6" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="S99" s="6" t="n">
         <v>0</v>
@@ -8490,40 +8490,40 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>ROGERIO RIGUETTI</t>
+          <t>VICENTE SANTINI</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO FEDERAL</t>
+          <t>1º SUPLENTE</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>EMPRESÁRIO</t>
+          <t>ADVOGADO</t>
         </is>
       </c>
       <c r="G100" s="6" t="n">
-        <v>40063200</v>
+        <v>41555091.06</v>
       </c>
       <c r="H100" s="6" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>25000000</v>
+        <v>25374808.01</v>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
@@ -8561,40 +8561,40 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>ALEXIS FONTEYNE</t>
+          <t>MARCOS ESPINHEIRA</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO FEDERAL</t>
+          <t>1º SUPLENTE</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>MOBILIZA</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>ADMINISTRADOR</t>
+          <t>EMPRESÁRIO</t>
         </is>
       </c>
       <c r="G101" s="6" t="n">
-        <v>40000000</v>
+        <v>41134000</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>24000000</v>
+        <v>18000000</v>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
@@ -8602,28 +8602,28 @@
         </is>
       </c>
       <c r="L101" s="6" t="n">
-        <v>1121194.08</v>
+        <v>0</v>
       </c>
       <c r="M101" s="6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="N101" s="6" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="O101" s="6" t="n">
-        <v>162601</v>
+        <v>0</v>
       </c>
       <c r="P101" s="6" t="n">
-        <v>420533.08</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="6" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="R101" s="6" t="n">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="S101" s="6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>THAIS TAKAHASHI</t>
+          <t>NELSON PADOVANI</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO FEDERAL</t>
+          <t>2º SUPLENTE</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -8647,25 +8647,25 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>CIDADANIA</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>ADVOGADO</t>
+          <t>ADMINISTRADOR</t>
         </is>
       </c>
       <c r="G102" s="6" t="n">
-        <v>38891871.24</v>
+        <v>41009681.74</v>
       </c>
       <c r="H102" s="6" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="J102" s="6" t="n">
-        <v>3500000</v>
+        <v>17704839</v>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
@@ -8673,16 +8673,16 @@
         </is>
       </c>
       <c r="L102" s="6" t="n">
-        <v>589876.3300000001</v>
+        <v>0</v>
       </c>
       <c r="M102" s="6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="N102" s="6" t="n">
-        <v>158375.33</v>
+        <v>0</v>
       </c>
       <c r="O102" s="6" t="n">
-        <v>6501</v>
+        <v>0</v>
       </c>
       <c r="P102" s="6" t="n">
         <v>0</v>
@@ -8691,10 +8691,10 @@
         <v>0</v>
       </c>
       <c r="R102" s="6" t="n">
-        <v>425000</v>
+        <v>0</v>
       </c>
       <c r="S102" s="6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -8703,22 +8703,22 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>MATTIOLO</t>
+          <t>ROGERIO RIGUETTI</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>DEPUTADO ESTADUAL</t>
+          <t>DEPUTADO FEDERAL</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="G103" s="6" t="n">
-        <v>38247149</v>
+        <v>40063200</v>
       </c>
       <c r="H103" s="6" t="n">
         <v>0.12</v>
@@ -8736,7 +8736,7 @@
         <v>22</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>27875560</v>
+        <v>25000000</v>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
@@ -8744,16 +8744,16 @@
         </is>
       </c>
       <c r="L103" s="6" t="n">
-        <v>343697.99</v>
+        <v>0</v>
       </c>
       <c r="M103" s="6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="N103" s="6" t="n">
-        <v>28500</v>
+        <v>0</v>
       </c>
       <c r="O103" s="6" t="n">
-        <v>115197.99</v>
+        <v>0</v>
       </c>
       <c r="P103" s="6" t="n">
         <v>0</v>
@@ -8762,7 +8762,7 @@
         <v>0</v>
       </c>
       <c r="R103" s="6" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="S103" s="6" t="n">
         <v>0</v>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>SANZIO RODRIGUES</t>
+          <t>ALEXIS FONTEYNE</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
@@ -8789,16 +8789,16 @@
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>EMPRESÁRIO</t>
+          <t>ADMINISTRADOR</t>
         </is>
       </c>
       <c r="G104" s="9" t="n">
-        <v>37770000</v>
+        <v>40000000</v>
       </c>
       <c r="H104" s="9" t="n">
         <v>0.12</v>
@@ -8807,7 +8807,7 @@
         <v>7</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>35000000</v>
+        <v>24000000</v>
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
@@ -8815,34 +8815,34 @@
         </is>
       </c>
       <c r="L104" s="9" t="n">
-        <v>20000</v>
+        <v>1121194.08</v>
       </c>
       <c r="M104" s="9" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N104" s="9" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="O104" s="9" t="n">
-        <v>0</v>
+        <v>162601</v>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0</v>
+        <v>420533.08</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R104" s="9" t="n">
-        <v>20000</v>
+        <v>400000</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 00:46:28.</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9038,7 @@
         <v>271714826.33</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>6.06</v>
+        <v>5.52</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>264113813.76</v>
@@ -9103,7 +9103,7 @@
         <v>96360942.05</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>94608886.36</v>
@@ -9168,7 +9168,7 @@
         <v>31000000</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>15000000</v>
@@ -9233,7 +9233,7 @@
         <v>17000000</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>9000000</v>
@@ -9298,7 +9298,7 @@
         <v>15000000</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>15000000</v>
@@ -9363,7 +9363,7 @@
         <v>13400000</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>13250000</v>
@@ -9428,7 +9428,7 @@
         <v>12925015.88</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>12552711.88</v>
@@ -9493,7 +9493,7 @@
         <v>9817290</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>5620170</v>
@@ -9558,7 +9558,7 @@
         <v>9457826</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>8931553.75</v>
@@ -9623,7 +9623,7 @@
         <v>9157196.560000001</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>8139149.6</v>
@@ -9688,7 +9688,7 @@
         <v>8920500</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>6879000</v>
@@ -9753,7 +9753,7 @@
         <v>6995623.63</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>3846831.65</v>
@@ -9818,7 +9818,7 @@
         <v>6379700</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>4900000</v>
@@ -9883,7 +9883,7 @@
         <v>6350000</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>6350000</v>
@@ -9948,7 +9948,7 @@
         <v>6279227</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>4672182.32</v>
@@ -10013,7 +10013,7 @@
         <v>6000000</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>1000</v>
@@ -10078,7 +10078,7 @@
         <v>6000000</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>6000000</v>
@@ -10143,7 +10143,7 @@
         <v>5941049.63</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>4377145.24</v>
@@ -10208,7 +10208,7 @@
         <v>5698948.42</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>3247580.97</v>
@@ -10273,7 +10273,7 @@
         <v>5465974</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>4545447.5</v>
@@ -10338,7 +10338,7 @@
         <v>5092796.17</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>2608986.1</v>
@@ -10403,7 +10403,7 @@
         <v>5030000</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>5030000</v>
@@ -10468,7 +10468,7 @@
         <v>4860473.9</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>3775459.9</v>
@@ -10533,7 +10533,7 @@
         <v>4800000</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>4800000</v>
@@ -10598,7 +10598,7 @@
         <v>4750000</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>1950000</v>
@@ -10663,7 +10663,7 @@
         <v>4725010.64</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>4278188.41</v>
@@ -10728,7 +10728,7 @@
         <v>4600000</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>2500000</v>
@@ -10793,7 +10793,7 @@
         <v>4500000</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>4500000</v>
@@ -10858,7 +10858,7 @@
         <v>4415528.32</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>4404691.09</v>
@@ -10923,7 +10923,7 @@
         <v>4361068.9</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>2931289.36</v>
@@ -11118,7 +11118,7 @@
         <v>4148608</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>2074304</v>
@@ -11183,7 +11183,7 @@
         <v>4050000</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>4050000</v>
@@ -11248,7 +11248,7 @@
         <v>4025000</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>3025000</v>
@@ -11313,7 +11313,7 @@
         <v>3992074.4</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>3345524.8</v>
@@ -11703,7 +11703,7 @@
         <v>3664444.75</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>2775403.75</v>
@@ -11768,7 +11768,7 @@
         <v>3600000</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L47" s="6" t="n">
         <v>0</v>
@@ -11833,7 +11833,7 @@
         <v>3600000</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L48" s="6" t="n">
         <v>3600000</v>
@@ -11898,7 +11898,7 @@
         <v>3550000</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L49" s="6" t="n">
         <v>2550000</v>
@@ -11963,7 +11963,7 @@
         <v>3544000</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L50" s="6" t="n">
         <v>3544000</v>
@@ -12028,7 +12028,7 @@
         <v>3525287.95</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L51" s="6" t="n">
         <v>2962641.32</v>
@@ -12093,7 +12093,7 @@
         <v>3500000</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L52" s="6" t="n">
         <v>3500000</v>
@@ -12158,7 +12158,7 @@
         <v>3450000</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L53" s="6" t="n">
         <v>2100000</v>
@@ -12223,7 +12223,7 @@
         <v>3400000</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L54" s="6" t="n">
         <v>3400000</v>
@@ -12288,7 +12288,7 @@
         <v>3392478.61</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>3056974.57</v>
@@ -12613,7 +12613,7 @@
         <v>3183519.5</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L60" s="6" t="n">
         <v>2227955</v>
@@ -12678,7 +12678,7 @@
         <v>3150000</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L61" s="6" t="n">
         <v>3150000</v>
@@ -12743,7 +12743,7 @@
         <v>3135000</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L62" s="6" t="n">
         <v>25000</v>
@@ -12808,7 +12808,7 @@
         <v>3122716.46</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L63" s="6" t="n">
         <v>2736315.46</v>
@@ -12873,7 +12873,7 @@
         <v>3095620</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L64" s="6" t="n">
         <v>2638885</v>
@@ -12938,7 +12938,7 @@
         <v>3093159.25</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L65" s="6" t="n">
         <v>1889810</v>
@@ -13003,7 +13003,7 @@
         <v>3088876.88</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L66" s="6" t="n">
         <v>1184829.14</v>
@@ -13068,7 +13068,7 @@
         <v>3072492</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L67" s="6" t="n">
         <v>2946822</v>
@@ -13133,7 +13133,7 @@
         <v>3064378.8</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L68" s="6" t="n">
         <v>2680552.8</v>
@@ -13198,7 +13198,7 @@
         <v>3051300</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L69" s="6" t="n">
         <v>2235665</v>
@@ -13263,7 +13263,7 @@
         <v>3031718.5</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L70" s="6" t="n">
         <v>2735748.5</v>
@@ -13328,7 +13328,7 @@
         <v>3000000</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L71" s="6" t="n">
         <v>3000000</v>
@@ -13393,7 +13393,7 @@
         <v>2974896.09</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>1534769.67</v>
@@ -13458,7 +13458,7 @@
         <v>2974854</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L73" s="6" t="n">
         <v>2974854</v>
@@ -13523,7 +13523,7 @@
         <v>2973690.65</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L74" s="6" t="n">
         <v>2313704.49</v>
@@ -13588,7 +13588,7 @@
         <v>2964622.1</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L75" s="6" t="n">
         <v>2169411.1</v>
@@ -13653,7 +13653,7 @@
         <v>2956779.23</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L76" s="6" t="n">
         <v>2752822.74</v>
@@ -14238,7 +14238,7 @@
         <v>2670000</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L85" s="6" t="n">
         <v>2070000</v>
@@ -14303,7 +14303,7 @@
         <v>2630000</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L86" s="6" t="n">
         <v>1230000</v>
@@ -14368,7 +14368,7 @@
         <v>2614250</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L87" s="6" t="n">
         <v>1064250</v>
@@ -14433,7 +14433,7 @@
         <v>2590000</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L88" s="6" t="n">
         <v>750000</v>
@@ -14498,7 +14498,7 @@
         <v>2583889.36</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L89" s="6" t="n">
         <v>1848705</v>
@@ -14563,7 +14563,7 @@
         <v>2567000</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L90" s="6" t="n">
         <v>2517000</v>
@@ -14628,7 +14628,7 @@
         <v>2550000</v>
       </c>
       <c r="K91" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L91" s="6" t="n">
         <v>1950000</v>
@@ -14693,7 +14693,7 @@
         <v>2544850</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>2259050</v>
@@ -14758,7 +14758,7 @@
         <v>2535303</v>
       </c>
       <c r="K93" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L93" s="6" t="n">
         <v>1786590.5</v>
@@ -14823,7 +14823,7 @@
         <v>2531795</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L94" s="6" t="n">
         <v>2316995</v>
@@ -14888,7 +14888,7 @@
         <v>2500000</v>
       </c>
       <c r="K95" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L95" s="6" t="n">
         <v>2500000</v>
@@ -14953,7 +14953,7 @@
         <v>2500000</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L96" s="6" t="n">
         <v>2500000</v>
@@ -15018,7 +15018,7 @@
         <v>2500000</v>
       </c>
       <c r="K97" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L97" s="6" t="n">
         <v>1000000</v>
@@ -15083,7 +15083,7 @@
         <v>2474000</v>
       </c>
       <c r="K98" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L98" s="6" t="n">
         <v>740500</v>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 00:46:28.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 00:46:28.</t>
         </is>
       </c>
     </row>
@@ -17316,7 +17316,7 @@
         <v>936919682.97</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>14.38</v>
+        <v>13.28</v>
       </c>
     </row>
     <row r="6">
@@ -17327,19 +17327,19 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Minas Gerais</t>
+          <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>537442966.99</v>
+        <v>662466396.27</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>8.25</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -17350,19 +17350,19 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Minas Gerais</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>500585904.47</v>
+        <v>537442966.99</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>7.68</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="8">
@@ -17373,19 +17373,19 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>346543085.6</v>
+        <v>500585904.47</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>5.32</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="9">
@@ -17396,19 +17396,19 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Paraná</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>346016801.61</v>
+        <v>346543085.6</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>5.31</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="10">
@@ -17419,16 +17419,16 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Sul</t>
+          <t>Paraná</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>319025875.49</v>
+        <v>346016801.61</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.9</v>
@@ -17442,19 +17442,19 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Pernambuco</t>
+          <t>Rio Grande do Sul</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>260307452.89</v>
+        <v>319025875.49</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="12">
@@ -17465,19 +17465,19 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Pernambuco</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>247970964</v>
+        <v>260307452.89</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>3.81</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="13">
@@ -17488,19 +17488,19 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>231521015.11</v>
+        <v>247970964</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.55</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="14">
@@ -17511,19 +17511,19 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>222808386.63</v>
+        <v>231521015.11</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="15">
@@ -17534,19 +17534,19 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Santa Catarina</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>214563038.42</v>
+        <v>222808386.63</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>3.29</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="16">
@@ -17557,19 +17557,19 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Pará</t>
+          <t>Santa Catarina</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>191210667.05</v>
+        <v>214563038.42</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="17">
@@ -17580,19 +17580,19 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Presidenciáveis, circunscrição nacional</t>
+          <t>Distrito Federal</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>187525522.68</v>
+        <v>197465309.26</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18">
@@ -17603,19 +17603,19 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Distrito Federal</t>
+          <t>Pará</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>165125867.65</v>
+        <v>191210667.05</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="19">
@@ -17626,19 +17626,19 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>161529050.76</v>
+        <v>175697342.77</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="20">
@@ -17649,19 +17649,19 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Mato Grosso</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>154449742.09</v>
+        <v>161529050.76</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="21">
@@ -17672,19 +17672,19 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Paraíba</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>149350586.97</v>
+        <v>154449742.09</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="22">
@@ -17695,19 +17695,19 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>146264467.78</v>
+        <v>149350586.97</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="23">
@@ -17718,19 +17718,19 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>145098928.3</v>
+        <v>146264467.78</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="24">
@@ -17741,19 +17741,19 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Piauí</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>141609035.02</v>
+        <v>145098928.3</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="25">
@@ -17776,7 +17776,7 @@
         <v>122464826.8</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="26">
@@ -17799,7 +17799,7 @@
         <v>118727000.65</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="27">
@@ -17822,7 +17822,7 @@
         <v>117989279.13</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="28">
@@ -17845,7 +17845,7 @@
         <v>115979377.26</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="29">
@@ -17868,7 +17868,7 @@
         <v>115928772.61</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="30">
@@ -17891,7 +17891,7 @@
         <v>107022802.11</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="31">
@@ -17914,7 +17914,7 @@
         <v>105860219.13</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="32">
@@ -17937,7 +17937,7 @@
         <v>104560152.87</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="33">
@@ -17960,7 +17960,7 @@
         <v>147810636.54</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>27.23</v>
+        <v>25.11</v>
       </c>
     </row>
     <row r="34">
@@ -17971,19 +17971,19 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Paraná</t>
+          <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>35734691.7</v>
+        <v>47540943.62</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>6.58</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="35">
@@ -17994,19 +17994,19 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Minas Gerais</t>
+          <t>Paraná</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>31641290.85</v>
+        <v>35734691.7</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>5.83</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="36">
@@ -18017,19 +18017,19 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Minas Gerais</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>27916615.98</v>
+        <v>31641290.85</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>5.14</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="37">
@@ -18040,19 +18040,19 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>21923959.19</v>
+        <v>27916615.98</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>4.04</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="38">
@@ -18063,19 +18063,19 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Pernambuco</t>
+          <t>Distrito Federal</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>21166735.92</v>
+        <v>23492838.61</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>3.9</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="39">
@@ -18086,19 +18086,19 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Sul</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>18050807.7</v>
+        <v>21923959.19</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>3.32</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="40">
@@ -18109,19 +18109,19 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Santa Catarina</t>
+          <t>Pernambuco</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>17840460.01</v>
+        <v>21166735.92</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>3.29</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="41">
@@ -18132,19 +18132,19 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Presidenciáveis, circunscrição nacional</t>
+          <t>Rio Grande do Sul</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>17543696.24</v>
+        <v>18050807.7</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>3.23</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="42">
@@ -18155,19 +18155,19 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santa Catarina</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>17151108.64</v>
+        <v>17840460.01</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>3.16</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="43">
@@ -18178,19 +18178,19 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Distrito Federal</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>16979850.61</v>
+        <v>17421238</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>3.13</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="44">
@@ -18201,19 +18201,19 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>16299200.1</v>
+        <v>17151108.64</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="45">
@@ -18224,19 +18224,19 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>15345139.27</v>
+        <v>16299200.1</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="46">
@@ -18247,19 +18247,19 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Piauí</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>12937118.35</v>
+        <v>15345139.27</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="47">
@@ -18270,19 +18270,19 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>12558574.97</v>
+        <v>12937118.35</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="48">
@@ -18293,19 +18293,19 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Amapá</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>12135824.21</v>
+        <v>12558574.97</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="49">
@@ -18316,19 +18316,19 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>11635177.76</v>
+        <v>12135824.21</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="50">
@@ -18339,19 +18339,19 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>10539115.61</v>
+        <v>11635177.76</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="51">
@@ -18362,19 +18362,19 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Paraíba</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>10239043.56</v>
+        <v>10539115.61</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="52">
@@ -18385,19 +18385,19 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Acre</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>9679796.74</v>
+        <v>10239043.56</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="53">
@@ -18408,19 +18408,19 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Acre</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>8166532.99</v>
+        <v>9679796.74</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="54">
@@ -18431,19 +18431,19 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>8121238</v>
+        <v>8166532.99</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="55">
@@ -18466,7 +18466,7 @@
         <v>7868495.17</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="56">
@@ -18489,7 +18489,7 @@
         <v>7513506.75</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="57">
@@ -18512,7 +18512,7 @@
         <v>7286528.8</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="58">
@@ -18535,7 +18535,7 @@
         <v>6935311.45</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="59">
@@ -18558,7 +18558,7 @@
         <v>6569838.31</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="60">
@@ -18581,7 +18581,7 @@
         <v>5311997.37</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="61">
@@ -18604,7 +18604,7 @@
         <v>621090945.2</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>12.88</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="62">
@@ -18615,19 +18615,19 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>412041448.93</v>
+        <v>533098902.3</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>8.550000000000001</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="63">
@@ -18638,19 +18638,19 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Minas Gerais</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>375391552.64</v>
+        <v>412041448.93</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>7.79</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="64">
@@ -18661,19 +18661,19 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Minas Gerais</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>282673417.37</v>
+        <v>375391552.64</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>5.86</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="65">
@@ -18684,19 +18684,19 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Sul</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>248639457.06</v>
+        <v>282673417.37</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>5.16</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="66">
@@ -18707,19 +18707,19 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Paraná</t>
+          <t>Rio Grande do Sul</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>237540200.29</v>
+        <v>248639457.06</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>4.93</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="67">
@@ -18730,19 +18730,19 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Pernambuco</t>
+          <t>Paraná</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>199480839.32</v>
+        <v>237540200.29</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>4.14</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="68">
@@ -18753,19 +18753,19 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Pernambuco</t>
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>183035826.39</v>
+        <v>199480839.32</v>
       </c>
       <c r="E68" s="12" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="69">
@@ -18776,19 +18776,19 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>172963239.83</v>
+        <v>183035826.39</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>3.59</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="70">
@@ -18799,19 +18799,19 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>164178786.19</v>
+        <v>172963239.83</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>3.41</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="71">
@@ -18822,19 +18822,19 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Pará</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>154899399.83</v>
+        <v>164178786.19</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>3.21</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="72">
@@ -18845,19 +18845,19 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Santa Catarina</t>
+          <t>Pará</t>
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>145766980.5</v>
+        <v>154899399.83</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="73">
@@ -18868,19 +18868,19 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Presidenciáveis, circunscrição nacional</t>
+          <t>Santa Catarina</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>136625008.59</v>
+        <v>145766980.5</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="74">
@@ -18891,19 +18891,19 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Paraíba</t>
+          <t>Distrito Federal</t>
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>122116962.45</v>
+        <v>132546947.2</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="75">
@@ -18914,19 +18914,19 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>119665278.8</v>
+        <v>127588307.47</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="76">
@@ -18937,19 +18937,19 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Distrito Federal</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>108892976.98</v>
+        <v>122116962.45</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="77">
@@ -18960,19 +18960,19 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>105817480.74</v>
+        <v>119665278.8</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="78">
@@ -18983,19 +18983,19 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>105814677.94</v>
+        <v>105817480.74</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="79">
@@ -19018,7 +19018,7 @@
         <v>104059277.83</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="80">
@@ -19041,7 +19041,7 @@
         <v>97316118.98</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="81">
@@ -19064,7 +19064,7 @@
         <v>96671722.64</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="82">
@@ -19087,7 +19087,7 @@
         <v>96310229.08</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="83">
@@ -19110,7 +19110,7 @@
         <v>92214955.93000001</v>
       </c>
       <c r="E83" s="12" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="84">
@@ -19133,7 +19133,7 @@
         <v>89116564.23</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="85">
@@ -19156,7 +19156,7 @@
         <v>88384512.84999999</v>
       </c>
       <c r="E85" s="12" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="86">
@@ -19179,7 +19179,7 @@
         <v>88057920.31999999</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="87">
@@ -19202,7 +19202,7 @@
         <v>87415825.06</v>
       </c>
       <c r="E87" s="12" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="88">
@@ -19225,7 +19225,7 @@
         <v>84766787.34</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="89">
@@ -19245,7 +19245,7 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>803275588.21</v>
+        <v>803281920.24</v>
       </c>
       <c r="E89" s="12" t="n">
         <v>25.84</v>
@@ -19268,7 +19268,7 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>201313907.16</v>
+        <v>201322892.06</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>6.48</v>
@@ -19337,7 +19337,7 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>139965790.09</v>
+        <v>139980665.09</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>4.5</v>
@@ -19406,7 +19406,7 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>118244586.69</v>
+        <v>118252586.69</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>3.8</v>
@@ -19429,7 +19429,7 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>107587049.99</v>
+        <v>107593449.99</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>3.46</v>
@@ -19475,7 +19475,7 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>93790000.17</v>
+        <v>93797800.17</v>
       </c>
       <c r="E99" s="12" t="n">
         <v>3.02</v>
@@ -20536,7 +20536,7 @@
         <v>95501785.09</v>
       </c>
       <c r="E145" s="12" t="n">
-        <v>14.63</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="146">
@@ -20559,7 +20559,7 @@
         <v>79175202.48</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>12.13</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="147">
@@ -20570,19 +20570,19 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso</t>
+          <t>Presidenciáveis, circunscrição nacional</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
-        <v>38004015.09</v>
+        <v>46564040</v>
       </c>
       <c r="E147" s="12" t="n">
-        <v>5.82</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="148">
@@ -20593,19 +20593,19 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Mato Grosso</t>
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>37892212.12</v>
+        <v>38004015.09</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>5.81</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="149">
@@ -20616,19 +20616,19 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
-        <v>36583332.49</v>
+        <v>37892212.12</v>
       </c>
       <c r="E149" s="12" t="n">
-        <v>5.61</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="150">
@@ -20639,19 +20639,19 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>34534235.11</v>
+        <v>36583332.49</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>5.29</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="151">
@@ -20662,19 +20662,19 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Paraná</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>34170748.87</v>
+        <v>34534235.11</v>
       </c>
       <c r="E151" s="12" t="n">
-        <v>5.24</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="152">
@@ -20685,19 +20685,19 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Sul</t>
+          <t>Paraná</t>
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>26694458.13</v>
+        <v>34170748.87</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>4.09</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="153">
@@ -20708,19 +20708,19 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Santa Catarina</t>
+          <t>Rio Grande do Sul</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
-        <v>25667583.64</v>
+        <v>26694458.13</v>
       </c>
       <c r="E153" s="12" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="154">
@@ -20731,19 +20731,19 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Santa Catarina</t>
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>23588176.33</v>
+        <v>25667583.64</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>3.61</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="155">
@@ -20763,7 +20763,7 @@
         </is>
       </c>
       <c r="D155" s="6" t="n">
-        <v>23536403.49</v>
+        <v>24893303.88</v>
       </c>
       <c r="E155" s="12" t="n">
         <v>3.61</v>
@@ -20777,19 +20777,19 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>21974792.07</v>
+        <v>23588176.33</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>3.37</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="157">
@@ -20800,19 +20800,19 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
-        <v>20567992.65</v>
+        <v>21974792.07</v>
       </c>
       <c r="E157" s="12" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="158">
@@ -20823,19 +20823,19 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Pernambuco</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D158" s="6" t="n">
-        <v>20259773.27</v>
+        <v>20567992.65</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="159">
@@ -20846,19 +20846,19 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Pará</t>
+          <t>Pernambuco</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
-        <v>16976974.61</v>
+        <v>20259773.27</v>
       </c>
       <c r="E159" s="12" t="n">
-        <v>2.6</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="160">
@@ -20869,19 +20869,19 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Pará</t>
         </is>
       </c>
       <c r="D160" s="6" t="n">
-        <v>15382781.29</v>
+        <v>16976974.61</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="161">
@@ -20892,19 +20892,19 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Presidenciáveis, circunscrição nacional</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
-        <v>14167409.09</v>
+        <v>16010270.57</v>
       </c>
       <c r="E161" s="12" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="162">
@@ -20915,19 +20915,19 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Piauí</t>
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>13664442.35</v>
+        <v>15382781.29</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="163">
@@ -20950,7 +20950,7 @@
         <v>12158755.75</v>
       </c>
       <c r="E163" s="12" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="164">
@@ -20973,7 +20973,7 @@
         <v>9842620.949999999</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="165">
@@ -20996,7 +20996,7 @@
         <v>9677069.92</v>
       </c>
       <c r="E165" s="12" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="166">
@@ -21019,7 +21019,7 @@
         <v>9414726.800000001</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="167">
@@ -21042,7 +21042,7 @@
         <v>7627122.96</v>
       </c>
       <c r="E167" s="12" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="168">
@@ -21065,7 +21065,7 @@
         <v>7208102.49</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="169">
@@ -21088,7 +21088,7 @@
         <v>5600837.96</v>
       </c>
       <c r="E169" s="12" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="170">
@@ -21111,7 +21111,7 @@
         <v>4883292.25</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="171">
@@ -21134,7 +21134,7 @@
         <v>4001024.31</v>
       </c>
       <c r="E171" s="12" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="172">
@@ -21157,7 +21157,7 @@
         <v>3889894.6</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="173">
@@ -21180,7 +21180,7 @@
         <v>2630</v>
       </c>
       <c r="E173" s="12" t="n">
-        <v>12.53</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="174">
@@ -21203,7 +21203,7 @@
         <v>2055</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>9.789999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="175">
@@ -21226,7 +21226,7 @@
         <v>1832</v>
       </c>
       <c r="E175" s="12" t="n">
-        <v>8.73</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="176">
@@ -21249,7 +21249,7 @@
         <v>1224</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>5.83</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="177">
@@ -21272,7 +21272,7 @@
         <v>1090</v>
       </c>
       <c r="E177" s="12" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="178">
@@ -21295,7 +21295,7 @@
         <v>1054</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="179">
@@ -21318,7 +21318,7 @@
         <v>961</v>
       </c>
       <c r="E179" s="12" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="180">
@@ -21341,7 +21341,7 @@
         <v>906</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="181">
@@ -21364,7 +21364,7 @@
         <v>741</v>
       </c>
       <c r="E181" s="12" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="182">
@@ -21410,7 +21410,7 @@
         <v>700</v>
       </c>
       <c r="E183" s="12" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="184">
@@ -21430,10 +21430,10 @@
         </is>
       </c>
       <c r="D184" s="6" t="n">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="185">
@@ -21456,7 +21456,7 @@
         <v>619</v>
       </c>
       <c r="E185" s="12" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="186">
@@ -21476,10 +21476,10 @@
         </is>
       </c>
       <c r="D186" s="6" t="n">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="187">
@@ -21525,7 +21525,7 @@
         <v>455</v>
       </c>
       <c r="E188" s="12" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="189">
@@ -21571,7 +21571,7 @@
         <v>438</v>
       </c>
       <c r="E190" s="12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="191">
@@ -21617,7 +21617,7 @@
         <v>413</v>
       </c>
       <c r="E192" s="12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="193">
@@ -21640,7 +21640,7 @@
         <v>411</v>
       </c>
       <c r="E193" s="12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="194">
@@ -21663,7 +21663,7 @@
         <v>402</v>
       </c>
       <c r="E194" s="12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="195">
@@ -21798,10 +21798,10 @@
         </is>
       </c>
       <c r="D200" s="6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E200" s="12" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="201">
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 00:46:28.</t>
         </is>
       </c>
     </row>
@@ -22465,7 +22465,7 @@
     <row r="231">
       <c r="A231" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: a serie de fornecedores cobre 69.3% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
+          <t>Nota 1: a serie de fornecedores cobre 69.4% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 00:46:28.</t>
         </is>
       </c>
     </row>
@@ -23928,43 +23928,43 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1647</v>
+        <v>1656</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>7.85</v>
+        <v>7.88</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4898820044.67</v>
+        <v>4925073710.64</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1151080118.25</v>
+        <v>1363098234.27</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>17.67</v>
+        <v>19.32</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>868755521.58</v>
+        <v>1010221550.1</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>18.02</v>
+        <v>19.2</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>105743709.72</v>
+        <v>134715552.66</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>19.48</v>
+        <v>22.88</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>21449551.93</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>107345448.37</v>
+        <v>134121257.38</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>827422313.91</v>
+        <v>1023759673.32</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>84.66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
@@ -23974,43 +23974,43 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>5.26</v>
+        <v>5.27</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>773060589.24</v>
+        <v>788242541.16</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>694741554.0700001</v>
+        <v>964972653.25</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>10.66</v>
+        <v>13.68</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>572019546.96</v>
+        <v>833431382.37</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>11.87</v>
+        <v>15.84</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>4699622.71</v>
+        <v>6064915.15</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.87</v>
+        <v>1.03</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>12040411.8</v>
+        <v>12100411.8</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>76949125.29000001</v>
+        <v>82918847.58</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>490007302.72</v>
+        <v>691516959.9400001</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>83.01000000000001</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
@@ -24023,7 +24023,7 @@
         <v>846</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>1817696708.82</v>
@@ -24032,19 +24032,19 @@
         <v>642319399.0700001</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>9.859999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>524376209.33</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>10.88</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>64074031.19</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>11.8</v>
+        <v>10.88</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>7781568.76</v>
@@ -24069,7 +24069,7 @@
         <v>1134</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>5.4</v>
+        <v>5.39</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>2567364147.06</v>
@@ -24078,19 +24078,19 @@
         <v>632180770.23</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>9.699999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>430511803.71</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>8.93</v>
+        <v>8.18</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>34632737.02</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>6.38</v>
+        <v>5.88</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>18474921.2</v>
@@ -24112,43 +24112,43 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1309</v>
+        <v>1315</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>6.24</v>
+        <v>6.25</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2484193186.63</v>
+        <v>2627364468.4</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>572950011.35</v>
+        <v>592344769.1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>350156242.76</v>
+        <v>359929872.29</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>7.26</v>
+        <v>6.84</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>117288639.51</v>
+        <v>126288639.51</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>21.6</v>
+        <v>21.45</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>11228711.93</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>62046873.88</v>
+        <v>62427852.1</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>396401756.59</v>
+        <v>412027090.09</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>81.59</v>
+        <v>82.08</v>
       </c>
     </row>
     <row r="10">
@@ -24158,43 +24158,43 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1294367106.67</v>
+        <v>1297000000.84</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>526750730.58</v>
+        <v>551781830.58</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>8.09</v>
+        <v>7.82</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>418495289.17</v>
+        <v>435745289.17</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>8.68</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>54788027.01</v>
+        <v>60961127.01</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>10.09</v>
+        <v>10.35</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>7614300.3</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>29275326.97</v>
+        <v>30283326.97</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>334822100.2</v>
+        <v>353155285.48</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>89.84999999999999</v>
+        <v>90.02</v>
       </c>
     </row>
     <row r="11">
@@ -24204,43 +24204,43 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>6.77</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3339602389.67</v>
+        <v>3422608758.32</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>520548892.18</v>
+        <v>535242442.18</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>7.99</v>
+        <v>7.59</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>395807248.96</v>
+        <v>407807248.96</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>8.210000000000001</v>
+        <v>7.75</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>17328836.54</v>
+        <v>17628836.54</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>3.19</v>
+        <v>2.99</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>14488576.43</v>
+        <v>14503576.43</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>64642029.51</v>
+        <v>66606879.51</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>337534907.69</v>
+        <v>347715264.44</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>79.37</v>
+        <v>79.48</v>
       </c>
     </row>
     <row r="12">
@@ -24253,7 +24253,7 @@
         <v>1237</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>1812875005.9</v>
@@ -24262,19 +24262,19 @@
         <v>294389410.12</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>4.52</v>
+        <v>4.17</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>237865482.3</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4.93</v>
+        <v>4.52</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>5640256.810000001</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>9919217.029999999</v>
@@ -24308,19 +24308,19 @@
         <v>229600878.09</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>166995631.66</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3.46</v>
+        <v>3.17</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>46290560.08</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>8.529999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>2887239.21</v>
@@ -24342,31 +24342,31 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>4.6</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>931393345.11</v>
+        <v>941267717.34</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>220676750.51</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>3.39</v>
+        <v>3.13</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>148425976.38</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>3.08</v>
+        <v>2.82</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>6702544.83</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>10819094.97</v>
@@ -24391,7 +24391,7 @@
         <v>1094</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>2591694177.84</v>
@@ -24400,19 +24400,19 @@
         <v>209118973.9</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>150270544.11</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>4462718.01</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>11581495.5</v>
@@ -24437,7 +24437,7 @@
         <v>1309</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>1884208841.62</v>
@@ -24446,19 +24446,19 @@
         <v>144143178.36</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>34395735.16</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>44449677.11</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>8.19</v>
+        <v>7.55</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>7301251.22</v>
@@ -24483,7 +24483,7 @@
         <v>799</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>139488473.87</v>
@@ -24492,19 +24492,19 @@
         <v>135276815.82</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>123923665.62</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2.57</v>
+        <v>2.35</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>1957373.78</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>792959.91</v>
@@ -24529,7 +24529,7 @@
         <v>980</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>1072776812.99</v>
@@ -24538,19 +24538,19 @@
         <v>98452018.93000001</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>65247540.29</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>13457331.38</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>4722415.95</v>
@@ -24584,19 +24584,19 @@
         <v>97284178.53</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>67578077.34999999</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>14150615.09</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>3328973.82</v>
@@ -24621,7 +24621,7 @@
         <v>539</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>280452197.14</v>
@@ -24630,19 +24630,19 @@
         <v>91936463.76000001</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>83798847.27</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>1626000</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>1864312.46</v>
@@ -24676,19 +24676,19 @@
         <v>73226422.78</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>60379791.05</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>4467405.01</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>1268839.67</v>
@@ -24710,31 +24710,31 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>328303892.2</v>
+        <v>330099422.77</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>60082969.54</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>43108728</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>193073.13</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>3374813.86</v>
@@ -24768,19 +24768,19 @@
         <v>35868431.86</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>32836384.31</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>489726.2</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>562325.3300000001</v>
@@ -24814,19 +24814,19 @@
         <v>33868398.27</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>29538402.63</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>412960.64</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>509308.86</v>
@@ -24860,13 +24860,13 @@
         <v>11912981</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>2234662.44</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>295</v>
@@ -24897,7 +24897,7 @@
         <v>581</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>243522021.57</v>
@@ -24906,13 +24906,13 @@
         <v>10059569.16</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>2308000</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>10000</v>
@@ -24943,7 +24943,7 @@
         <v>547</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>184054953.85</v>
@@ -24952,13 +24952,13 @@
         <v>9128325.68</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>3270747.94</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>3674.78</v>
@@ -24998,7 +24998,7 @@
         <v>6209966.24</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>2903963.13</v>
@@ -25044,7 +25044,7 @@
         <v>5206083.96</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>6000</v>
@@ -25096,7 +25096,7 @@
         <v>3191097</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
@@ -25142,7 +25142,7 @@
         <v>1283730.22</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 00:46:28.</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
         <v>2945185</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>121725</v>
@@ -26909,7 +26909,7 @@
         <v>1057896</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>120000</v>
@@ -26964,7 +26964,7 @@
         <v>1032800</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>43000</v>
@@ -27019,7 +27019,7 @@
         <v>1030133.3</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>30000</v>
@@ -27074,7 +27074,7 @@
         <v>1028239</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>10000</v>
@@ -27129,7 +27129,7 @@
         <v>1012251</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>10000</v>
@@ -27184,7 +27184,7 @@
         <v>1004484</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>80000</v>
@@ -27239,7 +27239,7 @@
         <v>995696.73</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>120000</v>
@@ -27294,7 +27294,7 @@
         <v>983700</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>0</v>
@@ -27349,7 +27349,7 @@
         <v>981483.92</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>120500</v>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-09 18:50:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 00:46:28.</t>
         </is>
       </c>
     </row>
@@ -28228,7 +28228,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Nota 2: outras 4162 candidaturas NAO declararam receita alguma, das quais 924 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
+          <t>Nota 2: outras 4180 candidaturas NAO declararam receita alguma, das quais 942 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
         </is>
       </c>
     </row>
@@ -28930,7 +28930,7 @@
         <v>72.05</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>48</v>
@@ -28939,19 +28939,19 @@
         <v>62304</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>19.76</v>
+        <v>20.16</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>141609035.02</v>
+        <v>175697342.77</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>34.12</v>
+        <v>42.33</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>47.35</v>
+        <v>58.75</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>38.1</v>
+        <v>48.49</v>
       </c>
     </row>
     <row r="19">
@@ -29188,7 +29188,7 @@
         <v>74.86</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>40</v>
@@ -29197,19 +29197,19 @@
         <v>56331</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>29.65</v>
+        <v>30.18</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>165125867.65</v>
+        <v>197465309.26</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>54.86</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>73.28</v>
+        <v>87.64</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>55.86</v>
+        <v>69.25</v>
       </c>
     </row>
     <row r="25">
@@ -29540,7 +29540,7 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>2</v>
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>187525522.68</v>
+        <v>662466396.27</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>73.69</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>20989</v>
+        <v>21025</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>1790</v>
@@ -29602,19 +29602,19 @@
         <v>88182</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>13.3</v>
+        <v>13.32</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>6514401473.040001</v>
+        <v>7055770095.99</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>30.41</v>
+        <v>32.94</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>41.27</v>
+        <v>44.7</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>33.98</v>
+        <v>37.07</v>
       </c>
     </row>
     <row r="34">

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 06:49:42.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 06:49:42.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-10 06:49:42</t>
+          <t>2026-10-10 09:03:04</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 06:49:42.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 06:49:42.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 06:49:42.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 06:49:42.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 06:49:42.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 06:49:42.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 06:49:42.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -581,7 +581,7 @@
         <v>4495080252.41</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>13.67</v>
+        <v>13.66</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>0</v>
@@ -655,7 +655,7 @@
         <v>31995985.59</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="8">
@@ -668,25 +668,25 @@
         <v>11295</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>53.66</v>
+        <v>53.63</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>12007434756.34</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>36.51</v>
+        <v>36.5</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>1783225197.04</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>24.61</v>
+        <v>24.54</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>1174536671.28</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>23.39</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="9">
@@ -699,25 +699,25 @@
         <v>7803</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>37.07</v>
+        <v>37.05</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>8707767692.280001</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>26.48</v>
+        <v>26.47</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>3396921482.72</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>46.88</v>
+        <v>46.74</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>2271018014.26</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>45.22</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="10">
@@ -727,28 +727,28 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1753027042.26</v>
+        <v>1755573651.78</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.33</v>
+        <v>5.34</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>729348136.9300001</v>
+        <v>749780272.78</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>10.06</v>
+        <v>10.32</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>580042105.5700001</v>
+        <v>608553187</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>11.55</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="11">
@@ -761,7 +761,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>1223996865.97</v>
@@ -773,13 +773,13 @@
         <v>771349229.63</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>10.64</v>
+        <v>10.61</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>577600810.63</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>11.5</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="12">
@@ -792,7 +792,7 @@
         <v>319</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>2079741446.05</v>
@@ -804,13 +804,13 @@
         <v>518076265.71</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>7.15</v>
+        <v>7.13</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>387212575.68</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>7.71</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="13">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>785862735.59</v>
+        <v>791514463.25</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>0</v>
@@ -854,7 +854,7 @@
         <v>20</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>575737935.76</v>
@@ -882,25 +882,25 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>21049</v>
+        <v>21061</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32890384607.86</v>
+        <v>32898582945.04</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7246570798.099999</v>
+        <v>7267002933.95</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>5022406163.01</v>
+        <v>5050917244.440001</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21009</v>
+        <v>21013</v>
       </c>
     </row>
     <row r="14">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21009</v>
+        <v>21013</v>
       </c>
     </row>
     <row r="16">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21046</v>
+        <v>21058</v>
       </c>
     </row>
     <row r="19">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>279</v>
+        <v>295</v>
       </c>
     </row>
     <row r="23">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>6706621</v>
+        <v>6737183</v>
       </c>
     </row>
     <row r="61">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-10 09:03:04</t>
+          <t>2026-10-10 15:03:15</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-691554841.14</v>
+        <v>-711986976.99</v>
       </c>
     </row>
     <row r="65">
@@ -2340,7 +2340,7 @@
         <v>495030000</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>5</v>
@@ -3209,7 +3209,7 @@
         <v>5446578.61</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N25" s="6" t="n">
         <v>0</v>
@@ -3221,7 +3221,7 @@
         <v>4300000</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R25" s="6" t="n">
         <v>500000</v>
@@ -5765,7 +5765,7 @@
         <v>3264000</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="N61" s="6" t="n">
         <v>220000</v>
@@ -8552,7 +8552,7 @@
         <v>270000</v>
       </c>
       <c r="S100" s="6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9038,7 @@
         <v>274430273.36</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5.46</v>
+        <v>5.43</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>266900377</v>
@@ -9103,7 +9103,7 @@
         <v>96854689.95</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>95147634.26000001</v>
@@ -9168,7 +9168,7 @@
         <v>31000000</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>15000000</v>
@@ -9493,7 +9493,7 @@
         <v>9817290</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>5620170</v>
@@ -9948,7 +9948,7 @@
         <v>6279227</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>4672182.32</v>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
         </is>
       </c>
     </row>
@@ -17316,7 +17316,7 @@
         <v>939338671.25</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>12.96</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="6">
@@ -17339,7 +17339,7 @@
         <v>771349229.63</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>10.64</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="7">
@@ -17362,7 +17362,7 @@
         <v>538365356.08</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>7.43</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="8">
@@ -17385,7 +17385,7 @@
         <v>500975044.6</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>6.91</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="9">
@@ -17408,7 +17408,7 @@
         <v>347379154.28</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="10">
@@ -17431,7 +17431,7 @@
         <v>346218803.68</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>4.78</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="11">
@@ -17454,7 +17454,7 @@
         <v>319429268.6</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="12">
@@ -17477,7 +17477,7 @@
         <v>260376041.15</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="13">
@@ -17500,7 +17500,7 @@
         <v>248129335.7</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="14">
@@ -17523,7 +17523,7 @@
         <v>231968669.42</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="15">
@@ -17546,7 +17546,7 @@
         <v>223427397.48</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="16">
@@ -17569,7 +17569,7 @@
         <v>215953205.16</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="17">
@@ -17592,7 +17592,7 @@
         <v>206561665.78</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="18">
@@ -17615,7 +17615,7 @@
         <v>191413183.8</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="19">
@@ -17638,7 +17638,7 @@
         <v>189081171.59</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -17661,7 +17661,7 @@
         <v>176143006.2</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="21">
@@ -17684,7 +17684,7 @@
         <v>162298081</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="22">
@@ -17730,7 +17730,7 @@
         <v>146357084.1</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="24">
@@ -17776,7 +17776,7 @@
         <v>134640502.61</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="26">
@@ -17787,19 +17787,19 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Rio Grande do Norte</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>122885231.77</v>
+        <v>125207710.92</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="27">
@@ -17810,19 +17810,19 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>118738334.43</v>
+        <v>122885231.77</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="28">
@@ -17833,16 +17833,16 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso do Sul</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>118100015.06</v>
+        <v>118738334.43</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>1.63</v>
@@ -17856,19 +17856,19 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Alagoas</t>
+          <t>Mato Grosso do Sul</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>116112117.63</v>
+        <v>118100015.06</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="30">
@@ -17879,16 +17879,16 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Amapá</t>
+          <t>Alagoas</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>116027014.96</v>
+        <v>116112117.63</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>1.6</v>
@@ -17902,19 +17902,19 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Roraima</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>105896079.13</v>
+        <v>116027014.96</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="32">
@@ -17925,19 +17925,19 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Norte</t>
+          <t>Roraima</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>104775575.07</v>
+        <v>105896079.13</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="33">
@@ -17960,7 +17960,7 @@
         <v>148115915.91</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>23.94</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="34">
@@ -17983,7 +17983,7 @@
         <v>63540943.62</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>10.27</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="35">
@@ -18006,7 +18006,7 @@
         <v>35734691.7</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>5.78</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="36">
@@ -18029,7 +18029,7 @@
         <v>31641290.85</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="37">
@@ -18052,7 +18052,7 @@
         <v>30492838.61</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>4.93</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="38">
@@ -18075,7 +18075,7 @@
         <v>27973665.98</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>4.52</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="39">
@@ -18121,7 +18121,7 @@
         <v>21166735.92</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="41">
@@ -18144,7 +18144,7 @@
         <v>18058068.75</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="42">
@@ -18190,7 +18190,7 @@
         <v>17621238</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="44">
@@ -18236,7 +18236,7 @@
         <v>16319200.1</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="46">
@@ -18282,7 +18282,7 @@
         <v>15345139.27</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="48">
@@ -18420,7 +18420,7 @@
         <v>10240268.05</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="54">
@@ -18546,19 +18546,19 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Roraima</t>
+          <t>Rio Grande do Norte</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>6569838.31</v>
+        <v>6693216.87</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="60">
@@ -18569,19 +18569,19 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Norte</t>
+          <t>Roraima</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5311997.37</v>
+        <v>6569838.31</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>0.86</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="61">
@@ -18604,7 +18604,7 @@
         <v>621682134.8</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>11.52</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="62">
@@ -18627,7 +18627,7 @@
         <v>613298902.3</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>11.36</v>
+        <v>11.33</v>
       </c>
     </row>
     <row r="63">
@@ -18650,7 +18650,7 @@
         <v>412090448.93</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>7.63</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="64">
@@ -18673,7 +18673,7 @@
         <v>375418971.54</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>6.95</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="65">
@@ -18696,7 +18696,7 @@
         <v>282735417.37</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="66">
@@ -18719,7 +18719,7 @@
         <v>248689457.06</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>4.61</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="67">
@@ -18742,7 +18742,7 @@
         <v>237550200.29</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="68">
@@ -18765,7 +18765,7 @@
         <v>199480839.32</v>
       </c>
       <c r="E68" s="12" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="69">
@@ -18788,7 +18788,7 @@
         <v>183040826.39</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="70">
@@ -18811,7 +18811,7 @@
         <v>172963239.83</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="71">
@@ -18834,7 +18834,7 @@
         <v>164184836.19</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="72">
@@ -18857,7 +18857,7 @@
         <v>154899399.83</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="73">
@@ -18880,7 +18880,7 @@
         <v>151165278.8</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="74">
@@ -18903,7 +18903,7 @@
         <v>145779081.5</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="75">
@@ -19018,7 +19018,7 @@
         <v>105817480.74</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="80">
@@ -19029,16 +19029,16 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Rio Grande do Norte</t>
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>104059277.83</v>
+        <v>104528005.98</v>
       </c>
       <c r="E80" s="12" t="n">
         <v>1.93</v>
@@ -19052,19 +19052,19 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Piauí</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>97316118.98</v>
+        <v>104059277.83</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="82">
@@ -19075,19 +19075,19 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Amapá</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>96676722.64</v>
+        <v>97316118.98</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="83">
@@ -19098,19 +19098,19 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Alagoas</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>96310229.08</v>
+        <v>96676722.64</v>
       </c>
       <c r="E83" s="12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="84">
@@ -19121,19 +19121,19 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Roraima</t>
+          <t>Alagoas</t>
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>92214955.93000001</v>
+        <v>96310229.08</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="85">
@@ -19144,19 +19144,19 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Norte</t>
+          <t>Roraima</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>89116564.23</v>
+        <v>92214955.93000001</v>
       </c>
       <c r="E85" s="12" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="86">
@@ -19179,7 +19179,7 @@
         <v>88384512.84999999</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="87">
@@ -20536,7 +20536,7 @@
         <v>96577263.26000001</v>
       </c>
       <c r="E145" s="12" t="n">
-        <v>13.84</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="146">
@@ -20559,7 +20559,7 @@
         <v>79531300.44</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>11.39</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="147">
@@ -20582,7 +20582,7 @@
         <v>48942505.72</v>
       </c>
       <c r="E147" s="12" t="n">
-        <v>7.01</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
@@ -20628,7 +20628,7 @@
         <v>38085709.47</v>
       </c>
       <c r="E149" s="12" t="n">
-        <v>5.46</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="150">
@@ -20674,7 +20674,7 @@
         <v>34900719.44</v>
       </c>
       <c r="E151" s="12" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="152">
@@ -20697,7 +20697,7 @@
         <v>34253029.36</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>4.91</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="153">
@@ -20720,7 +20720,7 @@
         <v>26980128.92</v>
       </c>
       <c r="E153" s="12" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="154">
@@ -20858,7 +20858,7 @@
         <v>20297773.72</v>
       </c>
       <c r="E159" s="12" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="160">
@@ -20927,7 +20927,7 @@
         <v>15534495.24</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="163">
@@ -21085,10 +21085,10 @@
         </is>
       </c>
       <c r="D169" s="6" t="n">
-        <v>5630860.16</v>
+        <v>6396511.16</v>
       </c>
       <c r="E169" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="170">
@@ -21249,7 +21249,7 @@
         <v>1224</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>5.82</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="177">
@@ -21295,7 +21295,7 @@
         <v>1054</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179">
@@ -21318,7 +21318,7 @@
         <v>961</v>
       </c>
       <c r="E179" s="12" t="n">
-        <v>4.57</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="180">
@@ -21410,7 +21410,7 @@
         <v>700</v>
       </c>
       <c r="E183" s="12" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="184">
@@ -21729,10 +21729,10 @@
         </is>
       </c>
       <c r="D197" s="6" t="n">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="E197" s="12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="198">
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
         </is>
       </c>
     </row>
@@ -23931,7 +23931,7 @@
         <v>1662</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>7.9</v>
+        <v>7.89</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>5281805806.47</v>
@@ -23940,19 +23940,19 @@
         <v>1405735148.87</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>19.4</v>
+        <v>19.34</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1023721550.1</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>18.96</v>
+        <v>18.91</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>150890397.42</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>24.39</v>
+        <v>24.33</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>21851884.12</v>
@@ -23974,135 +23974,135 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>5.27</v>
+        <v>5.28</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>788242541.16</v>
+        <v>788542541.16</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1048828854.66</v>
+        <v>1054100225.91</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>14.47</v>
+        <v>14.51</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>915483382.37</v>
+        <v>918728039.12</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>16.96</v>
+        <v>16.97</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>6064915.15</v>
+        <v>6246134.65</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>12220887.03</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>83634087.52</v>
+        <v>84399738.52</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>692449994.6800001</v>
+        <v>701055413.41</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>87.86</v>
+        <v>87.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1140</v>
+        <v>849</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>5.42</v>
+        <v>4.03</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2577905190.84</v>
+        <v>1819943318.34</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>654049334.59</v>
+        <v>658108511.73</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>9.029999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>448626803.71</v>
+        <v>536542994.33</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>8.31</v>
+        <v>9.91</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>34632737.02</v>
+        <v>65276808.97</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>5.6</v>
+        <v>10.53</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>18839446.7</v>
+        <v>8056189.56</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>83964607.95999999</v>
+        <v>29340316.97</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>511180752.93</v>
+        <v>472711959.95</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>73.89</v>
+        <v>91.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>846</v>
+        <v>1140</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>4.02</v>
+        <v>5.41</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1817696708.82</v>
+        <v>2577905190.84</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>642947747.13</v>
+        <v>654049334.59</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>8.869999999999999</v>
+        <v>9</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>524376209.33</v>
+        <v>448626803.71</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>9.710000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>64076808.97</v>
+        <v>34632737.02</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>10.36</v>
+        <v>5.59</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>7912189.56</v>
+        <v>18839446.7</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>29340316.97</v>
+        <v>83964607.95999999</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>452806297.25</v>
+        <v>511180752.93</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>91.52</v>
+        <v>73.89</v>
       </c>
     </row>
     <row r="9">
@@ -24115,7 +24115,7 @@
         <v>1321</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>6.28</v>
+        <v>6.27</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>2779509683.8</v>
@@ -24124,19 +24124,19 @@
         <v>604229188.12</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>8.34</v>
+        <v>8.31</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>370429872.29</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>6.86</v>
+        <v>6.84</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>126534864</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>20.45</v>
+        <v>20.41</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>11619412.8</v>
@@ -24170,19 +24170,19 @@
         <v>576017200.2</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7.95</v>
+        <v>7.93</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>446416289.17</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>8.27</v>
+        <v>8.25</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>74186678.76000001</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>11.99</v>
+        <v>11.96</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>7762845.27</v>
@@ -24204,31 +24204,31 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>6.77</v>
+        <v>6.79</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3426703758.32</v>
+        <v>3431895006.71</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>536133443.18</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>7.4</v>
+        <v>7.38</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>407807248.96</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>7.55</v>
+        <v>7.53</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>17628836.54</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>14746735.62</v>
@@ -24253,7 +24253,7 @@
         <v>1237</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>5.88</v>
+        <v>5.87</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>1812875005.9</v>
@@ -24262,13 +24262,13 @@
         <v>295199071.52</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>237965482.3</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>5640256.810000001</v>
@@ -24308,19 +24308,19 @@
         <v>229740786.52</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>166995631.66</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>46290560.08</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>7.48</v>
+        <v>7.47</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>2903506.06</v>
@@ -24342,25 +24342,25 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>941267717.34</v>
+        <v>941728196.61</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>222285982.7</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>148455951.38</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>6709805.88</v>
@@ -24391,7 +24391,7 @@
         <v>1094</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>2591694177.84</v>
@@ -24400,7 +24400,7 @@
         <v>209562747.69</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>150291927.09</v>
@@ -24446,7 +24446,7 @@
         <v>144146207.42</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>34396229.06</v>
@@ -24458,7 +24458,7 @@
         <v>44449677.11</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>7309289.36</v>
@@ -24467,7 +24467,7 @@
         <v>27042953.19</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>88921572.93000001</v>
+        <v>88921572.92999999</v>
       </c>
       <c r="N16" s="6" t="n">
         <v>54.7</v>
@@ -24483,7 +24483,7 @@
         <v>799</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>139488473.87</v>
@@ -24492,13 +24492,13 @@
         <v>135333277.13</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>123925665.62</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>1959373.78</v>
@@ -24529,7 +24529,7 @@
         <v>980</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>1072776812.99</v>
@@ -24596,7 +24596,7 @@
         <v>14150615.09</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>3349975.82</v>
@@ -24713,7 +24713,7 @@
         <v>239</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>330099422.77</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 09:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
         </is>
       </c>
     </row>
@@ -28228,7 +28228,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Nota 2: outras 4171 candidaturas NAO declararam receita alguma, das quais 954 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
+          <t>Nota 2: outras 4177 candidaturas NAO declararam receita alguma, das quais 960 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
         </is>
       </c>
     </row>
@@ -29059,7 +29059,7 @@
         <v>76.81999999999999</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>40</v>
@@ -29068,19 +29068,19 @@
         <v>66524</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>12.4</v>
+        <v>12.85</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>104775575.07</v>
+        <v>125207710.92</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>30.25</v>
+        <v>36.15</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>39.38</v>
+        <v>47.05</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>35.49</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="22">
@@ -29593,7 +29593,7 @@
         <v>73.69</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>21049</v>
+        <v>21061</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>1790</v>
@@ -29605,16 +29605,16 @@
         <v>13.34</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>7246570798.1</v>
+        <v>7267002933.950001</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>33.83</v>
+        <v>33.92</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>45.91</v>
+        <v>46.04</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>38.12</v>
+        <v>38.23</v>
       </c>
     </row>
     <row r="34">

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-10 15:03:15</t>
+          <t>2026-10-10 15:32:40</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:03:15.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>6737183</v>
+        <v>6736268</v>
       </c>
     </row>
     <row r="61">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-10 15:32:40</t>
+          <t>2026-10-10 21:03:37</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
         </is>
       </c>
     </row>
@@ -24467,7 +24467,7 @@
         <v>27042953.19</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>88921572.92999999</v>
+        <v>88921572.93000001</v>
       </c>
       <c r="N16" s="6" t="n">
         <v>54.7</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 15:32:40.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-10 21:03:37</t>
+          <t>2026-10-11 03:02:32</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-10 21:03:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -646,16 +646,16 @@
         <v>1.03</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>47650486.07</v>
+        <v>47721071.07</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>0.66</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>31995985.59</v>
+        <v>32240780.04</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="8">
@@ -677,16 +677,16 @@
         <v>36.5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1783225197.04</v>
+        <v>1786322147.49</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>24.54</v>
+        <v>24.55</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>1174536671.28</v>
+        <v>1178011139.66</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>23.25</v>
+        <v>23.27</v>
       </c>
     </row>
     <row r="9">
@@ -708,16 +708,16 @@
         <v>26.47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3396921482.72</v>
+        <v>3398271892.38</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>46.74</v>
+        <v>46.71</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2271018014.26</v>
+        <v>2277354655.9</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>44.96</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="10">
@@ -739,16 +739,16 @@
         <v>5.34</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>749780272.78</v>
+        <v>752116844.6800001</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>10.32</v>
+        <v>10.34</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>608553187</v>
+        <v>608688653.1</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>12.05</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="11">
@@ -770,16 +770,16 @@
         <v>3.72</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>771349229.63</v>
+        <v>772962838.47</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>10.61</v>
+        <v>10.62</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>577600810.63</v>
+        <v>577765223.13</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>11.44</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="12">
@@ -801,16 +801,16 @@
         <v>6.32</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>518076265.71</v>
+        <v>518242811.64</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>7.13</v>
+        <v>7.12</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>387212575.68</v>
+        <v>388004216</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>7.67</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="13">
@@ -894,13 +894,13 @@
         <v>100</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7267002933.95</v>
+        <v>7275637605.73</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>5050917244.440001</v>
+        <v>5062064667.83</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>100</v>
@@ -909,14 +909,14 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-10.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
         </is>
       </c>
     </row>
@@ -1025,14 +1025,14 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-10.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>174694</v>
+        <v>175416</v>
       </c>
     </row>
     <row r="24">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6555015956.96</v>
+        <v>6561108386.47</v>
       </c>
     </row>
     <row r="26">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{"REC_FEFC": 4842461527.81, "REC_FINANCIAMENTO_COLETIVO": 18392697.58, "REC_FUNDO_PARTIDARIO": 549248002.62, "REC_ORIGEM_NAO_IDENTIFICADA": 1110352.96, "REC_OUTROS_CANDIDATOS": 120164524.76, "REC_PARTIDO_OUTROS_RECURSOS": 202097173.28, "REC_PESSOAS_FISICAS": 659628291.07, "REC_PROPRIOS": 161913386.88, "REC_SEM_ORIGEM": 0.0}</t>
+          <t>{"REC_FEFC": 4843153724.77, "REC_FINANCIAMENTO_COLETIVO": 18421406.44, "REC_FUNDO_PARTIDARIO": 549470560.59, "REC_ORIGEM_NAO_IDENTIFICADA": 1110352.96, "REC_OUTROS_CANDIDATOS": 120427781.78, "REC_PARTIDO_OUTROS_RECURSOS": 202691423.31, "REC_PESSOAS_FISICAS": 662879762.49, "REC_PROPRIOS": 162953374.13, "REC_SEM_ORIGEM": 0.0}</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>78227</v>
+        <v>78551</v>
       </c>
     </row>
     <row r="30">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>995938</v>
+        <v>999494</v>
       </c>
     </row>
     <row r="36">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>792270</v>
+        <v>794856</v>
       </c>
     </row>
     <row r="37">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4515086289.75</v>
+        <v>4526188163.6</v>
       </c>
     </row>
     <row r="38">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>715285</v>
+        <v>721450</v>
       </c>
     </row>
     <row r="39">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3165095682.6</v>
+        <v>3184714428.42</v>
       </c>
     </row>
     <row r="40">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>73453</v>
+        <v>74063</v>
       </c>
     </row>
     <row r="43">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>798246.8199999999</v>
+        <v>800630.04</v>
       </c>
     </row>
     <row r="44">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>546729</v>
+        <v>547905</v>
       </c>
     </row>
     <row r="46">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>55897</v>
+        <v>56069</v>
       </c>
     </row>
     <row r="48">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>55748</v>
+        <v>55920</v>
       </c>
     </row>
     <row r="49">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="52">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2538404262.32</v>
+        <v>2550373740.61</v>
       </c>
     </row>
     <row r="53">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64057144.72</v>
+        <v>64125144.72</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>184086496.99</v>
+        <v>186468947.28</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4869081817.25</v>
+        <v>4869107818.95</v>
       </c>
     </row>
     <row r="57">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4795568655.36</v>
+        <v>4795594655.36</v>
       </c>
     </row>
     <row r="58">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-11 03:02:32</t>
+          <t>2026-10-11 09:04:27</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-711986976.99</v>
+        <v>-714529219.26</v>
       </c>
     </row>
     <row r="65">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>5446578.61</v>
+        <v>5566578.61</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="N25" s="6" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="L39" s="6" t="n">
-        <v>300000</v>
+        <v>318400</v>
       </c>
       <c r="M39" s="6" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
         <v>300000</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0</v>
+        <v>18400</v>
       </c>
       <c r="P39" s="6" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>11275000</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="N58" s="6" t="n">
         <v>0</v>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="L72" s="6" t="n">
-        <v>13190970.74</v>
+        <v>13353255.74</v>
       </c>
       <c r="M72" s="6" t="n">
         <v>0.18</v>
@@ -6552,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="O72" s="6" t="n">
-        <v>2525000</v>
+        <v>2680000</v>
       </c>
       <c r="P72" s="6" t="n">
         <v>1499763</v>
@@ -8602,13 +8602,13 @@
         </is>
       </c>
       <c r="L101" s="6" t="n">
-        <v>590752.51</v>
+        <v>645752.51</v>
       </c>
       <c r="M101" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="N101" s="6" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="O101" s="6" t="n">
         <v>5000</v>
@@ -8842,14 +8842,14 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-10.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8895,7 @@
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="29" customWidth="1" min="13" max="13"/>
     <col width="34" customWidth="1" min="14" max="14"/>
     <col width="48" customWidth="1" min="15" max="15"/>
@@ -9032,19 +9032,19 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>5958</v>
+        <v>5970</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>274430273.36</v>
+        <v>276471283.48</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5.43</v>
+        <v>5.46</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>266900377</v>
+        <v>268996583.77</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>97.26000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -9097,19 +9097,19 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>96854689.95</v>
+        <v>96979034.95999999</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>1.92</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>95147634.26000001</v>
+        <v>95181979.27</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>98.23999999999999</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>13400000</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>13250000</v>
@@ -9620,16 +9620,16 @@
         <v>241</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>9152196.560000001</v>
+        <v>9155691.550000001</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0.18</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>8134149.6</v>
+        <v>8139644.59</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>88.88</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
@@ -9973,37 +9973,37 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>05.060.706/0003-24</t>
+          <t>***.883.424-**</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>SANTANA   ASSOCIADOS MARKETING E PROPAGANDA LTDA</t>
+          <t>EULINA PONCE DE LEON</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>PESSOA JURÍDICA</t>
+          <t>PESSOA FÍSICA</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>...</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>...</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>SALVADOR</t>
+          <t>...</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Receita (BrasilAPI)</t>
+          <t>...</t>
         </is>
       </c>
       <c r="I20" s="5" t="n">
@@ -10016,19 +10016,19 @@
         <v>0.12</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>6000000</v>
+        <v>1000</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>100</v>
+        <v>0.02</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>ACM NETO (UNIÃO)</t>
+          <t>DANI PORTELA (PT)</t>
         </is>
       </c>
     </row>
@@ -10038,37 +10038,37 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>***.883.424-**</t>
+          <t>05.060.706/0003-24</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>EULINA PONCE DE LEON</t>
+          <t>SANTANA   ASSOCIADOS MARKETING E PROPAGANDA LTDA</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>PESSOA FÍSICA</t>
+          <t>PESSOA JURÍDICA</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>SALVADOR</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>Receita (BrasilAPI)</t>
         </is>
       </c>
       <c r="I21" s="5" t="n">
@@ -10081,19 +10081,19 @@
         <v>0.12</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>1000</v>
+        <v>6000000</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.02</v>
+        <v>100</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>DANI PORTELA (PT)</t>
+          <t>ACM NETO (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -10270,20 +10270,20 @@
         <v>66</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>5465974</v>
+        <v>5484884</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0.11</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4545447.5</v>
+        <v>4597957.5</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>83.16</v>
+        <v>83.83</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>PP; PT; PL; REPUBLICANOS</t>
+          <t>PP; PL; PT; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
@@ -10536,10 +10536,10 @@
         <v>0.1</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>3775459.9</v>
+        <v>3925144.9</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>77.58</v>
+        <v>80.66</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>4800000</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>4800000</v>
@@ -10660,13 +10660,13 @@
         <v>224</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>4759033.34</v>
+        <v>4759819.81</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>4307463.71</v>
+        <v>4308250.18</v>
       </c>
       <c r="M30" s="6" t="n">
         <v>90.51000000000001</v>
@@ -10818,12 +10818,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>05.018.135/0001-06</t>
+          <t>13.007.646/0001-42</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>POLIS PROPAGANDA   MARKETING LTDA</t>
+          <t>GRAFICA EDITORA J ANDRADE LTDA</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -10833,17 +10833,17 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>LAURO DE FREITAS</t>
+          <t>ARACAJU</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -10852,28 +10852,28 @@
         </is>
       </c>
       <c r="I33" s="5" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>4500000</v>
+        <v>4500430.16</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>4500000</v>
+        <v>3055501.42</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>100</v>
+        <v>67.89</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>REPUBLICANOS; PSD; PP; UNIÃO</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>CIRO GOMES (PSDB)</t>
+          <t>GUSTINHO RIBEIRO (PP); VALMIR DE FRANCISQUINHO (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -10883,12 +10883,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>34.028.316/0001-03</t>
+          <t>05.018.135/0001-06</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>EMPRESA BRASILEIRA DE CORREIOS E TELEGRAFOS</t>
+          <t>POLIS PROPAGANDA   MARKETING LTDA</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -10898,17 +10898,17 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Atividades de Correio</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>LAURO DE FREITAS</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -10917,28 +10917,28 @@
         </is>
       </c>
       <c r="I34" s="5" t="n">
-        <v>188</v>
+        <v>1</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>4427325.7</v>
+        <v>4500000</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>4416488.47</v>
+        <v>4500000</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>99.76000000000001</v>
+        <v>100</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>PSD; PL; UNIÃO; MDB</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>FABIO SILVA (UNIÃO); PAULO FILHO DA FUNDAÇÃO (PSD)</t>
+          <t>CIRO GOMES (PSDB)</t>
         </is>
       </c>
     </row>
@@ -10948,12 +10948,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>13.007.646/0001-42</t>
+          <t>34.028.316/0001-03</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>GRAFICA EDITORA J ANDRADE LTDA</t>
+          <t>EMPRESA BRASILEIRA DE CORREIOS E TELEGRAFOS</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -10963,17 +10963,17 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades de Correio</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>ARACAJU</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -10982,28 +10982,28 @@
         </is>
       </c>
       <c r="I35" s="5" t="n">
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>4362788.9</v>
+        <v>4429240.36</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>2931289.36</v>
+        <v>4418403.13</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>67.19</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS; PSD; PP; UNIÃO</t>
+          <t>PSD; PL; UNIÃO; MDB</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>GUSTINHO RIBEIRO (PP); VALMIR DE FRANCISQUINHO (REPUBLICANOS)</t>
+          <t>FABIO SILVA (UNIÃO); PAULO FILHO DA FUNDAÇÃO (PSD)</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
         <v>3790000</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>2110000</v>
@@ -11771,10 +11771,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>2775403.75</v>
+        <v>2812803.75</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>75.73999999999999</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
@@ -12118,12 +12118,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>47.402.712/0001-09</t>
+          <t>85.057.529/0001-02</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>NE ELEICOES SPE LTDA</t>
+          <t>HELLOGRAF ARTES GRAFICAS LTDA</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -12133,17 +12133,17 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>CURITIBA</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -12152,28 +12152,28 @@
         </is>
       </c>
       <c r="I53" s="5" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>3450000</v>
+        <v>3457182.88</v>
       </c>
       <c r="K53" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>2100000</v>
+        <v>1476325.14</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>60.87</v>
+        <v>42.7</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>PSD; UNIÃO; PSDB</t>
+          <t>NOVO; PV; PSD; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>RAQUEL LYRA (PSD); MIGUEL COELHO (UNIÃO)</t>
+          <t>ALIEL MACHADO (PV); JEFFREY CHIQUINI (NOVO)</t>
         </is>
       </c>
     </row>
@@ -12183,12 +12183,12 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>17.861.454/0001-50</t>
+          <t>47.402.712/0001-09</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>RMR CONSULTORIA DE INTELIGENCIA LTDA</t>
+          <t>NE ELEICOES SPE LTDA</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -12198,17 +12198,17 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Pesquisas de mercado e de opinião pública</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -12217,28 +12217,28 @@
         </is>
       </c>
       <c r="I54" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>3400000</v>
+        <v>3450000</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>3400000</v>
+        <v>2100000</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>100</v>
+        <v>60.87</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD; UNIÃO; PSDB</t>
         </is>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>RAQUEL LYRA (PSD); MIGUEL COELHO (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -12285,16 +12285,16 @@
         <v>17</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>3394275.57</v>
+        <v>3411091.28</v>
       </c>
       <c r="K55" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>3058771.53</v>
+        <v>3087074.6</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>90.12</v>
+        <v>90.5</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
@@ -12313,12 +12313,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>24.347.979/0001-37</t>
+          <t>17.861.454/0001-50</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>MACIEL ART DESIGNER GRAFICO - LTDA</t>
+          <t>RMR CONSULTORIA DE INTELIGENCIA LTDA</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -12328,17 +12328,17 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Comércio varejista de artigos recreativos e esportivos</t>
+          <t>Pesquisas de mercado e de opinião pública</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -12347,28 +12347,28 @@
         </is>
       </c>
       <c r="I56" s="5" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>3345250.5</v>
+        <v>3400000</v>
       </c>
       <c r="K56" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>2472030</v>
+        <v>3400000</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>73.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>PSD; PT; PODE; REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>DANIEL COELHO (PSD); LUNA ZARATTINI (PT)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -12378,12 +12378,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>22.317.550/0001-71</t>
+          <t>24.347.979/0001-37</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>M DESIGNER CITY LTDA</t>
+          <t>MACIEL ART DESIGNER GRAFICO - LTDA</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Edição de livros</t>
+          <t>Comércio varejista de artigos recreativos e esportivos</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -12412,28 +12412,28 @@
         </is>
       </c>
       <c r="I57" s="5" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>3342913.16</v>
+        <v>3345250.5</v>
       </c>
       <c r="K57" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>2232877.46</v>
+        <v>2472030</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>66.79000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>PT; REPUBLICANOS; UNIÃO; PSD</t>
+          <t>PSD; PT; PODE; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>LULA (PT); JILMAR TATTO (PT)</t>
+          <t>DANIEL COELHO (PSD); LUNA ZARATTINI (PT)</t>
         </is>
       </c>
     </row>
@@ -12443,12 +12443,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>25.188.538/0001-00</t>
+          <t>22.317.550/0001-71</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>ESSENT INOVACAO CONTABIL LTDA</t>
+          <t>M DESIGNER CITY LTDA</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -12458,17 +12458,17 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Atividades de contabilidade, consultoria e auditoria contábil e tributária</t>
+          <t>Edição de livros</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>HORIZONTINA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -12477,28 +12477,28 @@
         </is>
       </c>
       <c r="I58" s="5" t="n">
-        <v>187</v>
+        <v>43</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>3252935.86</v>
+        <v>3342913.16</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>1538688.52</v>
+        <v>2232877.46</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>47.3</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>PT; MDB; PSD; PL</t>
+          <t>PT; REPUBLICANOS; UNIÃO; PSD</t>
         </is>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>LULA (PT); RICARDO FERRAÇO (MDB)</t>
+          <t>LULA (PT); JILMAR TATTO (PT)</t>
         </is>
       </c>
     </row>
@@ -12508,12 +12508,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>00.887.925/0001-04</t>
+          <t>25.188.538/0001-00</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>GRAFMARQUES INDUSTRIA EDITORA E SERVICOS LTDA</t>
+          <t>ESSENT INOVACAO CONTABIL LTDA</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -12523,17 +12523,17 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Atividades de contabilidade, consultoria e auditoria contábil e tributária</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>HORIZONTINA</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -12542,28 +12542,28 @@
         </is>
       </c>
       <c r="I59" s="5" t="n">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>3231690.9</v>
+        <v>3252935.86</v>
       </c>
       <c r="K59" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>2232704.6</v>
+        <v>1538688.52</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>69.09</v>
+        <v>47.3</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>MDB; UNIÃO; PSD; PP</t>
+          <t>PT; MDB; PSD; PL</t>
         </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>ISNALDO BULHÕES JR (MDB); RENAN FILHO (MDB)</t>
+          <t>LULA (PT); RICARDO FERRAÇO (MDB)</t>
         </is>
       </c>
     </row>
@@ -12573,12 +12573,12 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>45.443.633/0001-02</t>
+          <t>00.887.925/0001-04</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>JD IMPRESSOS PERSONALIZADOS LTDA</t>
+          <t>GRAFMARQUES INDUSTRIA EDITORA E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -12588,17 +12588,17 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>JOAO PESSOA</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -12607,28 +12607,28 @@
         </is>
       </c>
       <c r="I60" s="5" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>3183519.5</v>
+        <v>3231690.9</v>
       </c>
       <c r="K60" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>2227955</v>
+        <v>2232704.6</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>69.98</v>
+        <v>69.09</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>PL; REPUBLICANOS; PP; UNIÃO</t>
+          <t>MDB; UNIÃO; PSD; PP</t>
         </is>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>TIÃO GOMES (REPUBLICANOS); EFRAIM FILHO (PL)</t>
+          <t>ISNALDO BULHÕES JR (MDB); RENAN FILHO (MDB)</t>
         </is>
       </c>
     </row>
@@ -12638,12 +12638,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>07.556.546/0001-72</t>
+          <t>21.246.199/0001-02</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>PRESSGRAF IMPORTACAO TECNOLOGIA E SERVICOS GRAFICOS LTDA</t>
+          <t>LEANDRO ROSA ADVOGADOS ASSOCIADOS</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -12653,17 +12653,17 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades jurídicas, exceto cartórios</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>SALVADOR</t>
+          <t>CURITIBA</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -12672,28 +12672,28 @@
         </is>
       </c>
       <c r="I61" s="5" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>3164378.8</v>
+        <v>3220000</v>
       </c>
       <c r="K61" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>2883468.8</v>
+        <v>195000</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>91.12</v>
+        <v>6.06</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>PSD; REPUBLICANOS; PSDB; UNIÃO</t>
+          <t>PL; NOVO</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>RAIMUNDO COSTA (PSD); MÁRCIO MARINHO (REPUBLICANOS)</t>
+          <t>SERGIO MORO (PL); DELTAN DALLAGNOL (NOVO)</t>
         </is>
       </c>
     </row>
@@ -12703,12 +12703,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>11.197.995/0001-49</t>
+          <t>45.443.633/0001-02</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>BUCCHIANERI ADVOCACIA</t>
+          <t>JD IMPRESSOS PERSONALIZADOS LTDA</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -12718,17 +12718,17 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Atividades jurídicas, exceto cartórios</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>JOAO PESSOA</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -12737,28 +12737,28 @@
         </is>
       </c>
       <c r="I62" s="5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>3150000</v>
+        <v>3183519.5</v>
       </c>
       <c r="K62" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>3150000</v>
+        <v>2227955</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>100</v>
+        <v>69.98</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PL; REPUBLICANOS; PP; UNIÃO</t>
         </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>TIÃO GOMES (REPUBLICANOS); EFRAIM FILHO (PL)</t>
         </is>
       </c>
     </row>
@@ -12768,12 +12768,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>21.246.199/0001-02</t>
+          <t>07.556.546/0001-72</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>LEANDRO ROSA ADVOGADOS ASSOCIADOS</t>
+          <t>PRESSGRAF IMPORTACAO TECNOLOGIA E SERVICOS GRAFICOS LTDA</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Atividades jurídicas, exceto cartórios</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>CURITIBA</t>
+          <t>SALVADOR</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -12802,28 +12802,28 @@
         </is>
       </c>
       <c r="I63" s="5" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>3135000</v>
+        <v>3164378.8</v>
       </c>
       <c r="K63" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L63" s="6" t="n">
-        <v>110000</v>
+        <v>2883468.8</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>3.51</v>
+        <v>91.12</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>PL; NOVO</t>
+          <t>PSD; REPUBLICANOS; PSDB; UNIÃO</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>SERGIO MORO (PL); DELTAN DALLAGNOL (NOVO)</t>
+          <t>RAIMUNDO COSTA (PSD); MÁRCIO MARINHO (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -12833,12 +12833,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>41.470.063/0001-99</t>
+          <t>11.197.995/0001-49</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>SETE CORES INDUSTRIA E COMERCIO LTDA</t>
+          <t>BUCCHIANERI ADVOCACIA</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -12848,17 +12848,17 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Atividades jurídicas, exceto cartórios</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>SAO LUIS</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -12867,28 +12867,28 @@
         </is>
       </c>
       <c r="I64" s="5" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>3122716.46</v>
+        <v>3150000</v>
       </c>
       <c r="K64" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>2736315.46</v>
+        <v>3150000</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>87.63</v>
+        <v>100</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>PL; PCDOB; PDT; REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>SILVIO ANTÔNIO (PL); MÁRCIO JERRY (PCDOB)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -12898,12 +12898,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>51.847.516/0001-07</t>
+          <t>41.470.063/0001-99</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>VOLARE IMPRESSAO TEXTIL LTDA</t>
+          <t>SETE CORES INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -12913,17 +12913,17 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -12932,28 +12932,28 @@
         </is>
       </c>
       <c r="I65" s="5" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>3102120</v>
+        <v>3122716.46</v>
       </c>
       <c r="K65" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L65" s="6" t="n">
-        <v>2681385</v>
+        <v>2736315.46</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>86.44</v>
+        <v>87.63</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>PSD; MDB; REPUBLICANOS; NOVO</t>
+          <t>PL; PCDOB; PDT; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>TARCÍSIO (REPUBLICANOS); BALEIA ROSSI (MDB)</t>
+          <t>SILVIO ANTÔNIO (PL); MÁRCIO JERRY (PCDOB)</t>
         </is>
       </c>
     </row>
@@ -12963,12 +12963,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>17.940.670/0001-90</t>
+          <t>51.847.516/0001-07</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>C. KZAN</t>
+          <t>VOLARE IMPRESSAO TEXTIL LTDA</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>BELEM</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -12997,28 +12997,28 @@
         </is>
       </c>
       <c r="I66" s="5" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>3093159.25</v>
+        <v>3102120</v>
       </c>
       <c r="K66" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L66" s="6" t="n">
-        <v>1889810</v>
+        <v>2681385</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>61.1</v>
+        <v>86.44</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>PODE; MDB; PSD; PDT</t>
+          <t>PSD; MDB; REPUBLICANOS; NOVO</t>
         </is>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>DR. DANIEL (PODE); DRA. ALESSANDRA HABER (PODE)</t>
+          <t>TARCÍSIO (REPUBLICANOS); BALEIA ROSSI (MDB)</t>
         </is>
       </c>
     </row>
@@ -13028,12 +13028,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>85.057.529/0001-02</t>
+          <t>17.940.670/0001-90</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>HELLOGRAF ARTES GRAFICAS LTDA</t>
+          <t>C. KZAN</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -13043,17 +13043,17 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>CURITIBA</t>
+          <t>BELEM</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -13062,28 +13062,28 @@
         </is>
       </c>
       <c r="I67" s="5" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>3088876.88</v>
+        <v>3093159.25</v>
       </c>
       <c r="K67" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L67" s="6" t="n">
-        <v>1184829.14</v>
+        <v>1889810</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>38.36</v>
+        <v>61.1</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>PV; PSD; REPUBLICANOS; NOVO</t>
+          <t>PODE; MDB; PSD; PDT</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>ALIEL MACHADO (PV); SANDRO ALEX (PSD)</t>
+          <t>DR. DANIEL (PODE); DRA. ALESSANDRA HABER (PODE)</t>
         </is>
       </c>
     </row>
@@ -13418,12 +13418,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>07.046.094/0001-89</t>
+          <t>05.677.050/0001-21</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>ELYON SOLUCOES GRAFICAS LTDA</t>
+          <t>ANS IMPRESSOES GRAFICAS LTDA.</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -13433,17 +13433,17 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -13452,28 +13452,28 @@
         </is>
       </c>
       <c r="I73" s="5" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>2974896.09</v>
+        <v>2975389.15</v>
       </c>
       <c r="K73" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L73" s="6" t="n">
-        <v>1534769.67</v>
+        <v>2315402.99</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>51.59</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>PL; PSD; PT; PP</t>
+          <t>PP; NOVO; PL; PSD</t>
         </is>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>ZÉ TROVÃO (PL); ÂNGELA MALUF (PSD)</t>
+          <t>ANY ORTIZ (PP); JESSÉ SANGALLI (PL)</t>
         </is>
       </c>
     </row>
@@ -13483,12 +13483,12 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>27.830.860/0001-09</t>
+          <t>07.046.094/0001-89</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>F PIRES PRODUCOES DE EVENTOS, COMERCIO E SERVICOS LTDA</t>
+          <t>ELYON SOLUCOES GRAFICAS LTDA</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -13498,17 +13498,17 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de produtos diversos não especificados anteriormente</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>BELEM</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -13517,28 +13517,28 @@
         </is>
       </c>
       <c r="I74" s="5" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>2974854</v>
+        <v>2974896.09</v>
       </c>
       <c r="K74" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L74" s="6" t="n">
-        <v>2974854</v>
+        <v>1534769.67</v>
       </c>
       <c r="M74" s="6" t="n">
-        <v>100</v>
+        <v>51.59</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL; PSD; PT; PP</t>
         </is>
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>DELEGADO FEDERAL EGUCHI (REPUBLICANOS); WR DO TAPAJÓS (REPUBLICANOS)</t>
+          <t>ZÉ TROVÃO (PL); ÂNGELA MALUF (PSD)</t>
         </is>
       </c>
     </row>
@@ -13548,12 +13548,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>05.677.050/0001-21</t>
+          <t>27.830.860/0001-09</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>ANS IMPRESSOES GRAFICAS LTDA.</t>
+          <t>F PIRES PRODUCOES DE EVENTOS, COMERCIO E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -13563,17 +13563,17 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
+          <t>Fabricação de produtos diversos não especificados anteriormente</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>BELEM</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -13582,28 +13582,28 @@
         </is>
       </c>
       <c r="I75" s="5" t="n">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>2973690.65</v>
+        <v>2974854</v>
       </c>
       <c r="K75" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L75" s="6" t="n">
-        <v>2313704.49</v>
+        <v>2974854</v>
       </c>
       <c r="M75" s="6" t="n">
-        <v>77.81</v>
+        <v>100</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>PP; NOVO; PL; PSD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>ANY ORTIZ (PP); JESSÉ SANGALLI (PL)</t>
+          <t>DELEGADO FEDERAL EGUCHI (REPUBLICANOS); WR DO TAPAJÓS (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -13678,12 +13678,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>00.212.872/0001-13</t>
+          <t>47.461.986/0001-60</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>ASA SUL INDUSTRIA E COMERCIO DE MALHAS LTDA</t>
+          <t>BLUEGRAF EDITORA LTDA</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -13693,17 +13693,17 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Confecção de peças do vestuário, exceto roupas íntimas</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>FORTALEZA</t>
+          <t>GUARULHOS</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -13712,28 +13712,28 @@
         </is>
       </c>
       <c r="I77" s="5" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>2908749</v>
+        <v>2952478.38</v>
       </c>
       <c r="K77" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L77" s="6" t="n">
-        <v>2611639</v>
+        <v>2370661.08</v>
       </c>
       <c r="M77" s="6" t="n">
-        <v>89.79000000000001</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>PSB; PT; UNIÃO; PRD</t>
+          <t>PSD; PL; PODE; PP</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>DAYANY DO CAPITÃO (UNIÃO); TAINAH MARINHO (PSB)</t>
+          <t>WALTER IHOSHI (PSD); DRA. SANDRA TADEU (PL)</t>
         </is>
       </c>
     </row>
@@ -13743,12 +13743,12 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>47.461.986/0001-60</t>
+          <t>00.212.872/0001-13</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>BLUEGRAF EDITORA LTDA</t>
+          <t>ASA SUL INDUSTRIA E COMERCIO DE MALHAS LTDA</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -13758,17 +13758,17 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Confecção de peças do vestuário, exceto roupas íntimas</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>GUARULHOS</t>
+          <t>FORTALEZA</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -13777,28 +13777,28 @@
         </is>
       </c>
       <c r="I78" s="5" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>2864078.38</v>
+        <v>2908749</v>
       </c>
       <c r="K78" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L78" s="6" t="n">
-        <v>2168111.08</v>
+        <v>2611639</v>
       </c>
       <c r="M78" s="6" t="n">
-        <v>75.7</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>PSD; PL; PP; PODE</t>
+          <t>PSB; PT; UNIÃO; PRD</t>
         </is>
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>WALTER IHOSHI (PSD); DRA. SANDRA TADEU (PL)</t>
+          <t>DAYANY DO CAPITÃO (UNIÃO); TAINAH MARINHO (PSB)</t>
         </is>
       </c>
     </row>
@@ -13808,12 +13808,12 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>56.019.930/0001-41</t>
+          <t>09.521.937/0001-87</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>INOVE IMPRESSOES GRAFICAS E MARKETING POLITICO LTDA</t>
+          <t>ECOPRINT SERVICOS GRAFICOS LTDA</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -13828,12 +13828,12 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>JUAZEIRO DO NORTE</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -13842,28 +13842,28 @@
         </is>
       </c>
       <c r="I79" s="5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>2802399.41</v>
+        <v>2893829.38</v>
       </c>
       <c r="K79" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L79" s="6" t="n">
-        <v>1860497.53</v>
+        <v>2803418.38</v>
       </c>
       <c r="M79" s="6" t="n">
-        <v>66.39</v>
+        <v>96.88</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>PL; PSB; UNIÃO; REPUBLICANOS</t>
+          <t>MDB; CIDADANIA; PSD; UNIÃO</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>VINICIUS DINIZ (PL); BERNARDO ROSSI (UNIÃO)</t>
+          <t>YURY DO PAREDÃO (MDB); SANDRINHA CAVALCANTE (CIDADANIA)</t>
         </is>
       </c>
     </row>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>09.521.937/0001-87</t>
+          <t>56.019.930/0001-41</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>ECOPRINT SERVICOS GRAFICOS LTDA</t>
+          <t>INOVE IMPRESSOES GRAFICAS E MARKETING POLITICO LTDA</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -13893,12 +13893,12 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>JUAZEIRO DO NORTE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -13907,28 +13907,28 @@
         </is>
       </c>
       <c r="I80" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>2800704.38</v>
+        <v>2803233.41</v>
       </c>
       <c r="K80" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L80" s="6" t="n">
-        <v>2710293.38</v>
+        <v>1861331.53</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>96.77</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>MDB; CIDADANIA; PSD; UNIÃO</t>
+          <t>PL; PSB; UNIÃO; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>YURY DO PAREDÃO (MDB); SANDRINHA CAVALCANTE (CIDADANIA)</t>
+          <t>VINICIUS DINIZ (PL); BERNARDO ROSSI (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -14523,12 +14523,12 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>64.752.158/0001-09</t>
+          <t>67.820.413/0001-93</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>OKAN COMUNICACAO LTDA</t>
+          <t>LGS SERVICOS LTDA</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -14538,17 +14538,17 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -14557,28 +14557,28 @@
         </is>
       </c>
       <c r="I90" s="5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>2567000</v>
+        <v>2568850</v>
       </c>
       <c r="K90" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L90" s="6" t="n">
-        <v>2517000</v>
+        <v>2259050</v>
       </c>
       <c r="M90" s="6" t="n">
-        <v>98.05</v>
+        <v>87.94</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>PT; PSOL; UNIÃO</t>
+          <t>PSD; REPUBLICANOS; UNIÃO; PL</t>
         </is>
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>PATRUS ANANIAS (PT); DUDA SALABERT (PSOL)</t>
+          <t>CAPITÃO SAMUEL (UNIÃO); GRACINHA GARCEZ (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -14588,12 +14588,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>17.340.447/0001-02</t>
+          <t>64.752.158/0001-09</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>MARICLEYDSON COSTA DA SILVA  LTDA</t>
+          <t>OKAN COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -14603,17 +14603,17 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>NATAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -14622,28 +14622,28 @@
         </is>
       </c>
       <c r="I91" s="5" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>2559953</v>
+        <v>2567000</v>
       </c>
       <c r="K91" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L91" s="6" t="n">
-        <v>1786590.5</v>
+        <v>2517000</v>
       </c>
       <c r="M91" s="6" t="n">
-        <v>69.79000000000001</v>
+        <v>98.05</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>PL; PT; PV; PDT</t>
+          <t>PT; PSOL; UNIÃO</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>NINA (PL); LUÍZ EDUARDO (PL)</t>
+          <t>PATRUS ANANIAS (PT); DUDA SALABERT (PSOL)</t>
         </is>
       </c>
     </row>
@@ -14653,12 +14653,12 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>26.983.273/0001-97</t>
+          <t>17.340.447/0001-02</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>VITORINO   MENDONCA LTDA</t>
+          <t>MARICLEYDSON COSTA DA SILVA  LTDA</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -14668,17 +14668,17 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>NATAL</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -14687,28 +14687,28 @@
         </is>
       </c>
       <c r="I92" s="5" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>2550000</v>
+        <v>2559953</v>
       </c>
       <c r="K92" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L92" s="6" t="n">
-        <v>1950000</v>
+        <v>1786590.5</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>76.47</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PL; PT; PV; PDT</t>
         </is>
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>WILDER MORAIS (PL); MARCOS ROGÉRIO (PL)</t>
+          <t>NINA (PL); LUÍZ EDUARDO (PL)</t>
         </is>
       </c>
     </row>
@@ -14718,12 +14718,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>67.820.413/0001-93</t>
+          <t>26.983.273/0001-97</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>LGS SERVICOS LTDA</t>
+          <t>VITORINO   MENDONCA LTDA</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -14733,17 +14733,17 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -14752,28 +14752,28 @@
         </is>
       </c>
       <c r="I93" s="5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>2544850</v>
+        <v>2550000</v>
       </c>
       <c r="K93" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L93" s="6" t="n">
-        <v>2259050</v>
+        <v>1950000</v>
       </c>
       <c r="M93" s="6" t="n">
-        <v>88.77</v>
+        <v>76.47</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>PSD; REPUBLICANOS; UNIÃO; PL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>CAPITÃO SAMUEL (UNIÃO); GRACINHA GARCEZ (REPUBLICANOS)</t>
+          <t>WILDER MORAIS (PL); MARCOS ROGÉRIO (PL)</t>
         </is>
       </c>
     </row>
@@ -15495,14 +15495,14 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-10.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
         </is>
       </c>
     </row>
@@ -15543,7 +15543,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="33" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -15632,7 +15632,7 @@
         <v>970908352.83</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>14.81</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="6">
@@ -15658,10 +15658,10 @@
         <v>971</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>597136752.99</v>
+        <v>597661752.99</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>9.109999999999999</v>
@@ -15719,16 +15719,16 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>486777337.61</v>
+        <v>486877337.61</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>7.43</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="9">
@@ -15786,13 +15786,13 @@
         <v>1035</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>402799251.3</v>
+        <v>402749251.3</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>6.15</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="11">
@@ -15850,10 +15850,10 @@
         <v>841</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>233428027.03</v>
+        <v>233478027.03</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>3.56</v>
@@ -16010,13 +16010,13 @@
         <v>866</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>89450574.70999999</v>
+        <v>89588574.70999999</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="18">
@@ -16042,10 +16042,10 @@
         <v>538</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>80928165.18000001</v>
+        <v>80943165.18000001</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>1.23</v>
@@ -16074,10 +16074,10 @@
         <v>339</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>66421322.27</v>
+        <v>66436322.27</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>1.01</v>
@@ -16263,13 +16263,13 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>27449524.67</v>
+        <v>27459524.67</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>0.42</v>
@@ -16359,13 +16359,13 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>2444</v>
+        <v>2454</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>16126405.12</v>
+        <v>16154251.98</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0.25</v>
@@ -16458,10 +16458,10 @@
         <v>98</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>10728909.15</v>
+        <v>10733909.15</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>0.16</v>
@@ -16624,7 +16624,7 @@
         <v>6887480.7</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="37">
@@ -16650,10 +16650,10 @@
         <v>32</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>6686453.55</v>
+        <v>6698838.55</v>
       </c>
       <c r="H37" s="6" t="n">
         <v>0.1</v>
@@ -16746,10 +16746,10 @@
         <v>59</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>6056127.43</v>
+        <v>6069127.43</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>0.09</v>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE-RIO DE JANEIRO-RJ-ESTADUAL</t>
+          <t>REPUBLICANOS RIO GRANDE DO SUL - RS - ESTADUAL</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -16867,17 +16867,17 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>46</v>
+        <v>256</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>5361550</v>
+        <v>5361904</v>
       </c>
       <c r="H44" s="6" t="n">
         <v>0.08</v>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS RIO GRANDE DO SUL - RS - ESTADUAL</t>
+          <t>SOLIDARIEDADE-RIO DE JANEIRO-RJ-ESTADUAL</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -16899,17 +16899,17 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>5350684</v>
+        <v>5361550</v>
       </c>
       <c r="H45" s="6" t="n">
         <v>0.08</v>
@@ -17095,13 +17095,13 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>5023297.06</v>
+        <v>5025435.02</v>
       </c>
       <c r="H51" s="6" t="n">
         <v>0.08</v>
@@ -17206,14 +17206,14 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-10.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
         </is>
       </c>
     </row>
@@ -17313,10 +17313,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>939338671.25</v>
+        <v>940060770.7</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>12.93</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="6">
@@ -17336,10 +17336,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>771349229.63</v>
+        <v>772962838.47</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>10.61</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="7">
@@ -17359,10 +17359,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>538365356.08</v>
+        <v>538525118.08</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>7.41</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="8">
@@ -17382,7 +17382,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>500975044.6</v>
+        <v>501106811.34</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>6.89</v>
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>347379154.28</v>
+        <v>347986863.58</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>4.78</v>
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>346218803.68</v>
+        <v>346492424.23</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.76</v>
@@ -17451,10 +17451,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>319429268.6</v>
+        <v>319520408.32</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="12">
@@ -17474,7 +17474,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>260376041.15</v>
+        <v>260456309.01</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>3.58</v>
@@ -17497,10 +17497,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>248129335.7</v>
+        <v>248537140.7</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="14">
@@ -17520,7 +17520,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>231968669.42</v>
+        <v>232263101.77</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>3.19</v>
@@ -17543,7 +17543,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>223427397.48</v>
+        <v>223564597.48</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>3.07</v>
@@ -17566,7 +17566,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>215953205.16</v>
+        <v>216342827.56</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>2.97</v>
@@ -17589,7 +17589,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>206561665.78</v>
+        <v>206637988.78</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>2.84</v>
@@ -17612,7 +17612,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>191413183.8</v>
+        <v>191486245.93</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>2.63</v>
@@ -17635,7 +17635,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>189081171.59</v>
+        <v>189101995.69</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>2.6</v>
@@ -17658,7 +17658,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>176143006.2</v>
+        <v>176329731.25</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>2.42</v>
@@ -17681,10 +17681,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>162298081</v>
+        <v>162669914.67</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="22">
@@ -17704,7 +17704,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>149380915.19</v>
+        <v>149546550.28</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>2.06</v>
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>146357084.1</v>
+        <v>146374557.1</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>2.01</v>
@@ -17750,7 +17750,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>145250642.75</v>
+        <v>145326561.75</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>2</v>
@@ -17773,7 +17773,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>134640502.61</v>
+        <v>134802502.61</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>1.85</v>
@@ -17796,10 +17796,10 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>125207710.92</v>
+        <v>127266043.44</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="27">
@@ -17819,7 +17819,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>122885231.77</v>
+        <v>123124375.75</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>1.69</v>
@@ -17842,7 +17842,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>118738334.43</v>
+        <v>118839693.01</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>1.63</v>
@@ -17865,10 +17865,10 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>118100015.06</v>
+        <v>118101205.06</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="30">
@@ -17888,7 +17888,7 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>116112117.63</v>
+        <v>116218732.63</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>1.6</v>
@@ -17911,7 +17911,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>116027014.96</v>
+        <v>116096217.41</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>1.6</v>
@@ -17960,7 +17960,7 @@
         <v>148115915.91</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>23.89</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="34">
@@ -17983,7 +17983,7 @@
         <v>63540943.62</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="35">
@@ -18026,7 +18026,7 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>31641290.85</v>
+        <v>31656290.85</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>5.1</v>
@@ -18049,7 +18049,7 @@
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>30492838.61</v>
+        <v>30505223.61</v>
       </c>
       <c r="E37" s="12" t="n">
         <v>4.92</v>
@@ -18072,7 +18072,7 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>27973665.98</v>
+        <v>27968964.14</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>4.51</v>
@@ -18095,10 +18095,10 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>21923959.19</v>
+        <v>22089689.69</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="40">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>18058068.75</v>
+        <v>18066288.75</v>
       </c>
       <c r="E41" s="12" t="n">
         <v>2.91</v>
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>17621238</v>
+        <v>17640588</v>
       </c>
       <c r="E43" s="12" t="n">
         <v>2.84</v>
@@ -18259,7 +18259,7 @@
         <v>15904796.74</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="47">
@@ -18302,7 +18302,7 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>12937118.35</v>
+        <v>12942292.35</v>
       </c>
       <c r="E48" s="12" t="n">
         <v>2.09</v>
@@ -18325,7 +18325,7 @@
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>12561352.75</v>
+        <v>12561528.57</v>
       </c>
       <c r="E49" s="12" t="n">
         <v>2.03</v>
@@ -18417,7 +18417,7 @@
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>10240268.05</v>
+        <v>10241492.54</v>
       </c>
       <c r="E53" s="12" t="n">
         <v>1.65</v>
@@ -18512,7 +18512,7 @@
         <v>7286528.8</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="58">
@@ -18627,7 +18627,7 @@
         <v>613298902.3</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>11.33</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="63">
@@ -18647,7 +18647,7 @@
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>412090448.93</v>
+        <v>412113586.89</v>
       </c>
       <c r="E63" s="12" t="n">
         <v>7.61</v>
@@ -18670,7 +18670,7 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>375418971.54</v>
+        <v>375428030.54</v>
       </c>
       <c r="E64" s="12" t="n">
         <v>6.93</v>
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>151165278.8</v>
+        <v>151175278.8</v>
       </c>
       <c r="E73" s="12" t="n">
         <v>2.79</v>
@@ -18926,7 +18926,7 @@
         <v>134561947.2</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="76">
@@ -18946,7 +18946,7 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>127568682.47</v>
+        <v>127618682.47</v>
       </c>
       <c r="E76" s="12" t="n">
         <v>2.36</v>
@@ -18969,7 +18969,7 @@
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>122116962.45</v>
+        <v>122216962.45</v>
       </c>
       <c r="E77" s="12" t="n">
         <v>2.26</v>
@@ -18995,7 +18995,7 @@
         <v>108586825.06</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -19006,19 +19006,19 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Rio Grande do Norte</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>105817480.74</v>
+        <v>106528005.98</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="80">
@@ -19029,19 +19029,19 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Norte</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>104528005.98</v>
+        <v>105817480.74</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="81">
@@ -19110,7 +19110,7 @@
         <v>96676722.64</v>
       </c>
       <c r="E83" s="12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="84">
@@ -19245,10 +19245,10 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>813090411.73</v>
+        <v>816318310.92</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>25.93</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="90">
@@ -19268,7 +19268,7 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>202649614.23</v>
+        <v>203082907.12</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>6.46</v>
@@ -19291,10 +19291,10 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>187081607.76</v>
+        <v>187133628.35</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>5.97</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="92">
@@ -19314,10 +19314,10 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>156126271.54</v>
+        <v>156134142.47</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="93">
@@ -19337,10 +19337,10 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>140791110.53</v>
+        <v>140946146.11</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="94">
@@ -19360,10 +19360,10 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>127389138.11</v>
+        <v>128997084.29</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="95">
@@ -19383,10 +19383,10 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>125554964.15</v>
+        <v>126475422.23</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>4</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="96">
@@ -19406,10 +19406,10 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>118335391.18</v>
+        <v>118392416.57</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="97">
@@ -19429,10 +19429,10 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>107646906.79</v>
+        <v>108193086.12</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="98">
@@ -19452,10 +19452,10 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>106913616.42</v>
+        <v>106916431.42</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="99">
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>95897130.05</v>
+        <v>95979166.05</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="100">
@@ -19521,7 +19521,7 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>86297942.41</v>
+        <v>86394050.63</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>2.75</v>
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>85047202.04000001</v>
+        <v>85232387.48</v>
       </c>
       <c r="E102" s="12" t="n">
         <v>2.71</v>
@@ -19567,7 +19567,7 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>75689308.69</v>
+        <v>75729443.69</v>
       </c>
       <c r="E103" s="12" t="n">
         <v>2.41</v>
@@ -19590,10 +19590,10 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>73402827.20999999</v>
+        <v>73414734.05</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="105">
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>70285937.69</v>
+        <v>70390028.23999999</v>
       </c>
       <c r="E105" s="12" t="n">
         <v>2.24</v>
@@ -19636,10 +19636,10 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>59893631.04</v>
+        <v>60440709.12</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="107">
@@ -19659,10 +19659,10 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>56952749.44</v>
+        <v>57046236.94</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="108">
@@ -19682,10 +19682,10 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>53853911.16</v>
+        <v>53853536.66</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="109">
@@ -19705,7 +19705,7 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>53039866.14</v>
+        <v>53115098.14</v>
       </c>
       <c r="E109" s="12" t="n">
         <v>1.69</v>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>51578551.85</v>
+        <v>51728551.85</v>
       </c>
       <c r="E110" s="12" t="n">
         <v>1.64</v>
@@ -19751,7 +19751,7 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>48052060.9</v>
+        <v>48079007.1</v>
       </c>
       <c r="E111" s="12" t="n">
         <v>1.53</v>
@@ -19774,7 +19774,7 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>47532159.74</v>
+        <v>47674109.74</v>
       </c>
       <c r="E112" s="12" t="n">
         <v>1.52</v>
@@ -19820,7 +19820,7 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>31650703.29</v>
+        <v>31677684.79</v>
       </c>
       <c r="E114" s="12" t="n">
         <v>1.01</v>
@@ -19843,7 +19843,7 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>28244603.28</v>
+        <v>28288903.28</v>
       </c>
       <c r="E115" s="12" t="n">
         <v>0.9</v>
@@ -19912,10 +19912,10 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>147002888.78</v>
+        <v>147229523.42</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>20.17</v>
+        <v>20.14</v>
       </c>
     </row>
     <row r="119">
@@ -19935,10 +19935,10 @@
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>56955026.5</v>
+        <v>57043535.5</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>7.81</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="120">
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>51718192.7</v>
+        <v>51763069.59</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="121">
@@ -19981,10 +19981,10 @@
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>50589364.92</v>
+        <v>50648871.92</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>6.94</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="122">
@@ -20004,10 +20004,10 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>34389925.84</v>
+        <v>34586869.84</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>4.72</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="123">
@@ -20027,10 +20027,10 @@
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>33431880.5</v>
+        <v>33434380.5</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="124">
@@ -20050,10 +20050,10 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>31262494.03</v>
+        <v>31275109.75</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="125">
@@ -20073,10 +20073,10 @@
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>27724996.41</v>
+        <v>28099168.81</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="126">
@@ -20096,10 +20096,10 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>22545918.67</v>
+        <v>22849747.97</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="127">
@@ -20119,7 +20119,7 @@
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>22447589.55</v>
+        <v>22514974.55</v>
       </c>
       <c r="E127" s="12" t="n">
         <v>3.08</v>
@@ -20142,10 +20142,10 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>22051482.13</v>
+        <v>22066485.13</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="129">
@@ -20165,7 +20165,7 @@
         </is>
       </c>
       <c r="D129" s="6" t="n">
-        <v>21814220.38</v>
+        <v>21848220.38</v>
       </c>
       <c r="E129" s="12" t="n">
         <v>2.99</v>
@@ -20188,7 +20188,7 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>21696151.02</v>
+        <v>21788261.07</v>
       </c>
       <c r="E130" s="12" t="n">
         <v>2.98</v>
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>20234031.94</v>
+        <v>20292390.52</v>
       </c>
       <c r="E131" s="12" t="n">
         <v>2.78</v>
@@ -20234,7 +20234,7 @@
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>19684655.8</v>
+        <v>19744610.73</v>
       </c>
       <c r="E132" s="12" t="n">
         <v>2.7</v>
@@ -20257,10 +20257,10 @@
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>16519336.37</v>
+        <v>16520526.37</v>
       </c>
       <c r="E133" s="12" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="134">
@@ -20280,7 +20280,7 @@
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>16213524.15</v>
+        <v>16253407.69</v>
       </c>
       <c r="E134" s="12" t="n">
         <v>2.22</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>14887752.97</v>
+        <v>14900852.97</v>
       </c>
       <c r="E136" s="12" t="n">
         <v>2.04</v>
@@ -20349,10 +20349,10 @@
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>14426864.27</v>
+        <v>14584669.27</v>
       </c>
       <c r="E137" s="12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -20372,7 +20372,7 @@
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>13575270.18</v>
+        <v>13629021.7</v>
       </c>
       <c r="E138" s="12" t="n">
         <v>1.86</v>
@@ -20441,10 +20441,10 @@
         </is>
       </c>
       <c r="D141" s="6" t="n">
-        <v>9045155.07</v>
+        <v>9175658.73</v>
       </c>
       <c r="E141" s="12" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="142">
@@ -20487,10 +20487,10 @@
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>8355367.64</v>
+        <v>8356982.64</v>
       </c>
       <c r="E143" s="12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="144">
@@ -20513,7 +20513,7 @@
         <v>7776947.8</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="145">
@@ -20533,10 +20533,10 @@
         </is>
       </c>
       <c r="D145" s="6" t="n">
-        <v>96577263.26000001</v>
+        <v>97077728.06999999</v>
       </c>
       <c r="E145" s="12" t="n">
-        <v>13.82</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="146">
@@ -20556,10 +20556,10 @@
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>79531300.44</v>
+        <v>79581868.44</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>11.38</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="147">
@@ -20579,10 +20579,10 @@
         </is>
       </c>
       <c r="D147" s="6" t="n">
-        <v>48942505.72</v>
+        <v>50428829.56</v>
       </c>
       <c r="E147" s="12" t="n">
-        <v>7</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="148">
@@ -20602,10 +20602,10 @@
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>38347699.08</v>
+        <v>38717032.75</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>5.49</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="149">
@@ -20625,10 +20625,10 @@
         </is>
       </c>
       <c r="D149" s="6" t="n">
-        <v>38085709.47</v>
+        <v>38155289.32</v>
       </c>
       <c r="E149" s="12" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="150">
@@ -20648,7 +20648,7 @@
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>36649690.99</v>
+        <v>36899690.99</v>
       </c>
       <c r="E150" s="12" t="n">
         <v>5.25</v>
@@ -20671,10 +20671,10 @@
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>34900719.44</v>
+        <v>35025492.79</v>
       </c>
       <c r="E151" s="12" t="n">
-        <v>4.99</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="152">
@@ -20694,7 +20694,7 @@
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>34253029.36</v>
+        <v>34424142.91</v>
       </c>
       <c r="E152" s="12" t="n">
         <v>4.9</v>
@@ -20717,10 +20717,10 @@
         </is>
       </c>
       <c r="D153" s="6" t="n">
-        <v>26980128.92</v>
+        <v>26995578.92</v>
       </c>
       <c r="E153" s="12" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="154">
@@ -20740,10 +20740,10 @@
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>26892819.96</v>
+        <v>26957619.96</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="155">
@@ -20763,10 +20763,10 @@
         </is>
       </c>
       <c r="D155" s="6" t="n">
-        <v>24947163.01</v>
+        <v>24956101.01</v>
       </c>
       <c r="E155" s="12" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="156">
@@ -20786,10 +20786,10 @@
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>24004345.4</v>
+        <v>24308225.4</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="157">
@@ -20809,10 +20809,10 @@
         </is>
       </c>
       <c r="D157" s="6" t="n">
-        <v>21988797.89</v>
+        <v>22003170.89</v>
       </c>
       <c r="E157" s="12" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="158">
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="D158" s="6" t="n">
-        <v>20971384.05</v>
+        <v>21074584.05</v>
       </c>
       <c r="E158" s="12" t="n">
         <v>3</v>
@@ -20855,10 +20855,10 @@
         </is>
       </c>
       <c r="D159" s="6" t="n">
-        <v>20297773.72</v>
+        <v>20329773.72</v>
       </c>
       <c r="E159" s="12" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="160">
@@ -20878,10 +20878,10 @@
         </is>
       </c>
       <c r="D160" s="6" t="n">
-        <v>17162884.26</v>
+        <v>17196062.85</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="161">
@@ -20901,10 +20901,10 @@
         </is>
       </c>
       <c r="D161" s="6" t="n">
-        <v>16131563.09</v>
+        <v>16200863.09</v>
       </c>
       <c r="E161" s="12" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="162">
@@ -20924,7 +20924,7 @@
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>15534495.24</v>
+        <v>15610414.24</v>
       </c>
       <c r="E162" s="12" t="n">
         <v>2.22</v>
@@ -20947,10 +20947,10 @@
         </is>
       </c>
       <c r="D163" s="6" t="n">
-        <v>12871359.65</v>
+        <v>12882183.75</v>
       </c>
       <c r="E163" s="12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="164">
@@ -20970,7 +20970,7 @@
         </is>
       </c>
       <c r="D164" s="6" t="n">
-        <v>9850626.949999999</v>
+        <v>9893626.949999999</v>
       </c>
       <c r="E164" s="12" t="n">
         <v>1.41</v>
@@ -20993,10 +20993,10 @@
         </is>
       </c>
       <c r="D165" s="6" t="n">
-        <v>9785131.77</v>
+        <v>9885362.09</v>
       </c>
       <c r="E165" s="12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="166">
@@ -21019,7 +21019,7 @@
         <v>9684341.75</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="167">
@@ -21039,7 +21039,7 @@
         </is>
       </c>
       <c r="D167" s="6" t="n">
-        <v>7656226.69</v>
+        <v>7711906.85</v>
       </c>
       <c r="E167" s="12" t="n">
         <v>1.1</v>
@@ -21062,10 +21062,10 @@
         </is>
       </c>
       <c r="D168" s="6" t="n">
-        <v>7358089.05</v>
+        <v>7463089.05</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="169">
@@ -21085,7 +21085,7 @@
         </is>
       </c>
       <c r="D169" s="6" t="n">
-        <v>6396511.16</v>
+        <v>6454843.68</v>
       </c>
       <c r="E169" s="12" t="n">
         <v>0.92</v>
@@ -21108,10 +21108,10 @@
         </is>
       </c>
       <c r="D170" s="6" t="n">
-        <v>4954292.25</v>
+        <v>5116292.25</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="171">
@@ -21131,7 +21131,7 @@
         </is>
       </c>
       <c r="D171" s="6" t="n">
-        <v>4043661.51</v>
+        <v>4059112.44</v>
       </c>
       <c r="E171" s="12" t="n">
         <v>0.58</v>
@@ -22451,14 +22451,14 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-10.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
         </is>
       </c>
     </row>
@@ -22572,10 +22572,10 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>381032230.03</v>
+        <v>383292827.03</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>37598056.56</v>
+        <v>37780891.06</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>20334031.37</v>
@@ -22584,16 +22584,16 @@
         <v>6058498.32</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>43656554.88</v>
+        <v>43839389.38</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>18.08</v>
+        <v>17.98</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>401366261.4</v>
+        <v>403626858.4</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>15.75</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="6">
@@ -22603,10 +22603,10 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>526391128.54</v>
+        <v>528206683.06</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>33445152.09</v>
+        <v>34219994.39</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>7837843.22</v>
@@ -22615,16 +22615,16 @@
         <v>9195409.91</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>42640562</v>
+        <v>43415404.3</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>17.66</v>
+        <v>17.81</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>534228971.7600001</v>
+        <v>536044526.28</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>20.97</v>
+        <v>20.94</v>
       </c>
     </row>
     <row r="7">
@@ -22634,10 +22634,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>260291019.63</v>
+        <v>261869160.42</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>27989202.57</v>
+        <v>28186299.49</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>328650</v>
@@ -22646,16 +22646,16 @@
         <v>227830.33</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>28217032.9</v>
+        <v>28414129.82</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>11.69</v>
+        <v>11.65</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>260619669.63</v>
+        <v>262197810.42</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>10.23</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="8">
@@ -22665,10 +22665,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>145945434.03</v>
+        <v>146359834.03</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>5473373.95</v>
+        <v>5572853.95</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>10528907.87</v>
@@ -22677,16 +22677,16 @@
         <v>16191098.24</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>21664472.19</v>
+        <v>21763952.19</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>8.970000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>156474341.9</v>
+        <v>156888741.9</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="9">
@@ -22696,10 +22696,10 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>117466831.71</v>
+        <v>117831324.72</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>9088407.710000001</v>
+        <v>9188407.710000001</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>13436262.57</v>
@@ -22708,16 +22708,16 @@
         <v>9563476.6</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>18651884.31</v>
+        <v>18751884.31</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>7.73</v>
+        <v>7.69</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>130903094.28</v>
+        <v>131267587.29</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="10">
@@ -22727,10 +22727,10 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>231723577.78</v>
+        <v>233461070.58</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>17940766.81</v>
+        <v>18372880.05</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>1061795.06</v>
@@ -22739,16 +22739,16 @@
         <v>310317.66</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>18251084.47</v>
+        <v>18683197.71</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>7.56</v>
+        <v>7.66</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>232785372.84</v>
+        <v>234522865.64</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9.140000000000001</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="11">
@@ -22758,10 +22758,10 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>223249210.95</v>
+        <v>224613152.32</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>15698794.12</v>
+        <v>15952595.59</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>1405640</v>
@@ -22770,16 +22770,16 @@
         <v>529244.16</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>16228038.28</v>
+        <v>16481839.75</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>6.72</v>
+        <v>6.76</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>224654850.95</v>
+        <v>226018792.32</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>8.82</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="12">
@@ -22789,10 +22789,10 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>158093646.93</v>
+        <v>158312348.46</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>7016958.47</v>
+        <v>7062759.54</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>2161173.45</v>
@@ -22801,16 +22801,16 @@
         <v>2248827.43</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>9265785.9</v>
+        <v>9311586.970000001</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>160254820.38</v>
+        <v>160473521.91</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>6.29</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="13">
@@ -22820,10 +22820,10 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>65737361.39</v>
+        <v>65990761.39</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>3692114.24</v>
+        <v>3754114.24</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>12290674.22</v>
@@ -22832,13 +22832,13 @@
         <v>5493512.35</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>9185626.59</v>
+        <v>9247626.59</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>78028035.61</v>
+        <v>78281435.61</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>3.06</v>
@@ -22851,10 +22851,10 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>54040498.71</v>
+        <v>54264820.71</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2441601.64</v>
+        <v>2443966.12</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>752452.6</v>
@@ -22863,13 +22863,13 @@
         <v>3473642.61</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>5915244.25</v>
+        <v>5917608.73</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>54792951.31</v>
+        <v>55017273.31</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>2.15</v>
@@ -22882,10 +22882,10 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>82673714.38</v>
+        <v>83210006.84</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>4060575.49</v>
+        <v>4082123.36</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>53190</v>
@@ -22894,13 +22894,13 @@
         <v>1023161.61</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>5083737.100000001</v>
+        <v>5105284.97</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>82726904.38</v>
+        <v>83263196.84</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>3.25</v>
@@ -22913,10 +22913,10 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>27358484.84</v>
+        <v>27411392.78</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2956693.1</v>
+        <v>2957464.91</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>435855.87</v>
@@ -22925,13 +22925,13 @@
         <v>1598966.95</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>4555660.05</v>
+        <v>4556431.86</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>27794340.71</v>
+        <v>27847248.65</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>1.09</v>
@@ -22944,10 +22944,10 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>37947583.43</v>
+        <v>38052916.43</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>2772983.78</v>
+        <v>2777983.78</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>214985.86</v>
@@ -22956,16 +22956,16 @@
         <v>665907.63</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>3438891.41</v>
+        <v>3443891.41</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>38162569.29</v>
+        <v>38267902.29</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="18">
@@ -22975,7 +22975,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>14039831.4</v>
+        <v>14104831.4</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>663200</v>
@@ -22990,10 +22990,10 @@
         <v>2697521</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>15005247.9</v>
+        <v>15070247.9</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0.59</v>
@@ -23006,10 +23006,10 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>27041642.39</v>
+        <v>27205571.94</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>1787180.84</v>
+        <v>1788536.92</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>25327.5</v>
@@ -23018,13 +23018,13 @@
         <v>282176.1</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2069356.94</v>
+        <v>2070713.02</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>27066969.89</v>
+        <v>27230899.44</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>1.06</v>
@@ -23037,7 +23037,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>20343342.44</v>
+        <v>20348342.44</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>1007228.09</v>
@@ -23055,7 +23055,7 @@
         <v>0.64</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>20470862.44</v>
+        <v>20475862.44</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0.8</v>
@@ -23068,10 +23068,10 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>11648523.23</v>
+        <v>11896623.23</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>1232627.11</v>
+        <v>1235627.11</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>113916.98</v>
@@ -23080,16 +23080,16 @@
         <v>199564.49</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1432191.6</v>
+        <v>1435191.6</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>0.59</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>11762440.21</v>
+        <v>12010540.21</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="22">
@@ -23099,10 +23099,10 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>10571247.7</v>
+        <v>10592047.7</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1160211.39</v>
+        <v>1162211.39</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>206000</v>
@@ -23111,13 +23111,13 @@
         <v>120500</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1280711.39</v>
+        <v>1282711.39</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0.53</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>10777247.7</v>
+        <v>10798047.7</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0.42</v>
@@ -23130,10 +23130,10 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>14372345.98</v>
+        <v>14536316.03</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>856887.63</v>
+        <v>858287.63</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>933850</v>
@@ -23142,13 +23142,13 @@
         <v>110000</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>966887.63</v>
+        <v>968287.63</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>15306195.98</v>
+        <v>15470166.03</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0.6</v>
@@ -23161,10 +23161,10 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>13818251.41</v>
+        <v>13824801.41</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>945989.42</v>
+        <v>949256.42</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>56000</v>
@@ -23173,13 +23173,13 @@
         <v>18500</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>964489.42</v>
+        <v>967756.42</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>13874251.41</v>
+        <v>13880801.41</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0.54</v>
@@ -23188,63 +23188,63 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Publicidade por jornais e revistas</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>7040621.79</v>
+        <v>6114140.28</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>599428.08</v>
+        <v>727192.3100000001</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>22074.32</v>
+        <v>0</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>116396.95</v>
+        <v>420</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>715825.0299999999</v>
+        <v>727612.3100000001</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>7062696.11</v>
+        <v>6114140.28</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Publicidade por jornais e revistas</t>
+          <t>Alimentação</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>6058090.28</v>
+        <v>7235176.67</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>706155.71</v>
+        <v>600926.35</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0</v>
+        <v>22074.32</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>420</v>
+        <v>116396.95</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>706575.71</v>
+        <v>717323.2999999999</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>0.29</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>6058090.28</v>
+        <v>7257250.99</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="27">
@@ -23254,10 +23254,10 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>14742958.19</v>
+        <v>14749649.59</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>584051.51</v>
+        <v>701750.45</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>8104.55</v>
@@ -23266,13 +23266,13 @@
         <v>0</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>584051.51</v>
+        <v>701750.45</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>14751062.74</v>
+        <v>14757754.14</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0.58</v>
@@ -23285,10 +23285,10 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>8981057.35</v>
+        <v>9012357.35</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>286862.09</v>
+        <v>336862.09</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>0</v>
@@ -23297,13 +23297,13 @@
         <v>151786.7</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>438648.79</v>
+        <v>488648.79</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>8981057.35</v>
+        <v>9012357.35</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0.35</v>
@@ -23316,10 +23316,10 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>2614891.29</v>
+        <v>2621941.64</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>265254.36</v>
+        <v>265835.78</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>9126.799999999999</v>
@@ -23328,13 +23328,13 @@
         <v>99566.78999999999</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>364821.15</v>
+        <v>365402.57</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>0.15</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>2624018.09</v>
+        <v>2631068.44</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0.1</v>
@@ -23347,7 +23347,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>3370203.86</v>
+        <v>3371303.86</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>293667.18</v>
@@ -23365,7 +23365,7 @@
         <v>0.12</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>3370203.86</v>
+        <v>3371303.86</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0.13</v>
@@ -23412,7 +23412,7 @@
         <v>898514.8</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>82456.32000000001</v>
+        <v>85143.31999999999</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>18616.5</v>
@@ -23421,7 +23421,7 @@
         <v>24308.68</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>106765</v>
+        <v>109452</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>0.04</v>
@@ -23440,7 +23440,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>1432635.3</v>
+        <v>1433855.5</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>58367.11</v>
@@ -23458,7 +23458,7 @@
         <v>0.04</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1432635.3</v>
+        <v>1433855.5</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0.06</v>
@@ -23502,10 +23502,10 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>83630.09</v>
+        <v>83701.59</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>1110.6</v>
+        <v>1130.2</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>51744.89</v>
@@ -23514,13 +23514,13 @@
         <v>40426.19</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>41536.79</v>
+        <v>41556.39</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>135374.98</v>
+        <v>135446.48</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0.01</v>
@@ -23529,29 +23529,29 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Aquisição/Doação de bens móveis ou imóveis</t>
+          <t>Encargos financeiros, taxas bancárias e/ou op. cartão de crédito</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>421814.91</v>
+        <v>433974.27</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>20610.5</v>
+        <v>23961.96</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>1548.67</v>
+        <v>99335.53999999999</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>16208.2</v>
+        <v>12986.4</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>36818.7</v>
+        <v>36948.36</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>423363.58</v>
+        <v>533309.8100000001</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0.02</v>
@@ -23560,29 +23560,29 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Encargos financeiros, taxas bancárias e/ou op. cartão de crédito</t>
+          <t>Aquisição/Doação de bens móveis ou imóveis</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>432672.27</v>
+        <v>421914.91</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>23710.24</v>
+        <v>20610.5</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>99333.84</v>
+        <v>1548.67</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>12986.4</v>
+        <v>16208.2</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>36696.64</v>
+        <v>36818.7</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>532006.11</v>
+        <v>423463.58</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0.02</v>
@@ -23616,7 +23616,7 @@
         <v>895769.4</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="39">
@@ -23626,7 +23626,7 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>34545.97</v>
+        <v>36657.91</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>3261.35</v>
@@ -23644,7 +23644,7 @@
         <v>0.01</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>34645.21</v>
+        <v>36757.15</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
@@ -23657,7 +23657,7 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>81372.39999999999</v>
+        <v>82372.39999999999</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>3701.85</v>
@@ -23675,7 +23675,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>81372.39999999999</v>
+        <v>82372.39999999999</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
@@ -23777,14 +23777,14 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-10.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
         </is>
       </c>
     </row>
@@ -23937,16 +23937,16 @@
         <v>5281805806.47</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1405735148.87</v>
+        <v>1407806661.46</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>19.34</v>
+        <v>19.35</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1023721550.1</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>18.91</v>
+        <v>18.9</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>150890397.42</v>
@@ -23955,16 +23955,16 @@
         <v>24.33</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>21851884.12</v>
+        <v>21898287.12</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>137099241.47</v>
+        <v>138846409.06</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>1063651251.09</v>
+        <v>1065119816.62</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>83.56</v>
+        <v>83.44</v>
       </c>
     </row>
     <row r="6">
@@ -23983,16 +23983,16 @@
         <v>788542541.16</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1054100225.91</v>
+        <v>1056556575.52</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>14.51</v>
+        <v>14.52</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>918728039.12</v>
+        <v>920728039.12</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>16.97</v>
+        <v>17</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>6246134.65</v>
@@ -24001,16 +24001,16 @@
         <v>1.01</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>12220887.03</v>
+        <v>12271752.53</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>84399738.52</v>
+        <v>84763399.47</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>701055413.41</v>
+        <v>702414291.62</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>87.75</v>
+        <v>87.73999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -24029,10 +24029,10 @@
         <v>1819943318.34</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>658108511.73</v>
+        <v>658404982.35</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>9.06</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>536542994.33</v>
@@ -24041,22 +24041,22 @@
         <v>9.91</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>65276808.97</v>
+        <v>65426808.97</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>10.53</v>
+        <v>10.55</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>8056189.56</v>
+        <v>8070356.86</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>29340316.97</v>
+        <v>29472620.29</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>472711959.95</v>
+        <v>473050886.85</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>91.45</v>
+        <v>91.43000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -24075,7 +24075,7 @@
         <v>2577905190.84</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>654049334.59</v>
+        <v>654606240.41</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>9</v>
@@ -24084,25 +24084,25 @@
         <v>448626803.71</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>34632737.02</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>5.59</v>
+        <v>5.58</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>18839446.7</v>
+        <v>18973319.52</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>83964607.95999999</v>
+        <v>84251096.95999999</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>511180752.93</v>
+        <v>511381040.23</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>73.89</v>
+        <v>73.81999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -24121,34 +24121,34 @@
         <v>2779509683.8</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>604229188.12</v>
+        <v>604619649.46</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>8.31</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>370429872.29</v>
+        <v>370432010.25</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>6.84</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>126534864</v>
+        <v>126555644.82</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>20.41</v>
+        <v>20.4</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>11619412.8</v>
+        <v>11821936.46</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>63060608.13</v>
+        <v>63188329.1</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>421991948.48</v>
+        <v>424146313.18</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>82.25</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="10">
@@ -24167,34 +24167,34 @@
         <v>1297502449.57</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>576017200.2</v>
+        <v>576451516.6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7.93</v>
+        <v>7.92</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>446416289.17</v>
+        <v>446516289.17</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>8.25</v>
+        <v>8.24</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>74186678.76000001</v>
+        <v>74187903.25</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>11.96</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>7762845.27</v>
+        <v>7924570.21</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>30472319.77</v>
+        <v>30629543.88</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>361063798.43</v>
+        <v>362172406.18</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>90.38</v>
+        <v>90.33</v>
       </c>
     </row>
     <row r="11">
@@ -24213,7 +24213,7 @@
         <v>3431895006.71</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>536133443.18</v>
+        <v>536618527.49</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>7.38</v>
@@ -24225,22 +24225,22 @@
         <v>7.53</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>17628836.54</v>
+        <v>17642692.04</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>2.84</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>14746735.62</v>
+        <v>14952123.45</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>67233741.31999999</v>
+        <v>67491172.3</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>348257738.11</v>
+        <v>349989390.3</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>79.34999999999999</v>
+        <v>79.28</v>
       </c>
     </row>
     <row r="12">
@@ -24259,34 +24259,34 @@
         <v>1812875005.9</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>295199071.52</v>
+        <v>295587133.63</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>4.06</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>237965482.3</v>
+        <v>238015482.3</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5640256.810000001</v>
+        <v>5664780.810000001</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>0.91</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>10104174.22</v>
+        <v>10140250.16</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>31499707.55</v>
+        <v>31714016.89</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>192988893.58</v>
+        <v>193405232.64</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>82.52</v>
+        <v>82.44</v>
       </c>
     </row>
     <row r="13">
@@ -24305,7 +24305,7 @@
         <v>1457794419.27</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>229740786.52</v>
+        <v>230020966.24</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>3.16</v>
@@ -24317,22 +24317,22 @@
         <v>3.08</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>46290560.08</v>
+        <v>46292435.08</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>7.47</v>
+        <v>7.46</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>2903506.06</v>
+        <v>2916910.78</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>9721885.189999999</v>
+        <v>9985785.189999999</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>152451631.27</v>
+        <v>152820074.02</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>92.84</v>
+        <v>92.73</v>
       </c>
     </row>
     <row r="14">
@@ -24351,13 +24351,13 @@
         <v>941728196.61</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>222285982.7</v>
+        <v>222374886.05</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>3.06</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>148455951.38</v>
+        <v>148466010.38</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>2.74</v>
@@ -24369,16 +24369,16 @@
         <v>1.08</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>10856697.35</v>
+        <v>10858802.79</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>36358679.15</v>
+        <v>36386793.06</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>172101765.14</v>
+        <v>172264084.06</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>69.8</v>
+        <v>69.78</v>
       </c>
     </row>
     <row r="15">
@@ -24397,34 +24397,34 @@
         <v>2591694177.84</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>209562747.69</v>
+        <v>209944283.85</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>150291927.09</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>4462718.01</v>
+        <v>4458016.17</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>0.72</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>11717213.43</v>
+        <v>11729771.43</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31000481.43</v>
+        <v>31374161.43</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>143736258.16</v>
+        <v>143783995.4</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>73.84999999999999</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -24443,7 +24443,7 @@
         <v>1884208841.62</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>144146207.42</v>
+        <v>144312158.17</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>1.98</v>
@@ -24461,16 +24461,16 @@
         <v>7.17</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>7309289.36</v>
+        <v>7311250.99</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>27042953.19</v>
+        <v>27058281.31</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>88921572.93000001</v>
+        <v>90111146.33</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>54.7</v>
+        <v>54.64</v>
       </c>
     </row>
     <row r="17">
@@ -24489,7 +24489,7 @@
         <v>139488473.87</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>135333277.13</v>
+        <v>135351846.9</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>1.86</v>
@@ -24510,13 +24510,13 @@
         <v>812961.91</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>4137061.43</v>
+        <v>4141556.34</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>89589545.95999999</v>
+        <v>89664306.39</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>93.02</v>
+        <v>93.01000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -24535,7 +24535,7 @@
         <v>1072776812.99</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>99223308.09</v>
+        <v>99332232.69</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>1.37</v>
@@ -24547,22 +24547,22 @@
         <v>1.21</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>13757331.38</v>
+        <v>13772331.38</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>2.22</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>4900833.439999999</v>
+        <v>4906934.439999999</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>12720745.45</v>
+        <v>12808569.05</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>60457478.08</v>
+        <v>60709426.54</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>79.81999999999999</v>
+        <v>79.75</v>
       </c>
     </row>
     <row r="19">
@@ -24581,7 +24581,7 @@
         <v>577531754.64</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>97410430.53</v>
+        <v>97416169.03</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>1.34</v>
@@ -24599,13 +24599,13 @@
         <v>2.28</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>3349975.82</v>
+        <v>3349976.32</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>9198319.119999999</v>
+        <v>9204057.119999999</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>60863863.71</v>
+        <v>60944962.21</v>
       </c>
       <c r="N19" s="6" t="n">
         <v>83.90000000000001</v>
@@ -24627,13 +24627,13 @@
         <v>280452197.14</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>91990371.72</v>
+        <v>92007573.06999999</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>83779222.27</v>
+        <v>83794222.27</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>1.55</v>
@@ -24645,13 +24645,13 @@
         <v>0.26</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>1868672.42</v>
+        <v>1868672.92</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>3836443.11</v>
+        <v>3837143.96</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>52401582.96</v>
+        <v>52487646.85</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>92.84999999999999</v>
@@ -24673,7 +24673,7 @@
         <v>81485614.53</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>73253797.78</v>
+        <v>73470992.78</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>1.01</v>
@@ -24682,7 +24682,7 @@
         <v>60379791.05</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>4467405.01</v>
@@ -24691,16 +24691,16 @@
         <v>0.72</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>1269389.67</v>
+        <v>1309270.67</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>3954422.41</v>
+        <v>4039422.41</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>49446135.61</v>
+        <v>49463845.77</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>88.52</v>
+        <v>88.26000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -24719,7 +24719,7 @@
         <v>330099422.77</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>60125324.04</v>
+        <v>60262921.48</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>0.83</v>
@@ -24737,16 +24737,16 @@
         <v>0.03</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>3403743.36</v>
+        <v>3471243.36</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>10997477.67</v>
+        <v>11067575.11</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>43902490.06</v>
+        <v>43906560.06</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>72.02</v>
+        <v>71.84999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -24765,7 +24765,7 @@
         <v>121249861.96</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>36357738.48</v>
+        <v>36374038.48</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>0.5</v>
@@ -24786,13 +24786,13 @@
         <v>564325.3300000001</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>1040369.75</v>
+        <v>1056669.75</v>
       </c>
       <c r="M23" s="6" t="n">
         <v>11155393.72</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>93</v>
+        <v>92.95</v>
       </c>
     </row>
     <row r="24">
@@ -24811,13 +24811,13 @@
         <v>587079065.02</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>33874373.27</v>
+        <v>33939373.27</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>0.47</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>29543402.63</v>
+        <v>29553402.63</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0.55</v>
@@ -24829,16 +24829,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>510283.86</v>
+        <v>540283.86</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>2571259.84</v>
+        <v>2596259.84</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>19785689.57</v>
+        <v>19795689.57</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>88.43000000000001</v>
+        <v>88.29000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -24857,7 +24857,7 @@
         <v>286783798.5</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>12041379.96</v>
+        <v>12071919.96</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>0.17</v>
@@ -24875,16 +24875,16 @@
         <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>2037988.63</v>
+        <v>2040988.63</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>7430606.99</v>
+        <v>7458146.99</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>7580288.87</v>
+        <v>7596728.87</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>18.56</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="26">
@@ -24903,13 +24903,13 @@
         <v>243522021.57</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>10108415.41</v>
+        <v>10117106.01</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>0.14</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>2318000</v>
+        <v>2323000</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>0.04</v>
@@ -24924,13 +24924,13 @@
         <v>1835634.88</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>5494705.97</v>
+        <v>5498396.57</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>8228688.61</v>
+        <v>8287319.060000001</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>23.03</v>
+        <v>23.06</v>
       </c>
     </row>
     <row r="27">
@@ -24995,7 +24995,7 @@
         <v>652170016.89</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>6233098.63</v>
+        <v>6246280.37</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>0.09</v>
@@ -25013,16 +25013,16 @@
         <v>0.01</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>1050636.56</v>
+        <v>1063090.03</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>1922999.3</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>3470846.44</v>
+        <v>3471853.99</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>47.11</v>
+        <v>47.01</v>
       </c>
     </row>
     <row r="29">
@@ -25304,14 +25304,14 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-10.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
         </is>
       </c>
     </row>
@@ -25360,7 +25360,7 @@
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27486,7 +27486,7 @@
         <v>851941.8099999999</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>851941.8099999999</v>
+        <v>851941.8100000001</v>
       </c>
     </row>
     <row r="42">
@@ -28207,35 +28207,35 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 03:02:32.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-10.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: sao 2203 candidaturas com receita declarada e sem um real dos dois fundos publicos. que somam R$ 223.125.750,82 de receita.</t>
+          <t>Nota 1: sao 2200 candidaturas com receita declarada e sem um real dos dois fundos publicos. que somam R$ 223.590.002,17 de receita.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Nota 2: outras 4177 candidaturas NAO declararam receita alguma, das quais 960 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
+          <t>Nota 2: outras 4164 candidaturas NAO declararam receita alguma, das quais 960 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Nota 3: destas, 1262 nao receberam recurso partidario de especie alguma, nem mesmo fora dos dois fundos.</t>
+          <t>Nota 3: destas, 1256 nao receberam recurso partidario de especie alguma, nem mesmo fora dos dois fundos.</t>
         </is>
       </c>
     </row>
@@ -28383,13 +28383,13 @@
         <v>7.71</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>939338671.25</v>
+        <v>940060770.7</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>20.34</v>
+        <v>20.36</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>27.54</v>
+        <v>27.56</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>22.57</v>
@@ -28426,13 +28426,13 @@
         <v>11.18</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>538365356.08</v>
+        <v>538525118.08</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>25.09</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>32.87</v>
+        <v>32.88</v>
       </c>
       <c r="M6" s="6" t="n">
         <v>24.85</v>
@@ -28469,13 +28469,13 @@
         <v>15.98</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>500975044.6</v>
+        <v>501106811.34</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>29.08</v>
+        <v>29.09</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>38.96</v>
+        <v>38.97</v>
       </c>
       <c r="M7" s="6" t="n">
         <v>34.23</v>
@@ -28512,16 +28512,16 @@
         <v>10.81</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>347379154.28</v>
+        <v>347986863.58</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>23.33</v>
+        <v>23.37</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>30.68</v>
+        <v>30.74</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>26.91</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="9">
@@ -28555,13 +28555,13 @@
         <v>12.66</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>346218803.68</v>
+        <v>346492424.23</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>28.97</v>
+        <v>28.99</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>40.21</v>
+        <v>40.24</v>
       </c>
       <c r="M9" s="6" t="n">
         <v>31.74</v>
@@ -28598,16 +28598,16 @@
         <v>12.36</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>319429268.6</v>
+        <v>319520408.32</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>28.44</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>37.46</v>
+        <v>37.47</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>31.28</v>
+        <v>31.29</v>
       </c>
     </row>
     <row r="11">
@@ -28641,13 +28641,13 @@
         <v>13.3</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>260376041.15</v>
+        <v>260456309.01</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>27.17</v>
+        <v>27.18</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>36.03</v>
+        <v>36.04</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>30.53</v>
@@ -28684,13 +28684,13 @@
         <v>10.2</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>248129335.7</v>
+        <v>248537140.7</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>26.67</v>
+        <v>26.72</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>35.44</v>
+        <v>35.5</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>28.59</v>
@@ -28727,13 +28727,13 @@
         <v>11.82</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>191413183.8</v>
+        <v>191486245.93</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>21.86</v>
+        <v>21.87</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>30.54</v>
+        <v>30.55</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>25.82</v>
@@ -28770,13 +28770,13 @@
         <v>12.22</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>215953205.16</v>
+        <v>216342827.56</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>25.98</v>
+        <v>26.03</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>37.71</v>
+        <v>37.78</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>28.57</v>
@@ -28813,13 +28813,13 @@
         <v>11.93</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>223427397.48</v>
+        <v>223564597.48</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>31.81</v>
+        <v>31.83</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>43.07</v>
+        <v>43.09</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>36.48</v>
@@ -28856,13 +28856,13 @@
         <v>17.83</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>231968669.42</v>
+        <v>232263101.77</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>30.95</v>
+        <v>30.99</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>45.65</v>
+        <v>45.71</v>
       </c>
       <c r="M16" s="6" t="n">
         <v>34.39</v>
@@ -28899,16 +28899,16 @@
         <v>13.85</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>149380915.19</v>
+        <v>149546550.28</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>35.71</v>
+        <v>35.75</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>45.99</v>
+        <v>46.04</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>40.75</v>
+        <v>40.78</v>
       </c>
     </row>
     <row r="18">
@@ -28942,16 +28942,16 @@
         <v>20.16</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>176143006.2</v>
+        <v>176329731.25</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>42.44</v>
+        <v>42.48</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>58.9</v>
+        <v>58.96</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>48.55</v>
+        <v>48.57</v>
       </c>
     </row>
     <row r="19">
@@ -28985,13 +28985,13 @@
         <v>17.38</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>189081171.59</v>
+        <v>189101995.69</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>43.36</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>67.48</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>58.1</v>
@@ -29028,13 +29028,13 @@
         <v>14.84</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>145250642.75</v>
+        <v>145326561.75</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>42.81</v>
+        <v>42.84</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>53.62</v>
+        <v>53.65</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>44.08</v>
@@ -29071,16 +29071,16 @@
         <v>12.85</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>125207710.92</v>
+        <v>127266043.44</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>36.15</v>
+        <v>36.74</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>47.05</v>
+        <v>47.83</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>41.8</v>
+        <v>42.55</v>
       </c>
     </row>
     <row r="22">
@@ -29114,13 +29114,13 @@
         <v>17.24</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>162298081</v>
+        <v>162669914.67</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>41.08</v>
+        <v>41.18</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>61.5</v>
+        <v>61.64</v>
       </c>
       <c r="M22" s="6" t="n">
         <v>36.39</v>
@@ -29157,13 +29157,13 @@
         <v>12.24</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>116112117.63</v>
+        <v>116218732.63</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>36.05</v>
+        <v>36.08</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>47.54</v>
+        <v>47.59</v>
       </c>
       <c r="M23" s="6" t="n">
         <v>42.42</v>
@@ -29200,16 +29200,16 @@
         <v>30.18</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>206561665.78</v>
+        <v>206637988.78</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>68.63</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>91.67</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>73.25</v>
+        <v>73.26000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -29243,7 +29243,7 @@
         <v>20.99</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>118100015.06</v>
+        <v>118101205.06</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>40.08</v>
@@ -29286,13 +29286,13 @@
         <v>23.62</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>122885231.77</v>
+        <v>123124375.75</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>53.26</v>
+        <v>53.36</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>70.61</v>
+        <v>70.75</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>63.36</v>
@@ -29329,13 +29329,13 @@
         <v>34.52</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>146357084.1</v>
+        <v>146374557.1</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>83.28</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>115.36</v>
+        <v>115.38</v>
       </c>
       <c r="M27" s="6" t="n">
         <v>89.84999999999999</v>
@@ -29372,13 +29372,13 @@
         <v>31.11</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>118738334.43</v>
+        <v>118839693.01</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>74.40000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>100.39</v>
+        <v>100.48</v>
       </c>
       <c r="M28" s="6" t="n">
         <v>82.29000000000001</v>
@@ -29415,13 +29415,13 @@
         <v>65.08</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>134640502.61</v>
+        <v>134802502.61</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>151.66</v>
+        <v>151.84</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>219.06</v>
+        <v>219.32</v>
       </c>
       <c r="M29" s="6" t="n">
         <v>202.55</v>
@@ -29458,13 +29458,13 @@
         <v>55.74</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>116027014.96</v>
+        <v>116096217.41</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>143.25</v>
+        <v>143.34</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>200.84</v>
+        <v>200.96</v>
       </c>
       <c r="M30" s="6" t="n">
         <v>188.36</v>
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>771349229.63</v>
+        <v>772962838.47</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -29605,16 +29605,16 @@
         <v>13.34</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>7267002933.950001</v>
+        <v>7275637605.73</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>33.92</v>
+        <v>33.96</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>46.04</v>
+        <v>46.09</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>38.23</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="34">
@@ -29627,7 +29627,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-10.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-11 09:04:27</t>
+          <t>2026-10-11 15:03:10</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>575680870.9499999</v>
+        <v>575680870.95</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1.75</v>
@@ -6029,7 +6029,7 @@
         </is>
       </c>
       <c r="G65" s="6" t="n">
-        <v>58445503.79</v>
+        <v>58445503.79000001</v>
       </c>
       <c r="H65" s="6" t="n">
         <v>0.18</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
         </is>
       </c>
     </row>
@@ -24271,7 +24271,7 @@
         <v>4.39</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5664780.810000001</v>
+        <v>5664780.81</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>0.91</v>
@@ -24927,7 +24927,7 @@
         <v>5498396.57</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>8287319.060000001</v>
+        <v>8287319.06</v>
       </c>
       <c r="N26" s="6" t="n">
         <v>23.06</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 09:04:27.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-11 15:03:10</t>
+          <t>2026-10-11 21:04:53</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>575680870.95</v>
+        <v>575680870.9499999</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1.75</v>
@@ -6029,7 +6029,7 @@
         </is>
       </c>
       <c r="G65" s="6" t="n">
-        <v>58445503.79000001</v>
+        <v>58445503.79</v>
       </c>
       <c r="H65" s="6" t="n">
         <v>0.18</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
         </is>
       </c>
     </row>
@@ -24271,7 +24271,7 @@
         <v>4.39</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5664780.81</v>
+        <v>5664780.810000001</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>0.91</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 15:03:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-11 21:04:53</t>
+          <t>2026-10-12 03:02:46</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-11 21:04:53.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-12 03:02:46</t>
+          <t>2026-10-12 09:03:29</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 03:02:46.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-12 09:03:29</t>
+          <t>2026-10-12 15:03:07</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 09:03:29.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-12 15:03:07</t>
+          <t>2026-10-12 21:03:04</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 15:03:07.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-12 21:03:04</t>
+          <t>2026-10-13 03:02:52</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-12 21:03:04.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-13 03:02:52</t>
+          <t>2026-10-13 09:13:47</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 03:02:52.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -646,13 +646,13 @@
         <v>1.03</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>47721071.07</v>
+        <v>47759459.29</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>32240780.04</v>
+        <v>32297850.99</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0.64</v>
@@ -677,16 +677,16 @@
         <v>36.5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1786322147.49</v>
+        <v>1789536597.2</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>24.55</v>
+        <v>24.54</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>1178011139.66</v>
+        <v>1176388199.28</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>23.27</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="9">
@@ -708,16 +708,16 @@
         <v>26.47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3398271892.38</v>
+        <v>3400667363.28</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>46.71</v>
+        <v>46.63</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2277354655.9</v>
+        <v>2283855891.23</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>44.99</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="10">
@@ -739,16 +739,16 @@
         <v>5.34</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>752116844.6800001</v>
+        <v>762405184.63</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>10.34</v>
+        <v>10.45</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>608688653.1</v>
+        <v>610044593.85</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>12.02</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="11">
@@ -770,16 +770,16 @@
         <v>3.72</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>772962838.47</v>
+        <v>773225038.47</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>10.62</v>
+        <v>10.6</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>577765223.13</v>
+        <v>580965223.13</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>11.41</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="12">
@@ -801,16 +801,16 @@
         <v>6.32</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>518242811.64</v>
+        <v>518952810.44</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>7.12</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>388004216</v>
+        <v>388235659.38</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>7.66</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="13">
@@ -894,13 +894,13 @@
         <v>100</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7275637605.73</v>
+        <v>7292546453.31</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>5062064667.83</v>
+        <v>5071787417.860001</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>100</v>
@@ -909,14 +909,14 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -1025,14 +1025,14 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>175416</v>
+        <v>176132</v>
       </c>
     </row>
     <row r="24">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6561108386.47</v>
+        <v>6571806694.05</v>
       </c>
     </row>
     <row r="26">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{"REC_FEFC": 4843153724.77, "REC_FINANCIAMENTO_COLETIVO": 18421406.44, "REC_FUNDO_PARTIDARIO": 549470560.59, "REC_ORIGEM_NAO_IDENTIFICADA": 1110352.96, "REC_OUTROS_CANDIDATOS": 120427781.78, "REC_PARTIDO_OUTROS_RECURSOS": 202691423.31, "REC_PESSOAS_FISICAS": 662879762.49, "REC_PROPRIOS": 162953374.13, "REC_SEM_ORIGEM": 0.0}</t>
+          <t>{"REC_FEFC": 4844739920.29, "REC_FINANCIAMENTO_COLETIVO": 18454342.44, "REC_FUNDO_PARTIDARIO": 554667725.65, "REC_ORIGEM_NAO_IDENTIFICADA": 1122450.97, "REC_OUTROS_CANDIDATOS": 120906785.19, "REC_PARTIDO_OUTROS_RECURSOS": 202862333.19, "REC_PESSOAS_FISICAS": 665536838.19, "REC_PROPRIOS": 163516298.13, "REC_SEM_ORIGEM": 0.0}</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>78551</v>
+        <v>78845</v>
       </c>
     </row>
     <row r="30">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>999494</v>
+        <v>1004571</v>
       </c>
     </row>
     <row r="36">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>794856</v>
+        <v>799005</v>
       </c>
     </row>
     <row r="37">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4526188163.6</v>
+        <v>4533327912.13</v>
       </c>
     </row>
     <row r="38">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>721450</v>
+        <v>730118</v>
       </c>
     </row>
     <row r="39">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3184714428.42</v>
+        <v>3206794063.34</v>
       </c>
     </row>
     <row r="40">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>74063</v>
+        <v>74760</v>
       </c>
     </row>
     <row r="43">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>800630.04</v>
+        <v>808166.14</v>
       </c>
     </row>
     <row r="44">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>547905</v>
+        <v>550391</v>
       </c>
     </row>
     <row r="46">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>55920</v>
+        <v>56061</v>
       </c>
     </row>
     <row r="49">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>52</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>946</v>
+        <v>936</v>
       </c>
     </row>
     <row r="52">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2550373740.61</v>
+        <v>2563768465.62</v>
       </c>
     </row>
     <row r="53">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64125144.72</v>
+        <v>64325144.72</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>186468947.28</v>
+        <v>188939807.66</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4869107818.95</v>
+        <v>4946838977.85</v>
       </c>
     </row>
     <row r="57">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4795594655.36</v>
+        <v>4873234079.22</v>
       </c>
     </row>
     <row r="58">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>595860598.98</v>
+        <v>597404595.62</v>
       </c>
     </row>
     <row r="59">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>535417270.69</v>
+        <v>536487270.69</v>
       </c>
     </row>
     <row r="60">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-13 09:13:47</t>
+          <t>2026-10-13 15:05:10</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-714529219.26</v>
+        <v>-720739759.26</v>
       </c>
     </row>
     <row r="65">
@@ -3221,7 +3221,7 @@
         <v>4300000</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="R25" s="6" t="n">
         <v>500000</v>
@@ -7339,7 +7339,7 @@
         <v>2396323.01</v>
       </c>
       <c r="Q83" s="6" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="R83" s="6" t="n">
         <v>0</v>
@@ -8842,14 +8842,14 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -9032,19 +9032,19 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>5970</v>
+        <v>5982</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>276471283.48</v>
+        <v>277437844.84</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5.46</v>
+        <v>5.47</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>268996583.77</v>
+        <v>269968345.13</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>97.3</v>
+        <v>97.31</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -9097,19 +9097,19 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1874</v>
+        <v>1878</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>96979034.95999999</v>
+        <v>97494485.77</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>1.92</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>95181979.27</v>
+        <v>95727430.08</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>98.15000000000001</v>
+        <v>98.19</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
@@ -9422,19 +9422,19 @@
         </is>
       </c>
       <c r="I11" s="5" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>12954581.79</v>
+        <v>12977013.23</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0.26</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>12572277.79</v>
+        <v>12596709.23</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>97.05</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
@@ -9617,19 +9617,19 @@
         </is>
       </c>
       <c r="I14" s="5" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>9155691.550000001</v>
+        <v>9197191.550000001</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0.18</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>8139644.59</v>
+        <v>8181144.59</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>88.90000000000001</v>
+        <v>88.95</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
@@ -9973,37 +9973,37 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>***.883.424-**</t>
+          <t>05.060.706/0003-24</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>EULINA PONCE DE LEON</t>
+          <t>SANTANA   ASSOCIADOS MARKETING E PROPAGANDA LTDA</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>PESSOA FÍSICA</t>
+          <t>PESSOA JURÍDICA</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>SALVADOR</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>Receita (BrasilAPI)</t>
         </is>
       </c>
       <c r="I20" s="5" t="n">
@@ -10016,19 +10016,19 @@
         <v>0.12</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>1000</v>
+        <v>6000000</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0.02</v>
+        <v>100</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>DANI PORTELA (PT)</t>
+          <t>ACM NETO (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -10038,12 +10038,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>05.060.706/0003-24</t>
+          <t>02.495.060/0001-58</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>SANTANA   ASSOCIADOS MARKETING E PROPAGANDA LTDA</t>
+          <t>IMPRINT 2001 GRAFICA E EDITORA LTDA</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -10053,17 +10053,17 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>SALVADOR</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -10072,28 +10072,28 @@
         </is>
       </c>
       <c r="I21" s="5" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>6000000</v>
+        <v>5941049.63</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0.12</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>6000000</v>
+        <v>4377145.24</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>100</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PDT; PSD; PCDOB; UNIÃO</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>ACM NETO (UNIÃO)</t>
+          <t>FLÁVIO GANEM (UNIÃO); DELEGADA MARTHA ROCHA (PDT)</t>
         </is>
       </c>
     </row>
@@ -10103,12 +10103,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>02.495.060/0001-58</t>
+          <t>07.263.666/0001-81</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>IMPRINT 2001 GRAFICA E EDITORA LTDA</t>
+          <t>BRASPOR GRAFICA E EDITORA LTDA.</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>OSASCO</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -10137,28 +10137,28 @@
         </is>
       </c>
       <c r="I22" s="5" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>5941049.63</v>
+        <v>5698948.42</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4377145.24</v>
+        <v>3332636.47</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>73.68000000000001</v>
+        <v>58.48</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>PDT; PSD; PCDOB; UNIÃO</t>
+          <t>PT; PL; PODE; UNIÃO</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>FLÁVIO GANEM (UNIÃO); DELEGADA MARTHA ROCHA (PDT)</t>
+          <t>FLAVIO BOLSONARO (PL); CARLOS ZARATTINI (PT)</t>
         </is>
       </c>
     </row>
@@ -10168,12 +10168,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>07.263.666/0001-81</t>
+          <t>08.540.403/0001-35</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>BRASPOR GRAFICA E EDITORA LTDA.</t>
+          <t>GRAFICA J B LTDA</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -10183,17 +10183,17 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>OSASCO</t>
+          <t>JOAO PESSOA</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -10202,28 +10202,28 @@
         </is>
       </c>
       <c r="I23" s="5" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>5698948.42</v>
+        <v>5496084</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0.11</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>3332636.47</v>
+        <v>4609157.5</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>58.48</v>
+        <v>83.86</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>PT; PL; PODE; UNIÃO</t>
+          <t>PP; PL; PT; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL); CARLOS ZARATTINI (PT)</t>
+          <t>LUCAS RIBEIRO (PP); RUY CARNEIRO (PODE)</t>
         </is>
       </c>
     </row>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>08.540.403/0001-35</t>
+          <t>67.949.812/0001-59</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>GRAFICA J B LTDA</t>
+          <t>ALGORITMO DADOS ESTRATEGIA E COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -10248,17 +10248,17 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Agências de notícias</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>JOAO PESSOA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -10267,28 +10267,28 @@
         </is>
       </c>
       <c r="I24" s="5" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>5484884</v>
+        <v>5400000</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0.11</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4597957.5</v>
+        <v>3600000</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>83.83</v>
+        <v>66.67</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>PP; PL; PT; REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>LUCAS RIBEIRO (PP); RUY CARNEIRO (PODE)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>67.949.812/0001-59</t>
+          <t>35.659.497/0001-39</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>ALGORITMO DADOS ESTRATEGIA E COMUNICACAO LTDA</t>
+          <t>GRAFICA NMC LTDA</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Agências de notícias</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -10332,28 +10332,28 @@
         </is>
       </c>
       <c r="I25" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>5400000</v>
+        <v>5092796.17</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>3600000</v>
+        <v>2608986.1</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>66.67</v>
+        <v>51.23</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT; PL; REPUBLICANOS; UNIÃO</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>LULA (PT); MENDONÇA FILHO (PL)</t>
         </is>
       </c>
     </row>
@@ -10363,12 +10363,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>35.659.497/0001-39</t>
+          <t>32.951.141/0001-86</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>GRAFICA NMC LTDA</t>
+          <t>PARANOA DIGITAL PRODUCAO CINEMATOGRAFICA, DE VIDEOS E PROGRAMAS LTDA</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -10397,28 +10397,28 @@
         </is>
       </c>
       <c r="I26" s="5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>5092796.17</v>
+        <v>5030000</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>2608986.1</v>
+        <v>5030000</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>51.23</v>
+        <v>100</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>PT; PL; REPUBLICANOS; UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>LULA (PT); MENDONÇA FILHO (PL)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -10428,12 +10428,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>32.951.141/0001-86</t>
+          <t>02.933.302/0001-48</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>PARANOA DIGITAL PRODUCAO CINEMATOGRAFICA, DE VIDEOS E PROGRAMAS LTDA</t>
+          <t>QUALIGRAF - EDITORA E GRAFICA LTDA</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>FORTALEZA</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -10462,28 +10462,28 @@
         </is>
       </c>
       <c r="I27" s="5" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>5030000</v>
+        <v>4866473.9</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>5030000</v>
+        <v>3925144.9</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>100</v>
+        <v>80.66</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PL; PT; PP; UNIÃO</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>DANILO FORTE (PP); FERNANDO SANTANA (PT)</t>
         </is>
       </c>
     </row>
@@ -10493,12 +10493,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>02.933.302/0001-48</t>
+          <t>67.314.597/0001-10</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>QUALIGRAF - EDITORA E GRAFICA LTDA</t>
+          <t>ALL MG26 COMUNICACAO E ESTRATEGIA SPE LTDA</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -10508,17 +10508,17 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>FORTALEZA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -10527,28 +10527,28 @@
         </is>
       </c>
       <c r="I28" s="5" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>4866473.9</v>
+        <v>4800000</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>3925144.9</v>
+        <v>4800000</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>80.66</v>
+        <v>100</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>PL; PT; PP; UNIÃO</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>DANILO FORTE (PP); FERNANDO SANTANA (PT)</t>
+          <t>ALEXANDRE KALIL (PDT)</t>
         </is>
       </c>
     </row>
@@ -10558,12 +10558,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>67.314.597/0001-10</t>
+          <t>16.670.085/0001-55</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>ALL MG26 COMUNICACAO E ESTRATEGIA SPE LTDA</t>
+          <t>LOCALIZA RENT A CAR SA</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -10573,17 +10573,17 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Locação de automóveis sem condutor</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -10592,28 +10592,28 @@
         </is>
       </c>
       <c r="I29" s="5" t="n">
-        <v>1</v>
+        <v>224</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>4800000</v>
+        <v>4759819.81</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>4800000</v>
+        <v>4308250.18</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>100</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PL; PSD; UNIÃO; NOVO</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>ALEXANDRE KALIL (PDT)</t>
+          <t>MATEUS SIMÕES (PSD); LENA PINTO (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -10623,12 +10623,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>16.670.085/0001-55</t>
+          <t>04.986.141/0001-86</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>LOCALIZA RENT A CAR SA</t>
+          <t>F7 COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -10638,17 +10638,17 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Locação de automóveis sem condutor</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>SALVADOR</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -10657,28 +10657,28 @@
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>224</v>
+        <v>5</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>4759819.81</v>
+        <v>4750000</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>4308250.18</v>
+        <v>1950000</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>90.51000000000001</v>
+        <v>41.05</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>PL; PSD; UNIÃO; NOVO</t>
+          <t>MDB; PSD</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>MATEUS SIMÕES (PSD); LENA PINTO (UNIÃO)</t>
+          <t>RENAN FILHO (MDB); DANIEL VILELA (MDB)</t>
         </is>
       </c>
     </row>
@@ -10688,12 +10688,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>04.986.141/0001-86</t>
+          <t>05.060.706/0001-62</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>F7 COMUNICACAO LTDA</t>
+          <t>SANTANA   ASSOCIADOS MARKETING E PROPAGANDA LTDA</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>SALVADOR</t>
+          <t>LAURO DE FREITAS</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -10722,28 +10722,28 @@
         </is>
       </c>
       <c r="I31" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>4750000</v>
+        <v>4600000</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>1950000</v>
+        <v>2500000</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>41.05</v>
+        <v>54.35</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>MDB; PSD</t>
+          <t>UNIÃO; PL</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>RENAN FILHO (MDB); DANIEL VILELA (MDB)</t>
+          <t>ALCIDES FERNANDES (PL); CAPITÃO WAGNER (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -10753,12 +10753,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>05.060.706/0001-62</t>
+          <t>13.007.646/0001-42</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>SANTANA   ASSOCIADOS MARKETING E PROPAGANDA LTDA</t>
+          <t>GRAFICA EDITORA J ANDRADE LTDA</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -10768,17 +10768,17 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>LAURO DE FREITAS</t>
+          <t>ARACAJU</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -10787,28 +10787,28 @@
         </is>
       </c>
       <c r="I32" s="5" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>4600000</v>
+        <v>4515352.16</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>2500000</v>
+        <v>3070423.42</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>54.35</v>
+        <v>68</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO; PL</t>
+          <t>REPUBLICANOS; PSD; PP; UNIÃO</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>ALCIDES FERNANDES (PL); CAPITÃO WAGNER (UNIÃO)</t>
+          <t>GUSTINHO RIBEIRO (PP); VALMIR DE FRANCISQUINHO (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -10818,12 +10818,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>13.007.646/0001-42</t>
+          <t>57.780.367/0001-92</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>GRAFICA EDITORA J ANDRADE LTDA</t>
+          <t>AUREA TECNOLOGIA E SOLUCOES LTDA</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -10833,17 +10833,17 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>ARACAJU</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -10852,28 +10852,28 @@
         </is>
       </c>
       <c r="I33" s="5" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>4500430.16</v>
+        <v>4500000</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>3055501.42</v>
+        <v>4500000</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>67.89</v>
+        <v>100</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS; PSD; PP; UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>GUSTINHO RIBEIRO (PP); VALMIR DE FRANCISQUINHO (REPUBLICANOS)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -10985,13 +10985,13 @@
         <v>188</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>4429240.36</v>
+        <v>4429341.16</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>4418403.13</v>
+        <v>4418503.93</v>
       </c>
       <c r="M35" s="6" t="n">
         <v>99.76000000000001</v>
@@ -11050,16 +11050,16 @@
         <v>162</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>4328431.96</v>
+        <v>4341431.96</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>3487031.96</v>
+        <v>3500031.96</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>80.56</v>
+        <v>80.62</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
@@ -11078,12 +11078,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>27.997.819/0001-21</t>
+          <t>04.984.400/0001-30</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>GRID COMUNICACAO VISUAL, SINALIZACAO E EVENTOS LTDA</t>
+          <t>CTA - CLEITON TAXI AEREO LTDA</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -11093,17 +11093,17 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Transporte aéreo de carga</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>MOSSORO</t>
+          <t>NOVA OLINDA DO NORTE</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -11112,28 +11112,28 @@
         </is>
       </c>
       <c r="I37" s="5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>4244212.98</v>
+        <v>4266887.3</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>3219302.37</v>
+        <v>1123062.3</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>75.84999999999999</v>
+        <v>26.32</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>PV; PP; PT; MDB</t>
+          <t>PSD; MDB; UNIÃO; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>DR. BERNARDO (PV); KALINE DE DR. BERNARDO (PV)</t>
+          <t>OMAR AZIZ (PSD); EDUARDO BRAGA (MDB)</t>
         </is>
       </c>
     </row>
@@ -11143,12 +11143,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>31.399.764/0001-25</t>
+          <t>27.997.819/0001-21</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>LOG PRODUCOES   FILMES LTDA</t>
+          <t>GRID COMUNICACAO VISUAL, SINALIZACAO E EVENTOS LTDA</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -11158,17 +11158,17 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>MOSSORO</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -11177,28 +11177,28 @@
         </is>
       </c>
       <c r="I38" s="5" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>4148608</v>
+        <v>4244212.98</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>2074304</v>
+        <v>3219302.37</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>50</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PV; PP; PT; MDB</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>LULA (PT)</t>
+          <t>DR. BERNARDO (PV); KALINE DE DR. BERNARDO (PV)</t>
         </is>
       </c>
     </row>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>04.984.400/0001-30</t>
+          <t>31.399.764/0001-25</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>CTA - CLEITON TAXI AEREO LTDA</t>
+          <t>LOG PRODUCOES   FILMES LTDA</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -11223,17 +11223,17 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Transporte aéreo de carga</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>NOVA OLINDA DO NORTE</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -11242,28 +11242,28 @@
         </is>
       </c>
       <c r="I39" s="5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4081937.3</v>
+        <v>4148608</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>1045562.3</v>
+        <v>2074304</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>25.61</v>
+        <v>50</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>PSD; MDB; UNIÃO; REPUBLICANOS</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>OMAR AZIZ (PSD); EDUARDO BRAGA (MDB)</t>
+          <t>LULA (PT)</t>
         </is>
       </c>
     </row>
@@ -11508,7 +11508,7 @@
         <v>3800000</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L43" s="6" t="n">
         <v>3800000</v>
@@ -11576,10 +11576,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>2110000</v>
+        <v>2210000</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>55.67</v>
+        <v>58.31</v>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
@@ -11663,12 +11663,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>57.780.367/0001-92</t>
+          <t>60.259.384/0001-93</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>AUREA TECNOLOGIA E SOLUCOES LTDA</t>
+          <t>CDA COMUNICACAO EM SERVICOS GRAFICOS E EVENTOS LTDA</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -11678,17 +11678,17 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>SANTA RITA</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -11697,28 +11697,28 @@
         </is>
       </c>
       <c r="I46" s="5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>3700000</v>
+        <v>3664444.75</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>3700000</v>
+        <v>2812803.75</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>100</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>MDB; PL; PT; PSB</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>VENEZIANO (MDB); DR. MARCELO QUEIROGA (PL)</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>60.259.384/0001-93</t>
+          <t>04.405.470/0001-96</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>CDA COMUNICACAO EM SERVICOS GRAFICOS E EVENTOS LTDA</t>
+          <t>CONTACTO RELACOES PUBLICAS LTDA</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>SANTA RITA</t>
+          <t>NATAL</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -11762,28 +11762,28 @@
         </is>
       </c>
       <c r="I47" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>3664444.75</v>
+        <v>3600000</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>2812803.75</v>
+        <v>0</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>76.76000000000001</v>
+        <v>0</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>MDB; PL; PT; PSB</t>
+          <t>PT; PSB; REDE</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>VENEZIANO (MDB); DR. MARCELO QUEIROGA (PL)</t>
+          <t>ELMANO DE FREITAS (PT); CID GOMES (PSB)</t>
         </is>
       </c>
     </row>
@@ -11793,12 +11793,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>04.405.470/0001-96</t>
+          <t>24.759.252/0001-67</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>CONTACTO RELACOES PUBLICAS LTDA</t>
+          <t>FEIRA ROTULOS E ETIQUETAS ADESIVAS LTDA</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -11808,17 +11808,17 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>NATAL</t>
+          <t>FEIRA DE SANTANA</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -11827,28 +11827,28 @@
         </is>
       </c>
       <c r="I48" s="5" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>3600000</v>
+        <v>3555631.95</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0</v>
+        <v>2992985.32</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>0</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>PT; PSB; REDE</t>
+          <t>PT; UNIÃO; PSD; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>ELMANO DE FREITAS (PT); CID GOMES (PSB)</t>
+          <t>PROFESSORA DAYANE PIMENTEL (UNIÃO); GABRIEL NUNES (PSD)</t>
         </is>
       </c>
     </row>
@@ -11988,12 +11988,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>24.759.252/0001-67</t>
+          <t>30.007.119/0001-57</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>FEIRA ROTULOS E ETIQUETAS ADESIVAS LTDA</t>
+          <t>CONNECT FILMES - PRODUCAO DE FILMES E PUBLICIDADE LTDA</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -12003,17 +12003,17 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>FEIRA DE SANTANA</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -12022,28 +12022,28 @@
         </is>
       </c>
       <c r="I51" s="5" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>3525287.95</v>
+        <v>3500000</v>
       </c>
       <c r="K51" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>2962641.32</v>
+        <v>3500000</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>84.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>PT; UNIÃO; PSD; REPUBLICANOS</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>PROFESSORA DAYANE PIMENTEL (UNIÃO); GABRIEL NUNES (PSD)</t>
+          <t>TARCÍSIO (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -12053,12 +12053,12 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>30.007.119/0001-57</t>
+          <t>85.057.529/0001-02</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>CONNECT FILMES - PRODUCAO DE FILMES E PUBLICIDADE LTDA</t>
+          <t>HELLOGRAF ARTES GRAFICAS LTDA</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -12068,17 +12068,17 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>CURITIBA</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -12087,28 +12087,28 @@
         </is>
       </c>
       <c r="I52" s="5" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>3500000</v>
+        <v>3459072.88</v>
       </c>
       <c r="K52" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>3500000</v>
+        <v>1478215.14</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>100</v>
+        <v>42.73</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>NOVO; PV; PSD; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>TARCÍSIO (REPUBLICANOS)</t>
+          <t>ALIEL MACHADO (PV); JEFFREY CHIQUINI (NOVO)</t>
         </is>
       </c>
     </row>
@@ -12118,12 +12118,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>85.057.529/0001-02</t>
+          <t>47.402.712/0001-09</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>HELLOGRAF ARTES GRAFICAS LTDA</t>
+          <t>NE ELEICOES SPE LTDA</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -12133,17 +12133,17 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>CURITIBA</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -12152,28 +12152,28 @@
         </is>
       </c>
       <c r="I53" s="5" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>3457182.88</v>
+        <v>3450000</v>
       </c>
       <c r="K53" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>1476325.14</v>
+        <v>2100000</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>42.7</v>
+        <v>60.87</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>NOVO; PV; PSD; REPUBLICANOS</t>
+          <t>PSD; UNIÃO; PSDB</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>ALIEL MACHADO (PV); JEFFREY CHIQUINI (NOVO)</t>
+          <t>RAQUEL LYRA (PSD); MIGUEL COELHO (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -12183,12 +12183,12 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>47.402.712/0001-09</t>
+          <t>89.840.797/0001-49</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>NE ELEICOES SPE LTDA</t>
+          <t>GRAFICA E EDITORA COMUNICACAO IMPRESSA LTDA</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -12198,17 +12198,17 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Edição integrada à impressão de cadastros, listas e outros produtos gráficos</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -12217,28 +12217,28 @@
         </is>
       </c>
       <c r="I54" s="5" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>3450000</v>
+        <v>3411091.28</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>2100000</v>
+        <v>3087074.6</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>60.87</v>
+        <v>90.5</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>PSD; UNIÃO; PSDB</t>
+          <t>PL; PP; PDT; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>RAQUEL LYRA (PSD); MIGUEL COELHO (UNIÃO)</t>
+          <t>ZUCCO (PL); JULIANA BRIZOLA (PDT)</t>
         </is>
       </c>
     </row>
@@ -12248,12 +12248,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>89.840.797/0001-49</t>
+          <t>17.861.454/0001-50</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>GRAFICA E EDITORA COMUNICACAO IMPRESSA LTDA</t>
+          <t>RMR CONSULTORIA DE INTELIGENCIA LTDA</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -12263,17 +12263,17 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Edição integrada à impressão de cadastros, listas e outros produtos gráficos</t>
+          <t>Pesquisas de mercado e de opinião pública</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -12282,28 +12282,28 @@
         </is>
       </c>
       <c r="I55" s="5" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>3411091.28</v>
+        <v>3400000</v>
       </c>
       <c r="K55" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>3087074.6</v>
+        <v>3400000</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>90.5</v>
+        <v>100</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>PL; PP; PDT; REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>ZUCCO (PL); JULIANA BRIZOLA (PDT)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -12313,12 +12313,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>17.861.454/0001-50</t>
+          <t>24.347.979/0001-37</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>RMR CONSULTORIA DE INTELIGENCIA LTDA</t>
+          <t>MACIEL ART DESIGNER GRAFICO - LTDA</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -12328,17 +12328,17 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Pesquisas de mercado e de opinião pública</t>
+          <t>Comércio varejista de artigos recreativos e esportivos</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -12347,28 +12347,28 @@
         </is>
       </c>
       <c r="I56" s="5" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>3400000</v>
+        <v>3345250.5</v>
       </c>
       <c r="K56" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>3400000</v>
+        <v>2472030</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>100</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD; PT; PODE; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>DANIEL COELHO (PSD); LUNA ZARATTINI (PT)</t>
         </is>
       </c>
     </row>
@@ -12378,12 +12378,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>24.347.979/0001-37</t>
+          <t>22.317.550/0001-71</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>MACIEL ART DESIGNER GRAFICO - LTDA</t>
+          <t>M DESIGNER CITY LTDA</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Comércio varejista de artigos recreativos e esportivos</t>
+          <t>Edição de livros</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -12412,28 +12412,28 @@
         </is>
       </c>
       <c r="I57" s="5" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>3345250.5</v>
+        <v>3343294.16</v>
       </c>
       <c r="K57" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>2472030</v>
+        <v>2233258.46</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>73.90000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>PSD; PT; PODE; REPUBLICANOS</t>
+          <t>PT; REPUBLICANOS; UNIÃO; PSD</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>DANIEL COELHO (PSD); LUNA ZARATTINI (PT)</t>
+          <t>LULA (PT); JILMAR TATTO (PT)</t>
         </is>
       </c>
     </row>
@@ -12443,12 +12443,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>22.317.550/0001-71</t>
+          <t>45.443.633/0001-02</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>M DESIGNER CITY LTDA</t>
+          <t>JD IMPRESSOS PERSONALIZADOS LTDA</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -12458,17 +12458,17 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Edição de livros</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>JOAO PESSOA</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -12477,28 +12477,28 @@
         </is>
       </c>
       <c r="I58" s="5" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>3342913.16</v>
+        <v>3290879.5</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>2232877.46</v>
+        <v>2335315</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>66.79000000000001</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>PT; REPUBLICANOS; UNIÃO; PSD</t>
+          <t>PL; REPUBLICANOS; PP; UNIÃO</t>
         </is>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>LULA (PT); JILMAR TATTO (PT)</t>
+          <t>EFRAIM FILHO (PL); TIÃO GOMES (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -12545,16 +12545,16 @@
         <v>187</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>3252935.86</v>
+        <v>3273400.86</v>
       </c>
       <c r="K59" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>1538688.52</v>
+        <v>1539153.52</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>47.3</v>
+        <v>47.02</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
@@ -12703,12 +12703,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>45.443.633/0001-02</t>
+          <t>07.556.546/0001-72</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>JD IMPRESSOS PERSONALIZADOS LTDA</t>
+          <t>PRESSGRAF IMPORTACAO TECNOLOGIA E SERVICOS GRAFICOS LTDA</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -12723,12 +12723,12 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>JOAO PESSOA</t>
+          <t>SALVADOR</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -12737,28 +12737,28 @@
         </is>
       </c>
       <c r="I62" s="5" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>3183519.5</v>
+        <v>3164378.8</v>
       </c>
       <c r="K62" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>2227955</v>
+        <v>2883468.8</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>69.98</v>
+        <v>91.12</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>PL; REPUBLICANOS; PP; UNIÃO</t>
+          <t>PSD; REPUBLICANOS; PSDB; UNIÃO</t>
         </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>TIÃO GOMES (REPUBLICANOS); EFRAIM FILHO (PL)</t>
+          <t>RAIMUNDO COSTA (PSD); MÁRCIO MARINHO (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -12768,12 +12768,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>07.556.546/0001-72</t>
+          <t>11.197.995/0001-49</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>PRESSGRAF IMPORTACAO TECNOLOGIA E SERVICOS GRAFICOS LTDA</t>
+          <t>BUCCHIANERI ADVOCACIA</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades jurídicas, exceto cartórios</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>SALVADOR</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -12802,28 +12802,28 @@
         </is>
       </c>
       <c r="I63" s="5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>3164378.8</v>
+        <v>3150000</v>
       </c>
       <c r="K63" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L63" s="6" t="n">
-        <v>2883468.8</v>
+        <v>3150000</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>91.12</v>
+        <v>100</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>PSD; REPUBLICANOS; PSDB; UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>RAIMUNDO COSTA (PSD); MÁRCIO MARINHO (REPUBLICANOS)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -12833,12 +12833,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>11.197.995/0001-49</t>
+          <t>41.470.063/0001-99</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>BUCCHIANERI ADVOCACIA</t>
+          <t>SETE CORES INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -12848,17 +12848,17 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Atividades jurídicas, exceto cartórios</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -12867,28 +12867,28 @@
         </is>
       </c>
       <c r="I64" s="5" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>3150000</v>
+        <v>3122716.46</v>
       </c>
       <c r="K64" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>3150000</v>
+        <v>2736315.46</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>100</v>
+        <v>87.63</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PL; PCDOB; PDT; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>SILVIO ANTÔNIO (PL); MÁRCIO JERRY (PCDOB)</t>
         </is>
       </c>
     </row>
@@ -12898,12 +12898,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>41.470.063/0001-99</t>
+          <t>51.847.516/0001-07</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>SETE CORES INDUSTRIA E COMERCIO LTDA</t>
+          <t>VOLARE IMPRESSAO TEXTIL LTDA</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -12913,17 +12913,17 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>SAO LUIS</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -12932,28 +12932,28 @@
         </is>
       </c>
       <c r="I65" s="5" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>3122716.46</v>
+        <v>3102120</v>
       </c>
       <c r="K65" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L65" s="6" t="n">
-        <v>2736315.46</v>
+        <v>2681385</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>87.63</v>
+        <v>86.44</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>PL; PCDOB; PDT; REPUBLICANOS</t>
+          <t>PSD; MDB; REPUBLICANOS; NOVO</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>SILVIO ANTÔNIO (PL); MÁRCIO JERRY (PCDOB)</t>
+          <t>TARCÍSIO (REPUBLICANOS); BALEIA ROSSI (MDB)</t>
         </is>
       </c>
     </row>
@@ -12963,12 +12963,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>51.847.516/0001-07</t>
+          <t>17.940.670/0001-90</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>VOLARE IMPRESSAO TEXTIL LTDA</t>
+          <t>C. KZAN</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>BELEM</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -12997,28 +12997,28 @@
         </is>
       </c>
       <c r="I66" s="5" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>3102120</v>
+        <v>3093159.25</v>
       </c>
       <c r="K66" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L66" s="6" t="n">
-        <v>2681385</v>
+        <v>1889810</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>86.44</v>
+        <v>61.1</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>PSD; MDB; REPUBLICANOS; NOVO</t>
+          <t>PODE; MDB; PSD; PDT</t>
         </is>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>TARCÍSIO (REPUBLICANOS); BALEIA ROSSI (MDB)</t>
+          <t>DR. DANIEL (PODE); DRA. ALESSANDRA HABER (PODE)</t>
         </is>
       </c>
     </row>
@@ -13028,12 +13028,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>17.940.670/0001-90</t>
+          <t>35.844.647/0001-84</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>C. KZAN</t>
+          <t>J C SILVA LTDA</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -13043,17 +13043,17 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Fabricação de embalagens de papel</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>BELEM</t>
+          <t>TERESINA</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -13062,28 +13062,28 @@
         </is>
       </c>
       <c r="I67" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>3093159.25</v>
+        <v>3072492</v>
       </c>
       <c r="K67" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L67" s="6" t="n">
-        <v>1889810</v>
+        <v>2946822</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>61.1</v>
+        <v>95.91</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>PODE; MDB; PSD; PDT</t>
+          <t>PP; PT; MDB; PSD</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>DR. DANIEL (PODE); DRA. ALESSANDRA HABER (PODE)</t>
+          <t>AMANDA GENTIL (PP); ÁTILA LIRA (PP)</t>
         </is>
       </c>
     </row>
@@ -13093,12 +13093,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>35.844.647/0001-84</t>
+          <t>30.985.686/0001-88</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>J C SILVA LTDA</t>
+          <t>INK IMPRESSAO DE  MATERIAL PUBLICITARIO, ENCADERNACAO E EDICAO DE CADASTROS LTDA</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -13108,17 +13108,17 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de embalagens de papel</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>TERESINA</t>
+          <t>JOAO PESSOA</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -13127,28 +13127,28 @@
         </is>
       </c>
       <c r="I68" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>3072492</v>
+        <v>3051300</v>
       </c>
       <c r="K68" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>2946822</v>
+        <v>2235665</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>95.91</v>
+        <v>73.27</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>PP; PT; MDB; PSD</t>
+          <t>PSD; PODE; MDB; UNIÃO</t>
         </is>
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>AMANDA GENTIL (PP); ÁTILA LIRA (PP)</t>
+          <t>DOUTOR JHONY (PSD); MERSINHO LUCENA (PSD)</t>
         </is>
       </c>
     </row>
@@ -13158,12 +13158,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>30.985.686/0001-88</t>
+          <t>46.439.622/0001-11</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>INK IMPRESSAO DE  MATERIAL PUBLICITARIO, ENCADERNACAO E EDICAO DE CADASTROS LTDA</t>
+          <t>FEIRA BANDEIRAS E IMPRESSOS LTDA</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -13173,17 +13173,17 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>JOAO PESSOA</t>
+          <t>FEIRA DE SANTANA</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -13192,28 +13192,28 @@
         </is>
       </c>
       <c r="I69" s="5" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>3051300</v>
+        <v>3032135.98</v>
       </c>
       <c r="K69" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L69" s="6" t="n">
-        <v>2235665</v>
+        <v>2828179.49</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>73.27</v>
+        <v>93.27</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>PSD; PODE; MDB; UNIÃO</t>
+          <t>UNIÃO; PT; PSB; PSD</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>DOUTOR JHONY (PSD); MERSINHO LUCENA (PSD)</t>
+          <t>PROFESSORA DAYANE PIMENTEL (UNIÃO); VITOR BONFIM (PSB)</t>
         </is>
       </c>
     </row>
@@ -13353,12 +13353,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>52.272.919/0001-38</t>
+          <t>07.046.094/0001-89</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>JANELA COMUNICACAO LTDA</t>
+          <t>ELYON SOLUCOES GRAFICAS LTDA</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -13387,28 +13387,28 @@
         </is>
       </c>
       <c r="I72" s="5" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>3000000</v>
+        <v>3004398.31</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>3000000</v>
+        <v>1659250.29</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>100</v>
+        <v>55.23</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PL; PSD; PT; PP</t>
         </is>
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>MARCONI PERILLO (PSDB)</t>
+          <t>ZÉ TROVÃO (PL); ÂNGELA MALUF (PSD)</t>
         </is>
       </c>
     </row>
@@ -13418,12 +13418,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>05.677.050/0001-21</t>
+          <t>52.272.919/0001-38</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>ANS IMPRESSOES GRAFICAS LTDA.</t>
+          <t>JANELA COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -13433,17 +13433,17 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -13452,28 +13452,28 @@
         </is>
       </c>
       <c r="I73" s="5" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>2975389.15</v>
+        <v>3000000</v>
       </c>
       <c r="K73" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L73" s="6" t="n">
-        <v>2315402.99</v>
+        <v>3000000</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>77.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>PP; NOVO; PL; PSD</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>ANY ORTIZ (PP); JESSÉ SANGALLI (PL)</t>
+          <t>MARCONI PERILLO (PSDB)</t>
         </is>
       </c>
     </row>
@@ -13483,12 +13483,12 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>07.046.094/0001-89</t>
+          <t>05.677.050/0001-21</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>ELYON SOLUCOES GRAFICAS LTDA</t>
+          <t>ANS IMPRESSOES GRAFICAS LTDA.</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -13498,17 +13498,17 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -13517,28 +13517,28 @@
         </is>
       </c>
       <c r="I74" s="5" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>2974896.09</v>
+        <v>2975389.15</v>
       </c>
       <c r="K74" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L74" s="6" t="n">
-        <v>1534769.67</v>
+        <v>2315402.99</v>
       </c>
       <c r="M74" s="6" t="n">
-        <v>51.59</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>PL; PSD; PT; PP</t>
+          <t>PP; NOVO; PL; PSD</t>
         </is>
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>ZÉ TROVÃO (PL); ÂNGELA MALUF (PSD)</t>
+          <t>ANY ORTIZ (PP); JESSÉ SANGALLI (PL)</t>
         </is>
       </c>
     </row>
@@ -13613,12 +13613,12 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>46.439.622/0001-11</t>
+          <t>47.461.986/0001-60</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>FEIRA BANDEIRAS E IMPRESSOS LTDA</t>
+          <t>BLUEGRAF EDITORA LTDA</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -13628,17 +13628,17 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>FEIRA DE SANTANA</t>
+          <t>GUARULHOS</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -13647,28 +13647,28 @@
         </is>
       </c>
       <c r="I76" s="5" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>2956779.23</v>
+        <v>2952478.38</v>
       </c>
       <c r="K76" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L76" s="6" t="n">
-        <v>2752822.74</v>
+        <v>2370661.08</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>93.09999999999999</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO; PT; PSB; PSD</t>
+          <t>PSD; PL; PODE; PP</t>
         </is>
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>PROFESSORA DAYANE PIMENTEL (UNIÃO); VITOR BONFIM (PSB)</t>
+          <t>WALTER IHOSHI (PSD); DRA. SANDRA TADEU (PL)</t>
         </is>
       </c>
     </row>
@@ -13678,12 +13678,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>47.461.986/0001-60</t>
+          <t>00.212.872/0001-13</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>BLUEGRAF EDITORA LTDA</t>
+          <t>ASA SUL INDUSTRIA E COMERCIO DE MALHAS LTDA</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -13693,17 +13693,17 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Confecção de peças do vestuário, exceto roupas íntimas</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>GUARULHOS</t>
+          <t>FORTALEZA</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -13712,28 +13712,28 @@
         </is>
       </c>
       <c r="I77" s="5" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>2952478.38</v>
+        <v>2908749</v>
       </c>
       <c r="K77" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L77" s="6" t="n">
-        <v>2370661.08</v>
+        <v>2611639</v>
       </c>
       <c r="M77" s="6" t="n">
-        <v>80.29000000000001</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>PSD; PL; PODE; PP</t>
+          <t>PSB; PT; UNIÃO; PRD</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>WALTER IHOSHI (PSD); DRA. SANDRA TADEU (PL)</t>
+          <t>DAYANY DO CAPITÃO (UNIÃO); TAINAH MARINHO (PSB)</t>
         </is>
       </c>
     </row>
@@ -13743,12 +13743,12 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>00.212.872/0001-13</t>
+          <t>09.521.937/0001-87</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>ASA SUL INDUSTRIA E COMERCIO DE MALHAS LTDA</t>
+          <t>ECOPRINT SERVICOS GRAFICOS LTDA</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Confecção de peças do vestuário, exceto roupas íntimas</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>FORTALEZA</t>
+          <t>JUAZEIRO DO NORTE</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -13777,28 +13777,28 @@
         </is>
       </c>
       <c r="I78" s="5" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>2908749</v>
+        <v>2893829.38</v>
       </c>
       <c r="K78" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L78" s="6" t="n">
-        <v>2611639</v>
+        <v>2803418.38</v>
       </c>
       <c r="M78" s="6" t="n">
-        <v>89.79000000000001</v>
+        <v>96.88</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>PSB; PT; UNIÃO; PRD</t>
+          <t>MDB; CIDADANIA; PSD; UNIÃO</t>
         </is>
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>DAYANY DO CAPITÃO (UNIÃO); TAINAH MARINHO (PSB)</t>
+          <t>YURY DO PAREDÃO (MDB); SANDRINHA CAVALCANTE (CIDADANIA)</t>
         </is>
       </c>
     </row>
@@ -13808,12 +13808,12 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>09.521.937/0001-87</t>
+          <t>56.019.930/0001-41</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>ECOPRINT SERVICOS GRAFICOS LTDA</t>
+          <t>INOVE IMPRESSOES GRAFICAS E MARKETING POLITICO LTDA</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -13828,12 +13828,12 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>JUAZEIRO DO NORTE</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -13842,28 +13842,28 @@
         </is>
       </c>
       <c r="I79" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>2893829.38</v>
+        <v>2803233.41</v>
       </c>
       <c r="K79" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L79" s="6" t="n">
-        <v>2803418.38</v>
+        <v>1861331.53</v>
       </c>
       <c r="M79" s="6" t="n">
-        <v>96.88</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>MDB; CIDADANIA; PSD; UNIÃO</t>
+          <t>PL; PSB; UNIÃO; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>YURY DO PAREDÃO (MDB); SANDRINHA CAVALCANTE (CIDADANIA)</t>
+          <t>VINICIUS DINIZ (PL); BERNARDO ROSSI (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>56.019.930/0001-41</t>
+          <t>60.496.721/0001-66</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>INOVE IMPRESSOES GRAFICAS E MARKETING POLITICO LTDA</t>
+          <t>LRS COMUNICACAO E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -13888,17 +13888,17 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -13907,28 +13907,28 @@
         </is>
       </c>
       <c r="I80" s="5" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>2803233.41</v>
+        <v>2800000</v>
       </c>
       <c r="K80" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L80" s="6" t="n">
-        <v>1861331.53</v>
+        <v>1585000</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>66.40000000000001</v>
+        <v>56.61</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>PL; PSB; UNIÃO; REPUBLICANOS</t>
+          <t>REDE; PSD; PSOL; PT</t>
         </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>VINICIUS DINIZ (PL); BERNARDO ROSSI (UNIÃO)</t>
+          <t>MARINA SILVA (REDE); RACHEL SHEHERAZADE (PSD)</t>
         </is>
       </c>
     </row>
@@ -13938,12 +13938,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>60.496.721/0001-66</t>
+          <t>64.433.090/0001-97</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>LRS COMUNICACAO E CONSULTORIA LTDA</t>
+          <t>GAB INDUSTRIA GRAFICA LTDA</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -13953,17 +13953,17 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>NEROPOLIS</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -13972,28 +13972,28 @@
         </is>
       </c>
       <c r="I81" s="5" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>2800000</v>
+        <v>2762102.16</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L81" s="6" t="n">
-        <v>1585000</v>
+        <v>2474316.85</v>
       </c>
       <c r="M81" s="6" t="n">
-        <v>56.61</v>
+        <v>89.58</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>REDE; PSD; PSOL; PT</t>
+          <t>UNIÃO; PT; MDB; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>MARINA SILVA (REDE); RACHEL SHEHERAZADE (PSD)</t>
+          <t>GRACINHA CAIADO (UNIÃO); MARUSSA BOLDRIN (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -14068,12 +14068,12 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>64.433.090/0001-97</t>
+          <t>17.620.604/0001-33</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>GAB INDUSTRIA GRAFICA LTDA</t>
+          <t>T. P. MONTENEGRO GRAFICA LTDA</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -14083,17 +14083,17 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Edição de livros</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>NEROPOLIS</t>
+          <t>BELEM</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -14102,28 +14102,28 @@
         </is>
       </c>
       <c r="I83" s="5" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>2747145.04</v>
+        <v>2715232.4</v>
       </c>
       <c r="K83" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L83" s="6" t="n">
-        <v>2450822.55</v>
+        <v>558352</v>
       </c>
       <c r="M83" s="6" t="n">
-        <v>89.20999999999999</v>
+        <v>20.56</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO; PT; MDB; REPUBLICANOS</t>
+          <t>MDB; PSD; PODE; UNIÃO</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>GRACINHA CAIADO (UNIÃO); MARUSSA BOLDRIN (REPUBLICANOS)</t>
+          <t>ANTONIO DOIDO (MDB); DR. FURLAN (PSD)</t>
         </is>
       </c>
     </row>
@@ -14133,12 +14133,12 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>17.620.604/0001-33</t>
+          <t>20.174.243/0001-53</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>T. P. MONTENEGRO GRAFICA LTDA</t>
+          <t>GUIA SERVICOS DE COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -14148,17 +14148,17 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Edição de livros</t>
+          <t>Outras atividades de prestação de serviços de informação não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>BELEM</t>
+          <t>JOAO PESSOA</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -14167,28 +14167,28 @@
         </is>
       </c>
       <c r="I84" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>2715232.4</v>
+        <v>2670000</v>
       </c>
       <c r="K84" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L84" s="6" t="n">
-        <v>558352</v>
+        <v>2070000</v>
       </c>
       <c r="M84" s="6" t="n">
-        <v>20.56</v>
+        <v>77.53</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>MDB; PSD; PODE; UNIÃO</t>
+          <t>MDB; PL; PSD; PP</t>
         </is>
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>ANTONIO DOIDO (MDB); DR. FURLAN (PSD)</t>
+          <t>CÍCERO LUCENA (MDB); EDUARDO GOMES (PL)</t>
         </is>
       </c>
     </row>
@@ -14198,12 +14198,12 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>20.174.243/0001-53</t>
+          <t>49.925.441/0001-93</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>GUIA SERVICOS DE COMUNICACAO LTDA</t>
+          <t>2HC CRIATIVIDADE E PRODUCOES LTDA</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -14213,17 +14213,17 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Outras atividades de prestação de serviços de informação não especificadas anteriormente</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>JOAO PESSOA</t>
+          <t>MOSSORO</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -14235,25 +14235,25 @@
         <v>7</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>2670000</v>
+        <v>2630000</v>
       </c>
       <c r="K85" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L85" s="6" t="n">
-        <v>2070000</v>
+        <v>1230000</v>
       </c>
       <c r="M85" s="6" t="n">
-        <v>77.53</v>
+        <v>46.77</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>MDB; PL; PSD; PP</t>
+          <t>UNIÃO; AVANTE; REPUBLICANOS; PL</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>CÍCERO LUCENA (MDB); EDUARDO GOMES (PL)</t>
+          <t>ALLYSON (UNIÃO); DANI RIBEIRO (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -14263,12 +14263,12 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>49.925.441/0001-93</t>
+          <t>51.615.351/0001-48</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>2HC CRIATIVIDADE E PRODUCOES LTDA</t>
+          <t>ART MUSIC STUDIO PRODUTORA DE AUDIO   VIDEO LTDA</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -14278,17 +14278,17 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Atividades de gravação de som e de edição de música</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>MOSSORO</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -14297,28 +14297,28 @@
         </is>
       </c>
       <c r="I86" s="5" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>2630000</v>
+        <v>2614250</v>
       </c>
       <c r="K86" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L86" s="6" t="n">
-        <v>1230000</v>
+        <v>1064250</v>
       </c>
       <c r="M86" s="6" t="n">
-        <v>46.77</v>
+        <v>40.71</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO; AVANTE; REPUBLICANOS; PL</t>
+          <t>PSD; PL; PSDB; PDT</t>
         </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>ALLYSON (UNIÃO); DANI RIBEIRO (UNIÃO)</t>
+          <t>LAUREZ MOREIRA (PSD); FILIPE MARTINS (PL)</t>
         </is>
       </c>
     </row>
@@ -14328,12 +14328,12 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>51.615.351/0001-48</t>
+          <t>16.724.877/0001-65</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>ART MUSIC STUDIO PRODUTORA DE AUDIO   VIDEO LTDA</t>
+          <t>EBA - COMUNICACAO E MARKETING POLITICO LTDA</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -14343,17 +14343,17 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Atividades de gravação de som e de edição de música</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>NATAL</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -14362,28 +14362,28 @@
         </is>
       </c>
       <c r="I87" s="5" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>2614250</v>
+        <v>2590000</v>
       </c>
       <c r="K87" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L87" s="6" t="n">
-        <v>1064250</v>
+        <v>750000</v>
       </c>
       <c r="M87" s="6" t="n">
-        <v>40.71</v>
+        <v>28.96</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>PSD; PL; PSDB; PDT</t>
+          <t>PL; PODE; PSDB</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>LAUREZ MOREIRA (PSD); FILIPE MARTINS (PL)</t>
+          <t>ÁLVARO DIAS (PL); STYVENSON VALENTIM (PODE)</t>
         </is>
       </c>
     </row>
@@ -14393,12 +14393,12 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>16.724.877/0001-65</t>
+          <t>31.321.080/0001-00</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>EBA - COMUNICACAO E MARKETING POLITICO LTDA</t>
+          <t>UNIGRAFICA INDUSTRIA GRAFICA LTDA</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Fabricação de embalagens de papel</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>NATAL</t>
+          <t>PARNAMIRIM</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -14427,28 +14427,28 @@
         </is>
       </c>
       <c r="I88" s="5" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>2590000</v>
+        <v>2583889.36</v>
       </c>
       <c r="K88" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L88" s="6" t="n">
-        <v>750000</v>
+        <v>1848705</v>
       </c>
       <c r="M88" s="6" t="n">
-        <v>28.96</v>
+        <v>71.55</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>PL; PODE; PSDB</t>
+          <t>PL; UNIÃO; PSD; PP</t>
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>ÁLVARO DIAS (PL); STYVENSON VALENTIM (PODE)</t>
+          <t>JUNINHO SAIA RODADA (PL); ZENAIDE MAIA (PSD)</t>
         </is>
       </c>
     </row>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>31.321.080/0001-00</t>
+          <t>67.820.413/0001-93</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>UNIGRAFICA INDUSTRIA GRAFICA LTDA</t>
+          <t>LGS SERVICOS LTDA</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -14473,17 +14473,17 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de embalagens de papel</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>PARNAMIRIM</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -14492,28 +14492,28 @@
         </is>
       </c>
       <c r="I89" s="5" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>2583889.36</v>
+        <v>2568850</v>
       </c>
       <c r="K89" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L89" s="6" t="n">
-        <v>1848705</v>
+        <v>2259050</v>
       </c>
       <c r="M89" s="6" t="n">
-        <v>71.55</v>
+        <v>87.94</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>PL; UNIÃO; PSD; PP</t>
+          <t>PSD; REPUBLICANOS; UNIÃO; PL</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>JUNINHO SAIA RODADA (PL); ZENAIDE MAIA (PSD)</t>
+          <t>CAPITÃO SAMUEL (UNIÃO); GRACINHA GARCEZ (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -14523,12 +14523,12 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>67.820.413/0001-93</t>
+          <t>64.752.158/0001-09</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>LGS SERVICOS LTDA</t>
+          <t>OKAN COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -14538,17 +14538,17 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -14557,28 +14557,28 @@
         </is>
       </c>
       <c r="I90" s="5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>2568850</v>
+        <v>2567000</v>
       </c>
       <c r="K90" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L90" s="6" t="n">
-        <v>2259050</v>
+        <v>2517000</v>
       </c>
       <c r="M90" s="6" t="n">
-        <v>87.94</v>
+        <v>98.05</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>PSD; REPUBLICANOS; UNIÃO; PL</t>
+          <t>PT; PSOL; UNIÃO</t>
         </is>
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>CAPITÃO SAMUEL (UNIÃO); GRACINHA GARCEZ (REPUBLICANOS)</t>
+          <t>PATRUS ANANIAS (PT); DUDA SALABERT (PSOL)</t>
         </is>
       </c>
     </row>
@@ -14588,12 +14588,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>64.752.158/0001-09</t>
+          <t>17.340.447/0001-02</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>OKAN COMUNICACAO LTDA</t>
+          <t>MARICLEYDSON COSTA DA SILVA  LTDA</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -14603,17 +14603,17 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>NATAL</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -14622,28 +14622,28 @@
         </is>
       </c>
       <c r="I91" s="5" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>2567000</v>
+        <v>2563744.6</v>
       </c>
       <c r="K91" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L91" s="6" t="n">
-        <v>2517000</v>
+        <v>1790382.1</v>
       </c>
       <c r="M91" s="6" t="n">
-        <v>98.05</v>
+        <v>69.83</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>PT; PSOL; UNIÃO</t>
+          <t>PL; PT; PV; PDT</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>PATRUS ANANIAS (PT); DUDA SALABERT (PSOL)</t>
+          <t>NINA (PL); LUÍZ EDUARDO (PL)</t>
         </is>
       </c>
     </row>
@@ -14653,12 +14653,12 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>17.340.447/0001-02</t>
+          <t>26.983.273/0001-97</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>MARICLEYDSON COSTA DA SILVA  LTDA</t>
+          <t>VITORINO   MENDONCA LTDA</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -14668,17 +14668,17 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>NATAL</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -14687,28 +14687,28 @@
         </is>
       </c>
       <c r="I92" s="5" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>2559953</v>
+        <v>2550000</v>
       </c>
       <c r="K92" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L92" s="6" t="n">
-        <v>1786590.5</v>
+        <v>2200000</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>69.79000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>PL; PT; PV; PDT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>NINA (PL); LUÍZ EDUARDO (PL)</t>
+          <t>WILDER MORAIS (PL); MARCOS ROGÉRIO (PL)</t>
         </is>
       </c>
     </row>
@@ -14718,12 +14718,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>26.983.273/0001-97</t>
+          <t>35.593.706/0001-99</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>VITORINO   MENDONCA LTDA</t>
+          <t>UNIPAUTA FORMULARIOS LTDA</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -14733,17 +14733,17 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Impressão de material de segurança</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>OLINDA</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -14752,28 +14752,28 @@
         </is>
       </c>
       <c r="I93" s="5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>2550000</v>
+        <v>2531795</v>
       </c>
       <c r="K93" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L93" s="6" t="n">
-        <v>1950000</v>
+        <v>2316995</v>
       </c>
       <c r="M93" s="6" t="n">
-        <v>76.47</v>
+        <v>91.52</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>MDB; PCDOB; REPUBLICANOS; PODE</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>WILDER MORAIS (PL); MARCOS ROGÉRIO (PL)</t>
+          <t>IZA ARRUDA (MDB); RENILDO CALHEIROS (PCDOB)</t>
         </is>
       </c>
     </row>
@@ -14783,12 +14783,12 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>35.593.706/0001-99</t>
+          <t>15.687.382/0001-40</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>UNIPAUTA FORMULARIOS LTDA</t>
+          <t>CARAMBOLA PRODUCOES LTDA</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -14798,17 +14798,17 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Impressão de material de segurança</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>OLINDA</t>
+          <t>BALNEARIO CAMBORIU</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -14817,28 +14817,28 @@
         </is>
       </c>
       <c r="I94" s="5" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>2531795</v>
+        <v>2513200</v>
       </c>
       <c r="K94" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L94" s="6" t="n">
-        <v>2316995</v>
+        <v>2513200</v>
       </c>
       <c r="M94" s="6" t="n">
-        <v>91.52</v>
+        <v>100</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>MDB; PCDOB; REPUBLICANOS; PODE</t>
+          <t>PDT; PL</t>
         </is>
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>IZA ARRUDA (MDB); RENILDO CALHEIROS (PCDOB)</t>
+          <t>REQUIÃO FILHO (PDT); THIAGO AURICCHIO (PL)</t>
         </is>
       </c>
     </row>
@@ -14848,12 +14848,12 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>15.687.382/0001-40</t>
+          <t>05.555.136/0001-81</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>CARAMBOLA PRODUCOES LTDA</t>
+          <t>CONDADO MARKETING LTDA</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -14863,17 +14863,17 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>BALNEARIO CAMBORIU</t>
+          <t>LAJEADO</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -14882,28 +14882,28 @@
         </is>
       </c>
       <c r="I95" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>2513200</v>
+        <v>2500000</v>
       </c>
       <c r="K95" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L95" s="6" t="n">
-        <v>2513200</v>
+        <v>2500000</v>
       </c>
       <c r="M95" s="6" t="n">
         <v>100</v>
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>PDT; PL</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>REQUIÃO FILHO (PDT); THIAGO AURICCHIO (PL)</t>
+          <t>JULIANA BRIZOLA (PDT)</t>
         </is>
       </c>
     </row>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>68.154.614/0001-61</t>
+          <t>22.966.876/0001-20</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>ESTUDIO 90 PRODUCOES LTDA</t>
+          <t>REDE DE NEGOCIOS E PRODUCAO DE EVENTOS LTDA</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -14928,17 +14928,17 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Atividades de organização de eventos, exceto culturais e esportivos</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="I96" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J96" s="6" t="n">
         <v>2500000</v>
@@ -14956,19 +14956,19 @@
         <v>0.05</v>
       </c>
       <c r="L96" s="6" t="n">
-        <v>2500000</v>
+        <v>1000000</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t>MDB; PSD</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>GABRIEL SOUZA (MDB); FREDERICO ANTUNES (PSD)</t>
+          <t>RAQUEL LYRA (PSD)</t>
         </is>
       </c>
     </row>
@@ -14978,12 +14978,12 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>22.966.876/0001-20</t>
+          <t>68.154.614/0001-61</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>REDE DE NEGOCIOS E PRODUCAO DE EVENTOS LTDA</t>
+          <t>ESTUDIO 90 PRODUCOES LTDA</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -14993,17 +14993,17 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Atividades de organização de eventos, exceto culturais e esportivos</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -15012,7 +15012,7 @@
         </is>
       </c>
       <c r="I97" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J97" s="6" t="n">
         <v>2500000</v>
@@ -15021,19 +15021,19 @@
         <v>0.05</v>
       </c>
       <c r="L97" s="6" t="n">
-        <v>1000000</v>
+        <v>2500000</v>
       </c>
       <c r="M97" s="6" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>MDB; PSD</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>RAQUEL LYRA (PSD)</t>
+          <t>GABRIEL SOUZA (MDB); FREDERICO ANTUNES (PSD)</t>
         </is>
       </c>
     </row>
@@ -15043,12 +15043,12 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>05.555.136/0001-81</t>
+          <t>23.929.195/0001-54</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>CONDADO MARKETING LTDA</t>
+          <t>SERATA EDITORA GRAFICA E PUBLICIDADE LTDA</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -15058,17 +15058,17 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>LAJEADO</t>
+          <t>CUIABA</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -15077,28 +15077,28 @@
         </is>
       </c>
       <c r="I98" s="5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J98" s="6" t="n">
-        <v>2500000</v>
+        <v>2482058.21</v>
       </c>
       <c r="K98" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L98" s="6" t="n">
-        <v>2500000</v>
+        <v>1543613.61</v>
       </c>
       <c r="M98" s="6" t="n">
-        <v>100</v>
+        <v>62.19</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PL; REPUBLICANOS; PV; PT</t>
         </is>
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t>JULIANA BRIZOLA (PDT)</t>
+          <t>CORONEL FERNANDA (PL); ZÉ MEDEIROS (PL)</t>
         </is>
       </c>
     </row>
@@ -15108,12 +15108,12 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>23.929.195/0001-54</t>
+          <t>14.876.708/0001-15</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>SERATA EDITORA GRAFICA E PUBLICIDADE LTDA</t>
+          <t>NOGUEIRA, ALBUQUERQUE E FREIRE ASSOCIADOS S/S</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -15123,17 +15123,17 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Atividades de contabilidade, consultoria e auditoria contábil e tributária</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>CUIABA</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -15142,28 +15142,28 @@
         </is>
       </c>
       <c r="I99" s="5" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>2482058.21</v>
+        <v>2474000</v>
       </c>
       <c r="K99" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L99" s="6" t="n">
-        <v>1543613.61</v>
+        <v>820500</v>
       </c>
       <c r="M99" s="6" t="n">
-        <v>62.19</v>
+        <v>33.16</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>PL; REPUBLICANOS; PV; PT</t>
+          <t>MDB; PP; PL; PSDB</t>
         </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>CORONEL FERNANDA (PL); ZÉ MEDEIROS (PL)</t>
+          <t>ARTHUR LIRA (PP); DANIEL BARBOSA (PP)</t>
         </is>
       </c>
     </row>
@@ -15173,12 +15173,12 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>14.876.708/0001-15</t>
+          <t>41.220.067/0001-19</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>NOGUEIRA, ALBUQUERQUE E FREIRE ASSOCIADOS S/S</t>
+          <t>JMARTELO SOLUCOES EM COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -15188,17 +15188,17 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Atividades de contabilidade, consultoria e auditoria contábil e tributária</t>
+          <t>Fotocópias, preparação de documentos e outros serviços especializados de apoio administrativo</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -15207,28 +15207,28 @@
         </is>
       </c>
       <c r="I100" s="5" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>2474000</v>
+        <v>2400000</v>
       </c>
       <c r="K100" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L100" s="6" t="n">
-        <v>820500</v>
+        <v>1600000</v>
       </c>
       <c r="M100" s="6" t="n">
-        <v>33.16</v>
+        <v>66.67</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
         <is>
-          <t>MDB; PP; PL; PSDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t>ARTHUR LIRA (PP); DANIEL BARBOSA (PP)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -15238,12 +15238,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>41.220.067/0001-19</t>
+          <t>25.358.819/0001-56</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>JMARTELO SOLUCOES EM COMUNICACAO LTDA</t>
+          <t>MIOLO COMUNICACAO GRAFICA E EDITORA LTDA</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -15253,17 +15253,17 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Fotocópias, preparação de documentos e outros serviços especializados de apoio administrativo</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -15272,28 +15272,28 @@
         </is>
       </c>
       <c r="I101" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>2400000</v>
+        <v>2343940.2</v>
       </c>
       <c r="K101" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L101" s="6" t="n">
-        <v>1600000</v>
+        <v>2322135</v>
       </c>
       <c r="M101" s="6" t="n">
-        <v>66.67</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PL; PDT</t>
         </is>
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>FLAVIO BOLSONARO (PL); EVANDRO ARAUJO (PL)</t>
         </is>
       </c>
     </row>
@@ -15303,12 +15303,12 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>25.358.819/0001-56</t>
+          <t>06.340.575/0001-30</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>MIOLO COMUNICACAO GRAFICA E EDITORA LTDA</t>
+          <t>MAVIMIX ADESIVOS DECORATIVOS LTDA</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -15318,17 +15318,17 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Comércio varejista de outros produtos novos não especificados anteriormente</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -15337,28 +15337,28 @@
         </is>
       </c>
       <c r="I102" s="5" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J102" s="6" t="n">
-        <v>2343940.2</v>
+        <v>2304363.37</v>
       </c>
       <c r="K102" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L102" s="6" t="n">
-        <v>2322135</v>
+        <v>1795898.68</v>
       </c>
       <c r="M102" s="6" t="n">
-        <v>99.06999999999999</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
-          <t>PL; PDT</t>
+          <t>UNIÃO; REPUBLICANOS; PL; PRD</t>
         </is>
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL); EVANDRO ARAUJO (PL)</t>
+          <t>RUEDA (UNIÃO); WAGUINHO (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -15368,12 +15368,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>06.340.575/0001-30</t>
+          <t>31.792.812/0001-40</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>MAVIMIX ADESIVOS DECORATIVOS LTDA</t>
+          <t>SANTIER CONSULTORIA E ESTRATEGIA LTDA</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -15383,17 +15383,17 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Comércio varejista de outros produtos novos não especificados anteriormente</t>
+          <t>Outras atividades de prestação de serviços de informação não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -15402,28 +15402,28 @@
         </is>
       </c>
       <c r="I103" s="5" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>2304363.37</v>
+        <v>2302560</v>
       </c>
       <c r="K103" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L103" s="6" t="n">
-        <v>1795898.68</v>
+        <v>1369560</v>
       </c>
       <c r="M103" s="6" t="n">
-        <v>77.93000000000001</v>
+        <v>59.48</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO; REPUBLICANOS; PL; PRD</t>
+          <t>PT; PSOL; AVANTE; PODE</t>
         </is>
       </c>
       <c r="O103" s="4" t="inlineStr">
         <is>
-          <t>RUEDA (UNIÃO); WAGUINHO (REPUBLICANOS)</t>
+          <t>FÁBIO TRAD (PT); ÁUREA CAROLINA (PSOL)</t>
         </is>
       </c>
     </row>
@@ -15433,12 +15433,12 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>31.792.812/0001-40</t>
+          <t>08.668.296/0001-25</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>SANTIER CONSULTORIA E ESTRATEGIA LTDA</t>
+          <t>COTA PESQUISAS DE MERCADO E DE OPINIAO PUBLICA LTDA</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -15448,17 +15448,17 @@
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>Outras atividades de prestação de serviços de informação não especificadas anteriormente</t>
+          <t>Pesquisas de mercado e de opinião pública</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>CURITIBA</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
@@ -15467,42 +15467,42 @@
         </is>
       </c>
       <c r="I104" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>2302560</v>
+        <v>2302500</v>
       </c>
       <c r="K104" s="9" t="n">
         <v>0.05</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>1369560</v>
+        <v>1609250</v>
       </c>
       <c r="M104" s="9" t="n">
-        <v>59.48</v>
+        <v>69.89</v>
       </c>
       <c r="N104" s="7" t="inlineStr">
         <is>
-          <t>PT; PSOL; AVANTE; PODE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O104" s="7" t="inlineStr">
         <is>
-          <t>FÁBIO TRAD (PT); ÁUREA CAROLINA (PSOL)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -15543,7 +15543,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="33" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -15626,13 +15626,13 @@
         <v>1417</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1992</v>
+        <v>1995</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>970908352.83</v>
+        <v>971778352.83</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>14.8</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="6">
@@ -15655,16 +15655,16 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2201</v>
+        <v>2206</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>597661752.99</v>
+        <v>597767672.99</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="7">
@@ -15690,13 +15690,13 @@
         <v>704</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>528558048.97</v>
+        <v>532558048.97</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>8.06</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="8">
@@ -15728,7 +15728,7 @@
         <v>486877337.61</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>7.42</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="9">
@@ -15754,13 +15754,13 @@
         <v>798</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>472861618.52</v>
+        <v>472886618.52</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>7.21</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="10">
@@ -15786,13 +15786,13 @@
         <v>1035</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>402749251.3</v>
+        <v>402817607.56</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="11">
@@ -15824,7 +15824,7 @@
         <v>361936325.06</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>5.52</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="12">
@@ -15850,10 +15850,10 @@
         <v>841</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>233478027.03</v>
+        <v>233648027.03</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>3.56</v>
@@ -15888,7 +15888,7 @@
         <v>208376091.46</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="14">
@@ -15914,13 +15914,13 @@
         <v>596</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>142219368.76</v>
+        <v>142245368.76</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="15">
@@ -15978,10 +15978,10 @@
         <v>701</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>122213891.09</v>
+        <v>122283891.09</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>1.86</v>
@@ -16010,13 +16010,13 @@
         <v>866</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>89588574.70999999</v>
+        <v>89500982.73</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="18">
@@ -16042,10 +16042,10 @@
         <v>538</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>80943165.18000001</v>
+        <v>81043165.18000001</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>1.23</v>
@@ -16074,10 +16074,10 @@
         <v>339</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>66436322.27</v>
+        <v>66486322.27</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>1.01</v>
@@ -16170,13 +16170,13 @@
         <v>151</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1873</v>
+        <v>1890</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>46007278.74</v>
+        <v>46436245.26</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="23">
@@ -16208,7 +16208,7 @@
         <v>42351998</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="24">
@@ -16330,10 +16330,10 @@
         <v>68</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>17353148</v>
+        <v>17353154.4</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>0.26</v>
@@ -16359,13 +16359,13 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>2454</v>
+        <v>2466</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>16154251.98</v>
+        <v>16186752.98</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0.25</v>
@@ -16455,13 +16455,13 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>10733909.15</v>
+        <v>10753769.15</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>0.16</v>
@@ -16615,13 +16615,13 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>6887480.7</v>
+        <v>6888472.45</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>0.1</v>
@@ -16717,7 +16717,7 @@
         <v>804</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>6399278.84</v>
+        <v>6398441.92</v>
       </c>
       <c r="H39" s="6" t="n">
         <v>0.1</v>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS RIO GRANDE DO SUL - RS - ESTADUAL</t>
+          <t>SOLIDARIEDADE-RIO DE JANEIRO-RJ-ESTADUAL</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -16867,17 +16867,17 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>256</v>
+        <v>47</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>5361904</v>
+        <v>5372830</v>
       </c>
       <c r="H44" s="6" t="n">
         <v>0.08</v>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE-RIO DE JANEIRO-RJ-ESTADUAL</t>
+          <t>REPUBLICANOS RIO GRANDE DO SUL - RS - ESTADUAL</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -16899,17 +16899,17 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>46</v>
+        <v>256</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>5361550</v>
+        <v>5361904</v>
       </c>
       <c r="H45" s="6" t="n">
         <v>0.08</v>
@@ -17095,13 +17095,13 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>5025435.02</v>
+        <v>5029256.29</v>
       </c>
       <c r="H51" s="6" t="n">
         <v>0.08</v>
@@ -17206,14 +17206,14 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -17313,10 +17313,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>940060770.7</v>
+        <v>941059970.52</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>12.92</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="6">
@@ -17336,10 +17336,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>772962838.47</v>
+        <v>773225038.47</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>10.62</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="7">
@@ -17359,7 +17359,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>538525118.08</v>
+        <v>539785425.37</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>7.4</v>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>501106811.34</v>
+        <v>501598033.74</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>6.89</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="9">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>347986863.58</v>
+        <v>348267772.86</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>4.78</v>
@@ -17428,10 +17428,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>346492424.23</v>
+        <v>346616717.24</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>4.76</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="11">
@@ -17451,10 +17451,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>319520408.32</v>
+        <v>319738833.72</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="12">
@@ -17474,10 +17474,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>260456309.01</v>
+        <v>260541558.01</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="13">
@@ -17497,10 +17497,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>248537140.7</v>
+        <v>248624871.27</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="14">
@@ -17520,7 +17520,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>232263101.77</v>
+        <v>232655729.4</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>3.19</v>
@@ -17543,7 +17543,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>223564597.48</v>
+        <v>223689101.98</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>3.07</v>
@@ -17566,7 +17566,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>216342827.56</v>
+        <v>216368096.53</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>2.97</v>
@@ -17589,7 +17589,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>206637988.78</v>
+        <v>206745533</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>2.84</v>
@@ -17612,7 +17612,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>191486245.93</v>
+        <v>191668164.35</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>2.63</v>
@@ -17635,7 +17635,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>189101995.69</v>
+        <v>189498535.69</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>2.6</v>
@@ -17658,7 +17658,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>176329731.25</v>
+        <v>176399645.6</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>2.42</v>
@@ -17681,10 +17681,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>162669914.67</v>
+        <v>162804286.45</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="22">
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>149546550.28</v>
+        <v>149704962.6</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="23">
@@ -17727,10 +17727,10 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>146374557.1</v>
+        <v>147117921.93</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="24">
@@ -17750,10 +17750,10 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>145326561.75</v>
+        <v>145328090.58</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="25">
@@ -17764,19 +17764,19 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Acre</t>
+          <t>Rio Grande do Norte</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>134802502.61</v>
+        <v>135306463.94</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="26">
@@ -17787,19 +17787,19 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Norte</t>
+          <t>Acre</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>127266043.44</v>
+        <v>134802502.61</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="27">
@@ -17819,7 +17819,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>123124375.75</v>
+        <v>123147279.67</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>1.69</v>
@@ -17842,10 +17842,10 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>118839693.01</v>
+        <v>121101896.75</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="29">
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>118101205.06</v>
+        <v>118148055.06</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>1.62</v>
@@ -17888,7 +17888,7 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>116218732.63</v>
+        <v>116578380.72</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>1.6</v>
@@ -17914,7 +17914,7 @@
         <v>116096217.41</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="32">
@@ -17934,10 +17934,10 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>105896079.13</v>
+        <v>105927367.84</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="33">
@@ -17957,10 +17957,10 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>148115915.91</v>
+        <v>148128914.06</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>23.88</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="34">
@@ -17983,7 +17983,7 @@
         <v>63540943.62</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>10.24</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="35">
@@ -18003,10 +18003,10 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>35734691.7</v>
+        <v>35742843.27</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="36">
@@ -18026,10 +18026,10 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>31656290.85</v>
+        <v>32343843.12</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>5.1</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="37">
@@ -18049,10 +18049,10 @@
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>30505223.61</v>
+        <v>30508223.61</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>4.92</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="38">
@@ -18072,10 +18072,10 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>27968964.14</v>
+        <v>28214065.41</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>4.51</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="39">
@@ -18095,10 +18095,10 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>22089689.69</v>
+        <v>22096617.42</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="40">
@@ -18121,7 +18121,7 @@
         <v>21166735.92</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="41">
@@ -18144,7 +18144,7 @@
         <v>18066288.75</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="42">
@@ -18167,7 +18167,7 @@
         <v>17840460.01</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="43">
@@ -18190,7 +18190,7 @@
         <v>17640588</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="44">
@@ -18213,7 +18213,7 @@
         <v>17151108.64</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="45">
@@ -18233,10 +18233,10 @@
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>16319200.1</v>
+        <v>16369200.1</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="46">
@@ -18259,7 +18259,7 @@
         <v>15904796.74</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="47">
@@ -18282,7 +18282,7 @@
         <v>15345139.27</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="48">
@@ -18293,19 +18293,19 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>12942292.35</v>
+        <v>14752756.34</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2.09</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="49">
@@ -18316,19 +18316,19 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Rio Grande do Norte</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>12561528.57</v>
+        <v>14693216.87</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="50">
@@ -18339,19 +18339,19 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Amapá</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>12135824.21</v>
+        <v>12944500.35</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="51">
@@ -18362,19 +18362,19 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>11635177.76</v>
+        <v>12135824.21</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="52">
@@ -18385,19 +18385,19 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>10541115.61</v>
+        <v>11635177.76</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="53">
@@ -18408,19 +18408,19 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Paraíba</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>10241492.54</v>
+        <v>10541115.61</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="54">
@@ -18431,19 +18431,19 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>8166532.99</v>
+        <v>10241492.54</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="55">
@@ -18454,19 +18454,19 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso do Sul</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>7868612.31</v>
+        <v>8226531.29</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="56">
@@ -18477,19 +18477,19 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso</t>
+          <t>Mato Grosso do Sul</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>7663506.75</v>
+        <v>7868612.31</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="57">
@@ -18500,19 +18500,19 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Alagoas</t>
+          <t>Mato Grosso</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>7286528.8</v>
+        <v>7663506.75</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="58">
@@ -18523,19 +18523,19 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Pará</t>
+          <t>Alagoas</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>6935311.45</v>
+        <v>7286528.8</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="59">
@@ -18546,19 +18546,19 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Norte</t>
+          <t>Pará</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>6693216.87</v>
+        <v>6935311.45</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="60">
@@ -18578,10 +18578,10 @@
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>6569838.31</v>
+        <v>6499838.31</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="61">
@@ -18601,7 +18601,7 @@
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>621682134.8</v>
+        <v>622102134.8</v>
       </c>
       <c r="E61" s="12" t="n">
         <v>11.48</v>
@@ -18647,7 +18647,7 @@
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>412113586.89</v>
+        <v>412211008.89</v>
       </c>
       <c r="E63" s="12" t="n">
         <v>7.61</v>
@@ -18670,7 +18670,7 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>375428030.54</v>
+        <v>375586208.06</v>
       </c>
       <c r="E64" s="12" t="n">
         <v>6.93</v>
@@ -18693,7 +18693,7 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>282735417.37</v>
+        <v>282869261.37</v>
       </c>
       <c r="E65" s="12" t="n">
         <v>5.22</v>
@@ -18716,7 +18716,7 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>248689457.06</v>
+        <v>248720457.06</v>
       </c>
       <c r="E66" s="12" t="n">
         <v>4.59</v>
@@ -18739,7 +18739,7 @@
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>237550200.29</v>
+        <v>237590400.29</v>
       </c>
       <c r="E67" s="12" t="n">
         <v>4.39</v>
@@ -18762,7 +18762,7 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>199480839.32</v>
+        <v>199505839.32</v>
       </c>
       <c r="E68" s="12" t="n">
         <v>3.68</v>
@@ -18831,7 +18831,7 @@
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>164184836.19</v>
+        <v>164214758.19</v>
       </c>
       <c r="E71" s="12" t="n">
         <v>3.03</v>
@@ -18900,7 +18900,7 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>145779081.5</v>
+        <v>145738001.5</v>
       </c>
       <c r="E74" s="12" t="n">
         <v>2.69</v>
@@ -18946,7 +18946,7 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>127618682.47</v>
+        <v>127622892.47</v>
       </c>
       <c r="E76" s="12" t="n">
         <v>2.36</v>
@@ -19038,10 +19038,10 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>105817480.74</v>
+        <v>106417480.74</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="81">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>92214955.93000001</v>
+        <v>92302455.93000001</v>
       </c>
       <c r="E85" s="12" t="n">
         <v>1.7</v>
@@ -19225,7 +19225,7 @@
         <v>84766787.34</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="89">
@@ -19245,10 +19245,10 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>816318310.92</v>
+        <v>819200968.3099999</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>25.96</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="90">
@@ -19268,7 +19268,7 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>203082907.12</v>
+        <v>203760481.7</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>6.46</v>
@@ -19291,7 +19291,7 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>187133628.35</v>
+        <v>187408260</v>
       </c>
       <c r="E91" s="12" t="n">
         <v>5.95</v>
@@ -19314,10 +19314,10 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>156134142.47</v>
+        <v>156239331.41</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4.97</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="93">
@@ -19337,7 +19337,7 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>140946146.11</v>
+        <v>141222145.56</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>4.48</v>
@@ -19360,7 +19360,7 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>128997084.29</v>
+        <v>129097965.33</v>
       </c>
       <c r="E94" s="12" t="n">
         <v>4.1</v>
@@ -19383,7 +19383,7 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>126475422.23</v>
+        <v>126758185.15</v>
       </c>
       <c r="E95" s="12" t="n">
         <v>4.02</v>
@@ -19406,7 +19406,7 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>118392416.57</v>
+        <v>118476033.04</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>3.76</v>
@@ -19429,10 +19429,10 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>108193086.12</v>
+        <v>108241241.27</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="98">
@@ -19452,10 +19452,10 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>106916431.42</v>
+        <v>107981951.67</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="99">
@@ -19475,7 +19475,7 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>95979166.05</v>
+        <v>96006194.84999999</v>
       </c>
       <c r="E99" s="12" t="n">
         <v>3.05</v>
@@ -19501,7 +19501,7 @@
         <v>93917224.66</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="101">
@@ -19521,7 +19521,7 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>86394050.63</v>
+        <v>86582945.14</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>2.75</v>
@@ -19544,10 +19544,10 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>85232387.48</v>
+        <v>86092672.01000001</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="103">
@@ -19567,10 +19567,10 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>75729443.69</v>
+        <v>75762869.03</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="104">
@@ -19590,7 +19590,7 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>73414734.05</v>
+        <v>73419187.95</v>
       </c>
       <c r="E104" s="12" t="n">
         <v>2.33</v>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>70390028.23999999</v>
+        <v>70424428.56</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="106">
@@ -19636,7 +19636,7 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>60440709.12</v>
+        <v>60503975.33</v>
       </c>
       <c r="E106" s="12" t="n">
         <v>1.92</v>
@@ -19659,7 +19659,7 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>57046236.94</v>
+        <v>57058343.64</v>
       </c>
       <c r="E107" s="12" t="n">
         <v>1.81</v>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>53853536.66</v>
+        <v>53893372</v>
       </c>
       <c r="E108" s="12" t="n">
         <v>1.71</v>
@@ -19705,10 +19705,10 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>53115098.14</v>
+        <v>53447799.64</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="110">
@@ -19751,7 +19751,7 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>48079007.1</v>
+        <v>48103744.51</v>
       </c>
       <c r="E111" s="12" t="n">
         <v>1.53</v>
@@ -19774,7 +19774,7 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>47674109.74</v>
+        <v>47807081.22</v>
       </c>
       <c r="E112" s="12" t="n">
         <v>1.52</v>
@@ -19823,7 +19823,7 @@
         <v>31677684.79</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -19912,10 +19912,10 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>147229523.42</v>
+        <v>147514746.61</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>20.14</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="119">
@@ -19935,10 +19935,10 @@
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>57043535.5</v>
+        <v>57727971.49</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>7.8</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="120">
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>51763069.59</v>
+        <v>51809041.72</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>7.08</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="121">
@@ -19981,10 +19981,10 @@
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>50648871.92</v>
+        <v>50738196.27</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>6.93</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="122">
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>34586869.84</v>
+        <v>34707428.84</v>
       </c>
       <c r="E122" s="12" t="n">
         <v>4.73</v>
@@ -20027,10 +20027,10 @@
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>33434380.5</v>
+        <v>33467956.25</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>4.57</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="124">
@@ -20050,7 +20050,7 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>31275109.75</v>
+        <v>31366123.89</v>
       </c>
       <c r="E124" s="12" t="n">
         <v>4.28</v>
@@ -20073,10 +20073,10 @@
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>28099168.81</v>
+        <v>28100937.52</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="126">
@@ -20096,10 +20096,10 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>22849747.97</v>
+        <v>23009813.25</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="127">
@@ -20119,10 +20119,10 @@
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>22514974.55</v>
+        <v>22535382.27</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="128">
@@ -20142,10 +20142,10 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>22066485.13</v>
+        <v>22087424.13</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="129">
@@ -20165,7 +20165,7 @@
         </is>
       </c>
       <c r="D129" s="6" t="n">
-        <v>21848220.38</v>
+        <v>21898220.38</v>
       </c>
       <c r="E129" s="12" t="n">
         <v>2.99</v>
@@ -20188,10 +20188,10 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>21788261.07</v>
+        <v>21792874.57</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="131">
@@ -20211,10 +20211,10 @@
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>20292390.52</v>
+        <v>20545294.26</v>
       </c>
       <c r="E131" s="12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="132">
@@ -20234,7 +20234,7 @@
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>19744610.73</v>
+        <v>19820402.55</v>
       </c>
       <c r="E132" s="12" t="n">
         <v>2.7</v>
@@ -20257,10 +20257,10 @@
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>16520526.37</v>
+        <v>16520926.37</v>
       </c>
       <c r="E133" s="12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="134">
@@ -20280,7 +20280,7 @@
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>16253407.69</v>
+        <v>16282903.9</v>
       </c>
       <c r="E134" s="12" t="n">
         <v>2.22</v>
@@ -20303,10 +20303,10 @@
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>15780709.38</v>
+        <v>15926469.38</v>
       </c>
       <c r="E135" s="12" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="136">
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>14900852.97</v>
+        <v>14974917.8</v>
       </c>
       <c r="E136" s="12" t="n">
         <v>2.04</v>
@@ -20349,10 +20349,10 @@
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>14584669.27</v>
+        <v>14584812.03</v>
       </c>
       <c r="E137" s="12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="138">
@@ -20395,10 +20395,10 @@
         </is>
       </c>
       <c r="D139" s="6" t="n">
-        <v>10353946.76</v>
+        <v>10355475.59</v>
       </c>
       <c r="E139" s="12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="140">
@@ -20421,7 +20421,7 @@
         <v>9856868.189999999</v>
       </c>
       <c r="E140" s="12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="141">
@@ -20441,10 +20441,10 @@
         </is>
       </c>
       <c r="D141" s="6" t="n">
-        <v>9175658.73</v>
+        <v>9184562.65</v>
       </c>
       <c r="E141" s="12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="142">
@@ -20464,7 +20464,7 @@
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>8615120.220000001</v>
+        <v>8626908.92</v>
       </c>
       <c r="E142" s="12" t="n">
         <v>1.18</v>
@@ -20510,7 +20510,7 @@
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>7776947.8</v>
+        <v>7776948.3</v>
       </c>
       <c r="E144" s="12" t="n">
         <v>1.06</v>
@@ -20533,10 +20533,10 @@
         </is>
       </c>
       <c r="D145" s="6" t="n">
-        <v>97077728.06999999</v>
+        <v>97323954.7</v>
       </c>
       <c r="E145" s="12" t="n">
-        <v>13.81</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="146">
@@ -20556,10 +20556,10 @@
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>79581868.44</v>
+        <v>79841958.22</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>11.32</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="147">
@@ -20579,10 +20579,10 @@
         </is>
       </c>
       <c r="D147" s="6" t="n">
-        <v>50428829.56</v>
+        <v>50691029.56</v>
       </c>
       <c r="E147" s="12" t="n">
-        <v>7.17</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="148">
@@ -20602,10 +20602,10 @@
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>38717032.75</v>
+        <v>38817828.78</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>5.51</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="149">
@@ -20625,10 +20625,10 @@
         </is>
       </c>
       <c r="D149" s="6" t="n">
-        <v>38155289.32</v>
+        <v>38288117.59</v>
       </c>
       <c r="E149" s="12" t="n">
-        <v>5.43</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="150">
@@ -20648,10 +20648,10 @@
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>36899690.99</v>
+        <v>36987278.8</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="151">
@@ -20671,10 +20671,10 @@
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>35025492.79</v>
+        <v>35248529.42</v>
       </c>
       <c r="E151" s="12" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="152">
@@ -20694,10 +20694,10 @@
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>34424142.91</v>
+        <v>34506606.04</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>4.9</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="153">
@@ -20717,10 +20717,10 @@
         </is>
       </c>
       <c r="D153" s="6" t="n">
-        <v>26995578.92</v>
+        <v>27059871.18</v>
       </c>
       <c r="E153" s="12" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="154">
@@ -20740,10 +20740,10 @@
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>26957619.96</v>
+        <v>26992849.96</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="155">
@@ -20763,7 +20763,7 @@
         </is>
       </c>
       <c r="D155" s="6" t="n">
-        <v>24956101.01</v>
+        <v>25043370.51</v>
       </c>
       <c r="E155" s="12" t="n">
         <v>3.55</v>
@@ -20786,7 +20786,7 @@
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>24308225.4</v>
+        <v>24404225.4</v>
       </c>
       <c r="E156" s="12" t="n">
         <v>3.46</v>
@@ -20809,7 +20809,7 @@
         </is>
       </c>
       <c r="D157" s="6" t="n">
-        <v>22003170.89</v>
+        <v>22072470.89</v>
       </c>
       <c r="E157" s="12" t="n">
         <v>3.13</v>
@@ -20832,10 +20832,10 @@
         </is>
       </c>
       <c r="D158" s="6" t="n">
-        <v>21074584.05</v>
+        <v>21099088.55</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="159">
@@ -20855,7 +20855,7 @@
         </is>
       </c>
       <c r="D159" s="6" t="n">
-        <v>20329773.72</v>
+        <v>20388773.72</v>
       </c>
       <c r="E159" s="12" t="n">
         <v>2.89</v>
@@ -20878,10 +20878,10 @@
         </is>
       </c>
       <c r="D160" s="6" t="n">
-        <v>17196062.85</v>
+        <v>17360485.06</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="161">
@@ -20901,7 +20901,7 @@
         </is>
       </c>
       <c r="D161" s="6" t="n">
-        <v>16200863.09</v>
+        <v>16266163.94</v>
       </c>
       <c r="E161" s="12" t="n">
         <v>2.3</v>
@@ -20927,7 +20927,7 @@
         <v>15610414.24</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="163">
@@ -20947,10 +20947,10 @@
         </is>
       </c>
       <c r="D163" s="6" t="n">
-        <v>12882183.75</v>
+        <v>13132963.75</v>
       </c>
       <c r="E163" s="12" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="164">
@@ -20970,10 +20970,10 @@
         </is>
       </c>
       <c r="D164" s="6" t="n">
-        <v>9893626.949999999</v>
+        <v>9902926.949999999</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="165">
@@ -20993,10 +20993,10 @@
         </is>
       </c>
       <c r="D165" s="6" t="n">
-        <v>9885362.09</v>
+        <v>9899362.09</v>
       </c>
       <c r="E165" s="12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="166">
@@ -21016,7 +21016,7 @@
         </is>
       </c>
       <c r="D166" s="6" t="n">
-        <v>9684341.75</v>
+        <v>9730791.75</v>
       </c>
       <c r="E166" s="12" t="n">
         <v>1.38</v>
@@ -21030,19 +21030,19 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Paraíba</t>
+          <t>Alagoas</t>
         </is>
       </c>
       <c r="D167" s="6" t="n">
-        <v>7711906.85</v>
+        <v>7822737.14</v>
       </c>
       <c r="E167" s="12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="168">
@@ -21053,19 +21053,19 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Alagoas</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="D168" s="6" t="n">
-        <v>7463089.05</v>
+        <v>7794376.85</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="169">
@@ -21085,7 +21085,7 @@
         </is>
       </c>
       <c r="D169" s="6" t="n">
-        <v>6454843.68</v>
+        <v>6495263.68</v>
       </c>
       <c r="E169" s="12" t="n">
         <v>0.92</v>
@@ -21111,7 +21111,7 @@
         <v>5116292.25</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="171">
@@ -21154,7 +21154,7 @@
         </is>
       </c>
       <c r="D172" s="6" t="n">
-        <v>3925754.6</v>
+        <v>3929754.61</v>
       </c>
       <c r="E172" s="12" t="n">
         <v>0.5600000000000001</v>
@@ -22451,14 +22451,14 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -22472,7 +22472,7 @@
     <row r="232">
       <c r="A232" s="10" t="inlineStr">
         <is>
-          <t>Nota 2: a serie por UF do doador cobre apenas 11.1% do valor doado, porque o TSE nao publica a UF do doador pessoa fisica. Para leitura integral use a serie por UF do candidato que recebeu.</t>
+          <t>Nota 2: a serie por UF do doador cobre apenas 11.2% do valor doado, porque o TSE nao publica a UF do doador pessoa fisica. Para leitura integral use a serie por UF do candidato que recebeu.</t>
         </is>
       </c>
     </row>
@@ -22572,28 +22572,28 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>383292827.03</v>
+        <v>385111893.35</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>37780891.06</v>
+        <v>38680786.06</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>20334031.37</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>6058498.32</v>
+        <v>6068158.32</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>43839389.38</v>
+        <v>44748944.38</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>17.98</v>
+        <v>18.13</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>403626858.4</v>
+        <v>405445924.72</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>15.77</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="6">
@@ -22603,10 +22603,10 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>528206683.06</v>
+        <v>529989370.41</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>34219994.39</v>
+        <v>34294678.89</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>7837843.22</v>
@@ -22615,16 +22615,16 @@
         <v>9195409.91</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>43415404.3</v>
+        <v>43490088.8</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>17.81</v>
+        <v>17.62</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>536044526.28</v>
+        <v>537827213.63</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>20.94</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="7">
@@ -22634,10 +22634,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>261869160.42</v>
+        <v>262869912.82</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>28186299.49</v>
+        <v>28293999.49</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>328650</v>
@@ -22646,16 +22646,16 @@
         <v>227830.33</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>28414129.82</v>
+        <v>28521829.82</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>11.65</v>
+        <v>11.56</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>262197810.42</v>
+        <v>263198562.82</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="8">
@@ -22665,90 +22665,90 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>146359834.03</v>
+        <v>147339579.03</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>5572853.95</v>
+        <v>5589853.95</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>10528907.87</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>16191098.24</v>
+        <v>16201598.24</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>21763952.19</v>
+        <v>21791452.19</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>8.93</v>
+        <v>8.83</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>156888741.9</v>
+        <v>157868486.9</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.13</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Serviços advocatícios</t>
+          <t>Atividades de militância e mobilização de rua</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>117831324.72</v>
+        <v>235628026.44</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>9188407.710000001</v>
+        <v>19049261.29</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>13436262.57</v>
+        <v>1061795.06</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>9563476.6</v>
+        <v>310317.66</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>18751884.31</v>
+        <v>19359578.95</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>7.69</v>
+        <v>7.85</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>131267587.29</v>
+        <v>236689821.5</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>5.13</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Atividades de militância e mobilização de rua</t>
+          <t>Serviços advocatícios</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>233461070.58</v>
+        <v>118199276.79</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>18372880.05</v>
+        <v>9188407.710000001</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1061795.06</v>
+        <v>13436262.57</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>310317.66</v>
+        <v>9563476.6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>18683197.71</v>
+        <v>18751884.31</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>7.66</v>
+        <v>7.6</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>234522865.64</v>
+        <v>131635539.36</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9.16</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="11">
@@ -22758,28 +22758,28 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>224613152.32</v>
+        <v>226099283.08</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>15952595.59</v>
+        <v>16509416.28</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>1405640</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>529244.16</v>
+        <v>758113.3</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>16481839.75</v>
+        <v>17267529.58</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>6.76</v>
+        <v>7</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>226018792.32</v>
+        <v>227504923.08</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>8.83</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="12">
@@ -22789,10 +22789,10 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>158312348.46</v>
+        <v>159521447.71</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>7062759.54</v>
+        <v>7070439.54</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>2161173.45</v>
@@ -22801,16 +22801,16 @@
         <v>2248827.43</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>9311586.970000001</v>
+        <v>9319266.970000001</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>160473521.91</v>
+        <v>161682621.16</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>6.27</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="13">
@@ -22820,7 +22820,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>65990761.39</v>
+        <v>66380931.39</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>3754114.24</v>
@@ -22835,10 +22835,10 @@
         <v>9247626.59</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>78281435.61</v>
+        <v>78671605.61</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>3.06</v>
@@ -22851,25 +22851,25 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>54264820.71</v>
+        <v>54504312.9</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2443966.12</v>
+        <v>2458966.12</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>752452.6</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>3473642.61</v>
+        <v>3675202.61</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>5917608.73</v>
+        <v>6134168.73</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>55017273.31</v>
+        <v>55256765.5</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>2.15</v>
@@ -22882,10 +22882,10 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>83210006.84</v>
+        <v>83705434.05</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>4082123.36</v>
+        <v>4130383.99</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>53190</v>
@@ -22894,16 +22894,16 @@
         <v>1023161.61</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>5105284.97</v>
+        <v>5153545.600000001</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>2.09</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>83263196.84</v>
+        <v>83758624.05</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="16">
@@ -22913,25 +22913,25 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>27411392.78</v>
+        <v>27586692.78</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2957464.91</v>
+        <v>2990569.31</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>435855.87</v>
+        <v>527134.87</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1598966.95</v>
+        <v>1602466.95</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>4556431.86</v>
+        <v>4593036.26</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>27847248.65</v>
+        <v>28113827.65</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>1.09</v>
@@ -22944,10 +22944,10 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>38052916.43</v>
+        <v>38116666.43</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>2777983.78</v>
+        <v>2785733.78</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>214985.86</v>
@@ -22956,13 +22956,13 @@
         <v>665907.63</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>3443891.41</v>
+        <v>3451641.41</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>38267902.29</v>
+        <v>38331652.29</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>1.49</v>
@@ -22990,7 +22990,7 @@
         <v>2697521</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>15070247.9</v>
@@ -23006,25 +23006,25 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>27205571.94</v>
+        <v>27369612.79</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>1788536.92</v>
+        <v>1795116.62</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>25327.5</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>282176.1</v>
+        <v>286176.1</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2070713.02</v>
+        <v>2081292.72</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>27230899.44</v>
+        <v>27394940.29</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>1.06</v>
@@ -23037,10 +23037,10 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>20348342.44</v>
+        <v>20364103.46</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1007228.09</v>
+        <v>1013132.07</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>127520</v>
@@ -23049,13 +23049,13 @@
         <v>544826.95</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1552055.04</v>
+        <v>1557959.02</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>20475862.44</v>
+        <v>20491623.46</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0.8</v>
@@ -23068,7 +23068,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>11896623.23</v>
+        <v>11980203.23</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>1235627.11</v>
@@ -23077,16 +23077,16 @@
         <v>113916.98</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>199564.49</v>
+        <v>202564.49</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1435191.6</v>
+        <v>1438191.6</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>12010540.21</v>
+        <v>12094120.21</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0.47</v>
@@ -23099,7 +23099,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>10592047.7</v>
+        <v>10763047.7</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>1162211.39</v>
@@ -23114,75 +23114,75 @@
         <v>1282711.39</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>10798047.7</v>
+        <v>10969047.7</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Publicidade por carros de som</t>
+          <t>Produção de jingles, vinhetas e slogans</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>14536316.03</v>
+        <v>13888201.41</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>858287.63</v>
+        <v>954256.42</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>933850</v>
+        <v>56000</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>110000</v>
+        <v>18500</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>968287.63</v>
+        <v>972756.42</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>15470166.03</v>
+        <v>13944201.41</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Produção de jingles, vinhetas e slogans</t>
+          <t>Publicidade por carros de som</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>13824801.41</v>
+        <v>14693666.03</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>949256.42</v>
+        <v>858287.63</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>56000</v>
+        <v>933850</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>18500</v>
+        <v>110000</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>967756.42</v>
+        <v>968287.63</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>13880801.41</v>
+        <v>15627516.03</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="25">
@@ -23192,10 +23192,10 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>6114140.28</v>
+        <v>6127990.28</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>727192.3100000001</v>
+        <v>729492.3100000001</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>0</v>
@@ -23204,13 +23204,13 @@
         <v>420</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>727612.3100000001</v>
+        <v>729912.3100000001</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>6114140.28</v>
+        <v>6127990.28</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0.24</v>
@@ -23223,28 +23223,28 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>7235176.67</v>
+        <v>7386946.52</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>600926.35</v>
+        <v>600987.22</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>22074.32</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>116396.95</v>
+        <v>128501.95</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>717323.2999999999</v>
+        <v>729489.1699999999</v>
       </c>
       <c r="G26" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>7409020.84</v>
+      </c>
+      <c r="I26" s="6" t="n">
         <v>0.29</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>7257250.99</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>0.28</v>
       </c>
     </row>
     <row r="27">
@@ -23254,10 +23254,10 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>14749649.59</v>
+        <v>14789875.09</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>701750.45</v>
+        <v>704588.0600000001</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>8104.55</v>
@@ -23266,13 +23266,13 @@
         <v>0</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>701750.45</v>
+        <v>704588.0600000001</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>0.29</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>14757754.14</v>
+        <v>14797979.64</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0.58</v>
@@ -23285,7 +23285,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>9012357.35</v>
+        <v>9099711.26</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>336862.09</v>
@@ -23297,13 +23297,13 @@
         <v>151786.7</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>488648.79</v>
+        <v>488648.7899999999</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>9012357.35</v>
+        <v>9099711.26</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0.35</v>
@@ -23316,10 +23316,10 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>2621941.64</v>
+        <v>2634914.93</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>265835.78</v>
+        <v>267059.74</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>9126.799999999999</v>
@@ -23328,13 +23328,13 @@
         <v>99566.78999999999</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>365402.57</v>
+        <v>366626.53</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>0.15</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>2631068.44</v>
+        <v>2644041.73</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0.1</v>
@@ -23347,7 +23347,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>3371303.86</v>
+        <v>3372643.86</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>293667.18</v>
@@ -23365,7 +23365,7 @@
         <v>0.12</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>3371303.86</v>
+        <v>3372643.86</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0.13</v>
@@ -23378,7 +23378,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>2357945.54</v>
+        <v>2367945.54</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>186090.2</v>
@@ -23396,7 +23396,7 @@
         <v>0.08</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>2357945.54</v>
+        <v>2367945.54</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0.09</v>
@@ -23412,7 +23412,7 @@
         <v>898514.8</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>85143.31999999999</v>
+        <v>85143.32000000001</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>18616.5</v>
@@ -23440,10 +23440,10 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>1433855.5</v>
+        <v>1440289.23</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>58367.11</v>
+        <v>58664.51</v>
       </c>
       <c r="D33" s="6" t="n">
         <v>0</v>
@@ -23452,13 +23452,13 @@
         <v>40453.96</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>98821.07000000001</v>
+        <v>99118.47</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>0.04</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1433855.5</v>
+        <v>1440289.23</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0.06</v>
@@ -23471,7 +23471,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>934270.9300000001</v>
+        <v>959650.9300000001</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>40923.94</v>
@@ -23489,7 +23489,7 @@
         <v>0.02</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>934270.9300000001</v>
+        <v>959650.9300000001</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0.04</v>
@@ -23533,25 +23533,25 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>433974.27</v>
+        <v>436798.76</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>23961.96</v>
+        <v>26342.36</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>99335.53999999999</v>
+        <v>99791.58</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>12986.4</v>
+        <v>13788.9</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>36948.36</v>
+        <v>40131.26</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>533309.8100000001</v>
+        <v>536590.34</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0.02</v>
@@ -23564,7 +23564,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>421914.91</v>
+        <v>430493.91</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>20610.5</v>
@@ -23579,10 +23579,10 @@
         <v>36818.7</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>423463.58</v>
+        <v>432042.58</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0.02</v>
@@ -23626,7 +23626,7 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>36657.91</v>
+        <v>38992.87</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>3261.35</v>
@@ -23644,7 +23644,7 @@
         <v>0.01</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>36757.15</v>
+        <v>39092.11</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
@@ -23777,14 +23777,14 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -23937,34 +23937,34 @@
         <v>5281805806.47</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1407806661.46</v>
+        <v>1409339581.28</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>19.35</v>
+        <v>19.33</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1023721550.1</v>
+        <v>1024361550.1</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>18.9</v>
+        <v>18.91</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>150890397.42</v>
+        <v>151137505.82</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>24.33</v>
+        <v>23.93</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>21898287.12</v>
+        <v>21948898.27</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>138846409.06</v>
+        <v>139408629.58</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>1065119816.62</v>
+        <v>1071026538.15</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>83.44</v>
+        <v>83.41</v>
       </c>
     </row>
     <row r="6">
@@ -23983,34 +23983,34 @@
         <v>788542541.16</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1056556575.52</v>
+        <v>1057144307.24</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>14.52</v>
+        <v>14.5</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>920728039.12</v>
+        <v>920820959.12</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>17</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>6246134.65</v>
+        <v>6176134.65</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>12271752.53</v>
+        <v>12370225.24</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>84763399.47</v>
+        <v>85135052.48</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>702414291.62</v>
+        <v>697883667.52</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>87.73999999999999</v>
+        <v>87.69</v>
       </c>
     </row>
     <row r="7">
@@ -24029,34 +24029,34 @@
         <v>1819943318.34</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>658404982.35</v>
+        <v>668946919.73</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>9.050000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>536542994.33</v>
+        <v>536651994.33</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>9.91</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>65426808.97</v>
+        <v>75609738.73999999</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>10.55</v>
+        <v>11.97</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>8070356.86</v>
+        <v>8122431.99</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>29472620.29</v>
+        <v>29642872.29</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>473050886.85</v>
+        <v>474094188.43</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>91.43000000000001</v>
+        <v>91.53</v>
       </c>
     </row>
     <row r="8">
@@ -24075,13 +24075,13 @@
         <v>2577905190.84</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>654606240.41</v>
+        <v>655287244.45</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>9</v>
+        <v>8.99</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>448626803.71</v>
+        <v>448666803.71</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>8.279999999999999</v>
@@ -24090,19 +24090,19 @@
         <v>34632737.02</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>5.58</v>
+        <v>5.48</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>18973319.52</v>
+        <v>18922595.77</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>84251096.95999999</v>
+        <v>84575958.48999999</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>511381040.23</v>
+        <v>512484289.44</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>73.81999999999999</v>
+        <v>73.75</v>
       </c>
     </row>
     <row r="9">
@@ -24121,10 +24121,10 @@
         <v>2779509683.8</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>604619649.46</v>
+        <v>605065027.8099999</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>8.31</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>370432010.25</v>
@@ -24133,22 +24133,22 @@
         <v>6.84</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>126555644.82</v>
+        <v>126619464.39</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>20.4</v>
+        <v>20.05</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>11821936.46</v>
+        <v>11884790.46</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>63188329.1</v>
+        <v>63493468.32</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>424146313.18</v>
+        <v>425494401.76</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>82.2</v>
+        <v>82.15000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -24167,10 +24167,10 @@
         <v>1297502449.57</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>576451516.6</v>
+        <v>576656855.17</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7.92</v>
+        <v>7.91</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>446516289.17</v>
@@ -24182,19 +24182,19 @@
         <v>74187903.25</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>11.96</v>
+        <v>11.75</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>7924570.21</v>
+        <v>8062753.11</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>30629543.88</v>
+        <v>30674373.88</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>362172406.18</v>
+        <v>362213876.57</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>90.33</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="11">
@@ -24213,10 +24213,10 @@
         <v>3431895006.71</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>536618527.49</v>
+        <v>537203229.91</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>7.38</v>
+        <v>7.37</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>407807248.96</v>
@@ -24225,22 +24225,22 @@
         <v>7.53</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>17642692.04</v>
+        <v>17650611.52</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>14952123.45</v>
+        <v>15048690.04</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>67491172.3</v>
+        <v>67883952.39</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>349989390.3</v>
+        <v>351618264.86</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>79.28</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="12">
@@ -24259,34 +24259,34 @@
         <v>1812875005.9</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>295587133.63</v>
+        <v>295865533.79</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>4.06</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>238015482.3</v>
+        <v>238185682.3</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4.39</v>
+        <v>4.4</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5664780.810000001</v>
+        <v>5678988.810000001</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>10140250.16</v>
+        <v>10145870.45</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>31714016.89</v>
+        <v>31800231.76</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>193405232.64</v>
+        <v>193710408.87</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>82.44</v>
+        <v>82.42</v>
       </c>
     </row>
     <row r="13">
@@ -24305,7 +24305,7 @@
         <v>1457794419.27</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>230020966.24</v>
+        <v>230641485.51</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>3.16</v>
@@ -24317,19 +24317,19 @@
         <v>3.08</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>46292435.08</v>
+        <v>46882987.35</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>7.46</v>
+        <v>7.42</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>2916910.78</v>
+        <v>2918310.78</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>9985785.189999999</v>
+        <v>9986352.189999999</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>152820074.02</v>
+        <v>152821474.02</v>
       </c>
       <c r="N13" s="6" t="n">
         <v>92.73</v>
@@ -24351,13 +24351,13 @@
         <v>941728196.61</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>222374886.05</v>
+        <v>222436516.05</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>148466010.38</v>
+        <v>148468909.38</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>2.74</v>
@@ -24366,19 +24366,19 @@
         <v>6709805.88</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>10858802.79</v>
+        <v>10884683.79</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>36386793.06</v>
+        <v>36412793.06</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>172264084.06</v>
+        <v>172315950.61</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>69.78</v>
+        <v>69.76000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -24397,34 +24397,34 @@
         <v>2591694177.84</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>209944283.85</v>
+        <v>210403265</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>2.89</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>150291927.09</v>
+        <v>150317927.09</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>2.77</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>4458016.17</v>
+        <v>4457357.34</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>11729771.43</v>
+        <v>11733934.69</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31374161.43</v>
+        <v>31737764.53</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>143783995.4</v>
+        <v>144506391.86</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>73.70999999999999</v>
+        <v>73.56</v>
       </c>
     </row>
     <row r="16">
@@ -24443,7 +24443,7 @@
         <v>1884208841.62</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>144312158.17</v>
+        <v>144321776.59</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>1.98</v>
@@ -24452,25 +24452,25 @@
         <v>34396229.06</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>44449677.11</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>7.17</v>
+        <v>7.04</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>7311250.99</v>
+        <v>7330389.71</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>27058281.31</v>
+        <v>27108631.98</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>90111146.33</v>
+        <v>90524955.17</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>54.64</v>
+        <v>54.63</v>
       </c>
     </row>
     <row r="17">
@@ -24489,13 +24489,13 @@
         <v>139488473.87</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>135351846.9</v>
+        <v>135467418.7</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>1.86</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>123925665.62</v>
+        <v>123997665.62</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>2.29</v>
@@ -24504,19 +24504,19 @@
         <v>1959373.78</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>812961.91</v>
+        <v>821011.21</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>4141556.34</v>
+        <v>4174006.34</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>89664306.39</v>
+        <v>89940476.53</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>93.01000000000001</v>
+        <v>92.98</v>
       </c>
     </row>
     <row r="18">
@@ -24535,10 +24535,10 @@
         <v>1072776812.99</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>99332232.69</v>
+        <v>99461887.94</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>65447540.29</v>
@@ -24547,19 +24547,19 @@
         <v>1.21</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>13772331.38</v>
+        <v>13872331.38</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>4906934.439999999</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>12808569.05</v>
+        <v>12838224.3</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>60709426.54</v>
+        <v>61088163.04</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>79.75</v>
@@ -24581,7 +24581,7 @@
         <v>577531754.64</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>97416169.03</v>
+        <v>97456207.38</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>1.34</v>
@@ -24593,22 +24593,22 @@
         <v>1.25</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>14150615.09</v>
+        <v>14150621.49</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>3349976.32</v>
+        <v>3368096.32</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>9204057.119999999</v>
+        <v>9223157.119999999</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>60944962.21</v>
+        <v>60969268.11</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>83.90000000000001</v>
+        <v>83.86</v>
       </c>
     </row>
     <row r="20">
@@ -24627,7 +24627,7 @@
         <v>280452197.14</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>92007573.06999999</v>
+        <v>92074434.59999999</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>1.26</v>
@@ -24639,19 +24639,19 @@
         <v>1.55</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>1638050</v>
+        <v>1699330</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>1868672.92</v>
+        <v>1869153.42</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>3837143.96</v>
+        <v>3841731.77</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>52487646.85</v>
+        <v>53094938.65</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>92.84999999999999</v>
@@ -24688,7 +24688,7 @@
         <v>4467405.01</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>1309270.67</v>
@@ -24719,7 +24719,7 @@
         <v>330099422.77</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>60262921.48</v>
+        <v>60307921.48</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>0.83</v>
@@ -24740,13 +24740,13 @@
         <v>3471243.36</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>11067575.11</v>
+        <v>11112575.11</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>43906560.06</v>
+        <v>43954410.06</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>71.84999999999999</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="23">
@@ -24765,13 +24765,13 @@
         <v>121249861.96</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>36374038.48</v>
+        <v>36803005</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>33321190.93</v>
+        <v>33750157.45</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>0.62</v>
@@ -24789,10 +24789,10 @@
         <v>1056669.75</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>11155393.72</v>
+        <v>11366169.54</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>92.95</v>
+        <v>93.04000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -24857,7 +24857,7 @@
         <v>286783798.5</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>12071919.96</v>
+        <v>12107936.16</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>0.17</v>
@@ -24875,16 +24875,16 @@
         <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>2040988.63</v>
+        <v>2046899.83</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>7458146.99</v>
+        <v>7488251.99</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>7596728.87</v>
+        <v>7618835.57</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>18.51</v>
+        <v>18.46</v>
       </c>
     </row>
     <row r="26">
@@ -24903,7 +24903,7 @@
         <v>243522021.57</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>10117106.01</v>
+        <v>10135622.14</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>0.14</v>
@@ -24921,16 +24921,16 @@
         <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>1835634.88</v>
+        <v>1848905.88</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>5498396.57</v>
+        <v>5503641.7</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>8287319.06</v>
+        <v>8396083.199999999</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>23.06</v>
+        <v>23.02</v>
       </c>
     </row>
     <row r="27">
@@ -25041,7 +25041,7 @@
         <v>463597846.48</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>5214962.98</v>
+        <v>5230812.98</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -25059,16 +25059,16 @@
         <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>2216428.14</v>
+        <v>2229278.14</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>2060883.58</v>
+        <v>2063883.58</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>3335407.88</v>
+        <v>3346427.08</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="30">
@@ -25133,13 +25133,13 @@
         <v>16313701.99</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>1911692.09</v>
+        <v>1915902.59</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>0.03</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>1295831.22</v>
+        <v>1300041.22</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>0.02</v>
@@ -25154,13 +25154,13 @@
         <v>8271.67</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>248034.15</v>
+        <v>248034.65</v>
       </c>
       <c r="M31" s="6" t="n">
         <v>1095692.48</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>67.78</v>
+        <v>67.86</v>
       </c>
     </row>
     <row r="32">
@@ -25304,14 +25304,14 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -26576,16 +26576,16 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>1103250</v>
+        <v>1104869</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>120000</v>
+        <v>121619</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>10.88</v>
+        <v>11.01</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>975500</v>
@@ -26634,7 +26634,7 @@
         <v>1092324.33</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>127000</v>
@@ -27291,16 +27291,16 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>986483.92</v>
+        <v>993283.92</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>120500</v>
+        <v>127300</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>12.22</v>
+        <v>12.82</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>251605</v>
@@ -27309,7 +27309,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>614378.9199999999</v>
+        <v>614378.92</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>0</v>
@@ -27483,7 +27483,7 @@
         <v>31240</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>851941.8099999999</v>
+        <v>851941.8100000001</v>
       </c>
       <c r="O41" s="6" t="n">
         <v>851941.8100000001</v>
@@ -28207,35 +28207,35 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 09:13:47.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: sao 2200 candidaturas com receita declarada e sem um real dos dois fundos publicos. que somam R$ 223.590.002,17 de receita.</t>
+          <t>Nota 1: sao 2200 candidaturas com receita declarada e sem um real dos dois fundos publicos. que somam R$ 224.320.213,64 de receita.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Nota 2: outras 4164 candidaturas NAO declararam receita alguma, das quais 960 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
+          <t>Nota 2: outras 4155 candidaturas NAO declararam receita alguma, das quais 960 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Nota 3: destas, 1256 nao receberam recurso partidario de especie alguma, nem mesmo fora dos dois fundos.</t>
+          <t>Nota 3: destas, 1253 nao receberam recurso partidario de especie alguma, nem mesmo fora dos dois fundos.</t>
         </is>
       </c>
     </row>
@@ -28383,16 +28383,16 @@
         <v>7.71</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>940060770.7</v>
+        <v>941059970.52</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>20.36</v>
+        <v>20.38</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>27.56</v>
+        <v>27.59</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.57</v>
+        <v>22.58</v>
       </c>
     </row>
     <row r="6">
@@ -28426,16 +28426,16 @@
         <v>11.18</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>538525118.08</v>
+        <v>539785425.37</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>25.09</v>
+        <v>25.15</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>32.88</v>
+        <v>32.95</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>24.85</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="7">
@@ -28469,16 +28469,16 @@
         <v>15.98</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>501106811.34</v>
+        <v>501598033.74</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>29.09</v>
+        <v>29.12</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>38.97</v>
+        <v>39.01</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>34.23</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="8">
@@ -28512,16 +28512,16 @@
         <v>10.81</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>347986863.58</v>
+        <v>348267772.86</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>23.37</v>
+        <v>23.39</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>30.74</v>
+        <v>30.76</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>26.92</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="9">
@@ -28555,16 +28555,16 @@
         <v>12.66</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>346492424.23</v>
+        <v>346616717.24</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>28.99</v>
+        <v>29</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>40.24</v>
+        <v>40.26</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>31.74</v>
+        <v>31.75</v>
       </c>
     </row>
     <row r="10">
@@ -28598,13 +28598,13 @@
         <v>12.36</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>319520408.32</v>
+        <v>319738833.72</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>28.44</v>
+        <v>28.46</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>37.47</v>
+        <v>37.5</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>31.29</v>
@@ -28641,13 +28641,13 @@
         <v>13.3</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>260456309.01</v>
+        <v>260541558.01</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>27.18</v>
+        <v>27.19</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>36.04</v>
+        <v>36.05</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>30.53</v>
@@ -28684,13 +28684,13 @@
         <v>10.2</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>248537140.7</v>
+        <v>248624871.27</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>26.72</v>
+        <v>26.73</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>35.5</v>
+        <v>35.51</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>28.59</v>
@@ -28727,13 +28727,13 @@
         <v>11.82</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>191486245.93</v>
+        <v>191668164.35</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>21.87</v>
+        <v>21.89</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>30.55</v>
+        <v>30.58</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>25.82</v>
@@ -28770,13 +28770,13 @@
         <v>12.22</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>216342827.56</v>
+        <v>216368096.53</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>26.03</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>37.78</v>
+        <v>37.79</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>28.57</v>
@@ -28813,16 +28813,16 @@
         <v>11.93</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>223564597.48</v>
+        <v>223689101.98</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>31.83</v>
+        <v>31.84</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>43.09</v>
+        <v>43.12</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>36.48</v>
+        <v>36.49</v>
       </c>
     </row>
     <row r="16">
@@ -28856,13 +28856,13 @@
         <v>17.83</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>232263101.77</v>
+        <v>232655729.4</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>30.99</v>
+        <v>31.04</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>45.71</v>
+        <v>45.79</v>
       </c>
       <c r="M16" s="6" t="n">
         <v>34.39</v>
@@ -28899,13 +28899,13 @@
         <v>13.85</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>149546550.28</v>
+        <v>149704962.6</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>35.75</v>
+        <v>35.79</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>46.04</v>
+        <v>46.09</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>40.78</v>
@@ -28942,13 +28942,13 @@
         <v>20.16</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>176329731.25</v>
+        <v>176399645.6</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>42.48</v>
+        <v>42.5</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>58.96</v>
+        <v>58.99</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>48.57</v>
@@ -28985,13 +28985,13 @@
         <v>17.38</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>189101995.69</v>
+        <v>189498535.69</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>43.36</v>
+        <v>43.45</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>67.48999999999999</v>
+        <v>67.63</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>58.1</v>
@@ -29028,7 +29028,7 @@
         <v>14.84</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>145326561.75</v>
+        <v>145328090.58</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>42.84</v>
@@ -29071,16 +29071,16 @@
         <v>12.85</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>127266043.44</v>
+        <v>135306463.94</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>36.74</v>
+        <v>39.06</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>47.83</v>
+        <v>50.85</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>42.55</v>
+        <v>45.56</v>
       </c>
     </row>
     <row r="22">
@@ -29114,13 +29114,13 @@
         <v>17.24</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>162669914.67</v>
+        <v>162804286.45</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>41.18</v>
+        <v>41.21</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>61.64</v>
+        <v>61.69</v>
       </c>
       <c r="M22" s="6" t="n">
         <v>36.39</v>
@@ -29157,13 +29157,13 @@
         <v>12.24</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>116218732.63</v>
+        <v>116578380.72</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>36.08</v>
+        <v>36.19</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>47.59</v>
+        <v>47.73</v>
       </c>
       <c r="M23" s="6" t="n">
         <v>42.42</v>
@@ -29200,13 +29200,13 @@
         <v>30.18</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>206637988.78</v>
+        <v>206745533</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>68.65000000000001</v>
+        <v>68.69</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>91.70999999999999</v>
+        <v>91.75</v>
       </c>
       <c r="M24" s="6" t="n">
         <v>73.26000000000001</v>
@@ -29243,13 +29243,13 @@
         <v>20.99</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>118101205.06</v>
+        <v>118148055.06</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>40.08</v>
+        <v>40.1</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>58.32</v>
+        <v>58.34</v>
       </c>
       <c r="M25" s="6" t="n">
         <v>47.37</v>
@@ -29286,13 +29286,13 @@
         <v>23.62</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>123124375.75</v>
+        <v>123147279.67</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>53.36</v>
+        <v>53.37</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>70.75</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>63.36</v>
@@ -29329,16 +29329,16 @@
         <v>34.52</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>146374557.1</v>
+        <v>147117921.93</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>83.29000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>115.38</v>
+        <v>115.96</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>89.84999999999999</v>
+        <v>90.37</v>
       </c>
     </row>
     <row r="28">
@@ -29372,16 +29372,16 @@
         <v>31.11</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>118839693.01</v>
+        <v>121101896.75</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>74.45999999999999</v>
+        <v>75.88</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>100.48</v>
+        <v>102.39</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>82.29000000000001</v>
+        <v>84.14</v>
       </c>
     </row>
     <row r="29">
@@ -29501,16 +29501,16 @@
         <v>102.85</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>105896079.13</v>
+        <v>105927367.84</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>139.15</v>
+        <v>139.19</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>263.7</v>
+        <v>263.78</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>245.99</v>
+        <v>246.04</v>
       </c>
     </row>
     <row r="32">
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>772962838.47</v>
+        <v>773225038.47</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -29605,16 +29605,16 @@
         <v>13.34</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>7275637605.73</v>
+        <v>7292546453.309999</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>33.96</v>
+        <v>34.04</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>46.09</v>
+        <v>46.2</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>38.24</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="34">
@@ -29627,7 +29627,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-11.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -646,13 +646,13 @@
         <v>1.03</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>47759459.29</v>
+        <v>47867732.18</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>32297850.99</v>
+        <v>32379885.41</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0.64</v>
@@ -677,16 +677,16 @@
         <v>36.5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1789536597.2</v>
+        <v>1791649865.2</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>24.54</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>1176388199.28</v>
+        <v>1180242374.12</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>23.19</v>
+        <v>23.15</v>
       </c>
     </row>
     <row r="9">
@@ -708,16 +708,16 @@
         <v>26.47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3400667363.28</v>
+        <v>3403116791.96</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>46.63</v>
+        <v>46.61</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2283855891.23</v>
+        <v>2291356663.53</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>45.03</v>
+        <v>44.95</v>
       </c>
     </row>
     <row r="10">
@@ -739,16 +739,16 @@
         <v>5.34</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>762405184.63</v>
+        <v>762568509.14</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>10.45</v>
+        <v>10.44</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>610044593.85</v>
+        <v>617772495.04</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>12.03</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="11">
@@ -770,16 +770,16 @@
         <v>3.72</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>773225038.47</v>
+        <v>777520950.2900001</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>10.6</v>
+        <v>10.65</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>580965223.13</v>
+        <v>587347887.3099999</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>11.45</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="12">
@@ -801,16 +801,16 @@
         <v>6.32</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>518952810.44</v>
+        <v>518986939.51</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>7.12</v>
+        <v>7.11</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>388235659.38</v>
+        <v>388998567.06</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>7.65</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="13">
@@ -894,13 +894,13 @@
         <v>100</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7292546453.31</v>
+        <v>7301710788.28</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>5071787417.860001</v>
+        <v>5098097872.47</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>100</v>
@@ -909,14 +909,14 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
         </is>
       </c>
     </row>
@@ -1025,14 +1025,14 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>176132</v>
+        <v>177022</v>
       </c>
     </row>
     <row r="24">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6571806694.05</v>
+        <v>6577836013.57</v>
       </c>
     </row>
     <row r="26">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{"REC_FEFC": 4844739920.29, "REC_FINANCIAMENTO_COLETIVO": 18454342.44, "REC_FUNDO_PARTIDARIO": 554667725.65, "REC_ORIGEM_NAO_IDENTIFICADA": 1122450.97, "REC_OUTROS_CANDIDATOS": 120906785.19, "REC_PARTIDO_OUTROS_RECURSOS": 202862333.19, "REC_PESSOAS_FISICAS": 665536838.19, "REC_PROPRIOS": 163516298.13, "REC_SEM_ORIGEM": 0.0}</t>
+          <t>{"REC_FEFC": 4845870044.69, "REC_FINANCIAMENTO_COLETIVO": 19062483.46, "REC_FUNDO_PARTIDARIO": 554667577.4, "REC_ORIGEM_NAO_IDENTIFICADA": 1142082.6, "REC_OUTROS_CANDIDATOS": 121375656.27, "REC_PARTIDO_OUTROS_RECURSOS": 203436494.15, "REC_PESSOAS_FISICAS": 668235463.88, "REC_PROPRIOS": 164046211.12, "REC_SEM_ORIGEM": 0.0}</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>78845</v>
+        <v>79256</v>
       </c>
     </row>
     <row r="30">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1004571</v>
+        <v>1011340</v>
       </c>
     </row>
     <row r="36">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>799005</v>
+        <v>804775</v>
       </c>
     </row>
     <row r="37">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4533327912.13</v>
+        <v>4554851842.71</v>
       </c>
     </row>
     <row r="38">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>730118</v>
+        <v>742817</v>
       </c>
     </row>
     <row r="39">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3206794063.34</v>
+        <v>3237241449.26</v>
       </c>
     </row>
     <row r="40">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>74760</v>
+        <v>75888</v>
       </c>
     </row>
     <row r="43">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>808166.14</v>
+        <v>813631.13</v>
       </c>
     </row>
     <row r="44">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>550391</v>
+        <v>552703</v>
       </c>
     </row>
     <row r="46">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>526</v>
       </c>
     </row>
     <row r="47">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>56069</v>
+        <v>56595</v>
       </c>
     </row>
     <row r="48">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>56061</v>
+        <v>56445</v>
       </c>
     </row>
     <row r="49">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>192</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="52">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2563768465.62</v>
+        <v>2584556390.44</v>
       </c>
     </row>
     <row r="53">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64325144.72</v>
+        <v>64368644.72</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>188939807.66</v>
+        <v>190585344.69</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4946838977.85</v>
+        <v>4946943100.24</v>
       </c>
     </row>
     <row r="57">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4873234079.22</v>
+        <v>4873261169.22</v>
       </c>
     </row>
     <row r="58">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>597404595.62</v>
+        <v>597489111.75</v>
       </c>
     </row>
     <row r="59">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>536487270.69</v>
+        <v>536532270.69</v>
       </c>
     </row>
     <row r="60">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>6736268</v>
+        <v>6715380</v>
       </c>
     </row>
     <row r="61">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-13 15:05:10</t>
+          <t>2026-10-14 09:12:37</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-720739759.26</v>
+        <v>-723874774.71</v>
       </c>
     </row>
     <row r="65">
@@ -5549,13 +5549,13 @@
         </is>
       </c>
       <c r="L58" s="6" t="n">
-        <v>11275000</v>
+        <v>11286400</v>
       </c>
       <c r="M58" s="6" t="n">
         <v>0.15</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="O58" s="6" t="n">
         <v>225000</v>
@@ -8602,13 +8602,13 @@
         </is>
       </c>
       <c r="L101" s="6" t="n">
-        <v>645752.51</v>
+        <v>652752.51</v>
       </c>
       <c r="M101" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="N101" s="6" t="n">
-        <v>30000</v>
+        <v>37000</v>
       </c>
       <c r="O101" s="6" t="n">
         <v>5000</v>
@@ -8842,14 +8842,14 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
         </is>
       </c>
     </row>
@@ -9032,19 +9032,19 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>5982</v>
+        <v>6057</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>277437844.84</v>
+        <v>279926342.72</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5.47</v>
+        <v>5.49</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>269968345.13</v>
+        <v>272447538.12</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>97.31</v>
+        <v>97.33</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -9097,19 +9097,19 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1878</v>
+        <v>1885</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>97494485.77</v>
+        <v>99655049.3</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>95727430.08</v>
+        <v>97958093.61</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>98.19</v>
+        <v>98.3</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>17000000</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>9000000</v>
@@ -9298,7 +9298,7 @@
         <v>15000000</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>15000000</v>
@@ -9422,16 +9422,16 @@
         </is>
       </c>
       <c r="I11" s="5" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>12977013.23</v>
+        <v>12977413.23</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>12596709.23</v>
+        <v>12597109.23</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>97.06999999999999</v>
@@ -9617,19 +9617,19 @@
         </is>
       </c>
       <c r="I14" s="5" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>9197191.550000001</v>
+        <v>9207590.32</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0.18</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>8181144.59</v>
+        <v>8191543.36</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>88.95</v>
+        <v>88.97</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>8920500</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>6879000</v>
@@ -9883,7 +9883,7 @@
         <v>6350000</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>6350000</v>
@@ -9942,19 +9942,19 @@
         </is>
       </c>
       <c r="I19" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>6279227</v>
+        <v>6299891</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0.12</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>4672182.32</v>
+        <v>4692846.32</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>74.41</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
@@ -10146,10 +10146,10 @@
         <v>0.11</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>3332636.47</v>
+        <v>3530637.6</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>58.48</v>
+        <v>61.95</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
@@ -10341,10 +10341,10 @@
         <v>0.1</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>2608986.1</v>
+        <v>2611986.1</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>51.23</v>
+        <v>51.29</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
@@ -10688,12 +10688,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>05.060.706/0001-62</t>
+          <t>11.197.995/0001-49</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>SANTANA   ASSOCIADOS MARKETING E PROPAGANDA LTDA</t>
+          <t>BUCCHIANERI ADVOCACIA</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -10703,17 +10703,17 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Atividades jurídicas, exceto cartórios</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>LAURO DE FREITAS</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -10722,28 +10722,28 @@
         </is>
       </c>
       <c r="I31" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>4600000</v>
+        <v>4720000</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>2500000</v>
+        <v>3150000</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>54.35</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO; PL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>ALCIDES FERNANDES (PL); CAPITÃO WAGNER (UNIÃO)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -10753,12 +10753,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>13.007.646/0001-42</t>
+          <t>05.060.706/0001-62</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>GRAFICA EDITORA J ANDRADE LTDA</t>
+          <t>SANTANA   ASSOCIADOS MARKETING E PROPAGANDA LTDA</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -10768,17 +10768,17 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>ARACAJU</t>
+          <t>LAURO DE FREITAS</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -10787,28 +10787,28 @@
         </is>
       </c>
       <c r="I32" s="5" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>4515352.16</v>
+        <v>4600000</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>3070423.42</v>
+        <v>2500000</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>68</v>
+        <v>54.35</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS; PSD; PP; UNIÃO</t>
+          <t>UNIÃO; PL</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>GUSTINHO RIBEIRO (PP); VALMIR DE FRANCISQUINHO (REPUBLICANOS)</t>
+          <t>ALCIDES FERNANDES (PL); CAPITÃO WAGNER (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -10818,12 +10818,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>57.780.367/0001-92</t>
+          <t>13.007.646/0001-42</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>AUREA TECNOLOGIA E SOLUCOES LTDA</t>
+          <t>GRAFICA EDITORA J ANDRADE LTDA</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -10833,17 +10833,17 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>ARACAJU</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -10852,28 +10852,28 @@
         </is>
       </c>
       <c r="I33" s="5" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>4500000</v>
+        <v>4515352.16</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>4500000</v>
+        <v>3077855.42</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>100</v>
+        <v>68.16</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS; PSD; PP; UNIÃO</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>GUSTINHO RIBEIRO (PP); VALMIR DE FRANCISQUINHO (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -10948,12 +10948,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>34.028.316/0001-03</t>
+          <t>57.780.367/0001-92</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>EMPRESA BRASILEIRA DE CORREIOS E TELEGRAFOS</t>
+          <t>AUREA TECNOLOGIA E SOLUCOES LTDA</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -10963,17 +10963,17 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Atividades de Correio</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -10982,28 +10982,28 @@
         </is>
       </c>
       <c r="I35" s="5" t="n">
-        <v>188</v>
+        <v>1</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>4429341.16</v>
+        <v>4500000</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>4418503.93</v>
+        <v>4500000</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>99.76000000000001</v>
+        <v>100</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>PSD; PL; UNIÃO; MDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>FABIO SILVA (UNIÃO); PAULO FILHO DA FUNDAÇÃO (PSD)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -11013,12 +11013,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>22.507.365/0001-40</t>
+          <t>34.028.316/0001-03</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>LETSROCKET COMUNICACAO DIGITAL LTDA</t>
+          <t>EMPRESA BRASILEIRA DE CORREIOS E TELEGRAFOS</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -11028,17 +11028,17 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Atividades de Correio</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>FLORIANOPOLIS</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -11047,28 +11047,28 @@
         </is>
       </c>
       <c r="I36" s="5" t="n">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>4341431.96</v>
+        <v>4432760.58</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>3500031.96</v>
+        <v>4421923.35</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>80.62</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>PL; PP; REPUBLICANOS; MDB</t>
+          <t>PSD; PL; UNIÃO; MDB</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>ESPERIDIÃO AMIN (PP); ROBERTO CIDADE (UNIÃO)</t>
+          <t>FABIO SILVA (UNIÃO); PAULO FILHO DA FUNDAÇÃO (PSD)</t>
         </is>
       </c>
     </row>
@@ -11078,12 +11078,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>04.984.400/0001-30</t>
+          <t>22.507.365/0001-40</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>CTA - CLEITON TAXI AEREO LTDA</t>
+          <t>LETSROCKET COMUNICACAO DIGITAL LTDA</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -11093,17 +11093,17 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Transporte aéreo de carga</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>NOVA OLINDA DO NORTE</t>
+          <t>FLORIANOPOLIS</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -11112,28 +11112,28 @@
         </is>
       </c>
       <c r="I37" s="5" t="n">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>4266887.3</v>
+        <v>4341431.96</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>1123062.3</v>
+        <v>3500031.96</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>26.32</v>
+        <v>80.62</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>PSD; MDB; UNIÃO; REPUBLICANOS</t>
+          <t>PL; PP; REPUBLICANOS; MDB</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>OMAR AZIZ (PSD); EDUARDO BRAGA (MDB)</t>
+          <t>ESPERIDIÃO AMIN (PP); ROBERTO CIDADE (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -11143,12 +11143,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>27.997.819/0001-21</t>
+          <t>17.620.604/0001-33</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>GRID COMUNICACAO VISUAL, SINALIZACAO E EVENTOS LTDA</t>
+          <t>T. P. MONTENEGRO GRAFICA LTDA</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -11158,17 +11158,17 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Edição de livros</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>MOSSORO</t>
+          <t>BELEM</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -11177,28 +11177,28 @@
         </is>
       </c>
       <c r="I38" s="5" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>4244212.98</v>
+        <v>4288264.4</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>3219302.37</v>
+        <v>2116316</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>75.84999999999999</v>
+        <v>49.35</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>PV; PP; PT; MDB</t>
+          <t>MDB; PSD; PODE; UNIÃO</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>DR. BERNARDO (PV); KALINE DE DR. BERNARDO (PV)</t>
+          <t>ANTONIO DOIDO (MDB); HANA GHASSAN (MDB)</t>
         </is>
       </c>
     </row>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>31.399.764/0001-25</t>
+          <t>04.984.400/0001-30</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>LOG PRODUCOES   FILMES LTDA</t>
+          <t>CTA - CLEITON TAXI AEREO LTDA</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -11223,17 +11223,17 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Transporte aéreo de carga</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>NOVA OLINDA DO NORTE</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -11242,28 +11242,28 @@
         </is>
       </c>
       <c r="I39" s="5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4148608</v>
+        <v>4273137.3</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>2074304</v>
+        <v>1129312.3</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>50</v>
+        <v>26.43</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD; MDB; UNIÃO; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>LULA (PT)</t>
+          <t>EDUARDO BRAGA (MDB); OMAR AZIZ (PSD)</t>
         </is>
       </c>
     </row>
@@ -11273,12 +11273,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>09.649.862/0001-14</t>
+          <t>27.997.819/0001-21</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>IRMAOS SOUTELLO   MENDONCA CONSULTORIA, COMUNICACAO E DESENVOLVIMENTO DE PROJETOS LTDA.</t>
+          <t>GRID COMUNICACAO VISUAL, SINALIZACAO E EVENTOS LTDA</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -11288,17 +11288,17 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Atividades de consultoria em gestão empresarial</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>MOSSORO</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -11307,28 +11307,28 @@
         </is>
       </c>
       <c r="I40" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>4050000</v>
+        <v>4254762.98</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>4050000</v>
+        <v>3287532.37</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>100</v>
+        <v>77.27</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>PSB; PL; PSDB</t>
+          <t>PV; PP; PT; MDB</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>SIMONE TEBET (PSB); ARTHUR HENRIQUE (PL)</t>
+          <t>DR. BERNARDO (PV); KALINE DE DR. BERNARDO (PV)</t>
         </is>
       </c>
     </row>
@@ -11338,12 +11338,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>67.565.691/0001-41</t>
+          <t>31.399.764/0001-25</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>D26 COMUNICACAO SPE LTDA.</t>
+          <t>LOG PRODUCOES   FILMES LTDA</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -11353,17 +11353,17 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -11372,28 +11372,28 @@
         </is>
       </c>
       <c r="I41" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>4025000</v>
+        <v>4148608</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>3025000</v>
+        <v>2074304</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>75.16</v>
+        <v>50</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>PL; PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>CARLOS PORTINHO (PL); DOUGLAS RUAS (PL)</t>
+          <t>LULA (PT)</t>
         </is>
       </c>
     </row>
@@ -11403,12 +11403,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>51.735.365/0001-03</t>
+          <t>09.649.862/0001-14</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>BIGRAFICA EMBALAGENS LTDA</t>
+          <t>IRMAOS SOUTELLO   MENDONCA CONSULTORIA, COMUNICACAO E DESENVOLVIMENTO DE PROJETOS LTDA.</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -11418,17 +11418,17 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Atividades de consultoria em gestão empresarial</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -11437,28 +11437,28 @@
         </is>
       </c>
       <c r="I42" s="5" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>3992074.4</v>
+        <v>4050000</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>3345524.8</v>
+        <v>4050000</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>83.8</v>
+        <v>100</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>PL; PDT; PT; PSD</t>
+          <t>PSB; PL; PSDB</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>ALEXANDRE KALIL (PDT); FLÁVIO ROSCOE (PL)</t>
+          <t>SIMONE TEBET (PSB); ARTHUR HENRIQUE (PL)</t>
         </is>
       </c>
     </row>
@@ -11468,12 +11468,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>23.024.523/0001-73</t>
+          <t>67.565.691/0001-41</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>D. P. MALACHIAS - FILMES</t>
+          <t>D26 COMUNICACAO SPE LTDA.</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -11483,17 +11483,17 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>SOROCABA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -11502,28 +11502,28 @@
         </is>
       </c>
       <c r="I43" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>3800000</v>
+        <v>4025000</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>3800000</v>
+        <v>3025000</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>100</v>
+        <v>75.16</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL; PSD</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>TARCÍSIO (REPUBLICANOS)</t>
+          <t>CARLOS PORTINHO (PL); DOUGLAS RUAS (PL)</t>
         </is>
       </c>
     </row>
@@ -11533,12 +11533,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>09.204.155/0001-14</t>
+          <t>51.735.365/0001-03</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>VITA PORTO SOCIEDADE DE ADVOGADOS</t>
+          <t>BIGRAFICA EMBALAGENS LTDA</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -11548,17 +11548,17 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Atividades jurídicas, exceto cartórios</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -11567,28 +11567,28 @@
         </is>
       </c>
       <c r="I44" s="5" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>3790000</v>
+        <v>3992074.4</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>2210000</v>
+        <v>3348221.8</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>58.31</v>
+        <v>83.87</v>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>PL; UNIÃO; MDB; PSD</t>
+          <t>PL; PDT; PT; PSD</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>EDUARDO CURY (PL); DELEGADO DA CUNHA (UNIÃO)</t>
+          <t>ALEXANDRE KALIL (PDT); FLÁVIO ROSCOE (PL)</t>
         </is>
       </c>
     </row>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>02.344.116/0001-73</t>
+          <t>23.024.523/0001-73</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>ANDREUCCI   CAMPOS TURISMO LTDA</t>
+          <t>D. P. MALACHIAS - FILMES</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Agências de viagens</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>MOGI DAS CRUZES</t>
+          <t>SOROCABA</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -11635,25 +11635,25 @@
         <v>1</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>3748738.99</v>
+        <v>3800000</v>
       </c>
       <c r="K45" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>3748738.99</v>
+        <v>3800000</v>
       </c>
       <c r="M45" s="6" t="n">
         <v>100</v>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>TARCÍSIO (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -11663,12 +11663,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>60.259.384/0001-93</t>
+          <t>09.204.155/0001-14</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>CDA COMUNICACAO EM SERVICOS GRAFICOS E EVENTOS LTDA</t>
+          <t>VITA PORTO SOCIEDADE DE ADVOGADOS</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -11678,17 +11678,17 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades jurídicas, exceto cartórios</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>SANTA RITA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -11697,28 +11697,28 @@
         </is>
       </c>
       <c r="I46" s="5" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>3664444.75</v>
+        <v>3790000</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>2812803.75</v>
+        <v>2210000</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>76.76000000000001</v>
+        <v>58.31</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>MDB; PL; PT; PSB</t>
+          <t>PL; UNIÃO; MDB; PSD</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>VENEZIANO (MDB); DR. MARCELO QUEIROGA (PL)</t>
+          <t>EDUARDO CURY (PL); DELEGADO DA CUNHA (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>04.405.470/0001-96</t>
+          <t>02.344.116/0001-73</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>CONTACTO RELACOES PUBLICAS LTDA</t>
+          <t>ANDREUCCI   CAMPOS TURISMO LTDA</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Agências de viagens</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>NATAL</t>
+          <t>MOGI DAS CRUZES</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -11762,28 +11762,28 @@
         </is>
       </c>
       <c r="I47" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>3600000</v>
+        <v>3748738.99</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0</v>
+        <v>3748738.99</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>PT; PSB; REDE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>ELMANO DE FREITAS (PT); CID GOMES (PSB)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -11793,12 +11793,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>24.759.252/0001-67</t>
+          <t>60.259.384/0001-93</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>FEIRA ROTULOS E ETIQUETAS ADESIVAS LTDA</t>
+          <t>CDA COMUNICACAO EM SERVICOS GRAFICOS E EVENTOS LTDA</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -11808,17 +11808,17 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>FEIRA DE SANTANA</t>
+          <t>SANTA RITA</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -11827,28 +11827,28 @@
         </is>
       </c>
       <c r="I48" s="5" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>3555631.95</v>
+        <v>3664444.75</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>2992985.32</v>
+        <v>2812803.75</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>84.18000000000001</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>PT; UNIÃO; PSD; REPUBLICANOS</t>
+          <t>MDB; PL; PT; PSB</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>PROFESSORA DAYANE PIMENTEL (UNIÃO); GABRIEL NUNES (PSD)</t>
+          <t>VENEZIANO (MDB); DR. MARCELO QUEIROGA (PL)</t>
         </is>
       </c>
     </row>
@@ -11858,12 +11858,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>04.639.525/0001-22</t>
+          <t>04.405.470/0001-96</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>MALHEIROS, PENTEADO E TOLEDO - ADVOGADOS</t>
+          <t>CONTACTO RELACOES PUBLICAS LTDA</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -11873,17 +11873,17 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Atividades jurídicas, exceto cartórios</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>NATAL</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -11895,25 +11895,25 @@
         <v>3</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>3550000</v>
+        <v>3600000</v>
       </c>
       <c r="K49" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>2550000</v>
+        <v>0</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>71.83</v>
+        <v>0</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS; PSD; MDB</t>
+          <t>PT; PSB; REDE</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>TARCÍSIO (REPUBLICANOS); RONALDO CAIADO (PSD)</t>
+          <t>ELMANO DE FREITAS (PT); CID GOMES (PSB)</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>23.087.346/0001-74</t>
+          <t>24.759.252/0001-67</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>VENTURA ESTUDIO LTDA</t>
+          <t>FEIRA ROTULOS E ETIQUETAS ADESIVAS LTDA</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -11938,17 +11938,17 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>FLORIANOPOLIS</t>
+          <t>FEIRA DE SANTANA</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -11957,28 +11957,28 @@
         </is>
       </c>
       <c r="I50" s="5" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>3544000</v>
+        <v>3555631.95</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>3544000</v>
+        <v>2992985.32</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>100</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT; UNIÃO; PSD; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>CAROL DE TONI (PL); JORGINHO MELLO (PL)</t>
+          <t>PROFESSORA DAYANE PIMENTEL (UNIÃO); GABRIEL NUNES (PSD)</t>
         </is>
       </c>
     </row>
@@ -11988,12 +11988,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>30.007.119/0001-57</t>
+          <t>04.639.525/0001-22</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>CONNECT FILMES - PRODUCAO DE FILMES E PUBLICIDADE LTDA</t>
+          <t>MALHEIROS, PENTEADO E TOLEDO - ADVOGADOS</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -12003,17 +12003,17 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Atividades jurídicas, exceto cartórios</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -12022,28 +12022,28 @@
         </is>
       </c>
       <c r="I51" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>3500000</v>
+        <v>3550000</v>
       </c>
       <c r="K51" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>3500000</v>
+        <v>2550000</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>100</v>
+        <v>71.83</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>REPUBLICANOS; PSD; MDB</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>TARCÍSIO (REPUBLICANOS)</t>
+          <t>TARCÍSIO (REPUBLICANOS); RONALDO CAIADO (PSD)</t>
         </is>
       </c>
     </row>
@@ -12053,12 +12053,12 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>85.057.529/0001-02</t>
+          <t>23.087.346/0001-74</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>HELLOGRAF ARTES GRAFICAS LTDA</t>
+          <t>VENTURA ESTUDIO LTDA</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -12068,17 +12068,17 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>CURITIBA</t>
+          <t>FLORIANOPOLIS</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -12087,28 +12087,28 @@
         </is>
       </c>
       <c r="I52" s="5" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>3459072.88</v>
+        <v>3544000</v>
       </c>
       <c r="K52" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>1478215.14</v>
+        <v>3544000</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>42.73</v>
+        <v>100</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>NOVO; PV; PSD; REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>ALIEL MACHADO (PV); JEFFREY CHIQUINI (NOVO)</t>
+          <t>CAROL DE TONI (PL); JORGINHO MELLO (PL)</t>
         </is>
       </c>
     </row>
@@ -12118,12 +12118,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>47.402.712/0001-09</t>
+          <t>85.057.529/0001-02</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>NE ELEICOES SPE LTDA</t>
+          <t>HELLOGRAF ARTES GRAFICAS LTDA</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -12133,17 +12133,17 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>CURITIBA</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -12152,28 +12152,28 @@
         </is>
       </c>
       <c r="I53" s="5" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>3450000</v>
+        <v>3501582.88</v>
       </c>
       <c r="K53" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>2100000</v>
+        <v>1539725.14</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>60.87</v>
+        <v>43.97</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>PSD; UNIÃO; PSDB</t>
+          <t>NOVO; PV; PSD; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>RAQUEL LYRA (PSD); MIGUEL COELHO (UNIÃO)</t>
+          <t>ALIEL MACHADO (PV); JEFFREY CHIQUINI (NOVO)</t>
         </is>
       </c>
     </row>
@@ -12183,12 +12183,12 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>89.840.797/0001-49</t>
+          <t>30.007.119/0001-57</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>GRAFICA E EDITORA COMUNICACAO IMPRESSA LTDA</t>
+          <t>CONNECT FILMES - PRODUCAO DE FILMES E PUBLICIDADE LTDA</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -12198,17 +12198,17 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Edição integrada à impressão de cadastros, listas e outros produtos gráficos</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -12217,28 +12217,28 @@
         </is>
       </c>
       <c r="I54" s="5" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>3411091.28</v>
+        <v>3500000</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>3087074.6</v>
+        <v>3500000</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>90.5</v>
+        <v>100</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>PL; PP; PDT; REPUBLICANOS</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>ZUCCO (PL); JULIANA BRIZOLA (PDT)</t>
+          <t>TARCÍSIO (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -12248,12 +12248,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>17.861.454/0001-50</t>
+          <t>47.402.712/0001-09</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>RMR CONSULTORIA DE INTELIGENCIA LTDA</t>
+          <t>NE ELEICOES SPE LTDA</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -12263,17 +12263,17 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Pesquisas de mercado e de opinião pública</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -12282,28 +12282,28 @@
         </is>
       </c>
       <c r="I55" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>3400000</v>
+        <v>3450000</v>
       </c>
       <c r="K55" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>3400000</v>
+        <v>2100000</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>100</v>
+        <v>60.87</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD; UNIÃO; PSDB</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>RAQUEL LYRA (PSD); MIGUEL COELHO (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -12313,12 +12313,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>24.347.979/0001-37</t>
+          <t>89.840.797/0001-49</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>MACIEL ART DESIGNER GRAFICO - LTDA</t>
+          <t>GRAFICA E EDITORA COMUNICACAO IMPRESSA LTDA</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -12328,17 +12328,17 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Comércio varejista de artigos recreativos e esportivos</t>
+          <t>Edição integrada à impressão de cadastros, listas e outros produtos gráficos</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -12347,28 +12347,28 @@
         </is>
       </c>
       <c r="I56" s="5" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>3345250.5</v>
+        <v>3411091.28</v>
       </c>
       <c r="K56" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>2472030</v>
+        <v>3087074.6</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>73.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>PSD; PT; PODE; REPUBLICANOS</t>
+          <t>PL; PP; PDT; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>DANIEL COELHO (PSD); LUNA ZARATTINI (PT)</t>
+          <t>ZUCCO (PL); JULIANA BRIZOLA (PDT)</t>
         </is>
       </c>
     </row>
@@ -12378,12 +12378,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>22.317.550/0001-71</t>
+          <t>17.861.454/0001-50</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>M DESIGNER CITY LTDA</t>
+          <t>RMR CONSULTORIA DE INTELIGENCIA LTDA</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -12393,17 +12393,17 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Edição de livros</t>
+          <t>Pesquisas de mercado e de opinião pública</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -12412,28 +12412,28 @@
         </is>
       </c>
       <c r="I57" s="5" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>3343294.16</v>
+        <v>3400000</v>
       </c>
       <c r="K57" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>2233258.46</v>
+        <v>3400000</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>66.8</v>
+        <v>100</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>PT; REPUBLICANOS; UNIÃO; PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>LULA (PT); JILMAR TATTO (PT)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -12443,12 +12443,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>45.443.633/0001-02</t>
+          <t>24.347.979/0001-37</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>JD IMPRESSOS PERSONALIZADOS LTDA</t>
+          <t>MACIEL ART DESIGNER GRAFICO - LTDA</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -12458,17 +12458,17 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Comércio varejista de artigos recreativos e esportivos</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>JOAO PESSOA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -12477,28 +12477,28 @@
         </is>
       </c>
       <c r="I58" s="5" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>3290879.5</v>
+        <v>3345250.5</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>2335315</v>
+        <v>2472030</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>70.95999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>PL; REPUBLICANOS; PP; UNIÃO</t>
+          <t>PSD; PT; PODE; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>EFRAIM FILHO (PL); TIÃO GOMES (REPUBLICANOS)</t>
+          <t>DANIEL COELHO (PSD); LUNA ZARATTINI (PT)</t>
         </is>
       </c>
     </row>
@@ -12508,12 +12508,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>25.188.538/0001-00</t>
+          <t>22.317.550/0001-71</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>ESSENT INOVACAO CONTABIL LTDA</t>
+          <t>M DESIGNER CITY LTDA</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -12523,17 +12523,17 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Atividades de contabilidade, consultoria e auditoria contábil e tributária</t>
+          <t>Edição de livros</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>HORIZONTINA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -12542,28 +12542,28 @@
         </is>
       </c>
       <c r="I59" s="5" t="n">
-        <v>187</v>
+        <v>43</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>3273400.86</v>
+        <v>3343294.16</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L59" s="6" t="n">
-        <v>1539153.52</v>
+        <v>2233258.46</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>47.02</v>
+        <v>66.8</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>PT; MDB; PSD; PL</t>
+          <t>PT; REPUBLICANOS; UNIÃO; PSD</t>
         </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>LULA (PT); RICARDO FERRAÇO (MDB)</t>
+          <t>LULA (PT); JILMAR TATTO (PT)</t>
         </is>
       </c>
     </row>
@@ -12573,12 +12573,12 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>00.887.925/0001-04</t>
+          <t>45.443.633/0001-02</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>GRAFMARQUES INDUSTRIA EDITORA E SERVICOS LTDA</t>
+          <t>JD IMPRESSOS PERSONALIZADOS LTDA</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -12588,17 +12588,17 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>JOAO PESSOA</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -12607,28 +12607,28 @@
         </is>
       </c>
       <c r="I60" s="5" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>3231690.9</v>
+        <v>3290879.5</v>
       </c>
       <c r="K60" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>2232704.6</v>
+        <v>2335315</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>69.09</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>MDB; UNIÃO; PSD; PP</t>
+          <t>PL; REPUBLICANOS; PP; UNIÃO</t>
         </is>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>ISNALDO BULHÕES JR (MDB); RENAN FILHO (MDB)</t>
+          <t>EFRAIM FILHO (PL); TIÃO GOMES (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -12638,12 +12638,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>21.246.199/0001-02</t>
+          <t>25.188.538/0001-00</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>LEANDRO ROSA ADVOGADOS ASSOCIADOS</t>
+          <t>ESSENT INOVACAO CONTABIL LTDA</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -12653,17 +12653,17 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Atividades jurídicas, exceto cartórios</t>
+          <t>Atividades de contabilidade, consultoria e auditoria contábil e tributária</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>CURITIBA</t>
+          <t>HORIZONTINA</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -12672,28 +12672,28 @@
         </is>
       </c>
       <c r="I61" s="5" t="n">
-        <v>8</v>
+        <v>187</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>3220000</v>
+        <v>3273400.86</v>
       </c>
       <c r="K61" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>195000</v>
+        <v>1539153.52</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>6.06</v>
+        <v>47.02</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>PL; NOVO</t>
+          <t>PT; MDB; PSD; PL</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>SERGIO MORO (PL); DELTAN DALLAGNOL (NOVO)</t>
+          <t>LULA (PT); RICARDO FERRAÇO (MDB)</t>
         </is>
       </c>
     </row>
@@ -12703,12 +12703,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>07.556.546/0001-72</t>
+          <t>00.887.925/0001-04</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>PRESSGRAF IMPORTACAO TECNOLOGIA E SERVICOS GRAFICOS LTDA</t>
+          <t>GRAFMARQUES INDUSTRIA EDITORA E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -12718,17 +12718,17 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>SALVADOR</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -12737,28 +12737,28 @@
         </is>
       </c>
       <c r="I62" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>3164378.8</v>
+        <v>3233690.9</v>
       </c>
       <c r="K62" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>2883468.8</v>
+        <v>2234704.6</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>91.12</v>
+        <v>69.11</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>PSD; REPUBLICANOS; PSDB; UNIÃO</t>
+          <t>MDB; UNIÃO; PSD; PP</t>
         </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>RAIMUNDO COSTA (PSD); MÁRCIO MARINHO (REPUBLICANOS)</t>
+          <t>ISNALDO BULHÕES JR (MDB); RENAN FILHO (MDB)</t>
         </is>
       </c>
     </row>
@@ -12768,12 +12768,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>11.197.995/0001-49</t>
+          <t>21.246.199/0001-02</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>BUCCHIANERI ADVOCACIA</t>
+          <t>LEANDRO ROSA ADVOGADOS ASSOCIADOS</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>CURITIBA</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -12802,28 +12802,28 @@
         </is>
       </c>
       <c r="I63" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>3150000</v>
+        <v>3220000</v>
       </c>
       <c r="K63" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L63" s="6" t="n">
-        <v>3150000</v>
+        <v>195000</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>100</v>
+        <v>6.06</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PL; NOVO</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>SERGIO MORO (PL); DELTAN DALLAGNOL (NOVO)</t>
         </is>
       </c>
     </row>
@@ -12833,12 +12833,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>41.470.063/0001-99</t>
+          <t>07.556.546/0001-72</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>SETE CORES INDUSTRIA E COMERCIO LTDA</t>
+          <t>PRESSGRAF IMPORTACAO TECNOLOGIA E SERVICOS GRAFICOS LTDA</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -12848,17 +12848,17 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>SAO LUIS</t>
+          <t>SALVADOR</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -12867,28 +12867,28 @@
         </is>
       </c>
       <c r="I64" s="5" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>3122716.46</v>
+        <v>3164378.8</v>
       </c>
       <c r="K64" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>2736315.46</v>
+        <v>2883468.8</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>87.63</v>
+        <v>91.12</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>PL; PCDOB; PDT; REPUBLICANOS</t>
+          <t>PSD; REPUBLICANOS; PSDB; UNIÃO</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>SILVIO ANTÔNIO (PL); MÁRCIO JERRY (PCDOB)</t>
+          <t>RAIMUNDO COSTA (PSD); MÁRCIO MARINHO (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -12932,19 +12932,19 @@
         </is>
       </c>
       <c r="I65" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>3102120</v>
+        <v>3128920</v>
       </c>
       <c r="K65" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L65" s="6" t="n">
-        <v>2681385</v>
+        <v>2713435</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>86.44</v>
+        <v>86.72</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
@@ -12963,12 +12963,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>17.940.670/0001-90</t>
+          <t>41.470.063/0001-99</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>C. KZAN</t>
+          <t>SETE CORES INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -12978,17 +12978,17 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>BELEM</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -12997,28 +12997,28 @@
         </is>
       </c>
       <c r="I66" s="5" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>3093159.25</v>
+        <v>3122716.46</v>
       </c>
       <c r="K66" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L66" s="6" t="n">
-        <v>1889810</v>
+        <v>2736315.46</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>61.1</v>
+        <v>87.63</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>PODE; MDB; PSD; PDT</t>
+          <t>PL; PCDOB; PDT; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>DR. DANIEL (PODE); DRA. ALESSANDRA HABER (PODE)</t>
+          <t>SILVIO ANTÔNIO (PL); MÁRCIO JERRY (PCDOB)</t>
         </is>
       </c>
     </row>
@@ -13028,12 +13028,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>35.844.647/0001-84</t>
+          <t>24.935.788/0001-96</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>J C SILVA LTDA</t>
+          <t>AFA INDUSTRIA COMERCIO E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -13043,17 +13043,17 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de embalagens de papel</t>
+          <t>Confecção de roupas profissionais</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>TERESINA</t>
+          <t>APARECIDA DE GOIANIA</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -13062,28 +13062,28 @@
         </is>
       </c>
       <c r="I67" s="5" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>3072492</v>
+        <v>3101962.1</v>
       </c>
       <c r="K67" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L67" s="6" t="n">
-        <v>2946822</v>
+        <v>2273937.1</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>95.91</v>
+        <v>73.31</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>PP; PT; MDB; PSD</t>
+          <t>SOLIDARIEDADE; UNIÃO; PSDB; MDB</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>AMANDA GENTIL (PP); ÁTILA LIRA (PP)</t>
+          <t>DENES PEREIRA (SOLIDARIEDADE); SALMA DA PESTALOZZI (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -13093,12 +13093,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>30.985.686/0001-88</t>
+          <t>17.940.670/0001-90</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>INK IMPRESSAO DE  MATERIAL PUBLICITARIO, ENCADERNACAO E EDICAO DE CADASTROS LTDA</t>
+          <t>C. KZAN</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -13113,12 +13113,12 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>JOAO PESSOA</t>
+          <t>BELEM</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -13130,25 +13130,25 @@
         <v>15</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>3051300</v>
+        <v>3093159.25</v>
       </c>
       <c r="K68" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>2235665</v>
+        <v>1889810</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>73.27</v>
+        <v>61.1</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>PSD; PODE; MDB; UNIÃO</t>
+          <t>PODE; MDB; PSD; PDT</t>
         </is>
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>DOUTOR JHONY (PSD); MERSINHO LUCENA (PSD)</t>
+          <t>DR. DANIEL (PODE); DRA. ALESSANDRA HABER (PODE)</t>
         </is>
       </c>
     </row>
@@ -13158,12 +13158,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>46.439.622/0001-11</t>
+          <t>47.461.986/0001-60</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>FEIRA BANDEIRAS E IMPRESSOS LTDA</t>
+          <t>BLUEGRAF EDITORA LTDA</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -13173,17 +13173,17 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>FEIRA DE SANTANA</t>
+          <t>GUARULHOS</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -13192,28 +13192,28 @@
         </is>
       </c>
       <c r="I69" s="5" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>3032135.98</v>
+        <v>3078931.38</v>
       </c>
       <c r="K69" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L69" s="6" t="n">
-        <v>2828179.49</v>
+        <v>2488678.08</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>93.27</v>
+        <v>80.83</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO; PT; PSB; PSD</t>
+          <t>PSD; PL; PP; PODE</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>PROFESSORA DAYANE PIMENTEL (UNIÃO); VITOR BONFIM (PSB)</t>
+          <t>WALTER IHOSHI (PSD); DRA. SANDRA TADEU (PL)</t>
         </is>
       </c>
     </row>
@@ -13223,12 +13223,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>23.444.709/0001-81</t>
+          <t>35.844.647/0001-84</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>SIEART GRAFICA E EDITORA LTDA</t>
+          <t>J C SILVA LTDA</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Fabricação de embalagens de papel</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>PARNAIBA</t>
+          <t>TERESINA</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -13257,28 +13257,28 @@
         </is>
       </c>
       <c r="I70" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>3031718.5</v>
+        <v>3072492</v>
       </c>
       <c r="K70" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>2735748.5</v>
+        <v>2946822</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>90.23999999999999</v>
+        <v>95.91</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>PT; PP; PL; MDB</t>
+          <t>PP; PT; MDB; PSD</t>
         </is>
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>RAFAEL FONTELES (PT); JÚNIOR PERCY (PP)</t>
+          <t>AMANDA GENTIL (PP); ÁTILA LIRA (PP)</t>
         </is>
       </c>
     </row>
@@ -13288,12 +13288,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>24.935.788/0001-96</t>
+          <t>30.985.686/0001-88</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>AFA INDUSTRIA COMERCIO E SERVICOS LTDA</t>
+          <t>INK IMPRESSAO DE  MATERIAL PUBLICITARIO, ENCADERNACAO E EDICAO DE CADASTROS LTDA</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -13303,17 +13303,17 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Confecção de roupas profissionais</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>APARECIDA DE GOIANIA</t>
+          <t>JOAO PESSOA</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -13322,28 +13322,28 @@
         </is>
       </c>
       <c r="I71" s="5" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>3014142.1</v>
+        <v>3051300</v>
       </c>
       <c r="K71" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L71" s="6" t="n">
-        <v>2169411.1</v>
+        <v>2235665</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>71.97</v>
+        <v>73.27</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE; UNIÃO; PSDB; MDB</t>
+          <t>PSD; PODE; MDB; UNIÃO</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>DENES PEREIRA (SOLIDARIEDADE); SALMA DA PESTALOZZI (UNIÃO)</t>
+          <t>DOUTOR JHONY (PSD); MERSINHO LUCENA (PSD)</t>
         </is>
       </c>
     </row>
@@ -13353,12 +13353,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>07.046.094/0001-89</t>
+          <t>46.439.622/0001-11</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>ELYON SOLUCOES GRAFICAS LTDA</t>
+          <t>FEIRA BANDEIRAS E IMPRESSOS LTDA</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -13368,17 +13368,17 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>FEIRA DE SANTANA</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -13390,25 +13390,25 @@
         <v>35</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>3004398.31</v>
+        <v>3032135.98</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>1659250.29</v>
+        <v>2828179.49</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>55.23</v>
+        <v>93.27</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>PL; PSD; PT; PP</t>
+          <t>UNIÃO; PT; PSB; PSD</t>
         </is>
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>ZÉ TROVÃO (PL); ÂNGELA MALUF (PSD)</t>
+          <t>PROFESSORA DAYANE PIMENTEL (UNIÃO); VITOR BONFIM (PSB)</t>
         </is>
       </c>
     </row>
@@ -13418,12 +13418,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>52.272.919/0001-38</t>
+          <t>23.444.709/0001-81</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>JANELA COMUNICACAO LTDA</t>
+          <t>SIEART GRAFICA E EDITORA LTDA</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -13433,17 +13433,17 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>PARNAIBA</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -13452,28 +13452,28 @@
         </is>
       </c>
       <c r="I73" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>3000000</v>
+        <v>3031718.5</v>
       </c>
       <c r="K73" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L73" s="6" t="n">
-        <v>3000000</v>
+        <v>2735748.5</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>100</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PT; PP; PL; MDB</t>
         </is>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>MARCONI PERILLO (PSDB)</t>
+          <t>RAFAEL FONTELES (PT); JÚNIOR PERCY (PP)</t>
         </is>
       </c>
     </row>
@@ -13483,12 +13483,12 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>05.677.050/0001-21</t>
+          <t>07.046.094/0001-89</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>ANS IMPRESSOES GRAFICAS LTDA.</t>
+          <t>ELYON SOLUCOES GRAFICAS LTDA</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -13498,17 +13498,17 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -13517,28 +13517,28 @@
         </is>
       </c>
       <c r="I74" s="5" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>2975389.15</v>
+        <v>3008940.14</v>
       </c>
       <c r="K74" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L74" s="6" t="n">
-        <v>2315402.99</v>
+        <v>1693341.36</v>
       </c>
       <c r="M74" s="6" t="n">
-        <v>77.81999999999999</v>
+        <v>56.28</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>PP; NOVO; PL; PSD</t>
+          <t>PL; PSD; PT; PP</t>
         </is>
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>ANY ORTIZ (PP); JESSÉ SANGALLI (PL)</t>
+          <t>ZÉ TROVÃO (PL); ÂNGELA MALUF (PSD)</t>
         </is>
       </c>
     </row>
@@ -13548,12 +13548,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>27.830.860/0001-09</t>
+          <t>52.272.919/0001-38</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>F PIRES PRODUCOES DE EVENTOS, COMERCIO E SERVICOS LTDA</t>
+          <t>JANELA COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -13563,17 +13563,17 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de produtos diversos não especificados anteriormente</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>BELEM</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -13582,28 +13582,28 @@
         </is>
       </c>
       <c r="I75" s="5" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>2974854</v>
+        <v>3000000</v>
       </c>
       <c r="K75" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L75" s="6" t="n">
-        <v>2974854</v>
+        <v>3000000</v>
       </c>
       <c r="M75" s="6" t="n">
         <v>100</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>DELEGADO FEDERAL EGUCHI (REPUBLICANOS); WR DO TAPAJÓS (REPUBLICANOS)</t>
+          <t>MARCONI PERILLO (PSDB)</t>
         </is>
       </c>
     </row>
@@ -13613,12 +13613,12 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>47.461.986/0001-60</t>
+          <t>05.677.050/0001-21</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>BLUEGRAF EDITORA LTDA</t>
+          <t>ANS IMPRESSOES GRAFICAS LTDA.</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -13628,17 +13628,17 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>GUARULHOS</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -13647,28 +13647,28 @@
         </is>
       </c>
       <c r="I76" s="5" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>2952478.38</v>
+        <v>2975389.15</v>
       </c>
       <c r="K76" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L76" s="6" t="n">
-        <v>2370661.08</v>
+        <v>2315687.99</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>80.29000000000001</v>
+        <v>77.83</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>PSD; PL; PODE; PP</t>
+          <t>PP; NOVO; PL; PSD</t>
         </is>
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>WALTER IHOSHI (PSD); DRA. SANDRA TADEU (PL)</t>
+          <t>ANY ORTIZ (PP); JESSÉ SANGALLI (PL)</t>
         </is>
       </c>
     </row>
@@ -13678,12 +13678,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>00.212.872/0001-13</t>
+          <t>27.830.860/0001-09</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>ASA SUL INDUSTRIA E COMERCIO DE MALHAS LTDA</t>
+          <t>F PIRES PRODUCOES DE EVENTOS, COMERCIO E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -13693,17 +13693,17 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Confecção de peças do vestuário, exceto roupas íntimas</t>
+          <t>Fabricação de produtos diversos não especificados anteriormente</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>FORTALEZA</t>
+          <t>BELEM</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -13712,28 +13712,28 @@
         </is>
       </c>
       <c r="I77" s="5" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>2908749</v>
+        <v>2974854</v>
       </c>
       <c r="K77" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L77" s="6" t="n">
-        <v>2611639</v>
+        <v>2974854</v>
       </c>
       <c r="M77" s="6" t="n">
-        <v>89.79000000000001</v>
+        <v>100</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>PSB; PT; UNIÃO; PRD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>DAYANY DO CAPITÃO (UNIÃO); TAINAH MARINHO (PSB)</t>
+          <t>DELEGADO FEDERAL EGUCHI (REPUBLICANOS); WR DO TAPAJÓS (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -13743,12 +13743,12 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>09.521.937/0001-87</t>
+          <t>00.212.872/0001-13</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>ECOPRINT SERVICOS GRAFICOS LTDA</t>
+          <t>ASA SUL INDUSTRIA E COMERCIO DE MALHAS LTDA</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Confecção de peças do vestuário, exceto roupas íntimas</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>JUAZEIRO DO NORTE</t>
+          <t>FORTALEZA</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -13777,28 +13777,28 @@
         </is>
       </c>
       <c r="I78" s="5" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>2893829.38</v>
+        <v>2908749</v>
       </c>
       <c r="K78" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L78" s="6" t="n">
-        <v>2803418.38</v>
+        <v>2611639</v>
       </c>
       <c r="M78" s="6" t="n">
-        <v>96.88</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>MDB; CIDADANIA; PSD; UNIÃO</t>
+          <t>PSB; PT; UNIÃO; PRD</t>
         </is>
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>YURY DO PAREDÃO (MDB); SANDRINHA CAVALCANTE (CIDADANIA)</t>
+          <t>DAYANY DO CAPITÃO (UNIÃO); TAINAH MARINHO (PSB)</t>
         </is>
       </c>
     </row>
@@ -13808,12 +13808,12 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>56.019.930/0001-41</t>
+          <t>09.521.937/0001-87</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>INOVE IMPRESSOES GRAFICAS E MARKETING POLITICO LTDA</t>
+          <t>ECOPRINT SERVICOS GRAFICOS LTDA</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -13828,12 +13828,12 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>JUAZEIRO DO NORTE</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -13842,28 +13842,28 @@
         </is>
       </c>
       <c r="I79" s="5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>2803233.41</v>
+        <v>2893829.38</v>
       </c>
       <c r="K79" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L79" s="6" t="n">
-        <v>1861331.53</v>
+        <v>2803418.38</v>
       </c>
       <c r="M79" s="6" t="n">
-        <v>66.40000000000001</v>
+        <v>96.88</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>PL; PSB; UNIÃO; REPUBLICANOS</t>
+          <t>MDB; CIDADANIA; PSD; UNIÃO</t>
         </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>VINICIUS DINIZ (PL); BERNARDO ROSSI (UNIÃO)</t>
+          <t>YURY DO PAREDÃO (MDB); SANDRINHA CAVALCANTE (CIDADANIA)</t>
         </is>
       </c>
     </row>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>60.496.721/0001-66</t>
+          <t>64.433.090/0001-97</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>LRS COMUNICACAO E CONSULTORIA LTDA</t>
+          <t>GAB INDUSTRIA GRAFICA LTDA</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -13888,17 +13888,17 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>NEROPOLIS</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -13907,28 +13907,28 @@
         </is>
       </c>
       <c r="I80" s="5" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>2800000</v>
+        <v>2840200.19</v>
       </c>
       <c r="K80" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L80" s="6" t="n">
-        <v>1585000</v>
+        <v>2552414.88</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>56.61</v>
+        <v>89.87</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>REDE; PSD; PSOL; PT</t>
+          <t>UNIÃO; PT; MDB; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>MARINA SILVA (REDE); RACHEL SHEHERAZADE (PSD)</t>
+          <t>GRACINHA CAIADO (UNIÃO); MARUSSA BOLDRIN (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -13938,12 +13938,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>64.433.090/0001-97</t>
+          <t>56.019.930/0001-41</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>GAB INDUSTRIA GRAFICA LTDA</t>
+          <t>INOVE IMPRESSOES GRAFICAS E MARKETING POLITICO LTDA</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -13958,12 +13958,12 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>NEROPOLIS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -13972,28 +13972,28 @@
         </is>
       </c>
       <c r="I81" s="5" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>2762102.16</v>
+        <v>2803233.41</v>
       </c>
       <c r="K81" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L81" s="6" t="n">
-        <v>2474316.85</v>
+        <v>2065519.03</v>
       </c>
       <c r="M81" s="6" t="n">
-        <v>89.58</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO; PT; MDB; REPUBLICANOS</t>
+          <t>PL; PSB; UNIÃO; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>GRACINHA CAIADO (UNIÃO); MARUSSA BOLDRIN (REPUBLICANOS)</t>
+          <t>VINICIUS DINIZ (PL); BERNARDO ROSSI (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -14003,12 +14003,12 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>61.144.095/0001-01</t>
+          <t>60.496.721/0001-66</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>SUDESTE GRAFICA LTDA</t>
+          <t>LRS COMUNICACAO E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -14018,17 +14018,17 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>LEOPOLDINA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -14037,28 +14037,28 @@
         </is>
       </c>
       <c r="I82" s="5" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>2755239.1</v>
+        <v>2800000</v>
       </c>
       <c r="K82" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L82" s="6" t="n">
-        <v>2195722.4</v>
+        <v>1585000</v>
       </c>
       <c r="M82" s="6" t="n">
-        <v>79.69</v>
+        <v>56.61</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>PL; REPUBLICANOS; PSDB; AVANTE</t>
+          <t>REDE; PSD; PSOL; PT</t>
         </is>
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>DANI CUNHA (PL); EDUARDO CUNHA (REPUBLICANOS)</t>
+          <t>MARINA SILVA (REDE); RACHEL SHEHERAZADE (PSD)</t>
         </is>
       </c>
     </row>
@@ -14068,12 +14068,12 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>17.620.604/0001-33</t>
+          <t>61.144.095/0001-01</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>T. P. MONTENEGRO GRAFICA LTDA</t>
+          <t>SUDESTE GRAFICA LTDA</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -14083,17 +14083,17 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Edição de livros</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>BELEM</t>
+          <t>LEOPOLDINA</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -14102,28 +14102,28 @@
         </is>
       </c>
       <c r="I83" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>2715232.4</v>
+        <v>2755239.1</v>
       </c>
       <c r="K83" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L83" s="6" t="n">
-        <v>558352</v>
+        <v>2195722.4</v>
       </c>
       <c r="M83" s="6" t="n">
-        <v>20.56</v>
+        <v>79.69</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>MDB; PSD; PODE; UNIÃO</t>
+          <t>PL; REPUBLICANOS; PSDB; AVANTE</t>
         </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>ANTONIO DOIDO (MDB); DR. FURLAN (PSD)</t>
+          <t>DANI CUNHA (PL); EDUARDO CUNHA (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -14306,10 +14306,10 @@
         <v>0.05</v>
       </c>
       <c r="L86" s="6" t="n">
-        <v>1064250</v>
+        <v>1314250</v>
       </c>
       <c r="M86" s="6" t="n">
-        <v>40.71</v>
+        <v>50.27</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
@@ -14436,10 +14436,10 @@
         <v>0.05</v>
       </c>
       <c r="L88" s="6" t="n">
-        <v>1848705</v>
+        <v>2107905</v>
       </c>
       <c r="M88" s="6" t="n">
-        <v>71.55</v>
+        <v>81.58</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
@@ -14631,10 +14631,10 @@
         <v>0.05</v>
       </c>
       <c r="L91" s="6" t="n">
-        <v>1790382.1</v>
+        <v>1832692.1</v>
       </c>
       <c r="M91" s="6" t="n">
-        <v>69.83</v>
+        <v>71.48</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
@@ -14848,12 +14848,12 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>05.555.136/0001-81</t>
+          <t>68.154.614/0001-61</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>CONDADO MARKETING LTDA</t>
+          <t>ESTUDIO 90 PRODUCOES LTDA</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -14873,7 +14873,7 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>LAJEADO</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -14882,7 +14882,7 @@
         </is>
       </c>
       <c r="I95" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J95" s="6" t="n">
         <v>2500000</v>
@@ -14898,12 +14898,12 @@
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>MDB; PSD</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>JULIANA BRIZOLA (PDT)</t>
+          <t>GABRIEL SOUZA (MDB); FREDERICO ANTUNES (PSD)</t>
         </is>
       </c>
     </row>
@@ -14978,12 +14978,12 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>68.154.614/0001-61</t>
+          <t>05.555.136/0001-81</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>ESTUDIO 90 PRODUCOES LTDA</t>
+          <t>CONDADO MARKETING LTDA</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>LAJEADO</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -15012,7 +15012,7 @@
         </is>
       </c>
       <c r="I97" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J97" s="6" t="n">
         <v>2500000</v>
@@ -15028,12 +15028,12 @@
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>MDB; PSD</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>GABRIEL SOUZA (MDB); FREDERICO ANTUNES (PSD)</t>
+          <t>JULIANA BRIZOLA (PDT)</t>
         </is>
       </c>
     </row>
@@ -15495,14 +15495,14 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
         </is>
       </c>
     </row>
@@ -15626,13 +15626,13 @@
         <v>1417</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>971778352.83</v>
+        <v>972028352.83</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>14.79</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="6">
@@ -15664,7 +15664,7 @@
         <v>597767672.99</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="7">
@@ -15690,10 +15690,10 @@
         <v>704</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>532558048.97</v>
+        <v>532565326.54</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>8.1</v>
@@ -15728,7 +15728,7 @@
         <v>486877337.61</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>7.41</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="9">
@@ -15760,7 +15760,7 @@
         <v>472886618.52</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>7.2</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="10">
@@ -15792,7 +15792,7 @@
         <v>402817607.56</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="11">
@@ -15815,16 +15815,16 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1417</v>
+        <v>1422</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>361936325.06</v>
+        <v>362852325.06</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>5.51</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="12">
@@ -15856,7 +15856,7 @@
         <v>233648027.03</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="13">
@@ -15879,13 +15879,13 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>208376091.46</v>
+        <v>208526091.46</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>3.17</v>
@@ -15914,10 +15914,10 @@
         <v>596</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>142245368.76</v>
+        <v>142270368.76</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>2.16</v>
@@ -15946,13 +15946,13 @@
         <v>521</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>140309968.88</v>
+        <v>140317788.88</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="16">
@@ -15975,13 +15975,13 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>122283891.09</v>
+        <v>122302507.59</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>1.86</v>
@@ -16135,13 +16135,13 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>49387686</v>
+        <v>49399186</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>0.75</v>
@@ -16359,13 +16359,13 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1233</v>
+        <v>1257</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>2466</v>
+        <v>2550</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>16186752.98</v>
+        <v>16342043.63</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0.25</v>
@@ -16711,13 +16711,13 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>6398441.92</v>
+        <v>6401744.69</v>
       </c>
       <c r="H39" s="6" t="n">
         <v>0.1</v>
@@ -16775,13 +16775,13 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>6019815.61</v>
+        <v>6025193.61</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>0.09</v>
@@ -16848,7 +16848,7 @@
         <v>5590239.71</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="44">
@@ -16906,10 +16906,10 @@
         <v>72</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>5361904</v>
+        <v>5372279</v>
       </c>
       <c r="H45" s="6" t="n">
         <v>0.08</v>
@@ -16953,7 +16953,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS - MINAS GERAIS - MG - ESTADUAL</t>
+          <t>UNIAO BRASIL - MARANHAO - MA- ESTADUAL</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -16963,17 +16963,17 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="F47" s="5" t="n">
-        <v>174</v>
-      </c>
       <c r="G47" s="6" t="n">
-        <v>5253552.74</v>
+        <v>5299000</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0.08</v>
@@ -16985,7 +16985,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>PARTIDO SOCIAL DEMOCRATICO</t>
+          <t>REPUBLICANOS - MINAS GERAIS - MG - ESTADUAL</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -16995,17 +16995,17 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>5225000</v>
+        <v>5253552.74</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>0.08</v>
@@ -17017,7 +17017,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>UNIAO BRASIL - MARANHAO - MA- ESTADUAL</t>
+          <t>PARTIDO SOCIAL DEMOCRATICO</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
@@ -17037,7 +17037,7 @@
         <v>47</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>5199000</v>
+        <v>5225000</v>
       </c>
       <c r="H49" s="6" t="n">
         <v>0.08</v>
@@ -17206,14 +17206,14 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
         </is>
       </c>
     </row>
@@ -17313,10 +17313,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>941059970.52</v>
+        <v>941352416.62</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>12.9</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="6">
@@ -17336,10 +17336,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>773225038.47</v>
+        <v>777520950.29</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>10.6</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="7">
@@ -17359,7 +17359,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>539785425.37</v>
+        <v>540061272.24</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>7.4</v>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>501598033.74</v>
+        <v>501738323.89</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>6.88</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="9">
@@ -17405,10 +17405,10 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>348267772.86</v>
+        <v>348382819.68</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>4.78</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="10">
@@ -17428,10 +17428,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>346616717.24</v>
+        <v>347809594.83</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="11">
@@ -17451,7 +17451,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>319738833.72</v>
+        <v>319875531.57</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.38</v>
@@ -17474,7 +17474,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>260541558.01</v>
+        <v>260673741.06</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>3.57</v>
@@ -17497,7 +17497,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>248624871.27</v>
+        <v>248641151.84</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>3.41</v>
@@ -17520,10 +17520,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>232655729.4</v>
+        <v>233323038.34</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="15">
@@ -17543,7 +17543,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>223689101.98</v>
+        <v>223955484.48</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>3.07</v>
@@ -17566,7 +17566,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>216368096.53</v>
+        <v>216778997.14</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>2.97</v>
@@ -17589,10 +17589,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>206745533</v>
+        <v>206867725.89</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="18">
@@ -17612,7 +17612,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>191668164.35</v>
+        <v>191797404.38</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>2.63</v>
@@ -17635,7 +17635,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>189498535.69</v>
+        <v>189645533.43</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>2.6</v>
@@ -17658,7 +17658,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>176399645.6</v>
+        <v>176762535.6</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>2.42</v>
@@ -17681,7 +17681,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>162804286.45</v>
+        <v>162812264.63</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>2.23</v>
@@ -17704,7 +17704,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>149704962.6</v>
+        <v>149734962.6</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>2.05</v>
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>147117921.93</v>
+        <v>147135522.01</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>2.02</v>
@@ -17750,7 +17750,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>145328090.58</v>
+        <v>145383532.58</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>1.99</v>
@@ -17773,10 +17773,10 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>135306463.94</v>
+        <v>135383050.09</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="26">
@@ -17796,7 +17796,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>134802502.61</v>
+        <v>134862023.11</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>1.85</v>
@@ -17819,7 +17819,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>123147279.67</v>
+        <v>123176777.67</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>1.69</v>
@@ -17842,7 +17842,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>121101896.75</v>
+        <v>121115288.53</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>1.66</v>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>118148055.06</v>
+        <v>118181676.81</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>1.62</v>
@@ -17888,7 +17888,7 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>116578380.72</v>
+        <v>116715353.72</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>1.6</v>
@@ -17934,7 +17934,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>105927367.84</v>
+        <v>105927597.84</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>1.45</v>
@@ -17957,7 +17957,7 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>148128914.06</v>
+        <v>148150465.81</v>
       </c>
       <c r="E33" s="12" t="n">
         <v>23.46</v>
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>35742843.27</v>
+        <v>35743802.27</v>
       </c>
       <c r="E35" s="12" t="n">
         <v>5.66</v>
@@ -18072,10 +18072,10 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>28214065.41</v>
+        <v>27986415.41</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>4.47</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="39">
@@ -18095,7 +18095,7 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>22096617.42</v>
+        <v>22106720.42</v>
       </c>
       <c r="E39" s="12" t="n">
         <v>3.5</v>
@@ -18118,7 +18118,7 @@
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>21166735.92</v>
+        <v>21168199.92</v>
       </c>
       <c r="E40" s="12" t="n">
         <v>3.35</v>
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>18066288.75</v>
+        <v>18076663.75</v>
       </c>
       <c r="E41" s="12" t="n">
         <v>2.86</v>
@@ -18233,10 +18233,10 @@
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>16369200.1</v>
+        <v>16469200.1</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="46">
@@ -18302,7 +18302,7 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>14752756.34</v>
+        <v>14754856.34</v>
       </c>
       <c r="E48" s="12" t="n">
         <v>2.34</v>
@@ -18348,7 +18348,7 @@
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>12944500.35</v>
+        <v>12945389.35</v>
       </c>
       <c r="E50" s="12" t="n">
         <v>2.05</v>
@@ -18394,10 +18394,10 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>11635177.76</v>
+        <v>11715177.76</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="53">
@@ -18486,7 +18486,7 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>7868612.31</v>
+        <v>7868672.31</v>
       </c>
       <c r="E56" s="12" t="n">
         <v>1.25</v>
@@ -18601,7 +18601,7 @@
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>622102134.8</v>
+        <v>622130571.3</v>
       </c>
       <c r="E61" s="12" t="n">
         <v>11.48</v>
@@ -18647,7 +18647,7 @@
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>412211008.89</v>
+        <v>412234740.22</v>
       </c>
       <c r="E63" s="12" t="n">
         <v>7.61</v>
@@ -18670,7 +18670,7 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>375586208.06</v>
+        <v>375591669.06</v>
       </c>
       <c r="E64" s="12" t="n">
         <v>6.93</v>
@@ -18693,7 +18693,7 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>282869261.37</v>
+        <v>282895761.37</v>
       </c>
       <c r="E65" s="12" t="n">
         <v>5.22</v>
@@ -18739,10 +18739,10 @@
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>237590400.29</v>
+        <v>238190400.29</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>4.39</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="68">
@@ -18762,7 +18762,7 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>199505839.32</v>
+        <v>199540439.32</v>
       </c>
       <c r="E68" s="12" t="n">
         <v>3.68</v>
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>172963239.83</v>
+        <v>173113239.83</v>
       </c>
       <c r="E70" s="12" t="n">
         <v>3.19</v>
@@ -18831,7 +18831,7 @@
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>164214758.19</v>
+        <v>164218808.19</v>
       </c>
       <c r="E71" s="12" t="n">
         <v>3.03</v>
@@ -18923,7 +18923,7 @@
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>134561947.2</v>
+        <v>134562015.2</v>
       </c>
       <c r="E75" s="12" t="n">
         <v>2.48</v>
@@ -18946,7 +18946,7 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>127622892.47</v>
+        <v>127872892.47</v>
       </c>
       <c r="E76" s="12" t="n">
         <v>2.36</v>
@@ -19015,7 +19015,7 @@
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>106528005.98</v>
+        <v>106535283.55</v>
       </c>
       <c r="E79" s="12" t="n">
         <v>1.97</v>
@@ -19245,10 +19245,10 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>819200968.3099999</v>
+        <v>826003852.21</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>25.99</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="90">
@@ -19268,10 +19268,10 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>203760481.7</v>
+        <v>203873157.36</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>6.46</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="91">
@@ -19291,10 +19291,10 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>187408260</v>
+        <v>187674729.31</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>5.95</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="92">
@@ -19314,10 +19314,10 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>156239331.41</v>
+        <v>156351988.77</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4.96</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="93">
@@ -19337,10 +19337,10 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>141222145.56</v>
+        <v>143718170.64</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="94">
@@ -19360,10 +19360,10 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>129097965.33</v>
+        <v>129822127.23</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="95">
@@ -19383,10 +19383,10 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>126758185.15</v>
+        <v>126952208.92</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
@@ -19406,10 +19406,10 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>118476033.04</v>
+        <v>118896945.02</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="97">
@@ -19420,19 +19420,19 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>108241241.27</v>
+        <v>108567682.72</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="98">
@@ -19443,19 +19443,19 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>107981951.67</v>
+        <v>108474024.08</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="99">
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>96006194.84999999</v>
+        <v>96209682.41</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="100">
@@ -19498,10 +19498,10 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>93917224.66</v>
+        <v>93947507.66</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="101">
@@ -19521,10 +19521,10 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>86582945.14</v>
+        <v>87597105.36</v>
       </c>
       <c r="E101" s="12" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="102">
@@ -19544,10 +19544,10 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>86092672.01000001</v>
+        <v>86176267.23999999</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="103">
@@ -19567,10 +19567,10 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>75762869.03</v>
+        <v>78719268.72</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="104">
@@ -19590,10 +19590,10 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>73419187.95</v>
+        <v>73512652.16</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="105">
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>70424428.56</v>
+        <v>70490467.59999999</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="106">
@@ -19636,10 +19636,10 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>60503975.33</v>
+        <v>60567880.04</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="107">
@@ -19659,10 +19659,10 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>57058343.64</v>
+        <v>57992375.47</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="108">
@@ -19682,10 +19682,10 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>53893372</v>
+        <v>54082320.9</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="109">
@@ -19705,7 +19705,7 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>53447799.64</v>
+        <v>53978496.57</v>
       </c>
       <c r="E109" s="12" t="n">
         <v>1.7</v>
@@ -19728,10 +19728,10 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>51728551.85</v>
+        <v>51730364.17</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="111">
@@ -19751,10 +19751,10 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>48103744.51</v>
+        <v>49088929.85</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="112">
@@ -19774,10 +19774,10 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>47807081.22</v>
+        <v>47810880.66</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="113">
@@ -19797,10 +19797,10 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>37694623.51</v>
+        <v>37706072.69</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="114">
@@ -19820,7 +19820,7 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>31677684.79</v>
+        <v>31679646.88</v>
       </c>
       <c r="E114" s="12" t="n">
         <v>1</v>
@@ -19843,10 +19843,10 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>28288903.28</v>
+        <v>29064493.28</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="116">
@@ -19912,10 +19912,10 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>147514746.61</v>
+        <v>147573990.29</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>20.12</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="119">
@@ -19935,10 +19935,10 @@
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>57727971.49</v>
+        <v>57846735.76</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>7.87</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="120">
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>51809041.72</v>
+        <v>51841352.22</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>7.07</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="121">
@@ -19981,10 +19981,10 @@
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>50738196.27</v>
+        <v>50868591.02</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>6.92</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="122">
@@ -20004,10 +20004,10 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>34707428.84</v>
+        <v>34915659.34</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="123">
@@ -20027,7 +20027,7 @@
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>33467956.25</v>
+        <v>33472930.43</v>
       </c>
       <c r="E123" s="12" t="n">
         <v>4.56</v>
@@ -20050,7 +20050,7 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>31366123.89</v>
+        <v>31437670.23</v>
       </c>
       <c r="E124" s="12" t="n">
         <v>4.28</v>
@@ -20073,10 +20073,10 @@
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>28100937.52</v>
+        <v>28206250.02</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="126">
@@ -20096,7 +20096,7 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>23009813.25</v>
+        <v>23030946.25</v>
       </c>
       <c r="E126" s="12" t="n">
         <v>3.14</v>
@@ -20119,10 +20119,10 @@
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>22535382.27</v>
+        <v>22637064.86</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="128">
@@ -20142,10 +20142,10 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>22087424.13</v>
+        <v>22168761.28</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="129">
@@ -20165,10 +20165,10 @@
         </is>
       </c>
       <c r="D129" s="6" t="n">
-        <v>21898220.38</v>
+        <v>21998322.88</v>
       </c>
       <c r="E129" s="12" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -20188,10 +20188,10 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>21792874.57</v>
+        <v>21892874.57</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="131">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>20545294.26</v>
+        <v>20558685.04</v>
       </c>
       <c r="E131" s="12" t="n">
         <v>2.8</v>
@@ -20257,7 +20257,7 @@
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>16520926.37</v>
+        <v>16535448.12</v>
       </c>
       <c r="E133" s="12" t="n">
         <v>2.25</v>
@@ -20280,7 +20280,7 @@
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>16282903.9</v>
+        <v>16270903.9</v>
       </c>
       <c r="E134" s="12" t="n">
         <v>2.22</v>
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>15926469.38</v>
+        <v>15962369.38</v>
       </c>
       <c r="E135" s="12" t="n">
         <v>2.17</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>14974917.8</v>
+        <v>14974250.85</v>
       </c>
       <c r="E136" s="12" t="n">
         <v>2.04</v>
@@ -20349,7 +20349,7 @@
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>14584812.03</v>
+        <v>14599052.6</v>
       </c>
       <c r="E137" s="12" t="n">
         <v>1.99</v>
@@ -20418,10 +20418,10 @@
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>9856868.189999999</v>
+        <v>9915138.689999999</v>
       </c>
       <c r="E140" s="12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="141">
@@ -20441,7 +20441,7 @@
         </is>
       </c>
       <c r="D141" s="6" t="n">
-        <v>9184562.65</v>
+        <v>9208910.65</v>
       </c>
       <c r="E141" s="12" t="n">
         <v>1.25</v>
@@ -20467,7 +20467,7 @@
         <v>8626908.92</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="143">
@@ -20510,7 +20510,7 @@
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>7776948.3</v>
+        <v>7778510.3</v>
       </c>
       <c r="E144" s="12" t="n">
         <v>1.06</v>
@@ -20533,10 +20533,10 @@
         </is>
       </c>
       <c r="D145" s="6" t="n">
-        <v>97323954.7</v>
+        <v>97510234.92</v>
       </c>
       <c r="E145" s="12" t="n">
-        <v>13.79</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="146">
@@ -20556,10 +20556,10 @@
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>79841958.22</v>
+        <v>79993260.81999999</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>11.31</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="147">
@@ -20579,10 +20579,10 @@
         </is>
       </c>
       <c r="D147" s="6" t="n">
-        <v>50691029.56</v>
+        <v>53079939.7</v>
       </c>
       <c r="E147" s="12" t="n">
-        <v>7.18</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="148">
@@ -20605,7 +20605,7 @@
         <v>38817828.78</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="149">
@@ -20625,10 +20625,10 @@
         </is>
       </c>
       <c r="D149" s="6" t="n">
-        <v>38288117.59</v>
+        <v>38384306.24</v>
       </c>
       <c r="E149" s="12" t="n">
-        <v>5.42</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="150">
@@ -20648,10 +20648,10 @@
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>36987278.8</v>
+        <v>36989168.8</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>5.24</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="151">
@@ -20671,10 +20671,10 @@
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>35248529.42</v>
+        <v>35692971.86</v>
       </c>
       <c r="E151" s="12" t="n">
-        <v>4.99</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="152">
@@ -20694,7 +20694,7 @@
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>34506606.04</v>
+        <v>34739447.88</v>
       </c>
       <c r="E152" s="12" t="n">
         <v>4.89</v>
@@ -20717,10 +20717,10 @@
         </is>
       </c>
       <c r="D153" s="6" t="n">
-        <v>27059871.18</v>
+        <v>27362684.15</v>
       </c>
       <c r="E153" s="12" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="154">
@@ -20740,10 +20740,10 @@
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>26992849.96</v>
+        <v>27055232.47</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="155">
@@ -20763,10 +20763,10 @@
         </is>
       </c>
       <c r="D155" s="6" t="n">
-        <v>25043370.51</v>
+        <v>25063408.81</v>
       </c>
       <c r="E155" s="12" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="156">
@@ -20786,10 +20786,10 @@
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>24404225.4</v>
+        <v>24471539.22</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="157">
@@ -20809,10 +20809,10 @@
         </is>
       </c>
       <c r="D157" s="6" t="n">
-        <v>22072470.89</v>
+        <v>22080737.92</v>
       </c>
       <c r="E157" s="12" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="158">
@@ -20832,10 +20832,10 @@
         </is>
       </c>
       <c r="D158" s="6" t="n">
-        <v>21099088.55</v>
+        <v>21114788.55</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="159">
@@ -20855,10 +20855,10 @@
         </is>
       </c>
       <c r="D159" s="6" t="n">
-        <v>20388773.72</v>
+        <v>20411805.62</v>
       </c>
       <c r="E159" s="12" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="160">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="D160" s="6" t="n">
-        <v>17360485.06</v>
+        <v>17489725.09</v>
       </c>
       <c r="E160" s="12" t="n">
         <v>2.46</v>
@@ -20901,10 +20901,10 @@
         </is>
       </c>
       <c r="D161" s="6" t="n">
-        <v>16266163.94</v>
+        <v>16275963.94</v>
       </c>
       <c r="E161" s="12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="162">
@@ -20924,7 +20924,7 @@
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>15610414.24</v>
+        <v>15665414.24</v>
       </c>
       <c r="E162" s="12" t="n">
         <v>2.21</v>
@@ -20947,10 +20947,10 @@
         </is>
       </c>
       <c r="D163" s="6" t="n">
-        <v>13132963.75</v>
+        <v>13153963.75</v>
       </c>
       <c r="E163" s="12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="164">
@@ -20961,19 +20961,19 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="D164" s="6" t="n">
-        <v>9902926.949999999</v>
+        <v>9904362.09</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="165">
@@ -20984,19 +20984,19 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="D165" s="6" t="n">
-        <v>9899362.09</v>
+        <v>9902927.949999999</v>
       </c>
       <c r="E165" s="12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="166">
@@ -21016,10 +21016,10 @@
         </is>
       </c>
       <c r="D166" s="6" t="n">
-        <v>9730791.75</v>
+        <v>9749891.75</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="167">
@@ -21039,10 +21039,10 @@
         </is>
       </c>
       <c r="D167" s="6" t="n">
-        <v>7822737.14</v>
+        <v>7959537.14</v>
       </c>
       <c r="E167" s="12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="168">
@@ -21062,7 +21062,7 @@
         </is>
       </c>
       <c r="D168" s="6" t="n">
-        <v>7794376.85</v>
+        <v>7824376.85</v>
       </c>
       <c r="E168" s="12" t="n">
         <v>1.1</v>
@@ -21085,7 +21085,7 @@
         </is>
       </c>
       <c r="D169" s="6" t="n">
-        <v>6495263.68</v>
+        <v>6563010.26</v>
       </c>
       <c r="E169" s="12" t="n">
         <v>0.92</v>
@@ -21134,7 +21134,7 @@
         <v>4059112.44</v>
       </c>
       <c r="E171" s="12" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="172">
@@ -21157,7 +21157,7 @@
         <v>3929754.61</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="173">
@@ -22451,21 +22451,21 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: a serie de fornecedores cobre 69.5% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
+          <t>Nota 1: a serie de fornecedores cobre 69.7% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
         </is>
       </c>
     </row>
@@ -22572,25 +22572,25 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>385111893.35</v>
+        <v>388445912.44</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>38680786.06</v>
+        <v>38896902.72</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>20334031.37</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>6068158.32</v>
+        <v>6082558.32</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>44748944.38</v>
+        <v>44979461.04</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>18.13</v>
+        <v>18.1</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>405445924.72</v>
+        <v>408779943.81</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>15.76</v>
@@ -22603,28 +22603,28 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>529989370.41</v>
+        <v>532795363.15</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>34294678.89</v>
+        <v>34419100.39</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>7837843.22</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>9195409.91</v>
+        <v>9214674.949999999</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>43490088.8</v>
+        <v>43633775.34</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>17.62</v>
+        <v>17.56</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>537827213.63</v>
+        <v>540633206.37</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>20.9</v>
+        <v>20.84</v>
       </c>
     </row>
     <row r="7">
@@ -22634,10 +22634,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>262869912.82</v>
+        <v>266336338.73</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>28293999.49</v>
+        <v>28371248.06</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>328650</v>
@@ -22646,16 +22646,16 @@
         <v>227830.33</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>28521829.82</v>
+        <v>28599078.39</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>11.56</v>
+        <v>11.51</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>263198562.82</v>
+        <v>266664988.73</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>10.23</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="8">
@@ -22665,10 +22665,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>147339579.03</v>
+        <v>148591951.68</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>5589853.95</v>
+        <v>5592253.95</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>10528907.87</v>
@@ -22677,16 +22677,16 @@
         <v>16201598.24</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>21791452.19</v>
+        <v>21793852.19</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>157868486.9</v>
+        <v>159120859.55</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="9">
@@ -22696,10 +22696,10 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>235628026.44</v>
+        <v>239309878.39</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>19049261.29</v>
+        <v>19685470.77</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>1061795.06</v>
@@ -22708,16 +22708,16 @@
         <v>310317.66</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>19359578.95</v>
+        <v>19995788.43</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>7.85</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>236689821.5</v>
+        <v>240371673.45</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="10">
@@ -22727,28 +22727,28 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>118199276.79</v>
+        <v>118513944.53</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>9188407.710000001</v>
+        <v>9211407.710000001</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>13436262.57</v>
+        <v>13493262.57</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>9563476.6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>18751884.31</v>
+        <v>18774884.31</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>7.6</v>
+        <v>7.56</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>131635539.36</v>
+        <v>132007207.1</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.12</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="11">
@@ -22758,10 +22758,10 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>226099283.08</v>
+        <v>228333658.65</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>16509416.28</v>
+        <v>16858427.27</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>1405640</v>
@@ -22770,16 +22770,16 @@
         <v>758113.3</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>17267529.58</v>
+        <v>17616540.57</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>7</v>
+        <v>7.09</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>227504923.08</v>
+        <v>229739298.65</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>8.84</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -22789,10 +22789,10 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>159521447.71</v>
+        <v>161115293.71</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>7070439.54</v>
+        <v>7098827.73</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>2161173.45</v>
@@ -22801,16 +22801,16 @@
         <v>2248827.43</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>9319266.970000001</v>
+        <v>9347655.16</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>161682621.16</v>
+        <v>163276467.16</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>6.28</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="13">
@@ -22820,28 +22820,28 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>66380931.39</v>
+        <v>66730216.97</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>3754114.24</v>
+        <v>3779114.24</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>12290674.22</v>
+        <v>12310674.22</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>5493512.35</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>9247626.59</v>
+        <v>9272626.59</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>78671605.61</v>
+        <v>79040891.19</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="14">
@@ -22851,7 +22851,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>54504312.9</v>
+        <v>54632858.36</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>2458966.12</v>
@@ -22866,13 +22866,13 @@
         <v>6134168.73</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>55256765.5</v>
+        <v>55385310.96</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="15">
@@ -22882,28 +22882,28 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>83705434.05</v>
+        <v>84329192.36</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>4130383.99</v>
+        <v>4200899.32</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>53190</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1023161.61</v>
+        <v>1029012.7</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>5153545.600000001</v>
+        <v>5229912.02</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>83758624.05</v>
+        <v>84382382.36</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="16">
@@ -22913,7 +22913,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>27586692.78</v>
+        <v>27625286.95</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>2990569.31</v>
@@ -22928,10 +22928,10 @@
         <v>4593036.26</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>28113827.65</v>
+        <v>28152421.82</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>1.09</v>
@@ -22944,10 +22944,10 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>38116666.43</v>
+        <v>38206539.17</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>2785733.78</v>
+        <v>2793733.78</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>214985.86</v>
@@ -22956,16 +22956,16 @@
         <v>665907.63</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>3451641.41</v>
+        <v>3459641.41</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>38331652.29</v>
+        <v>38421525.03</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="18">
@@ -22975,7 +22975,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>14104831.4</v>
+        <v>14190081.4</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>663200</v>
@@ -22993,10 +22993,10 @@
         <v>1.09</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>15070247.9</v>
+        <v>15155497.9</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="19">
@@ -23006,10 +23006,10 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>27369612.79</v>
+        <v>27639518.39</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>1795116.62</v>
+        <v>1824937.17</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>25327.5</v>
@@ -23018,16 +23018,16 @@
         <v>286176.1</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2081292.72</v>
+        <v>2111113.27</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>27394940.29</v>
+        <v>27664845.89</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="20">
@@ -23037,7 +23037,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>20364103.46</v>
+        <v>20445094.66</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>1013132.07</v>
@@ -23055,10 +23055,10 @@
         <v>0.63</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>20491623.46</v>
+        <v>20572614.66</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="21">
@@ -23068,10 +23068,10 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>11980203.23</v>
+        <v>12009433.23</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>1235627.11</v>
+        <v>1236127.11</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>113916.98</v>
@@ -23080,13 +23080,13 @@
         <v>202564.49</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1438191.6</v>
+        <v>1438691.6</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>0.58</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>12094120.21</v>
+        <v>12123350.21</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0.47</v>
@@ -23099,10 +23099,10 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>10763047.7</v>
+        <v>10786154.3</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1162211.39</v>
+        <v>1163711.39</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>206000</v>
@@ -23111,78 +23111,78 @@
         <v>120500</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1282711.39</v>
+        <v>1284211.39</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0.52</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>10969047.7</v>
+        <v>10992154.3</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Produção de jingles, vinhetas e slogans</t>
+          <t>Publicidade por carros de som</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>13888201.41</v>
+        <v>14820956.02</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>954256.42</v>
+        <v>863387.63</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>56000</v>
+        <v>933850</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>18500</v>
+        <v>110000</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>972756.42</v>
+        <v>973387.63</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>0.39</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>13944201.41</v>
+        <v>15754806.02</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Publicidade por carros de som</t>
+          <t>Produção de jingles, vinhetas e slogans</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>14693666.03</v>
+        <v>13920301.41</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>858287.63</v>
+        <v>954256.42</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>933850</v>
+        <v>56000</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>110000</v>
+        <v>18500</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>968287.63</v>
+        <v>972756.42</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>0.39</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>15627516.03</v>
+        <v>13976301.41</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="25">
@@ -23192,10 +23192,10 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>6127990.28</v>
+        <v>6162857.09</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>729492.3100000001</v>
+        <v>777512.3099999999</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>0</v>
@@ -23204,13 +23204,13 @@
         <v>420</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>729912.3100000001</v>
+        <v>777932.3099999999</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>6127990.28</v>
+        <v>6162857.09</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0.24</v>
@@ -23223,7 +23223,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>7386946.52</v>
+        <v>7443749.61</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>600987.22</v>
@@ -23238,10 +23238,10 @@
         <v>729489.1699999999</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>7409020.84</v>
+        <v>7465823.930000001</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0.29</v>
@@ -23254,7 +23254,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>14789875.09</v>
+        <v>14806633.51</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>704588.0600000001</v>
@@ -23269,13 +23269,13 @@
         <v>704588.0600000001</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>14797979.64</v>
+        <v>14814738.06</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="28">
@@ -23285,7 +23285,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>9099711.26</v>
+        <v>9122954.050000001</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>336862.09</v>
@@ -23297,13 +23297,13 @@
         <v>151786.7</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>488648.7899999999</v>
+        <v>488648.79</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>9099711.26</v>
+        <v>9122954.050000001</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0.35</v>
@@ -23316,7 +23316,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>2634914.93</v>
+        <v>2666919.12</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>267059.74</v>
@@ -23334,7 +23334,7 @@
         <v>0.15</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>2644041.73</v>
+        <v>2676045.92</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0.1</v>
@@ -23347,7 +23347,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>3372643.86</v>
+        <v>3373103.86</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>293667.18</v>
@@ -23365,7 +23365,7 @@
         <v>0.12</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>3372643.86</v>
+        <v>3373103.86</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0.13</v>
@@ -23378,7 +23378,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>2367945.54</v>
+        <v>2379945.54</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>186090.2</v>
@@ -23393,10 +23393,10 @@
         <v>186090.2</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>2367945.54</v>
+        <v>2379945.54</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0.09</v>
@@ -23409,7 +23409,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>898514.8</v>
+        <v>899739.25</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>85143.32000000001</v>
@@ -23427,7 +23427,7 @@
         <v>0.04</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>917131.3</v>
+        <v>918355.75</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0.04</v>
@@ -23440,7 +23440,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>1440289.23</v>
+        <v>1440911.61</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>58664.51</v>
@@ -23458,7 +23458,7 @@
         <v>0.04</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1440289.23</v>
+        <v>1440911.61</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0.06</v>
@@ -23502,13 +23502,13 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>83701.59</v>
+        <v>83753.74000000001</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>1130.2</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>51744.89</v>
+        <v>51744.89000000001</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>40426.19</v>
@@ -23520,7 +23520,7 @@
         <v>0.02</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>135446.48</v>
+        <v>135498.63</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0.01</v>
@@ -23533,25 +23533,25 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>436798.76</v>
+        <v>439627.23</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>26342.36</v>
+        <v>26628.12</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>99791.58</v>
+        <v>99823.97</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>13788.9</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>40131.26</v>
+        <v>40417.02</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>536590.34</v>
+        <v>539451.2</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0.02</v>
@@ -23564,7 +23564,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>430493.91</v>
+        <v>431882.91</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>20610.5</v>
@@ -23582,7 +23582,7 @@
         <v>0.01</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>432042.58</v>
+        <v>433431.58</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0.02</v>
@@ -23601,7 +23601,7 @@
         <v>2750.04</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>33020.01</v>
+        <v>33020.00999999999</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>25183.19</v>
@@ -23626,7 +23626,7 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>38992.87</v>
+        <v>39497.46</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>3261.35</v>
@@ -23644,7 +23644,7 @@
         <v>0.01</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>39092.11</v>
+        <v>39596.7</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>23996.69</v>
+        <v>24180.37</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>389.88</v>
@@ -23706,7 +23706,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>23996.69</v>
+        <v>24180.37</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
@@ -23719,7 +23719,7 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>9865.049999999999</v>
+        <v>9868.549999999999</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>2.5</v>
@@ -23737,7 +23737,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>9865.049999999999</v>
+        <v>9868.549999999999</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
@@ -23777,14 +23777,14 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
         </is>
       </c>
     </row>
@@ -23823,7 +23823,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -23937,34 +23937,34 @@
         <v>5281805806.47</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1409339581.28</v>
+        <v>1412353509.95</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>19.33</v>
+        <v>19.34</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1024361550.1</v>
+        <v>1024611550.1</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>18.91</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>151137505.82</v>
+        <v>150909665.82</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>23.93</v>
+        <v>23.9</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>21948898.27</v>
+        <v>22078270.52</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>139408629.58</v>
+        <v>142029564.22</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>1071026538.15</v>
+        <v>1081239815</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>83.41</v>
+        <v>83.23</v>
       </c>
     </row>
     <row r="6">
@@ -23983,7 +23983,7 @@
         <v>788542541.16</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1057144307.24</v>
+        <v>1058987664.58</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>14.5</v>
@@ -23992,7 +23992,7 @@
         <v>920820959.12</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>17</v>
+        <v>16.99</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>6176134.65</v>
@@ -24001,16 +24001,16 @@
         <v>0.98</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>12370225.24</v>
+        <v>12280078.79</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>85135052.48</v>
+        <v>85214022.03</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>697883667.52</v>
+        <v>700321839.36</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>87.69</v>
+        <v>87.54000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -24029,34 +24029,34 @@
         <v>1819943318.34</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>668946919.73</v>
+        <v>669290913.9400001</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>9.17</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>536651994.33</v>
+        <v>536659271.9</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>9.91</v>
+        <v>9.9</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>75609738.73999999</v>
+        <v>75709738.73999999</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>11.97</v>
+        <v>11.99</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>8122431.99</v>
+        <v>8146956.06</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>29642872.29</v>
+        <v>29670677.53</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>474094188.43</v>
+        <v>475094185.84</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>91.53</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="8">
@@ -24075,10 +24075,10 @@
         <v>2577905190.84</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>655287244.45</v>
+        <v>655828920.45</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>8.99</v>
+        <v>8.98</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>448666803.71</v>
@@ -24093,16 +24093,16 @@
         <v>5.48</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>18922595.77</v>
+        <v>18938430.73</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>84575958.48999999</v>
+        <v>85021165.52</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>512484289.44</v>
+        <v>513472976.49</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>73.75</v>
+        <v>73.69</v>
       </c>
     </row>
     <row r="9">
@@ -24121,34 +24121,34 @@
         <v>2779509683.8</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>605065027.8099999</v>
+        <v>606328460.38</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>370432010.25</v>
+        <v>371047010.25</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>6.84</v>
+        <v>6.85</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>126619464.39</v>
+        <v>126709839.39</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>20.05</v>
+        <v>20.07</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>11884790.46</v>
+        <v>11955348.21</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>63493468.32</v>
+        <v>63735678.14</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>425494401.76</v>
+        <v>426512725.79</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>82.15000000000001</v>
+        <v>82.09</v>
       </c>
     </row>
     <row r="10">
@@ -24167,10 +24167,10 @@
         <v>1297502449.57</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>576656855.17</v>
+        <v>576657426.78</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7.91</v>
+        <v>7.9</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>446516289.17</v>
@@ -24179,19 +24179,19 @@
         <v>8.24</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>74187903.25</v>
+        <v>74209455</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>11.75</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>8062753.11</v>
+        <v>8066939.64</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>30674373.88</v>
+        <v>30539207.21</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>362213876.57</v>
+        <v>363056568.82</v>
       </c>
       <c r="N10" s="6" t="n">
         <v>90.3</v>
@@ -24213,10 +24213,10 @@
         <v>3431895006.71</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>537203229.91</v>
+        <v>537330031.36</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>7.37</v>
+        <v>7.36</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>407807248.96</v>
@@ -24225,22 +24225,22 @@
         <v>7.53</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>17650611.52</v>
+        <v>17652075.52</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>2.8</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>15048690.04</v>
+        <v>15049687.49</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>67883952.39</v>
+        <v>68002242.39</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>351618264.86</v>
+        <v>358144512.44</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>79.2</v>
+        <v>79.18000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -24259,34 +24259,34 @@
         <v>1812875005.9</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>295865533.79</v>
+        <v>296299367.62</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>4.06</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>238185682.3</v>
+        <v>238186413.63</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>4.4</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5678988.810000001</v>
+        <v>5680836.81</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>0.9</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>10145870.45</v>
+        <v>10301475.45</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>31800231.76</v>
+        <v>32015291.76</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>193710408.87</v>
+        <v>194039246.59</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>82.42</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="13">
@@ -24305,34 +24305,34 @@
         <v>1457794419.27</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>230641485.51</v>
+        <v>230837653.51</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>3.16</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>166995631.66</v>
+        <v>167145631.66</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>3.08</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>46882987.35</v>
+        <v>46890710.35</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>7.42</v>
+        <v>7.43</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>2918310.78</v>
+        <v>2944615.78</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>9986352.189999999</v>
+        <v>9996352.189999999</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>152821474.02</v>
+        <v>152983175.21</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>92.73</v>
+        <v>92.72</v>
       </c>
     </row>
     <row r="14">
@@ -24351,13 +24351,13 @@
         <v>941728196.61</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>222436516.05</v>
+        <v>222531253.45</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>3.05</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>148468909.38</v>
+        <v>148497258.38</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>2.74</v>
@@ -24369,16 +24369,16 @@
         <v>1.06</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>10884683.79</v>
+        <v>10905584.29</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>36412793.06</v>
+        <v>36440614.96</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>172315950.61</v>
+        <v>172613146.16</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>69.76000000000001</v>
+        <v>69.75</v>
       </c>
     </row>
     <row r="15">
@@ -24397,34 +24397,34 @@
         <v>2591694177.84</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>210403265</v>
+        <v>210668930.63</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>2.89</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>150317927.09</v>
+        <v>150342927.09</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>2.77</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>4457357.34</v>
+        <v>4459707.34</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>0.71</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>11733934.69</v>
+        <v>11739127.87</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31737764.53</v>
+        <v>31959608.98</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>144506391.86</v>
+        <v>144991030.17</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>73.56</v>
+        <v>73.48</v>
       </c>
     </row>
     <row r="16">
@@ -24443,13 +24443,13 @@
         <v>1884208841.62</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>144321776.59</v>
+        <v>144355225.43</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>1.98</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>34396229.06</v>
+        <v>34400279.06</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0.63</v>
@@ -24461,16 +24461,16 @@
         <v>7.04</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>7330389.71</v>
+        <v>7330390.21</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>27108631.98</v>
+        <v>27137480.32</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>90524955.17</v>
+        <v>90574628.17</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>54.63</v>
+        <v>54.62</v>
       </c>
     </row>
     <row r="17">
@@ -24489,13 +24489,13 @@
         <v>139488473.87</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>135467418.7</v>
+        <v>135574307.88</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>1.86</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>123997665.62</v>
+        <v>124016282.12</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>2.29</v>
@@ -24507,16 +24507,16 @@
         <v>0.31</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>821011.21</v>
+        <v>830911.21</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>4174006.34</v>
+        <v>4176262.37</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>89940476.53</v>
+        <v>89965893.28</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>92.98</v>
+        <v>92.92</v>
       </c>
     </row>
     <row r="18">
@@ -24535,7 +24535,7 @@
         <v>1072776812.99</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>99461887.94</v>
+        <v>99495630.70999999</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>1.36</v>
@@ -24547,7 +24547,7 @@
         <v>1.21</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>13872331.38</v>
+        <v>13874711.38</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>2.2</v>
@@ -24556,13 +24556,13 @@
         <v>4906934.439999999</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>12838224.3</v>
+        <v>12858174.3</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>61088163.04</v>
+        <v>61163750.13</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>79.75</v>
+        <v>79.72</v>
       </c>
     </row>
     <row r="19">
@@ -24581,13 +24581,13 @@
         <v>577531754.64</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>97456207.38</v>
+        <v>97563707.88</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>1.34</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>67578077.34999999</v>
+        <v>67589577.34999999</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>1.25</v>
@@ -24599,16 +24599,16 @@
         <v>2.24</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>3368096.32</v>
+        <v>3464096.82</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>9223157.119999999</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>60969268.11</v>
+        <v>61002363.11</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>83.86</v>
+        <v>83.78</v>
       </c>
     </row>
     <row r="20">
@@ -24627,7 +24627,7 @@
         <v>280452197.14</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>92074434.59999999</v>
+        <v>92082831.40000001</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>1.26</v>
@@ -24648,13 +24648,13 @@
         <v>1869153.42</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>3841731.77</v>
+        <v>3850128.57</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>53094938.65</v>
+        <v>53163810.58</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>92.84999999999999</v>
+        <v>92.84</v>
       </c>
     </row>
     <row r="21">
@@ -24673,7 +24673,7 @@
         <v>81485614.53</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>73470992.78</v>
+        <v>73514593.78</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>1.01</v>
@@ -24694,13 +24694,13 @@
         <v>1309270.67</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4039422.41</v>
+        <v>4081773.41</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>49463845.77</v>
+        <v>49464097.13</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>88.26000000000001</v>
+        <v>88.20999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -24719,7 +24719,7 @@
         <v>330099422.77</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>60307921.48</v>
+        <v>60383921.48</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>0.83</v>
@@ -24740,13 +24740,13 @@
         <v>3471243.36</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>11112575.11</v>
+        <v>11188575.11</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>43954410.06</v>
+        <v>44093323.13</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>71.8</v>
+        <v>71.70999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -24789,7 +24789,7 @@
         <v>1056669.75</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>11366169.54</v>
+        <v>11389767.54</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>93.04000000000001</v>
@@ -24814,7 +24814,7 @@
         <v>33939373.27</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>29553402.63</v>
@@ -24857,7 +24857,7 @@
         <v>286783798.5</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>12107936.16</v>
+        <v>12107937.16</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>0.17</v>
@@ -24875,13 +24875,13 @@
         <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>2046899.83</v>
+        <v>2046900.83</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>7488251.99</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>7618835.57</v>
+        <v>7714214.57</v>
       </c>
       <c r="N25" s="6" t="n">
         <v>18.46</v>
@@ -24903,7 +24903,7 @@
         <v>243522021.57</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>10135622.14</v>
+        <v>10199298.73</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>0.14</v>
@@ -24921,16 +24921,16 @@
         <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>1848905.88</v>
+        <v>1858924.47</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>5503641.7</v>
+        <v>5557299.7</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>8396083.199999999</v>
+        <v>8521015.1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>23.02</v>
+        <v>22.87</v>
       </c>
     </row>
     <row r="27">
@@ -24949,7 +24949,7 @@
         <v>184054953.85</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>9128325.68</v>
+        <v>9660363.26</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>0.13</v>
@@ -24967,16 +24967,16 @@
         <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>325852.38</v>
+        <v>372691.54</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>1389652.4</v>
+        <v>1751525.3</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>5481518.37</v>
+        <v>6818600.63</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>35.87</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="28">
@@ -24995,13 +24995,13 @@
         <v>652170016.89</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>6246280.37</v>
+        <v>6265644.37</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>2903963.13</v>
+        <v>2913963.13</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0.05</v>
@@ -25013,16 +25013,16 @@
         <v>0.01</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>1063090.03</v>
+        <v>1066913.03</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>1922999.3</v>
+        <v>1928540.3</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>3471853.99</v>
+        <v>3491296.03</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>47.01</v>
+        <v>47.03</v>
       </c>
     </row>
     <row r="29">
@@ -25065,7 +25065,7 @@
         <v>2063883.58</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>3346427.08</v>
+        <v>3344627.08</v>
       </c>
       <c r="N29" s="6" t="n">
         <v>0.11</v>
@@ -25087,7 +25087,7 @@
         <v>26021399.15</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>3556151.12</v>
+        <v>3558651.12</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>0.05</v>
@@ -25108,13 +25108,13 @@
         <v>24107.29</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>126425.33</v>
+        <v>128925.33</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>3033459.84</v>
+        <v>3033461.54</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>89.73</v>
+        <v>89.67</v>
       </c>
     </row>
     <row r="31">
@@ -25133,13 +25133,13 @@
         <v>16313701.99</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>1915902.59</v>
+        <v>1928912.59</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>0.03</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>1300041.22</v>
+        <v>1309641.22</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>0.02</v>
@@ -25154,13 +25154,13 @@
         <v>8271.67</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>248034.65</v>
+        <v>248774.65</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>1095692.48</v>
+        <v>1115934.21</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>67.86</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -25304,14 +25304,14 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
         </is>
       </c>
     </row>
@@ -25350,7 +25350,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="35" customWidth="1" min="8" max="8"/>
@@ -25360,7 +25360,7 @@
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2690130.31</v>
+        <v>2815477.53</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>0.04</v>
@@ -25598,10 +25598,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>276467.93</v>
+        <v>306214.95</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>2393662.38</v>
+        <v>2489262.58</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>20000</v>
@@ -25613,10 +25613,10 @@
         <v>0</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>1286828.37</v>
+        <v>1288625.19</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1286828.37</v>
+        <v>1288625.19</v>
       </c>
     </row>
     <row r="8">
@@ -26496,7 +26496,7 @@
         <v>1110756.58</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>626408.9399999999</v>
+        <v>626408.9400000001</v>
       </c>
     </row>
     <row r="24">
@@ -26603,10 +26603,10 @@
         <v>12750</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>804507.87</v>
+        <v>899886.87</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>502907.87</v>
+        <v>622886.87</v>
       </c>
     </row>
     <row r="26">
@@ -26658,10 +26658,10 @@
         <v>7324.33</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1085204.2</v>
+        <v>1084891.05</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1085204.2</v>
+        <v>1084891.05</v>
       </c>
     </row>
     <row r="27">
@@ -27318,10 +27318,10 @@
         <v>45605</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>702398.92</v>
+        <v>700598.92</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>568397.59</v>
+        <v>568667.59</v>
       </c>
     </row>
     <row r="39">
@@ -28207,35 +28207,35 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-13 15:05:10.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: sao 2200 candidaturas com receita declarada e sem um real dos dois fundos publicos. que somam R$ 224.320.213,64 de receita.</t>
+          <t>Nota 1: sao 2217 candidaturas com receita declarada e sem um real dos dois fundos publicos. que somam R$ 224.545.761,35 de receita.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Nota 2: outras 4155 candidaturas NAO declararam receita alguma, das quais 960 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
+          <t>Nota 2: outras 4125 candidaturas NAO declararam receita alguma, das quais 960 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Nota 3: destas, 1253 nao receberam recurso partidario de especie alguma, nem mesmo fora dos dois fundos.</t>
+          <t>Nota 3: destas, 1254 nao receberam recurso partidario de especie alguma, nem mesmo fora dos dois fundos.</t>
         </is>
       </c>
     </row>
@@ -28383,16 +28383,16 @@
         <v>7.71</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>941059970.52</v>
+        <v>941352416.62</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>20.38</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>27.59</v>
+        <v>27.6</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>22.58</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="6">
@@ -28426,16 +28426,16 @@
         <v>11.18</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>539785425.37</v>
+        <v>540061272.24</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>25.15</v>
+        <v>25.17</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>32.95</v>
+        <v>32.97</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>24.9</v>
+        <v>24.91</v>
       </c>
     </row>
     <row r="7">
@@ -28469,16 +28469,16 @@
         <v>15.98</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>501598033.74</v>
+        <v>501738323.89</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>29.12</v>
+        <v>29.13</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>39.01</v>
+        <v>39.02</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>34.25</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="8">
@@ -28512,13 +28512,13 @@
         <v>10.81</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>348267772.86</v>
+        <v>348382819.68</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>23.39</v>
+        <v>23.4</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>30.76</v>
+        <v>30.77</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>26.94</v>
@@ -28555,16 +28555,16 @@
         <v>12.66</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>346616717.24</v>
+        <v>347809594.83</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>40.26</v>
+        <v>40.4</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>31.75</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="10">
@@ -28598,13 +28598,13 @@
         <v>12.36</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>319738833.72</v>
+        <v>319875531.57</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>28.46</v>
+        <v>28.48</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>37.5</v>
+        <v>37.52</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>31.29</v>
@@ -28641,16 +28641,16 @@
         <v>13.3</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>260541558.01</v>
+        <v>260673741.06</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>27.19</v>
+        <v>27.2</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>36.05</v>
+        <v>36.07</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>30.53</v>
+        <v>30.54</v>
       </c>
     </row>
     <row r="12">
@@ -28684,13 +28684,13 @@
         <v>10.2</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>248624871.27</v>
+        <v>248641151.84</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>26.73</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>35.51</v>
+        <v>35.52</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>28.59</v>
@@ -28727,13 +28727,13 @@
         <v>11.82</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>191668164.35</v>
+        <v>191797404.38</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>21.89</v>
+        <v>21.9</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>30.58</v>
+        <v>30.6</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>25.82</v>
@@ -28770,13 +28770,13 @@
         <v>12.22</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>216368096.53</v>
+        <v>216778997.14</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>26.03</v>
+        <v>26.08</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>37.79</v>
+        <v>37.86</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>28.57</v>
@@ -28813,16 +28813,16 @@
         <v>11.93</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>223689101.98</v>
+        <v>223955484.48</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>31.84</v>
+        <v>31.88</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>43.12</v>
+        <v>43.17</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>36.49</v>
+        <v>36.54</v>
       </c>
     </row>
     <row r="16">
@@ -28856,13 +28856,13 @@
         <v>17.83</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>232655729.4</v>
+        <v>233323038.34</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>31.04</v>
+        <v>31.13</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>45.79</v>
+        <v>45.92</v>
       </c>
       <c r="M16" s="6" t="n">
         <v>34.39</v>
@@ -28899,13 +28899,13 @@
         <v>13.85</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>149704962.6</v>
+        <v>149734962.6</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>35.79</v>
+        <v>35.8</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>46.09</v>
+        <v>46.1</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>40.78</v>
@@ -28942,16 +28942,16 @@
         <v>20.16</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>176399645.6</v>
+        <v>176762535.6</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>42.5</v>
+        <v>42.59</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>58.99</v>
+        <v>59.11</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>48.57</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="19">
@@ -28985,16 +28985,16 @@
         <v>17.38</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>189498535.69</v>
+        <v>189645533.43</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>43.45</v>
+        <v>43.49</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>67.63</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>58.1</v>
+        <v>58.13</v>
       </c>
     </row>
     <row r="20">
@@ -29028,13 +29028,13 @@
         <v>14.84</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>145328090.58</v>
+        <v>145383532.58</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>42.84</v>
+        <v>42.85</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>53.65</v>
+        <v>53.67</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>44.08</v>
@@ -29071,13 +29071,13 @@
         <v>12.85</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>135306463.94</v>
+        <v>135383050.09</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>39.06</v>
+        <v>39.09</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>50.85</v>
+        <v>50.88</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>45.56</v>
@@ -29114,7 +29114,7 @@
         <v>17.24</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>162804286.45</v>
+        <v>162812264.63</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>41.21</v>
@@ -29157,13 +29157,13 @@
         <v>12.24</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>116578380.72</v>
+        <v>116715353.72</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>36.19</v>
+        <v>36.23</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>47.73</v>
+        <v>47.79</v>
       </c>
       <c r="M23" s="6" t="n">
         <v>42.42</v>
@@ -29200,13 +29200,13 @@
         <v>30.18</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>206745533</v>
+        <v>206867725.89</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>68.69</v>
+        <v>68.73</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>91.75</v>
+        <v>91.81</v>
       </c>
       <c r="M24" s="6" t="n">
         <v>73.26000000000001</v>
@@ -29243,13 +29243,13 @@
         <v>20.99</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>118148055.06</v>
+        <v>118181676.81</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>40.1</v>
+        <v>40.11</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>58.34</v>
+        <v>58.36</v>
       </c>
       <c r="M25" s="6" t="n">
         <v>47.37</v>
@@ -29286,13 +29286,13 @@
         <v>23.62</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>123147279.67</v>
+        <v>123176777.67</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>53.37</v>
+        <v>53.39</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>70.76000000000001</v>
+        <v>70.78</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>63.36</v>
@@ -29329,13 +29329,13 @@
         <v>34.52</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>147117921.93</v>
+        <v>147135522.01</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>83.72</v>
+        <v>83.73</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>115.96</v>
+        <v>115.98</v>
       </c>
       <c r="M27" s="6" t="n">
         <v>90.37</v>
@@ -29372,13 +29372,13 @@
         <v>31.11</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>121101896.75</v>
+        <v>121115288.53</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>75.88</v>
+        <v>75.89</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>102.39</v>
+        <v>102.4</v>
       </c>
       <c r="M28" s="6" t="n">
         <v>84.14</v>
@@ -29415,13 +29415,13 @@
         <v>65.08</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>134802502.61</v>
+        <v>134862023.11</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>151.84</v>
+        <v>151.91</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>219.32</v>
+        <v>219.42</v>
       </c>
       <c r="M29" s="6" t="n">
         <v>202.55</v>
@@ -29501,7 +29501,7 @@
         <v>102.85</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>105927367.84</v>
+        <v>105927597.84</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>139.19</v>
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>773225038.47</v>
+        <v>777520950.29</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -29605,16 +29605,16 @@
         <v>13.34</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>7292546453.309999</v>
+        <v>7301710788.279999</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>34.04</v>
+        <v>34.09</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>46.2</v>
+        <v>46.26</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>38.32</v>
+        <v>38.33</v>
       </c>
     </row>
     <row r="34">
@@ -29627,7 +29627,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-13.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-14 09:12:37</t>
+          <t>2026-10-14 16:19:51</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
         </is>
       </c>
     </row>
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
         </is>
       </c>
     </row>
@@ -24271,7 +24271,7 @@
         <v>4.4</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5680836.81</v>
+        <v>5680836.810000001</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>0.9</v>
@@ -25304,7 +25304,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 09:12:37.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -646,16 +646,16 @@
         <v>1.03</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>47867732.18</v>
+        <v>47902742.53</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>0.66</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>32379885.41</v>
+        <v>33142536.24</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="8">
@@ -677,16 +677,16 @@
         <v>36.5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1791649865.2</v>
+        <v>1795036958.61</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>24.54</v>
+        <v>24.56</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>1180242374.12</v>
+        <v>1185992166.35</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>23.15</v>
+        <v>23.17</v>
       </c>
     </row>
     <row r="9">
@@ -708,16 +708,16 @@
         <v>26.47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3403116791.96</v>
+        <v>3405144473.64</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>46.61</v>
+        <v>46.59</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2291356663.53</v>
+        <v>2300421308.43</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>44.95</v>
+        <v>44.94</v>
       </c>
     </row>
     <row r="10">
@@ -739,16 +739,16 @@
         <v>5.34</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>762568509.14</v>
+        <v>764441395.64</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>10.44</v>
+        <v>10.46</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>617772495.04</v>
+        <v>622010881.96</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>12.12</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="11">
@@ -773,13 +773,13 @@
         <v>777520950.2900001</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>10.65</v>
+        <v>10.64</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>587347887.3099999</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>11.52</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="12">
@@ -801,16 +801,16 @@
         <v>6.32</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>518986939.51</v>
+        <v>519238923.51</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>388998567.06</v>
+        <v>389674253.59</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>7.63</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="13">
@@ -894,13 +894,13 @@
         <v>100</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7301710788.28</v>
+        <v>7309285444.219999</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>5098097872.47</v>
+        <v>5118589033.88</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>100</v>
@@ -909,14 +909,14 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-15.</t>
         </is>
       </c>
     </row>
@@ -1025,14 +1025,14 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-15.</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>177022</v>
+        <v>177837</v>
       </c>
     </row>
     <row r="24">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6577836013.57</v>
+        <v>6584449799.51</v>
       </c>
     </row>
     <row r="26">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{"REC_FEFC": 4845870044.69, "REC_FINANCIAMENTO_COLETIVO": 19062483.46, "REC_FUNDO_PARTIDARIO": 554667577.4, "REC_ORIGEM_NAO_IDENTIFICADA": 1142082.6, "REC_OUTROS_CANDIDATOS": 121375656.27, "REC_PARTIDO_OUTROS_RECURSOS": 203436494.15, "REC_PESSOAS_FISICAS": 668235463.88, "REC_PROPRIOS": 164046211.12, "REC_SEM_ORIGEM": 0.0}</t>
+          <t>{"REC_FEFC": 4846572870.23, "REC_FINANCIAMENTO_COLETIVO": 19072031.46, "REC_FUNDO_PARTIDARIO": 555209101.2, "REC_ORIGEM_NAO_IDENTIFICADA": 1143592.6, "REC_OUTROS_CANDIDATOS": 121648113.99, "REC_PARTIDO_OUTROS_RECURSOS": 203701509.93, "REC_PESSOAS_FISICAS": 671734426.98, "REC_PROPRIOS": 165368153.12, "REC_SEM_ORIGEM": 0.0}</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>79256</v>
+        <v>79584</v>
       </c>
     </row>
     <row r="30">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1011340</v>
+        <v>1021111</v>
       </c>
     </row>
     <row r="36">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>804775</v>
+        <v>812297</v>
       </c>
     </row>
     <row r="37">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4554851842.71</v>
+        <v>4575269318.18</v>
       </c>
     </row>
     <row r="38">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>742817</v>
+        <v>758145</v>
       </c>
     </row>
     <row r="39">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3237241449.26</v>
+        <v>3276466222.2</v>
       </c>
     </row>
     <row r="40">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>75888</v>
+        <v>77548</v>
       </c>
     </row>
     <row r="43">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>813631.13</v>
+        <v>832285.7</v>
       </c>
     </row>
     <row r="44">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>552703</v>
+        <v>555982</v>
       </c>
     </row>
     <row r="46">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>56595</v>
+        <v>56603</v>
       </c>
     </row>
     <row r="48">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>56445</v>
+        <v>56768</v>
       </c>
     </row>
     <row r="49">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>54</v>
+        <v>366</v>
       </c>
     </row>
     <row r="50">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="B50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>934</v>
+        <v>930</v>
       </c>
     </row>
     <row r="52">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2584556390.44</v>
+        <v>2609579188.66</v>
       </c>
     </row>
     <row r="53">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64368644.72</v>
+        <v>64593609.19</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>190585344.69</v>
+        <v>193665111.04</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4946943100.24</v>
+        <v>4952188986.11</v>
       </c>
     </row>
     <row r="57">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4873261169.22</v>
+        <v>4878479319.22</v>
       </c>
     </row>
     <row r="58">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>597489111.75</v>
+        <v>600380096.67</v>
       </c>
     </row>
     <row r="59">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>536532270.69</v>
+        <v>538642770.6900001</v>
       </c>
     </row>
     <row r="60">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-14 16:19:51</t>
+          <t>2026-10-15 09:44:30</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-723874774.71</v>
+        <v>-724835644.71</v>
       </c>
     </row>
     <row r="65">
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="L50" s="6" t="n">
-        <v>3105570</v>
+        <v>3165670</v>
       </c>
       <c r="M50" s="6" t="n">
         <v>0.04</v>
@@ -5549,22 +5549,22 @@
         </is>
       </c>
       <c r="L58" s="6" t="n">
-        <v>11286400</v>
+        <v>11522900</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="N58" s="6" t="n">
         <v>11400</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>225000</v>
+        <v>261500</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>50000</v>
+        <v>250000</v>
       </c>
       <c r="Q58" s="6" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="R58" s="6" t="n">
         <v>11000000</v>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="L101" s="6" t="n">
-        <v>652752.51</v>
+        <v>653592.36</v>
       </c>
       <c r="M101" s="6" t="n">
         <v>0.01</v>
@@ -8842,14 +8842,14 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-15.</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8895,7 @@
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
     <col width="29" customWidth="1" min="13" max="13"/>
     <col width="34" customWidth="1" min="14" max="14"/>
     <col width="48" customWidth="1" min="15" max="15"/>
@@ -9032,19 +9032,19 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>6057</v>
+        <v>6074</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>279926342.72</v>
+        <v>281516195.39</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5.49</v>
+        <v>5.5</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>272447538.12</v>
+        <v>274070810.41</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>97.33</v>
+        <v>97.36</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -9097,19 +9097,19 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>99655049.3</v>
+        <v>99805530.3</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>1.95</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>97958093.61</v>
+        <v>98296574.61</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>98.3</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
@@ -9323,12 +9323,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>09.383.641/0001-47</t>
+          <t>24.080.493/0001-85</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>F.A.R.O PROPAGANDA E PUBLICIDADE LTDA</t>
+          <t>EBANX PAGAMENTOS LTDA</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -9338,17 +9338,17 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Administração de cartões de crédito</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>SAO JOSE DOS CAMPOS</t>
+          <t>CURITIBA</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -9357,28 +9357,28 @@
         </is>
       </c>
       <c r="I10" s="5" t="n">
-        <v>3</v>
+        <v>212</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>13400000</v>
+        <v>13407413.23</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0.26</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>13250000</v>
+        <v>13027109.23</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>98.88</v>
+        <v>97.16</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>PL; PSDB</t>
+          <t>PL; UNIÃO; PT; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL); PAULO SERRA (PSDB)</t>
+          <t>TOME ABDUCH (REPUBLICANOS); ANDRÉ DO PRADO (PL)</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>24.080.493/0001-85</t>
+          <t>09.383.641/0001-47</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>EBANX PAGAMENTOS LTDA</t>
+          <t>F.A.R.O PROPAGANDA E PUBLICIDADE LTDA</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -9403,17 +9403,17 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Administração de cartões de crédito</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>CURITIBA</t>
+          <t>SAO JOSE DOS CAMPOS</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -9422,28 +9422,28 @@
         </is>
       </c>
       <c r="I11" s="5" t="n">
-        <v>212</v>
+        <v>3</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>12977413.23</v>
+        <v>13400000</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>12597109.23</v>
+        <v>13250000</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>97.06999999999999</v>
+        <v>98.88</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>PL; UNIÃO; REPUBLICANOS; MDB</t>
+          <t>PL; PSDB</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>TOME ABDUCH (REPUBLICANOS); ANDRÉ DO PRADO (PL)</t>
+          <t>FLAVIO BOLSONARO (PL); PAULO SERRA (PSDB)</t>
         </is>
       </c>
     </row>
@@ -9552,19 +9552,19 @@
         </is>
       </c>
       <c r="I13" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>9457826</v>
+        <v>9537826</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0.19</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>8931553.75</v>
+        <v>9011553.75</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>94.44</v>
+        <v>94.48</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
@@ -9620,16 +9620,16 @@
         <v>245</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>9207590.32</v>
+        <v>9216127.32</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0.18</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>8191543.36</v>
+        <v>8200937.34</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>88.97</v>
+        <v>88.98</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
@@ -9756,10 +9756,10 @@
         <v>0.14</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>3846831.65</v>
+        <v>4207291.65</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>54.99</v>
+        <v>60.14</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>6379700</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>4900000</v>
@@ -10103,12 +10103,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>07.263.666/0001-81</t>
+          <t>08.540.403/0001-35</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>BRASPOR GRAFICA E EDITORA LTDA.</t>
+          <t>GRAFICA J B LTDA</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -10118,17 +10118,17 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>OSASCO</t>
+          <t>JOAO PESSOA</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -10137,28 +10137,28 @@
         </is>
       </c>
       <c r="I22" s="5" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>5698948.42</v>
+        <v>5772141.5</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0.11</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>3530637.6</v>
+        <v>4885215</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>61.95</v>
+        <v>84.63</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>PT; PL; PODE; UNIÃO</t>
+          <t>PT; PP; PL; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL); CARLOS ZARATTINI (PT)</t>
+          <t>HUMBERTO COSTA (PT); LUCAS RIBEIRO (PP)</t>
         </is>
       </c>
     </row>
@@ -10168,12 +10168,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>08.540.403/0001-35</t>
+          <t>07.263.666/0001-81</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>GRAFICA J B LTDA</t>
+          <t>BRASPOR GRAFICA E EDITORA LTDA.</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -10183,17 +10183,17 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>JOAO PESSOA</t>
+          <t>OSASCO</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -10202,28 +10202,28 @@
         </is>
       </c>
       <c r="I23" s="5" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>5496084</v>
+        <v>5727634.42</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0.11</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4609157.5</v>
+        <v>3870095.67</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>83.86</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>PP; PL; PT; REPUBLICANOS</t>
+          <t>PT; PL; PODE; UNIÃO</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>LUCAS RIBEIRO (PP); RUY CARNEIRO (PODE)</t>
+          <t>FLAVIO BOLSONARO (PL); CARLOS ZARATTINI (PT)</t>
         </is>
       </c>
     </row>
@@ -10341,10 +10341,10 @@
         <v>0.1</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>2611986.1</v>
+        <v>3203236.1</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>51.29</v>
+        <v>62.9</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
@@ -10595,16 +10595,16 @@
         <v>224</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>4759819.81</v>
+        <v>4764273.04</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>4308250.18</v>
+        <v>4312703.41</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>90.51000000000001</v>
+        <v>90.52</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
@@ -10883,12 +10883,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>05.018.135/0001-06</t>
+          <t>57.780.367/0001-92</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>POLIS PROPAGANDA   MARKETING LTDA</t>
+          <t>AUREA TECNOLOGIA E SOLUCOES LTDA</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -10898,17 +10898,17 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Agências de publicidade</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>LAURO DE FREITAS</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -10933,12 +10933,12 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>CIRO GOMES (PSDB)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -10948,12 +10948,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>57.780.367/0001-92</t>
+          <t>05.018.135/0001-06</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>AUREA TECNOLOGIA E SOLUCOES LTDA</t>
+          <t>POLIS PROPAGANDA   MARKETING LTDA</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -10963,17 +10963,17 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Agências de publicidade</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>LAURO DE FREITAS</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -10998,12 +10998,12 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>CIRO GOMES (PSDB)</t>
         </is>
       </c>
     </row>
@@ -11047,16 +11047,16 @@
         </is>
       </c>
       <c r="I36" s="5" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>4432760.58</v>
+        <v>4451674.91</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0.09</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>4421923.35</v>
+        <v>4440837.68</v>
       </c>
       <c r="M36" s="6" t="n">
         <v>99.76000000000001</v>
@@ -11118,13 +11118,13 @@
         <v>4341431.96</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>3500031.96</v>
+        <v>3510031.96</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>80.62</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>11</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>4288264.4</v>
+        <v>4338356.4</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0.08</v>
@@ -11189,7 +11189,7 @@
         <v>2116316</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>49.35</v>
+        <v>48.78</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>04.984.400/0001-30</t>
+          <t>27.997.819/0001-21</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>CTA - CLEITON TAXI AEREO LTDA</t>
+          <t>GRID COMUNICACAO VISUAL, SINALIZACAO E EVENTOS LTDA</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -11223,17 +11223,17 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Transporte aéreo de carga</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>NOVA OLINDA DO NORTE</t>
+          <t>MOSSORO</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -11242,28 +11242,28 @@
         </is>
       </c>
       <c r="I39" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4273137.3</v>
+        <v>4288232.98</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>1129312.3</v>
+        <v>3321002.37</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>26.43</v>
+        <v>77.44</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>PSD; MDB; UNIÃO; REPUBLICANOS</t>
+          <t>PV; PP; PT; MDB</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>EDUARDO BRAGA (MDB); OMAR AZIZ (PSD)</t>
+          <t>DR. BERNARDO (PV); KALINE DE DR. BERNARDO (PV)</t>
         </is>
       </c>
     </row>
@@ -11273,12 +11273,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>27.997.819/0001-21</t>
+          <t>04.984.400/0001-30</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>GRID COMUNICACAO VISUAL, SINALIZACAO E EVENTOS LTDA</t>
+          <t>CTA - CLEITON TAXI AEREO LTDA</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -11288,17 +11288,17 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Transporte aéreo de carga</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>MOSSORO</t>
+          <t>NOVA OLINDA DO NORTE</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -11307,28 +11307,28 @@
         </is>
       </c>
       <c r="I40" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>4254762.98</v>
+        <v>4273137.3</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>3287532.37</v>
+        <v>1129312.3</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>77.27</v>
+        <v>26.43</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>PV; PP; PT; MDB</t>
+          <t>PSD; MDB; UNIÃO; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>DR. BERNARDO (PV); KALINE DE DR. BERNARDO (PV)</t>
+          <t>EDUARDO BRAGA (MDB); OMAR AZIZ (PSD)</t>
         </is>
       </c>
     </row>
@@ -12573,12 +12573,12 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>45.443.633/0001-02</t>
+          <t>17.940.670/0001-90</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>JD IMPRESSOS PERSONALIZADOS LTDA</t>
+          <t>C. KZAN</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -12593,12 +12593,12 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>JOAO PESSOA</t>
+          <t>BELEM</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -12607,28 +12607,28 @@
         </is>
       </c>
       <c r="I60" s="5" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>3290879.5</v>
+        <v>3334759.25</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>2335315</v>
+        <v>2131410</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>70.95999999999999</v>
+        <v>63.91</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>PL; REPUBLICANOS; PP; UNIÃO</t>
+          <t>PODE; MDB; PSD; PDT</t>
         </is>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>EFRAIM FILHO (PL); TIÃO GOMES (REPUBLICANOS)</t>
+          <t>DR. DANIEL (PODE); DRA. ALESSANDRA HABER (PODE)</t>
         </is>
       </c>
     </row>
@@ -12638,12 +12638,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>25.188.538/0001-00</t>
+          <t>45.443.633/0001-02</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>ESSENT INOVACAO CONTABIL LTDA</t>
+          <t>JD IMPRESSOS PERSONALIZADOS LTDA</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -12653,17 +12653,17 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Atividades de contabilidade, consultoria e auditoria contábil e tributária</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>HORIZONTINA</t>
+          <t>JOAO PESSOA</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -12672,28 +12672,28 @@
         </is>
       </c>
       <c r="I61" s="5" t="n">
-        <v>187</v>
+        <v>28</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>3273400.86</v>
+        <v>3290879.5</v>
       </c>
       <c r="K61" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>1539153.52</v>
+        <v>2337815</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>47.02</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>PT; MDB; PSD; PL</t>
+          <t>PL; REPUBLICANOS; PP; UNIÃO</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>LULA (PT); RICARDO FERRAÇO (MDB)</t>
+          <t>EFRAIM FILHO (PL); TIÃO GOMES (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -12703,12 +12703,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>00.887.925/0001-04</t>
+          <t>25.188.538/0001-00</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>GRAFMARQUES INDUSTRIA EDITORA E SERVICOS LTDA</t>
+          <t>ESSENT INOVACAO CONTABIL LTDA</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -12718,17 +12718,17 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Atividades de contabilidade, consultoria e auditoria contábil e tributária</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>HORIZONTINA</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -12737,28 +12737,28 @@
         </is>
       </c>
       <c r="I62" s="5" t="n">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>3233690.9</v>
+        <v>3275680.86</v>
       </c>
       <c r="K62" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>2234704.6</v>
+        <v>1546233.52</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>69.11</v>
+        <v>47.2</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>MDB; UNIÃO; PSD; PP</t>
+          <t>PT; MDB; PSD; PL</t>
         </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>ISNALDO BULHÕES JR (MDB); RENAN FILHO (MDB)</t>
+          <t>LULA (PT); RICARDO FERRAÇO (MDB)</t>
         </is>
       </c>
     </row>
@@ -12768,12 +12768,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>21.246.199/0001-02</t>
+          <t>00.887.925/0001-04</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>LEANDRO ROSA ADVOGADOS ASSOCIADOS</t>
+          <t>GRAFMARQUES INDUSTRIA EDITORA E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Atividades jurídicas, exceto cartórios</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>CURITIBA</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -12802,28 +12802,28 @@
         </is>
       </c>
       <c r="I63" s="5" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>3220000</v>
+        <v>3233690.9</v>
       </c>
       <c r="K63" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L63" s="6" t="n">
-        <v>195000</v>
+        <v>2234704.6</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>6.06</v>
+        <v>69.11</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>PL; NOVO</t>
+          <t>MDB; UNIÃO; PSD; PP</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>SERGIO MORO (PL); DELTAN DALLAGNOL (NOVO)</t>
+          <t>ISNALDO BULHÕES JR (MDB); RENAN FILHO (MDB)</t>
         </is>
       </c>
     </row>
@@ -12833,12 +12833,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>07.556.546/0001-72</t>
+          <t>21.246.199/0001-02</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>PRESSGRAF IMPORTACAO TECNOLOGIA E SERVICOS GRAFICOS LTDA</t>
+          <t>LEANDRO ROSA ADVOGADOS ASSOCIADOS</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -12848,17 +12848,17 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades jurídicas, exceto cartórios</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>SALVADOR</t>
+          <t>CURITIBA</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -12867,28 +12867,28 @@
         </is>
       </c>
       <c r="I64" s="5" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>3164378.8</v>
+        <v>3220000</v>
       </c>
       <c r="K64" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>2883468.8</v>
+        <v>195000</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>91.12</v>
+        <v>6.06</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>PSD; REPUBLICANOS; PSDB; UNIÃO</t>
+          <t>PL; NOVO</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>RAIMUNDO COSTA (PSD); MÁRCIO MARINHO (REPUBLICANOS)</t>
+          <t>SERGIO MORO (PL); DELTAN DALLAGNOL (NOVO)</t>
         </is>
       </c>
     </row>
@@ -12898,12 +12898,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>51.847.516/0001-07</t>
+          <t>47.461.986/0001-60</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>VOLARE IMPRESSAO TEXTIL LTDA</t>
+          <t>BLUEGRAF EDITORA LTDA</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>GUARULHOS</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -12932,28 +12932,28 @@
         </is>
       </c>
       <c r="I65" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>3128920</v>
+        <v>3168799.38</v>
       </c>
       <c r="K65" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L65" s="6" t="n">
-        <v>2713435</v>
+        <v>2578546.08</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>86.72</v>
+        <v>81.37</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>PSD; MDB; REPUBLICANOS; NOVO</t>
+          <t>PSD; PL; PP; PODE</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>TARCÍSIO (REPUBLICANOS); BALEIA ROSSI (MDB)</t>
+          <t>WALTER IHOSHI (PSD); DRA. SANDRA TADEU (PL)</t>
         </is>
       </c>
     </row>
@@ -12963,12 +12963,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>41.470.063/0001-99</t>
+          <t>07.556.546/0001-72</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>SETE CORES INDUSTRIA E COMERCIO LTDA</t>
+          <t>PRESSGRAF IMPORTACAO TECNOLOGIA E SERVICOS GRAFICOS LTDA</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -12978,17 +12978,17 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>SAO LUIS</t>
+          <t>SALVADOR</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -12997,28 +12997,28 @@
         </is>
       </c>
       <c r="I66" s="5" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>3122716.46</v>
+        <v>3164378.8</v>
       </c>
       <c r="K66" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L66" s="6" t="n">
-        <v>2736315.46</v>
+        <v>2883468.8</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>87.63</v>
+        <v>91.12</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>PL; PCDOB; PDT; REPUBLICANOS</t>
+          <t>PSD; REPUBLICANOS; PSDB; UNIÃO</t>
         </is>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>SILVIO ANTÔNIO (PL); MÁRCIO JERRY (PCDOB)</t>
+          <t>RAIMUNDO COSTA (PSD); MÁRCIO MARINHO (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -13028,12 +13028,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>24.935.788/0001-96</t>
+          <t>51.847.516/0001-07</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>AFA INDUSTRIA COMERCIO E SERVICOS LTDA</t>
+          <t>VOLARE IMPRESSAO TEXTIL LTDA</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -13043,17 +13043,17 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Confecção de roupas profissionais</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>APARECIDA DE GOIANIA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -13062,28 +13062,28 @@
         </is>
       </c>
       <c r="I67" s="5" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>3101962.1</v>
+        <v>3141920</v>
       </c>
       <c r="K67" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L67" s="6" t="n">
-        <v>2273937.1</v>
+        <v>2713435</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>73.31</v>
+        <v>86.36</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE; UNIÃO; PSDB; MDB</t>
+          <t>PSD; MDB; REPUBLICANOS; NOVO</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>DENES PEREIRA (SOLIDARIEDADE); SALMA DA PESTALOZZI (UNIÃO)</t>
+          <t>TARCÍSIO (REPUBLICANOS); BALEIA ROSSI (MDB)</t>
         </is>
       </c>
     </row>
@@ -13093,12 +13093,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>17.940.670/0001-90</t>
+          <t>41.470.063/0001-99</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>C. KZAN</t>
+          <t>SETE CORES INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -13108,17 +13108,17 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>BELEM</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -13127,28 +13127,28 @@
         </is>
       </c>
       <c r="I68" s="5" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>3093159.25</v>
+        <v>3127366.46</v>
       </c>
       <c r="K68" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>1889810</v>
+        <v>2740965.46</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>61.1</v>
+        <v>87.64</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>PODE; MDB; PSD; PDT</t>
+          <t>PL; PCDOB; PDT; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>DR. DANIEL (PODE); DRA. ALESSANDRA HABER (PODE)</t>
+          <t>SILVIO ANTÔNIO (PL); MÁRCIO JERRY (PCDOB)</t>
         </is>
       </c>
     </row>
@@ -13158,12 +13158,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>47.461.986/0001-60</t>
+          <t>46.439.622/0001-11</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>BLUEGRAF EDITORA LTDA</t>
+          <t>FEIRA BANDEIRAS E IMPRESSOS LTDA</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -13173,17 +13173,17 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>GUARULHOS</t>
+          <t>FEIRA DE SANTANA</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -13192,28 +13192,28 @@
         </is>
       </c>
       <c r="I69" s="5" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>3078931.38</v>
+        <v>3123601.33</v>
       </c>
       <c r="K69" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L69" s="6" t="n">
-        <v>2488678.08</v>
+        <v>2919644.84</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>80.83</v>
+        <v>93.47</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>PSD; PL; PP; PODE</t>
+          <t>UNIÃO; PT; PSB; PSD</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>WALTER IHOSHI (PSD); DRA. SANDRA TADEU (PL)</t>
+          <t>PROFESSORA DAYANE PIMENTEL (UNIÃO); VITOR BONFIM (PSB)</t>
         </is>
       </c>
     </row>
@@ -13223,12 +13223,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>35.844.647/0001-84</t>
+          <t>24.935.788/0001-96</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>J C SILVA LTDA</t>
+          <t>AFA INDUSTRIA COMERCIO E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -13238,17 +13238,17 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de embalagens de papel</t>
+          <t>Confecção de roupas profissionais</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>TERESINA</t>
+          <t>APARECIDA DE GOIANIA</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -13257,28 +13257,28 @@
         </is>
       </c>
       <c r="I70" s="5" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>3072492</v>
+        <v>3101962.1</v>
       </c>
       <c r="K70" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>2946822</v>
+        <v>2273937.1</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>95.91</v>
+        <v>73.31</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>PP; PT; MDB; PSD</t>
+          <t>SOLIDARIEDADE; UNIÃO; PSDB; MDB</t>
         </is>
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>AMANDA GENTIL (PP); ÁTILA LIRA (PP)</t>
+          <t>DENES PEREIRA (SOLIDARIEDADE); SALMA DA PESTALOZZI (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -13288,12 +13288,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>30.985.686/0001-88</t>
+          <t>35.844.647/0001-84</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>INK IMPRESSAO DE  MATERIAL PUBLICITARIO, ENCADERNACAO E EDICAO DE CADASTROS LTDA</t>
+          <t>J C SILVA LTDA</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -13303,17 +13303,17 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Fabricação de embalagens de papel</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>JOAO PESSOA</t>
+          <t>TERESINA</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -13322,28 +13322,28 @@
         </is>
       </c>
       <c r="I71" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>3051300</v>
+        <v>3072492</v>
       </c>
       <c r="K71" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L71" s="6" t="n">
-        <v>2235665</v>
+        <v>2946822</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>73.27</v>
+        <v>95.91</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>PSD; PODE; MDB; UNIÃO</t>
+          <t>PP; PT; MDB; PSD</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>DOUTOR JHONY (PSD); MERSINHO LUCENA (PSD)</t>
+          <t>AMANDA GENTIL (PP); ÁTILA LIRA (PP)</t>
         </is>
       </c>
     </row>
@@ -13353,12 +13353,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>46.439.622/0001-11</t>
+          <t>30.985.686/0001-88</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>FEIRA BANDEIRAS E IMPRESSOS LTDA</t>
+          <t>INK IMPRESSAO DE  MATERIAL PUBLICITARIO, ENCADERNACAO E EDICAO DE CADASTROS LTDA</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -13368,17 +13368,17 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de produtos de papel, cartolina, papel-cartão e papelão ondulado para uso comercial e de escritório</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>FEIRA DE SANTANA</t>
+          <t>JOAO PESSOA</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -13387,28 +13387,28 @@
         </is>
       </c>
       <c r="I72" s="5" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>3032135.98</v>
+        <v>3051300</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>2828179.49</v>
+        <v>2235665</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>93.27</v>
+        <v>73.27</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO; PT; PSB; PSD</t>
+          <t>PSD; PODE; MDB; UNIÃO</t>
         </is>
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>PROFESSORA DAYANE PIMENTEL (UNIÃO); VITOR BONFIM (PSB)</t>
+          <t>DOUTOR JHONY (PSD); MERSINHO LUCENA (PSD)</t>
         </is>
       </c>
     </row>
@@ -13517,19 +13517,19 @@
         </is>
       </c>
       <c r="I74" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>3008940.14</v>
+        <v>3031344.14</v>
       </c>
       <c r="K74" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L74" s="6" t="n">
-        <v>1693341.36</v>
+        <v>1715745.36</v>
       </c>
       <c r="M74" s="6" t="n">
-        <v>56.28</v>
+        <v>56.6</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
@@ -13647,16 +13647,16 @@
         </is>
       </c>
       <c r="I76" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>2975389.15</v>
+        <v>2976070.15</v>
       </c>
       <c r="K76" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L76" s="6" t="n">
-        <v>2315687.99</v>
+        <v>2316368.99</v>
       </c>
       <c r="M76" s="6" t="n">
         <v>77.83</v>
@@ -13873,12 +13873,12 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>64.433.090/0001-97</t>
+          <t>56.019.930/0001-41</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>GAB INDUSTRIA GRAFICA LTDA</t>
+          <t>INOVE IMPRESSOES GRAFICAS E MARKETING POLITICO LTDA</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -13893,12 +13893,12 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>NEROPOLIS</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -13907,28 +13907,28 @@
         </is>
       </c>
       <c r="I80" s="5" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>2840200.19</v>
+        <v>2846058.41</v>
       </c>
       <c r="K80" s="6" t="n">
         <v>0.06</v>
       </c>
       <c r="L80" s="6" t="n">
-        <v>2552414.88</v>
+        <v>2154919.03</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>89.87</v>
+        <v>75.72</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO; PT; MDB; REPUBLICANOS</t>
+          <t>PL; PSB; UNIÃO; PP</t>
         </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>GRACINHA CAIADO (UNIÃO); MARUSSA BOLDRIN (REPUBLICANOS)</t>
+          <t>VINICIUS DINIZ (PL); BERNARDO ROSSI (UNIÃO)</t>
         </is>
       </c>
     </row>
@@ -13938,12 +13938,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>56.019.930/0001-41</t>
+          <t>64.433.090/0001-97</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>INOVE IMPRESSOES GRAFICAS E MARKETING POLITICO LTDA</t>
+          <t>GAB INDUSTRIA GRAFICA LTDA</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -13958,12 +13958,12 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>NEROPOLIS</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -13972,28 +13972,28 @@
         </is>
       </c>
       <c r="I81" s="5" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>2803233.41</v>
+        <v>2840308.59</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="L81" s="6" t="n">
-        <v>2065519.03</v>
+        <v>2552523.28</v>
       </c>
       <c r="M81" s="6" t="n">
-        <v>73.68000000000001</v>
+        <v>89.87</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>PL; PSB; UNIÃO; REPUBLICANOS</t>
+          <t>UNIÃO; PT; MDB; REPUBLICANOS</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>VINICIUS DINIZ (PL); BERNARDO ROSSI (UNIÃO)</t>
+          <t>GRACINHA CAIADO (UNIÃO); MARUSSA BOLDRIN (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -14102,10 +14102,10 @@
         </is>
       </c>
       <c r="I83" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>2755239.1</v>
+        <v>2768706.1</v>
       </c>
       <c r="K83" s="6" t="n">
         <v>0.05</v>
@@ -14114,7 +14114,7 @@
         <v>2195722.4</v>
       </c>
       <c r="M83" s="6" t="n">
-        <v>79.69</v>
+        <v>79.31</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
@@ -14263,12 +14263,12 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>51.615.351/0001-48</t>
+          <t>06.933.485/0001-52</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>ART MUSIC STUDIO PRODUTORA DE AUDIO   VIDEO LTDA</t>
+          <t>HERINGER TAXI AEREO LTDA</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -14278,17 +14278,17 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Atividades de gravação de som e de edição de música</t>
+          <t>Transporte aéreo de passageiros não regular</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>PALMAS</t>
+          <t>IMPERATRIZ</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -14297,28 +14297,28 @@
         </is>
       </c>
       <c r="I86" s="5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>2614250</v>
+        <v>2617650</v>
       </c>
       <c r="K86" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L86" s="6" t="n">
-        <v>1314250</v>
+        <v>1641650</v>
       </c>
       <c r="M86" s="6" t="n">
-        <v>50.27</v>
+        <v>62.71</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>PSD; PL; PSDB; PDT</t>
+          <t>PODE; PT; UNIÃO; MDB</t>
         </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>LAUREZ MOREIRA (PSD); FILIPE MARTINS (PL)</t>
+          <t>DR. DANIEL (PODE); HILDO ROCHA (MDB)</t>
         </is>
       </c>
     </row>
@@ -14328,12 +14328,12 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>16.724.877/0001-65</t>
+          <t>51.615.351/0001-48</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>EBA - COMUNICACAO E MARKETING POLITICO LTDA</t>
+          <t>ART MUSIC STUDIO PRODUTORA DE AUDIO   VIDEO LTDA</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -14343,17 +14343,17 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Atividades de gravação de som e de edição de música</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>NATAL</t>
+          <t>PALMAS</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -14362,28 +14362,28 @@
         </is>
       </c>
       <c r="I87" s="5" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>2590000</v>
+        <v>2614250</v>
       </c>
       <c r="K87" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L87" s="6" t="n">
-        <v>750000</v>
+        <v>1314250</v>
       </c>
       <c r="M87" s="6" t="n">
-        <v>28.96</v>
+        <v>50.27</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>PL; PODE; PSDB</t>
+          <t>PSD; PL; PSDB; PDT</t>
         </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>ÁLVARO DIAS (PL); STYVENSON VALENTIM (PODE)</t>
+          <t>LAUREZ MOREIRA (PSD); FILIPE MARTINS (PL)</t>
         </is>
       </c>
     </row>
@@ -14393,12 +14393,12 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>31.321.080/0001-00</t>
+          <t>16.724.877/0001-65</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>UNIGRAFICA INDUSTRIA GRAFICA LTDA</t>
+          <t>EBA - COMUNICACAO E MARKETING POLITICO LTDA</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Fabricação de embalagens de papel</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>PARNAMIRIM</t>
+          <t>NATAL</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -14427,28 +14427,28 @@
         </is>
       </c>
       <c r="I88" s="5" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>2583889.36</v>
+        <v>2590000</v>
       </c>
       <c r="K88" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L88" s="6" t="n">
-        <v>2107905</v>
+        <v>790000</v>
       </c>
       <c r="M88" s="6" t="n">
-        <v>81.58</v>
+        <v>30.5</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>PL; UNIÃO; PSD; PP</t>
+          <t>PL; PODE; PSDB</t>
         </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>JUNINHO SAIA RODADA (PL); ZENAIDE MAIA (PSD)</t>
+          <t>ÁLVARO DIAS (PL); STYVENSON VALENTIM (PODE)</t>
         </is>
       </c>
     </row>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>67.820.413/0001-93</t>
+          <t>31.321.080/0001-00</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>LGS SERVICOS LTDA</t>
+          <t>UNIGRAFICA INDUSTRIA GRAFICA LTDA</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -14473,17 +14473,17 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Fabricação de embalagens de papel</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t>PARNAMIRIM</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -14492,28 +14492,28 @@
         </is>
       </c>
       <c r="I89" s="5" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>2568850</v>
+        <v>2583889.36</v>
       </c>
       <c r="K89" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L89" s="6" t="n">
-        <v>2259050</v>
+        <v>2110305</v>
       </c>
       <c r="M89" s="6" t="n">
-        <v>87.94</v>
+        <v>81.67</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>PSD; REPUBLICANOS; UNIÃO; PL</t>
+          <t>PL; UNIÃO; PSD; PP</t>
         </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>CAPITÃO SAMUEL (UNIÃO); GRACINHA GARCEZ (REPUBLICANOS)</t>
+          <t>JUNINHO SAIA RODADA (PL); ZENAIDE MAIA (PSD)</t>
         </is>
       </c>
     </row>
@@ -14523,12 +14523,12 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>64.752.158/0001-09</t>
+          <t>67.820.413/0001-93</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>OKAN COMUNICACAO LTDA</t>
+          <t>LGS SERVICOS LTDA</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -14538,17 +14538,17 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -14557,28 +14557,28 @@
         </is>
       </c>
       <c r="I90" s="5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>2567000</v>
+        <v>2568850</v>
       </c>
       <c r="K90" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L90" s="6" t="n">
-        <v>2517000</v>
+        <v>2259050</v>
       </c>
       <c r="M90" s="6" t="n">
-        <v>98.05</v>
+        <v>87.94</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>PT; PSOL; UNIÃO</t>
+          <t>PSD; REPUBLICANOS; UNIÃO; PL</t>
         </is>
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>PATRUS ANANIAS (PT); DUDA SALABERT (PSOL)</t>
+          <t>CAPITÃO SAMUEL (UNIÃO); GRACINHA GARCEZ (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -14588,12 +14588,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>17.340.447/0001-02</t>
+          <t>64.752.158/0001-09</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>MARICLEYDSON COSTA DA SILVA  LTDA</t>
+          <t>OKAN COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -14603,17 +14603,17 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>NATAL</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -14622,28 +14622,28 @@
         </is>
       </c>
       <c r="I91" s="5" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>2563744.6</v>
+        <v>2567000</v>
       </c>
       <c r="K91" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L91" s="6" t="n">
-        <v>1832692.1</v>
+        <v>2517000</v>
       </c>
       <c r="M91" s="6" t="n">
-        <v>71.48</v>
+        <v>98.05</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>PL; PT; PV; PDT</t>
+          <t>PT; PSOL; UNIÃO</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>NINA (PL); LUÍZ EDUARDO (PL)</t>
+          <t>PATRUS ANANIAS (PT); DUDA SALABERT (PSOL)</t>
         </is>
       </c>
     </row>
@@ -14653,12 +14653,12 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>26.983.273/0001-97</t>
+          <t>17.340.447/0001-02</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>VITORINO   MENDONCA LTDA</t>
+          <t>MARICLEYDSON COSTA DA SILVA  LTDA</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -14668,17 +14668,17 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>NATAL</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -14687,28 +14687,28 @@
         </is>
       </c>
       <c r="I92" s="5" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>2550000</v>
+        <v>2563744.6</v>
       </c>
       <c r="K92" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L92" s="6" t="n">
-        <v>2200000</v>
+        <v>1914692.1</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>86.27</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PL; PT; PV; PDT</t>
         </is>
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>WILDER MORAIS (PL); MARCOS ROGÉRIO (PL)</t>
+          <t>NINA (PL); LUÍZ EDUARDO (PL)</t>
         </is>
       </c>
     </row>
@@ -14718,12 +14718,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>35.593.706/0001-99</t>
+          <t>26.983.273/0001-97</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>UNIPAUTA FORMULARIOS LTDA</t>
+          <t>VITORINO   MENDONCA LTDA</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -14733,17 +14733,17 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Impressão de material de segurança</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>OLINDA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -14752,28 +14752,28 @@
         </is>
       </c>
       <c r="I93" s="5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>2531795</v>
+        <v>2550000</v>
       </c>
       <c r="K93" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L93" s="6" t="n">
-        <v>2316995</v>
+        <v>2200000</v>
       </c>
       <c r="M93" s="6" t="n">
-        <v>91.52</v>
+        <v>86.27</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>MDB; PCDOB; REPUBLICANOS; PODE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>IZA ARRUDA (MDB); RENILDO CALHEIROS (PCDOB)</t>
+          <t>WILDER MORAIS (PL); MARCOS ROGÉRIO (PL)</t>
         </is>
       </c>
     </row>
@@ -14783,12 +14783,12 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>15.687.382/0001-40</t>
+          <t>35.593.706/0001-99</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>CARAMBOLA PRODUCOES LTDA</t>
+          <t>UNIPAUTA FORMULARIOS LTDA</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -14798,17 +14798,17 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Atividades de publicidade não especificadas anteriormente</t>
+          <t>Impressão de material de segurança</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>BALNEARIO CAMBORIU</t>
+          <t>OLINDA</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -14817,28 +14817,28 @@
         </is>
       </c>
       <c r="I94" s="5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>2513200</v>
+        <v>2531795</v>
       </c>
       <c r="K94" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L94" s="6" t="n">
-        <v>2513200</v>
+        <v>2316995</v>
       </c>
       <c r="M94" s="6" t="n">
-        <v>100</v>
+        <v>91.52</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>PDT; PL</t>
+          <t>MDB; PCDOB; REPUBLICANOS; PODE</t>
         </is>
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>REQUIÃO FILHO (PDT); THIAGO AURICCHIO (PL)</t>
+          <t>IZA ARRUDA (MDB); RENILDO CALHEIROS (PCDOB)</t>
         </is>
       </c>
     </row>
@@ -14848,12 +14848,12 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>68.154.614/0001-61</t>
+          <t>15.687.382/0001-40</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>ESTUDIO 90 PRODUCOES LTDA</t>
+          <t>CARAMBOLA PRODUCOES LTDA</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -14863,17 +14863,17 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
+          <t>Atividades de publicidade não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>PORTO ALEGRE</t>
+          <t>BALNEARIO CAMBORIU</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -14885,25 +14885,25 @@
         <v>2</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>2500000</v>
+        <v>2513200</v>
       </c>
       <c r="K95" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L95" s="6" t="n">
-        <v>2500000</v>
+        <v>2513200</v>
       </c>
       <c r="M95" s="6" t="n">
         <v>100</v>
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>MDB; PSD</t>
+          <t>PDT; PL</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>GABRIEL SOUZA (MDB); FREDERICO ANTUNES (PSD)</t>
+          <t>REQUIÃO FILHO (PDT); THIAGO AURICCHIO (PL)</t>
         </is>
       </c>
     </row>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>22.966.876/0001-20</t>
+          <t>68.154.614/0001-61</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>REDE DE NEGOCIOS E PRODUCAO DE EVENTOS LTDA</t>
+          <t>ESTUDIO 90 PRODUCOES LTDA</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -14928,17 +14928,17 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Atividades de organização de eventos, exceto culturais e esportivos</t>
+          <t>Atividades de produção cinematográfica, de vídeos e de programas de televisão</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>RECIFE</t>
+          <t>PORTO ALEGRE</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="I96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J96" s="6" t="n">
         <v>2500000</v>
@@ -14956,19 +14956,19 @@
         <v>0.05</v>
       </c>
       <c r="L96" s="6" t="n">
-        <v>1000000</v>
+        <v>2500000</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>MDB; PSD</t>
         </is>
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>RAQUEL LYRA (PSD)</t>
+          <t>GABRIEL SOUZA (MDB); FREDERICO ANTUNES (PSD)</t>
         </is>
       </c>
     </row>
@@ -15043,12 +15043,12 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>23.929.195/0001-54</t>
+          <t>22.966.876/0001-20</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>SERATA EDITORA GRAFICA E PUBLICIDADE LTDA</t>
+          <t>REDE DE NEGOCIOS E PRODUCAO DE EVENTOS LTDA</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -15058,17 +15058,17 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
+          <t>Atividades de organização de eventos, exceto culturais e esportivos</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>CUIABA</t>
+          <t>RECIFE</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -15077,28 +15077,28 @@
         </is>
       </c>
       <c r="I98" s="5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J98" s="6" t="n">
-        <v>2482058.21</v>
+        <v>2500000</v>
       </c>
       <c r="K98" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L98" s="6" t="n">
-        <v>1543613.61</v>
+        <v>1000000</v>
       </c>
       <c r="M98" s="6" t="n">
-        <v>62.19</v>
+        <v>40</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
-          <t>PL; REPUBLICANOS; PV; PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t>CORONEL FERNANDA (PL); ZÉ MEDEIROS (PL)</t>
+          <t>RAQUEL LYRA (PSD)</t>
         </is>
       </c>
     </row>
@@ -15108,12 +15108,12 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>14.876.708/0001-15</t>
+          <t>23.929.195/0001-54</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>NOGUEIRA, ALBUQUERQUE E FREIRE ASSOCIADOS S/S</t>
+          <t>SERATA EDITORA GRAFICA E PUBLICIDADE LTDA</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -15123,17 +15123,17 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Atividades de contabilidade, consultoria e auditoria contábil e tributária</t>
+          <t>Impressão de jornais, livros, revistas e outras publicações periódicas</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>MACEIO</t>
+          <t>CUIABA</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -15142,28 +15142,28 @@
         </is>
       </c>
       <c r="I99" s="5" t="n">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>2474000</v>
+        <v>2482058.21</v>
       </c>
       <c r="K99" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L99" s="6" t="n">
-        <v>820500</v>
+        <v>1571613.61</v>
       </c>
       <c r="M99" s="6" t="n">
-        <v>33.16</v>
+        <v>63.32</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>MDB; PP; PL; PSDB</t>
+          <t>PL; REPUBLICANOS; PV; PT</t>
         </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>ARTHUR LIRA (PP); DANIEL BARBOSA (PP)</t>
+          <t>CORONEL FERNANDA (PL); ZÉ MEDEIROS (PL)</t>
         </is>
       </c>
     </row>
@@ -15173,12 +15173,12 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>41.220.067/0001-19</t>
+          <t>14.876.708/0001-15</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>JMARTELO SOLUCOES EM COMUNICACAO LTDA</t>
+          <t>NOGUEIRA, ALBUQUERQUE E FREIRE ASSOCIADOS S/S</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -15188,17 +15188,17 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Fotocópias, preparação de documentos e outros serviços especializados de apoio administrativo</t>
+          <t>Atividades de contabilidade, consultoria e auditoria contábil e tributária</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>CAMPINAS</t>
+          <t>MACEIO</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -15207,28 +15207,28 @@
         </is>
       </c>
       <c r="I100" s="5" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>2400000</v>
+        <v>2474000</v>
       </c>
       <c r="K100" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L100" s="6" t="n">
-        <v>1600000</v>
+        <v>850500</v>
       </c>
       <c r="M100" s="6" t="n">
-        <v>66.67</v>
+        <v>34.38</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>MDB; PP; PL; PSDB</t>
         </is>
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>ARTHUR LIRA (PP); DANIEL BARBOSA (PP)</t>
         </is>
       </c>
     </row>
@@ -15238,12 +15238,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>25.358.819/0001-56</t>
+          <t>41.220.067/0001-19</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>MIOLO COMUNICACAO GRAFICA E EDITORA LTDA</t>
+          <t>JMARTELO SOLUCOES EM COMUNICACAO LTDA</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -15253,17 +15253,17 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Impressão de materiais para outros usos</t>
+          <t>Fotocópias, preparação de documentos e outros serviços especializados de apoio administrativo</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>BRASILIA</t>
+          <t>CAMPINAS</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -15272,28 +15272,28 @@
         </is>
       </c>
       <c r="I101" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>2343940.2</v>
+        <v>2400000</v>
       </c>
       <c r="K101" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L101" s="6" t="n">
-        <v>2322135</v>
+        <v>1600000</v>
       </c>
       <c r="M101" s="6" t="n">
-        <v>99.06999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>PL; PDT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL); EVANDRO ARAUJO (PL)</t>
+          <t>FLAVIO BOLSONARO (PL)</t>
         </is>
       </c>
     </row>
@@ -15303,12 +15303,12 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>06.340.575/0001-30</t>
+          <t>25.358.819/0001-56</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>MAVIMIX ADESIVOS DECORATIVOS LTDA</t>
+          <t>MIOLO COMUNICACAO GRAFICA E EDITORA LTDA</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -15318,17 +15318,17 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Comércio varejista de outros produtos novos não especificados anteriormente</t>
+          <t>Impressão de materiais para outros usos</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>RIO DE JANEIRO</t>
+          <t>BRASILIA</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -15337,28 +15337,28 @@
         </is>
       </c>
       <c r="I102" s="5" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J102" s="6" t="n">
-        <v>2304363.37</v>
+        <v>2343940.2</v>
       </c>
       <c r="K102" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L102" s="6" t="n">
-        <v>1795898.68</v>
+        <v>2322135</v>
       </c>
       <c r="M102" s="6" t="n">
-        <v>77.93000000000001</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
-          <t>UNIÃO; REPUBLICANOS; PL; PRD</t>
+          <t>PL; PDT</t>
         </is>
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>RUEDA (UNIÃO); WAGUINHO (REPUBLICANOS)</t>
+          <t>FLAVIO BOLSONARO (PL); EVANDRO ARAUJO (PL)</t>
         </is>
       </c>
     </row>
@@ -15368,12 +15368,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>31.792.812/0001-40</t>
+          <t>06.340.575/0001-30</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>SANTIER CONSULTORIA E ESTRATEGIA LTDA</t>
+          <t>MAVIMIX ADESIVOS DECORATIVOS LTDA</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -15383,17 +15383,17 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Outras atividades de prestação de serviços de informação não especificadas anteriormente</t>
+          <t>Comércio varejista de outros produtos novos não especificados anteriormente</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>BELO HORIZONTE</t>
+          <t>RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -15402,28 +15402,28 @@
         </is>
       </c>
       <c r="I103" s="5" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>2302560</v>
+        <v>2304363.37</v>
       </c>
       <c r="K103" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="L103" s="6" t="n">
-        <v>1369560</v>
+        <v>1820773.33</v>
       </c>
       <c r="M103" s="6" t="n">
-        <v>59.48</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t>PT; PSOL; AVANTE; PODE</t>
+          <t>UNIÃO; REPUBLICANOS; PL; PRD</t>
         </is>
       </c>
       <c r="O103" s="4" t="inlineStr">
         <is>
-          <t>FÁBIO TRAD (PT); ÁUREA CAROLINA (PSOL)</t>
+          <t>RUEDA (UNIÃO); WAGUINHO (REPUBLICANOS)</t>
         </is>
       </c>
     </row>
@@ -15433,12 +15433,12 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>08.668.296/0001-25</t>
+          <t>31.792.812/0001-40</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>COTA PESQUISAS DE MERCADO E DE OPINIAO PUBLICA LTDA</t>
+          <t>SANTIER CONSULTORIA E ESTRATEGIA LTDA</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -15448,17 +15448,17 @@
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>Pesquisas de mercado e de opinião pública</t>
+          <t>Outras atividades de prestação de serviços de informação não especificadas anteriormente</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>CURITIBA</t>
+          <t>BELO HORIZONTE</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
@@ -15467,42 +15467,42 @@
         </is>
       </c>
       <c r="I104" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>2302500</v>
+        <v>2302560</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>1609250</v>
+        <v>1369560</v>
       </c>
       <c r="M104" s="9" t="n">
-        <v>69.89</v>
+        <v>59.48</v>
       </c>
       <c r="N104" s="7" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT; PSOL; AVANTE; PODE</t>
         </is>
       </c>
       <c r="O104" s="7" t="inlineStr">
         <is>
-          <t>FLAVIO BOLSONARO (PL)</t>
+          <t>FÁBIO TRAD (PT); ÁUREA CAROLINA (PSOL)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-15.</t>
         </is>
       </c>
     </row>
@@ -15626,13 +15626,13 @@
         <v>1417</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>972028352.83</v>
+        <v>972229824.3200001</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>14.78</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="6">
@@ -15658,13 +15658,13 @@
         <v>972</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>597767672.99</v>
+        <v>598067672.99</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>9.09</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="7">
@@ -15690,13 +15690,13 @@
         <v>704</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>532565326.54</v>
+        <v>532731515.54</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>8.1</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="8">
@@ -15728,7 +15728,7 @@
         <v>486877337.61</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>7.4</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="9">
@@ -15760,7 +15760,7 @@
         <v>472886618.52</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>7.19</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="10">
@@ -15824,7 +15824,7 @@
         <v>362852325.06</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>5.52</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="12">
@@ -15946,10 +15946,10 @@
         <v>521</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>140317788.88</v>
+        <v>140329788.88</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>2.13</v>
@@ -16010,10 +16010,10 @@
         <v>866</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>89500982.73</v>
+        <v>89520982.73</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>1.36</v>
@@ -16042,10 +16042,10 @@
         <v>538</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1528</v>
+        <v>1541</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>81043165.18000001</v>
+        <v>81055845.98</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>1.23</v>
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1890</v>
+        <v>1895</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>46436245.26</v>
+        <v>46530884.52</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0.71</v>
@@ -16263,13 +16263,13 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>27459524.67</v>
+        <v>27469524.67</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>0.42</v>
@@ -16359,13 +16359,13 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>2550</v>
+        <v>2560</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>16342043.63</v>
+        <v>16350691.63</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0.25</v>
@@ -16554,10 +16554,10 @@
         <v>38</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>7863886.52</v>
+        <v>7905886.52</v>
       </c>
       <c r="H34" s="6" t="n">
         <v>0.12</v>
@@ -16714,10 +16714,10 @@
         <v>151</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>6401744.69</v>
+        <v>6421744.75</v>
       </c>
       <c r="H39" s="6" t="n">
         <v>0.1</v>
@@ -16743,13 +16743,13 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>6069127.43</v>
+        <v>6102525.1</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>0.09</v>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE-RIO DE JANEIRO-RJ-ESTADUAL</t>
+          <t>REPUBLICANOS RIO GRANDE DO SUL - RS - ESTADUAL</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -16867,17 +16867,17 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>47</v>
+        <v>267</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>5372830</v>
+        <v>5383779</v>
       </c>
       <c r="H44" s="6" t="n">
         <v>0.08</v>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>REPUBLICANOS RIO GRANDE DO SUL - RS - ESTADUAL</t>
+          <t>SOLIDARIEDADE-RIO DE JANEIRO-RJ-ESTADUAL</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -16899,17 +16899,17 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>263</v>
+        <v>47</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>5372279</v>
+        <v>5372830</v>
       </c>
       <c r="H45" s="6" t="n">
         <v>0.08</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>5330693.51</v>
+        <v>5331179.98</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>0.08</v>
@@ -17206,14 +17206,14 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-15.</t>
         </is>
       </c>
     </row>
@@ -17313,7 +17313,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>941352416.62</v>
+        <v>941863602.37</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>12.89</v>
@@ -17339,7 +17339,7 @@
         <v>777520950.29</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>10.65</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="7">
@@ -17359,7 +17359,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>540061272.24</v>
+        <v>540734381.52</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>7.4</v>
@@ -17382,7 +17382,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>501738323.89</v>
+        <v>501949079.58</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>6.87</v>
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>348382819.68</v>
+        <v>348809893.96</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>4.77</v>
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>347809594.83</v>
+        <v>348269323.09</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>4.76</v>
@@ -17451,7 +17451,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>319875531.57</v>
+        <v>320180921.52</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>4.38</v>
@@ -17474,7 +17474,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>260673741.06</v>
+        <v>260758408.08</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>3.57</v>
@@ -17497,10 +17497,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>248641151.84</v>
+        <v>248829183.34</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="14">
@@ -17520,7 +17520,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>233323038.34</v>
+        <v>233931458.5</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>3.2</v>
@@ -17543,7 +17543,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>223955484.48</v>
+        <v>224083484.48</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>3.07</v>
@@ -17566,7 +17566,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>216778997.14</v>
+        <v>217166956.08</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>2.97</v>
@@ -17589,7 +17589,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>206867725.89</v>
+        <v>206920736.24</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>2.83</v>
@@ -17612,7 +17612,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>191797404.38</v>
+        <v>192361636.49</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>2.63</v>
@@ -17635,10 +17635,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>189645533.43</v>
+        <v>189655533.43</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="20">
@@ -17658,7 +17658,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>176762535.6</v>
+        <v>176872010.23</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>2.42</v>
@@ -17681,7 +17681,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>162812264.63</v>
+        <v>163121695.8</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>2.23</v>
@@ -17704,7 +17704,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>149734962.6</v>
+        <v>149765818.85</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>2.05</v>
@@ -17727,10 +17727,10 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>147135522.01</v>
+        <v>147279582.87</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="24">
@@ -17750,7 +17750,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>145383532.58</v>
+        <v>145500892.28</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>1.99</v>
@@ -17773,10 +17773,10 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>135383050.09</v>
+        <v>136913290.09</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="26">
@@ -17796,7 +17796,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>134862023.11</v>
+        <v>134882233.11</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>1.85</v>
@@ -17819,7 +17819,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>123176777.67</v>
+        <v>123217657.01</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>1.69</v>
@@ -17842,7 +17842,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>121115288.53</v>
+        <v>121396489.89</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>1.66</v>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>118181676.81</v>
+        <v>118199043.81</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>1.62</v>
@@ -17888,7 +17888,7 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>116715353.72</v>
+        <v>116947052.84</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>1.6</v>
@@ -17911,7 +17911,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>116096217.41</v>
+        <v>116160099.96</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>1.59</v>
@@ -17934,7 +17934,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>105927597.84</v>
+        <v>105994028.51</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>1.45</v>
@@ -17957,10 +17957,10 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>148150465.81</v>
+        <v>148152716.75</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>23.46</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="34">
@@ -17983,7 +17983,7 @@
         <v>63540943.62</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>10.06</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="35">
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>35743802.27</v>
+        <v>35779143.44</v>
       </c>
       <c r="E35" s="12" t="n">
         <v>5.66</v>
@@ -18026,7 +18026,7 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>32343843.12</v>
+        <v>32389921.59</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>5.12</v>
@@ -18072,7 +18072,7 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>27986415.41</v>
+        <v>27996415.41</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>4.43</v>
@@ -18095,7 +18095,7 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>22106720.42</v>
+        <v>22120475.07</v>
       </c>
       <c r="E39" s="12" t="n">
         <v>3.5</v>
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>18076663.75</v>
+        <v>18088163.75</v>
       </c>
       <c r="E41" s="12" t="n">
         <v>2.86</v>
@@ -18164,10 +18164,10 @@
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>17840460.01</v>
+        <v>17842960.01</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="43">
@@ -18187,7 +18187,7 @@
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>17640588</v>
+        <v>17644336</v>
       </c>
       <c r="E43" s="12" t="n">
         <v>2.79</v>
@@ -18213,7 +18213,7 @@
         <v>17151108.64</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="45">
@@ -18302,10 +18302,10 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>14754856.34</v>
+        <v>14904755.93</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="49">
@@ -18328,7 +18328,7 @@
         <v>14693216.87</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="50">
@@ -18348,7 +18348,7 @@
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>12945389.35</v>
+        <v>12945672.35</v>
       </c>
       <c r="E50" s="12" t="n">
         <v>2.05</v>
@@ -18371,7 +18371,7 @@
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>12135824.21</v>
+        <v>12136324.21</v>
       </c>
       <c r="E51" s="12" t="n">
         <v>1.92</v>
@@ -18397,7 +18397,7 @@
         <v>11715177.76</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="53">
@@ -18417,10 +18417,10 @@
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>10541115.61</v>
+        <v>10741115.61</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="54">
@@ -18489,7 +18489,7 @@
         <v>7868672.31</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="57">
@@ -18509,7 +18509,7 @@
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>7663506.75</v>
+        <v>7668205.73</v>
       </c>
       <c r="E57" s="12" t="n">
         <v>1.21</v>
@@ -18555,7 +18555,7 @@
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>6935311.45</v>
+        <v>6936280.45</v>
       </c>
       <c r="E59" s="12" t="n">
         <v>1.1</v>
@@ -18578,10 +18578,10 @@
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>6499838.31</v>
+        <v>6559838.31</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="61">
@@ -18601,7 +18601,7 @@
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>622130571.3</v>
+        <v>622281029.6</v>
       </c>
       <c r="E61" s="12" t="n">
         <v>11.48</v>
@@ -18627,7 +18627,7 @@
         <v>613298902.3</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>11.32</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="63">
@@ -18647,7 +18647,7 @@
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>412234740.22</v>
+        <v>412265001.24</v>
       </c>
       <c r="E63" s="12" t="n">
         <v>7.61</v>
@@ -18670,7 +18670,7 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>375591669.06</v>
+        <v>375702323.79</v>
       </c>
       <c r="E64" s="12" t="n">
         <v>6.93</v>
@@ -18693,7 +18693,7 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>282895761.37</v>
+        <v>282920761.37</v>
       </c>
       <c r="E65" s="12" t="n">
         <v>5.22</v>
@@ -18742,7 +18742,7 @@
         <v>238190400.29</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="68">
@@ -18762,7 +18762,7 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>199540439.32</v>
+        <v>199545419.32</v>
       </c>
       <c r="E68" s="12" t="n">
         <v>3.68</v>
@@ -18923,7 +18923,7 @@
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>134562015.2</v>
+        <v>134563486.7</v>
       </c>
       <c r="E75" s="12" t="n">
         <v>2.48</v>
@@ -18972,7 +18972,7 @@
         <v>122216962.45</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="78">
@@ -19015,10 +19015,10 @@
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>106535283.55</v>
+        <v>107735283.55</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="80">
@@ -19038,7 +19038,7 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>106417480.74</v>
+        <v>106467480.73</v>
       </c>
       <c r="E80" s="12" t="n">
         <v>1.96</v>
@@ -19176,7 +19176,7 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>88384512.84999999</v>
+        <v>88414512.84999999</v>
       </c>
       <c r="E86" s="12" t="n">
         <v>1.63</v>
@@ -19202,7 +19202,7 @@
         <v>88057920.31999999</v>
       </c>
       <c r="E87" s="12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="88">
@@ -19245,10 +19245,10 @@
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>826003852.21</v>
+        <v>829533418.9299999</v>
       </c>
       <c r="E89" s="12" t="n">
-        <v>26.04</v>
+        <v>26.06</v>
       </c>
     </row>
     <row r="90">
@@ -19268,10 +19268,10 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>203873157.36</v>
+        <v>204904970.51</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>6.43</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="91">
@@ -19291,10 +19291,10 @@
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>187674729.31</v>
+        <v>188185842.07</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>5.92</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="92">
@@ -19314,10 +19314,10 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>156351988.77</v>
+        <v>156434139.64</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4.93</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="93">
@@ -19337,10 +19337,10 @@
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>143718170.64</v>
+        <v>144022115.71</v>
       </c>
       <c r="E93" s="12" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="94">
@@ -19360,10 +19360,10 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>129822127.23</v>
+        <v>130362922.94</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="95">
@@ -19383,10 +19383,10 @@
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>126952208.92</v>
+        <v>127561515.78</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="96">
@@ -19406,10 +19406,10 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>118896945.02</v>
+        <v>119012354.72</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="97">
@@ -19429,10 +19429,10 @@
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>108567682.72</v>
+        <v>109796243.07</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="98">
@@ -19452,10 +19452,10 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>108474024.08</v>
+        <v>108667723.58</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="99">
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>96209682.41</v>
+        <v>96874485.12</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="100">
@@ -19498,10 +19498,10 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>93947507.66</v>
+        <v>93958450.43000001</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="101">
@@ -19521,7 +19521,7 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>87597105.36</v>
+        <v>87718083.37</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>2.76</v>
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>86176267.23999999</v>
+        <v>86453458.98999999</v>
       </c>
       <c r="E102" s="12" t="n">
         <v>2.72</v>
@@ -19567,10 +19567,10 @@
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>78719268.72</v>
+        <v>80007434.23</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="104">
@@ -19590,10 +19590,10 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>73512652.16</v>
+        <v>73565199.14</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="105">
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>70490467.59999999</v>
+        <v>70509757.59</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="106">
@@ -19636,10 +19636,10 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>60567880.04</v>
+        <v>60638114.54</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="107">
@@ -19659,7 +19659,7 @@
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>57992375.47</v>
+        <v>58173973.76</v>
       </c>
       <c r="E107" s="12" t="n">
         <v>1.83</v>
@@ -19682,7 +19682,7 @@
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>54082320.9</v>
+        <v>54169880</v>
       </c>
       <c r="E108" s="12" t="n">
         <v>1.7</v>
@@ -19705,7 +19705,7 @@
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>53978496.57</v>
+        <v>53975076.57</v>
       </c>
       <c r="E109" s="12" t="n">
         <v>1.7</v>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>51730364.17</v>
+        <v>51836828.47</v>
       </c>
       <c r="E110" s="12" t="n">
         <v>1.63</v>
@@ -19751,10 +19751,10 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>49088929.85</v>
+        <v>49147358.96</v>
       </c>
       <c r="E111" s="12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="112">
@@ -19774,10 +19774,10 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>47810880.66</v>
+        <v>47835270.66</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="113">
@@ -19797,7 +19797,7 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>37706072.69</v>
+        <v>37782697.73</v>
       </c>
       <c r="E113" s="12" t="n">
         <v>1.19</v>
@@ -19820,7 +19820,7 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>31679646.88</v>
+        <v>31734782.84</v>
       </c>
       <c r="E114" s="12" t="n">
         <v>1</v>
@@ -19846,7 +19846,7 @@
         <v>29064493.28</v>
       </c>
       <c r="E115" s="12" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="116">
@@ -19912,10 +19912,10 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>147573990.29</v>
+        <v>147716455.53</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>20.09</v>
+        <v>20.05</v>
       </c>
     </row>
     <row r="119">
@@ -19935,10 +19935,10 @@
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>57846735.76</v>
+        <v>58112431.09</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>7.88</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="120">
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>51841352.22</v>
+        <v>51897618.15</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>7.06</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="121">
@@ -19981,7 +19981,7 @@
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>50868591.02</v>
+        <v>51031603.3</v>
       </c>
       <c r="E121" s="12" t="n">
         <v>6.93</v>
@@ -20004,10 +20004,10 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>34915659.34</v>
+        <v>35265391.5</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>4.75</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="123">
@@ -20027,7 +20027,7 @@
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>33472930.43</v>
+        <v>33566820.41</v>
       </c>
       <c r="E123" s="12" t="n">
         <v>4.56</v>
@@ -20050,10 +20050,10 @@
         </is>
       </c>
       <c r="D124" s="6" t="n">
-        <v>31437670.23</v>
+        <v>31589761.8</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="125">
@@ -20073,10 +20073,10 @@
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>28206250.02</v>
+        <v>28464605.79</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="126">
@@ -20096,10 +20096,10 @@
         </is>
       </c>
       <c r="D126" s="6" t="n">
-        <v>23030946.25</v>
+        <v>23217207.53</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="127">
@@ -20119,7 +20119,7 @@
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>22637064.86</v>
+        <v>22667443.71</v>
       </c>
       <c r="E127" s="12" t="n">
         <v>3.08</v>
@@ -20142,10 +20142,10 @@
         </is>
       </c>
       <c r="D128" s="6" t="n">
-        <v>22168761.28</v>
+        <v>22199036.26</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="129">
@@ -20168,7 +20168,7 @@
         <v>21998322.88</v>
       </c>
       <c r="E129" s="12" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="130">
@@ -20188,7 +20188,7 @@
         </is>
       </c>
       <c r="D130" s="6" t="n">
-        <v>21892874.57</v>
+        <v>21928795.73</v>
       </c>
       <c r="E130" s="12" t="n">
         <v>2.98</v>
@@ -20211,10 +20211,10 @@
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>20558685.04</v>
+        <v>20680712.64</v>
       </c>
       <c r="E131" s="12" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="132">
@@ -20234,10 +20234,10 @@
         </is>
       </c>
       <c r="D132" s="6" t="n">
-        <v>19820402.55</v>
+        <v>19827758.8</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="133">
@@ -20257,7 +20257,7 @@
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>16535448.12</v>
+        <v>16552815.12</v>
       </c>
       <c r="E133" s="12" t="n">
         <v>2.25</v>
@@ -20280,7 +20280,7 @@
         </is>
       </c>
       <c r="D134" s="6" t="n">
-        <v>16270903.9</v>
+        <v>16333872.9</v>
       </c>
       <c r="E134" s="12" t="n">
         <v>2.22</v>
@@ -20326,10 +20326,10 @@
         </is>
       </c>
       <c r="D136" s="6" t="n">
-        <v>14974250.85</v>
+        <v>14986263.45</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="137">
@@ -20349,10 +20349,10 @@
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>14599052.6</v>
+        <v>14725867.1</v>
       </c>
       <c r="E137" s="12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -20372,10 +20372,10 @@
         </is>
       </c>
       <c r="D138" s="6" t="n">
-        <v>13629021.7</v>
+        <v>13629522.2</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="139">
@@ -20395,10 +20395,10 @@
         </is>
       </c>
       <c r="D139" s="6" t="n">
-        <v>10355475.59</v>
+        <v>10443438.75</v>
       </c>
       <c r="E139" s="12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="140">
@@ -20418,7 +20418,7 @@
         </is>
       </c>
       <c r="D140" s="6" t="n">
-        <v>9915138.689999999</v>
+        <v>9935348.689999999</v>
       </c>
       <c r="E140" s="12" t="n">
         <v>1.35</v>
@@ -20441,7 +20441,7 @@
         </is>
       </c>
       <c r="D141" s="6" t="n">
-        <v>9208910.65</v>
+        <v>9234250.68</v>
       </c>
       <c r="E141" s="12" t="n">
         <v>1.25</v>
@@ -20464,10 +20464,10 @@
         </is>
       </c>
       <c r="D142" s="6" t="n">
-        <v>8626908.92</v>
+        <v>8686908.92</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="143">
@@ -20487,7 +20487,7 @@
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>8356982.64</v>
+        <v>8365261.76</v>
       </c>
       <c r="E143" s="12" t="n">
         <v>1.14</v>
@@ -20510,7 +20510,7 @@
         </is>
       </c>
       <c r="D144" s="6" t="n">
-        <v>7778510.3</v>
+        <v>7780110.3</v>
       </c>
       <c r="E144" s="12" t="n">
         <v>1.06</v>
@@ -20533,10 +20533,10 @@
         </is>
       </c>
       <c r="D145" s="6" t="n">
-        <v>97510234.92</v>
+        <v>97718685.43000001</v>
       </c>
       <c r="E145" s="12" t="n">
-        <v>13.73</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="146">
@@ -20556,10 +20556,10 @@
         </is>
       </c>
       <c r="D146" s="6" t="n">
-        <v>79993260.81999999</v>
+        <v>80313354.70999999</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>11.26</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="147">
@@ -20582,7 +20582,7 @@
         <v>53079939.7</v>
       </c>
       <c r="E147" s="12" t="n">
-        <v>7.47</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="148">
@@ -20602,7 +20602,7 @@
         </is>
       </c>
       <c r="D148" s="6" t="n">
-        <v>38817828.78</v>
+        <v>39003369.97</v>
       </c>
       <c r="E148" s="12" t="n">
         <v>5.46</v>
@@ -20625,10 +20625,10 @@
         </is>
       </c>
       <c r="D149" s="6" t="n">
-        <v>38384306.24</v>
+        <v>38436187</v>
       </c>
       <c r="E149" s="12" t="n">
-        <v>5.4</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="150">
@@ -20648,10 +20648,10 @@
         </is>
       </c>
       <c r="D150" s="6" t="n">
-        <v>36989168.8</v>
+        <v>37050385.8</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>5.21</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="151">
@@ -20671,10 +20671,10 @@
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>35692971.86</v>
+        <v>35993371.86</v>
       </c>
       <c r="E151" s="12" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="152">
@@ -20694,10 +20694,10 @@
         </is>
       </c>
       <c r="D152" s="6" t="n">
-        <v>34739447.88</v>
+        <v>35024163.86</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>4.89</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="153">
@@ -20717,7 +20717,7 @@
         </is>
       </c>
       <c r="D153" s="6" t="n">
-        <v>27362684.15</v>
+        <v>27483937.32</v>
       </c>
       <c r="E153" s="12" t="n">
         <v>3.85</v>
@@ -20740,7 +20740,7 @@
         </is>
       </c>
       <c r="D154" s="6" t="n">
-        <v>27055232.47</v>
+        <v>27197930.85</v>
       </c>
       <c r="E154" s="12" t="n">
         <v>3.81</v>
@@ -20763,10 +20763,10 @@
         </is>
       </c>
       <c r="D155" s="6" t="n">
-        <v>25063408.81</v>
+        <v>25083438.81</v>
       </c>
       <c r="E155" s="12" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="156">
@@ -20786,10 +20786,10 @@
         </is>
       </c>
       <c r="D156" s="6" t="n">
-        <v>24471539.22</v>
+        <v>24712352.22</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="157">
@@ -20809,10 +20809,10 @@
         </is>
       </c>
       <c r="D157" s="6" t="n">
-        <v>22080737.92</v>
+        <v>22160786.19</v>
       </c>
       <c r="E157" s="12" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="158">
@@ -20832,10 +20832,10 @@
         </is>
       </c>
       <c r="D158" s="6" t="n">
-        <v>21114788.55</v>
+        <v>21242788.55</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="159">
@@ -20855,7 +20855,7 @@
         </is>
       </c>
       <c r="D159" s="6" t="n">
-        <v>20411805.62</v>
+        <v>20466197.66</v>
       </c>
       <c r="E159" s="12" t="n">
         <v>2.87</v>
@@ -20878,10 +20878,10 @@
         </is>
       </c>
       <c r="D160" s="6" t="n">
-        <v>17489725.09</v>
+        <v>18002988.2</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="161">
@@ -20901,10 +20901,10 @@
         </is>
       </c>
       <c r="D161" s="6" t="n">
-        <v>16275963.94</v>
+        <v>16289667.41</v>
       </c>
       <c r="E161" s="12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="162">
@@ -20924,10 +20924,10 @@
         </is>
       </c>
       <c r="D162" s="6" t="n">
-        <v>15665414.24</v>
+        <v>15694810.78</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="163">
@@ -20947,10 +20947,10 @@
         </is>
       </c>
       <c r="D163" s="6" t="n">
-        <v>13153963.75</v>
+        <v>13163963.75</v>
       </c>
       <c r="E163" s="12" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="164">
@@ -20961,19 +20961,19 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="D164" s="6" t="n">
-        <v>9904362.09</v>
+        <v>9976101.710000001</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="165">
@@ -20984,16 +20984,16 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="D165" s="6" t="n">
-        <v>9902927.949999999</v>
+        <v>9919901.4</v>
       </c>
       <c r="E165" s="12" t="n">
         <v>1.39</v>
@@ -21039,10 +21039,10 @@
         </is>
       </c>
       <c r="D167" s="6" t="n">
-        <v>7959537.14</v>
+        <v>8182957.14</v>
       </c>
       <c r="E167" s="12" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="168">
@@ -21062,7 +21062,7 @@
         </is>
       </c>
       <c r="D168" s="6" t="n">
-        <v>7824376.85</v>
+        <v>7847876.85</v>
       </c>
       <c r="E168" s="12" t="n">
         <v>1.1</v>
@@ -21085,10 +21085,10 @@
         </is>
       </c>
       <c r="D169" s="6" t="n">
-        <v>6563010.26</v>
+        <v>6891650.26</v>
       </c>
       <c r="E169" s="12" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="170">
@@ -21131,10 +21131,10 @@
         </is>
       </c>
       <c r="D171" s="6" t="n">
-        <v>4059112.44</v>
+        <v>4122494.49</v>
       </c>
       <c r="E171" s="12" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="172">
@@ -21154,7 +21154,7 @@
         </is>
       </c>
       <c r="D172" s="6" t="n">
-        <v>3929754.61</v>
+        <v>3936185.28</v>
       </c>
       <c r="E172" s="12" t="n">
         <v>0.55</v>
@@ -22451,21 +22451,21 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-15.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: a serie de fornecedores cobre 69.7% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
+          <t>Nota 1: a serie de fornecedores cobre 69.6% do valor contratado, que e' a parcela com UF conhecida na data desta extracao, e cresce a cada consulta de CNPJ.</t>
         </is>
       </c>
     </row>
@@ -22572,28 +22572,28 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>388445912.44</v>
+        <v>389930106.12</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>38896902.72</v>
+        <v>39146541.52</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>20334031.37</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>6082558.32</v>
+        <v>6298082.04</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>44979461.04</v>
+        <v>45444623.56</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>18.1</v>
+        <v>18.01</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>408779943.81</v>
+        <v>410264137.49</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>15.76</v>
+        <v>15.67</v>
       </c>
     </row>
     <row r="6">
@@ -22603,28 +22603,28 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>532795363.15</v>
+        <v>537179909.95</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>34419100.39</v>
+        <v>35387943.94</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>7837843.22</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>9214674.949999999</v>
+        <v>9324262.949999999</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>43633775.34</v>
+        <v>44712206.89</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>17.56</v>
+        <v>17.72</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>540633206.37</v>
+        <v>545017753.1700001</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>20.84</v>
+        <v>20.81</v>
       </c>
     </row>
     <row r="7">
@@ -22634,10 +22634,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>266336338.73</v>
+        <v>267960850.64</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>28371248.06</v>
+        <v>28826108.06</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>328650</v>
@@ -22646,16 +22646,16 @@
         <v>227830.33</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>28599078.39</v>
+        <v>29053938.39</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>11.51</v>
+        <v>11.52</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>266664988.73</v>
+        <v>268289500.64</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>10.28</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="8">
@@ -22665,7 +22665,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>148591951.68</v>
+        <v>151878001.68</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>5592253.95</v>
@@ -22680,13 +22680,13 @@
         <v>21793852.19</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>8.77</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>159120859.55</v>
+        <v>162406909.55</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6.13</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="9">
@@ -22696,10 +22696,10 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>239309878.39</v>
+        <v>244149667.53</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>19685470.77</v>
+        <v>20218326.28</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>1061795.06</v>
@@ -22708,16 +22708,16 @@
         <v>310317.66</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>19995788.43</v>
+        <v>20528643.94</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>8.050000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>240371673.45</v>
+        <v>245211462.59</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>9.27</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -22727,28 +22727,28 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>118513944.53</v>
+        <v>119151543.62</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>9211407.710000001</v>
+        <v>9223407.710000001</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>13493262.57</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>9563476.6</v>
+        <v>9765476.6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>18774884.31</v>
+        <v>18988884.31</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>7.56</v>
+        <v>7.53</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>132007207.1</v>
+        <v>132644806.19</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>5.09</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="11">
@@ -22758,10 +22758,10 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>228333658.65</v>
+        <v>231094372.88</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>16858427.27</v>
+        <v>17146680.77</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>1405640</v>
@@ -22770,16 +22770,16 @@
         <v>758113.3</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>17616540.57</v>
+        <v>17904794.07</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>7.09</v>
+        <v>7.1</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>229739298.65</v>
+        <v>232500012.88</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>8.859999999999999</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -22789,28 +22789,28 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>161115293.71</v>
+        <v>161941581.31</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>7098827.73</v>
+        <v>7196028.73</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2161173.45</v>
+        <v>2188283.45</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>2248827.43</v>
+        <v>2498200.63</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>9347655.16</v>
+        <v>9694229.359999999</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>163276467.16</v>
+        <v>164129864.76</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>6.29</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="13">
@@ -22820,28 +22820,28 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>66730216.97</v>
+        <v>67218901.97</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>3779114.24</v>
+        <v>3811451.56</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>12310674.22</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5493512.35</v>
+        <v>5497512.35</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>9272626.59</v>
+        <v>9308963.91</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>79040891.19</v>
+        <v>79529576.19</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="14">
@@ -22851,10 +22851,10 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>54632858.36</v>
+        <v>55168467.31</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2458966.12</v>
+        <v>2496902.12</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>752452.6</v>
@@ -22863,13 +22863,13 @@
         <v>3675202.61</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>6134168.73</v>
+        <v>6172104.73</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>55385310.96</v>
+        <v>55920919.91</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>2.14</v>
@@ -22882,10 +22882,10 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>84329192.36</v>
+        <v>85781414.08</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>4200899.32</v>
+        <v>4281117.18</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>53190</v>
@@ -22894,16 +22894,16 @@
         <v>1029012.7</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>5229912.02</v>
+        <v>5310129.88</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>84382382.36</v>
+        <v>85834604.08</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="16">
@@ -22913,10 +22913,10 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>27625286.95</v>
+        <v>28003028.17</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2990569.31</v>
+        <v>2992069.31</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>527134.87</v>
@@ -22925,13 +22925,13 @@
         <v>1602466.95</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>4593036.26</v>
+        <v>4594536.26</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>28152421.82</v>
+        <v>28530163.04</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>1.09</v>
@@ -22944,10 +22944,10 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>38206539.17</v>
+        <v>38522045.68</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>2793733.78</v>
+        <v>2808233.78</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>214985.86</v>
@@ -22956,13 +22956,13 @@
         <v>665907.63</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>3459641.41</v>
+        <v>3474141.41</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>38421525.03</v>
+        <v>38737031.54</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>1.48</v>
@@ -22990,7 +22990,7 @@
         <v>2697521</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>15155497.9</v>
@@ -23006,10 +23006,10 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>27639518.39</v>
+        <v>28069504.38</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>1824937.17</v>
+        <v>1891549.26</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>25327.5</v>
@@ -23018,13 +23018,13 @@
         <v>286176.1</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2111113.27</v>
+        <v>2177725.36</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>27664845.89</v>
+        <v>28094831.88</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>1.07</v>
@@ -23037,10 +23037,10 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>20445094.66</v>
+        <v>20522159.66</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1013132.07</v>
+        <v>1016432.07</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>127520</v>
@@ -23049,13 +23049,13 @@
         <v>544826.95</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1557959.02</v>
+        <v>1561259.02</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>20572614.66</v>
+        <v>20649679.66</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0.79</v>
@@ -23068,7 +23068,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>12009433.23</v>
+        <v>12527055.62</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>1236127.11</v>
@@ -23083,13 +23083,13 @@
         <v>1438691.6</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>12123350.21</v>
+        <v>12640972.6</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="22">
@@ -23099,10 +23099,10 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>10786154.3</v>
+        <v>10903869.18</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1163711.39</v>
+        <v>1181949.89</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>206000</v>
@@ -23111,13 +23111,13 @@
         <v>120500</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1284211.39</v>
+        <v>1302449.89</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0.52</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>10992154.3</v>
+        <v>11109869.18</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0.42</v>
@@ -23130,10 +23130,10 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>14820956.02</v>
+        <v>15153731.7</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>863387.63</v>
+        <v>992687.63</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>933850</v>
@@ -23142,13 +23142,13 @@
         <v>110000</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>973387.63</v>
+        <v>1102687.63</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>15754806.02</v>
+        <v>16087581.7</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0.61</v>
@@ -23161,10 +23161,10 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>13920301.41</v>
+        <v>14057978.97</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>954256.42</v>
+        <v>956756.42</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>56000</v>
@@ -23173,13 +23173,13 @@
         <v>18500</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>972756.42</v>
+        <v>975256.42</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>0.39</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>13976301.41</v>
+        <v>14113978.97</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0.54</v>
@@ -23192,10 +23192,10 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>6162857.09</v>
+        <v>6190715.09</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>777512.3099999999</v>
+        <v>781202.51</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>0</v>
@@ -23204,13 +23204,13 @@
         <v>420</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>777932.3099999999</v>
+        <v>781622.51</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>0.31</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>6162857.09</v>
+        <v>6190715.09</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0.24</v>
@@ -23219,63 +23219,63 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Correspondências e despesas postais</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>7443749.61</v>
+        <v>14849657.63</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>600987.22</v>
+        <v>777003.91</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>22074.32</v>
+        <v>8104.55</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>128501.95</v>
+        <v>0</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>729489.1699999999</v>
+        <v>777003.91</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>7465823.930000001</v>
+        <v>14857762.18</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.29</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Correspondências e despesas postais</t>
+          <t>Alimentação</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>14806633.51</v>
+        <v>7556689.75</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>704588.0600000001</v>
+        <v>612923.58</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>8104.55</v>
+        <v>22074.32</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0</v>
+        <v>128501.95</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>704588.0600000001</v>
+        <v>741425.5299999999</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>14814738.06</v>
+        <v>7578764.07</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.57</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="28">
@@ -23285,10 +23285,10 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>9122954.050000001</v>
+        <v>9151428.59</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>336862.09</v>
+        <v>336902.09</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>0</v>
@@ -23297,13 +23297,13 @@
         <v>151786.7</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>488648.79</v>
+        <v>488688.79</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>9122954.050000001</v>
+        <v>9151428.59</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0.35</v>
@@ -23316,10 +23316,10 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>2666919.12</v>
+        <v>2676140.92</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>267059.74</v>
+        <v>267094.24</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>9126.799999999999</v>
@@ -23328,13 +23328,13 @@
         <v>99566.78999999999</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>366626.53</v>
+        <v>366661.03</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>0.15</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>2676045.92</v>
+        <v>2685267.72</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0.1</v>
@@ -23409,10 +23409,10 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>899739.25</v>
+        <v>904471.95</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>85143.32000000001</v>
+        <v>86413.32000000001</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>18616.5</v>
@@ -23421,13 +23421,13 @@
         <v>24308.68</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>109452</v>
+        <v>110722</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>0.04</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>918355.75</v>
+        <v>923088.45</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0.04</v>
@@ -23440,7 +23440,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>1440911.61</v>
+        <v>1445528.16</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>58664.51</v>
@@ -23458,7 +23458,7 @@
         <v>0.04</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1440911.61</v>
+        <v>1445528.16</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0.06</v>
@@ -23502,7 +23502,7 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>83753.74000000001</v>
+        <v>84271.81</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>1130.2</v>
@@ -23520,7 +23520,7 @@
         <v>0.02</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>135498.63</v>
+        <v>136016.7</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0.01</v>
@@ -23533,25 +23533,25 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>439627.23</v>
+        <v>450487.41</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>26628.12</v>
+        <v>26914.43</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>99823.97</v>
+        <v>100449.84</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>13788.9</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>40417.02</v>
+        <v>40703.33</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>539451.2</v>
+        <v>550937.25</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0.02</v>
@@ -23564,7 +23564,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>431882.91</v>
+        <v>361172.71</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>20610.5</v>
@@ -23582,10 +23582,10 @@
         <v>0.01</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>433431.58</v>
+        <v>362721.38</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="38">
@@ -23601,7 +23601,7 @@
         <v>2750.04</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>33020.00999999999</v>
+        <v>33020.01</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>25183.19</v>
@@ -23719,10 +23719,10 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>9868.549999999999</v>
+        <v>9869.049999999999</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D42" s="6" t="n">
         <v>0</v>
@@ -23731,13 +23731,13 @@
         <v>0</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>9868.549999999999</v>
+        <v>9869.049999999999</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
@@ -23777,14 +23777,14 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-15.</t>
         </is>
       </c>
     </row>
@@ -23825,11 +23825,11 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="44" customWidth="1" min="14" max="14"/>
@@ -23937,34 +23937,34 @@
         <v>5281805806.47</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1412353509.95</v>
+        <v>1413776054.28</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>19.34</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1024611550.1</v>
+        <v>1024813021.59</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>18.91</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>150909665.82</v>
+        <v>151203289.93</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>23.9</v>
+        <v>23.92</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>22078270.52</v>
+        <v>22416742.52</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>142029564.22</v>
+        <v>142614793.95</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>1081239815</v>
+        <v>1086105368.92</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>83.23</v>
+        <v>83.18000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -23983,16 +23983,16 @@
         <v>788542541.16</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1058987664.58</v>
+        <v>1060582328.58</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>14.5</v>
+        <v>14.51</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>920820959.12</v>
+        <v>922036459.12</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>16.99</v>
+        <v>17.01</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>6176134.65</v>
@@ -24001,16 +24001,16 @@
         <v>0.98</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>12280078.79</v>
+        <v>12304578.6</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>85214022.03</v>
+        <v>85545118.22</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>700321839.36</v>
+        <v>703085615.05</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>87.54000000000001</v>
+        <v>87.52</v>
       </c>
     </row>
     <row r="7">
@@ -24029,10 +24029,10 @@
         <v>1819943318.34</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>669290913.9400001</v>
+        <v>669850325.22</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>9.17</v>
+        <v>9.16</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>536659271.9</v>
@@ -24041,22 +24041,22 @@
         <v>9.9</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>75709738.73999999</v>
+        <v>75858680.52</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>11.99</v>
+        <v>12</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>8146956.06</v>
+        <v>8281262.19</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>29670677.53</v>
+        <v>29808686.9</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>475094185.84</v>
+        <v>475884693.06</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>91.5</v>
+        <v>91.44</v>
       </c>
     </row>
     <row r="8">
@@ -24075,13 +24075,13 @@
         <v>2577905190.84</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>655828920.45</v>
+        <v>656146458.72</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>8.98</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>448666803.71</v>
+        <v>448681803.71</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>8.279999999999999</v>
@@ -24093,16 +24093,16 @@
         <v>5.48</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>18938430.73</v>
+        <v>19103480.73</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>85021165.52</v>
+        <v>85128480.59</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>513472976.49</v>
+        <v>514768882.62</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>73.69</v>
+        <v>73.66</v>
       </c>
     </row>
     <row r="9">
@@ -24121,7 +24121,7 @@
         <v>2779509683.8</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>606328460.38</v>
+        <v>606632208.83</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>8.300000000000001</v>
@@ -24133,22 +24133,22 @@
         <v>6.85</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>126709839.39</v>
+        <v>126722570.76</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>20.07</v>
+        <v>20.05</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>11955348.21</v>
+        <v>11984849.21</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>63735678.14</v>
+        <v>63890149.31</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>426512725.79</v>
+        <v>427358264.32</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>82.09</v>
+        <v>82.05</v>
       </c>
     </row>
     <row r="10">
@@ -24167,10 +24167,10 @@
         <v>1297502449.57</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>576657426.78</v>
+        <v>576844006.83</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7.9</v>
+        <v>7.89</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>446516289.17</v>
@@ -24179,22 +24179,22 @@
         <v>8.24</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>74209455</v>
+        <v>74245455</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>11.75</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>8066939.64</v>
+        <v>8163972.08</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>30539207.21</v>
+        <v>30579149.38</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>363056568.82</v>
+        <v>365179065.72</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>90.3</v>
+        <v>90.28</v>
       </c>
     </row>
     <row r="11">
@@ -24213,7 +24213,7 @@
         <v>3431895006.71</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>537330031.36</v>
+        <v>538110397.7</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>7.36</v>
@@ -24222,25 +24222,25 @@
         <v>407807248.96</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>7.53</v>
+        <v>7.52</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>17652075.52</v>
+        <v>17656542.34</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>15049687.49</v>
+        <v>15114290.24</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>68002242.39</v>
+        <v>68628368.97</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>358144512.44</v>
+        <v>359323801</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>79.18000000000001</v>
+        <v>79.06999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -24259,7 +24259,7 @@
         <v>1812875005.9</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>296299367.62</v>
+        <v>296602895.22</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>4.06</v>
@@ -24268,25 +24268,25 @@
         <v>238186413.63</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5680836.810000001</v>
+        <v>5685501.33</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>0.9</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>10301475.45</v>
+        <v>10352171.45</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>32015291.76</v>
+        <v>32199848.84</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>194039246.59</v>
+        <v>196955816.44</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>82.3</v>
+        <v>82.22</v>
       </c>
     </row>
     <row r="13">
@@ -24305,7 +24305,7 @@
         <v>1457794419.27</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>230837653.51</v>
+        <v>230984307.78</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>3.16</v>
@@ -24317,22 +24317,22 @@
         <v>3.08</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>46890710.35</v>
+        <v>46909124.75</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>7.43</v>
+        <v>7.42</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>2944615.78</v>
+        <v>2971655.13</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>9996352.189999999</v>
+        <v>10074952.71</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>152983175.21</v>
+        <v>153491503.42</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>92.72</v>
+        <v>92.67</v>
       </c>
     </row>
     <row r="14">
@@ -24351,13 +24351,13 @@
         <v>941728196.61</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>222531253.45</v>
+        <v>222860869.79</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>3.05</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>148497258.38</v>
+        <v>148532548.4</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>2.74</v>
@@ -24369,16 +24369,16 @@
         <v>1.06</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>10905584.29</v>
+        <v>11064396.82</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>36440614.96</v>
+        <v>36522867.5</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>172613146.16</v>
+        <v>173478904.89</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>69.75</v>
+        <v>69.66</v>
       </c>
     </row>
     <row r="15">
@@ -24397,13 +24397,13 @@
         <v>2591694177.84</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>210668930.63</v>
+        <v>211211399.13</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>2.89</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>150342927.09</v>
+        <v>150372927.09</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>2.77</v>
@@ -24415,16 +24415,16 @@
         <v>0.71</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>11739127.87</v>
+        <v>11793159.93</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>31959608.98</v>
+        <v>32379138.19</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>144991030.17</v>
+        <v>145325286.01</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>73.48</v>
+        <v>73.31</v>
       </c>
     </row>
     <row r="16">
@@ -24443,34 +24443,34 @@
         <v>1884208841.62</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>144355225.43</v>
+        <v>144440245.46</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>1.98</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>34400279.06</v>
+        <v>34400765.53</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0.63</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>44449677.11</v>
+        <v>44459677.11</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>7.04</v>
+        <v>7.03</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>7330390.21</v>
+        <v>7331199.03</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>27137480.32</v>
+        <v>27199855.06</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>90574628.17</v>
+        <v>90691132.23</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>54.62</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="17">
@@ -24489,13 +24489,13 @@
         <v>139488473.87</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>135574307.88</v>
+        <v>135624564.31</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>1.86</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>124016282.12</v>
+        <v>124041740.42</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>2.29</v>
@@ -24507,16 +24507,16 @@
         <v>0.31</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>830911.21</v>
+        <v>836322.0800000001</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>4176262.37</v>
+        <v>4195529.63</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>89965893.28</v>
+        <v>90138979.39</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>92.92</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -24535,7 +24535,7 @@
         <v>1072776812.99</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>99495630.70999999</v>
+        <v>99660587.70999999</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>1.36</v>
@@ -24547,22 +24547,22 @@
         <v>1.21</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>13874711.38</v>
+        <v>13887392.18</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>4906934.439999999</v>
+        <v>4906960.64</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>12858174.3</v>
+        <v>13010024.3</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>61163750.13</v>
+        <v>61462737.03</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>79.72</v>
+        <v>79.61</v>
       </c>
     </row>
     <row r="19">
@@ -24581,7 +24581,7 @@
         <v>577531754.64</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>97563707.88</v>
+        <v>97835344.19</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>1.34</v>
@@ -24599,16 +24599,16 @@
         <v>2.24</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>3464096.82</v>
+        <v>3535138.7</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>9223157.119999999</v>
+        <v>9423751.550000001</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>61002363.11</v>
+        <v>61873197.67</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>83.78</v>
+        <v>83.55</v>
       </c>
     </row>
     <row r="20">
@@ -24627,7 +24627,7 @@
         <v>280452197.14</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>92082831.40000001</v>
+        <v>92105331.40000001</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>1.26</v>
@@ -24648,13 +24648,13 @@
         <v>1869153.42</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>3850128.57</v>
+        <v>3872628.57</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>53163810.58</v>
+        <v>53407620.2</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>92.84</v>
+        <v>92.81999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -24673,7 +24673,7 @@
         <v>81485614.53</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>73514593.78</v>
+        <v>73534843.78</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>1.01</v>
@@ -24691,16 +24691,16 @@
         <v>0.71</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>1309270.67</v>
+        <v>1319520.67</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4081773.41</v>
+        <v>4091773.41</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>49464097.13</v>
+        <v>49476626.77</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>88.20999999999999</v>
+        <v>88.19</v>
       </c>
     </row>
     <row r="22">
@@ -24719,7 +24719,7 @@
         <v>330099422.77</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>60383921.48</v>
+        <v>60717930.68</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>0.83</v>
@@ -24737,16 +24737,16 @@
         <v>0.03</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>3471243.36</v>
+        <v>3559206.52</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>11188575.11</v>
+        <v>11434621.15</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>44093323.13</v>
+        <v>44103202.63</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>71.70999999999999</v>
+        <v>71.31999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -24765,13 +24765,13 @@
         <v>121249861.96</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>36803005</v>
+        <v>36889644.26</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>33750157.45</v>
+        <v>33814796.71</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>0.62</v>
@@ -24786,13 +24786,13 @@
         <v>564325.3300000001</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>1056669.75</v>
+        <v>1078669.75</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>11389767.54</v>
+        <v>11646528.38</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>93.04000000000001</v>
+        <v>92.98999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -24811,13 +24811,13 @@
         <v>587079065.02</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>33939373.27</v>
+        <v>33949373.27</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>0.46</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>29553402.63</v>
+        <v>29563402.63</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0.55</v>
@@ -24835,10 +24835,10 @@
         <v>2596259.84</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>19795689.57</v>
+        <v>19807289.57</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>88.29000000000001</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="25">
@@ -24903,7 +24903,7 @@
         <v>243522021.57</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>10199298.73</v>
+        <v>10209978.73</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>0.14</v>
@@ -24924,13 +24924,13 @@
         <v>1858924.47</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>5557299.7</v>
+        <v>5567749.7</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>8521015.1</v>
+        <v>8523045.5</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>22.87</v>
+        <v>22.85</v>
       </c>
     </row>
     <row r="27">
@@ -24995,7 +24995,7 @@
         <v>652170016.89</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>6265644.37</v>
+        <v>6268223.95</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>0.09</v>
@@ -25013,16 +25013,16 @@
         <v>0.01</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>1066913.03</v>
+        <v>1069015.03</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>1928540.3</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>3491296.03</v>
+        <v>3491396.03</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>47.03</v>
+        <v>47.01</v>
       </c>
     </row>
     <row r="29">
@@ -25041,7 +25041,7 @@
         <v>463597846.48</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>5230812.98</v>
+        <v>5249641.68</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -25059,13 +25059,13 @@
         <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>2229278.14</v>
+        <v>2229573.14</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>2063883.58</v>
+        <v>2066454.58</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>3344627.08</v>
+        <v>3349847.28</v>
       </c>
       <c r="N29" s="6" t="n">
         <v>0.11</v>
@@ -25133,13 +25133,13 @@
         <v>16313701.99</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>1928912.59</v>
+        <v>1933892.59</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>0.03</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>1309641.22</v>
+        <v>1314621.22</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>0.02</v>
@@ -25157,10 +25157,10 @@
         <v>248774.65</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>1115934.21</v>
+        <v>1117774.21</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>67.90000000000001</v>
+        <v>67.98</v>
       </c>
     </row>
     <row r="32">
@@ -25225,7 +25225,7 @@
         <v>4118169.08</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>85797.08</v>
+        <v>90997.08</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>0</v>
@@ -25246,7 +25246,7 @@
         <v>5000</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>26960</v>
+        <v>32160</v>
       </c>
       <c r="M33" s="6" t="n">
         <v>76920.81</v>
@@ -25304,14 +25304,14 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-15.</t>
         </is>
       </c>
     </row>
@@ -26493,10 +26493,10 @@
         <v>6500</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>1110756.58</v>
+        <v>1111183.35</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>626408.9400000001</v>
+        <v>1103683.35</v>
       </c>
     </row>
     <row r="24">
@@ -27327,7 +27327,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>LUIZ PAULO</t>
+          <t>ROBERTO ANDRADE</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -27342,11 +27342,11 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PRD</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>983700</v>
+        <v>987164.62</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>0.01</v>
@@ -27358,31 +27358,31 @@
         <v>0</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>258700</v>
+        <v>947863.7</v>
       </c>
       <c r="J39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>725000</v>
+        <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0</v>
+        <v>39300.92</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>1000</v>
+        <v>59700.92</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1012061.25</v>
+        <v>664649.09</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>270671.82</v>
+        <v>607606.6899999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>ROBERTO ANDRADE</t>
+          <t>LUIZ PAULO</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -27397,11 +27397,11 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>PRD</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>975831.29</v>
+        <v>983700</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>0.01</v>
@@ -27413,25 +27413,25 @@
         <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>936530.37</v>
+        <v>258700</v>
       </c>
       <c r="J40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0</v>
+        <v>725000</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>39300.92</v>
+        <v>0</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>56700.92</v>
+        <v>1000</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>549049.09</v>
+        <v>1012061.25</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>331063.4</v>
+        <v>270671.82</v>
       </c>
     </row>
     <row r="41">
@@ -27987,7 +27987,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>JOÃO COBALCHINI</t>
+          <t>LUCAS BARBOSA</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -27997,28 +27997,28 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>852350</v>
+        <v>853800</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>0</v>
+        <v>11.71</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>296200</v>
+        <v>753800</v>
       </c>
       <c r="J51" s="6" t="n">
         <v>0</v>
@@ -28027,22 +28027,22 @@
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>556150</v>
+        <v>0</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>356150</v>
+        <v>78000</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>319316.41</v>
+        <v>1216862.94</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>48430.41</v>
+        <v>630924.9400000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>TOM É MEU AMIGO</t>
+          <t>JOÃO COBALCHINI</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -28052,16 +28052,16 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>845000</v>
+        <v>852350</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>0.01</v>
@@ -28073,7 +28073,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>845000</v>
+        <v>296200</v>
       </c>
       <c r="J52" s="6" t="n">
         <v>0</v>
@@ -28082,22 +28082,22 @@
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>0</v>
+        <v>556150</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0</v>
+        <v>356150</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>854998.4</v>
+        <v>319316.41</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>819286.5</v>
+        <v>48430.41</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>ALEX CANZIANI</t>
+          <t>TOM É MEU AMIGO</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -28107,52 +28107,52 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>844637</v>
+        <v>845000</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>0.01</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>86000</v>
+        <v>0</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>10.18</v>
+        <v>0</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>367000</v>
+        <v>845000</v>
       </c>
       <c r="J53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>390837</v>
+        <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>254330</v>
+        <v>854998.4</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0</v>
+        <v>819286.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>FERNANDA PEREIRA ALTOÉ</t>
+          <t>ALEX CANZIANI</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -28162,80 +28162,80 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>832223.74</v>
+        <v>844637</v>
       </c>
       <c r="F54" s="9" t="n">
         <v>0.01</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>3500</v>
+        <v>86000</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.42</v>
+        <v>10.18</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>301123.3</v>
+        <v>367000</v>
       </c>
       <c r="J54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>527600.4399999999</v>
+        <v>390837</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="M54" s="9" t="n">
-        <v>70100.44</v>
+        <v>800</v>
       </c>
       <c r="N54" s="9" t="n">
-        <v>607160.39</v>
+        <v>254330</v>
       </c>
       <c r="O54" s="9" t="n">
-        <v>565160.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-14 16:19:51.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-15.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Nota 1: sao 2217 candidaturas com receita declarada e sem um real dos dois fundos publicos. que somam R$ 224.545.761,35 de receita.</t>
+          <t>Nota 1: sao 2229 candidaturas com receita declarada e sem um real dos dois fundos publicos. que somam R$ 225.479.019,09 de receita.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Nota 2: outras 4125 candidaturas NAO declararam receita alguma, das quais 960 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
+          <t>Nota 2: outras 4107 candidaturas NAO declararam receita alguma, das quais 960 sao vice ou suplente, que nao prestam conta propria. Ausencia de declaracao nao e' autofinanciamento, e por isso elas ficam fora desta tabela.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Nota 3: destas, 1254 nao receberam recurso partidario de especie alguma, nem mesmo fora dos dois fundos.</t>
+          <t>Nota 3: destas, 1255 nao receberam recurso partidario de especie alguma, nem mesmo fora dos dois fundos.</t>
         </is>
       </c>
     </row>
@@ -28383,13 +28383,13 @@
         <v>7.71</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>941352416.62</v>
+        <v>941863602.37</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>20.38</v>
+        <v>20.4</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>27.6</v>
+        <v>27.62</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>22.59</v>
@@ -28426,13 +28426,13 @@
         <v>11.18</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>540061272.24</v>
+        <v>540734381.52</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>25.17</v>
+        <v>25.2</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>32.97</v>
+        <v>33.01</v>
       </c>
       <c r="M6" s="6" t="n">
         <v>24.91</v>
@@ -28469,13 +28469,13 @@
         <v>15.98</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>501738323.89</v>
+        <v>501949079.58</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>29.13</v>
+        <v>29.14</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>39.02</v>
+        <v>39.04</v>
       </c>
       <c r="M7" s="6" t="n">
         <v>34.24</v>
@@ -28512,13 +28512,13 @@
         <v>10.81</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>348382819.68</v>
+        <v>348809893.96</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>23.4</v>
+        <v>23.43</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>30.77</v>
+        <v>30.81</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>26.94</v>
@@ -28555,13 +28555,13 @@
         <v>12.66</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>347809594.83</v>
+        <v>348269323.09</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>29.1</v>
+        <v>29.14</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>40.4</v>
+        <v>40.45</v>
       </c>
       <c r="M9" s="6" t="n">
         <v>31.82</v>
@@ -28598,13 +28598,13 @@
         <v>12.36</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>319875531.57</v>
+        <v>320180921.52</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>28.48</v>
+        <v>28.5</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>37.52</v>
+        <v>37.55</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>31.29</v>
@@ -28641,13 +28641,13 @@
         <v>13.3</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>260673741.06</v>
+        <v>260758408.08</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>27.2</v>
+        <v>27.21</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>36.07</v>
+        <v>36.08</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>30.54</v>
@@ -28684,13 +28684,13 @@
         <v>10.2</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>248641151.84</v>
+        <v>248829183.34</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>26.73</v>
+        <v>26.75</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>35.52</v>
+        <v>35.54</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>28.59</v>
@@ -28727,13 +28727,13 @@
         <v>11.82</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>191797404.38</v>
+        <v>192361636.49</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>21.9</v>
+        <v>21.97</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>30.6</v>
+        <v>30.69</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>25.82</v>
@@ -28770,13 +28770,13 @@
         <v>12.22</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>216778997.14</v>
+        <v>217166956.08</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>26.08</v>
+        <v>26.12</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>37.86</v>
+        <v>37.93</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>28.57</v>
@@ -28813,13 +28813,13 @@
         <v>11.93</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>223955484.48</v>
+        <v>224083484.48</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>31.88</v>
+        <v>31.9</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>43.17</v>
+        <v>43.19</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>36.54</v>
@@ -28856,16 +28856,16 @@
         <v>17.83</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>233323038.34</v>
+        <v>233931458.5</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>31.13</v>
+        <v>31.21</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>45.92</v>
+        <v>46.04</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>34.39</v>
+        <v>34.43</v>
       </c>
     </row>
     <row r="17">
@@ -28899,13 +28899,13 @@
         <v>13.85</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>149734962.6</v>
+        <v>149765818.85</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>35.8</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>46.1</v>
+        <v>46.11</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>40.78</v>
@@ -28942,13 +28942,13 @@
         <v>20.16</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>176762535.6</v>
+        <v>176872010.23</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>42.59</v>
+        <v>42.61</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>59.11</v>
+        <v>59.14</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>48.66</v>
@@ -28985,7 +28985,7 @@
         <v>17.38</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>189645533.43</v>
+        <v>189655533.43</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>43.49</v>
@@ -29028,13 +29028,13 @@
         <v>14.84</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>145383532.58</v>
+        <v>145500892.28</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>42.85</v>
+        <v>42.89</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>53.67</v>
+        <v>53.72</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>44.08</v>
@@ -29071,16 +29071,16 @@
         <v>12.85</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>135383050.09</v>
+        <v>136913290.09</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>39.09</v>
+        <v>39.53</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>50.88</v>
+        <v>51.45</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>45.56</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="22">
@@ -29114,16 +29114,16 @@
         <v>17.24</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>162812264.63</v>
+        <v>163121695.8</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>41.21</v>
+        <v>41.29</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>61.69</v>
+        <v>61.81</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>36.39</v>
+        <v>36.41</v>
       </c>
     </row>
     <row r="23">
@@ -29157,13 +29157,13 @@
         <v>12.24</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>116715353.72</v>
+        <v>116947052.84</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>36.23</v>
+        <v>36.31</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>47.79</v>
+        <v>47.88</v>
       </c>
       <c r="M23" s="6" t="n">
         <v>42.42</v>
@@ -29200,13 +29200,13 @@
         <v>30.18</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>206867725.89</v>
+        <v>206920736.24</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>68.73</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>91.81</v>
+        <v>91.83</v>
       </c>
       <c r="M24" s="6" t="n">
         <v>73.26000000000001</v>
@@ -29243,13 +29243,13 @@
         <v>20.99</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>118181676.81</v>
+        <v>118199043.81</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>40.11</v>
+        <v>40.12</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>58.36</v>
+        <v>58.37</v>
       </c>
       <c r="M25" s="6" t="n">
         <v>47.37</v>
@@ -29286,13 +29286,13 @@
         <v>23.62</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>123176777.67</v>
+        <v>123217657.01</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>53.39</v>
+        <v>53.4</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>70.78</v>
+        <v>70.8</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>63.36</v>
@@ -29329,16 +29329,16 @@
         <v>34.52</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>147135522.01</v>
+        <v>147279582.87</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>83.73</v>
+        <v>83.81</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>115.98</v>
+        <v>116.09</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>90.37</v>
+        <v>90.41</v>
       </c>
     </row>
     <row r="28">
@@ -29372,16 +29372,16 @@
         <v>31.11</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>121115288.53</v>
+        <v>121396489.89</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>75.89</v>
+        <v>76.06</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>102.4</v>
+        <v>102.64</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>84.14</v>
+        <v>84.27</v>
       </c>
     </row>
     <row r="29">
@@ -29415,13 +29415,13 @@
         <v>65.08</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>134862023.11</v>
+        <v>134882233.11</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>151.91</v>
+        <v>151.93</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>219.42</v>
+        <v>219.45</v>
       </c>
       <c r="M29" s="6" t="n">
         <v>202.55</v>
@@ -29458,13 +29458,13 @@
         <v>55.74</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>116096217.41</v>
+        <v>116160099.96</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>143.34</v>
+        <v>143.42</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>200.96</v>
+        <v>201.07</v>
       </c>
       <c r="M30" s="6" t="n">
         <v>188.36</v>
@@ -29501,16 +29501,16 @@
         <v>102.85</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>105927597.84</v>
+        <v>105994028.51</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>139.19</v>
+        <v>139.28</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>263.78</v>
+        <v>263.95</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>246.04</v>
+        <v>246.19</v>
       </c>
     </row>
     <row r="32">
@@ -29605,16 +29605,16 @@
         <v>13.34</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>7301710788.279999</v>
+        <v>7309285444.22</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>34.09</v>
+        <v>34.12</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>46.26</v>
+        <v>46.31</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>38.33</v>
+        <v>38.34</v>
       </c>
     </row>
     <row r="34">
@@ -29627,7 +29627,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-14.</t>
+          <t>Nota: a prestacao de contas eleitoral e' PARCIAL e e' atualizada diariamente pelo TSE. Ultima data de prestacao presente na base: 2026-10-15.</t>
         </is>
       </c>
     </row>

--- a/dados/TABELAS-IBGE-ABNT-2026.xlsx
+++ b/dados/TABELAS-IBGE-ABNT-2026.xlsx
@@ -581,7 +581,7 @@
         <v>4495080252.41</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>13.66</v>
+        <v>13.64</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>923439500.0599999</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>0</v>
@@ -637,7 +637,7 @@
         <v>433</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>338296381.14</v>
@@ -649,13 +649,13 @@
         <v>47902742.53</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>33142536.24</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="8">
@@ -668,25 +668,25 @@
         <v>11295</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>53.63</v>
+        <v>53.6</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>12007434756.34</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>36.5</v>
+        <v>36.43</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>1795036958.61</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>24.56</v>
+        <v>24.41</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>1185992166.35</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>23.17</v>
+        <v>23.03</v>
       </c>
     </row>
     <row r="9">
@@ -699,25 +699,25 @@
         <v>7803</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>37.05</v>
+        <v>37.03</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>8707767692.280001</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>26.47</v>
+        <v>26.42</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>3405144473.64</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>46.59</v>
+        <v>46.31</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>2300421308.43</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>44.94</v>
+        <v>44.67</v>
       </c>
     </row>
     <row r="10">
@@ -727,28 +727,28 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1755573651.78</v>
+        <v>1774582066.62</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.34</v>
+        <v>5.38</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>764441395.64</v>
+        <v>807767933.9299999</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>10.46</v>
+        <v>10.99</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>622010881.96</v>
+        <v>653491781.3200001</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>12.15</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="11">
@@ -767,19 +767,19 @@
         <v>1223996865.97</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>777520950.2900001</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>10.64</v>
+        <v>10.57</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>587347887.3099999</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>11.47</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="12">
@@ -798,19 +798,19 @@
         <v>2079741446.05</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>6.32</v>
+        <v>6.31</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>519238923.51</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>7.1</v>
+        <v>7.06</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>389674253.59</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>7.61</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="13">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>791514463.25</v>
+        <v>834903841.25</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>0</v>
@@ -882,25 +882,25 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>21061</v>
+        <v>21073</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>32898582945.04</v>
+        <v>32960980737.88</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7309285444.219999</v>
+        <v>7352611982.51</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>100</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>5118589033.88</v>
+        <v>5150069933.24</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>100</v>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 15:05:24.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 15:05:24.</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21013</v>
+        <v>21017</v>
       </c>
     </row>
     <row r="14">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21013</v>
+        <v>21017</v>
       </c>
     </row>
     <row r="16">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21058</v>
+        <v>21070</v>
       </c>
     </row>
     <row r="19">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>295</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>56603</v>
+        <v>56604</v>
       </c>
     </row>
     <row r="48">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="50">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-15 09:44:30</t>
+          <t>2026-10-15 15:05:24</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-724835644.71</v>
+        <v>-768162183</v>
       </c>
     </row>
     <row r="65">
@@ -1772,7 +1772,7 @@
         <v>1226983360</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>4</v>
@@ -1914,7 +1914,7 @@
         <v>650405604.49</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>15</v>
@@ -2073,7 +2073,7 @@
         <v>7713744.35</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>678014</v>
@@ -2085,7 +2085,7 @@
         <v>1000000</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="R9" s="6" t="n">
         <v>3000000</v>
@@ -2127,7 +2127,7 @@
         <v>548600000</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>3</v>
@@ -2269,7 +2269,7 @@
         <v>495224296</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>7</v>
@@ -2482,7 +2482,7 @@
         <v>478688485.93</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>58</v>
@@ -2553,7 +2553,7 @@
         <v>400000000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>3</v>
@@ -3008,7 +3008,7 @@
         <v>1744850.78</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="R22" s="6" t="n">
         <v>1230953.08</v>
@@ -3221,7 +3221,7 @@
         <v>4300000</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="R25" s="6" t="n">
         <v>500000</v>
@@ -4044,7 +4044,7 @@
         <v>107108276.43</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>22</v>
@@ -4186,7 +4186,7 @@
         <v>103733556.02</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>146</v>
@@ -4647,7 +4647,7 @@
         <v>16008194.03</v>
       </c>
       <c r="S45" s="6" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="46">
@@ -5251,7 +5251,7 @@
         <v>67500000</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="I54" s="5" t="n">
         <v>5</v>
@@ -5606,7 +5606,7 @@
         <v>64220956.82</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="I59" s="5" t="n">
         <v>35</v>
@@ -6274,7 +6274,7 @@
         <v>611286.47</v>
       </c>
       <c r="Q68" s="6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="R68" s="6" t="n">
         <v>800000</v>
@@ -6558,7 +6558,7 @@
         <v>1499763</v>
       </c>
       <c r="Q72" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="R72" s="6" t="n">
         <v>0</v>
@@ -6600,7 +6600,7 @@
         <v>51000000</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="I73" s="5" t="n">
         <v>8</v>
@@ -7339,7 +7339,7 @@
         <v>2396323.01</v>
       </c>
       <c r="Q83" s="6" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="R83" s="6" t="n">
         <v>0</v>
@@ -8049,7 +8049,7 @@
         <v>95000</v>
       </c>
       <c r="Q93" s="6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="R93" s="6" t="n">
         <v>2507629.39</v>
@@ -8659,7 +8659,7 @@
         <v>44497052.1</v>
       </c>
       <c r="H102" s="6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I102" s="5" t="n">
         <v>45</v>
@@ -8842,7 +8842,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 15:05:24.</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9038,7 @@
         <v>281516195.39</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>274070810.41</v>
@@ -9103,7 +9103,7 @@
         <v>99805530.3</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>98296574.61</v>
@@ -9168,7 +9168,7 @@
         <v>31000000</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>15000000</v>
@@ -10273,7 +10273,7 @@
         <v>5400000</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>3600000</v>
@@ -10468,7 +10468,7 @@
         <v>4866473.9</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>3925144.9</v>
@@ -12483,7 +12483,7 @@
         <v>3345250.5</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L58" s="6" t="n">
         <v>2472030</v>
@@ -12548,7 +12548,7 @@
         <v>3343294.16</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L59" s="6" t="n">
         <v>2233258.46</v>
@@ -12613,7 +12613,7 @@
         <v>3334759.25</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L60" s="6" t="n">
         <v>2131410</v>
@@ -15408,7 +15408,7 @@
         <v>2304363.37</v>
       </c>
       <c r="K103" s="6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="L103" s="6" t="n">
         <v>1820773.33</v>
@@ -15495,7 +15495,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 15:05:24.</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 15:05:24.</t>
         </is>
       </c>
     </row>
@@ -17316,7 +17316,7 @@
         <v>941863602.37</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>12.89</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="6">
@@ -17339,7 +17339,7 @@
         <v>777520950.29</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>10.64</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="7">
@@ -17362,7 +17362,7 @@
         <v>540734381.52</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>7.4</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="8">
@@ -17385,7 +17385,7 @@
         <v>501949079.58</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>6.87</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="9">
@@ -17408,7 +17408,7 @@
         <v>348809893.96</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="10">
@@ -17431,7 +17431,7 @@
         <v>348269323.09</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>4.76</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="11">
@@ -17454,7 +17454,7 @@
         <v>320180921.52</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="12">
@@ -17477,7 +17477,7 @@
         <v>260758408.08</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="13">
@@ -17500,7 +17500,7 @@
         <v>248829183.34</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="14">
@@ -17523,7 +17523,7 @@
         <v>233931458.5</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="15">
@@ -17546,7 +17546,7 @@
         <v>224083484.48</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="16">
@@ -17569,7 +17569,7 @@
         <v>217166956.08</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="17">
@@ -17592,7 +17592,7 @@
         <v>206920736.24</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="18">
@@ -17615,7 +17615,7 @@
         <v>192361636.49</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="19">
@@ -17638,7 +17638,7 @@
         <v>189655533.43</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="20">
@@ -17661,7 +17661,7 @@
         <v>176872010.23</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="21">
@@ -17672,19 +17672,19 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>163121695.8</v>
+        <v>164723028.18</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="22">
@@ -17695,19 +17695,19 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Paraíba</t>
+          <t>Mato Grosso</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>149765818.85</v>
+        <v>163121695.8</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="23">
@@ -17718,19 +17718,19 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>147279582.87</v>
+        <v>149765818.85</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="24">
@@ -17741,19 +17741,19 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>145500892.28</v>
+        <v>147279582.87</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -17764,19 +17764,19 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Norte</t>
+          <t>Piauí</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>136913290.09</v>
+        <v>145500892.28</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="26">
@@ -17787,19 +17787,19 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Acre</t>
+          <t>Rio Grande do Norte</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>134882233.11</v>
+        <v>136913290.09</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="27">
@@ -17810,19 +17810,19 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Acre</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>123217657.01</v>
+        <v>134882233.11</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="28">
@@ -17833,19 +17833,19 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>121396489.89</v>
+        <v>123217657.01</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="29">
@@ -17868,7 +17868,7 @@
         <v>118199043.81</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="30">
@@ -17891,7 +17891,7 @@
         <v>116947052.84</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="31">
@@ -17914,7 +17914,7 @@
         <v>116160099.96</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="32">
@@ -17937,7 +17937,7 @@
         <v>105994028.51</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="33">
@@ -17960,7 +17960,7 @@
         <v>148152716.75</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>23.44</v>
+        <v>22.93</v>
       </c>
     </row>
     <row r="34">
@@ -17983,7 +17983,7 @@
         <v>63540943.62</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>10.05</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="35">
@@ -18006,7 +18006,7 @@
         <v>35779143.44</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>5.66</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="36">
@@ -18029,7 +18029,7 @@
         <v>32389921.59</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>5.12</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="37">
@@ -18052,7 +18052,7 @@
         <v>30508223.61</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>4.83</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="38">
@@ -18063,19 +18063,19 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Rio de Janeiro</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>27996415.41</v>
+        <v>28980195.23</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>4.43</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="39">
@@ -18086,19 +18086,19 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Rio de Janeiro</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>22120475.07</v>
+        <v>27996415.41</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="40">
@@ -18109,19 +18109,19 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Pernambuco</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>21168199.92</v>
+        <v>22120475.07</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="41">
@@ -18132,19 +18132,19 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Sul</t>
+          <t>Pernambuco</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>18088163.75</v>
+        <v>21168199.92</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>2.86</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="42">
@@ -18155,19 +18155,19 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Santa Catarina</t>
+          <t>Rio Grande do Sul</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>17842960.01</v>
+        <v>18088163.75</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="43">
@@ -18178,19 +18178,19 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Espírito Santo</t>
+          <t>Santa Catarina</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>17644336</v>
+        <v>17842960.01</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="44">
@@ -18201,19 +18201,19 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Espírito Santo</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>17151108.64</v>
+        <v>17644336</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="45">
@@ -18224,19 +18224,19 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>16469200.1</v>
+        <v>17151108.64</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="46">
@@ -18247,19 +18247,19 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Acre</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>15904796.74</v>
+        <v>16469200.1</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="47">
@@ -18270,19 +18270,19 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Acre</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>15345139.27</v>
+        <v>15904796.74</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="48">
@@ -18293,19 +18293,19 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Piauí</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>14904755.93</v>
+        <v>15345139.27</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="49">
@@ -18328,7 +18328,7 @@
         <v>14693216.87</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="50">
@@ -18351,7 +18351,7 @@
         <v>12945672.35</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -18374,7 +18374,7 @@
         <v>12136324.21</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="52">
@@ -18397,7 +18397,7 @@
         <v>11715177.76</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="53">
@@ -18420,7 +18420,7 @@
         <v>10741115.61</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="54">
@@ -18443,7 +18443,7 @@
         <v>10241492.54</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="55">
@@ -18466,7 +18466,7 @@
         <v>8226531.29</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="56">
@@ -18489,7 +18489,7 @@
         <v>7868672.31</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="57">
@@ -18512,7 +18512,7 @@
         <v>7668205.73</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="58">
@@ -18535,7 +18535,7 @@
         <v>7286528.8</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="59">
@@ -18558,7 +18558,7 @@
         <v>6936280.45</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="60">
@@ -18581,7 +18581,7 @@
         <v>6559838.31</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="61">
@@ -18604,7 +18604,7 @@
         <v>622281029.6</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>11.48</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="62">
@@ -18627,7 +18627,7 @@
         <v>613298902.3</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>11.31</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="63">
@@ -18650,7 +18650,7 @@
         <v>412265001.24</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>7.61</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="64">
@@ -18673,7 +18673,7 @@
         <v>375702323.79</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>6.93</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="65">
@@ -18696,7 +18696,7 @@
         <v>282920761.37</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>5.22</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="66">
@@ -18719,7 +18719,7 @@
         <v>248720457.06</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="67">
@@ -18742,7 +18742,7 @@
         <v>238190400.29</v>
       </c>
       <c r="E67" s="12" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="68">
@@ -18765,7 +18765,7 @@
         <v>199545419.32</v>
       </c>
       <c r="E68" s="12" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="69">
@@ -18788,7 +18788,7 @@
         <v>183040826.39</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="70">
@@ -18811,7 +18811,7 @@
         <v>173113239.83</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="71">
@@ -18834,7 +18834,7 @@
         <v>164218808.19</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="72">
@@ -18857,7 +18857,7 @@
         <v>154899399.83</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="73">
@@ -18880,7 +18880,7 @@
         <v>151175278.8</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="74">
@@ -18903,7 +18903,7 @@
         <v>145738001.5</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="75">
@@ -18926,7 +18926,7 @@
         <v>134563486.7</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="76">
@@ -18949,7 +18949,7 @@
         <v>127872892.47</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="77">
@@ -18972,7 +18972,7 @@
         <v>122216962.45</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="78">
@@ -18983,19 +18983,19 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Acre</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>108586825.06</v>
+        <v>110836787.34</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="79">
@@ -19006,16 +19006,16 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Rio Grande do Norte</t>
+          <t>Acre</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>107735283.55</v>
+        <v>108586825.06</v>
       </c>
       <c r="E79" s="12" t="n">
         <v>1.99</v>
@@ -19029,19 +19029,19 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Rondônia</t>
+          <t>Rio Grande do Norte</t>
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>106467480.73</v>
+        <v>107735283.55</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="81">
@@ -19052,19 +19052,19 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Piauí</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>104059277.83</v>
+        <v>106467480.73</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="82">
@@ -19075,19 +19075,19 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Piauí</t>
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>97316118.98</v>
+        <v>104059277.83</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="83">
@@ -19098,19 +19098,19 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Amapá</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>96676722.64</v>
+        <v>97316118.98</v>
       </c>
       <c r="E83" s="12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="84">
@@ -19121,16 +19121,16 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Alagoas</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>96310229.08</v>
+        <v>96676722.64</v>
       </c>
       <c r="E84" s="12" t="n">
         <v>1.78</v>
@@ -19144,19 +19144,19 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Roraima</t>
+          <t>Alagoas</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>92302455.93000001</v>
+        <v>96310229.08</v>
       </c>
       <c r="E85" s="12" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="86">
@@ -19167,19 +19167,19 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso</t>
+          <t>Roraima</t>
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>88414512.84999999</v>
+        <v>92302455.93000001</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="87">
@@ -19190,16 +19190,16 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Mato Grosso do Sul</t>
+          <t>Mato Grosso</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>88057920.31999999</v>
+        <v>88414512.84999999</v>
       </c>
       <c r="E87" s="12" t="n">
         <v>1.62</v>
@@ -19213,19 +19213,19 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Mato Grosso do Sul</t>
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>84766787.34</v>
+        <v>88057920.31999999</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="89">
@@ -19521,7 +19521,7 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>87718083.37</v>
+        <v>87723073.27</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>2.76</v>
@@ -20536,7 +20536,7 @@
         <v>97718685.43000001</v>
       </c>
       <c r="E145" s="12" t="n">
-        <v>13.69</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="146">
@@ -20559,7 +20559,7 @@
         <v>80313354.70999999</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>11.25</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="147">
@@ -20582,7 +20582,7 @@
         <v>53079939.7</v>
       </c>
       <c r="E147" s="12" t="n">
-        <v>7.44</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="148">
@@ -20651,7 +20651,7 @@
         <v>37050385.8</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="151">
@@ -20697,7 +20697,7 @@
         <v>35024163.86</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>4.91</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="153">
@@ -20835,7 +20835,7 @@
         <v>21242788.55</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="159">
@@ -20858,7 +20858,7 @@
         <v>20466197.66</v>
       </c>
       <c r="E159" s="12" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="160">
@@ -20970,10 +20970,10 @@
         </is>
       </c>
       <c r="D164" s="6" t="n">
-        <v>9976101.710000001</v>
+        <v>10803801.71</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="165">
@@ -21019,7 +21019,7 @@
         <v>9749891.75</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="167">
@@ -21042,7 +21042,7 @@
         <v>8182957.14</v>
       </c>
       <c r="E167" s="12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="168">
@@ -21088,7 +21088,7 @@
         <v>6891650.26</v>
       </c>
       <c r="E169" s="12" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="170">
@@ -21180,7 +21180,7 @@
         <v>2630</v>
       </c>
       <c r="E173" s="12" t="n">
-        <v>12.49</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="174">
@@ -21203,7 +21203,7 @@
         <v>2055</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="175">
@@ -21226,7 +21226,7 @@
         <v>1832</v>
       </c>
       <c r="E175" s="12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="176">
@@ -21272,7 +21272,7 @@
         <v>1090</v>
       </c>
       <c r="E177" s="12" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="178">
@@ -21706,10 +21706,10 @@
         </is>
       </c>
       <c r="D196" s="6" t="n">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="E196" s="12" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="197">
@@ -22451,7 +22451,7 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 15:05:24.</t>
         </is>
       </c>
     </row>
@@ -23777,7 +23777,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 09:44:30.</t>
+          <t>Fonte: Brasil. Tribunal Superior Eleitoral. Dados abertos eleitorais, Eleicoes Gerais de 2026. Disponivel em: https://dadosabertos.tse.jus.br. Extracao de 2026-10-15 15:05:24.</t>
         </is>
       </c>
     </row>
@@ -23940,19 +23940,19 @@
         <v>1413776054.28</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>19.34</v>
+        <v>19.23</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1024813021.59</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>18.91</v>
+        <v>18.82</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>151203289.93</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>23.92</v>
+        <v>23.4</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>22416742.52</v>
@@ -23986,19 +23986,19 @@
         <v>1060582328.58</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>14.51</v>
+        <v>14.42</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>922036459.12</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>17.01</v>
+        <v>16.93</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>6176134.65</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>12304578.6</v>
@@ -24020,43 +24020,43 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1819943318.34</v>
+        <v>1827001539.18</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>669850325.22</v>
+        <v>696999939.51</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>9.16</v>
+        <v>9.48</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>536659271.9</v>
+        <v>550159271.9</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>75858680.52</v>
+        <v>88792469.81999999</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>12</v>
+        <v>13.74</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>8281262.19</v>
+        <v>8381262.18</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>29808686.9</v>
+        <v>30288686.9</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>475884693.06</v>
+        <v>495138295.62</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>91.44</v>
+        <v>91.67</v>
       </c>
     </row>
     <row r="8">
@@ -24078,19 +24078,19 @@
         <v>656146458.72</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>8.98</v>
+        <v>8.92</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>448681803.71</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>8.279999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>34632737.02</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>5.48</v>
+        <v>5.36</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>19103480.73</v>
@@ -24112,10 +24112,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>6.27</v>
+        <v>6.28</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>2779509683.8</v>
@@ -24124,19 +24124,19 @@
         <v>606632208.83</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>371047010.25</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>6.85</v>
+        <v>6.81</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>126722570.76</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>20.05</v>
+        <v>19.61</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>11984849.21</v>
@@ -24170,19 +24170,19 @@
         <v>576844006.83</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7.89</v>
+        <v>7.85</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>446516289.17</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>8.24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>74245455</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>11.75</v>
+        <v>11.49</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>8163972.08</v>
@@ -24204,31 +24204,31 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3431895006.71</v>
+        <v>3475284384.71</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>538110397.7</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>7.36</v>
+        <v>7.32</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>407807248.96</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>7.52</v>
+        <v>7.49</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>17656542.34</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>15114290.24</v>
@@ -24262,19 +24262,19 @@
         <v>296602895.22</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>238186413.63</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>5685501.33</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>10352171.45</v>
@@ -24299,7 +24299,7 @@
         <v>1126</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>5.35</v>
+        <v>5.34</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>1457794419.27</v>
@@ -24308,19 +2